--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,127 +40,163 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AKTIF </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUPAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
     <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -511,7 +547,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I42"/>
+  <x:dimension ref="A1:I54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -548,28 +584,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>294713</x:v>
+        <x:v>12662901</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>17182</x:v>
+        <x:v>9318155</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5200000000005</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>311895</x:v>
+        <x:v>21981056</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>38.3053274611475</x:v>
+        <x:v>33.5692946913826</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>277531</x:v>
+        <x:v>3344746</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999982</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -577,28 +613,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>43005</x:v>
+        <x:v>1206456</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>789</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>43794</x:v>
+        <x:v>1206456</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>5.37855211155516</x:v>
+        <x:v>1.8424900512599</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>42216</x:v>
+        <x:v>1206456</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -606,28 +642,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>43098</x:v>
+        <x:v>808681</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>949</x:v>
+        <x:v>7688</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>44047</x:v>
+        <x:v>816369</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>5.40962426034776</x:v>
+        <x:v>1.24675227331705</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>42149</x:v>
+        <x:v>800993</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -635,28 +671,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>26301</x:v>
+        <x:v>666707</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1339</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>27640</x:v>
+        <x:v>666809</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>3.39460155188803</x:v>
+        <x:v>1.01834542543662</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>24962</x:v>
+        <x:v>666605</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -664,28 +700,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>0</x:v>
+        <x:v>1253920</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1</x:v>
+        <x:v>666645</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5200000000014</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1</x:v>
+        <x:v>1920565</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.000122814817362085</x:v>
+        <x:v>2.93307166220564</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>-1</x:v>
+        <x:v>587275</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999981</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -693,28 +729,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
+        <x:v>515446</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C7" s="0">
+      <x:c r="E7" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E7" s="0">
-        <x:v>23.2000007629395</x:v>
-      </x:c>
       <x:c r="F7" s="0">
-        <x:v>5</x:v>
+        <x:v>515446</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.000614074086810426</x:v>
+        <x:v>0.78718505023118</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>-5</x:v>
+        <x:v>515446</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -722,28 +758,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>0</x:v>
+        <x:v>1030858</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>10</x:v>
+        <x:v>758925</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>10</x:v>
+        <x:v>1789783</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.00122814817362085</x:v>
+        <x:v>2.73334242725312</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>-10</x:v>
+        <x:v>271933</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5200000000002</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -751,28 +787,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>0</x:v>
+        <x:v>287548</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5199999999998</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>87</x:v>
+        <x:v>27849</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>87</x:v>
+        <x:v>315397</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.0106848891105014</x:v>
+        <x:v>0.481671801290074</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>-87</x:v>
+        <x:v>259699</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999997</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -780,28 +816,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>0</x:v>
+        <x:v>603088</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>130</x:v>
+        <x:v>348674</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5200000000002</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>130</x:v>
+        <x:v>951762</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.0159659262570711</x:v>
+        <x:v>1.45352339096264</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-130</x:v>
+        <x:v>254414</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999995</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -809,28 +845,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>0</x:v>
+        <x:v>291622</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>145</x:v>
+        <x:v>52286</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>145</x:v>
+        <x:v>343908</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.0178081485175023</x:v>
+        <x:v>0.525213574758374</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>-145</x:v>
+        <x:v>239336</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -838,28 +874,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>0</x:v>
+        <x:v>2087951</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5199999999991</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>145</x:v>
+        <x:v>1881846</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>145</x:v>
+        <x:v>3969797</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0178081485175023</x:v>
+        <x:v>6.06264254810899</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-145</x:v>
+        <x:v>206105</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999912</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -867,28 +903,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>0</x:v>
+        <x:v>365912</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>145</x:v>
+        <x:v>250951</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>145</x:v>
+        <x:v>616863</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0178081485175023</x:v>
+        <x:v>0.942068289676817</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-145</x:v>
+        <x:v>114961</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999997</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -896,28 +932,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>0</x:v>
+        <x:v>224856</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>160</x:v>
+        <x:v>120296</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999997</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>160</x:v>
+        <x:v>345152</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0196503707779336</x:v>
+        <x:v>0.527113401709184</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-160</x:v>
+        <x:v>104560</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5200000000003</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -925,28 +961,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>0</x:v>
+        <x:v>317418</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>195</x:v>
+        <x:v>225495</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>195</x:v>
+        <x:v>542913</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0239488893856066</x:v>
+        <x:v>0.829132435165198</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-195</x:v>
+        <x:v>91923</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5200000000002</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -954,28 +990,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>0</x:v>
+        <x:v>192920</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>215</x:v>
+        <x:v>111493</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999997</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>215</x:v>
+        <x:v>304413</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0264051857328483</x:v>
+        <x:v>0.464897123454298</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-215</x:v>
+        <x:v>81427</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5200000000004</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -983,28 +1019,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>0</x:v>
+        <x:v>134491</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>285</x:v>
+        <x:v>61971</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999998</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>285</x:v>
+        <x:v>196462</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0350022229481942</x:v>
+        <x:v>0.300035210940658</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-285</x:v>
+        <x:v>72520</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5200000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1012,28 +1048,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>0</x:v>
+        <x:v>535220</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5199999999998</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>295</x:v>
+        <x:v>465194</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5200000000004</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>295</x:v>
+        <x:v>1000414</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0362303711218151</x:v>
+        <x:v>1.5278243401675</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-295</x:v>
+        <x:v>70026</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999964</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1041,28 +1077,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>0</x:v>
+        <x:v>91912</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>424</x:v>
+        <x:v>32391</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>424</x:v>
+        <x:v>124303</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0520734825615241</x:v>
+        <x:v>0.189834557449057</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-424</x:v>
+        <x:v>59521</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1070,28 +1106,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>0</x:v>
+        <x:v>539312</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>617</x:v>
+        <x:v>481491</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>617</x:v>
+        <x:v>1020803</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0757767423124065</x:v>
+        <x:v>1.55896225954055</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-617</x:v>
+        <x:v>57821</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999991</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1099,28 +1135,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>0</x:v>
+        <x:v>83493</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>821</x:v>
+        <x:v>25975</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>821</x:v>
+        <x:v>109468</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.100830965054272</x:v>
+        <x:v>0.167178662903014</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-821</x:v>
+        <x:v>57518</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1128,28 +1164,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>0</x:v>
+        <x:v>754248</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5200000000006</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>1155</x:v>
+        <x:v>707052</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1155</x:v>
+        <x:v>1461300</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.141851114053208</x:v>
+        <x:v>2.23168579036955</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-1155</x:v>
+        <x:v>47196</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5200000000106</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1157,28 +1193,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>0</x:v>
+        <x:v>40591</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1230</x:v>
+        <x:v>10443</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1230</x:v>
+        <x:v>51034</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.151062225355365</x:v>
+        <x:v>0.0779387207457194</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-1230</x:v>
+        <x:v>30148</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1186,28 +1222,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>0</x:v>
+        <x:v>29728</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>1261</x:v>
+        <x:v>5798</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1261</x:v>
+        <x:v>35526</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.154869484693589</x:v>
+        <x:v>0.0542550259280563</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-1261</x:v>
+        <x:v>23930</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1215,28 +1251,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>0</x:v>
+        <x:v>20185</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>1503</x:v>
+        <x:v>6823</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1503</x:v>
+        <x:v>27008</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.184590670495214</x:v>
+        <x:v>0.0412464037680838</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-1503</x:v>
+        <x:v>13362</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1244,28 +1280,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>0</x:v>
+        <x:v>32382</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1814</x:v>
+        <x:v>19977</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1814</x:v>
+        <x:v>52359</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.222786078694822</x:v>
+        <x:v>0.0799622502552244</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1814</x:v>
+        <x:v>12405</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1273,28 +1309,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>0</x:v>
+        <x:v>15006</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>2324</x:v>
+        <x:v>3336</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>2324</x:v>
+        <x:v>18342</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.285421635549486</x:v>
+        <x:v>0.0280117571798798</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-2324</x:v>
+        <x:v>11670</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1302,28 +1338,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>350431</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>3084</x:v>
+        <x:v>342381</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>3084</x:v>
+        <x:v>692812</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.37876089674467</x:v>
+        <x:v>1.05805700116164</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-3084</x:v>
+        <x:v>8050</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999972</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1331,28 +1367,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>0</x:v>
+        <x:v>7811</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>4319</x:v>
+        <x:v>2155</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4319</x:v>
+        <x:v>9966</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.530437196186846</x:v>
+        <x:v>0.0152199962956429</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4319</x:v>
+        <x:v>5656</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1360,28 +1396,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>0</x:v>
+        <x:v>4103</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>4681</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4681</x:v>
+        <x:v>4821</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.57489616007192</x:v>
+        <x:v>0.00736259303043291</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-4681</x:v>
+        <x:v>3385</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1389,28 +1425,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
+        <x:v>2501</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="D31" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C31" s="0">
+      <x:c r="E31" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D31" s="0">
-        <x:v>4730</x:v>
-      </x:c>
-      <x:c r="E31" s="0">
-        <x:v>23.2000007629395</x:v>
-      </x:c>
       <x:c r="F31" s="0">
-        <x:v>4730</x:v>
+        <x:v>2501</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.580914086122663</x:v>
+        <x:v>0.00381950739869585</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-4730</x:v>
+        <x:v>2501</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1418,28 +1454,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>0</x:v>
+        <x:v>19074</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>6214</x:v>
+        <x:v>18221</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>6214</x:v>
+        <x:v>37295</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.763171275087997</x:v>
+        <x:v>0.0569566287222558</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-6214</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999995</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1447,28 +1483,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>0</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>6384</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>6384</x:v>
+        <x:v>1452</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.784049794039551</x:v>
+        <x:v>0.00221748290400095</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-6384</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1476,28 +1512,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>0</x:v>
+        <x:v>1350</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>8589</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>8589</x:v>
+        <x:v>2332</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.05485646632295</x:v>
+        <x:v>0.0035614119367288</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-8589</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1505,28 +1541,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="D35" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C35" s="0">
+      <x:c r="E35" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D35" s="0">
-        <x:v>10795</x:v>
-      </x:c>
-      <x:c r="E35" s="0">
-        <x:v>23.2000007629395</x:v>
-      </x:c>
       <x:c r="F35" s="0">
-        <x:v>10795</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>1.32578595342371</x:v>
+        <x:v>0.000306965608611702</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-10795</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1534,28 +1570,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>0</x:v>
+        <x:v>188337</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5199999999999</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>10972</x:v>
+        <x:v>188227</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>10972</x:v>
+        <x:v>376564</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>1.3475241760968</x:v>
+        <x:v>0.575085559409238</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-10972</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.5199999999086</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1563,28 +1599,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="D37" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C37" s="0">
+      <x:c r="E37" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D37" s="0">
-        <x:v>29038</x:v>
-      </x:c>
-      <x:c r="E37" s="0">
-        <x:v>23.2000007629395</x:v>
-      </x:c>
       <x:c r="F37" s="0">
-        <x:v>29038</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>3.56629666656023</x:v>
+        <x:v>6.10876833058113E-05</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-29038</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1592,28 +1628,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="D38" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C38" s="0">
+      <x:c r="E38" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D38" s="0">
-        <x:v>38088</x:v>
-      </x:c>
-      <x:c r="E38" s="0">
-        <x:v>23.2000007629395</x:v>
-      </x:c>
       <x:c r="F38" s="0">
-        <x:v>38088</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>4.6777707636871</x:v>
+        <x:v>1.52719208264528E-06</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-38088</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1627,22 +1663,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>47770</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>47770</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>5.8668638253868</x:v>
+        <x:v>0.00029474807195054</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-47770</x:v>
+        <x:v>-193</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1650,28 +1686,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>47780</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>47780</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>5.86809197356043</x:v>
+        <x:v>0.000465793585206811</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-47780</x:v>
+        <x:v>-303</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1679,28 +1715,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>0</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>62845</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>62845</x:v>
+        <x:v>913</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>7.71829719712024</x:v>
+        <x:v>0.00139432637145514</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-62845</x:v>
+        <x:v>-823</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1708,28 +1744,376 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>0</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>0</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>88602</x:v>
+        <x:v>1651</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>88602</x:v>
+        <x:v>2332</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>10.8816384479155</x:v>
+        <x:v>0.0035614119367288</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-88602</x:v>
+        <x:v>-970</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>23.2000007629395</x:v>
+        <x:v>25.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:9">
+      <x:c r="A43" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B43" s="0">
+        <x:v>672758</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>25.5199999999998</x:v>
+      </x:c>
+      <x:c r="D43" s="0">
+        <x:v>675155</x:v>
+      </x:c>
+      <x:c r="E43" s="0">
+        <x:v>25.5200000000013</x:v>
+      </x:c>
+      <x:c r="F43" s="0">
+        <x:v>1347913</x:v>
+      </x:c>
+      <x:c r="G43" s="0">
+        <x:v>2.05852206169465</x:v>
+      </x:c>
+      <x:c r="H43" s="0">
+        <x:v>-2397</x:v>
+      </x:c>
+      <x:c r="I43" s="0">
+        <x:v>25.5200000004046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
+      <x:c r="A44" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>5426</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="D44" s="0">
+        <x:v>7911</x:v>
+      </x:c>
+      <x:c r="E44" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="F44" s="0">
+        <x:v>13337</x:v>
+      </x:c>
+      <x:c r="G44" s="0">
+        <x:v>0.0203681608062401</x:v>
+      </x:c>
+      <x:c r="H44" s="0">
+        <x:v>-2485</x:v>
+      </x:c>
+      <x:c r="I44" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
+      <x:c r="A45" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B45" s="0">
+        <x:v>409667</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>25.5200000000004</x:v>
+      </x:c>
+      <x:c r="D45" s="0">
+        <x:v>412220</x:v>
+      </x:c>
+      <x:c r="E45" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="F45" s="0">
+        <x:v>821887</x:v>
+      </x:c>
+      <x:c r="G45" s="0">
+        <x:v>1.25517931922908</x:v>
+      </x:c>
+      <x:c r="H45" s="0">
+        <x:v>-2553</x:v>
+      </x:c>
+      <x:c r="I45" s="0">
+        <x:v>25.5199999999309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:9">
+      <x:c r="A46" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B46" s="0">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="D46" s="0">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="E46" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="F46" s="0">
+        <x:v>5361</x:v>
+      </x:c>
+      <x:c r="G46" s="0">
+        <x:v>0.00818727675506136</x:v>
+      </x:c>
+      <x:c r="H46" s="0">
+        <x:v>-4639</x:v>
+      </x:c>
+      <x:c r="I46" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
+      <x:c r="A47" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B47" s="0">
+        <x:v>153958</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>25.5199999999997</x:v>
+      </x:c>
+      <x:c r="D47" s="0">
+        <x:v>358876</x:v>
+      </x:c>
+      <x:c r="E47" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="F47" s="0">
+        <x:v>512834</x:v>
+      </x:c>
+      <x:c r="G47" s="0">
+        <x:v>0.783196024511311</x:v>
+      </x:c>
+      <x:c r="H47" s="0">
+        <x:v>-204918</x:v>
+      </x:c>
+      <x:c r="I47" s="0">
+        <x:v>25.5200000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
+      <x:c r="A48" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B48" s="0">
+        <x:v>723994</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>25.5199999999999</x:v>
+      </x:c>
+      <x:c r="D48" s="0">
+        <x:v>1007947</x:v>
+      </x:c>
+      <x:c r="E48" s="0">
+        <x:v>25.5199999999987</x:v>
+      </x:c>
+      <x:c r="F48" s="0">
+        <x:v>1731941</x:v>
+      </x:c>
+      <x:c r="G48" s="0">
+        <x:v>2.64500658280875</x:v>
+      </x:c>
+      <x:c r="H48" s="0">
+        <x:v>-283953</x:v>
+      </x:c>
+      <x:c r="I48" s="0">
+        <x:v>25.5199999999958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
+      <x:c r="A49" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B49" s="0">
+        <x:v>1242126</x:v>
+      </x:c>
+      <x:c r="C49" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="D49" s="0">
+        <x:v>1578952</x:v>
+      </x:c>
+      <x:c r="E49" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="F49" s="0">
+        <x:v>2821078</x:v>
+      </x:c>
+      <x:c r="G49" s="0">
+        <x:v>4.30832798612479</x:v>
+      </x:c>
+      <x:c r="H49" s="0">
+        <x:v>-336826</x:v>
+      </x:c>
+      <x:c r="I49" s="0">
+        <x:v>25.5199999999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
+      <x:c r="A50" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B50" s="0">
+        <x:v>1034629</x:v>
+      </x:c>
+      <x:c r="C50" s="0">
+        <x:v>25.5199999999998</x:v>
+      </x:c>
+      <x:c r="D50" s="0">
+        <x:v>1482325</x:v>
+      </x:c>
+      <x:c r="E50" s="0">
+        <x:v>25.5199999999982</x:v>
+      </x:c>
+      <x:c r="F50" s="0">
+        <x:v>2516954</x:v>
+      </x:c>
+      <x:c r="G50" s="0">
+        <x:v>3.84387222118237</x:v>
+      </x:c>
+      <x:c r="H50" s="0">
+        <x:v>-447696</x:v>
+      </x:c>
+      <x:c r="I50" s="0">
+        <x:v>25.5199999999944</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
+      <x:c r="A51" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B51" s="0">
+        <x:v>1057124</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>25.5200000000004</x:v>
+      </x:c>
+      <x:c r="D51" s="0">
+        <x:v>2061642</x:v>
+      </x:c>
+      <x:c r="E51" s="0">
+        <x:v>25.5200000000004</x:v>
+      </x:c>
+      <x:c r="F51" s="0">
+        <x:v>3118766</x:v>
+      </x:c>
+      <x:c r="G51" s="0">
+        <x:v>4.7629547428233</x:v>
+      </x:c>
+      <x:c r="H51" s="0">
+        <x:v>-1004518</x:v>
+      </x:c>
+      <x:c r="I51" s="0">
+        <x:v>25.5200000000003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
+      <x:c r="A52" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B52" s="0">
+        <x:v>7531</x:v>
+      </x:c>
+      <x:c r="C52" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="D52" s="0">
+        <x:v>1506677</x:v>
+      </x:c>
+      <x:c r="E52" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="F52" s="0">
+        <x:v>1514208</x:v>
+      </x:c>
+      <x:c r="G52" s="0">
+        <x:v>2.31248646907815</x:v>
+      </x:c>
+      <x:c r="H52" s="0">
+        <x:v>-1499146</x:v>
+      </x:c>
+      <x:c r="I52" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:9">
+      <x:c r="A53" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B53" s="0">
+        <x:v>104341</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="D53" s="0">
+        <x:v>1954315</x:v>
+      </x:c>
+      <x:c r="E53" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+      <x:c r="F53" s="0">
+        <x:v>2058656</x:v>
+      </x:c>
+      <x:c r="G53" s="0">
+        <x:v>3.14396314409021</x:v>
+      </x:c>
+      <x:c r="H53" s="0">
+        <x:v>-1849974</x:v>
+      </x:c>
+      <x:c r="I53" s="0">
+        <x:v>25.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:9">
+      <x:c r="A54" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B54" s="0">
+        <x:v>1959443</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>25.5200000000003</x:v>
+      </x:c>
+      <x:c r="D54" s="0">
+        <x:v>5541834</x:v>
+      </x:c>
+      <x:c r="E54" s="0">
+        <x:v>25.5199999999998</x:v>
+      </x:c>
+      <x:c r="F54" s="0">
+        <x:v>7501277</x:v>
+      </x:c>
+      <x:c r="G54" s="0">
+        <x:v>11.4558908441292</x:v>
+      </x:c>
+      <x:c r="H54" s="0">
+        <x:v>-3582391</x:v>
+      </x:c>
+      <x:c r="I54" s="0">
+        <x:v>25.5199999999996</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,163 +40,163 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUPAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
     <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AKTIF </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUPAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -584,28 +584,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>12662901</x:v>
+        <x:v>1686600</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>25.2587613611924</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>9318155</x:v>
+        <x:v>846982</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>25.5200000000005</x:v>
+        <x:v>25.1095601943819</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>21981056</x:v>
+        <x:v>2533582</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>33.5692946913826</x:v>
+        <x:v>8.6243334696979</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>3344746</x:v>
+        <x:v>839618</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>25.5199999999982</x:v>
+        <x:v>25.4092711199963</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -613,28 +613,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1206456</x:v>
+        <x:v>835909</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.9190876783077</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>0</x:v>
+        <x:v>365048</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>0</x:v>
+        <x:v>24.6851489379382</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1206456</x:v>
+        <x:v>1200957</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>1.8424900512599</x:v>
+        <x:v>4.08806727027899</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1206456</x:v>
+        <x:v>470861</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.1004551504372</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -642,28 +642,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>808681</x:v>
+        <x:v>1799441</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2536610034793</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>7688</x:v>
+        <x:v>1355575</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.7743006287654</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>816369</x:v>
+        <x:v>3155016</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.24675227331705</x:v>
+        <x:v>10.7396997950855</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>800993</x:v>
+        <x:v>443866</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>25.52</x:v>
+        <x:v>26.7176364824591</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -671,28 +671,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>666707</x:v>
+        <x:v>480885</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>25.1908063130564</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>102</x:v>
+        <x:v>77748</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.0117410467308</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>666809</x:v>
+        <x:v>558633</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.01834542543662</x:v>
+        <x:v>1.90159121716911</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>666605</x:v>
+        <x:v>403137</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>25.2253403953319</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -700,28 +700,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>1253920</x:v>
+        <x:v>404903</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>24.8711158757774</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>666645</x:v>
+        <x:v>7775</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>25.5200000000014</x:v>
+        <x:v>25.3623382359839</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1920565</x:v>
+        <x:v>412678</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2.93307166220564</x:v>
+        <x:v>1.4047592253213</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>587275</x:v>
+        <x:v>397128</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>25.5199999999981</x:v>
+        <x:v>24.8614986897552</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -729,28 +729,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>515446</x:v>
+        <x:v>758311</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4188425194174</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>0</x:v>
+        <x:v>542529</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>0</x:v>
+        <x:v>25.4049754201095</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>515446</x:v>
+        <x:v>1300840</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.78718505023118</x:v>
+        <x:v>4.42806980422256</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>515446</x:v>
+        <x:v>215782</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4537078164319</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -758,28 +758,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>1030858</x:v>
+        <x:v>742697</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.9023272854905</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>758925</x:v>
+        <x:v>604338</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.8778562403815</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1789783</x:v>
+        <x:v>1347035</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.73334242725312</x:v>
+        <x:v>4.58531795511434</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>271933</x:v>
+        <x:v>138359</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>25.5200000000002</x:v>
+        <x:v>25.0092143145894</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -787,28 +787,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>287548</x:v>
+        <x:v>219659</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>25.5199999999998</x:v>
+        <x:v>24.8943445012495</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>27849</x:v>
+        <x:v>92257</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.1876322530241</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>315397</x:v>
+        <x:v>311916</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.481671801290074</x:v>
+        <x:v>1.06176456832038</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>259699</x:v>
+        <x:v>127402</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>25.5199999999997</x:v>
+        <x:v>24.6819628422845</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -816,28 +816,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>603088</x:v>
+        <x:v>246676</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>24.6609885099653</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>348674</x:v>
+        <x:v>140882</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>25.5200000000002</x:v>
+        <x:v>24.9128549474699</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>951762</x:v>
+        <x:v>387558</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.45352339096264</x:v>
+        <x:v>1.3192505436371</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>254414</x:v>
+        <x:v>105794</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>25.5199999999995</x:v>
+        <x:v>24.3255871880705</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -845,28 +845,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>291622</x:v>
+        <x:v>273347</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.856635586657</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>52286</x:v>
+        <x:v>167903</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>24.8695949425782</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>343908</x:v>
+        <x:v>441250</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.525213574758374</x:v>
+        <x:v>1.50201854272102</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>239336</x:v>
+        <x:v>105444</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.8359998488507</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -874,28 +874,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2087951</x:v>
+        <x:v>114642</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>25.5199999999991</x:v>
+        <x:v>24.8026240588012</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1881846</x:v>
+        <x:v>11897</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2132453549717</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>3969797</x:v>
+        <x:v>126539</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>6.06264254810899</x:v>
+        <x:v>0.430739771960056</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>206105</x:v>
+        <x:v>102745</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>25.5199999999912</x:v>
+        <x:v>24.7550775936639</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -903,28 +903,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>365912</x:v>
+        <x:v>94500</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>25.154882453979</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>250951</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.3395853805165</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>616863</x:v>
+        <x:v>95513</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.942068289676817</x:v>
+        <x:v>0.325127018857592</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>114961</x:v>
+        <x:v>93487</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>25.5199999999997</x:v>
+        <x:v>25.1528810627205</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -932,28 +932,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>224856</x:v>
+        <x:v>180598</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.3260778827862</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>120296</x:v>
+        <x:v>91843</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>25.5199999999997</x:v>
+        <x:v>25.3864424326821</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>345152</x:v>
+        <x:v>272441</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.527113401709184</x:v>
+        <x:v>0.927391351382337</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>104560</x:v>
+        <x:v>88755</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>25.5200000000003</x:v>
+        <x:v>25.2636131049586</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -961,28 +961,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>317418</x:v>
+        <x:v>130834</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2163523264023</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>225495</x:v>
+        <x:v>45708</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.196327203255</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>542913</x:v>
+        <x:v>176542</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.829132435165198</x:v>
+        <x:v>0.600950385425617</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>91923</x:v>
+        <x:v>85126</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>25.5200000000002</x:v>
+        <x:v>25.227104720839</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -990,28 +990,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>192920</x:v>
+        <x:v>198531</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.1481383491639</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>111493</x:v>
+        <x:v>120754</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>25.5199999999997</x:v>
+        <x:v>24.9980921923708</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>304413</x:v>
+        <x:v>319285</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.464897123454298</x:v>
+        <x:v>1.08684870348483</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>81427</x:v>
+        <x:v>77777</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>25.5200000000004</x:v>
+        <x:v>25.3810950538116</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1019,28 +1019,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>134491</x:v>
+        <x:v>73125</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2315140396509</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>61971</x:v>
+        <x:v>11437</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>25.5199999999998</x:v>
+        <x:v>25.3453650610049</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>196462</x:v>
+        <x:v>84562</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.300035210940658</x:v>
+        <x:v>0.28784972693388</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>72520</x:v>
+        <x:v>61688</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>25.5200000000001</x:v>
+        <x:v>25.2104059776093</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1048,28 +1048,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>535220</x:v>
+        <x:v>449296</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>25.5199999999998</x:v>
+        <x:v>25.0486486947272</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>465194</x:v>
+        <x:v>389988</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>25.5200000000004</x:v>
+        <x:v>25.2134140578106</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1000414</x:v>
+        <x:v>839284</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.5278243401675</x:v>
+        <x:v>2.85692947446814</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>70026</x:v>
+        <x:v>59308</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>25.5199999999964</x:v>
+        <x:v>23.9652111413081</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1077,28 +1077,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>91912</x:v>
+        <x:v>73388</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.3590636797846</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>32391</x:v>
+        <x:v>32008</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.480878511568</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>124303</x:v>
+        <x:v>105396</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.189834557449057</x:v>
+        <x:v>0.358768830206514</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>59521</x:v>
+        <x:v>41380</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2648382294287</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1106,28 +1106,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>539312</x:v>
+        <x:v>259642</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>24.9860655308971</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>481491</x:v>
+        <x:v>219170</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.0880177594245</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>1020803</x:v>
+        <x:v>478812</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>1.55896225954055</x:v>
+        <x:v>1.62987989229991</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>57821</x:v>
+        <x:v>40472</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>25.5199999999991</x:v>
+        <x:v>24.4339586440036</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1135,28 +1135,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>83493</x:v>
+        <x:v>57751</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.7393525337232</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>25975</x:v>
+        <x:v>24358</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.0684581941078</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>109468</x:v>
+        <x:v>82109</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.167178662903014</x:v>
+        <x:v>0.279499695239161</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>57518</x:v>
+        <x:v>33393</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.4992915725742</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1164,28 +1164,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>754248</x:v>
+        <x:v>120004</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>25.5200000000006</x:v>
+        <x:v>24.3957741192105</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>707052</x:v>
+        <x:v>88961</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>25.1881698442408</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1461300</x:v>
+        <x:v>208965</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>2.23168579036955</x:v>
+        <x:v>0.711318537744356</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>47196</x:v>
+        <x:v>31043</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>25.5200000000106</x:v>
+        <x:v>22.124978252367</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1193,28 +1193,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>40591</x:v>
+        <x:v>54477</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.3140691089908</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>10443</x:v>
+        <x:v>25829</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.0399690091418</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>51034</x:v>
+        <x:v>80306</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0779387207457194</x:v>
+        <x:v>0.273362268763182</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>30148</x:v>
+        <x:v>28648</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.5611974069174</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1222,28 +1222,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>29728</x:v>
+        <x:v>127004</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.8549870953913</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>5798</x:v>
+        <x:v>99820</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.8890179944979</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>35526</x:v>
+        <x:v>226824</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0542550259280563</x:v>
+        <x:v>0.772110717131222</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>23930</x:v>
+        <x:v>27184</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.7300251932127</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1251,28 +1251,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>20185</x:v>
+        <x:v>32524</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.6169507127892</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>6823</x:v>
+        <x:v>15391</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.388441496507</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>27008</x:v>
+        <x:v>47915</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0412464037680838</x:v>
+        <x:v>0.163103044701365</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>13362</x:v>
+        <x:v>17133</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>25.52</x:v>
+        <x:v>23.9239013546967</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1280,28 +1280,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>32382</x:v>
+        <x:v>520691</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2519482514221</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>19977</x:v>
+        <x:v>506204</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2338202091357</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>52359</x:v>
+        <x:v>1026895</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0799622502552244</x:v>
+        <x:v>3.49555882476487</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>12405</x:v>
+        <x:v>14487</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.8853773614869</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1309,28 +1309,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>15006</x:v>
+        <x:v>156580</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.9630623037353</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>3336</x:v>
+        <x:v>145544</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2129648740339</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>18342</x:v>
+        <x:v>302124</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0280117571798798</x:v>
+        <x:v>1.02843252170208</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>11670</x:v>
+        <x:v>11036</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>25.52</x:v>
+        <x:v>21.6673193088516</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1338,28 +1338,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>350431</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>342381</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>25.52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>692812</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>1.05805700116164</x:v>
+        <x:v>0.034040080288295</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>8050</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>25.5199999999972</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1367,28 +1367,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>7811</x:v>
+        <x:v>2527</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.8288400202435</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>2155</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>25.52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>9966</x:v>
+        <x:v>2527</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0152199962956429</x:v>
+        <x:v>0.00860192828885214</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>5656</x:v>
+        <x:v>2527</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.8288400202435</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1396,28 +1396,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>4103</x:v>
+        <x:v>57609</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.1017993983022</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>718</x:v>
+        <x:v>55278</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.3206008565189</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4821</x:v>
+        <x:v>112887</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00736259303043291</x:v>
+        <x:v>0.384268254350475</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>3385</x:v>
+        <x:v>2331</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>25.52</x:v>
+        <x:v>19.9130791034478</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1425,28 +1425,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>2501</x:v>
+        <x:v>288267</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2934887406042</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>0</x:v>
+        <x:v>286698</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>0</x:v>
+        <x:v>25.2120103612725</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>2501</x:v>
+        <x:v>574965</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00381950739869585</x:v>
+        <x:v>1.95718547629595</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>2501</x:v>
+        <x:v>1569</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>25.52</x:v>
+        <x:v>40.1817541310862</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1454,28 +1454,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>19074</x:v>
+        <x:v>5701</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.291892499176</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>18221</x:v>
+        <x:v>4511</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2989357948515</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>37295</x:v>
+        <x:v>10212</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0569566287222558</x:v>
+        <x:v>0.0347617299904068</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>853</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>25.5199999999995</x:v>
+        <x:v>25.2651930817035</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1483,28 +1483,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1038</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4200000762939</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>414</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>25.52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>1452</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00221748290400095</x:v>
+        <x:v>0.0034040080288295</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>624</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4200000762939</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1512,28 +1512,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>1350</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>982</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>2332</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0035614119367288</x:v>
+        <x:v>0.000830577959034397</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>368</x:v>
+        <x:v>-44</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.5</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1541,28 +1541,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>201</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>25.52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>0</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>0</x:v>
+        <x:v>24.9883681461729</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>201</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000306965608611702</x:v>
+        <x:v>0.00148074349254083</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>201</x:v>
+        <x:v>-435</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.9883681461729</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1570,28 +1570,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>188337</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>188227</x:v>
+        <x:v>1118</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.1800536273417</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>376564</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.575085559409238</x:v>
+        <x:v>0.00411884971488369</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>110</x:v>
+        <x:v>-1026</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>25.5199999999086</x:v>
+        <x:v>25.1513644789162</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1599,28 +1599,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>0</x:v>
+        <x:v>1213</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>0</x:v>
+        <x:v>25.2540807291583</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>40</x:v>
+        <x:v>1248</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>6.10876833058113E-05</x:v>
+        <x:v>0.00424820201997921</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>40</x:v>
+        <x:v>-1178</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2467741294304</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1628,28 +1628,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>25.52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>0</x:v>
+        <x:v>1691</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>0</x:v>
+        <x:v>25.3822589233597</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>1</x:v>
+        <x:v>1691</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>1.52719208264528E-06</x:v>
+        <x:v>0.00575617757675068</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>1</x:v>
+        <x:v>-1691</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.3822589233597</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1657,28 +1657,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>0</x:v>
+        <x:v>24.5</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>193</x:v>
+        <x:v>3298</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4153547668688</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>193</x:v>
+        <x:v>3448</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.00029474807195054</x:v>
+        <x:v>0.0117370196834041</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-193</x:v>
+        <x:v>-3148</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4589707818086</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1686,28 +1686,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>1</x:v>
+        <x:v>4983</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.8896488114674</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>304</x:v>
+        <x:v>8409</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4382113330726</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>305</x:v>
+        <x:v>13392</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.000465793585206811</x:v>
+        <x:v>0.0455864755220846</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-303</x:v>
+        <x:v>-3426</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>25.52</x:v>
+        <x:v>26.2360767870011</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1715,28 +1715,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>45</x:v>
+        <x:v>14277</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>25.52</x:v>
+        <x:v>24.9508705877945</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>868</x:v>
+        <x:v>20376</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2787386784144</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>913</x:v>
+        <x:v>34653</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.00139432637145514</x:v>
+        <x:v>0.117959090223029</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-823</x:v>
+        <x:v>-6099</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>25.52</x:v>
+        <x:v>26.0462370764762</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1744,28 +1744,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>681</x:v>
+        <x:v>57238</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.1892515435618</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>1651</x:v>
+        <x:v>65149</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.2145264724256</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>2332</x:v>
+        <x:v>122387</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.0035614119367288</x:v>
+        <x:v>0.416606330624356</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-970</x:v>
+        <x:v>-7911</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.397396701007</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1773,28 +1773,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>672758</x:v>
+        <x:v>16070</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>25.5199999999998</x:v>
+        <x:v>25.0753355267186</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>675155</x:v>
+        <x:v>36492</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>25.5200000000013</x:v>
+        <x:v>25.275619301947</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>1347913</x:v>
+        <x:v>52562</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>2.05852206169465</x:v>
+        <x:v>0.178921470011336</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-2397</x:v>
+        <x:v>-20422</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>25.5200000004046</x:v>
+        <x:v>25.4332219005133</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1802,28 +1802,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>5426</x:v>
+        <x:v>301781</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.0783332560695</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>7911</x:v>
+        <x:v>371392</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4362266558872</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>13337</x:v>
+        <x:v>673173</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.0203681608062401</x:v>
+        <x:v>2.29148629679124</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-2485</x:v>
+        <x:v>-69611</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>25.52</x:v>
+        <x:v>26.9877835662947</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1831,28 +1831,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>409667</x:v>
+        <x:v>753465</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>25.5200000000004</x:v>
+        <x:v>25.3508864020303</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>412220</x:v>
+        <x:v>832491</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.1437734960229</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>821887</x:v>
+        <x:v>1585956</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.25517931922908</x:v>
+        <x:v>5.39860695737031</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-2553</x:v>
+        <x:v>-79026</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>25.5199999999309</x:v>
+        <x:v>23.1690775007194</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1860,28 +1860,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>361</x:v>
+        <x:v>44093</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4651940471016</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>5000</x:v>
+        <x:v>217668</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4910552790101</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>5361</x:v>
+        <x:v>261761</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.00818727675506136</x:v>
+        <x:v>0.891036545634438</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-4639</x:v>
+        <x:v>-173575</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4976247694237</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1889,28 +1889,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>153958</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>25.5199999999997</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>358876</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>512834</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.783196024511311</x:v>
+        <x:v>0.680805009773928</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-204918</x:v>
+        <x:v>-200001</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.5200000000002</x:v>
+        <x:v>25.5</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1918,28 +1918,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>723994</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1007947</x:v>
+        <x:v>207852</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>25.5199999999987</x:v>
+        <x:v>25.4623951899079</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1731941</x:v>
+        <x:v>207852</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>2.64500658280875</x:v>
+        <x:v>0.707529876808269</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-283953</x:v>
+        <x:v>-207852</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>25.5199999999958</x:v>
+        <x:v>25.4623951899079</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1947,28 +1947,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>1242126</x:v>
+        <x:v>20923</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4485111984087</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1578952</x:v>
+        <x:v>244310</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.0715927355113</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>2821078</x:v>
+        <x:v>265233</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>4.30832798612479</x:v>
+        <x:v>0.902855261510534</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-336826</x:v>
+        <x:v>-223387</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.5199999999999</x:v>
+        <x:v>25.036289584481</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1976,28 +1976,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>1034629</x:v>
+        <x:v>699516</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>25.5199999999998</x:v>
+        <x:v>25.1689412476608</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1482325</x:v>
+        <x:v>1088894</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>25.5199999999982</x:v>
+        <x:v>25.2318072692279</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>2516954</x:v>
+        <x:v>1788410</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>3.84387222118237</x:v>
+        <x:v>6.08776199883896</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-447696</x:v>
+        <x:v>-389378</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>25.5199999999944</x:v>
+        <x:v>25.3447458223626</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2005,28 +2005,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>1057124</x:v>
+        <x:v>1162991</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>25.5200000000004</x:v>
+        <x:v>25.0246115071036</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2061642</x:v>
+        <x:v>1611592</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>25.5200000000004</x:v>
+        <x:v>25.1312917092532</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>3118766</x:v>
+        <x:v>2774583</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>4.7629547428233</x:v>
+        <x:v>9.44470280865383</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1004518</x:v>
+        <x:v>-448601</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>25.5200000000003</x:v>
+        <x:v>25.4078584466838</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2034,28 +2034,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>7531</x:v>
+        <x:v>848321</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.1256407144295</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1506677</x:v>
+        <x:v>1429153</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4061259582126</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>1514208</x:v>
+        <x:v>2277474</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>2.31248646907815</x:v>
+        <x:v>7.75253978145043</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1499146</x:v>
+        <x:v>-580832</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.8157823175236</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2063,28 +2063,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>104341</x:v>
+        <x:v>177838</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4538563242685</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>1954315</x:v>
+        <x:v>955787</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4416867831483</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>2058656</x:v>
+        <x:v>1133625</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>3.14396314409021</x:v>
+        <x:v>3.85886860168184</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1849974</x:v>
+        <x:v>-777949</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>25.52</x:v>
+        <x:v>25.4389048439033</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2092,28 +2092,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>1959443</x:v>
+        <x:v>129575</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>25.5200000000003</x:v>
+        <x:v>25.3851026115587</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>5541834</x:v>
+        <x:v>1013653</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>25.5199999999998</x:v>
+        <x:v>24.6458108860812</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>7501277</x:v>
+        <x:v>1143228</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>11.4558908441292</x:v>
+        <x:v>3.89155729078269</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-3582391</x:v>
+        <x:v>-884078</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>25.5199999999996</x:v>
+        <x:v>24.5374565040824</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -43,160 +43,163 @@
     <x:t>IS</x:t>
   </x:si>
   <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUPAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUPAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
     <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -547,7 +550,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I54"/>
+  <x:dimension ref="A1:I55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -584,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1686600</x:v>
+        <x:v>7007571</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>25.2587613611924</x:v>
+        <x:v>24.1038594499285</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>846982</x:v>
+        <x:v>3826024</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>25.1095601943819</x:v>
+        <x:v>23.9753293334967</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2533582</x:v>
+        <x:v>10833595</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>8.6243334696979</x:v>
+        <x:v>7.69686137342092</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>839618</x:v>
+        <x:v>3181547</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>25.4092711199963</x:v>
+        <x:v>24.2584255494363</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -613,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>835909</x:v>
+        <x:v>2719920</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>24.9190876783077</x:v>
+        <x:v>24.0173663113074</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>365048</x:v>
+        <x:v>554790</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>24.6851489379382</x:v>
+        <x:v>23.8201298474419</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1200957</x:v>
+        <x:v>3274710</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.08806727027899</x:v>
+        <x:v>2.32655816542479</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>470861</x:v>
+        <x:v>2165130</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>25.1004551504372</x:v>
+        <x:v>24.0679059176073</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -642,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1799441</x:v>
+        <x:v>2363452</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>25.2536610034793</x:v>
+        <x:v>23.9875344528844</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1355575</x:v>
+        <x:v>1254801</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.7743006287654</x:v>
+        <x:v>24.1882614553203</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>3155016</x:v>
+        <x:v>3618253</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>10.7396997950855</x:v>
+        <x:v>2.57063253287245</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>443866</x:v>
+        <x:v>1108651</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>26.7176364824591</x:v>
+        <x:v>23.7603462364091</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -671,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>480885</x:v>
+        <x:v>3498629</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>25.1908063130564</x:v>
+        <x:v>24.0920463903216</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>77748</x:v>
+        <x:v>2480730</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>25.0117410467308</x:v>
+        <x:v>24.1685210845792</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>558633</x:v>
+        <x:v>5979359</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.90159121716911</x:v>
+        <x:v>4.24810945257938</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>403137</x:v>
+        <x:v>1017899</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>25.2253403953319</x:v>
+        <x:v>23.9056692858293</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -700,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>404903</x:v>
+        <x:v>1764541</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.8711158757774</x:v>
+        <x:v>24.4556153035907</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>7775</x:v>
+        <x:v>1026439</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>25.3623382359839</x:v>
+        <x:v>24.6280092855504</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>412678</x:v>
+        <x:v>2790980</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.4047592253213</x:v>
+        <x:v>1.98288621237828</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>397128</x:v>
+        <x:v>738102</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>24.8614986897552</x:v>
+        <x:v>24.2158762073023</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -729,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>758311</x:v>
+        <x:v>5351332</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>25.4188425194174</x:v>
+        <x:v>24.01657163425</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>542529</x:v>
+        <x:v>4720842</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>25.4049754201095</x:v>
+        <x:v>24.1898213188772</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1300840</x:v>
+        <x:v>10072174</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>4.42806980422256</x:v>
+        <x:v>7.15590041966443</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>215782</x:v>
+        <x:v>630490</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>25.4537078164319</x:v>
+        <x:v>22.7193513965381</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -758,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>742697</x:v>
+        <x:v>906515</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>24.9023272854905</x:v>
+        <x:v>23.9130370270164</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>604338</x:v>
+        <x:v>380628</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>24.8778562403815</x:v>
+        <x:v>24.2306147009961</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1347035</x:v>
+        <x:v>1287143</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>4.58531795511434</x:v>
+        <x:v>0.914466641845954</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>138359</x:v>
+        <x:v>525887</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>25.0092143145894</x:v>
+        <x:v>23.6831797479972</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -787,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>219659</x:v>
+        <x:v>8379007</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>24.8943445012495</x:v>
+        <x:v>23.757311612319</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>92257</x:v>
+        <x:v>7978547</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>25.1876322530241</x:v>
+        <x:v>23.6238519871128</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>311916</x:v>
+        <x:v>16357554</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.06176456832038</x:v>
+        <x:v>11.6214262713575</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>127402</x:v>
+        <x:v>400460</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>24.6819628422845</x:v>
+        <x:v>26.416288519651</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -816,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>246676</x:v>
+        <x:v>3311201</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>24.6609885099653</x:v>
+        <x:v>24.0408538869354</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>140882</x:v>
+        <x:v>2955327</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>24.9128549474699</x:v>
+        <x:v>24.2764067705434</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>387558</x:v>
+        <x:v>6266528</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.3192505436371</x:v>
+        <x:v>4.45213221545208</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>105794</x:v>
+        <x:v>355874</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>24.3255871880705</x:v>
+        <x:v>22.0847239171862</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -845,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>273347</x:v>
+        <x:v>1283209</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>24.856635586657</x:v>
+        <x:v>23.6886653980412</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>167903</x:v>
+        <x:v>967059</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>24.8695949425782</x:v>
+        <x:v>23.6817585351537</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>441250</x:v>
+        <x:v>2250268</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.50201854272102</x:v>
+        <x:v>1.59873069364741</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>105444</x:v>
+        <x:v>316150</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>24.8359998488507</x:v>
+        <x:v>23.709792533632</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -874,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>114642</x:v>
+        <x:v>1272992</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>24.8026240588012</x:v>
+        <x:v>23.7807804957084</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>11897</x:v>
+        <x:v>959998</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>25.2132453549717</x:v>
+        <x:v>23.8736224057088</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>126539</x:v>
+        <x:v>2232990</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.430739771960056</x:v>
+        <x:v>1.58645532514693</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>102745</x:v>
+        <x:v>312994</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>24.7550775936639</x:v>
+        <x:v>23.4960208903596</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -903,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>94500</x:v>
+        <x:v>830602</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>25.154882453979</x:v>
+        <x:v>23.9520265882245</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1013</x:v>
+        <x:v>590254</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>25.3395853805165</x:v>
+        <x:v>23.9552935857523</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>95513</x:v>
+        <x:v>1420856</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.325127018857592</x:v>
+        <x:v>1.00946469418446</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>93487</x:v>
+        <x:v>240348</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>25.1528810627205</x:v>
+        <x:v>23.9440033953591</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -932,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>180598</x:v>
+        <x:v>4891424</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>25.3260778827862</x:v>
+        <x:v>23.7962580792415</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>91843</x:v>
+        <x:v>4677054</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>25.3864424326821</x:v>
+        <x:v>23.7977556732039</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>272441</x:v>
+        <x:v>9568478</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.927391351382337</x:v>
+        <x:v>6.79804337531796</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>88755</x:v>
+        <x:v>214370</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>25.2636131049586</x:v>
+        <x:v>23.7635840678029</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -961,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>130834</x:v>
+        <x:v>256685</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>25.2163523264023</x:v>
+        <x:v>24.2685119918555</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>45708</x:v>
+        <x:v>43010</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>25.196327203255</x:v>
+        <x:v>24.1657377017318</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>176542</x:v>
+        <x:v>299695</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.600950385425617</x:v>
+        <x:v>0.212922014281259</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>85126</x:v>
+        <x:v>213675</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>25.227104720839</x:v>
+        <x:v>24.2891991205239</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -990,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>198531</x:v>
+        <x:v>1496022</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>25.1481383491639</x:v>
+        <x:v>23.7779870058208</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>120754</x:v>
+        <x:v>1305584</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>24.9980921923708</x:v>
+        <x:v>23.8274861666707</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>319285</x:v>
+        <x:v>2801606</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>1.08684870348483</x:v>
+        <x:v>1.99043558531995</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>77777</x:v>
+        <x:v>190438</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>25.3810950538116</x:v>
+        <x:v>23.4386360757594</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1019,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>73125</x:v>
+        <x:v>575345</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>25.2315140396509</x:v>
+        <x:v>24.1452334189908</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>11437</x:v>
+        <x:v>407056</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>25.3453650610049</x:v>
+        <x:v>24.1077156748198</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>84562</x:v>
+        <x:v>982401</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.28784972693388</x:v>
+        <x:v>0.697958924079226</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>61688</x:v>
+        <x:v>168289</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>25.2104059776093</x:v>
+        <x:v>24.2359810190794</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1048,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>449296</x:v>
+        <x:v>306906</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>25.0486486947272</x:v>
+        <x:v>23.9831306140094</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>389988</x:v>
+        <x:v>150724</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>25.2134140578106</x:v>
+        <x:v>24.2840655286146</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>839284</x:v>
+        <x:v>457630</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>2.85692947446814</x:v>
+        <x:v>0.325128885685556</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>59308</x:v>
+        <x:v>156182</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.9652111413081</x:v>
+        <x:v>23.6927122939152</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1077,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>73388</x:v>
+        <x:v>200927</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>25.3590636797846</x:v>
+        <x:v>24.2048851765142</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>32008</x:v>
+        <x:v>77648</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>25.480878511568</x:v>
+        <x:v>24.1360515939705</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>105396</x:v>
+        <x:v>278575</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.358768830206514</x:v>
+        <x:v>0.197917049428258</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>41380</x:v>
+        <x:v>123279</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>25.2648382294287</x:v>
+        <x:v>24.2482404115287</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1106,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>259642</x:v>
+        <x:v>103245</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>24.9860655308971</x:v>
+        <x:v>25.0202854520802</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>219170</x:v>
+        <x:v>2866</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>25.0880177594245</x:v>
+        <x:v>24.3073412854607</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>478812</x:v>
+        <x:v>106111</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>1.62987989229991</x:v>
+        <x:v>0.0753878705263642</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>40472</x:v>
+        <x:v>100379</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>24.4339586440036</x:v>
+        <x:v>25.0406412832952</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1135,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>57751</x:v>
+        <x:v>256564</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>24.7393525337232</x:v>
+        <x:v>24.2397190725217</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>24358</x:v>
+        <x:v>161385</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>25.0684581941078</x:v>
+        <x:v>24.1401326446576</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>82109</x:v>
+        <x:v>417949</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.279499695239161</x:v>
+        <x:v>0.296937029135748</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>33393</x:v>
+        <x:v>95179</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>24.4992915725742</x:v>
+        <x:v>24.4085772834806</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1164,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>120004</x:v>
+        <x:v>192116</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>24.3957741192105</x:v>
+        <x:v>23.6368213823554</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>88961</x:v>
+        <x:v>120600</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>25.1881698442408</x:v>
+        <x:v>23.8281872770838</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>208965</x:v>
+        <x:v>312716</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.711318537744356</x:v>
+        <x:v>0.222172944553557</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>31043</x:v>
+        <x:v>71516</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>22.124978252367</x:v>
+        <x:v>23.314114199288</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1193,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>54477</x:v>
+        <x:v>386895</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>25.3140691089908</x:v>
+        <x:v>23.7768208802388</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>25829</x:v>
+        <x:v>326394</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>25.0399690091418</x:v>
+        <x:v>23.726626282303</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>80306</x:v>
+        <x:v>713289</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.273362268763182</x:v>
+        <x:v>0.506764979878427</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>28648</x:v>
+        <x:v>60501</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>25.5611974069174</x:v>
+        <x:v>24.047613356374</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1222,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>127004</x:v>
+        <x:v>1231753</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>24.8549870953913</x:v>
+        <x:v>23.8747086016716</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>99820</x:v>
+        <x:v>1174486</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>24.8890179944979</x:v>
+        <x:v>23.8855414679447</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>226824</x:v>
+        <x:v>2406239</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.772110717131222</x:v>
+        <x:v>1.70954221699436</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>27184</x:v>
+        <x:v>57267</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>24.7300251932127</x:v>
+        <x:v>23.6525378964218</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1251,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>32524</x:v>
+        <x:v>136858</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>24.6169507127892</x:v>
+        <x:v>23.8604539770509</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>15391</x:v>
+        <x:v>87535</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>25.388441496507</x:v>
+        <x:v>24.3945954919467</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>47915</x:v>
+        <x:v>224393</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.163103044701365</x:v>
+        <x:v>0.159422778326681</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>17133</x:v>
+        <x:v>49323</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.9239013546967</x:v>
+        <x:v>22.9124970906814</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1280,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>520691</x:v>
+        <x:v>701554</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>25.2519482514221</x:v>
+        <x:v>23.7995331163266</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>506204</x:v>
+        <x:v>672889</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>25.2338202091357</x:v>
+        <x:v>23.7891115828012</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1026895</x:v>
+        <x:v>1374443</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>3.49555882476487</x:v>
+        <x:v>0.976490005087763</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>14487</x:v>
+        <x:v>28665</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>25.8853773614869</x:v>
+        <x:v>24.0441706628964</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1309,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>156580</x:v>
+        <x:v>91427</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>24.9630623037353</x:v>
+        <x:v>23.7751292892183</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>145544</x:v>
+        <x:v>65844</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>25.2129648740339</x:v>
+        <x:v>24.214993965176</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>302124</x:v>
+        <x:v>157271</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>1.02843252170208</x:v>
+        <x:v>0.111735124403236</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>11036</x:v>
+        <x:v>25583</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>21.6673193088516</x:v>
+        <x:v>22.6430318134038</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1338,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>10000</x:v>
+        <x:v>214573</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>25</x:v>
+        <x:v>24.0067886198883</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>0</x:v>
+        <x:v>191063</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>0</x:v>
+        <x:v>24.3175999183451</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>10000</x:v>
+        <x:v>405636</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.034040080288295</x:v>
+        <x:v>0.288189106207955</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>10000</x:v>
+        <x:v>23510</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>25</x:v>
+        <x:v>21.4808618178017</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1367,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>2527</x:v>
+        <x:v>22036</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>24.8288400202435</x:v>
+        <x:v>23.7779384685052</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>0</x:v>
+        <x:v>24.1599998474121</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>2527</x:v>
+        <x:v>23036</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00860192828885214</x:v>
+        <x:v>0.0163662107175064</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>2527</x:v>
+        <x:v>21036</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.8288400202435</x:v>
+        <x:v>23.7597762048188</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1396,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>57609</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>25.1017993983022</x:v>
+        <x:v>24.8800000277433</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>55278</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>25.3206008565189</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>112887</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.384268254350475</x:v>
+        <x:v>0.00781508586093814</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>2331</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>19.9130791034478</x:v>
+        <x:v>24.8800000277433</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1425,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>288267</x:v>
+        <x:v>270597</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>25.2934887406042</x:v>
+        <x:v>23.8642390645071</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>286698</x:v>
+        <x:v>261148</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>25.2120103612725</x:v>
+        <x:v>24.4637750775073</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>574965</x:v>
+        <x:v>531745</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>1.95718547629595</x:v>
+        <x:v>0.377784802829504</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>1569</x:v>
+        <x:v>9449</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>40.1817541310862</x:v>
+        <x:v>7.29448239999368</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1454,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>5701</x:v>
+        <x:v>7198</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>25.291892499176</x:v>
+        <x:v>23.7001609200734</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>4511</x:v>
+        <x:v>3184</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>25.2989357948515</x:v>
+        <x:v>24.3903705684384</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>10212</x:v>
+        <x:v>10382</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0347617299904068</x:v>
+        <x:v>0.00737602012802361</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>1190</x:v>
+        <x:v>4014</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>25.2651930817035</x:v>
+        <x:v>23.1526702572947</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1483,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1000</x:v>
+        <x:v>6224</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>25.4200000762939</x:v>
+        <x:v>23.8122875399332</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>0</x:v>
+        <x:v>2812</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>0</x:v>
+        <x:v>24.2543881865348</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>1000</x:v>
+        <x:v>9036</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0034040080288295</x:v>
+        <x:v>0.00641973780358518</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>1000</x:v>
+        <x:v>3412</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>25.4200000762939</x:v>
+        <x:v>23.447930266122</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1512,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>100</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.8133276853499</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>144</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>25.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>244</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.000830577959034397</x:v>
+        <x:v>0.00183796610202245</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-44</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.8133276853499</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1541,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>0</x:v>
+        <x:v>13056</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>0</x:v>
+        <x:v>23.7831887757661</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>435</x:v>
+        <x:v>11181</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.9883681461729</x:v>
+        <x:v>24.1357388286149</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>435</x:v>
+        <x:v>24237</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00148074349254083</x:v>
+        <x:v>0.0172194760010507</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-435</x:v>
+        <x:v>1875</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>24.9883681461729</x:v>
+        <x:v>21.6808623006185</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1570,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>92</x:v>
+        <x:v>15939</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.3162907965921</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>1118</x:v>
+        <x:v>15117</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>25.1800536273417</x:v>
+        <x:v>23.9855985601735</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>1210</x:v>
+        <x:v>31056</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00411884971488369</x:v>
+        <x:v>0.0220641187724813</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-1026</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>25.1513644789162</x:v>
+        <x:v>30.3978899911662</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1599,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>25.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>1213</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>25.2540807291583</x:v>
+        <x:v>24.1399993896484</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>1248</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00424820201997921</x:v>
+        <x:v>7.10462350994376E-07</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-1178</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>25.2467741294304</x:v>
+        <x:v>24.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1628,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>1691</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>25.3822589233597</x:v>
+        <x:v>24.6417083061463</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>1691</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.00575617757675068</x:v>
+        <x:v>0.000270686155728857</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-1691</x:v>
+        <x:v>-181</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>25.3822589233597</x:v>
+        <x:v>24.1675140001497</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1657,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>150</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>24.5</x:v>
+        <x:v>23.9019355773926</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>3298</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>25.4153547668688</x:v>
+        <x:v>24.4179756908882</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>3448</x:v>
+        <x:v>975</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.0117370196834041</x:v>
+        <x:v>0.000692700792219516</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-3148</x:v>
+        <x:v>-665</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>25.4589707818086</x:v>
+        <x:v>24.5382557173421</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1686,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>4983</x:v>
+        <x:v>7851</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>24.8896488114674</x:v>
+        <x:v>23.8303756373746</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>8409</x:v>
+        <x:v>8758</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>25.4382113330726</x:v>
+        <x:v>24.3661041142162</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>13392</x:v>
+        <x:v>16609</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.0455864755220846</x:v>
+        <x:v>0.0118000691876656</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-3426</x:v>
+        <x:v>-907</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>26.2360767870011</x:v>
+        <x:v>29.0033745350359</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1715,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>14277</x:v>
+        <x:v>222130</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>24.9508705877945</x:v>
+        <x:v>23.9065908216482</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>20376</x:v>
+        <x:v>230223</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>25.2787386784144</x:v>
+        <x:v>25.3974435217665</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>34653</x:v>
+        <x:v>452353</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.117959090223029</x:v>
+        <x:v>0.321379775859359</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-6099</x:v>
+        <x:v>-8093</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>26.0462370764762</x:v>
+        <x:v>66.3171408252723</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1744,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>57238</x:v>
+        <x:v>76349</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>25.1892515435618</x:v>
+        <x:v>24.1986400152724</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>65149</x:v>
+        <x:v>88257</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>25.2145264724256</x:v>
+        <x:v>24.2513689408119</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>122387</x:v>
+        <x:v>164606</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.416606330624356</x:v>
+        <x:v>0.11694636574778</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-7911</x:v>
+        <x:v>-11908</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>25.397396701007</x:v>
+        <x:v>24.5894442461544</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1773,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>16070</x:v>
+        <x:v>980020</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>25.0753355267186</x:v>
+        <x:v>23.9498131446903</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>36492</x:v>
+        <x:v>1027458</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>25.275619301947</x:v>
+        <x:v>23.8426419166229</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>52562</x:v>
+        <x:v>2007478</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.178921470011336</x:v>
+        <x:v>1.42623753944949</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-20422</x:v>
+        <x:v>-47438</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>25.4332219005133</x:v>
+        <x:v>21.6285952255604</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1802,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>301781</x:v>
+        <x:v>499017</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>25.0783332560695</x:v>
+        <x:v>23.6886220211898</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>371392</x:v>
+        <x:v>559795</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>25.4362266558872</x:v>
+        <x:v>23.7354549084852</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>673173</x:v>
+        <x:v>1058812</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2.29148629679124</x:v>
+        <x:v>0.752246062781057</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-69611</x:v>
+        <x:v>-60778</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>26.9877835662947</x:v>
+        <x:v>24.1199757370655</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1831,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>753465</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>25.3508864020303</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>832491</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>25.1437734960229</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>1585956</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>5.39860695737031</x:v>
+        <x:v>0.142093180661226</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-79026</x:v>
+        <x:v>-200001</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.1690775007194</x:v>
+        <x:v>25.5</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1860,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>44093</x:v>
+        <x:v>132107</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>25.4651940471016</x:v>
+        <x:v>23.8232351494244</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>217668</x:v>
+        <x:v>345135</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>25.4910552790101</x:v>
+        <x:v>24.6993545009486</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>261761</x:v>
+        <x:v>477242</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.891036545634438</x:v>
+        <x:v>0.339062473313258</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-173575</x:v>
+        <x:v>-213028</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>25.4976247694237</x:v>
+        <x:v>25.2426703991958</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1895,22 +1898,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>200001</x:v>
+        <x:v>256142</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>25.5</x:v>
+        <x:v>25.1030496077424</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>200001</x:v>
+        <x:v>256142</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.680805009773928</x:v>
+        <x:v>0.181979247508401</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-200001</x:v>
+        <x:v>-256142</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.5</x:v>
+        <x:v>25.1030496077424</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1918,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>0</x:v>
+        <x:v>1095260</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>0</x:v>
+        <x:v>24.110652994329</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>207852</x:v>
+        <x:v>1376100</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>25.4623951899079</x:v>
+        <x:v>23.8684564875898</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>207852</x:v>
+        <x:v>2471360</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0.707529876808269</x:v>
+        <x:v>1.75580823575346</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-207852</x:v>
+        <x:v>-280840</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>25.4623951899079</x:v>
+        <x:v>22.9239039097123</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1947,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>20923</x:v>
+        <x:v>4000779</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>25.4485111984087</x:v>
+        <x:v>23.870637438723</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>244310</x:v>
+        <x:v>4285204</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>25.0715927355113</x:v>
+        <x:v>23.9307641520243</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>265233</x:v>
+        <x:v>8285983</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.902855261510534</x:v>
+        <x:v>5.88687896247943</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-223387</x:v>
+        <x:v>-284425</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.036289584481</x:v>
+        <x:v>24.7765185404038</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1976,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>699516</x:v>
+        <x:v>319023</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>25.1689412476608</x:v>
+        <x:v>24.6330446270125</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1088894</x:v>
+        <x:v>1051582</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>25.2318072692279</x:v>
+        <x:v>25.2745914033478</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>1788410</x:v>
+        <x:v>1370605</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>6.08776199883896</x:v>
+        <x:v>0.973763250584646</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-389378</x:v>
+        <x:v>-732559</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>25.3447458223626</x:v>
+        <x:v>25.5539793805985</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2005,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>1162991</x:v>
+        <x:v>1000034</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>25.0246115071036</x:v>
+        <x:v>23.8857440517249</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>1611592</x:v>
+        <x:v>2077803</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>25.1312917092532</x:v>
+        <x:v>24.2817159154807</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2774583</x:v>
+        <x:v>3077837</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>9.44470280865383</x:v>
+        <x:v>2.18668731099748</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-448601</x:v>
+        <x:v>-1077769</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>25.4078584466838</x:v>
+        <x:v>24.649127973908</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2034,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>848321</x:v>
+        <x:v>1597828</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>25.1256407144295</x:v>
+        <x:v>23.8973700220498</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1429153</x:v>
+        <x:v>3700256</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>25.4061259582126</x:v>
+        <x:v>23.6295189371627</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>2277474</x:v>
+        <x:v>5298084</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>7.75253978145043</x:v>
+        <x:v>3.76408921440569</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-580832</x:v>
+        <x:v>-2102428</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>25.8157823175236</x:v>
+        <x:v>23.425954314135</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2063,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>177838</x:v>
+        <x:v>1035440</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>25.4538563242685</x:v>
+        <x:v>24.1204263669505</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>955787</x:v>
+        <x:v>3182050</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>25.4416867831483</x:v>
+        <x:v>23.6972280699747</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>1133625</x:v>
+        <x:v>4217490</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>3.85886860168184</x:v>
+        <x:v>2.99636786069527</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-777949</x:v>
+        <x:v>-2146610</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>25.4389048439033</x:v>
+        <x:v>23.4930939027898</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2092,28 +2095,57 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>129575</x:v>
+        <x:v>6126187</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>25.3851026115587</x:v>
+        <x:v>23.990656002459</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>1013653</x:v>
+        <x:v>8423630</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>24.6458108860812</x:v>
+        <x:v>23.8565453854684</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>1143228</x:v>
+        <x:v>14549817</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>3.89155729078269</x:v>
+        <x:v>10.3370971923579</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-884078</x:v>
+        <x:v>-2297443</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>24.5374565040824</x:v>
+        <x:v>23.4989362006618</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:9">
+      <x:c r="A55" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B55" s="0">
+        <x:v>3204524</x:v>
+      </x:c>
+      <x:c r="C55" s="0">
+        <x:v>23.9994069274439</x:v>
+      </x:c>
+      <x:c r="D55" s="0">
+        <x:v>6109191</x:v>
+      </x:c>
+      <x:c r="E55" s="0">
+        <x:v>24.0178492299952</x:v>
+      </x:c>
+      <x:c r="F55" s="0">
+        <x:v>9313715</x:v>
+      </x:c>
+      <x:c r="G55" s="0">
+        <x:v>6.61704385539158</x:v>
+      </x:c>
+      <x:c r="H55" s="0">
+        <x:v>-2904667</x:v>
+      </x:c>
+      <x:c r="I55" s="0">
+        <x:v>24.0381953836648</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -46,12 +46,15 @@
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
@@ -64,111 +67,111 @@
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKIF</x:t>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
+    <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
-    <x:t>BURGAN</x:t>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>BLUPAY</x:t>
   </x:si>
   <x:si>
@@ -178,16 +181,13 @@
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>7007571</x:v>
+        <x:v>11859140</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>24.1038594499285</x:v>
+        <x:v>24.0292096443329</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>3826024</x:v>
+        <x:v>7578193</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.9753293334967</x:v>
+        <x:v>23.9691784320974</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>10833595</x:v>
+        <x:v>19437333</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>7.69686137342092</x:v>
+        <x:v>8.62228119339022</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>3181547</x:v>
+        <x:v>4280947</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>24.2584255494363</x:v>
+        <x:v>24.1354777463076</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>2719920</x:v>
+        <x:v>4499113</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>24.0173663113074</x:v>
+        <x:v>23.982317557802</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>554790</x:v>
+        <x:v>1204747</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.8201298474419</x:v>
+        <x:v>23.8660430459874</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>3274710</x:v>
+        <x:v>5703860</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2.32655816542479</x:v>
+        <x:v>2.53019716273476</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>2165130</x:v>
+        <x:v>3294366</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24.0679059176073</x:v>
+        <x:v>24.024839053375</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2363452</x:v>
+        <x:v>6630871</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.9875344528844</x:v>
+        <x:v>23.9746088410456</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1254801</x:v>
+        <x:v>4410118</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.1882614553203</x:v>
+        <x:v>24.1670577129313</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>3618253</x:v>
+        <x:v>11040989</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.57063253287245</x:v>
+        <x:v>4.89771471277095</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>1108651</x:v>
+        <x:v>2220753</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.7603462364091</x:v>
+        <x:v>23.5924311589789</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>3498629</x:v>
+        <x:v>5136593</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>24.0920463903216</x:v>
+        <x:v>24.0268385733755</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>2480730</x:v>
+        <x:v>3685990</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>24.1685210845792</x:v>
+        <x:v>24.1044185479568</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>5979359</x:v>
+        <x:v>8822583</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.24810945257938</x:v>
+        <x:v>3.91364347557477</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>1017899</x:v>
+        <x:v>1450603</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.9056692858293</x:v>
+        <x:v>23.8297074420413</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>1764541</x:v>
+        <x:v>3359911</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.4556153035907</x:v>
+        <x:v>23.9421525650111</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1026439</x:v>
+        <x:v>1935461</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.6280092855504</x:v>
+        <x:v>24.1042438306163</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>2790980</x:v>
+        <x:v>5295372</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.98288621237828</x:v>
+        <x:v>2.34899440204092</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>738102</x:v>
+        <x:v>1424450</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>24.2158762073023</x:v>
+        <x:v>23.7219122455759</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>5351332</x:v>
+        <x:v>2375969</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>24.01657163425</x:v>
+        <x:v>24.312978217558</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>4720842</x:v>
+        <x:v>1330858</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.1898213188772</x:v>
+        <x:v>24.4691100896643</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>10072174</x:v>
+        <x:v>3706827</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>7.15590041966443</x:v>
+        <x:v>1.64432562477841</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>630490</x:v>
+        <x:v>1045111</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>22.7193513965381</x:v>
+        <x:v>24.1141578520201</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>906515</x:v>
+        <x:v>7608421</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.9130370270164</x:v>
+        <x:v>23.9791506000282</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>380628</x:v>
+        <x:v>6883616</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>24.2306147009961</x:v>
+        <x:v>24.1100405600696</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1287143</x:v>
+        <x:v>14492037</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.914466641845954</x:v>
+        <x:v>6.42857834863534</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>525887</x:v>
+        <x:v>724805</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.6831797479972</x:v>
+        <x:v>22.7360628410034</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>8379007</x:v>
+        <x:v>1340749</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.757311612319</x:v>
+        <x:v>23.9125237656881</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>7978547</x:v>
+        <x:v>697170</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.6238519871128</x:v>
+        <x:v>24.1162925041233</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>16357554</x:v>
+        <x:v>2037919</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>11.6214262713575</x:v>
+        <x:v>0.904008315716596</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>400460</x:v>
+        <x:v>643579</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>26.416288519651</x:v>
+        <x:v>23.6917871484665</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>3311201</x:v>
+        <x:v>14289602</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>24.0408538869354</x:v>
+        <x:v>23.7975714556314</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>2955327</x:v>
+        <x:v>13662028</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>24.2764067705434</x:v>
+        <x:v>23.7170953877397</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>6266528</x:v>
+        <x:v>27951630</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>4.45213221545208</x:v>
+        <x:v>12.399170898271</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>355874</x:v>
+        <x:v>627574</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.0847239171862</x:v>
+        <x:v>25.5495023719333</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1283209</x:v>
+        <x:v>1029827</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.6886653980412</x:v>
+        <x:v>24.0326218048599</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>967059</x:v>
+        <x:v>515952</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.6817585351537</x:v>
+        <x:v>24.0537816575247</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2250268</x:v>
+        <x:v>1545779</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.59873069364741</x:v>
+        <x:v>0.685698043082224</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>316150</x:v>
+        <x:v>513875</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.709792533632</x:v>
+        <x:v>24.0113764274781</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1272992</x:v>
+        <x:v>2524814</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.7807804957084</x:v>
+        <x:v>23.8336336133595</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>959998</x:v>
+        <x:v>2141434</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.8736224057088</x:v>
+        <x:v>23.8947803732533</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>2232990</x:v>
+        <x:v>4666248</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>1.58645532514693</x:v>
+        <x:v>2.06991887076765</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>312994</x:v>
+        <x:v>383380</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.4960208903596</x:v>
+        <x:v>23.4920880172764</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>830602</x:v>
+        <x:v>1290580</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.9520265882245</x:v>
+        <x:v>23.9405243420088</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>590254</x:v>
+        <x:v>964826</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.9552935857523</x:v>
+        <x:v>23.9678047776712</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>1420856</x:v>
+        <x:v>2255406</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.00946469418446</x:v>
+        <x:v>1.00048420929247</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>240348</x:v>
+        <x:v>325754</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.9440033953591</x:v>
+        <x:v>23.8597244942142</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>4891424</x:v>
+        <x:v>9538906</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.7962580792415</x:v>
+        <x:v>23.8560198120268</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>4677054</x:v>
+        <x:v>9271584</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.7977556732039</x:v>
+        <x:v>23.8560737186336</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>9568478</x:v>
+        <x:v>18810490</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>6.79804337531796</x:v>
+        <x:v>8.34421749966699</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>214370</x:v>
+        <x:v>267322</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.7635840678029</x:v>
+        <x:v>23.854150158076</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>256685</x:v>
+        <x:v>523312</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>24.2685119918555</x:v>
+        <x:v>23.9566376263347</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>43010</x:v>
+        <x:v>288234</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>24.1657377017318</x:v>
+        <x:v>24.1470408345306</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>299695</x:v>
+        <x:v>811546</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.212922014281259</x:v>
+        <x:v>0.359996806834099</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>213675</x:v>
+        <x:v>235078</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>24.2891991205239</x:v>
+        <x:v>23.7231803129701</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>1496022</x:v>
+        <x:v>277969</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.7779870058208</x:v>
+        <x:v>24.2314007865393</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1305584</x:v>
+        <x:v>59920</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.8274861666707</x:v>
+        <x:v>24.1033267287291</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>2801606</x:v>
+        <x:v>337889</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>1.99043558531995</x:v>
+        <x:v>0.149885479152589</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>190438</x:v>
+        <x:v>218049</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.4386360757594</x:v>
+        <x:v>24.2665956168021</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>575345</x:v>
+        <x:v>591339</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>24.1452334189908</x:v>
+        <x:v>23.798737756879</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>407056</x:v>
+        <x:v>377409</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>24.1077156748198</x:v>
+        <x:v>23.9736059274853</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>982401</x:v>
+        <x:v>968748</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.697958924079226</x:v>
+        <x:v>0.429730645739021</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>168289</x:v>
+        <x:v>213930</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>24.2359810190794</x:v>
+        <x:v>23.4902404848726</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>306906</x:v>
+        <x:v>2088526</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.9831306140094</x:v>
+        <x:v>23.9081565621912</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>150724</x:v>
+        <x:v>1876266</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>24.2840655286146</x:v>
+        <x:v>23.9031906672809</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>457630</x:v>
+        <x:v>3964792</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.325128885685556</x:v>
+        <x:v>1.75875730982764</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>156182</x:v>
+        <x:v>212260</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.6927122939152</x:v>
+        <x:v>23.9520524435619</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>200927</x:v>
+        <x:v>295604</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>24.2048851765142</x:v>
+        <x:v>24.0993702082548</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>77648</x:v>
+        <x:v>135445</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>24.1360515939705</x:v>
+        <x:v>24.0233781008305</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>278575</x:v>
+        <x:v>431049</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.197917049428258</x:v>
+        <x:v>0.191210681328023</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>123279</x:v>
+        <x:v>160159</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>24.2482404115287</x:v>
+        <x:v>24.1636360377747</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>103245</x:v>
+        <x:v>1611060</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>25.0202854520802</x:v>
+        <x:v>23.7142713722966</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>2866</x:v>
+        <x:v>1451739</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>24.3073412854607</x:v>
+        <x:v>23.7386007677695</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>106111</x:v>
+        <x:v>3062799</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0753878705263642</x:v>
+        <x:v>1.35863877090722</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>100379</x:v>
+        <x:v>159321</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>25.0406412832952</x:v>
+        <x:v>23.492580997177</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>256564</x:v>
+        <x:v>489924</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>24.2397190725217</x:v>
+        <x:v>24.1296099265259</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>161385</x:v>
+        <x:v>364629</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>24.1401326446576</x:v>
+        <x:v>24.0415175102345</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>417949</x:v>
+        <x:v>854553</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.296937029135748</x:v>
+        <x:v>0.379074447129922</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>95179</x:v>
+        <x:v>125295</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>24.4085772834806</x:v>
+        <x:v>24.3859733062291</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>192116</x:v>
+        <x:v>105414</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.6368213823554</x:v>
+        <x:v>24.9907521993639</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>120600</x:v>
+        <x:v>10684</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.8281872770838</x:v>
+        <x:v>23.9284804716221</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>312716</x:v>
+        <x:v>116098</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.222172944553557</x:v>
+        <x:v>0.0515003576874573</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>71516</x:v>
+        <x:v>94730</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.314114199288</x:v>
+        <x:v>25.1105591363342</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>386895</x:v>
+        <x:v>2300212</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.7768208802388</x:v>
+        <x:v>23.8088144869799</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>326394</x:v>
+        <x:v>2213865</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.726626282303</x:v>
+        <x:v>23.8469042957495</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>713289</x:v>
+        <x:v>4514077</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.506764979878427</x:v>
+        <x:v>2.00241675247398</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>60501</x:v>
+        <x:v>86347</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>24.047613356374</x:v>
+        <x:v>22.832223586407</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>1231753</x:v>
+        <x:v>1413398</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.8747086016716</x:v>
+        <x:v>23.9411439755554</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>1174486</x:v>
+        <x:v>1335090</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.8855414679447</x:v>
+        <x:v>23.8574696740662</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>2406239</x:v>
+        <x:v>2748488</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>1.70954221699436</x:v>
+        <x:v>1.21921234732454</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>57267</x:v>
+        <x:v>78308</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.6525378964218</x:v>
+        <x:v>25.3677252083187</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>136858</x:v>
+        <x:v>573513</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.8604539770509</x:v>
+        <x:v>23.8114635676758</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>87535</x:v>
+        <x:v>509943</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>24.3945954919467</x:v>
+        <x:v>23.8305420623237</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>224393</x:v>
+        <x:v>1083456</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.159422778326681</x:v>
+        <x:v>0.480614407988266</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>49323</x:v>
+        <x:v>63570</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>22.9124970906814</x:v>
+        <x:v>23.6584205474421</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>701554</x:v>
+        <x:v>178133</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.7995331163266</x:v>
+        <x:v>23.8635592874502</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>672889</x:v>
+        <x:v>122982</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.7891115828012</x:v>
+        <x:v>24.241851417345</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1374443</x:v>
+        <x:v>301115</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.976490005087763</x:v>
+        <x:v>0.133572759264231</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>28665</x:v>
+        <x:v>55151</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>24.0441706628964</x:v>
+        <x:v>23.0200002818343</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>91427</x:v>
+        <x:v>139221</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.7751292892183</x:v>
+        <x:v>23.8270062235687</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>65844</x:v>
+        <x:v>98273</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>24.214993965176</x:v>
+        <x:v>24.1187899341117</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>157271</x:v>
+        <x:v>237494</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.111735124403236</x:v>
+        <x:v>0.105350875541568</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>25583</x:v>
+        <x:v>40948</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>22.6430318134038</x:v>
+        <x:v>23.1267409948349</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>214573</x:v>
+        <x:v>1169559</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>24.0067886198883</x:v>
+        <x:v>23.8253634542567</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>191063</x:v>
+        <x:v>1143273</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>24.3175999183451</x:v>
+        <x:v>23.820441647407</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>405636</x:v>
+        <x:v>2312832</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.288189106207955</x:v>
+        <x:v>1.02595802917361</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>23510</x:v>
+        <x:v>26286</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>21.4808618178017</x:v>
+        <x:v>24.0394305957921</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,10 +1370,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>22036</x:v>
+        <x:v>22936</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.7779384685052</x:v>
+        <x:v>23.7887448489479</x:v>
       </x:c>
       <x:c r="D29" s="0">
         <x:v>1000</x:v>
@@ -1382,16 +1382,16 @@
         <x:v>24.1599998474121</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>23036</x:v>
+        <x:v>23936</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0163662107175064</x:v>
+        <x:v>0.010617862164783</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>21036</x:v>
+        <x:v>21936</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.7597762048188</x:v>
+        <x:v>23.7718203869464</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>11000</x:v>
+        <x:v>263374</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>24.8800000277433</x:v>
+        <x:v>23.8917105252602</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>0</x:v>
+        <x:v>246887</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>0</x:v>
+        <x:v>25.297762595684</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>11000</x:v>
+        <x:v>510261</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00781508586093814</x:v>
+        <x:v>0.226348636616993</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>11000</x:v>
+        <x:v>16487</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>24.8800000277433</x:v>
+        <x:v>2.83657754104567</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>270597</x:v>
+        <x:v>13283</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.8642390645071</x:v>
+        <x:v>24.7307761727278</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>261148</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>24.4637750775073</x:v>
+        <x:v>23.8400001525879</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>531745</x:v>
+        <x:v>14283</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.377784802829504</x:v>
+        <x:v>0.00633585082301119</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>9449</x:v>
+        <x:v>12283</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>7.29448239999368</x:v>
+        <x:v>24.8032972197147</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>7198</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.7001609200734</x:v>
+        <x:v>23.9006019500284</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>3184</x:v>
+        <x:v>3288</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>24.3903705684384</x:v>
+        <x:v>24.1793186774799</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>10382</x:v>
+        <x:v>11788</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00737602012802361</x:v>
+        <x:v>0.00522908419111222</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>4014</x:v>
+        <x:v>5212</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.1526702572947</x:v>
+        <x:v>23.7247729784511</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>6224</x:v>
+        <x:v>7782</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.8122875399332</x:v>
+        <x:v>23.7199124008057</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>2812</x:v>
+        <x:v>3473</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>24.2543881865348</x:v>
+        <x:v>24.3728303203588</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>9036</x:v>
+        <x:v>11255</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00641973780358518</x:v>
+        <x:v>0.00499264867415745</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>3412</x:v>
+        <x:v>4309</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.447930266122</x:v>
+        <x:v>23.1936687399545</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1530,7 +1530,7 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00183796610202245</x:v>
+        <x:v>0.00114757726521949</x:v>
       </x:c>
       <x:c r="H34" s="0">
         <x:v>2587</x:v>
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>13056</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.7831887757661</x:v>
+        <x:v>24.2818180431019</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>11181</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.1357388286149</x:v>
+        <x:v>24.2780184614549</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>24237</x:v>
+        <x:v>1645</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0172194760010507</x:v>
+        <x:v>0.000729711867524568</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>1875</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>21.6808623006185</x:v>
+        <x:v>24.2855491638184</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>15939</x:v>
+        <x:v>16942</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>24.3162907965921</x:v>
+        <x:v>24.2975870032699</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>15117</x:v>
+        <x:v>16765</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.9855985601735</x:v>
+        <x:v>23.9868149792369</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>31056</x:v>
+        <x:v>33707</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0220641187724813</x:v>
+        <x:v>0.0149522175797268</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>822</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>30.3978899911662</x:v>
+        <x:v>53.7331405790512</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1617,7 +1617,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>7.10462350994376E-07</x:v>
+        <x:v>4.43593840440467E-07</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>-1</x:v>
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>100</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>25.5</x:v>
+        <x:v>23.9423530803007</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>281</x:v>
+        <x:v>965</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>24.6417083061463</x:v>
+        <x:v>24.3100934478285</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>381</x:v>
+        <x:v>1135</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000270686155728857</x:v>
+        <x:v>0.00050347900889993</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-181</x:v>
+        <x:v>-795</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>24.1675140001497</x:v>
+        <x:v>24.3887297528345</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>155</x:v>
+        <x:v>16359</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.9019355773926</x:v>
+        <x:v>23.7321458226916</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>820</x:v>
+        <x:v>20062</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.4179756908882</x:v>
+        <x:v>24.0173939830486</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>975</x:v>
+        <x:v>36421</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.000692700792219516</x:v>
+        <x:v>0.0161561312626822</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-665</x:v>
+        <x:v>-3703</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>24.5382557173421</x:v>
+        <x:v>25.2775545704857</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>7851</x:v>
+        <x:v>126258</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.8303756373746</x:v>
+        <x:v>23.9545138739352</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>8758</x:v>
+        <x:v>134224</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>24.3661041142162</x:v>
+        <x:v>23.7885906405437</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>16609</x:v>
+        <x:v>260482</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.0118000691876656</x:v>
+        <x:v>0.115548210745614</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-907</x:v>
+        <x:v>-7966</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>29.0033745350359</x:v>
+        <x:v>21.1587719609622</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>222130</x:v>
+        <x:v>108871</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.9065908216482</x:v>
+        <x:v>24.2109950223874</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>230223</x:v>
+        <x:v>123279</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>25.3974435217665</x:v>
+        <x:v>24.1782116975861</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>452353</x:v>
+        <x:v>232150</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.321379775859359</x:v>
+        <x:v>0.102980310058254</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-8093</x:v>
+        <x:v>-14408</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>66.3171408252723</x:v>
+        <x:v>23.9304914481106</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>76349</x:v>
+        <x:v>242360</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>24.1986400152724</x:v>
+        <x:v>23.9799359159947</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>88257</x:v>
+        <x:v>259110</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.2513689408119</x:v>
+        <x:v>24.2192132011797</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>164606</x:v>
+        <x:v>501470</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.11694636574778</x:v>
+        <x:v>0.222449003165681</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-11908</x:v>
+        <x:v>-16750</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>24.5894442461544</x:v>
+        <x:v>27.6813769526695</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>980020</x:v>
+        <x:v>387597</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.9498131446903</x:v>
+        <x:v>23.8587798373096</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>1027458</x:v>
+        <x:v>442968</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.8426419166229</x:v>
+        <x:v>24.2355428082166</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>2007478</x:v>
+        <x:v>830565</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.42623753944949</x:v>
+        <x:v>0.368433518085436</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-47438</x:v>
+        <x:v>-55371</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>21.6285952255604</x:v>
+        <x:v>26.8728836045654</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>499017</x:v>
+        <x:v>517170</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.6886220211898</x:v>
+        <x:v>23.6895485620731</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>559795</x:v>
+        <x:v>576842</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.7354549084852</x:v>
+        <x:v>23.7396653688717</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>1058812</x:v>
+        <x:v>1094012</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.752246062781057</x:v>
+        <x:v>0.485296984567956</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-60778</x:v>
+        <x:v>-59672</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>24.1199757370655</x:v>
+        <x:v>24.1740216661641</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>0</x:v>
+        <x:v>6040268</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>0</x:v>
+        <x:v>23.9098533140168</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>200001</x:v>
+        <x:v>6149699</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>25.5</x:v>
+        <x:v>23.9330192649854</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>200001</x:v>
+        <x:v>12189967</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.142093180661226</x:v>
+        <x:v>5.40739427637255</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-200001</x:v>
+        <x:v>-109431</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>25.5</x:v>
+        <x:v>25.2117113387625</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>132107</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.8232351494244</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>345135</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.6993545009486</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>477242</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.339062473313258</x:v>
+        <x:v>0.0887192116819338</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-213028</x:v>
+        <x:v>-200001</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>25.2426703991958</x:v>
+        <x:v>25.5</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>0</x:v>
+        <x:v>156596</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>0</x:v>
+        <x:v>23.8575848956233</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>256142</x:v>
+        <x:v>387177</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>25.1030496077424</x:v>
+        <x:v>24.6267173975039</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>256142</x:v>
+        <x:v>543773</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.181979247508401</x:v>
+        <x:v>0.241214353397834</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-256142</x:v>
+        <x:v>-230581</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.1030496077424</x:v>
+        <x:v>25.1490634419068</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>1095260</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>24.110652994329</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1376100</x:v>
+        <x:v>316076</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.8684564875898</x:v>
+        <x:v>24.8882718238432</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>2471360</x:v>
+        <x:v>316076</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.75580823575346</x:v>
+        <x:v>0.140209366711061</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-280840</x:v>
+        <x:v>-316076</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>22.9239039097123</x:v>
+        <x:v>24.8882718238432</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>4000779</x:v>
+        <x:v>532504</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.870637438723</x:v>
+        <x:v>24.3383149590904</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>4285204</x:v>
+        <x:v>1233120</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.9307641520243</x:v>
+        <x:v>25.0762874344235</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>8285983</x:v>
+        <x:v>1765624</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>5.88687896247943</x:v>
+        <x:v>0.783219930933859</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-284425</x:v>
+        <x:v>-700616</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>24.7765185404038</x:v>
+        <x:v>25.6371842666465</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>319023</x:v>
+        <x:v>1578493</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>24.6330446270125</x:v>
+        <x:v>23.8945643965518</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1051582</x:v>
+        <x:v>2496941</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>25.2745914033478</x:v>
+        <x:v>24.2175164741394</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>1370605</x:v>
+        <x:v>4075434</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.973763250584646</x:v>
+        <x:v>1.80783741952165</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-732559</x:v>
+        <x:v>-918448</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>25.5539793805985</x:v>
+        <x:v>24.7725588867827</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>1000034</x:v>
+        <x:v>1556558</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.8857440517249</x:v>
+        <x:v>24.0525620956149</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2077803</x:v>
+        <x:v>2746826</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>24.2817159154807</x:v>
+        <x:v>23.7958340471932</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>3077837</x:v>
+        <x:v>4303384</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.18668731099748</x:v>
+        <x:v>1.90895463545006</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1077769</x:v>
+        <x:v>-1190268</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>24.649127973908</x:v>
+        <x:v>23.460101172248</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>1597828</x:v>
+        <x:v>2683066</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.8973700220498</x:v>
+        <x:v>23.8890021294991</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>3700256</x:v>
+        <x:v>4669222</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.6295189371627</x:v>
+        <x:v>23.6671616524617</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>5298084</x:v>
+        <x:v>7352288</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>3.76408921440569</x:v>
+        <x:v>3.26142966994436</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-2102428</x:v>
+        <x:v>-1986156</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.425954314135</x:v>
+        <x:v>23.3674809419018</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>1035440</x:v>
+        <x:v>1332118</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>24.1204263669505</x:v>
+        <x:v>24.0515030673847</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>3182050</x:v>
+        <x:v>3325273</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.6972280699747</x:v>
+        <x:v>23.7103408030578</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>4217490</x:v>
+        <x:v>4657391</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>2.99636786069527</x:v>
+        <x:v>2.06598996012287</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-2146610</x:v>
+        <x:v>-1993155</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.4930939027898</x:v>
+        <x:v>23.4823262265544</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>6126187</x:v>
+        <x:v>9471041</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>23.990656002459</x:v>
+        <x:v>23.9808900336827</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>8423630</x:v>
+        <x:v>12054586</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.8565453854684</x:v>
+        <x:v>23.8752990320411</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>14549817</x:v>
+        <x:v>21525627</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>10.3370971923579</x:v>
+        <x:v>9.548635548819</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-2297443</x:v>
+        <x:v>-2583545</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.4989362006618</x:v>
+        <x:v>23.4882120233851</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>3204524</x:v>
+        <x:v>4388109</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>23.9994069274439</x:v>
+        <x:v>23.9598664694917</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>6109191</x:v>
+        <x:v>13036663</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>24.0178492299952</x:v>
+        <x:v>23.9519617070509</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>9313715</x:v>
+        <x:v>17424772</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>6.61704385539158</x:v>
+        <x:v>7.72952153027951</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-2904667</x:v>
+        <x:v>-8648554</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>24.0381953836648</x:v>
+        <x:v>23.9479509835</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -52,135 +52,135 @@
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
+    <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUPAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
   </x:si>
   <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUPAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
@@ -190,13 +190,13 @@
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>11859140</x:v>
+        <x:v>18704519</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>24.0292096443329</x:v>
+        <x:v>23.8344829790672</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>7578193</x:v>
+        <x:v>12811688</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.9691784320974</x:v>
+        <x:v>23.7990178543616</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>19437333</x:v>
+        <x:v>31516207</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>8.62228119339022</x:v>
+        <x:v>9.35796053099705</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>4280947</x:v>
+        <x:v>5892831</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>24.1354777463076</x:v>
+        <x:v>23.9115882129707</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>4499113</x:v>
+        <x:v>7005593</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.982317557802</x:v>
+        <x:v>23.8112802831168</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1204747</x:v>
+        <x:v>2481085</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.8660430459874</x:v>
+        <x:v>23.6956489345715</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>5703860</x:v>
+        <x:v>9486678</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2.53019716273476</x:v>
+        <x:v>2.81683510627653</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>3294366</x:v>
+        <x:v>4524508</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24.024839053375</x:v>
+        <x:v>23.8746885485912</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>6630871</x:v>
+        <x:v>10041790</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.9746088410456</x:v>
+        <x:v>23.843438914191</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>4410118</x:v>
+        <x:v>6195436</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.1670577129313</x:v>
+        <x:v>23.982975824405</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>11040989</x:v>
+        <x:v>16237226</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.89771471277095</x:v>
+        <x:v>4.82124387750338</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2220753</x:v>
+        <x:v>3846354</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.5924311589789</x:v>
+        <x:v>23.618682691319</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>5136593</x:v>
+        <x:v>7363819</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>24.0268385733755</x:v>
+        <x:v>23.8832374150132</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>3685990</x:v>
+        <x:v>5228002</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>24.1044185479568</x:v>
+        <x:v>23.9495302501843</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>8822583</x:v>
+        <x:v>12591821</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>3.91364347557477</x:v>
+        <x:v>3.73883075242461</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>1450603</x:v>
+        <x:v>2135817</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.8297074420413</x:v>
+        <x:v>23.7209673914766</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>3359911</x:v>
+        <x:v>22581496</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.9421525650111</x:v>
+        <x:v>23.699322902334</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1935461</x:v>
+        <x:v>21242684</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.1042438306163</x:v>
+        <x:v>23.6460323684099</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>5295372</x:v>
+        <x:v>43824180</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2.34899440204092</x:v>
+        <x:v>13.0125096190449</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1424450</x:v>
+        <x:v>1338812</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.7219122455759</x:v>
+        <x:v>24.5448740120808</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>2375969</x:v>
+        <x:v>3234180</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>24.312978217558</x:v>
+        <x:v>24.1040652231138</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>1330858</x:v>
+        <x:v>1914225</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.4691100896643</x:v>
+        <x:v>24.1771856094917</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>3706827</x:v>
+        <x:v>5148405</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.64432562477841</x:v>
+        <x:v>1.52869191357919</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1045111</x:v>
+        <x:v>1319955</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>24.1141578520201</x:v>
+        <x:v>23.9980245841418</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>7608421</x:v>
+        <x:v>4702928</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.9791506000282</x:v>
+        <x:v>23.8317102899716</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>6883616</x:v>
+        <x:v>3538486</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>24.1100405600696</x:v>
+        <x:v>23.8377637942235</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>14492037</x:v>
+        <x:v>8241414</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>6.42857834863534</x:v>
+        <x:v>2.44708466763169</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>724805</x:v>
+        <x:v>1164442</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>22.7360628410034</x:v>
+        <x:v>23.8133150070412</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>1340749</x:v>
+        <x:v>2160174</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.9125237656881</x:v>
+        <x:v>23.7412305745457</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>697170</x:v>
+        <x:v>1155731</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>24.1162925041233</x:v>
+        <x:v>23.8751992193054</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>2037919</x:v>
+        <x:v>3315905</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.904008315716596</x:v>
+        <x:v>0.984576225004988</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>643579</x:v>
+        <x:v>1004443</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.6917871484665</x:v>
+        <x:v>23.5870837331851</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>14289602</x:v>
+        <x:v>10758210</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.7975714556314</x:v>
+        <x:v>23.846115035905</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>13662028</x:v>
+        <x:v>9778274</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.7170953877397</x:v>
+        <x:v>23.9320565975564</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>27951630</x:v>
+        <x:v>20536484</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>12.399170898271</x:v>
+        <x:v>6.09780252799623</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>627574</x:v>
+        <x:v>979936</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>25.5495023719333</x:v>
+        <x:v>22.9885486868619</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1029827</x:v>
+        <x:v>1558033</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>24.0326218048599</x:v>
+        <x:v>23.8691193674291</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>515952</x:v>
+        <x:v>759990</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>24.0537816575247</x:v>
+        <x:v>23.8866317751232</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>1545779</x:v>
+        <x:v>2318023</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.685698043082224</x:v>
+        <x:v>0.688279771228288</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>513875</x:v>
+        <x:v>798043</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>24.0113764274781</x:v>
+        <x:v>23.8524420020196</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2524814</x:v>
+        <x:v>1221963</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.8336336133595</x:v>
+        <x:v>23.7021857049132</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>2141434</x:v>
+        <x:v>628255</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.8947803732533</x:v>
+        <x:v>23.8085658008297</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>4666248</x:v>
+        <x:v>1850218</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.06991887076765</x:v>
+        <x:v>0.549376611777563</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>383380</x:v>
+        <x:v>593708</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.4920880172764</x:v>
+        <x:v>23.5896155068361</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1290580</x:v>
+        <x:v>2040943</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.9405243420088</x:v>
+        <x:v>23.774844079317</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>964826</x:v>
+        <x:v>1691211</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.9678047776712</x:v>
+        <x:v>23.8106860120267</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>2255406</x:v>
+        <x:v>3732154</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.00048420929247</x:v>
+        <x:v>1.10817110154159</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>325754</x:v>
+        <x:v>349732</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.8597244942142</x:v>
+        <x:v>23.6015220188251</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>9538906</x:v>
+        <x:v>745750</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.8560198120268</x:v>
+        <x:v>23.8123632427501</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>9271584</x:v>
+        <x:v>435689</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.8560737186336</x:v>
+        <x:v>23.9260506583222</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>18810490</x:v>
+        <x:v>1181439</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>8.34421749966699</x:v>
+        <x:v>0.350799178714007</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>267322</x:v>
+        <x:v>310061</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.854150158076</x:v>
+        <x:v>23.6526128826493</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>523312</x:v>
+        <x:v>839172</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.9566376263347</x:v>
+        <x:v>23.5618634892646</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>288234</x:v>
+        <x:v>565985</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>24.1470408345306</x:v>
+        <x:v>24.3765774686386</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>811546</x:v>
+        <x:v>1405157</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.359996806834099</x:v>
+        <x:v>0.417226722297332</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>235078</x:v>
+        <x:v>273187</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.7231803129701</x:v>
+        <x:v>21.8739504787041</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>277969</x:v>
+        <x:v>1498578</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>24.2314007865393</x:v>
+        <x:v>23.6460912868398</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>59920</x:v>
+        <x:v>1232057</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>24.1033267287291</x:v>
+        <x:v>23.653414262992</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>337889</x:v>
+        <x:v>2730635</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.149885479152589</x:v>
+        <x:v>0.810794730297308</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>218049</x:v>
+        <x:v>266521</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>24.2665956168021</x:v>
+        <x:v>23.6122390799627</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>591339</x:v>
+        <x:v>697018</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.798737756879</x:v>
+        <x:v>23.751475860407</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>377409</x:v>
+        <x:v>454970</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.9736059274853</x:v>
+        <x:v>23.8872602922994</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>968748</x:v>
+        <x:v>1151988</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.429730645739021</x:v>
+        <x:v>0.342054430477063</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>213930</x:v>
+        <x:v>242048</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.4902404848726</x:v>
+        <x:v>23.4962461415988</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>2088526</x:v>
+        <x:v>314867</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.9081565621912</x:v>
+        <x:v>24.1380674464938</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>1876266</x:v>
+        <x:v>80850</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.9031906672809</x:v>
+        <x:v>23.9554678526851</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>3964792</x:v>
+        <x:v>395717</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.75875730982764</x:v>
+        <x:v>0.117498405421838</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>212260</x:v>
+        <x:v>234017</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.9520524435619</x:v>
+        <x:v>24.2011533640102</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>295604</x:v>
+        <x:v>505869</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>24.0993702082548</x:v>
+        <x:v>23.8850032739004</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>135445</x:v>
+        <x:v>275310</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>24.0233781008305</x:v>
+        <x:v>23.7617243843443</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>431049</x:v>
+        <x:v>781179</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.191210681328023</x:v>
+        <x:v>0.231951841465052</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>160159</x:v>
+        <x:v>230559</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>24.1636360377747</x:v>
+        <x:v>24.0322103275555</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>1611060</x:v>
+        <x:v>2516271</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.7142713722966</x:v>
+        <x:v>23.8474819295833</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>1451739</x:v>
+        <x:v>2325729</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.7386007677695</x:v>
+        <x:v>23.8420111958406</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>3062799</x:v>
+        <x:v>4842000</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>1.35863877090722</x:v>
+        <x:v>1.43771250427083</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>159321</x:v>
+        <x:v>190542</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.492580997177</x:v>
+        <x:v>23.9142569404302</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>489924</x:v>
+        <x:v>8383644</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>24.1296099265259</x:v>
+        <x:v>23.7997401953946</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>364629</x:v>
+        <x:v>8224826</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>24.0415175102345</x:v>
+        <x:v>23.8257152486315</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>854553</x:v>
+        <x:v>16608470</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.379074447129922</x:v>
+        <x:v>4.93147562903901</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>125295</x:v>
+        <x:v>158818</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>24.3859733062291</x:v>
+        <x:v>22.4545507759734</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>105414</x:v>
+        <x:v>2923804</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>24.9907521993639</x:v>
+        <x:v>23.7378403441866</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>10684</x:v>
+        <x:v>2773546</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.9284804716221</x:v>
+        <x:v>23.7774355149475</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>116098</x:v>
+        <x:v>5697350</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0515003576874573</x:v>
+        <x:v>1.69168759525142</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>94730</x:v>
+        <x:v>150258</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>25.1105591363342</x:v>
+        <x:v>23.0069705902738</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>2300212</x:v>
+        <x:v>2612576</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.8088144869799</x:v>
+        <x:v>23.6116145386528</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>2213865</x:v>
+        <x:v>2477727</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.8469042957495</x:v>
+        <x:v>23.6340214315128</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>4514077</x:v>
+        <x:v>5090303</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.00241675247398</x:v>
+        <x:v>1.51143995737862</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>86347</x:v>
+        <x:v>134849</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>22.832223586407</x:v>
+        <x:v>23.1999083826911</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>1413398</x:v>
+        <x:v>360836</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.9411439755554</x:v>
+        <x:v>23.7040546551742</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>1335090</x:v>
+        <x:v>230435</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.8574696740662</x:v>
+        <x:v>23.9052205765496</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>2748488</x:v>
+        <x:v>591271</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>1.21921234732454</x:v>
+        <x:v>0.175563343682923</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>78308</x:v>
+        <x:v>130401</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>25.3677252083187</x:v>
+        <x:v>23.3485691213811</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>573513</x:v>
+        <x:v>255673</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.8114635676758</x:v>
+        <x:v>23.6709754586493</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>509943</x:v>
+        <x:v>148312</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.8305420623237</x:v>
+        <x:v>23.9113524453695</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1083456</x:v>
+        <x:v>403985</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.480614407988266</x:v>
+        <x:v>0.119953384146603</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>63570</x:v>
+        <x:v>107361</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.6584205474421</x:v>
+        <x:v>23.3389108201453</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>178133</x:v>
+        <x:v>118975</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.8635592874502</x:v>
+        <x:v>24.8155937782539</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>122982</x:v>
+        <x:v>25032</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>24.241851417345</x:v>
+        <x:v>23.634389728203</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>301115</x:v>
+        <x:v>144007</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.133572759264231</x:v>
+        <x:v>0.0427593276750369</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>55151</x:v>
+        <x:v>93943</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.0200002818343</x:v>
+        <x:v>25.1303367583682</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>139221</x:v>
+        <x:v>406691</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.8270062235687</x:v>
+        <x:v>23.7363487948182</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>98273</x:v>
+        <x:v>326683</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>24.1187899341117</x:v>
+        <x:v>24.093571203933</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>237494</x:v>
+        <x:v>733374</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.105350875541568</x:v>
+        <x:v>0.217757325507458</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>40948</x:v>
+        <x:v>80008</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>23.1267409948349</x:v>
+        <x:v>22.2777635498817</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>1169559</x:v>
+        <x:v>11581118</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.8253634542567</x:v>
+        <x:v>23.8015067473751</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1143273</x:v>
+        <x:v>11506936</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.820441647407</x:v>
+        <x:v>23.7996606153569</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>2312832</x:v>
+        <x:v>23088054</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>1.02595802917361</x:v>
+        <x:v>6.85542832199092</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>26286</x:v>
+        <x:v>74182</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.0394305957921</x:v>
+        <x:v>24.0878743699837</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>22936</x:v>
+        <x:v>1605890</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.7887448489479</x:v>
+        <x:v>23.7592682706217</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1000</x:v>
+        <x:v>1538760</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>24.1599998474121</x:v>
+        <x:v>23.7606246163083</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>23936</x:v>
+        <x:v>3144650</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.010617862164783</x:v>
+        <x:v>0.933726275620663</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>21936</x:v>
+        <x:v>67130</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.7718203869464</x:v>
+        <x:v>23.7281779907365</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>263374</x:v>
+        <x:v>52866</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.8917105252602</x:v>
+        <x:v>23.7641844319209</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>246887</x:v>
+        <x:v>18528</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>25.297762595684</x:v>
+        <x:v>23.9458016644076</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>510261</x:v>
+        <x:v>71394</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.226348636616993</x:v>
+        <x:v>0.0211986878417826</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>16487</x:v>
+        <x:v>34338</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>2.83657754104567</x:v>
+        <x:v>23.6661879241595</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>13283</x:v>
+        <x:v>26200</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>24.7307761727278</x:v>
+        <x:v>23.7304156818827</x:v>
       </x:c>
       <x:c r="D31" s="0">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.8400001525879</x:v>
+        <x:v>24.1599998474121</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>14283</x:v>
+        <x:v>27200</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00633585082301119</x:v>
+        <x:v>0.00807636929288857</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>12283</x:v>
+        <x:v>25200</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>24.8032972197147</x:v>
+        <x:v>23.7133686911871</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>8500</x:v>
+        <x:v>24631</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.9006019500284</x:v>
+        <x:v>24.1874166047799</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>3288</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>24.1793186774799</x:v>
+        <x:v>23.789999961853</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>11788</x:v>
+        <x:v>26631</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00522908419111222</x:v>
+        <x:v>0.00790741877348954</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>5212</x:v>
+        <x:v>22631</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.7247729784511</x:v>
+        <x:v>24.2225380437731</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>7782</x:v>
+        <x:v>21725</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.7199124008057</x:v>
+        <x:v>23.808285305607</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>3473</x:v>
+        <x:v>1355</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>24.3728303203588</x:v>
+        <x:v>24.110214239029</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>11255</x:v>
+        <x:v>23080</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00499264867415745</x:v>
+        <x:v>0.00685303688528927</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>4309</x:v>
+        <x:v>20370</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.1936687399545</x:v>
+        <x:v>23.7882011767515</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>2587</x:v>
+        <x:v>10222</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>24.8133276853499</x:v>
+        <x:v>23.6418271681447</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>0</x:v>
+        <x:v>4396</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>0</x:v>
+        <x:v>24.1861645682928</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>2587</x:v>
+        <x:v>14618</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00114757726521949</x:v>
+        <x:v>0.00434045464424431</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>2587</x:v>
+        <x:v>5826</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>24.8133276853499</x:v>
+        <x:v>23.2310981583522</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>1100</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>24.2818180431019</x:v>
+        <x:v>24.8111149049183</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>545</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.2780184614549</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>1645</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000729711867524568</x:v>
+        <x:v>0.000769333560215966</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>555</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>24.2855491638184</x:v>
+        <x:v>24.8111149049183</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>16942</x:v>
+        <x:v>137435</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>24.2975870032699</x:v>
+        <x:v>23.9408807758888</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>16765</x:v>
+        <x:v>135713</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.9868149792369</x:v>
+        <x:v>23.7862267443993</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>33707</x:v>
+        <x:v>273148</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0149522175797268</x:v>
+        <x:v>0.0811045632211003</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>177</x:v>
+        <x:v>1722</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>53.7331405790512</x:v>
+        <x:v>36.1293607849139</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>0</x:v>
+        <x:v>9892</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0</x:v>
+        <x:v>23.868268935824</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>1</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>24.1399993896484</x:v>
+        <x:v>23.710011287016</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>1</x:v>
+        <x:v>18392</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>4.43593840440467E-07</x:v>
+        <x:v>0.0054610508836326</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-1</x:v>
+        <x:v>1392</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>24.1399993896484</x:v>
+        <x:v>24.8346410729419</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>170</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.9423530803007</x:v>
+        <x:v>23.2999992370605</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>965</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>24.3100934478285</x:v>
+        <x:v>24.1399993896484</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>1135</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.00050347900889993</x:v>
+        <x:v>0.000230414065120645</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-795</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>24.3887297528345</x:v>
+        <x:v>23.2989139655456</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>16359</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.7321458226916</x:v>
+        <x:v>24.2585963868258</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>20062</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.0173939830486</x:v>
+        <x:v>24.2780184614549</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>36421</x:v>
+        <x:v>1685</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.0161561312626822</x:v>
+        <x:v>0.000500319200680781</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-3703</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>25.2775545704857</x:v>
+        <x:v>24.2408064193084</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>126258</x:v>
+        <x:v>847597</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.9545138739352</x:v>
+        <x:v>23.6463453835199</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>134224</x:v>
+        <x:v>848008</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.7885906405437</x:v>
+        <x:v>23.9072896351532</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>260482</x:v>
+        <x:v>1695605</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.115548210745614</x:v>
+        <x:v>0.503468093928982</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-7966</x:v>
+        <x:v>-411</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>21.1587719609622</x:v>
+        <x:v>562.047350101517</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>108871</x:v>
+        <x:v>19191</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>24.2109950223874</x:v>
+        <x:v>23.7026821765797</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>123279</x:v>
+        <x:v>22127</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>24.1782116975861</x:v>
+        <x:v>23.9805196254453</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>232150</x:v>
+        <x:v>41318</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.102980310058254</x:v>
+        <x:v>0.0122683612663077</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-14408</x:v>
+        <x:v>-2936</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>23.9304914481106</x:v>
+        <x:v>25.7965885904245</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>242360</x:v>
+        <x:v>126871</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.9799359159947</x:v>
+        <x:v>24.1037705993761</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>259110</x:v>
+        <x:v>133423</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.2192132011797</x:v>
+        <x:v>24.1253636604629</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>501470</x:v>
+        <x:v>260294</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.222449003165681</x:v>
+        <x:v>0.0772878848795271</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-16750</x:v>
+        <x:v>-6552</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>27.6813769526695</x:v>
+        <x:v>24.5434853413457</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>387597</x:v>
+        <x:v>3886985</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.8587798373096</x:v>
+        <x:v>23.7024261278805</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>442968</x:v>
+        <x:v>4001194</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>24.2355428082166</x:v>
+        <x:v>23.7149306636134</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>830565</x:v>
+        <x:v>7888179</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.368433518085436</x:v>
+        <x:v>2.34220024457384</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-55371</x:v>
+        <x:v>-114209</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>26.8728836045654</x:v>
+        <x:v>24.1405095831877</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>517170</x:v>
+        <x:v>712498</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.6895485620731</x:v>
+        <x:v>23.5965095792499</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>576842</x:v>
+        <x:v>840367</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.7396653688717</x:v>
+        <x:v>23.6561651261305</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>1094012</x:v>
+        <x:v>1552865</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.485296984567956</x:v>
+        <x:v>0.461084970661816</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-59672</x:v>
+        <x:v>-127869</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>24.1740216661641</x:v>
+        <x:v>23.9885714000614</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>6040268</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.9098533140168</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>6149699</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>23.9330192649854</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>12189967</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>5.40739427637255</x:v>
+        <x:v>0.0593853652554047</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-109431</x:v>
+        <x:v>-200001</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>25.2117113387625</x:v>
+        <x:v>25.5</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1869,22 +1869,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>200001</x:v>
+        <x:v>402335</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.6149061518141</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>200001</x:v>
+        <x:v>402335</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.0887192116819338</x:v>
+        <x:v>0.11946345733288</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-200001</x:v>
+        <x:v>-402335</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.6149061518141</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>156596</x:v>
+        <x:v>213979</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.8575848956233</x:v>
+        <x:v>23.7100417286304</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>387177</x:v>
+        <x:v>645810</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>24.6267173975039</x:v>
+        <x:v>24.1468293967121</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>543773</x:v>
+        <x:v>859789</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.241214353397834</x:v>
+        <x:v>0.255293142572183</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-230581</x:v>
+        <x:v>-431831</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.1490634419068</x:v>
+        <x:v>24.3632645031044</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>0</x:v>
+        <x:v>1749904</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>0</x:v>
+        <x:v>23.8591951324779</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>316076</x:v>
+        <x:v>2249852</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>24.8882718238432</x:v>
+        <x:v>23.6902262668013</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>316076</x:v>
+        <x:v>3999756</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0.140209366711061</x:v>
+        <x:v>1.1876289168179</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-316076</x:v>
+        <x:v>-499948</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>24.8882718238432</x:v>
+        <x:v>23.0988061712657</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>532504</x:v>
+        <x:v>781574</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>24.3383149590904</x:v>
+        <x:v>24.059569597589</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1233120</x:v>
+        <x:v>1453208</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>25.0762874344235</x:v>
+        <x:v>24.8318128030978</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>1765624</x:v>
+        <x:v>2234782</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.783219930933859</x:v>
+        <x:v>0.663563408863974</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-700616</x:v>
+        <x:v>-671634</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.6371842666465</x:v>
+        <x:v>25.7304647639908</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>1578493</x:v>
+        <x:v>1944353</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.8945643965518</x:v>
+        <x:v>23.8184127462699</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2496941</x:v>
+        <x:v>2690536</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.2175164741394</x:v>
+        <x:v>24.1699637959189</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>4075434</x:v>
+        <x:v>4634889</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.80783741952165</x:v>
+        <x:v>1.37621599983629</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-918448</x:v>
+        <x:v>-746183</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>24.7725588867827</x:v>
+        <x:v>25.0860116528632</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>1556558</x:v>
+        <x:v>2482510</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>24.0525620956149</x:v>
+        <x:v>23.8262854611565</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2746826</x:v>
+        <x:v>3364414</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.7958340471932</x:v>
+        <x:v>23.7364164071411</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>4303384</x:v>
+        <x:v>5846924</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>1.90895463545006</x:v>
+        <x:v>1.73609990630343</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1190268</x:v>
+        <x:v>-881904</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.460101172248</x:v>
+        <x:v>23.4834400908033</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>2683066</x:v>
+        <x:v>2550933</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.8890021294991</x:v>
+        <x:v>23.8612098268074</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>4669222</x:v>
+        <x:v>3800289</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.6671616524617</x:v>
+        <x:v>23.711434958143</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>7352288</x:v>
+        <x:v>6351222</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>3.26142966994436</x:v>
+        <x:v>1.885838762247</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1986156</x:v>
+        <x:v>-1249356</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.3674809419018</x:v>
+        <x:v>23.4056248807538</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>1332118</x:v>
+        <x:v>13772365</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>24.0515030673847</x:v>
+        <x:v>23.8232008567516</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>3325273</x:v>
+        <x:v>16900580</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.7103408030578</x:v>
+        <x:v>23.7570964214607</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>4657391</x:v>
+        <x:v>30672945</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>2.06598996012287</x:v>
+        <x:v>9.10757467354632</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1993155</x:v>
+        <x:v>-3128215</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.4823262265544</x:v>
+        <x:v>23.466063224911</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>9471041</x:v>
+        <x:v>5040067</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>23.9808900336827</x:v>
+        <x:v>23.7624984086982</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>12054586</x:v>
+        <x:v>9097136</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.8752990320411</x:v>
+        <x:v>23.6396494557448</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>21525627</x:v>
+        <x:v>14137203</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>9.548635548819</x:v>
+        <x:v>4.19769383075486</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-2583545</x:v>
+        <x:v>-4057069</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.4882120233851</x:v>
+        <x:v>23.4870351044076</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>4388109</x:v>
+        <x:v>7235814</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>23.9598664694917</x:v>
+        <x:v>23.7845775793988</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>13036663</x:v>
+        <x:v>21523266</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.9519617070509</x:v>
+        <x:v>23.7582142054154</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>17424772</x:v>
+        <x:v>28759080</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>7.72952153027951</x:v>
+        <x:v>8.53929965454874</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-8648554</x:v>
+        <x:v>-14287452</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.9479509835</x:v>
+        <x:v>23.7448625965661</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -49,148 +49,148 @@
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
   </x:si>
   <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUPAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUPAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
     <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
   </x:si>
   <x:si>
     <x:t>A1 CAPITAL</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>18704519</x:v>
+        <x:v>22565846</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.8344829790672</x:v>
+        <x:v>23.8142238960013</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>12811688</x:v>
+        <x:v>15898279</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.7990178543616</x:v>
+        <x:v>23.7798191745496</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>31516207</x:v>
+        <x:v>38464125</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.35796053099705</x:v>
+        <x:v>9.54824548630155</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>5892831</x:v>
+        <x:v>6667567</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.9115882129707</x:v>
+        <x:v>23.8962591962173</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>7005593</x:v>
+        <x:v>8533345</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.8112802831168</x:v>
+        <x:v>23.7890653323845</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>2481085</x:v>
+        <x:v>3703204</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.6956489345715</x:v>
+        <x:v>23.7071609222536</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>9486678</x:v>
+        <x:v>12236549</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2.81683510627653</x:v>
+        <x:v>3.037572640926</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>4524508</x:v>
+        <x:v>4830141</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.8746885485912</x:v>
+        <x:v>23.8518603396553</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>10041790</x:v>
+        <x:v>11194827</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.843438914191</x:v>
+        <x:v>23.8274504632559</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>6195436</x:v>
+        <x:v>7174601</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.982975824405</x:v>
+        <x:v>23.9461149401649</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>16237226</x:v>
+        <x:v>18369428</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.82124387750338</x:v>
+        <x:v>4.55998434871303</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>3846354</x:v>
+        <x:v>4020226</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.618682691319</x:v>
+        <x:v>23.6156787184099</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>7363819</x:v>
+        <x:v>28190588</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.8832374150132</x:v>
+        <x:v>23.700740184509</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>5228002</x:v>
+        <x:v>26110266</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.9495302501843</x:v>
+        <x:v>23.6588923962251</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>12591821</x:v>
+        <x:v>54300854</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>3.73883075242461</x:v>
+        <x:v>13.4795184891849</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2135817</x:v>
+        <x:v>2080322</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.7209673914766</x:v>
+        <x:v>24.2259746835925</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>22581496</x:v>
+        <x:v>3821723</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.699322902334</x:v>
+        <x:v>24.0423415914134</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>21242684</x:v>
+        <x:v>2332849</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.6460323684099</x:v>
+        <x:v>24.0936567464137</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>43824180</x:v>
+        <x:v>6154572</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>13.0125096190449</x:v>
+        <x:v>1.52779672796711</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1338812</x:v>
+        <x:v>1488874</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>24.5448740120808</x:v>
+        <x:v>23.9619382073612</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>3234180</x:v>
+        <x:v>5523363</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>24.1040652231138</x:v>
+        <x:v>23.8089361496679</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>1914225</x:v>
+        <x:v>4079734</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.1771856094917</x:v>
+        <x:v>23.827688163356</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>5148405</x:v>
+        <x:v>9603097</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.52869191357919</x:v>
+        <x:v>2.38385060325085</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1319955</x:v>
+        <x:v>1443629</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.9980245841418</x:v>
+        <x:v>23.755942459591</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>4702928</x:v>
+        <x:v>12433917</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.8317102899716</x:v>
+        <x:v>23.8261058264723</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>3538486</x:v>
+        <x:v>11335509</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.8377637942235</x:v>
+        <x:v>23.9020113797091</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>8241414</x:v>
+        <x:v>23769426</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.44708466763169</x:v>
+        <x:v>5.90046737099775</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1164442</x:v>
+        <x:v>1098408</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.8133150070412</x:v>
+        <x:v>23.0427647711766</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>2160174</x:v>
+        <x:v>2501399</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.7412305745457</x:v>
+        <x:v>23.7323083437636</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1155731</x:v>
+        <x:v>1468517</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.8751992193054</x:v>
+        <x:v>23.8322059345395</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>3315905</x:v>
+        <x:v>3969916</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.984576225004988</x:v>
+        <x:v>0.985482772011486</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>1004443</x:v>
+        <x:v>1032882</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.5870837331851</x:v>
+        <x:v>23.5902772982873</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>10758210</x:v>
+        <x:v>1748187</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.846115035905</x:v>
+        <x:v>23.8506202361658</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>9778274</x:v>
+        <x:v>877555</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.9320565975564</x:v>
+        <x:v>23.8658392272005</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>20536484</x:v>
+        <x:v>2625742</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>6.09780252799623</x:v>
+        <x:v>0.65180812509559</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>979936</x:v>
+        <x:v>870632</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.9885486868619</x:v>
+        <x:v>23.8352802283582</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1558033</x:v>
+        <x:v>10457595</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.8691193674291</x:v>
+        <x:v>23.7880373806841</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>759990</x:v>
+        <x:v>9672971</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.8866317751232</x:v>
+        <x:v>23.8105469564099</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2318023</x:v>
+        <x:v>20130566</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.688279771228288</x:v>
+        <x:v>4.99716517524305</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>798043</x:v>
+        <x:v>784624</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.8524420020196</x:v>
+        <x:v>23.5105357069927</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1221963</x:v>
+        <x:v>1504382</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.7021857049132</x:v>
+        <x:v>23.6963748332123</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>628255</x:v>
+        <x:v>903365</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.8085658008297</x:v>
+        <x:v>23.7946430976045</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>1850218</x:v>
+        <x:v>2407747</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.549376611777563</x:v>
+        <x:v>0.597693550156311</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>593708</x:v>
+        <x:v>601017</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.5896155068361</x:v>
+        <x:v>23.5486716722988</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>2040943</x:v>
+        <x:v>941179</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.774844079317</x:v>
+        <x:v>23.7812326905526</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1691211</x:v>
+        <x:v>624111</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.8106860120267</x:v>
+        <x:v>23.8941583502973</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>3732154</x:v>
+        <x:v>1565290</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.10817110154159</x:v>
+        <x:v>0.388563971681481</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>349732</x:v>
+        <x:v>317068</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.6015220188251</x:v>
+        <x:v>23.5589518346198</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>745750</x:v>
+        <x:v>2279592</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.8123632427501</x:v>
+        <x:v>23.7654636072163</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>435689</x:v>
+        <x:v>1974326</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.9260506583222</x:v>
+        <x:v>23.8012852035572</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1181439</x:v>
+        <x:v>4253918</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.350799178714007</x:v>
+        <x:v>1.0559827720661</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>310061</x:v>
+        <x:v>305266</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.6526128826493</x:v>
+        <x:v>23.5337853036475</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>839172</x:v>
+        <x:v>4113763</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.5618634892646</x:v>
+        <x:v>23.7160530401126</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>565985</x:v>
+        <x:v>3811447</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>24.3765774686386</x:v>
+        <x:v>23.7507692942051</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1405157</x:v>
+        <x:v>7925210</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.417226722297332</x:v>
+        <x:v>1.9673358125394</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>273187</x:v>
+        <x:v>302316</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>21.8739504787041</x:v>
+        <x:v>23.2783680928653</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>1498578</x:v>
+        <x:v>1917118</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.6460912868398</x:v>
+        <x:v>23.6623715678024</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1232057</x:v>
+        <x:v>1633109</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.653414262992</x:v>
+        <x:v>23.6761410736159</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>2730635</x:v>
+        <x:v>3550227</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.810794730297308</x:v>
+        <x:v>0.881300144695763</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>266521</x:v>
+        <x:v>284009</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.6122390799627</x:v>
+        <x:v>23.5831941337439</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>697018</x:v>
+        <x:v>367153</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.751475860407</x:v>
+        <x:v>24.0750719335851</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>454970</x:v>
+        <x:v>94163</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.8872602922994</x:v>
+        <x:v>23.9254880524565</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>1151988</x:v>
+        <x:v>461316</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.342054430477063</x:v>
+        <x:v>0.114516017581544</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>242048</x:v>
+        <x:v>272990</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.4962461415988</x:v>
+        <x:v>24.1266682081692</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>314867</x:v>
+        <x:v>579920</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>24.1380674464938</x:v>
+        <x:v>23.8547002281546</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>80850</x:v>
+        <x:v>309229</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.9554678526851</x:v>
+        <x:v>23.7554747112514</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>395717</x:v>
+        <x:v>889149</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.117498405421838</x:v>
+        <x:v>0.220720292633708</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>234017</x:v>
+        <x:v>270691</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>24.2011533640102</x:v>
+        <x:v>23.9680523801156</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>505869</x:v>
+        <x:v>763849</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.8850032739004</x:v>
+        <x:v>23.7484019791011</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>275310</x:v>
+        <x:v>524129</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.7617243843443</x:v>
+        <x:v>23.8595298217814</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>781179</x:v>
+        <x:v>1287978</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.231951841465052</x:v>
+        <x:v>0.319724681764</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>230559</x:v>
+        <x:v>239720</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>24.0322103275555</x:v>
+        <x:v>23.5054296569913</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>2516271</x:v>
+        <x:v>2754720</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.8474819295833</x:v>
+        <x:v>23.8383807678751</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>2325729</x:v>
+        <x:v>2521326</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.8420111958406</x:v>
+        <x:v>23.8373412031887</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>4842000</x:v>
+        <x:v>5276046</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>1.43771250427083</x:v>
+        <x:v>1.30971346430003</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>190542</x:v>
+        <x:v>233394</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.9142569404302</x:v>
+        <x:v>23.8496110543108</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>8383644</x:v>
+        <x:v>3852137</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.7997401953946</x:v>
+        <x:v>23.7720960868028</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>8224826</x:v>
+        <x:v>3619032</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.8257152486315</x:v>
+        <x:v>23.7359764065427</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>16608470</x:v>
+        <x:v>7471169</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>4.93147562903901</x:v>
+        <x:v>1.85462572414285</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>158818</x:v>
+        <x:v>233105</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.4545507759734</x:v>
+        <x:v>24.332866034642</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>2923804</x:v>
+        <x:v>8266181</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.7378403441866</x:v>
+        <x:v>23.865501755937</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>2773546</x:v>
+        <x:v>8092882</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.7774355149475</x:v>
+        <x:v>23.8715722882523</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>5697350</x:v>
+        <x:v>16359063</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.69168759525142</x:v>
+        <x:v>4.06093598775152</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>150258</x:v>
+        <x:v>173299</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.0069705902738</x:v>
+        <x:v>23.5820142476113</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>2612576</x:v>
+        <x:v>2985333</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.6116145386528</x:v>
+        <x:v>23.6115247215684</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>2477727</x:v>
+        <x:v>2834699</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.6340214315128</x:v>
+        <x:v>23.6384208397059</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>5090303</x:v>
+        <x:v>5820032</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>1.51143995737862</x:v>
+        <x:v>1.44475129160304</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>134849</x:v>
+        <x:v>150634</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.1999083826911</x:v>
+        <x:v>23.1053813595893</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>360836</x:v>
+        <x:v>386670</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.7040546551742</x:v>
+        <x:v>23.7030505904265</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>230435</x:v>
+        <x:v>267668</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.9052205765496</x:v>
+        <x:v>23.8822790135228</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>591271</x:v>
+        <x:v>654338</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.175563343682923</x:v>
+        <x:v>0.162431352721935</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>130401</x:v>
+        <x:v>119002</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.3485691213811</x:v>
+        <x:v>23.2999169157544</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>255673</x:v>
+        <x:v>340779</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.6709754586493</x:v>
+        <x:v>23.6671812553229</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>148312</x:v>
+        <x:v>242820</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.9113524453695</x:v>
+        <x:v>23.8405255359477</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>403985</x:v>
+        <x:v>583599</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.119953384146603</x:v>
+        <x:v>0.144871266863866</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>107361</x:v>
+        <x:v>97959</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.3389108201453</x:v>
+        <x:v>23.2374968136555</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>118975</x:v>
+        <x:v>119025</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>24.8155937782539</x:v>
+        <x:v>24.8150663284273</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>25032</x:v>
+        <x:v>25666</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.634389728203</x:v>
+        <x:v>23.6371208483121</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>144007</x:v>
+        <x:v>144691</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0427593276750369</x:v>
+        <x:v>0.0359177594097996</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>93943</x:v>
+        <x:v>93359</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>25.1303367583682</x:v>
+        <x:v>25.1389038662398</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>406691</x:v>
+        <x:v>12121819</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.7363487948182</x:v>
+        <x:v>23.7987595191594</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>326683</x:v>
+        <x:v>12033747</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>24.093571203933</x:v>
+        <x:v>23.7971082248989</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>733374</x:v>
+        <x:v>24155566</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.217757325507458</x:v>
+        <x:v>5.99632187209664</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>80008</x:v>
+        <x:v>88072</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>22.2777635498817</x:v>
+        <x:v>24.0243846594188</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>11581118</x:v>
+        <x:v>861726</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.8015067473751</x:v>
+        <x:v>23.5643978066881</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>11506936</x:v>
+        <x:v>790439</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.7996606153569</x:v>
+        <x:v>24.2277725098554</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>23088054</x:v>
+        <x:v>1652165</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>6.85542832199092</x:v>
+        <x:v>0.410129620883756</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>74182</x:v>
+        <x:v>71287</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.0878743699837</x:v>
+        <x:v>16.2088177290186</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1605890</x:v>
+        <x:v>48936</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.7592682706217</x:v>
+        <x:v>23.788965528456</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1538760</x:v>
+        <x:v>2395</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.7606246163083</x:v>
+        <x:v>23.9633155806826</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>3144650</x:v>
+        <x:v>51331</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.933726275620663</x:v>
+        <x:v>0.0127422887965694</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>67130</x:v>
+        <x:v>46541</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.7281779907365</x:v>
+        <x:v>23.779993474244</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>52866</x:v>
+        <x:v>1798705</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.7641844319209</x:v>
+        <x:v>23.7496479718054</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>18528</x:v>
+        <x:v>1756350</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.9458016644076</x:v>
+        <x:v>23.75285716173</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>71394</x:v>
+        <x:v>3555055</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0211986878417826</x:v>
+        <x:v>0.88249863625661</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>34338</x:v>
+        <x:v>42355</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>23.6661879241595</x:v>
+        <x:v>23.6165713403797</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1443,7 +1443,7 @@
         <x:v>27200</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00807636929288857</x:v>
+        <x:v>0.00675206513153236</x:v>
       </x:c>
       <x:c r="H31" s="0">
         <x:v>25200</x:v>
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>24631</x:v>
+        <x:v>26631</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>24.1874166047799</x:v>
+        <x:v>24.1463053989328</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.789999961853</x:v>
+        <x:v>23.7733332316081</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>26631</x:v>
+        <x:v>29631</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00790741877348954</x:v>
+        <x:v>0.00735553095266307</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>22631</x:v>
+        <x:v>23631</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>24.2225380437731</x:v>
+        <x:v>24.193654918715</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>21725</x:v>
+        <x:v>1266977</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.808285305607</x:v>
+        <x:v>23.6712955236568</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>1355</x:v>
+        <x:v>1254288</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>24.110214239029</x:v>
+        <x:v>23.6678482526805</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>23080</x:v>
+        <x:v>2521265</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00685303688528927</x:v>
+        <x:v>0.625872996097535</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>20370</x:v>
+        <x:v>12689</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.7882011767515</x:v>
+        <x:v>24.0120529212684</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>10222</x:v>
+        <x:v>52866</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.6418271681447</x:v>
+        <x:v>23.7641844319209</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>4396</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>24.1861645682928</x:v>
+        <x:v>23.8317126079002</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>14618</x:v>
+        <x:v>98940</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00434045464424431</x:v>
+        <x:v>0.024560636915949</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>5826</x:v>
+        <x:v>6792</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.2310981583522</x:v>
+        <x:v>23.3061023971638</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>2591</x:v>
+        <x:v>10222</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>24.8111149049183</x:v>
+        <x:v>23.6418271681447</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>0</x:v>
+        <x:v>24.1504549686209</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>2591</x:v>
+        <x:v>15056</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000769333560215966</x:v>
+        <x:v>0.00373746664045409</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>2591</x:v>
+        <x:v>5388</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>24.8111149049183</x:v>
+        <x:v>23.18549702941</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>137435</x:v>
+        <x:v>12392</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.9408807758888</x:v>
+        <x:v>23.8867748567102</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>135713</x:v>
+        <x:v>8989</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.7862267443993</x:v>
+        <x:v>23.7093732375326</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>273148</x:v>
+        <x:v>21381</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0811045632211003</x:v>
+        <x:v>0.00530757002122402</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>1722</x:v>
+        <x:v>3403</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>36.1293607849139</x:v>
+        <x:v>24.3553799565596</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>9892</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.868268935824</x:v>
+        <x:v>24.661509006279</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>8500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.710011287016</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>18392</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.0054610508836326</x:v>
+        <x:v>0.000766309744891191</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>1392</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>24.8346410729419</x:v>
+        <x:v>24.661509006279</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>775</x:v>
+        <x:v>166149</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.2999992370605</x:v>
+        <x:v>23.9121042458372</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>1</x:v>
+        <x:v>164345</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>24.1399993896484</x:v>
+        <x:v>23.7580361624239</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>776</x:v>
+        <x:v>330494</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000230414065120645</x:v>
+        <x:v>0.0820410666757594</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>774</x:v>
+        <x:v>1804</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.2989139655456</x:v>
+        <x:v>37.9477578869416</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>1140</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>24.2585963868258</x:v>
+        <x:v>23.2999992370605</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>545</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.2780184614549</x:v>
+        <x:v>24.1399993896484</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>1685</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.000500319200680781</x:v>
+        <x:v>0.0001926324463996</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>595</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>24.2408064193084</x:v>
+        <x:v>23.2989139655456</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>847597</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.6463453835199</x:v>
+        <x:v>24.2585963868258</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>848008</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.9072896351532</x:v>
+        <x:v>24.1270555421164</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>1695605</x:v>
+        <x:v>1877</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.503468093928982</x:v>
+        <x:v>0.000465942141613465</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>562.047350101517</x:v>
+        <x:v>24.4991561946443</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>19191</x:v>
+        <x:v>4573161</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.7026821765797</x:v>
+        <x:v>23.705426709038</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>22127</x:v>
+        <x:v>4573294</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.9805196254453</x:v>
+        <x:v>23.721985580211</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>41318</x:v>
+        <x:v>9146455</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0122683612663077</x:v>
+        <x:v>2.2704948486261</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-2936</x:v>
+        <x:v>-133</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>25.7965885904245</x:v>
+        <x:v>593.093292738262</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>126871</x:v>
+        <x:v>34838</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>24.1037705993761</x:v>
+        <x:v>23.681148559329</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>133423</x:v>
+        <x:v>37779</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.1253636604629</x:v>
+        <x:v>23.8544343909843</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>260294</x:v>
+        <x:v>72617</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.0772878848795271</x:v>
+        <x:v>0.0180262762373708</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-6552</x:v>
+        <x:v>-2941</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>24.5434853413457</x:v>
+        <x:v>25.9071143648731</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>3886985</x:v>
+        <x:v>126871</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.7024261278805</x:v>
+        <x:v>24.1037705993761</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>4001194</x:v>
+        <x:v>133423</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.7149306636134</x:v>
+        <x:v>24.1253636604629</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>7888179</x:v>
+        <x:v>260294</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>2.34220024457384</x:v>
+        <x:v>0.0646147809318781</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-114209</x:v>
+        <x:v>-6552</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>24.1405095831877</x:v>
+        <x:v>24.5434853413457</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>712498</x:v>
+        <x:v>1116468</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.5965095792499</x:v>
+        <x:v>23.6492183052909</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>840367</x:v>
+        <x:v>1191094</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.6561651261305</x:v>
+        <x:v>23.8404828768215</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>1552865</x:v>
+        <x:v>2307562</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.461084970661816</x:v>
+        <x:v>0.572823857317981</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-127869</x:v>
+        <x:v>-74626</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>23.9885714000614</x:v>
+        <x:v>26.7019624368618</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,10 +1834,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>0</x:v>
+        <x:v>23.6800003051758</x:v>
       </x:c>
       <x:c r="D45" s="0">
         <x:v>200001</x:v>
@@ -1846,16 +1846,16 @@
         <x:v>25.5</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>200001</x:v>
+        <x:v>200101</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.0593853652554047</x:v>
+        <x:v>0.0496726097384102</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-200001</x:v>
+        <x:v>-199901</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>25.5</x:v>
+        <x:v>25.5009104505204</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1869,22 +1869,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>402335</x:v>
+        <x:v>506001</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.6149061518141</x:v>
+        <x:v>24.440536134811</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>402335</x:v>
+        <x:v>506001</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.11946345733288</x:v>
+        <x:v>0.125608518699283</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-402335</x:v>
+        <x:v>-506001</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>24.6149061518141</x:v>
+        <x:v>24.440536134811</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>213979</x:v>
+        <x:v>2061245</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.7100417286304</x:v>
+        <x:v>23.8471927000453</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>645810</x:v>
+        <x:v>2650815</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>24.1468293967121</x:v>
+        <x:v>23.6940917471711</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>859789</x:v>
+        <x:v>4712060</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.255293142572183</x:v>
+        <x:v>1.16971088322384</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-431831</x:v>
+        <x:v>-589570</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>24.3632645031044</x:v>
+        <x:v>23.1588226975128</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>1749904</x:v>
+        <x:v>3245453</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.8591951324779</x:v>
+        <x:v>23.8583327019187</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>2249852</x:v>
+        <x:v>3883127</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.6902262668013</x:v>
+        <x:v>23.7130592435746</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>3999756</x:v>
+        <x:v>7128580</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.1876289168179</x:v>
+        <x:v>1.76958222262276</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-499948</x:v>
+        <x:v>-637674</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.0988061712657</x:v>
+        <x:v>22.9736874310134</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>781574</x:v>
+        <x:v>2231772</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>24.059569597589</x:v>
+        <x:v>23.8139750659987</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1453208</x:v>
+        <x:v>2909752</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>24.8318128030978</x:v>
+        <x:v>24.1338706498754</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>2234782</x:v>
+        <x:v>5141524</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.663563408863974</x:v>
+        <x:v>1.27632003394621</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-671634</x:v>
+        <x:v>-677980</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.7304647639908</x:v>
+        <x:v>25.1869017230926</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>1944353</x:v>
+        <x:v>886841</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.8184127462699</x:v>
+        <x:v>24.0139844672822</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2690536</x:v>
+        <x:v>1567924</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.1699637959189</x:v>
+        <x:v>24.7522017820063</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>4634889</x:v>
+        <x:v>2454765</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.37621599983629</x:v>
+        <x:v>0.609365189801693</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-746183</x:v>
+        <x:v>-681083</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>25.0860116528632</x:v>
+        <x:v>25.7134376102494</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2482510</x:v>
+        <x:v>431762</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.8262854611565</x:v>
+        <x:v>23.7334329341673</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>3364414</x:v>
+        <x:v>1346522</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.7364164071411</x:v>
+        <x:v>23.6630719108366</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>5846924</x:v>
+        <x:v>1778284</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>1.73609990630343</x:v>
+        <x:v>0.441437109939776</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-881904</x:v>
+        <x:v>-914760</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.4834400908033</x:v>
+        <x:v>23.629861870875</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>2550933</x:v>
+        <x:v>372160</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.8612098268074</x:v>
+        <x:v>23.7744762006189</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>3800289</x:v>
+        <x:v>1784801</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.711434958143</x:v>
+        <x:v>23.7954454730493</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>6351222</x:v>
+        <x:v>2156961</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>1.885838762247</x:v>
+        <x:v>0.535439013168205</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1249356</x:v>
+        <x:v>-1412641</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.4056248807538</x:v>
+        <x:v>23.8009698238417</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>13772365</x:v>
+        <x:v>15923862</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>23.8232008567516</x:v>
+        <x:v>23.8064077359706</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>16900580</x:v>
+        <x:v>19047325</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.7570964214607</x:v>
+        <x:v>23.7563001534872</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>30672945</x:v>
+        <x:v>34971187</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>9.10757467354632</x:v>
+        <x:v>8.68116663055139</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-3128215</x:v>
+        <x:v>-3123463</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.466063224911</x:v>
+        <x:v>23.5008445170286</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>5040067</x:v>
+        <x:v>5747426</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>23.7624984086982</x:v>
+        <x:v>23.762484491189</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>9097136</x:v>
+        <x:v>11228552</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.6396494557448</x:v>
+        <x:v>23.6604820537503</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>14137203</x:v>
+        <x:v>16975978</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>4.19769383075486</x:v>
+        <x:v>4.21407754145075</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-4057069</x:v>
+        <x:v>-5481126</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.4870351044076</x:v>
+        <x:v>23.5535238373183</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>7235814</x:v>
+        <x:v>10127683</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>23.7845775793988</x:v>
+        <x:v>23.7716503260081</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>21523266</x:v>
+        <x:v>24161792</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.7582142054154</x:v>
+        <x:v>23.7527968218313</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>28759080</x:v>
+        <x:v>34289475</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>8.53929965454874</x:v>
+        <x:v>8.5119400193401</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-14287452</x:v>
+        <x:v>-14034109</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.7448625965661</x:v>
+        <x:v>23.7391912332084</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -73,118 +73,121 @@
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AKTIF </x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUPAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUPAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
     <x:t>ATA</x:t>
@@ -550,7 +553,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I55"/>
+  <x:dimension ref="A1:I56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -587,28 +590,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>22565846</x:v>
+        <x:v>24513877</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.8142238960013</x:v>
+        <x:v>23.82</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>15898279</x:v>
+        <x:v>17987621</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.7798191745496</x:v>
+        <x:v>23.794</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>38464125</x:v>
+        <x:v>42501498</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.54824548630155</x:v>
+        <x:v>9.67820148756046</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>6667567</x:v>
+        <x:v>6526256</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.8962591962173</x:v>
+        <x:v>23.891</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +619,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>8533345</x:v>
+        <x:v>9580036</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.7890653323845</x:v>
+        <x:v>23.799</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>3703204</x:v>
+        <x:v>4709508</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.7071609222536</x:v>
+        <x:v>23.743</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>12236549</x:v>
+        <x:v>14289544</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>3.037572640926</x:v>
+        <x:v>3.25393439067396</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>4830141</x:v>
+        <x:v>4870528</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.8518603396553</x:v>
+        <x:v>23.854</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +648,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>11194827</x:v>
+        <x:v>11748385</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.8274504632559</x:v>
+        <x:v>23.83</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>7174601</x:v>
+        <x:v>7710243</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.9461149401649</x:v>
+        <x:v>23.943</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>18369428</x:v>
+        <x:v>19458628</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.55998434871303</x:v>
+        <x:v>4.43100905420994</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>4020226</x:v>
+        <x:v>4038142</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.6156787184099</x:v>
+        <x:v>23.614</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +677,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>28190588</x:v>
+        <x:v>31090507</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.700740184509</x:v>
+        <x:v>23.717</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>26110266</x:v>
+        <x:v>28652634</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.6588923962251</x:v>
+        <x:v>23.679</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>54300854</x:v>
+        <x:v>59743141</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.4795184891849</x:v>
+        <x:v>13.6043712176388</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2080322</x:v>
+        <x:v>2437873</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.2259746835925</x:v>
+        <x:v>24.174</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +706,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>3821723</x:v>
+        <x:v>4160441</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.0423415914134</x:v>
+        <x:v>24.031</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>2332849</x:v>
+        <x:v>2625629</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.0936567464137</x:v>
+        <x:v>24.076</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>6154572</x:v>
+        <x:v>6786070</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.52779672796711</x:v>
+        <x:v>1.54528559837325</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1488874</x:v>
+        <x:v>1534812</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.9619382073612</x:v>
+        <x:v>23.955</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +735,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>5523363</x:v>
+        <x:v>5991810</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.8089361496679</x:v>
+        <x:v>23.814</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>4079734</x:v>
+        <x:v>4583305</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.827688163356</x:v>
+        <x:v>23.836</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>9603097</x:v>
+        <x:v>10575115</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2.38385060325085</x:v>
+        <x:v>2.4081055619292</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1443629</x:v>
+        <x:v>1408505</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.755942459591</x:v>
+        <x:v>23.742</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +764,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>12433917</x:v>
+        <x:v>13667540</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.8261058264723</x:v>
+        <x:v>23.836</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>11335509</x:v>
+        <x:v>12328852</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.9020113797091</x:v>
+        <x:v>23.902</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>23769426</x:v>
+        <x:v>25996392</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>5.90046737099775</x:v>
+        <x:v>5.9197518102916</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1098408</x:v>
+        <x:v>1338688</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.0427647711766</x:v>
+        <x:v>23.228</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +793,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>2501399</x:v>
+        <x:v>2787964</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.7323083437636</x:v>
+        <x:v>23.75</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1468517</x:v>
+        <x:v>1634529</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.8322059345395</x:v>
+        <x:v>23.836</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>3969916</x:v>
+        <x:v>4422493</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.985482772011486</x:v>
+        <x:v>1.00706517053412</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>1032882</x:v>
+        <x:v>1153435</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.5902772982873</x:v>
+        <x:v>23.627</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +822,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1748187</x:v>
+        <x:v>1896120</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.8506202361658</x:v>
+        <x:v>23.854</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>877555</x:v>
+        <x:v>1008632</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.8658392272005</x:v>
+        <x:v>23.869</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>2625742</x:v>
+        <x:v>2904752</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.65180812509559</x:v>
+        <x:v>0.661453747521893</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>870632</x:v>
+        <x:v>887488</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.8352802283582</x:v>
+        <x:v>23.836</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +851,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>10457595</x:v>
+        <x:v>11370071</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.7880373806841</x:v>
+        <x:v>23.795</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>9672971</x:v>
+        <x:v>10612309</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.8105469564099</x:v>
+        <x:v>23.818</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>20130566</x:v>
+        <x:v>21982380</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>4.99716517524305</x:v>
+        <x:v>5.00570362993134</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>784624</x:v>
+        <x:v>757762</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.5105357069927</x:v>
+        <x:v>23.485</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +880,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1504382</x:v>
+        <x:v>1580345</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.6963748332123</x:v>
+        <x:v>23.702</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>903365</x:v>
+        <x:v>958111</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.7946430976045</x:v>
+        <x:v>23.804</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>2407747</x:v>
+        <x:v>2538456</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.597693550156311</x:v>
+        <x:v>0.578042887695553</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>601017</x:v>
+        <x:v>622234</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.5486716722988</x:v>
+        <x:v>23.545</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +909,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>941179</x:v>
+        <x:v>2187783</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.7812326905526</x:v>
+        <x:v>23.696</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>624111</x:v>
+        <x:v>1742655</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.8941583502973</x:v>
+        <x:v>23.692</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>1565290</x:v>
+        <x:v>3930438</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.388563971681481</x:v>
+        <x:v>0.895017180297132</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>317068</x:v>
+        <x:v>445128</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.5589518346198</x:v>
+        <x:v>23.712</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +938,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>2279592</x:v>
+        <x:v>8979281</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.7654636072163</x:v>
+        <x:v>23.869</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1974326</x:v>
+        <x:v>8569667</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.8012852035572</x:v>
+        <x:v>23.872</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>4253918</x:v>
+        <x:v>17548948</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>1.0559827720661</x:v>
+        <x:v>3.99614749199478</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>305266</x:v>
+        <x:v>409614</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.5337853036475</x:v>
+        <x:v>23.801</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +967,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>4113763</x:v>
+        <x:v>2418627</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.7160530401126</x:v>
+        <x:v>23.779</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>3811447</x:v>
+        <x:v>2111776</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.7507692942051</x:v>
+        <x:v>23.812</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>7925210</x:v>
+        <x:v>4530403</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>1.9673358125394</x:v>
+        <x:v>1.03163782730313</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>302316</x:v>
+        <x:v>306851</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.2783680928653</x:v>
+        <x:v>23.553</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +996,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>1917118</x:v>
+        <x:v>394468</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.6623715678024</x:v>
+        <x:v>24.069</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1633109</x:v>
+        <x:v>105888</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.6761410736159</x:v>
+        <x:v>23.921</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>3550227</x:v>
+        <x:v>500356</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.881300144695763</x:v>
+        <x:v>0.113938247153307</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>284009</x:v>
+        <x:v>288580</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.5831941337439</x:v>
+        <x:v>24.124</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1025,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>367153</x:v>
+        <x:v>4785216</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>24.0750719335851</x:v>
+        <x:v>23.732</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>94163</x:v>
+        <x:v>4502582</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.9254880524565</x:v>
+        <x:v>23.766</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>461316</x:v>
+        <x:v>9287798</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.114516017581544</x:v>
+        <x:v>2.11496499299298</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>272990</x:v>
+        <x:v>282634</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>24.1266682081692</x:v>
+        <x:v>23.191</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1054,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>579920</x:v>
+        <x:v>618997</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.8547002281546</x:v>
+        <x:v>23.857</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>309229</x:v>
+        <x:v>343702</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.7554747112514</x:v>
+        <x:v>23.764</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>889149</x:v>
+        <x:v>962699</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.220720292633708</x:v>
+        <x:v>0.219220388276031</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>270691</x:v>
+        <x:v>275295</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.9680523801156</x:v>
+        <x:v>23.973</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1083,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>763849</x:v>
+        <x:v>3100439</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.7484019791011</x:v>
+        <x:v>23.841</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>524129</x:v>
+        <x:v>2843039</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.8595298217814</x:v>
+        <x:v>23.847</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>1287978</x:v>
+        <x:v>5943478</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.319724681764</x:v>
+        <x:v>1.35341529893565</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>239720</x:v>
+        <x:v>257400</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.5054296569913</x:v>
+        <x:v>23.774</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1112,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>2754720</x:v>
+        <x:v>1046625</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.8383807678751</x:v>
+        <x:v>23.785</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>2521326</x:v>
+        <x:v>798221</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.8373412031887</x:v>
+        <x:v>23.9</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>5276046</x:v>
+        <x:v>1844846</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>1.30971346430003</x:v>
+        <x:v>0.420097929289927</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>233394</x:v>
+        <x:v>248404</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.8496110543108</x:v>
+        <x:v>23.418</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1141,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>3852137</x:v>
+        <x:v>815935</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.7720960868028</x:v>
+        <x:v>23.761</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>3619032</x:v>
+        <x:v>610645</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.7359764065427</x:v>
+        <x:v>23.858</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>7471169</x:v>
+        <x:v>1426580</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>1.85462572414285</x:v>
+        <x:v>0.324852754087021</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>233105</x:v>
+        <x:v>205290</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>24.332866034642</x:v>
+        <x:v>23.475</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1170,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>8266181</x:v>
+        <x:v>3015463</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.865501755937</x:v>
+        <x:v>23.614</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>8092882</x:v>
+        <x:v>2877873</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.8715722882523</x:v>
+        <x:v>23.643</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>16359063</x:v>
+        <x:v>5893336</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>4.06093598775152</x:v>
+        <x:v>1.34199724541224</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>173299</x:v>
+        <x:v>137590</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.5820142476113</x:v>
+        <x:v>23.022</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1199,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>2985333</x:v>
+        <x:v>397092</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.6115247215684</x:v>
+        <x:v>23.708</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>2834699</x:v>
+        <x:v>283026</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.6384208397059</x:v>
+        <x:v>23.884</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>5820032</x:v>
+        <x:v>680118</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>1.44475129160304</x:v>
+        <x:v>0.154872636237825</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>150634</x:v>
+        <x:v>114066</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.1053813595893</x:v>
+        <x:v>23.27</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1228,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>386670</x:v>
+        <x:v>478596</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.7030505904265</x:v>
+        <x:v>23.714</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>267668</x:v>
+        <x:v>368776</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.8822790135228</x:v>
+        <x:v>23.864</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>654338</x:v>
+        <x:v>847372</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.162431352721935</x:v>
+        <x:v>0.192958774086435</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>119002</x:v>
+        <x:v>109820</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.2999169157544</x:v>
+        <x:v>23.21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1257,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>340779</x:v>
+        <x:v>122525</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.6671812553229</x:v>
+        <x:v>24.789</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>242820</x:v>
+        <x:v>27860</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.8405255359477</x:v>
+        <x:v>23.659</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>583599</x:v>
+        <x:v>150385</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.144871266863866</x:v>
+        <x:v>0.0342448242814119</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>97959</x:v>
+        <x:v>94665</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.2374968136555</x:v>
+        <x:v>25.121</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1286,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>119025</x:v>
+        <x:v>12289303</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>24.8150663284273</x:v>
+        <x:v>23.8</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>25666</x:v>
+        <x:v>12198207</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.6371208483121</x:v>
+        <x:v>23.798</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>144691</x:v>
+        <x:v>24487510</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0359177594097996</x:v>
+        <x:v>5.5761577088095</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>93359</x:v>
+        <x:v>91096</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>25.1389038662398</x:v>
+        <x:v>24.007</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1315,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>12121819</x:v>
+        <x:v>1751490</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.7987595191594</x:v>
+        <x:v>23.748</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>12033747</x:v>
+        <x:v>1676483</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.7971082248989</x:v>
+        <x:v>23.72</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>24155566</x:v>
+        <x:v>3427973</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>5.99632187209664</x:v>
+        <x:v>0.780598683555039</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>88072</x:v>
+        <x:v>75007</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>24.0243846594188</x:v>
+        <x:v>24.389</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1344,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>861726</x:v>
+        <x:v>870744</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.5643978066881</x:v>
+        <x:v>23.569</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>790439</x:v>
+        <x:v>801557</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>24.2277725098554</x:v>
+        <x:v>24.223</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1652165</x:v>
+        <x:v>1672301</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.410129620883756</x:v>
+        <x:v>0.380806954753662</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>71287</x:v>
+        <x:v>69187</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>16.2088177290186</x:v>
+        <x:v>15.992</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1373,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>48936</x:v>
+        <x:v>31431</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.788965528456</x:v>
+        <x:v>24.115</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>2395</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.9633155806826</x:v>
+        <x:v>23.863</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>51331</x:v>
+        <x:v>37431</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0127422887965694</x:v>
+        <x:v>0.00852357627208518</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>46541</x:v>
+        <x:v>25431</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.779993474244</x:v>
+        <x:v>24.174</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1402,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>1798705</x:v>
+        <x:v>26200</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.7496479718054</x:v>
+        <x:v>23.73</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1756350</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.75285716173</x:v>
+        <x:v>24.16</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>3555055</x:v>
+        <x:v>27200</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.88249863625661</x:v>
+        <x:v>0.00619383063772587</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>42355</x:v>
+        <x:v>25200</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>23.6165713403797</x:v>
+        <x:v>23.713</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1431,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>26200</x:v>
+        <x:v>84063</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.7304156818827</x:v>
+        <x:v>23.81</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1000</x:v>
+        <x:v>63457</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>24.1599998474121</x:v>
+        <x:v>23.873</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>27200</x:v>
+        <x:v>147520</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00675206513153236</x:v>
+        <x:v>0.0335924226351956</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>25200</x:v>
+        <x:v>20606</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>23.7133686911871</x:v>
+        <x:v>23.618</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1460,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>26631</x:v>
+        <x:v>1873700</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>24.1463053989328</x:v>
+        <x:v>23.757</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>3000</x:v>
+        <x:v>1866702</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.7733332316081</x:v>
+        <x:v>23.764</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>29631</x:v>
+        <x:v>3740402</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00735553095266307</x:v>
+        <x:v>0.851743253860702</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>23631</x:v>
+        <x:v>6998</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>24.193654918715</x:v>
+        <x:v>21.674</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1489,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1266977</x:v>
+        <x:v>52866</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.6712955236568</x:v>
+        <x:v>23.764</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>1254288</x:v>
+        <x:v>46318</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.6678482526805</x:v>
+        <x:v>23.831</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>2521265</x:v>
+        <x:v>99184</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.625872996097535</x:v>
+        <x:v>0.022585621248978</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>12689</x:v>
+        <x:v>6548</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>24.0120529212684</x:v>
+        <x:v>23.288</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1518,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>52866</x:v>
+        <x:v>14852</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.7641844319209</x:v>
+        <x:v>23.897</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>46074</x:v>
+        <x:v>9083</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.8317126079002</x:v>
+        <x:v>23.711</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>98940</x:v>
+        <x:v>23935</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.024560636915949</x:v>
+        <x:v>0.00545034324683708</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>6792</x:v>
+        <x:v>5769</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.3061023971638</x:v>
+        <x:v>24.189</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1547,25 +1550,25 @@
         <x:v>10222</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.6418271681447</x:v>
+        <x:v>23.642</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>4834</x:v>
+        <x:v>4994</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.1504549686209</x:v>
+        <x:v>24.141</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>15056</x:v>
+        <x:v>15216</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00373746664045409</x:v>
+        <x:v>0.00346490172733959</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>5388</x:v>
+        <x:v>5228</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.18549702941</x:v>
+        <x:v>23.165</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1576,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>12392</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.8867748567102</x:v>
+        <x:v>24.661</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>8989</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.7093732375326</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>21381</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00530757002122402</x:v>
+        <x:v>0.00070295423450955</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>3403</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>24.3553799565596</x:v>
+        <x:v>24.661</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1605,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>3087</x:v>
+        <x:v>166251</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>24.661509006279</x:v>
+        <x:v>23.912</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>0</x:v>
+        <x:v>165145</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>0</x:v>
+        <x:v>23.758</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>3087</x:v>
+        <x:v>331396</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.000766309744891191</x:v>
+        <x:v>0.0754636286036691</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>3087</x:v>
+        <x:v>1106</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>24.661509006279</x:v>
+        <x:v>46.88</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1634,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>166149</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.9121042458372</x:v>
+        <x:v>23.299</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>164345</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.7580361624239</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>330494</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.0820410666757594</x:v>
+        <x:v>0.000176706344664532</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>1804</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>37.9477578869416</x:v>
+        <x:v>23.298</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1663,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>775</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.2999992370605</x:v>
+        <x:v>24.258</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>1</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.1399993896484</x:v>
+        <x:v>24.128</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>776</x:v>
+        <x:v>1877</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.0001926324463996</x:v>
+        <x:v>0.000427419856875421</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>774</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.2989139655456</x:v>
+        <x:v>24.496</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1692,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>1140</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>24.2585963868258</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>737</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>24.1270555421164</x:v>
+        <x:v>24.125</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>1877</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.000465942141613465</x:v>
+        <x:v>9.10857446724392E-06</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>403</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>24.4991561946443</x:v>
+        <x:v>24.125</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1721,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>4573161</x:v>
+        <x:v>55388</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.705426709038</x:v>
+        <x:v>23.75</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>4573294</x:v>
+        <x:v>60173</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.721985580211</x:v>
+        <x:v>23.877</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>9146455</x:v>
+        <x:v>115561</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2.2704948486261</x:v>
+        <x:v>0.0263148993502294</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-133</x:v>
+        <x:v>-4785</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>593.093292738262</x:v>
+        <x:v>25.347</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1750,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>34838</x:v>
+        <x:v>126871</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.681148559329</x:v>
+        <x:v>24.104</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>37779</x:v>
+        <x:v>133813</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.8544343909843</x:v>
+        <x:v>24.124</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>72617</x:v>
+        <x:v>260684</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.0180262762373708</x:v>
+        <x:v>0.0593614906604754</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-2941</x:v>
+        <x:v>-6942</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>25.9071143648731</x:v>
+        <x:v>24.503</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1779,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>126871</x:v>
+        <x:v>5710541</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>24.1037705993761</x:v>
+        <x:v>23.737</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>133423</x:v>
+        <x:v>5765878</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>24.1253636604629</x:v>
+        <x:v>23.749</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>260294</x:v>
+        <x:v>11476419</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.0646147809318781</x:v>
+        <x:v>2.61334542696983</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-6552</x:v>
+        <x:v>-55337</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>24.5434853413457</x:v>
+        <x:v>25.022</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1808,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1116468</x:v>
+        <x:v>1347468</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.6492183052909</x:v>
+        <x:v>23.684</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>1191094</x:v>
+        <x:v>1421094</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.8404828768215</x:v>
+        <x:v>23.844</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>2307562</x:v>
+        <x:v>2768562</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.572823857317981</x:v>
+        <x:v>0.630441328604544</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-74626</x:v>
+        <x:v>-73626</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>26.7019624368618</x:v>
+        <x:v>26.77</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1837,7 +1840,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.6800003051758</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="D45" s="0">
         <x:v>200001</x:v>
@@ -1849,13 +1852,13 @@
         <x:v>200101</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.0496726097384102</x:v>
+        <x:v>0.0455658714867494</x:v>
       </x:c>
       <x:c r="H45" s="0">
         <x:v>-199901</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>25.5009104505204</x:v>
+        <x:v>25.501</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1869,22 +1872,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>506001</x:v>
+        <x:v>556155</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.440536134811</x:v>
+        <x:v>24.393</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>506001</x:v>
+        <x:v>556155</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.125608518699283</x:v>
+        <x:v>0.126644480820751</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-506001</x:v>
+        <x:v>-556155</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>24.440536134811</x:v>
+        <x:v>24.393</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1895,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>2061245</x:v>
+        <x:v>2345245</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.8471927000453</x:v>
+        <x:v>23.85</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2650815</x:v>
+        <x:v>2956551</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.6940917471711</x:v>
+        <x:v>23.715</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>4712060</x:v>
+        <x:v>5301796</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>1.16971088322384</x:v>
+        <x:v>1.2072950919034</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-589570</x:v>
+        <x:v>-611306</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.1588226975128</x:v>
+        <x:v>23.199</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1924,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>3245453</x:v>
+        <x:v>3399325</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.8583327019187</x:v>
+        <x:v>23.863</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>3883127</x:v>
+        <x:v>4013670</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.7130592435746</x:v>
+        <x:v>23.72</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>7128580</x:v>
+        <x:v>7412995</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.76958222262276</x:v>
+        <x:v>1.68804542457017</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-637674</x:v>
+        <x:v>-614345</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>22.9736874310134</x:v>
+        <x:v>22.929</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1953,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>2231772</x:v>
+        <x:v>988776</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.8139750659987</x:v>
+        <x:v>23.996</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>2909752</x:v>
+        <x:v>1668330</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>24.1338706498754</x:v>
+        <x:v>24.699</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>5141524</x:v>
+        <x:v>2657106</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.27632003394621</x:v>
+        <x:v>0.605061196709016</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-677980</x:v>
+        <x:v>-679554</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.1869017230926</x:v>
+        <x:v>25.723</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1982,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>886841</x:v>
+        <x:v>2498049</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>24.0139844672822</x:v>
+        <x:v>23.817</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1567924</x:v>
+        <x:v>3200665</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.7522017820063</x:v>
+        <x:v>24.115</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>2454765</x:v>
+        <x:v>5698714</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.609365189801693</x:v>
+        <x:v>1.29767902091314</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-681083</x:v>
+        <x:v>-702616</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>25.7134376102494</x:v>
+        <x:v>25.174</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2011,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>431762</x:v>
+        <x:v>4020317</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.7334329341673</x:v>
+        <x:v>23.776</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>1346522</x:v>
+        <x:v>4810389</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.6630719108366</x:v>
+        <x:v>23.76</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1778284</x:v>
+        <x:v>8830706</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>0.441437109939776</x:v>
+        <x:v>2.01087857998344</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-914760</x:v>
+        <x:v>-790072</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.629861870875</x:v>
+        <x:v>23.676</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2040,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>372160</x:v>
+        <x:v>464537</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.7744762006189</x:v>
+        <x:v>23.743</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1784801</x:v>
+        <x:v>1420854</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.7954454730493</x:v>
+        <x:v>23.673</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>2156961</x:v>
+        <x:v>1885391</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>0.535439013168205</x:v>
+        <x:v>0.429330608084287</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1412641</x:v>
+        <x:v>-956317</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.8009698238417</x:v>
+        <x:v>23.638</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2069,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>15923862</x:v>
+        <x:v>550460</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>23.8064077359706</x:v>
+        <x:v>23.823</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>19047325</x:v>
+        <x:v>1960674</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.7563001534872</x:v>
+        <x:v>23.805</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>34971187</x:v>
+        <x:v>2511134</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>8.68116663055139</x:v>
+        <x:v>0.571821275905702</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-3123463</x:v>
+        <x:v>-1410214</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.5008445170286</x:v>
+        <x:v>23.798</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2098,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>5747426</x:v>
+        <x:v>16959001</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>23.762484491189</x:v>
+        <x:v>23.811</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>11228552</x:v>
+        <x:v>19780080</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.6604820537503</x:v>
+        <x:v>23.761</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>16975978</x:v>
+        <x:v>36739081</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>4.21407754145075</x:v>
+        <x:v>8.36601637866516</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-5481126</x:v>
+        <x:v>-2821079</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.5535238373183</x:v>
+        <x:v>23.465</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2127,57 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>10127683</x:v>
+        <x:v>6011251</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>23.7716503260081</x:v>
+        <x:v>23.769</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>24161792</x:v>
+        <x:v>11446128</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.7527968218313</x:v>
+        <x:v>23.665</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>34289475</x:v>
+        <x:v>17457379</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>8.5119400193401</x:v>
+        <x:v>3.97529591561</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-14034109</x:v>
+        <x:v>-5434877</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.7391912332084</x:v>
+        <x:v>23.549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:9">
+      <x:c r="A56" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B56" s="0">
+        <x:v>11171731</x:v>
+      </x:c>
+      <x:c r="C56" s="0">
+        <x:v>23.779</x:v>
+      </x:c>
+      <x:c r="D56" s="0">
+        <x:v>25342065</x:v>
+      </x:c>
+      <x:c r="E56" s="0">
+        <x:v>23.759</x:v>
+      </x:c>
+      <x:c r="F56" s="0">
+        <x:v>36513796</x:v>
+      </x:c>
+      <x:c r="G56" s="0">
+        <x:v>8.31471574869383</x:v>
+      </x:c>
+      <x:c r="H56" s="0">
+        <x:v>-14170334</x:v>
+      </x:c>
+      <x:c r="I56" s="0">
+        <x:v>23.743</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -52,139 +52,139 @@
     <x:t>AK</x:t>
   </x:si>
   <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
   </x:si>
   <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
     <x:t>GCM</x:t>
   </x:si>
   <x:si>
-    <x:t>DINAMIK</x:t>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
   </x:si>
   <x:si>
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AKTIF </x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AKTIF </x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
+    <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
     <x:t>BLUPAY</x:t>
   </x:si>
   <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
@@ -590,28 +590,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>24513877</x:v>
+        <x:v>27551936</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.82</x:v>
+        <x:v>23.915</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>17987621</x:v>
+        <x:v>21593053</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.794</x:v>
+        <x:v>23.94</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>42501498</x:v>
+        <x:v>49144989</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.67820148756046</x:v>
+        <x:v>9.62912803083902</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>6526256</x:v>
+        <x:v>5958883</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.891</x:v>
+        <x:v>23.823</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -619,28 +619,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>9580036</x:v>
+        <x:v>11910321</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.799</x:v>
+        <x:v>23.973</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>4709508</x:v>
+        <x:v>6710515</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.743</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>14289544</x:v>
+        <x:v>18620836</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>3.25393439067396</x:v>
+        <x:v>3.64843735920373</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>4870528</x:v>
+        <x:v>5199806</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.854</x:v>
+        <x:v>23.938</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -648,28 +648,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>11748385</x:v>
+        <x:v>13164207</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.83</x:v>
+        <x:v>23.919</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>7710243</x:v>
+        <x:v>9392616</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.943</x:v>
+        <x:v>24.078</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>19458628</x:v>
+        <x:v>22556823</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.43100905420994</x:v>
+        <x:v>4.41962733242191</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>4038142</x:v>
+        <x:v>3771591</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.614</x:v>
+        <x:v>23.523</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -677,28 +677,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>31090507</x:v>
+        <x:v>35929378</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.717</x:v>
+        <x:v>23.849</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>28652634</x:v>
+        <x:v>33567022</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.679</x:v>
+        <x:v>23.825</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>59743141</x:v>
+        <x:v>69496400</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.6043712176388</x:v>
+        <x:v>13.6166422436762</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2437873</x:v>
+        <x:v>2362356</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.174</x:v>
+        <x:v>24.192</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -706,28 +706,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>4160441</x:v>
+        <x:v>16188133</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.031</x:v>
+        <x:v>23.966</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>2625629</x:v>
+        <x:v>14526535</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.076</x:v>
+        <x:v>24.025</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>6786070</x:v>
+        <x:v>30714668</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.54528559837325</x:v>
+        <x:v>6.01801885837667</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1534812</x:v>
+        <x:v>1661598</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.955</x:v>
+        <x:v>23.447</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -735,28 +735,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>5991810</x:v>
+        <x:v>4847618</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.814</x:v>
+        <x:v>24.132</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>4583305</x:v>
+        <x:v>3237015</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.836</x:v>
+        <x:v>24.177</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>10575115</x:v>
+        <x:v>8084633</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2.4081055619292</x:v>
+        <x:v>1.58404687483695</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1408505</x:v>
+        <x:v>1610603</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.742</x:v>
+        <x:v>24.042</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -764,28 +764,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>13667540</x:v>
+        <x:v>13947164</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.836</x:v>
+        <x:v>23.982</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>12328852</x:v>
+        <x:v>12865854</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.902</x:v>
+        <x:v>23.989</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>25996392</x:v>
+        <x:v>26813018</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>5.9197518102916</x:v>
+        <x:v>5.25355663860645</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1338688</x:v>
+        <x:v>1081310</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.228</x:v>
+        <x:v>23.891</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -793,28 +793,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>2787964</x:v>
+        <x:v>3191177</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.75</x:v>
+        <x:v>23.87</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1634529</x:v>
+        <x:v>2206899</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.836</x:v>
+        <x:v>24.064</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>4422493</x:v>
+        <x:v>5398076</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.00706517053412</x:v>
+        <x:v>1.05766154356448</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>1153435</x:v>
+        <x:v>984278</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.627</x:v>
+        <x:v>23.435</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -822,28 +822,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1896120</x:v>
+        <x:v>2124458</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.854</x:v>
+        <x:v>23.933</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1008632</x:v>
+        <x:v>1321752</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.869</x:v>
+        <x:v>24.072</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>2904752</x:v>
+        <x:v>3446210</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.661453747521893</x:v>
+        <x:v>0.675226467364918</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>887488</x:v>
+        <x:v>802706</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.836</x:v>
+        <x:v>23.704</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -851,28 +851,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>11370071</x:v>
+        <x:v>1964811</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.795</x:v>
+        <x:v>23.9</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>10612309</x:v>
+        <x:v>1271088</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.818</x:v>
+        <x:v>23.995</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>21982380</x:v>
+        <x:v>3235899</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>5.00570362993134</x:v>
+        <x:v>0.634019589786945</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>757762</x:v>
+        <x:v>693723</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.485</x:v>
+        <x:v>23.724</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -880,28 +880,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1580345</x:v>
+        <x:v>10535003</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.702</x:v>
+        <x:v>23.992</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>958111</x:v>
+        <x:v>9887239</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.804</x:v>
+        <x:v>23.998</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>2538456</x:v>
+        <x:v>20422242</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.578042887695553</x:v>
+        <x:v>4.00139234734141</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>622234</x:v>
+        <x:v>647764</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.545</x:v>
+        <x:v>23.897</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -909,28 +909,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>2187783</x:v>
+        <x:v>6807751</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.696</x:v>
+        <x:v>23.911</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1742655</x:v>
+        <x:v>6200733</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.692</x:v>
+        <x:v>24.056</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>3930438</x:v>
+        <x:v>13008484</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.895017180297132</x:v>
+        <x:v>2.54879206348222</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>445128</x:v>
+        <x:v>607018</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.712</x:v>
+        <x:v>22.429</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -938,28 +938,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>8979281</x:v>
+        <x:v>13285106</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.869</x:v>
+        <x:v>23.888</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>8569667</x:v>
+        <x:v>12861308</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.872</x:v>
+        <x:v>23.857</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>17548948</x:v>
+        <x:v>26146414</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>3.99614749199478</x:v>
+        <x:v>5.12294687772382</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>409614</x:v>
+        <x:v>423798</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.801</x:v>
+        <x:v>24.831</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -967,28 +967,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>2418627</x:v>
+        <x:v>3583600</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.779</x:v>
+        <x:v>23.965</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>2111776</x:v>
+        <x:v>3177900</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.812</x:v>
+        <x:v>23.936</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>4530403</x:v>
+        <x:v>6761500</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>1.03163782730313</x:v>
+        <x:v>1.32480137864143</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>306851</x:v>
+        <x:v>405700</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.553</x:v>
+        <x:v>24.196</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -996,28 +996,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>394468</x:v>
+        <x:v>435892</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>24.069</x:v>
+        <x:v>24.131</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>105888</x:v>
+        <x:v>139897</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.921</x:v>
+        <x:v>24.095</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>500356</x:v>
+        <x:v>575789</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.113938247153307</x:v>
+        <x:v>0.112816100126684</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>288580</x:v>
+        <x:v>295995</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>24.124</x:v>
+        <x:v>24.147</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1025,28 +1025,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>4785216</x:v>
+        <x:v>988805</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.732</x:v>
+        <x:v>23.931</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>4502582</x:v>
+        <x:v>714375</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.766</x:v>
+        <x:v>23.993</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>9287798</x:v>
+        <x:v>1703180</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.11496499299298</x:v>
+        <x:v>0.333709267481256</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>282634</x:v>
+        <x:v>274430</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.191</x:v>
+        <x:v>23.772</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1054,28 +1054,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>618997</x:v>
+        <x:v>711008</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.857</x:v>
+        <x:v>23.95</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>343702</x:v>
+        <x:v>478966</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.764</x:v>
+        <x:v>24.047</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>962699</x:v>
+        <x:v>1189974</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.219220388276031</x:v>
+        <x:v>0.23315524598794</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>275295</x:v>
+        <x:v>232042</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.973</x:v>
+        <x:v>23.75</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1083,28 +1083,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>3100439</x:v>
+        <x:v>2725090</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.841</x:v>
+        <x:v>23.908</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>2843039</x:v>
+        <x:v>2518101</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.847</x:v>
+        <x:v>23.964</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>5943478</x:v>
+        <x:v>5243191</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.35341529893565</x:v>
+        <x:v>1.02731445171639</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>257400</x:v>
+        <x:v>206989</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.774</x:v>
+        <x:v>23.234</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1112,28 +1112,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>1046625</x:v>
+        <x:v>1132717</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.785</x:v>
+        <x:v>23.836</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>798221</x:v>
+        <x:v>932997</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.9</x:v>
+        <x:v>24.015</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>1844846</x:v>
+        <x:v>2065714</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.420097929289927</x:v>
+        <x:v>0.404741663104179</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>248404</x:v>
+        <x:v>199720</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.418</x:v>
+        <x:v>22.997</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1141,28 +1141,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>815935</x:v>
+        <x:v>518246</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.761</x:v>
+        <x:v>23.996</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>610645</x:v>
+        <x:v>339473</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.858</x:v>
+        <x:v>24.018</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1426580</x:v>
+        <x:v>857719</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.324852754087021</x:v>
+        <x:v>0.168055507459432</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>205290</x:v>
+        <x:v>178773</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.475</x:v>
+        <x:v>23.955</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1170,28 +1170,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>3015463</x:v>
+        <x:v>2302328</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.614</x:v>
+        <x:v>23.752</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>2877873</x:v>
+        <x:v>2155617</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.643</x:v>
+        <x:v>23.858</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>5893336</x:v>
+        <x:v>4457945</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.34199724541224</x:v>
+        <x:v>0.873458800844144</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>137590</x:v>
+        <x:v>146711</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.022</x:v>
+        <x:v>22.193</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1199,28 +1199,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>397092</x:v>
+        <x:v>569193</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.708</x:v>
+        <x:v>23.855</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>283026</x:v>
+        <x:v>468534</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.884</x:v>
+        <x:v>23.999</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>680118</x:v>
+        <x:v>1037727</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.154872636237825</x:v>
+        <x:v>0.203325025549573</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>114066</x:v>
+        <x:v>100659</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.27</x:v>
+        <x:v>23.185</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1228,28 +1228,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>478596</x:v>
+        <x:v>129745</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.714</x:v>
+        <x:v>24.777</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>368776</x:v>
+        <x:v>36034</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.864</x:v>
+        <x:v>23.859</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>847372</x:v>
+        <x:v>165779</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.192958774086435</x:v>
+        <x:v>0.0324815865931817</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>109820</x:v>
+        <x:v>93711</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.21</x:v>
+        <x:v>25.13</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1257,28 +1257,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>122525</x:v>
+        <x:v>3122262</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>24.789</x:v>
+        <x:v>23.65</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>27860</x:v>
+        <x:v>3051156</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.659</x:v>
+        <x:v>23.706</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>150385</x:v>
+        <x:v>6173418</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0342448242814119</x:v>
+        <x:v>1.20957667342007</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>94665</x:v>
+        <x:v>71106</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>25.121</x:v>
+        <x:v>21.225</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1286,28 +1286,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>12289303</x:v>
+        <x:v>45431</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.8</x:v>
+        <x:v>24.393</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>12198207</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.798</x:v>
+        <x:v>24.045</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>24487510</x:v>
+        <x:v>53431</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>5.5761577088095</x:v>
+        <x:v>0.0104688992771116</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>91096</x:v>
+        <x:v>37431</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>24.007</x:v>
+        <x:v>24.467</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1315,28 +1315,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1751490</x:v>
+        <x:v>1945209</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.748</x:v>
+        <x:v>23.799</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1676483</x:v>
+        <x:v>1913232</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.72</x:v>
+        <x:v>23.812</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>3427973</x:v>
+        <x:v>3858441</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.780598683555039</x:v>
+        <x:v>0.755996148222528</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>75007</x:v>
+        <x:v>31977</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>24.389</x:v>
+        <x:v>23.054</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1344,28 +1344,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>870744</x:v>
+        <x:v>39534</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.569</x:v>
+        <x:v>24.66</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>801557</x:v>
+        <x:v>13456</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>24.223</x:v>
+        <x:v>24.054</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1672301</x:v>
+        <x:v>52990</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.380806954753662</x:v>
+        <x:v>0.0103824927980788</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>69187</x:v>
+        <x:v>26078</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>15.992</x:v>
+        <x:v>24.973</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1373,28 +1373,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>31431</x:v>
+        <x:v>906944</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>24.115</x:v>
+        <x:v>23.616</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>6000</x:v>
+        <x:v>882470</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.863</x:v>
+        <x:v>24.273</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>37431</x:v>
+        <x:v>1789414</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00852357627208518</x:v>
+        <x:v>0.350605358893778</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>25431</x:v>
+        <x:v>24474</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.174</x:v>
+        <x:v>-0.091</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1402,28 +1402,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>26200</x:v>
+        <x:v>84063</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.73</x:v>
+        <x:v>23.81</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1000</x:v>
+        <x:v>64123</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>24.16</x:v>
+        <x:v>23.884</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>27200</x:v>
+        <x:v>148186</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00619383063772587</x:v>
+        <x:v>0.0290345362856406</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>25200</x:v>
+        <x:v>19940</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>23.713</x:v>
+        <x:v>23.574</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1431,28 +1431,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>84063</x:v>
+        <x:v>5121789</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.81</x:v>
+        <x:v>23.797</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>63457</x:v>
+        <x:v>5108622</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.873</x:v>
+        <x:v>23.875</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>147520</x:v>
+        <x:v>10230411</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0335924226351956</x:v>
+        <x:v>2.00447572237942</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>20606</x:v>
+        <x:v>13167</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>23.618</x:v>
+        <x:v>-6.517</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1460,28 +1460,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1873700</x:v>
+        <x:v>27200</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.757</x:v>
+        <x:v>23.762</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1866702</x:v>
+        <x:v>16470</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.764</x:v>
+        <x:v>24.087</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>3740402</x:v>
+        <x:v>43670</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.851743253860702</x:v>
+        <x:v>0.00855639668790525</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>6998</x:v>
+        <x:v>10730</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>21.674</x:v>
+        <x:v>23.263</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1489,28 +1489,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>52866</x:v>
+        <x:v>72288</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.764</x:v>
+        <x:v>24.028</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>46318</x:v>
+        <x:v>63143</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.831</x:v>
+        <x:v>23.89</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>99184</x:v>
+        <x:v>135431</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.022585621248978</x:v>
+        <x:v>0.026535410117694</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>6548</x:v>
+        <x:v>9145</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.288</x:v>
+        <x:v>24.98</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1518,28 +1518,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>14852</x:v>
+        <x:v>10222</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.897</x:v>
+        <x:v>23.642</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>9083</x:v>
+        <x:v>5348</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.711</x:v>
+        <x:v>24.167</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>23935</x:v>
+        <x:v>15570</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00545034324683708</x:v>
+        <x:v>0.00305067772912033</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>5769</x:v>
+        <x:v>4874</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>24.189</x:v>
+        <x:v>23.065</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1547,28 +1547,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>10222</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.642</x:v>
+        <x:v>24.661</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>4994</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.141</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>15216</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00346490172733959</x:v>
+        <x:v>0.000604845353230215</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>5228</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.165</x:v>
+        <x:v>24.661</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1576,28 +1576,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>3087</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>24.661</x:v>
+        <x:v>23.299</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>0</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>3087</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00070295423450955</x:v>
+        <x:v>0.000152044053808438</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>3087</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>24.661</x:v>
+        <x:v>23.298</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1605,28 +1605,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>166251</x:v>
+        <x:v>2206735</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.912</x:v>
+        <x:v>23.909</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>165145</x:v>
+        <x:v>2206060</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.758</x:v>
+        <x:v>23.92</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>331396</x:v>
+        <x:v>4412795</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.0754636286036691</x:v>
+        <x:v>0.864612423228872</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>1106</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>46.88</x:v>
+        <x:v>-11.391</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1634,28 +1634,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>775</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.299</x:v>
+        <x:v>24.339</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>1</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>24</x:v>
+        <x:v>24.215</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>776</x:v>
+        <x:v>2221</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000176706344664532</x:v>
+        <x:v>0.000435167324108943</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>774</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.298</x:v>
+        <x:v>24.577</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1663,28 +1663,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>1140</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>24.258</x:v>
+        <x:v>24.036</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>737</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.128</x:v>
+        <x:v>24.833</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>1877</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.000427419856875421</x:v>
+        <x:v>6.26985788900774E-05</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>403</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>24.496</x:v>
+        <x:v>27.625</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1692,28 +1692,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>0</x:v>
+        <x:v>190492</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>0</x:v>
+        <x:v>24.009</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>40</x:v>
+        <x:v>193627</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>24.125</x:v>
+        <x:v>23.937</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>40</x:v>
+        <x:v>384119</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>9.10857446724392E-06</x:v>
+        <x:v>0.0752616107021176</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-40</x:v>
+        <x:v>-3135</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>24.125</x:v>
+        <x:v>19.588</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1721,28 +1721,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>55388</x:v>
+        <x:v>126971</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.75</x:v>
+        <x:v>24.104</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>60173</x:v>
+        <x:v>133813</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.877</x:v>
+        <x:v>24.124</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>115561</x:v>
+        <x:v>260784</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0263148993502294</x:v>
+        <x:v>0.0510962068664686</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-4785</x:v>
+        <x:v>-6842</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>25.347</x:v>
+        <x:v>24.498</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1750,28 +1750,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>126871</x:v>
+        <x:v>63331</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>24.104</x:v>
+        <x:v>23.93</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>133813</x:v>
+        <x:v>72752</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.124</x:v>
+        <x:v>24.214</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>260684</x:v>
+        <x:v>136083</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.0593614906604754</x:v>
+        <x:v>0.0266631584721825</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-6942</x:v>
+        <x:v>-9421</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>24.503</x:v>
+        <x:v>26.124</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1779,28 +1779,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>5710541</x:v>
+        <x:v>1478354</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.737</x:v>
+        <x:v>23.726</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>5765878</x:v>
+        <x:v>1551805</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.749</x:v>
+        <x:v>23.897</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>11476419</x:v>
+        <x:v>3030159</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>2.61334542696983</x:v>
+        <x:v>0.593708322221806</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-55337</x:v>
+        <x:v>-73451</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>25.022</x:v>
+        <x:v>27.328</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1808,28 +1808,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1347468</x:v>
+        <x:v>7134617</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.684</x:v>
+        <x:v>23.907</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>1421094</x:v>
+        <x:v>7299757</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.844</x:v>
+        <x:v>23.922</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>2768562</x:v>
+        <x:v>14434374</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.630441328604544</x:v>
+        <x:v>2.82817105302463</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-73626</x:v>
+        <x:v>-165140</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>26.77</x:v>
+        <x:v>24.577</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1852,7 +1852,7 @@
         <x:v>200101</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.0455658714867494</x:v>
+        <x:v>0.0392064010452605</x:v>
       </x:c>
       <x:c r="H45" s="0">
         <x:v>-199901</x:v>
@@ -1866,28 +1866,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>0</x:v>
+        <x:v>2971858</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>0</x:v>
+        <x:v>23.954</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>556155</x:v>
+        <x:v>3505395</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.393</x:v>
+        <x:v>24.164</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>556155</x:v>
+        <x:v>6477253</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.126644480820751</x:v>
+        <x:v>1.26910799441091</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-556155</x:v>
+        <x:v>-533537</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>24.393</x:v>
+        <x:v>25.331</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1895,28 +1895,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>2345245</x:v>
+        <x:v>1254608</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.85</x:v>
+        <x:v>24.136</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2956551</x:v>
+        <x:v>1804077</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.715</x:v>
+        <x:v>24.7</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>5301796</x:v>
+        <x:v>3058685</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>1.2072950919034</x:v>
+        <x:v>0.599297508663739</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-611306</x:v>
+        <x:v>-549469</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.199</x:v>
+        <x:v>25.99</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1924,28 +1924,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>3399325</x:v>
+        <x:v>3692032</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.863</x:v>
+        <x:v>24.065</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4013670</x:v>
+        <x:v>4249159</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.72</x:v>
+        <x:v>24.037</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>7412995</x:v>
+        <x:v>7941191</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.68804542457017</x:v>
+        <x:v>1.55594184498335</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-614345</x:v>
+        <x:v>-557127</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>22.929</x:v>
+        <x:v>23.849</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1953,28 +1953,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>988776</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.996</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1668330</x:v>
+        <x:v>678087</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>24.699</x:v>
+        <x:v>24.396</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>2657106</x:v>
+        <x:v>678087</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.605061196709016</x:v>
+        <x:v>0.132859660199487</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-679554</x:v>
+        <x:v>-678087</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.723</x:v>
+        <x:v>24.396</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1982,28 +1982,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2498049</x:v>
+        <x:v>3638627</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.817</x:v>
+        <x:v>23.905</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>3200665</x:v>
+        <x:v>4341251</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.115</x:v>
+        <x:v>23.79</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>5698714</x:v>
+        <x:v>7979878</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.29767902091314</x:v>
+        <x:v>1.5635219072381</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-702616</x:v>
+        <x:v>-702624</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>25.174</x:v>
+        <x:v>23.199</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2011,28 +2011,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>4020317</x:v>
+        <x:v>4504801</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.776</x:v>
+        <x:v>23.885</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>4810389</x:v>
+        <x:v>5411312</x:v>
       </x:c>
       <x:c r="E51" s="0">
+        <x:v>23.864</x:v>
+      </x:c>
+      <x:c r="F51" s="0">
+        <x:v>9916113</x:v>
+      </x:c>
+      <x:c r="G51" s="0">
+        <x:v>1.94289435379194</x:v>
+      </x:c>
+      <x:c r="H51" s="0">
+        <x:v>-906511</x:v>
+      </x:c>
+      <x:c r="I51" s="0">
         <x:v>23.76</x:v>
-      </x:c>
-      <x:c r="F51" s="0">
-        <x:v>8830706</x:v>
-      </x:c>
-      <x:c r="G51" s="0">
-        <x:v>2.01087857998344</x:v>
-      </x:c>
-      <x:c r="H51" s="0">
-        <x:v>-790072</x:v>
-      </x:c>
-      <x:c r="I51" s="0">
-        <x:v>23.676</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2040,28 +2040,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>464537</x:v>
+        <x:v>482988</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.743</x:v>
+        <x:v>23.774</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1420854</x:v>
+        <x:v>1459112</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.673</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>1885391</x:v>
+        <x:v>1942100</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>0.429330608084287</x:v>
+        <x:v>0.38052159394506</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-956317</x:v>
+        <x:v>-976124</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.638</x:v>
+        <x:v>23.664</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2069,25 +2069,25 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>550460</x:v>
+        <x:v>962076</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>23.823</x:v>
+        <x:v>24.214</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>1960674</x:v>
+        <x:v>2387892</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.805</x:v>
+        <x:v>23.966</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>2511134</x:v>
+        <x:v>3349968</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>0.571821275905702</x:v>
+        <x:v>0.656369477897609</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1410214</x:v>
+        <x:v>-1425816</x:v>
       </x:c>
       <x:c r="I53" s="0">
         <x:v>23.798</x:v>
@@ -2098,28 +2098,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>16959001</x:v>
+        <x:v>18731394</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>23.811</x:v>
+        <x:v>23.895</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>19780080</x:v>
+        <x:v>21937708</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.761</x:v>
+        <x:v>23.851</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>36739081</x:v>
+        <x:v>40669102</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>8.36601637866516</x:v>
+        <x:v>7.96842156292376</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-2821079</x:v>
+        <x:v>-3206314</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.465</x:v>
+        <x:v>23.595</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2127,28 +2127,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>6011251</x:v>
+        <x:v>7308319</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>23.769</x:v>
+        <x:v>23.953</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>11446128</x:v>
+        <x:v>12981096</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.665</x:v>
+        <x:v>23.795</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>17457379</x:v>
+        <x:v>20289415</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>3.97529591561</x:v>
+        <x:v>3.97536714690944</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-5434877</x:v>
+        <x:v>-5672777</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.549</x:v>
+        <x:v>23.592</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
@@ -2156,28 +2156,28 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>11171731</x:v>
+        <x:v>14517923</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>23.779</x:v>
+        <x:v>23.992</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>25342065</x:v>
+        <x:v>27045688</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>23.759</x:v>
+        <x:v>23.818</x:v>
       </x:c>
       <x:c r="F56" s="0">
-        <x:v>36513796</x:v>
+        <x:v>41563611</x:v>
       </x:c>
       <x:c r="G56" s="0">
-        <x:v>8.31471574869383</x:v>
+        <x:v>8.14368544762496</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>-14170334</x:v>
+        <x:v>-12527765</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>23.743</x:v>
+        <x:v>23.618</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -52,70 +52,76 @@
     <x:t>AK</x:t>
   </x:si>
   <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>HALK</x:t>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
     <x:t>HSBC</x:t>
   </x:si>
   <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
+    <x:t>ACAR</x:t>
   </x:si>
   <x:si>
     <x:t>BIZIM</x:t>
@@ -124,15 +130,12 @@
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
     <x:t>DINAMIK</x:t>
   </x:si>
   <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
     <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
@@ -145,33 +148,30 @@
     <x:t xml:space="preserve">ALLBATROSS </x:t>
   </x:si>
   <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">AKTIF </x:t>
   </x:si>
   <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
+    <x:t>BLUPAY</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>BLUPAY</x:t>
-  </x:si>
-  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
@@ -181,10 +181,10 @@
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
@@ -590,28 +590,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>27551936</x:v>
+        <x:v>29852667</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.915</x:v>
+        <x:v>23.995</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>21593053</x:v>
+        <x:v>24137138</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.94</x:v>
+        <x:v>24.051</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>49144989</x:v>
+        <x:v>53989805</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.62912803083902</x:v>
+        <x:v>9.53517952995877</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>5958883</x:v>
+        <x:v>5715529</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.823</x:v>
+        <x:v>23.758</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -619,28 +619,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>11910321</x:v>
+        <x:v>13886902</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.973</x:v>
+        <x:v>24.118</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>6710515</x:v>
+        <x:v>8616128</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>24</x:v>
+        <x:v>24.203</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>18620836</x:v>
+        <x:v>22503030</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>3.64843735920373</x:v>
+        <x:v>3.97427682908001</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>5199806</x:v>
+        <x:v>5270774</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.938</x:v>
+        <x:v>23.978</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -648,28 +648,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>13164207</x:v>
+        <x:v>14642358</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.919</x:v>
+        <x:v>24.029</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>9392616</x:v>
+        <x:v>10779440</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.078</x:v>
+        <x:v>24.182</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>22556823</x:v>
+        <x:v>25421798</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.41962733242191</x:v>
+        <x:v>4.48976261174396</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>3771591</x:v>
+        <x:v>3862918</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.523</x:v>
+        <x:v>23.601</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -677,28 +677,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>35929378</x:v>
+        <x:v>39858373</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.849</x:v>
+        <x:v>23.955</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>33567022</x:v>
+        <x:v>37262651</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.825</x:v>
+        <x:v>23.936</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>69496400</x:v>
+        <x:v>77121024</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.6166422436762</x:v>
+        <x:v>13.6204012845436</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2362356</x:v>
+        <x:v>2595722</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.192</x:v>
+        <x:v>24.222</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -706,28 +706,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>16188133</x:v>
+        <x:v>5526568</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.966</x:v>
+        <x:v>24.242</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>14526535</x:v>
+        <x:v>3750511</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.025</x:v>
+        <x:v>24.291</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>30714668</x:v>
+        <x:v>9277079</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>6.01801885837667</x:v>
+        <x:v>1.63843180723862</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1661598</x:v>
+        <x:v>1776057</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.447</x:v>
+        <x:v>24.137</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -735,28 +735,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>4847618</x:v>
+        <x:v>15518028</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>24.132</x:v>
+        <x:v>24.082</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>3237015</x:v>
+        <x:v>14284537</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.177</x:v>
+        <x:v>24.091</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>8084633</x:v>
+        <x:v>29802565</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.58404687483695</x:v>
+        <x:v>5.26345312283061</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1610603</x:v>
+        <x:v>1233491</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>24.042</x:v>
+        <x:v>23.98</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -764,28 +764,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>13947164</x:v>
+        <x:v>18155667</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.982</x:v>
+        <x:v>24.074</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>12865854</x:v>
+        <x:v>17079854</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.989</x:v>
+        <x:v>24.153</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>26813018</x:v>
+        <x:v>35235521</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>5.25355663860645</x:v>
+        <x:v>6.22297151409664</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1081310</x:v>
+        <x:v>1075813</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.891</x:v>
+        <x:v>22.817</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -793,28 +793,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>3191177</x:v>
+        <x:v>3768227</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.87</x:v>
+        <x:v>24.035</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>2206899</x:v>
+        <x:v>2770882</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>24.064</x:v>
+        <x:v>24.238</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>5398076</x:v>
+        <x:v>6539109</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.05766154356448</x:v>
+        <x:v>1.15487689353516</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>984278</x:v>
+        <x:v>997345</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.435</x:v>
+        <x:v>23.469</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -822,28 +822,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>2124458</x:v>
+        <x:v>2347231</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.933</x:v>
+        <x:v>24.022</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1321752</x:v>
+        <x:v>1415089</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>24.072</x:v>
+        <x:v>24.133</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>3446210</x:v>
+        <x:v>3762320</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.675226467364918</x:v>
+        <x:v>0.66446612743192</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>802706</x:v>
+        <x:v>932142</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.704</x:v>
+        <x:v>23.853</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -851,28 +851,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1964811</x:v>
+        <x:v>8015289</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.9</x:v>
+        <x:v>24.066</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1271088</x:v>
+        <x:v>7083727</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.995</x:v>
+        <x:v>24.157</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>3235899</x:v>
+        <x:v>15099016</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.634019589786945</x:v>
+        <x:v>2.6666484215996</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>693723</x:v>
+        <x:v>931562</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.724</x:v>
+        <x:v>23.378</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -880,28 +880,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>10535003</x:v>
+        <x:v>2066461</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.992</x:v>
+        <x:v>23.945</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>9887239</x:v>
+        <x:v>1378690</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.998</x:v>
+        <x:v>24.089</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>20422242</x:v>
+        <x:v>3445151</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>4.00139234734141</x:v>
+        <x:v>0.608450674952744</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>647764</x:v>
+        <x:v>687771</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.897</x:v>
+        <x:v>23.656</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -909,28 +909,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>6807751</x:v>
+        <x:v>11805460</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.911</x:v>
+        <x:v>24.094</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>6200733</x:v>
+        <x:v>11449334</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>24.056</x:v>
+        <x:v>24.123</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>13008484</x:v>
+        <x:v>23254794</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2.54879206348222</x:v>
+        <x:v>4.10704642704689</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>607018</x:v>
+        <x:v>356126</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>22.429</x:v>
+        <x:v>23.174</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -938,28 +938,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>13285106</x:v>
+        <x:v>503734</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.888</x:v>
+        <x:v>24.232</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>12861308</x:v>
+        <x:v>173948</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.857</x:v>
+        <x:v>24.291</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>26146414</x:v>
+        <x:v>677682</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>5.12294687772382</x:v>
+        <x:v>0.119685920966403</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>423798</x:v>
+        <x:v>329786</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>24.831</x:v>
+        <x:v>24.201</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -967,28 +967,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>3583600</x:v>
+        <x:v>1031893</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.965</x:v>
+        <x:v>23.975</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>3177900</x:v>
+        <x:v>727747</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.936</x:v>
+        <x:v>24.013</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>6761500</x:v>
+        <x:v>1759640</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>1.32480137864143</x:v>
+        <x:v>0.310771326329048</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>405700</x:v>
+        <x:v>304146</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>24.196</x:v>
+        <x:v>23.885</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -996,28 +996,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>435892</x:v>
+        <x:v>3213478</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>24.131</x:v>
+        <x:v>24.056</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>139897</x:v>
+        <x:v>2951231</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>24.095</x:v>
+        <x:v>24.117</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>575789</x:v>
+        <x:v>6164709</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.112816100126684</x:v>
+        <x:v>1.0887538316716</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>295995</x:v>
+        <x:v>262247</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>24.147</x:v>
+        <x:v>23.364</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1025,28 +1025,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>988805</x:v>
+        <x:v>808664</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.931</x:v>
+        <x:v>24.077</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>714375</x:v>
+        <x:v>559580</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.993</x:v>
+        <x:v>24.186</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>1703180</x:v>
+        <x:v>1368244</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.333709267481256</x:v>
+        <x:v>0.241646588291788</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>274430</x:v>
+        <x:v>249084</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.772</x:v>
+        <x:v>23.832</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1054,28 +1054,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>711008</x:v>
+        <x:v>3859411</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.95</x:v>
+        <x:v>24.033</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>478966</x:v>
+        <x:v>3623179</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>24.047</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1189974</x:v>
+        <x:v>7482590</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.23315524598794</x:v>
+        <x:v>1.32150577315614</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>232042</x:v>
+        <x:v>236232</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.75</x:v>
+        <x:v>23.818</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1083,28 +1083,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>2725090</x:v>
+        <x:v>2228571</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.908</x:v>
+        <x:v>23.954</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>2518101</x:v>
+        <x:v>2003817</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.964</x:v>
+        <x:v>23.85</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>5243191</x:v>
+        <x:v>4232388</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.02731445171639</x:v>
+        <x:v>0.747485185776151</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>206989</x:v>
+        <x:v>224754</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.234</x:v>
+        <x:v>24.883</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1112,28 +1112,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>1132717</x:v>
+        <x:v>617834</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.836</x:v>
+        <x:v>24.16</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>932997</x:v>
+        <x:v>424841</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>24.015</x:v>
+        <x:v>24.182</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>2065714</x:v>
+        <x:v>1042675</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.404741663104179</x:v>
+        <x:v>0.184147605578493</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>199720</x:v>
+        <x:v>192993</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.997</x:v>
+        <x:v>24.112</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1141,28 +1141,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>518246</x:v>
+        <x:v>1210884</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.996</x:v>
+        <x:v>23.903</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>339473</x:v>
+        <x:v>1033400</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>24.018</x:v>
+        <x:v>24.106</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>857719</x:v>
+        <x:v>2244284</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.168055507459432</x:v>
+        <x:v>0.396364662850959</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>178773</x:v>
+        <x:v>177484</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.955</x:v>
+        <x:v>22.724</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1170,28 +1170,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>2302328</x:v>
+        <x:v>2363676</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.752</x:v>
+        <x:v>23.782</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>2155617</x:v>
+        <x:v>2217545</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.858</x:v>
+        <x:v>23.894</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>4457945</x:v>
+        <x:v>4581221</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.873458800844144</x:v>
+        <x:v>0.809092840794985</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>146711</x:v>
+        <x:v>146131</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>22.193</x:v>
+        <x:v>22.085</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1199,28 +1199,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>569193</x:v>
+        <x:v>6080465</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.855</x:v>
+        <x:v>23.957</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>468534</x:v>
+        <x:v>5951870</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.999</x:v>
+        <x:v>24.01</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1037727</x:v>
+        <x:v>12032335</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.203325025549573</x:v>
+        <x:v>2.12503961423099</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>100659</x:v>
+        <x:v>128595</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.185</x:v>
+        <x:v>21.502</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1228,28 +1228,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>129745</x:v>
+        <x:v>613213</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>24.777</x:v>
+        <x:v>23.916</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>36034</x:v>
+        <x:v>487057</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.859</x:v>
+        <x:v>24.039</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>165779</x:v>
+        <x:v>1100270</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0324815865931817</x:v>
+        <x:v>0.194319501273023</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>93711</x:v>
+        <x:v>126156</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>25.13</x:v>
+        <x:v>23.441</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1257,28 +1257,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>3122262</x:v>
+        <x:v>131335</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.65</x:v>
+        <x:v>24.778</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>3051156</x:v>
+        <x:v>36969</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.706</x:v>
+        <x:v>23.891</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>6173418</x:v>
+        <x:v>168304</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>1.20957667342007</x:v>
+        <x:v>0.0297242943479826</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>71106</x:v>
+        <x:v>94366</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>21.225</x:v>
+        <x:v>25.126</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1286,28 +1286,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>45431</x:v>
+        <x:v>14210399</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>24.393</x:v>
+        <x:v>23.963</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>8000</x:v>
+        <x:v>14155187</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>24.045</x:v>
+        <x:v>23.963</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>53431</x:v>
+        <x:v>28365586</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0104688992771116</x:v>
+        <x:v>5.00966719517667</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>37431</x:v>
+        <x:v>55212</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>24.467</x:v>
+        <x:v>23.957</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1315,28 +1315,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1945209</x:v>
+        <x:v>3273308</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.799</x:v>
+        <x:v>23.712</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1913232</x:v>
+        <x:v>3229149</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.812</x:v>
+        <x:v>23.776</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>3858441</x:v>
+        <x:v>6502457</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.755996148222528</x:v>
+        <x:v>1.14840375661363</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>31977</x:v>
+        <x:v>44159</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>23.054</x:v>
+        <x:v>19.038</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1344,28 +1344,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>39534</x:v>
+        <x:v>51121</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>24.66</x:v>
+        <x:v>24.458</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>13456</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>24.054</x:v>
+        <x:v>24.18</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>52990</x:v>
+        <x:v>60121</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0103824927980788</x:v>
+        <x:v>0.0106180144292177</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>26078</x:v>
+        <x:v>42121</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.973</x:v>
+        <x:v>24.518</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1373,28 +1373,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>906944</x:v>
+        <x:v>2343844</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.616</x:v>
+        <x:v>23.97</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>882470</x:v>
+        <x:v>2307834</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>24.273</x:v>
+        <x:v>23.968</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1789414</x:v>
+        <x:v>4651678</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.350605358893778</x:v>
+        <x:v>0.821536303855137</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>24474</x:v>
+        <x:v>36010</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>-0.091</x:v>
+        <x:v>24.073</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1402,28 +1402,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>84063</x:v>
+        <x:v>40730</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.81</x:v>
+        <x:v>24.672</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>64123</x:v>
+        <x:v>13771</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.884</x:v>
+        <x:v>24.079</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>148186</x:v>
+        <x:v>54501</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0290345362856406</x:v>
+        <x:v>0.0096254620582957</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>19940</x:v>
+        <x:v>26959</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>23.574</x:v>
+        <x:v>24.975</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1431,28 +1431,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>5121789</x:v>
+        <x:v>915198</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.797</x:v>
+        <x:v>23.629</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>5108622</x:v>
+        <x:v>898093</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.875</x:v>
+        <x:v>24.284</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>10230411</x:v>
+        <x:v>1813291</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>2.00447572237942</x:v>
+        <x:v>0.32024666925651</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>13167</x:v>
+        <x:v>17105</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>-6.517</x:v>
+        <x:v>-10.784</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1460,10 +1460,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>27200</x:v>
+        <x:v>29200</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.762</x:v>
+        <x:v>23.806</x:v>
       </x:c>
       <x:c r="D32" s="0">
         <x:v>16470</x:v>
@@ -1472,16 +1472,16 @@
         <x:v>24.087</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>43670</x:v>
+        <x:v>45670</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00855639668790525</x:v>
+        <x:v>0.00806581259430771</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>10730</x:v>
+        <x:v>12730</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.263</x:v>
+        <x:v>23.442</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1489,28 +1489,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>72288</x:v>
+        <x:v>84063</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>24.028</x:v>
+        <x:v>23.81</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>63143</x:v>
+        <x:v>73096</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.89</x:v>
+        <x:v>24.037</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>135431</x:v>
+        <x:v>157159</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.026535410117694</x:v>
+        <x:v>0.0277559676266434</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>9145</x:v>
+        <x:v>10967</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>24.98</x:v>
+        <x:v>22.3</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1518,28 +1518,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>10222</x:v>
+        <x:v>87492</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.642</x:v>
+        <x:v>24.177</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>5348</x:v>
+        <x:v>77036</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>24.167</x:v>
+        <x:v>24.131</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>15570</x:v>
+        <x:v>164528</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00305067772912033</x:v>
+        <x:v>0.029057412185598</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>4874</x:v>
+        <x:v>10456</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.065</x:v>
+        <x:v>24.516</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1547,28 +1547,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>3087</x:v>
+        <x:v>10722</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>24.661</x:v>
+        <x:v>23.683</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>0</x:v>
+        <x:v>6144</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>0</x:v>
+        <x:v>24.274</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>3087</x:v>
+        <x:v>16866</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000604845353230215</x:v>
+        <x:v>0.00297871677721905</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>3087</x:v>
+        <x:v>4578</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>24.661</x:v>
+        <x:v>22.889</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1576,28 +1576,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>775</x:v>
+        <x:v>8087</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.299</x:v>
+        <x:v>24.525</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>1</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>24</x:v>
+        <x:v>24.55</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>776</x:v>
+        <x:v>13087</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.000152044053808438</x:v>
+        <x:v>0.00231130478260795</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>774</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.298</x:v>
+        <x:v>24.483</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1605,28 +1605,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>2206735</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.909</x:v>
+        <x:v>23.299</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>2206060</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.92</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>4412795</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.864612423228872</x:v>
+        <x:v>0.00013704993591379</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>675</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>-11.391</x:v>
+        <x:v>23.298</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1649,7 +1649,7 @@
         <x:v>2221</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000435167324108943</x:v>
+        <x:v>0.000392252458330576</x:v>
       </x:c>
       <x:c r="H38" s="0">
         <x:v>459</x:v>
@@ -1663,10 +1663,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>24.036</x:v>
+        <x:v>24.043</x:v>
       </x:c>
       <x:c r="D39" s="0">
         <x:v>180</x:v>
@@ -1675,16 +1675,16 @@
         <x:v>24.833</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.26985788900774E-05</x:v>
+        <x:v>5.66920482323796E-05</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-40</x:v>
+        <x:v>-39</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>27.625</x:v>
+        <x:v>27.692</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1692,28 +1692,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>190492</x:v>
+        <x:v>77982</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>24.009</x:v>
+        <x:v>24.17</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>193627</x:v>
+        <x:v>79107</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.937</x:v>
+        <x:v>24.291</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>384119</x:v>
+        <x:v>157089</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.0752616107021176</x:v>
+        <x:v>0.0277436048746924</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-3135</x:v>
+        <x:v>-1125</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>19.588</x:v>
+        <x:v>32.67</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1721,28 +1721,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>126971</x:v>
+        <x:v>192464</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>24.104</x:v>
+        <x:v>24.019</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>133813</x:v>
+        <x:v>193752</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>24.124</x:v>
+        <x:v>23.938</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>260784</x:v>
+        <x:v>386216</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0510962068664686</x:v>
+        <x:v>0.0682098943928869</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-6842</x:v>
+        <x:v>-1288</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>24.498</x:v>
+        <x:v>11.738</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1750,28 +1750,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>63331</x:v>
+        <x:v>132471</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.93</x:v>
+        <x:v>24.143</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>72752</x:v>
+        <x:v>137913</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.214</x:v>
+        <x:v>24.15</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>136083</x:v>
+        <x:v>270384</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.0266631584721825</x:v>
+        <x:v>0.0477527189073636</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-9421</x:v>
+        <x:v>-5442</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>26.124</x:v>
+        <x:v>24.314</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1779,28 +1779,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>1478354</x:v>
+        <x:v>1489059</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.726</x:v>
+        <x:v>23.735</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>1551805</x:v>
+        <x:v>1561120</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.897</x:v>
+        <x:v>23.903</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>3030159</x:v>
+        <x:v>3050179</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.593708322221806</x:v>
+        <x:v>0.53869437690153</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-73451</x:v>
+        <x:v>-72061</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>27.328</x:v>
+        <x:v>27.378</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1808,28 +1808,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>7134617</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.907</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>7299757</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.922</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>14434374</x:v>
+        <x:v>200101</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2.82817105302463</x:v>
+        <x:v>0.035339986116347</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-165140</x:v>
+        <x:v>-199901</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>24.577</x:v>
+        <x:v>25.501</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1837,28 +1837,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>100</x:v>
+        <x:v>8169354</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.68</x:v>
+        <x:v>24.039</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>200001</x:v>
+        <x:v>8408417</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.057</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>200101</x:v>
+        <x:v>16577771</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.0392064010452605</x:v>
+        <x:v>2.92781243961789</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-199901</x:v>
+        <x:v>-239063</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>25.501</x:v>
+        <x:v>24.677</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1866,28 +1866,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>2971858</x:v>
+        <x:v>3373806</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.954</x:v>
+        <x:v>24.075</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>3505395</x:v>
+        <x:v>3934049</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.164</x:v>
+        <x:v>24.251</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>6477253</x:v>
+        <x:v>7307855</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.26910799441091</x:v>
+        <x:v>1.29064569512535</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-533537</x:v>
+        <x:v>-560243</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>25.331</x:v>
+        <x:v>25.314</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1895,28 +1895,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1254608</x:v>
+        <x:v>1392336</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>24.136</x:v>
+        <x:v>24.222</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1804077</x:v>
+        <x:v>1962374</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.724</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>3058685</x:v>
+        <x:v>3354710</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.599297508663739</x:v>
+        <x:v>0.592477822821327</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-549469</x:v>
+        <x:v>-570038</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.99</x:v>
+        <x:v>25.95</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1924,28 +1924,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>3692032</x:v>
+        <x:v>4214844</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>24.065</x:v>
+        <x:v>24.169</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4249159</x:v>
+        <x:v>4805285</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>24.037</x:v>
+        <x:v>24.14</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>7941191</x:v>
+        <x:v>9020129</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.55594184498335</x:v>
+        <x:v>1.59305167704139</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-557127</x:v>
+        <x:v>-590441</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.849</x:v>
+        <x:v>23.929</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1953,28 +1953,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>0</x:v>
+        <x:v>3861759</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>0</x:v>
+        <x:v>23.953</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>678087</x:v>
+        <x:v>4583278</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>24.396</x:v>
+        <x:v>23.855</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>678087</x:v>
+        <x:v>8445037</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.132859660199487</x:v>
+        <x:v>1.49148425211287</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-678087</x:v>
+        <x:v>-721519</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>24.396</x:v>
+        <x:v>23.33</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1982,28 +1982,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>3638627</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.905</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>4341251</x:v>
+        <x:v>728023</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>23.79</x:v>
+        <x:v>24.424</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>7979878</x:v>
+        <x:v>728023</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.5635219072381</x:v>
+        <x:v>0.128576682337326</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-702624</x:v>
+        <x:v>-728023</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.199</x:v>
+        <x:v>24.424</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2011,28 +2011,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>4504801</x:v>
+        <x:v>5021000</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.885</x:v>
+        <x:v>23.993</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>5411312</x:v>
+        <x:v>5778867</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.864</x:v>
+        <x:v>23.933</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>9916113</x:v>
+        <x:v>10799867</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>1.94289435379194</x:v>
+        <x:v>1.90737252606631</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-906511</x:v>
+        <x:v>-757867</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.76</x:v>
+        <x:v>23.536</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2040,28 +2040,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>482988</x:v>
+        <x:v>527425</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.774</x:v>
+        <x:v>23.865</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1459112</x:v>
+        <x:v>1472357</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.7</x:v>
+        <x:v>23.713</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>1942100</x:v>
+        <x:v>1999782</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>0.38052159394506</x:v>
+        <x:v>0.353182983172101</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-976124</x:v>
+        <x:v>-944932</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.664</x:v>
+        <x:v>23.627</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2069,28 +2069,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>962076</x:v>
+        <x:v>1059953</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>24.214</x:v>
+        <x:v>24.287</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>2387892</x:v>
+        <x:v>2480904</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.966</x:v>
+        <x:v>24.011</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>3349968</x:v>
+        <x:v>3540857</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>0.656369477897609</x:v>
+        <x:v>0.625353382641616</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1425816</x:v>
+        <x:v>-1420951</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.798</x:v>
+        <x:v>23.806</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2098,28 +2098,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>18731394</x:v>
+        <x:v>20445641</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>23.895</x:v>
+        <x:v>23.983</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>21937708</x:v>
+        <x:v>23613942</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.851</x:v>
+        <x:v>23.933</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>40669102</x:v>
+        <x:v>44059583</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>7.96842156292376</x:v>
+        <x:v>7.78139565275555</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-3206314</x:v>
+        <x:v>-3168301</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.595</x:v>
+        <x:v>23.608</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2127,28 +2127,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>7308319</x:v>
+        <x:v>8145605</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>23.953</x:v>
+        <x:v>24.063</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>12981096</x:v>
+        <x:v>14191745</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.795</x:v>
+        <x:v>23.889</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>20289415</x:v>
+        <x:v>22337350</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>3.97536714690944</x:v>
+        <x:v>3.94501596131945</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-5672777</x:v>
+        <x:v>-6046140</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.592</x:v>
+        <x:v>23.655</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
@@ -2156,28 +2156,28 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>14517923</x:v>
+        <x:v>15841879</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>23.992</x:v>
+        <x:v>24.06</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>27045688</x:v>
+        <x:v>27986346</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>23.818</x:v>
+        <x:v>23.859</x:v>
       </x:c>
       <x:c r="F56" s="0">
-        <x:v>41563611</x:v>
+        <x:v>43828225</x:v>
       </x:c>
       <x:c r="G56" s="0">
-        <x:v>8.14368544762496</x:v>
+        <x:v>7.7405353446716</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>-12527765</x:v>
+        <x:v>-12144467</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>23.618</x:v>
+        <x:v>23.596</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -61,12 +61,12 @@
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
@@ -79,63 +79,66 @@
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
   </x:si>
   <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
     <x:t>GCM</x:t>
   </x:si>
   <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
     <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
@@ -151,12 +154,6 @@
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">AKTIF </x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
@@ -184,10 +181,10 @@
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
   </x:si>
   <x:si>
     <x:t>ATA</x:t>
@@ -553,7 +550,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I56"/>
+  <x:dimension ref="A1:I55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -590,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>29852667</x:v>
+        <x:v>31052431</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.995</x:v>
+        <x:v>24.0200755173556</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>24137138</x:v>
+        <x:v>25366388</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>24.051</x:v>
+        <x:v>24.0810305729383</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>53989805</x:v>
+        <x:v>56418819</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.53517952995877</x:v>
+        <x:v>9.41234315207973</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>5715529</x:v>
+        <x:v>5686043</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.758</x:v>
+        <x:v>23.7481448283907</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -619,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>13886902</x:v>
+        <x:v>15203669</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>24.118</x:v>
+        <x:v>24.1656962512101</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>8616128</x:v>
+        <x:v>9648290</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>24.203</x:v>
+        <x:v>24.2558644665432</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>22503030</x:v>
+        <x:v>24851959</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>3.97427682908001</x:v>
+        <x:v>4.14604861029466</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>5270774</x:v>
+        <x:v>5555379</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.978</x:v>
+        <x:v>24.0090968382238</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -648,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>14642358</x:v>
+        <x:v>15721799</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>24.029</x:v>
+        <x:v>24.0752359195301</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>10779440</x:v>
+        <x:v>11608200</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.182</x:v>
+        <x:v>24.2165967988321</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>25421798</x:v>
+        <x:v>27329999</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.48976261174396</x:v>
+        <x:v>4.5594596535953</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>3862918</x:v>
+        <x:v>4113599</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.601</x:v>
+        <x:v>23.6763284520999</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -677,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>39858373</x:v>
+        <x:v>42165005</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.955</x:v>
+        <x:v>23.9919655694375</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>37262651</x:v>
+        <x:v>39614712</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.936</x:v>
+        <x:v>23.9784969417441</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>77121024</x:v>
+        <x:v>81779717</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.6204012845436</x:v>
+        <x:v>13.6432979797746</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2595722</x:v>
+        <x:v>2550293</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.222</x:v>
+        <x:v>24.2011791018085</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -706,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>5526568</x:v>
+        <x:v>6033513</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.242</x:v>
+        <x:v>24.2781502336674</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>3750511</x:v>
+        <x:v>4280039</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.291</x:v>
+        <x:v>24.3299980846515</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>9277079</x:v>
+        <x:v>10313552</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.63843180723862</x:v>
+        <x:v>1.72060834064638</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1776057</x:v>
+        <x:v>1753474</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>24.137</x:v>
+        <x:v>24.1515952780318</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -735,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>15518028</x:v>
+        <x:v>16209614</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>24.082</x:v>
+        <x:v>24.105523825484</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>14284537</x:v>
+        <x:v>15033185</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.091</x:v>
+        <x:v>24.1162733280977</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>29802565</x:v>
+        <x:v>31242799</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>5.26345312283061</x:v>
+        <x:v>5.21223149352796</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1233491</x:v>
+        <x:v>1176429</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.98</x:v>
+        <x:v>23.9681595974262</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -764,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>18155667</x:v>
+        <x:v>19681879</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>24.074</x:v>
+        <x:v>24.1186578655639</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>17079854</x:v>
+        <x:v>18538281</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>24.153</x:v>
+        <x:v>24.1950891342762</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>35235521</x:v>
+        <x:v>38220160</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>6.22297151409664</x:v>
+        <x:v>6.37626358764071</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1075813</x:v>
+        <x:v>1143598</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>22.817</x:v>
+        <x:v>22.8796697451086</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -793,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>3768227</x:v>
+        <x:v>2520900</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>24.035</x:v>
+        <x:v>24.0664196987213</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>2770882</x:v>
+        <x:v>1549337</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>24.238</x:v>
+        <x:v>24.1858784265054</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>6539109</x:v>
+        <x:v>4070237</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.15487689353516</x:v>
+        <x:v>0.679037031141888</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>997345</x:v>
+        <x:v>971563</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.469</x:v>
+        <x:v>23.8759206503541</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -822,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>2347231</x:v>
+        <x:v>4061253</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>24.022</x:v>
+        <x:v>24.0817303682459</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1415089</x:v>
+        <x:v>3093907</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>24.133</x:v>
+        <x:v>24.2875153385798</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>3762320</x:v>
+        <x:v>7155160</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.66446612743192</x:v>
+        <x:v>1.19369427474252</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>932142</x:v>
+        <x:v>967346</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.853</x:v>
+        <x:v>23.4235588761317</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -851,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>8015289</x:v>
+        <x:v>8558493</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>24.066</x:v>
+        <x:v>24.1054712412875</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>7083727</x:v>
+        <x:v>7631806</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>24.157</x:v>
+        <x:v>24.1919455541526</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>15099016</x:v>
+        <x:v>16190299</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2.6666484215996</x:v>
+        <x:v>2.70102516542881</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>931562</x:v>
+        <x:v>926687</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.378</x:v>
+        <x:v>23.3933050192838</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -880,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2066461</x:v>
+        <x:v>2099320</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.945</x:v>
+        <x:v>23.9554723674326</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1378690</x:v>
+        <x:v>1440162</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>24.089</x:v>
+        <x:v>24.1154058758016</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>3445151</x:v>
+        <x:v>3539482</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.608450674952744</x:v>
+        <x:v>0.590491253718187</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>687771</x:v>
+        <x:v>659158</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.656</x:v>
+        <x:v>23.6060414854898</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -909,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>11805460</x:v>
+        <x:v>12655496</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>24.094</x:v>
+        <x:v>24.1340763308441</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>11449334</x:v>
+        <x:v>12236394</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>24.123</x:v>
+        <x:v>24.1605090309738</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>23254794</x:v>
+        <x:v>24891890</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>4.10704642704689</x:v>
+        <x:v>4.15271029306413</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>356126</x:v>
+        <x:v>419102</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.174</x:v>
+        <x:v>23.3623288009592</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -938,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>503734</x:v>
+        <x:v>517068</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>24.232</x:v>
+        <x:v>24.2451037663564</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>173948</x:v>
+        <x:v>186164</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>24.291</x:v>
+        <x:v>24.3207709705416</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>677682</x:v>
+        <x:v>703232</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.119685920966403</x:v>
+        <x:v>0.117320089587897</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>329786</x:v>
+        <x:v>330904</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>24.201</x:v>
+        <x:v>24.2025339896238</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -967,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>1031893</x:v>
+        <x:v>2817217</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.975</x:v>
+        <x:v>24.1129026877716</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>727747</x:v>
+        <x:v>2497459</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>24.013</x:v>
+        <x:v>23.9959464109219</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1759640</x:v>
+        <x:v>5314676</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.310771326329048</x:v>
+        <x:v>0.886646603753306</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>304146</x:v>
+        <x:v>319758</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.885</x:v>
+        <x:v>25.0263857162648</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -996,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>3213478</x:v>
+        <x:v>1040670</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>24.056</x:v>
+        <x:v>23.9815649187758</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>2951231</x:v>
+        <x:v>743416</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>24.117</x:v>
+        <x:v>24.0273920696261</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>6164709</x:v>
+        <x:v>1784086</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>1.0887538316716</x:v>
+        <x:v>0.297638801067802</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>262247</x:v>
+        <x:v>297254</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.364</x:v>
+        <x:v>23.8669537203512</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1025,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>808664</x:v>
+        <x:v>868063</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>24.077</x:v>
+        <x:v>24.119229992467</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>559580</x:v>
+        <x:v>620848</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>24.186</x:v>
+        <x:v>24.2355618587496</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>1368244</x:v>
+        <x:v>1488911</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.241646588291788</x:v>
+        <x:v>0.248394799878852</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>249084</x:v>
+        <x:v>247215</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.832</x:v>
+        <x:v>23.8270777908698</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1054,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>3859411</x:v>
+        <x:v>4055508</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>24.033</x:v>
+        <x:v>24.0655997424665</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>3623179</x:v>
+        <x:v>3828234</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>24.047</x:v>
+        <x:v>24.0831822395816</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>7482590</x:v>
+        <x:v>7883742</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.32150577315614</x:v>
+        <x:v>1.3152435010464</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>236232</x:v>
+        <x:v>227274</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.818</x:v>
+        <x:v>23.7694377826241</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1083,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>2228571</x:v>
+        <x:v>1318371</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.954</x:v>
+        <x:v>23.9571642252742</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>2003817</x:v>
+        <x:v>1129617</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.85</x:v>
+        <x:v>24.144736632047</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>4232388</x:v>
+        <x:v>2447988</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.747485185776151</x:v>
+        <x:v>0.408397472626525</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>224754</x:v>
+        <x:v>188754</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>24.883</x:v>
+        <x:v>22.8346185869226</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1112,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>617834</x:v>
+        <x:v>2442767</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>24.16</x:v>
+        <x:v>23.8119990287948</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>424841</x:v>
+        <x:v>2270956</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>24.182</x:v>
+        <x:v>23.9126991512019</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>1042675</x:v>
+        <x:v>4713723</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.184147605578493</x:v>
+        <x:v>0.786389704468126</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>192993</x:v>
+        <x:v>171811</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>24.112</x:v>
+        <x:v>22.4809693090374</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1141,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>1210884</x:v>
+        <x:v>629535</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.903</x:v>
+        <x:v>24.1686557729146</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>1033400</x:v>
+        <x:v>470127</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>24.106</x:v>
+        <x:v>24.2335721764003</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>2244284</x:v>
+        <x:v>1099662</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.396364662850959</x:v>
+        <x:v>0.183456447312417</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>177484</x:v>
+        <x:v>159408</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.724</x:v>
+        <x:v>23.9772039384927</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1170,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>2363676</x:v>
+        <x:v>3323752</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.782</x:v>
+        <x:v>24.0776025116695</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>2217545</x:v>
+        <x:v>3188421</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.894</x:v>
+        <x:v>24.1586378161196</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>4581221</x:v>
+        <x:v>6512173</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.809092840794985</x:v>
+        <x:v>1.0864248495118</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>146131</x:v>
+        <x:v>135331</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>22.085</x:v>
+        <x:v>22.1683971821421</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1199,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>6080465</x:v>
+        <x:v>133026</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.957</x:v>
+        <x:v>24.7775005554616</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>5951870</x:v>
+        <x:v>40113</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>24.01</x:v>
+        <x:v>23.9663810350061</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>12032335</x:v>
+        <x:v>173139</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.12503961423099</x:v>
+        <x:v>0.0288847535253783</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>128595</x:v>
+        <x:v>92913</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>21.502</x:v>
+        <x:v>25.1276823096191</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1228,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>613213</x:v>
+        <x:v>635263</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.916</x:v>
+        <x:v>23.9444866230441</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>487057</x:v>
+        <x:v>552762</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>24.039</x:v>
+        <x:v>24.1044460764785</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1100270</x:v>
+        <x:v>1188025</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.194319501273023</x:v>
+        <x:v>0.198198033412389</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>126156</x:v>
+        <x:v>82501</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.441</x:v>
+        <x:v>22.8727480089752</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1257,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>131335</x:v>
+        <x:v>14607671</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>24.778</x:v>
+        <x:v>23.9828309175174</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>36969</x:v>
+        <x:v>14532847</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.891</x:v>
+        <x:v>23.9823775712095</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>168304</x:v>
+        <x:v>29140518</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0297242943479826</x:v>
+        <x:v>4.86150826810742</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>94366</x:v>
+        <x:v>74824</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>25.126</x:v>
+        <x:v>24.0708830469269</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1286,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>14210399</x:v>
+        <x:v>124301</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.963</x:v>
+        <x:v>24.1249702295503</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>14155187</x:v>
+        <x:v>73096</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.963</x:v>
+        <x:v>24.0368506886237</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>28365586</x:v>
+        <x:v>197397</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>5.00966719517667</x:v>
+        <x:v>0.0329317120443638</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>55212</x:v>
+        <x:v>51205</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.957</x:v>
+        <x:v>24.2507623585136</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1315,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>3273308</x:v>
+        <x:v>3309732</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.712</x:v>
+        <x:v>23.7230137345541</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>3229149</x:v>
+        <x:v>3266134</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.776</x:v>
+        <x:v>23.7867418849586</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>6502457</x:v>
+        <x:v>6575866</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>1.14840375661363</x:v>
+        <x:v>1.09705074319429</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>44159</x:v>
+        <x:v>43598</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>19.038</x:v>
+        <x:v>18.9488342127137</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1344,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>51121</x:v>
+        <x:v>52266</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>24.458</x:v>
+        <x:v>24.4580771815867</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>9000</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>24.18</x:v>
+        <x:v>24.2981818806041</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>60121</x:v>
+        <x:v>63266</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0106180144292177</x:v>
+        <x:v>0.0105546573362246</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>42121</x:v>
+        <x:v>41266</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.518</x:v>
+        <x:v>24.5006993962624</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1373,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>2343844</x:v>
+        <x:v>120044</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.97</x:v>
+        <x:v>24.3624364250658</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>2307834</x:v>
+        <x:v>79605</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.968</x:v>
+        <x:v>24.2943072781282</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4651678</x:v>
+        <x:v>199649</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.821536303855137</x:v>
+        <x:v>0.0333074128682057</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>36010</x:v>
+        <x:v>40439</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.073</x:v>
+        <x:v>24.4965500466185</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1402,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>40730</x:v>
+        <x:v>41092</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>24.672</x:v>
+        <x:v>24.6724685055597</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>13771</x:v>
+        <x:v>13910</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>24.079</x:v>
+        <x:v>24.0871124338881</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>54501</x:v>
+        <x:v>55002</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0096254620582957</x:v>
+        <x:v>0.00917597544979964</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>26959</x:v>
+        <x:v>27182</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>24.975</x:v>
+        <x:v>24.9720161090088</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1431,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>915198</x:v>
+        <x:v>926682</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.629</x:v>
+        <x:v>23.6427816155354</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>898093</x:v>
+        <x:v>908113</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>24.284</x:v>
+        <x:v>24.2891570444312</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1813291</x:v>
+        <x:v>1834795</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.32024666925651</x:v>
+        <x:v>0.306098575968422</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>17105</x:v>
+        <x:v>18569</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>-10.784</x:v>
+        <x:v>-7.96807141159956</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1460,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>29200</x:v>
+        <x:v>2413578</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.806</x:v>
+        <x:v>23.9898775046432</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>16470</x:v>
+        <x:v>2397888</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>24.087</x:v>
+        <x:v>23.9965843577974</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>45670</x:v>
+        <x:v>4811466</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00806581259430771</x:v>
+        <x:v>0.802696154567937</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>12730</x:v>
+        <x:v>15690</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.442</x:v>
+        <x:v>22.96487542074</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1489,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>84063</x:v>
+        <x:v>6456406</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.81</x:v>
+        <x:v>23.993833105902</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>73096</x:v>
+        <x:v>6441577</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>24.037</x:v>
+        <x:v>24.056289122015</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>157159</x:v>
+        <x:v>12897983</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0277559676266434</x:v>
+        <x:v>2.15176857859592</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>10967</x:v>
+        <x:v>14829</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>22.3</x:v>
+        <x:v>-3.13646812176574</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1518,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>87492</x:v>
+        <x:v>29200</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>24.177</x:v>
+        <x:v>23.8059784394094</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>77036</x:v>
+        <x:v>16470</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>24.131</x:v>
+        <x:v>24.0873474004128</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>164528</x:v>
+        <x:v>45670</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.029057412185598</x:v>
+        <x:v>0.00761911928279607</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>10456</x:v>
+        <x:v>12730</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>24.516</x:v>
+        <x:v>23.4419449132723</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1547,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>10722</x:v>
+        <x:v>97468</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.683</x:v>
+        <x:v>24.2439143849167</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>6144</x:v>
+        <x:v>87045</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.274</x:v>
+        <x:v>24.1830929959236</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>16866</x:v>
+        <x:v>184513</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00297871677721905</x:v>
+        <x:v>0.0307822762475706</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>4578</x:v>
+        <x:v>10423</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>22.889</x:v>
+        <x:v>24.7518485502148</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1576,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>8087</x:v>
+        <x:v>11128</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>24.525</x:v>
+        <x:v>23.7100537082088</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>5000</x:v>
+        <x:v>6789</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>24.55</x:v>
+        <x:v>24.3062659404225</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>13087</x:v>
+        <x:v>17917</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00231130478260795</x:v>
+        <x:v>0.00298909043551253</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>3087</x:v>
+        <x:v>4339</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>24.483</x:v>
+        <x:v>22.7771924856924</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1605,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>775</x:v>
+        <x:v>8087</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.299</x:v>
+        <x:v>24.5245555796552</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>1</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>24</x:v>
+        <x:v>24.5500005722046</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>776</x:v>
+        <x:v>13087</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00013704993591379</x:v>
+        <x:v>0.00218330225649118</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>774</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>23.298</x:v>
+        <x:v>24.4833424397954</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1634,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>1340</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>24.339</x:v>
+        <x:v>23.2999992370605</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>881</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>24.215</x:v>
+        <x:v>24.1399993896484</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>2221</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000392252458330576</x:v>
+        <x:v>0.000129459964165749</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>459</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>24.577</x:v>
+        <x:v>23.2989139655456</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1663,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>141</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>24.043</x:v>
+        <x:v>24.3394027823832</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>180</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.833</x:v>
+        <x:v>24.2141656215291</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>321</x:v>
+        <x:v>2221</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>5.66920482323796E-05</x:v>
+        <x:v>0.000370529098469237</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-39</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>27.692</x:v>
+        <x:v>24.5797817338266</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1692,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>77982</x:v>
+        <x:v>214081</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>24.17</x:v>
+        <x:v>24.0832058213055</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>79107</x:v>
+        <x:v>214243</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>24.291</x:v>
+        <x:v>24.01220248465</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>157089</x:v>
+        <x:v>428324</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.0277436048746924</x:v>
+        <x:v>0.071457228983673</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-1125</x:v>
+        <x:v>-162</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>32.67</x:v>
+        <x:v>-69.8178303212295</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1721,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>192464</x:v>
+        <x:v>133471</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>24.019</x:v>
+        <x:v>24.1465597741973</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>193752</x:v>
+        <x:v>137915</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.938</x:v>
+        <x:v>24.1501759394169</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>386216</x:v>
+        <x:v>271386</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0682098943928869</x:v>
+        <x:v>0.0452752858699561</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-1288</x:v>
+        <x:v>-4444</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>11.738</x:v>
+        <x:v>24.2587837675045</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1750,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>132471</x:v>
+        <x:v>1489484</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>24.143</x:v>
+        <x:v>23.7350085063385</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>137913</x:v>
+        <x:v>1562315</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.15</x:v>
+        <x:v>23.9035464467877</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>270384</x:v>
+        <x:v>3051799</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.0477527189073636</x:v>
+        <x:v>0.509131171625088</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-5442</x:v>
+        <x:v>-72831</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>24.314</x:v>
+        <x:v>27.3503557133365</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1779,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>1489059</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.735</x:v>
+        <x:v>23.6800003051758</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>1561120</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.903</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>3050179</x:v>
+        <x:v>200101</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.53869437690153</x:v>
+        <x:v>0.0333828199607352</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-72061</x:v>
+        <x:v>-199901</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>27.378</x:v>
+        <x:v>25.5009104505204</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1808,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>100</x:v>
+        <x:v>9192862</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.68</x:v>
+        <x:v>24.1108376278135</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>200001</x:v>
+        <x:v>9407578</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.125188963795</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>200101</x:v>
+        <x:v>18600440</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.035339986116347</x:v>
+        <x:v>3.1031086286948</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-199901</x:v>
+        <x:v>-214716</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>25.501</x:v>
+        <x:v>24.7396278094956</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1837,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>8169354</x:v>
+        <x:v>3468685</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>24.039</x:v>
+        <x:v>24.0932371371692</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>8408417</x:v>
+        <x:v>3997220</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>24.057</x:v>
+        <x:v>24.2558981955217</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>16577771</x:v>
+        <x:v>7465905</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.92781243961789</x:v>
+        <x:v>1.24553581670733</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-239063</x:v>
+        <x:v>-528535</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>24.677</x:v>
+        <x:v>25.323414960147</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1866,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>3373806</x:v>
+        <x:v>1443087</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>24.075</x:v>
+        <x:v>24.2390580307777</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>3934049</x:v>
+        <x:v>1993243</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.251</x:v>
+        <x:v>24.7239266292097</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>7307855</x:v>
+        <x:v>3436330</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.29064569512535</x:v>
+        <x:v>0.573282420955783</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-560243</x:v>
+        <x:v>-550156</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>25.314</x:v>
+        <x:v>25.9957614744272</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1895,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1392336</x:v>
+        <x:v>4507300</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>24.222</x:v>
+        <x:v>24.1951035357367</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1962374</x:v>
+        <x:v>5149887</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>24.724</x:v>
+        <x:v>24.1698351416795</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>3354710</x:v>
+        <x:v>9657187</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.592477822821327</x:v>
+        <x:v>1.6111070656726</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-570038</x:v>
+        <x:v>-642587</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.95</x:v>
+        <x:v>23.9925949663666</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1924,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>4214844</x:v>
+        <x:v>3960661</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>24.169</x:v>
+        <x:v>23.9721850668096</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4805285</x:v>
+        <x:v>4741216</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>24.14</x:v>
+        <x:v>23.8853439465745</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>9020129</x:v>
+        <x:v>8701877</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.59305167704139</x:v>
+        <x:v>1.45173284097262</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-590441</x:v>
+        <x:v>-780555</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.929</x:v>
+        <x:v>23.4446982033386</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1953,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>3861759</x:v>
+        <x:v>5230190</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.953</x:v>
+        <x:v>24.019302006987</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>4583278</x:v>
+        <x:v>6011272</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.855</x:v>
+        <x:v>23.9599217966711</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>8445037</x:v>
+        <x:v>11241462</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.49148425211287</x:v>
+        <x:v>1.87541142743638</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-721519</x:v>
+        <x:v>-781082</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.33</x:v>
+        <x:v>23.5623069723732</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1988,22 +1985,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>728023</x:v>
+        <x:v>801452</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.424</x:v>
+        <x:v>24.4491900781843</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>728023</x:v>
+        <x:v>801452</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.128576682337326</x:v>
+        <x:v>0.133706117526505</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-728023</x:v>
+        <x:v>-801452</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>24.424</x:v>
+        <x:v>24.4491900781843</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2011,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>5021000</x:v>
+        <x:v>553178</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.993</x:v>
+        <x:v>23.8994283238805</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>5778867</x:v>
+        <x:v>1510622</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.933</x:v>
+        <x:v>23.738331968981</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>10799867</x:v>
+        <x:v>2063800</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>1.90737252606631</x:v>
+        <x:v>0.34430344593463</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-757867</x:v>
+        <x:v>-957444</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.536</x:v>
+        <x:v>23.645256071685</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2040,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>527425</x:v>
+        <x:v>1094386</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.865</x:v>
+        <x:v>24.2975019706794</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1472357</x:v>
+        <x:v>2484300</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.713</x:v>
+        <x:v>24.0121861548467</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>1999782</x:v>
+        <x:v>3578686</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>0.353182983172101</x:v>
+        <x:v>0.597031651186169</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-944932</x:v>
+        <x:v>-1389914</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.627</x:v>
+        <x:v>23.7875351085043</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2069,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>1059953</x:v>
+        <x:v>21599564</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>24.287</x:v>
+        <x:v>24.0195699223881</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>2480904</x:v>
+        <x:v>24684911</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>24.011</x:v>
+        <x:v>23.9658146764994</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>3540857</x:v>
+        <x:v>46284475</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>0.625353382641616</x:v>
+        <x:v>7.72163205532281</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1420951</x:v>
+        <x:v>-3085347</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.806</x:v>
+        <x:v>23.5894907576953</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2098,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>20445641</x:v>
+        <x:v>8422323</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>23.983</x:v>
+        <x:v>24.0807575616496</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>23613942</x:v>
+        <x:v>14457788</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.933</x:v>
+        <x:v>23.902624711513</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>44059583</x:v>
+        <x:v>22880111</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>7.78139565275555</x:v>
+        <x:v>3.81708550279427</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-3168301</x:v>
+        <x:v>-6035465</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.608</x:v>
+        <x:v>23.6540452895859</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2127,57 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>8145605</x:v>
+        <x:v>16452802</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>24.063</x:v>
+        <x:v>24.0832689953114</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>14191745</x:v>
+        <x:v>28943419</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.889</x:v>
+        <x:v>23.884690938095</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>22337350</x:v>
+        <x:v>45396221</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>3.94501596131945</x:v>
+        <x:v>7.57344477309332</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-6046140</x:v>
+        <x:v>-12490617</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.655</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:9">
-      <x:c r="A56" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B56" s="0">
-        <x:v>15841879</x:v>
-      </x:c>
-      <x:c r="C56" s="0">
-        <x:v>24.06</x:v>
-      </x:c>
-      <x:c r="D56" s="0">
-        <x:v>27986346</x:v>
-      </x:c>
-      <x:c r="E56" s="0">
-        <x:v>23.859</x:v>
-      </x:c>
-      <x:c r="F56" s="0">
-        <x:v>43828225</x:v>
-      </x:c>
-      <x:c r="G56" s="0">
-        <x:v>7.7405353446716</x:v>
-      </x:c>
-      <x:c r="H56" s="0">
-        <x:v>-12144467</x:v>
-      </x:c>
-      <x:c r="I56" s="0">
-        <x:v>23.596</x:v>
+        <x:v>23.6231213569505</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -61,12 +61,12 @@
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
@@ -79,10 +79,13 @@
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKER</x:t>
+    <x:t>TEB</x:t>
   </x:si>
   <x:si>
     <x:t>BTCTURK</x:t>
@@ -91,24 +94,21 @@
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
@@ -118,10 +118,13 @@
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>HSBC</x:t>
   </x:si>
   <x:si>
-    <x:t>INVEST AZ</x:t>
+    <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
     <x:t>BIZIM</x:t>
@@ -130,45 +133,45 @@
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
+    <x:t xml:space="preserve">AKTIF </x:t>
   </x:si>
   <x:si>
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
     <x:t>BLUPAY</x:t>
   </x:si>
   <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
@@ -181,10 +184,10 @@
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
     <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
     <x:t>ATA</x:t>
@@ -550,7 +553,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I55"/>
+  <x:dimension ref="A1:I56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -587,28 +590,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>31052431</x:v>
+        <x:v>31727921</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>24.0200755173556</x:v>
+        <x:v>24.032</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>25366388</x:v>
+        <x:v>26048602</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>24.0810305729383</x:v>
+        <x:v>24.094</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>56418819</x:v>
+        <x:v>57776523</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.41234315207973</x:v>
+        <x:v>9.33819286275592</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>5686043</x:v>
+        <x:v>5679319</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.7481448283907</x:v>
+        <x:v>23.746</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +619,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>15203669</x:v>
+        <x:v>15980857</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>24.1656962512101</x:v>
+        <x:v>24.186</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>9648290</x:v>
+        <x:v>10425368</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>24.2558644665432</x:v>
+        <x:v>24.28</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>24851959</x:v>
+        <x:v>26406225</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.14604861029466</x:v>
+        <x:v>4.26793460429121</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>5555379</x:v>
+        <x:v>5555489</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24.0090968382238</x:v>
+        <x:v>24.009</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +648,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>15721799</x:v>
+        <x:v>16086068</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>24.0752359195301</x:v>
+        <x:v>24.086</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>11608200</x:v>
+        <x:v>12058780</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.2165967988321</x:v>
+        <x:v>24.229</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>27329999</x:v>
+        <x:v>28144848</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.5594596535953</x:v>
+        <x:v>4.54894142240007</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>4113599</x:v>
+        <x:v>4027288</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.6763284520999</x:v>
+        <x:v>23.658</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +677,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>42165005</x:v>
+        <x:v>43328315</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.9919655694375</x:v>
+        <x:v>24.007</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>39614712</x:v>
+        <x:v>40699739</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.9784969417441</x:v>
+        <x:v>23.994</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>81779717</x:v>
+        <x:v>84028054</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.6432979797746</x:v>
+        <x:v>13.5811248824037</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2550293</x:v>
+        <x:v>2628576</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.2011791018085</x:v>
+        <x:v>24.205</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +706,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>6033513</x:v>
+        <x:v>6297641</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.2781502336674</x:v>
+        <x:v>24.291</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>4280039</x:v>
+        <x:v>4544261</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.3299980846515</x:v>
+        <x:v>24.343</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>10313552</x:v>
+        <x:v>10841902</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.72060834064638</x:v>
+        <x:v>1.7523341076634</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1753474</x:v>
+        <x:v>1753380</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>24.1515952780318</x:v>
+        <x:v>24.157</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +735,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>16209614</x:v>
+        <x:v>16791015</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>24.105523825484</x:v>
+        <x:v>24.121</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>15033185</x:v>
+        <x:v>15518086</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.1162733280977</x:v>
+        <x:v>24.13</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>31242799</x:v>
+        <x:v>32309101</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>5.21223149352796</x:v>
+        <x:v>5.22199330617836</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1176429</x:v>
+        <x:v>1272929</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.9681595974262</x:v>
+        <x:v>24.013</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +764,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>19681879</x:v>
+        <x:v>20418551</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>24.1186578655639</x:v>
+        <x:v>24.135</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>18538281</x:v>
+        <x:v>19313672</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>24.1950891342762</x:v>
+        <x:v>24.21</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>38220160</x:v>
+        <x:v>39732223</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>6.37626358764071</x:v>
+        <x:v>6.42176340795078</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1143598</x:v>
+        <x:v>1104879</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>22.8796697451086</x:v>
+        <x:v>22.819</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +793,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>2520900</x:v>
+        <x:v>4301387</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>24.0664196987213</x:v>
+        <x:v>24.109</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1549337</x:v>
+        <x:v>3293651</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>24.1858784265054</x:v>
+        <x:v>24.306</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>4070237</x:v>
+        <x:v>7595038</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.679037031141888</x:v>
+        <x:v>1.22755621074602</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>971563</x:v>
+        <x:v>1007736</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.8759206503541</x:v>
+        <x:v>23.466</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +822,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>4061253</x:v>
+        <x:v>2550686</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>24.0817303682459</x:v>
+        <x:v>24.073</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>3093907</x:v>
+        <x:v>1617832</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>24.2875153385798</x:v>
+        <x:v>24.202</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>7155160</x:v>
+        <x:v>4168518</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.19369427474252</x:v>
+        <x:v>0.67374121900464</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>967346</x:v>
+        <x:v>932854</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.4235588761317</x:v>
+        <x:v>23.849</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +851,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>8558493</x:v>
+        <x:v>8792556</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>24.1054712412875</x:v>
+        <x:v>24.118</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>7631806</x:v>
+        <x:v>8005231</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>24.1919455541526</x:v>
+        <x:v>24.21</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>16190299</x:v>
+        <x:v>16797787</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2.70102516542881</x:v>
+        <x:v>2.71496044636494</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>926687</x:v>
+        <x:v>787325</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.3933050192838</x:v>
+        <x:v>23.185</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +880,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2099320</x:v>
+        <x:v>2128703</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.9554723674326</x:v>
+        <x:v>23.964</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1440162</x:v>
+        <x:v>1442474</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>24.1154058758016</x:v>
+        <x:v>24.116</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>3539482</x:v>
+        <x:v>3571177</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.590491253718187</x:v>
+        <x:v>0.577195335431281</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>659158</x:v>
+        <x:v>686229</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.6060414854898</x:v>
+        <x:v>23.644</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +909,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>12655496</x:v>
+        <x:v>13083773</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>24.1340763308441</x:v>
+        <x:v>24.149</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>12236394</x:v>
+        <x:v>12704396</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>24.1605090309738</x:v>
+        <x:v>24.176</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>24891890</x:v>
+        <x:v>25788169</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>4.15271029306413</x:v>
+        <x:v>4.16804063649423</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>419102</x:v>
+        <x:v>379377</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.3623288009592</x:v>
+        <x:v>23.254</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +938,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>517068</x:v>
+        <x:v>528930</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>24.2451037663564</x:v>
+        <x:v>24.252</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>186164</x:v>
+        <x:v>189913</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>24.3207709705416</x:v>
+        <x:v>24.326</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>703232</x:v>
+        <x:v>718843</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.117320089587897</x:v>
+        <x:v>0.11618377540722</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>330904</x:v>
+        <x:v>339017</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>24.2025339896238</x:v>
+        <x:v>24.211</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +967,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>2817217</x:v>
+        <x:v>1117767</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>24.1129026877716</x:v>
+        <x:v>24.021</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>2497459</x:v>
+        <x:v>820820</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.9959464109219</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>5314676</x:v>
+        <x:v>1938587</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.886646603753306</x:v>
+        <x:v>0.31332621534237</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>319758</x:v>
+        <x:v>296947</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>25.0263857162648</x:v>
+        <x:v>23.858</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +996,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>1040670</x:v>
+        <x:v>2982558</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.9815649187758</x:v>
+        <x:v>24.136</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>743416</x:v>
+        <x:v>2686835</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>24.0273920696261</x:v>
+        <x:v>24.04</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>1784086</x:v>
+        <x:v>5669393</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.297638801067802</x:v>
+        <x:v>0.916321760116274</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>297254</x:v>
+        <x:v>295723</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.8669537203512</x:v>
+        <x:v>25.004</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1025,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>868063</x:v>
+        <x:v>1423407</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>24.119229992467</x:v>
+        <x:v>24.008</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>620848</x:v>
+        <x:v>1176913</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>24.2355618587496</x:v>
+        <x:v>24.16</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>1488911</x:v>
+        <x:v>2600320</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.248394799878852</x:v>
+        <x:v>0.420279525385795</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>247215</x:v>
+        <x:v>246494</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.8270777908698</x:v>
+        <x:v>23.282</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1054,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>4055508</x:v>
+        <x:v>882235</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>24.0655997424665</x:v>
+        <x:v>24.126</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>3828234</x:v>
+        <x:v>637341</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>24.0831822395816</x:v>
+        <x:v>24.244</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>7883742</x:v>
+        <x:v>1519576</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.3152435010464</x:v>
+        <x:v>0.245603110412428</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>227274</x:v>
+        <x:v>244894</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.7694377826241</x:v>
+        <x:v>23.818</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1083,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>1318371</x:v>
+        <x:v>4328853</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.9571642252742</x:v>
+        <x:v>24.097</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>1129617</x:v>
+        <x:v>4143988</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>24.144736632047</x:v>
+        <x:v>24.119</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>2447988</x:v>
+        <x:v>8472841</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.408397472626525</x:v>
+        <x:v>1.3694320676491</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>188754</x:v>
+        <x:v>184865</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>22.8346185869226</x:v>
+        <x:v>23.626</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1112,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>2442767</x:v>
+        <x:v>2481932</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.8119990287948</x:v>
+        <x:v>23.823</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>2270956</x:v>
+        <x:v>2305444</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.9126991512019</x:v>
+        <x:v>23.923</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>4713723</x:v>
+        <x:v>4787376</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.786389704468126</x:v>
+        <x:v>0.773764810916867</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>171811</x:v>
+        <x:v>176488</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.4809693090374</x:v>
+        <x:v>22.519</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1141,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>629535</x:v>
+        <x:v>639749</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>24.1686557729146</x:v>
+        <x:v>24.174</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>470127</x:v>
+        <x:v>475751</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>24.2335721764003</x:v>
+        <x:v>24.237</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1099662</x:v>
+        <x:v>1115500</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.183456447312417</x:v>
+        <x:v>0.180293890970286</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>159408</x:v>
+        <x:v>163998</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.9772039384927</x:v>
+        <x:v>23.991</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1170,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>3323752</x:v>
+        <x:v>704483</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>24.0776025116695</x:v>
+        <x:v>24.004</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>3188421</x:v>
+        <x:v>556926</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>24.1586378161196</x:v>
+        <x:v>24.108</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>6512173</x:v>
+        <x:v>1261409</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.0864248495118</x:v>
+        <x:v>0.203876590510926</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>135331</x:v>
+        <x:v>147557</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>22.1683971821421</x:v>
+        <x:v>23.614</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1199,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>133026</x:v>
+        <x:v>3398576</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>24.7775005554616</x:v>
+        <x:v>24.089</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>40113</x:v>
+        <x:v>3297514</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.9663810350061</x:v>
+        <x:v>24.173</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>173139</x:v>
+        <x:v>6696090</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0288847535253783</x:v>
+        <x:v>1.0822627704054</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>92913</x:v>
+        <x:v>101062</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>25.1276823096191</x:v>
+        <x:v>21.34</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1228,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>635263</x:v>
+        <x:v>133081</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.9444866230441</x:v>
+        <x:v>24.777</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>552762</x:v>
+        <x:v>55293</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>24.1044460764785</x:v>
+        <x:v>24.103</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1188025</x:v>
+        <x:v>188374</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.198198033412389</x:v>
+        <x:v>0.030446150979504</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>82501</x:v>
+        <x:v>77788</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>22.8727480089752</x:v>
+        <x:v>25.257</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1257,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>14607671</x:v>
+        <x:v>14694333</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.9828309175174</x:v>
+        <x:v>23.987</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>14532847</x:v>
+        <x:v>14628074</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.9823775712095</x:v>
+        <x:v>23.987</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>29140518</x:v>
+        <x:v>29322407</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>4.86150826810742</x:v>
+        <x:v>4.73926566619844</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>74824</x:v>
+        <x:v>66259</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>24.0708830469269</x:v>
+        <x:v>23.933</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1286,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>124301</x:v>
+        <x:v>134584</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>24.1249702295503</x:v>
+        <x:v>24.158</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>73096</x:v>
+        <x:v>83285</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>24.0368506886237</x:v>
+        <x:v>24.118</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>197397</x:v>
+        <x:v>217869</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0329317120443638</x:v>
+        <x:v>0.0352133121755314</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>51205</x:v>
+        <x:v>51299</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>24.2507623585136</x:v>
+        <x:v>24.224</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1315,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>3309732</x:v>
+        <x:v>3341980</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.7230137345541</x:v>
+        <x:v>23.731</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>3266134</x:v>
+        <x:v>3290717</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.7867418849586</x:v>
+        <x:v>23.793</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>6575866</x:v>
+        <x:v>6632697</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>1.09705074319429</x:v>
+        <x:v>1.07201680838812</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>43598</x:v>
+        <x:v>51263</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>18.9488342127137</x:v>
+        <x:v>19.77</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1344,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>52266</x:v>
+        <x:v>125291</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>24.4580771815867</x:v>
+        <x:v>24.368</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>11000</x:v>
+        <x:v>80681</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>24.2981818806041</x:v>
+        <x:v>24.296</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>63266</x:v>
+        <x:v>205972</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0105546573362246</x:v>
+        <x:v>0.0332904467153131</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>41266</x:v>
+        <x:v>44610</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.5006993962624</x:v>
+        <x:v>24.497</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1373,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>120044</x:v>
+        <x:v>54266</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>24.3624364250658</x:v>
+        <x:v>24.46</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>79605</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>24.2943072781282</x:v>
+        <x:v>24.298</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>199649</x:v>
+        <x:v>65266</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0333074128682057</x:v>
+        <x:v>0.0105486876629912</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>40439</x:v>
+        <x:v>43266</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.4965500466185</x:v>
+        <x:v>24.501</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1402,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>41092</x:v>
+        <x:v>6744709</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>24.6724685055597</x:v>
+        <x:v>24.017</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>13910</x:v>
+        <x:v>6709390</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>24.0871124338881</x:v>
+        <x:v>24.076</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>55002</x:v>
+        <x:v>13454099</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00917597544979964</x:v>
+        <x:v>2.17453326598784</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>27182</x:v>
+        <x:v>35319</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>24.9720161090088</x:v>
+        <x:v>12.804</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1431,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>926682</x:v>
+        <x:v>41136</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.6427816155354</x:v>
+        <x:v>24.672</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>908113</x:v>
+        <x:v>14155</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>24.2891570444312</x:v>
+        <x:v>24.096</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1834795</x:v>
+        <x:v>55291</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.306098575968422</x:v>
+        <x:v>0.00893646752634522</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>18569</x:v>
+        <x:v>26981</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>-7.96807141159956</x:v>
+        <x:v>24.975</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1460,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>2413578</x:v>
+        <x:v>993683</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.9898775046432</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2397888</x:v>
+        <x:v>976001</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.9965843577974</x:v>
+        <x:v>24.306</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>4811466</x:v>
+        <x:v>1969684</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.802696154567937</x:v>
+        <x:v>0.318352301516734</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>15690</x:v>
+        <x:v>17682</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>22.96487542074</x:v>
+        <x:v>-9.753</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1489,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>6456406</x:v>
+        <x:v>97488</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.993833105902</x:v>
+        <x:v>24.244</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>6441577</x:v>
+        <x:v>87230</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>24.056289122015</x:v>
+        <x:v>24.184</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>12897983</x:v>
+        <x:v>184718</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>2.15176857859592</x:v>
+        <x:v>0.0298552460351854</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>14829</x:v>
+        <x:v>10258</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>-3.13646812176574</x:v>
+        <x:v>24.756</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1518,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>29200</x:v>
+        <x:v>29229</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.8059784394094</x:v>
+        <x:v>23.807</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>16470</x:v>
+        <x:v>19470</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>24.0873474004128</x:v>
+        <x:v>24.145</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>45670</x:v>
+        <x:v>48699</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00761911928279607</x:v>
+        <x:v>0.00787102841448854</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>12730</x:v>
+        <x:v>9759</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.4419449132723</x:v>
+        <x:v>23.132</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1547,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>97468</x:v>
+        <x:v>11128</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>24.2439143849167</x:v>
+        <x:v>23.71</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>87045</x:v>
+        <x:v>6933</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.1830929959236</x:v>
+        <x:v>24.309</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>184513</x:v>
+        <x:v>18061</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0307822762475706</x:v>
+        <x:v>0.00291912861032213</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>10423</x:v>
+        <x:v>4195</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>24.7518485502148</x:v>
+        <x:v>22.72</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1576,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>11128</x:v>
+        <x:v>218085</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.7100537082088</x:v>
+        <x:v>24.093</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>6789</x:v>
+        <x:v>214626</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>24.3062659404225</x:v>
+        <x:v>24.013</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>17917</x:v>
+        <x:v>432711</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00298909043551253</x:v>
+        <x:v>0.0699373822103483</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>4339</x:v>
+        <x:v>3459</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>22.7771924856924</x:v>
+        <x:v>29.069</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1605,25 +1608,25 @@
         <x:v>8087</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>24.5245555796552</x:v>
+        <x:v>24.525</x:v>
       </x:c>
       <x:c r="D37" s="0">
         <x:v>5000</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>24.5500005722046</x:v>
+        <x:v>24.55</x:v>
       </x:c>
       <x:c r="F37" s="0">
         <x:v>13087</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00218330225649118</x:v>
+        <x:v>0.00211520049406377</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>3087</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>24.4833424397954</x:v>
+        <x:v>24.483</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1634,25 +1637,25 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.2999992370605</x:v>
+        <x:v>23.299</x:v>
       </x:c>
       <x:c r="D38" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>24.1399993896484</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F38" s="0">
         <x:v>776</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000129459964165749</x:v>
+        <x:v>0.000125421837196721</x:v>
       </x:c>
       <x:c r="H38" s="0">
         <x:v>774</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.2989139655456</x:v>
+        <x:v>23.298</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1663,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>1340</x:v>
+        <x:v>2437818</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>24.3394027823832</x:v>
+        <x:v>23.996</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>881</x:v>
+        <x:v>2437455</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.2141656215291</x:v>
+        <x:v>24.008</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>2221</x:v>
+        <x:v>4875273</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.000370529098469237</x:v>
+        <x:v>0.787971258370578</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>459</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>24.5797817338266</x:v>
+        <x:v>-54.862</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1692,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>214081</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>24.0832058213055</x:v>
+        <x:v>24.043</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>214243</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>24.01220248465</x:v>
+        <x:v>24.833</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>428324</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.071457228983673</x:v>
+        <x:v>5.18819713146229E-05</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-162</x:v>
+        <x:v>-39</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>-69.8178303212295</x:v>
+        <x:v>27.692</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1721,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>133471</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>24.1465597741973</x:v>
+        <x:v>24.339</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>137915</x:v>
+        <x:v>1881</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>24.1501759394169</x:v>
+        <x:v>24.462</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>271386</x:v>
+        <x:v>3221</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0452752858699561</x:v>
+        <x:v>0.000520597600013709</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-4444</x:v>
+        <x:v>-541</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>24.2587837675045</x:v>
+        <x:v>24.767</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1750,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>1489484</x:v>
+        <x:v>133471</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.7350085063385</x:v>
+        <x:v>24.147</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>1562315</x:v>
+        <x:v>137915</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.9035464467877</x:v>
+        <x:v>24.15</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>3051799</x:v>
+        <x:v>271386</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.509131171625088</x:v>
+        <x:v>0.0438630550379759</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-72831</x:v>
+        <x:v>-4444</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>27.3503557133365</x:v>
+        <x:v>24.259</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1779,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>100</x:v>
+        <x:v>9899475</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.6800003051758</x:v>
+        <x:v>24.146</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>200001</x:v>
+        <x:v>9944832</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.149</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>200101</x:v>
+        <x:v>19844307</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.0333828199607352</x:v>
+        <x:v>3.20735752813885</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-199901</x:v>
+        <x:v>-45357</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>25.5009104505204</x:v>
+        <x:v>24.911</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1808,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>9192862</x:v>
+        <x:v>1539559</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>24.1108376278135</x:v>
+        <x:v>23.763</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>9407578</x:v>
+        <x:v>1612459</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>24.125188963795</x:v>
+        <x:v>23.926</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>18600440</x:v>
+        <x:v>3152018</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>3.1031086286948</x:v>
+        <x:v>0.509448309841667</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-214716</x:v>
+        <x:v>-72900</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>24.7396278094956</x:v>
+        <x:v>27.358</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1837,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>3468685</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>24.0932371371692</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>3997220</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>24.2558981955217</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>7465905</x:v>
+        <x:v>200101</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.24553581670733</x:v>
+        <x:v>0.0323415400063158</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-528535</x:v>
+        <x:v>-199901</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>25.323414960147</x:v>
+        <x:v>25.501</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1866,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>1443087</x:v>
+        <x:v>3486533</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>24.2390580307777</x:v>
+        <x:v>24.096</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>1993243</x:v>
+        <x:v>4025589</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.7239266292097</x:v>
+        <x:v>24.258</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>3436330</x:v>
+        <x:v>7512122</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.573282420955783</x:v>
+        <x:v>1.21415482279111</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-550156</x:v>
+        <x:v>-539056</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>25.9957614744272</x:v>
+        <x:v>25.31</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1895,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>4507300</x:v>
+        <x:v>1461449</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>24.1951035357367</x:v>
+        <x:v>24.243</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>5149887</x:v>
+        <x:v>2028562</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>24.1698351416795</x:v>
+        <x:v>24.72</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>9657187</x:v>
+        <x:v>3490011</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>1.6111070656726</x:v>
+        <x:v>0.564076793114388</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-642587</x:v>
+        <x:v>-567113</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.9925949663666</x:v>
+        <x:v>25.95</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1924,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>3960661</x:v>
+        <x:v>4608178</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.9721850668096</x:v>
+        <x:v>24.204</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4741216</x:v>
+        <x:v>5262931</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.8853439465745</x:v>
+        <x:v>24.178</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>8701877</x:v>
+        <x:v>9871109</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.45173284097262</x:v>
+        <x:v>1.59542864168697</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-780555</x:v>
+        <x:v>-654753</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.4446982033386</x:v>
+        <x:v>23.996</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1953,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>5230190</x:v>
+        <x:v>4008822</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>24.019302006987</x:v>
+        <x:v>23.979</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>6011272</x:v>
+        <x:v>4763805</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.9599217966711</x:v>
+        <x:v>23.888</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>11241462</x:v>
+        <x:v>8772627</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.87541142743638</x:v>
+        <x:v>1.41788530332675</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-781082</x:v>
+        <x:v>-754983</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.5623069723732</x:v>
+        <x:v>23.406</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1985,22 +1988,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>801452</x:v>
+        <x:v>866623</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.4491900781843</x:v>
+        <x:v>24.462</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>801452</x:v>
+        <x:v>866623</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.133706117526505</x:v>
+        <x:v>0.14006887734141</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-801452</x:v>
+        <x:v>-866623</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>24.4491900781843</x:v>
+        <x:v>24.462</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2011,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>553178</x:v>
+        <x:v>5516470</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.8994283238805</x:v>
+        <x:v>24.051</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>1510622</x:v>
+        <x:v>6406672</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.738331968981</x:v>
+        <x:v>23.998</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2063800</x:v>
+        <x:v>11923142</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>0.34430344593463</x:v>
+        <x:v>1.92709068917189</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-957444</x:v>
+        <x:v>-890202</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.645256071685</x:v>
+        <x:v>23.666</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2040,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>1094386</x:v>
+        <x:v>589771</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>24.2975019706794</x:v>
+        <x:v>23.947</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>2484300</x:v>
+        <x:v>1549770</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>24.0121861548467</x:v>
+        <x:v>23.76</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>3578686</x:v>
+        <x:v>2139541</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>0.597031651186169</x:v>
+        <x:v>0.345805622393955</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1389914</x:v>
+        <x:v>-959999</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.7875351085043</x:v>
+        <x:v>23.645</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2069,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>21599564</x:v>
+        <x:v>1097940</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>24.0195699223881</x:v>
+        <x:v>24.299</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>24684911</x:v>
+        <x:v>2485595</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.9658146764994</x:v>
+        <x:v>24.012</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>46284475</x:v>
+        <x:v>3583535</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>7.72163205532281</x:v>
+        <x:v>0.579192710513854</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-3085347</x:v>
+        <x:v>-1387655</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.5894907576953</x:v>
+        <x:v>23.786</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2098,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>8422323</x:v>
+        <x:v>22605431</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>24.0807575616496</x:v>
+        <x:v>24.044</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>14457788</x:v>
+        <x:v>25699163</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.902624711513</x:v>
+        <x:v>23.99</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>22880111</x:v>
+        <x:v>48304594</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>3.81708550279427</x:v>
+        <x:v>7.80728211922899</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-6035465</x:v>
+        <x:v>-3093732</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.6540452895859</x:v>
+        <x:v>23.595</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2127,57 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>16452802</x:v>
+        <x:v>8558079</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>24.0832689953114</x:v>
+        <x:v>24.088</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>28943419</x:v>
+        <x:v>14556761</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.884690938095</x:v>
+        <x:v>23.907</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>45396221</x:v>
+        <x:v>23114840</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>7.57344477309332</x:v>
+        <x:v>3.73596095271682</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-12490617</x:v>
+        <x:v>-5998682</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.6231213569505</x:v>
+        <x:v>23.648</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:9">
+      <x:c r="A56" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B56" s="0">
+        <x:v>16807622</x:v>
+      </x:c>
+      <x:c r="C56" s="0">
+        <x:v>24.094</x:v>
+      </x:c>
+      <x:c r="D56" s="0">
+        <x:v>29230430</x:v>
+      </x:c>
+      <x:c r="E56" s="0">
+        <x:v>23.892</x:v>
+      </x:c>
+      <x:c r="F56" s="0">
+        <x:v>46038052</x:v>
+      </x:c>
+      <x:c r="G56" s="0">
+        <x:v>7.44094982319351</x:v>
+      </x:c>
+      <x:c r="H56" s="0">
+        <x:v>-12422808</x:v>
+      </x:c>
+      <x:c r="I56" s="0">
+        <x:v>23.618</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -58,73 +58,76 @@
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>ING</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
     <x:t>DINAMIK</x:t>
   </x:si>
   <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
+    <x:t>ACAR</x:t>
   </x:si>
   <x:si>
     <x:t>BIZIM</x:t>
@@ -139,58 +142,52 @@
     <x:t>GCM</x:t>
   </x:si>
   <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALTERNATIF</x:t>
   </x:si>
   <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ALLBATROSS </x:t>
   </x:si>
   <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AKTIF </x:t>
-  </x:si>
-  <x:si>
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
     <x:t>BLUPAY</x:t>
   </x:si>
   <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
   </x:si>
   <x:si>
     <x:t>UNLU</x:t>
@@ -553,7 +550,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I56"/>
+  <x:dimension ref="A1:I55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -590,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>31727921</x:v>
+        <x:v>33324699</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>24.032</x:v>
+        <x:v>24.0419352352023</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>26048602</x:v>
+        <x:v>27326615</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>24.094</x:v>
+        <x:v>24.1025773612407</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>57776523</x:v>
+        <x:v>60651314</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.33819286275592</x:v>
+        <x:v>9.28105061236698</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>5679319</x:v>
+        <x:v>5998084</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.746</x:v>
+        <x:v>23.7656563383024</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -619,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>15980857</x:v>
+        <x:v>17221726</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>24.186</x:v>
+        <x:v>24.1967920974818</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>10425368</x:v>
+        <x:v>11626841</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>24.28</x:v>
+        <x:v>24.2833607793951</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>26406225</x:v>
+        <x:v>28848567</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.26793460429121</x:v>
+        <x:v>4.41449645132601</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>5555489</x:v>
+        <x:v>5594885</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24.009</x:v>
+        <x:v>24.0168920101367</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -648,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>16086068</x:v>
+        <x:v>16777144</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>24.086</x:v>
+        <x:v>24.0948454510736</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>12058780</x:v>
+        <x:v>12844415</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.229</x:v>
+        <x:v>24.2316360894215</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>28144848</x:v>
+        <x:v>29621559</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.54894142240007</x:v>
+        <x:v>4.53278206464273</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>4027288</x:v>
+        <x:v>3932729</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.658</x:v>
+        <x:v>23.6480829797581</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -677,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>43328315</x:v>
+        <x:v>45697252</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>24.007</x:v>
+        <x:v>24.0217167613274</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>40699739</x:v>
+        <x:v>43330279</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.994</x:v>
+        <x:v>24.0106708328615</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>84028054</x:v>
+        <x:v>89027531</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.5811248824037</x:v>
+        <x:v>13.6232666138951</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2628576</x:v>
+        <x:v>2366973</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.205</x:v>
+        <x:v>24.2239257270589</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -706,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>6297641</x:v>
+        <x:v>6597931</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.291</x:v>
+        <x:v>24.2885055992753</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>4544261</x:v>
+        <x:v>4863515</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.343</x:v>
+        <x:v>24.338954810031</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>10841902</x:v>
+        <x:v>11461446</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.7523341076634</x:v>
+        <x:v>1.75386571867035</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1753380</x:v>
+        <x:v>1734416</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>24.157</x:v>
+        <x:v>24.1470398302508</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -735,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>16791015</x:v>
+        <x:v>17915999</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>24.121</x:v>
+        <x:v>24.1411210559481</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>15518086</x:v>
+        <x:v>16721296</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.13</x:v>
+        <x:v>24.1502926561661</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>32309101</x:v>
+        <x:v>34637295</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>5.22199330617836</x:v>
+        <x:v>5.30030541416606</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1272929</x:v>
+        <x:v>1194703</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>24.013</x:v>
+        <x:v>24.0127535520253</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -764,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>20418551</x:v>
+        <x:v>2848633</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>24.135</x:v>
+        <x:v>24.1014031888222</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>19313672</x:v>
+        <x:v>1660102</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>24.21</x:v>
+        <x:v>24.2052721951032</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>39732223</x:v>
+        <x:v>4508735</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>6.42176340795078</x:v>
+        <x:v>0.689940497130045</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1104879</x:v>
+        <x:v>1188531</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>22.819</x:v>
+        <x:v>23.9563222905829</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -793,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>4301387</x:v>
+        <x:v>4741955</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>24.109</x:v>
+        <x:v>24.1263020099233</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>3293651</x:v>
+        <x:v>3717752</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>24.306</x:v>
+        <x:v>24.3046310363431</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>7595038</x:v>
+        <x:v>8459707</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.22755621074602</x:v>
+        <x:v>1.29453038449909</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>1007736</x:v>
+        <x:v>1024203</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.466</x:v>
+        <x:v>23.4789859069338</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -822,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>2550686</x:v>
+        <x:v>9224692</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>24.073</x:v>
+        <x:v>24.1239115714059</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1617832</x:v>
+        <x:v>8466003</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>24.202</x:v>
+        <x:v>24.2107989182608</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>4168518</x:v>
+        <x:v>17690695</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.67374121900464</x:v>
+        <x:v>2.70708455983241</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>932854</x:v>
+        <x:v>758689</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.849</x:v>
+        <x:v>23.1543594372162</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -851,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>8792556</x:v>
+        <x:v>2144414</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>24.118</x:v>
+        <x:v>23.9662925808854</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>8005231</x:v>
+        <x:v>1445128</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>24.21</x:v>
+        <x:v>24.1160627406181</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>16797787</x:v>
+        <x:v>3589542</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2.71496044636494</x:v>
+        <x:v>0.549282757125707</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>787325</x:v>
+        <x:v>699286</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.185</x:v>
+        <x:v>23.6567810914602</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -880,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2128703</x:v>
+        <x:v>21508275</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.964</x:v>
+        <x:v>24.144007770572</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1442474</x:v>
+        <x:v>20919756</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>24.116</x:v>
+        <x:v>24.2181528246992</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>3571177</x:v>
+        <x:v>42428031</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.577195335431281</x:v>
+        <x:v>6.49246779870384</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>686229</x:v>
+        <x:v>588519</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.644</x:v>
+        <x:v>21.5084149673693</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -909,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>13083773</x:v>
+        <x:v>578195</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>24.149</x:v>
+        <x:v>24.236328914475</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>12704396</x:v>
+        <x:v>208186</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>24.176</x:v>
+        <x:v>24.3162616162972</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>25788169</x:v>
+        <x:v>786381</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>4.16804063649423</x:v>
+        <x:v>0.120334439277008</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>379377</x:v>
+        <x:v>370009</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.254</x:v>
+        <x:v>24.1913546855736</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -938,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>528930</x:v>
+        <x:v>3104454</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>24.252</x:v>
+        <x:v>24.1425672616146</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>189913</x:v>
+        <x:v>2796967</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>24.326</x:v>
+        <x:v>24.0467982356084</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>718843</x:v>
+        <x:v>5901421</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.11618377540722</x:v>
+        <x:v>0.90305359230775</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>339017</x:v>
+        <x:v>307487</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>24.211</x:v>
+        <x:v>25.0137026441231</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -967,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>1117767</x:v>
+        <x:v>1690588</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>24.021</x:v>
+        <x:v>24.1091377008618</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>820820</x:v>
+        <x:v>1407787</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>24.08</x:v>
+        <x:v>24.155390248435</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1938587</x:v>
+        <x:v>3098375</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.31332621534237</x:v>
+        <x:v>0.474122872112755</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>296947</x:v>
+        <x:v>282801</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.858</x:v>
+        <x:v>23.8788919266583</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -996,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>2982558</x:v>
+        <x:v>4559482</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>24.136</x:v>
+        <x:v>24.1086168662942</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>2686835</x:v>
+        <x:v>4290818</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>24.04</x:v>
+        <x:v>24.125621722086</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>5669393</x:v>
+        <x:v>8850300</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.916321760116274</x:v>
+        <x:v>1.35430012669852</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>295723</x:v>
+        <x:v>268664</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>25.004</x:v>
+        <x:v>23.8370332476516</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1025,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1423407</x:v>
+        <x:v>1468889</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>24.008</x:v>
+        <x:v>24.0219739966253</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1176913</x:v>
+        <x:v>1203139</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>24.16</x:v>
+        <x:v>24.1666706948365</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>2600320</x:v>
+        <x:v>2672028</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.420279525385795</x:v>
+        <x:v>0.408881942865438</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>246494</x:v>
+        <x:v>265750</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.282</x:v>
+        <x:v>23.3668837208429</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1054,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>882235</x:v>
+        <x:v>912324</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>24.126</x:v>
+        <x:v>24.130913588607</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>637341</x:v>
+        <x:v>666382</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>24.244</x:v>
+        <x:v>24.2501358863468</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1519576</x:v>
+        <x:v>1578706</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.245603110412428</x:v>
+        <x:v>0.241578447715864</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>244894</x:v>
+        <x:v>245942</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.818</x:v>
+        <x:v>23.8078797301671</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1083,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>4328853</x:v>
+        <x:v>13692406</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>24.097</x:v>
+        <x:v>24.1550065193752</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>4143988</x:v>
+        <x:v>13452895</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>24.119</x:v>
+        <x:v>24.1822644174899</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>8472841</x:v>
+        <x:v>27145301</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.3694320676491</x:v>
+        <x:v>4.15385744930334</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>184865</x:v>
+        <x:v>239511</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.626</x:v>
+        <x:v>22.6239802147045</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1112,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>2481932</x:v>
+        <x:v>648462</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.823</x:v>
+        <x:v>24.174848778734</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>2305444</x:v>
+        <x:v>480638</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.923</x:v>
+        <x:v>24.2382772170583</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>4787376</x:v>
+        <x:v>1129100</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.773764810916867</x:v>
+        <x:v>0.172778354751285</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>176488</x:v>
+        <x:v>167824</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.519</x:v>
+        <x:v>23.9931934866463</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1141,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>639749</x:v>
+        <x:v>3238114</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>24.174</x:v>
+        <x:v>23.9416626277536</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>475751</x:v>
+        <x:v>3087189</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>24.237</x:v>
+        <x:v>24.034577758836</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1115500</x:v>
+        <x:v>6325303</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.180293890970286</x:v>
+        <x:v>0.967917319673514</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>163998</x:v>
+        <x:v>150925</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.991</x:v>
+        <x:v>22.0410724630288</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1170,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>704483</x:v>
+        <x:v>762062</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>24.004</x:v>
+        <x:v>24.0164935137161</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>556926</x:v>
+        <x:v>651001</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>24.108</x:v>
+        <x:v>24.1452545435118</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1261409</x:v>
+        <x:v>1413063</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.203876590510926</x:v>
+        <x:v>0.216231246390855</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>147557</x:v>
+        <x:v>111061</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.614</x:v>
+        <x:v>23.2617410879496</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1199,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>3398576</x:v>
+        <x:v>14967854</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>24.089</x:v>
+        <x:v>23.9912579145193</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>3297514</x:v>
+        <x:v>14872176</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>24.173</x:v>
+        <x:v>23.9914669558545</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>6696090</x:v>
+        <x:v>29840030</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>1.0822627704054</x:v>
+        <x:v>4.56621316900981</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>101062</x:v>
+        <x:v>95678</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>21.34</x:v>
+        <x:v>23.9587645562896</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1228,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>133081</x:v>
+        <x:v>3614697</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>24.777</x:v>
+        <x:v>24.1059766931259</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>55293</x:v>
+        <x:v>3523382</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>24.103</x:v>
+        <x:v>24.1900982094941</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>188374</x:v>
+        <x:v>7138079</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.030446150979504</x:v>
+        <x:v>1.09229080303312</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>77788</x:v>
+        <x:v>91315</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>25.257</x:v>
+        <x:v>20.8601546859595</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1257,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>14694333</x:v>
+        <x:v>135581</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.987</x:v>
+        <x:v>24.7652885799599</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>14628074</x:v>
+        <x:v>58083</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.987</x:v>
+        <x:v>24.1043029689794</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>29322407</x:v>
+        <x:v>193664</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>4.73926566619844</x:v>
+        <x:v>0.0296350609286625</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>66259</x:v>
+        <x:v>77498</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.933</x:v>
+        <x:v>25.2606823609941</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1286,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>134584</x:v>
+        <x:v>169830</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>24.158</x:v>
+        <x:v>24.1953885165301</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>83285</x:v>
+        <x:v>93285</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>24.118</x:v>
+        <x:v>24.1782261752709</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>217869</x:v>
+        <x:v>263115</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0352133121755314</x:v>
+        <x:v>0.0402626665577754</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>51299</x:v>
+        <x:v>76545</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>24.224</x:v>
+        <x:v>24.2163041740436</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1315,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>3341980</x:v>
+        <x:v>7281335</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.731</x:v>
+        <x:v>24.0378410092074</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>3290717</x:v>
+        <x:v>7228648</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.793</x:v>
+        <x:v>24.0920516985951</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>6632697</x:v>
+        <x:v>14509983</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>1.07201680838812</x:v>
+        <x:v>2.22036222673732</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>51263</x:v>
+        <x:v>52687</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>19.77</x:v>
+        <x:v>16.6001430681404</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1344,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>125291</x:v>
+        <x:v>3370431</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>24.368</x:v>
+        <x:v>23.7352808278131</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>80681</x:v>
+        <x:v>3322562</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>24.296</x:v>
+        <x:v>23.7963753810148</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>205972</x:v>
+        <x:v>6692993</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0332904467153131</x:v>
+        <x:v>1.02418237437062</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>44610</x:v>
+        <x:v>47869</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.497</x:v>
+        <x:v>19.4947401673637</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1373,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>54266</x:v>
+        <x:v>66966</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>24.46</x:v>
+        <x:v>24.4455672910278</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>11000</x:v>
+        <x:v>21000</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>24.298</x:v>
+        <x:v>24.3123811086019</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>65266</x:v>
+        <x:v>87966</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0105486876629912</x:v>
+        <x:v>0.0134608278753445</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>43266</x:v>
+        <x:v>45966</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.501</x:v>
+        <x:v>24.506414652794</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1402,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>6744709</x:v>
+        <x:v>130774</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>24.017</x:v>
+        <x:v>24.3630088059572</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>6709390</x:v>
+        <x:v>90534</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>24.076</x:v>
+        <x:v>24.2848552730866</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>13454099</x:v>
+        <x:v>221308</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>2.17453326598784</x:v>
+        <x:v>0.0338652308327848</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>35319</x:v>
+        <x:v>40240</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>12.804</x:v>
+        <x:v>24.5388426018046</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1431,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>41136</x:v>
+        <x:v>2544695</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>24.672</x:v>
+        <x:v>24.0096057316687</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>14155</x:v>
+        <x:v>2510047</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>24.096</x:v>
+        <x:v>24.0153931432544</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>55291</x:v>
+        <x:v>5054742</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00893646752634522</x:v>
+        <x:v>0.773492167613336</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>26981</x:v>
+        <x:v>34648</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>24.975</x:v>
+        <x:v>23.5903412694057</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1460,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>993683</x:v>
+        <x:v>41146</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.7</x:v>
+        <x:v>24.672316040833</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>976001</x:v>
+        <x:v>16986</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>24.306</x:v>
+        <x:v>24.0878485026439</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>1969684</x:v>
+        <x:v>58132</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.318352301516734</x:v>
+        <x:v>0.00889553743548107</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>17682</x:v>
+        <x:v>24160</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>-9.753</x:v>
+        <x:v>25.0832334913165</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1489,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>97488</x:v>
+        <x:v>1059981</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>24.244</x:v>
+        <x:v>23.7333652916977</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>87230</x:v>
+        <x:v>1041299</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>24.184</x:v>
+        <x:v>24.3007024033135</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>184718</x:v>
+        <x:v>2101280</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0298552460351854</x:v>
+        <x:v>0.321544328466725</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>10258</x:v>
+        <x:v>18682</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>24.756</x:v>
+        <x:v>-7.88892177544624</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1518,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>29229</x:v>
+        <x:v>111149</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.807</x:v>
+        <x:v>24.2269636903444</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>19470</x:v>
+        <x:v>97061</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>24.145</x:v>
+        <x:v>24.1769842966548</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>48699</x:v>
+        <x:v>208210</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00787102841448854</x:v>
+        <x:v>0.0318609345875166</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>9759</x:v>
+        <x:v>14088</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.132</x:v>
+        <x:v>24.5713028393301</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1547,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>11128</x:v>
+        <x:v>29229</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.71</x:v>
+        <x:v>23.8066670235299</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>6933</x:v>
+        <x:v>19470</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.309</x:v>
+        <x:v>24.1447667662156</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>18061</x:v>
+        <x:v>48699</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00291912861032213</x:v>
+        <x:v>0.0074520707625833</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>4195</x:v>
+        <x:v>9759</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>22.72</x:v>
+        <x:v>23.1321304941632</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1576,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>218085</x:v>
+        <x:v>10517196</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>24.093</x:v>
+        <x:v>24.1562125839914</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>214626</x:v>
+        <x:v>10512514</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>24.013</x:v>
+        <x:v>24.1596208929822</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>432711</x:v>
+        <x:v>21029710</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0699373822103483</x:v>
+        <x:v>3.21803090487702</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>3459</x:v>
+        <x:v>4682</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>29.069</x:v>
+        <x:v>16.5035222846695</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1605,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>8087</x:v>
+        <x:v>11218</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>24.525</x:v>
+        <x:v>23.7129682352845</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>5000</x:v>
+        <x:v>6933</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>24.55</x:v>
+        <x:v>24.3090436386027</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>13087</x:v>
+        <x:v>18151</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00211520049406377</x:v>
+        <x:v>0.0027775218466837</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>3087</x:v>
+        <x:v>4285</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>24.483</x:v>
+        <x:v>22.7485363166836</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1634,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>775</x:v>
+        <x:v>8087</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.299</x:v>
+        <x:v>24.5245555796552</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>1</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>24</x:v>
+        <x:v>24.5500005722046</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>776</x:v>
+        <x:v>13087</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000125421837196721</x:v>
+        <x:v>0.00200261299143571</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>774</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.298</x:v>
+        <x:v>24.4833424397954</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1663,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>2437818</x:v>
+        <x:v>226358</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.996</x:v>
+        <x:v>24.0983549233532</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>2437455</x:v>
+        <x:v>224637</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.008</x:v>
+        <x:v>24.0166401583729</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>4875273</x:v>
+        <x:v>450995</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.787971258370578</x:v>
+        <x:v>0.0690126420166997</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>363</x:v>
+        <x:v>1721</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>-54.862</x:v>
+        <x:v>34.7643396188048</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1692,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>141</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>24.043</x:v>
+        <x:v>23.2999992370605</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>180</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>24.833</x:v>
+        <x:v>24.1399993896484</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>321</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>5.18819713146229E-05</x:v>
+        <x:v>0.000118745906728365</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-39</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>27.692</x:v>
+        <x:v>23.2989139655456</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1724,25 +1721,25 @@
         <x:v>1340</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>24.339</x:v>
+        <x:v>24.3394027823832</x:v>
       </x:c>
       <x:c r="D41" s="0">
         <x:v>1881</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>24.462</x:v>
+        <x:v>24.4618182975773</x:v>
       </x:c>
       <x:c r="F41" s="0">
         <x:v>3221</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.000520597600013709</x:v>
+        <x:v>0.000492887326768123</x:v>
       </x:c>
       <x:c r="H41" s="0">
         <x:v>-541</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>24.767</x:v>
+        <x:v>24.76502863096</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1750,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>133471</x:v>
+        <x:v>133971</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>24.147</x:v>
+        <x:v>24.1463113627855</x:v>
       </x:c>
       <x:c r="D42" s="0">
         <x:v>137915</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.15</x:v>
+        <x:v>24.1501759394169</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>271386</x:v>
+        <x:v>271886</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.0438630550379759</x:v>
+        <x:v>0.0416048319545725</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-4444</x:v>
+        <x:v>-3944</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>24.259</x:v>
+        <x:v>24.2814490621037</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1779,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>9899475</x:v>
+        <x:v>1760009</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>24.146</x:v>
+        <x:v>23.8626256769488</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>9944832</x:v>
+        <x:v>1854459</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>24.149</x:v>
+        <x:v>24.0090578733968</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>19844307</x:v>
+        <x:v>3614468</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>3.20735752813885</x:v>
+        <x:v>0.553097010310129</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-45357</x:v>
+        <x:v>-94450</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>24.911</x:v>
+        <x:v>26.7377183671853</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1808,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1539559</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.763</x:v>
+        <x:v>23.6800003051758</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>1612459</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.926</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>3152018</x:v>
+        <x:v>200101</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.509448309841667</x:v>
+        <x:v>0.0306200704668203</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-72900</x:v>
+        <x:v>-199901</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>27.358</x:v>
+        <x:v>25.5009104505204</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1837,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>100</x:v>
+        <x:v>1619905</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.68</x:v>
+        <x:v>24.2652573552562</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>200001</x:v>
+        <x:v>2059034</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.7145399275061</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>200101</x:v>
+        <x:v>3678939</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.0323415400063158</x:v>
+        <x:v>0.562962561022351</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-199901</x:v>
+        <x:v>-439129</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>25.501</x:v>
+        <x:v>26.3719004871604</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1866,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>3486533</x:v>
+        <x:v>3557306</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>24.096</x:v>
+        <x:v>24.1019141507018</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>4025589</x:v>
+        <x:v>4090212</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.258</x:v>
+        <x:v>24.2587724069056</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>7512122</x:v>
+        <x:v>7647518</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.21415482279111</x:v>
+        <x:v>1.17024672568491</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-539056</x:v>
+        <x:v>-532906</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>25.31</x:v>
+        <x:v>25.3058479060424</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1895,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1461449</x:v>
+        <x:v>5020839</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>24.243</x:v>
+        <x:v>24.2082601617772</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2028562</x:v>
+        <x:v>5596465</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>24.72</x:v>
+        <x:v>24.1807356339596</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>3490011</x:v>
+        <x:v>10617304</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.564076793114388</x:v>
+        <x:v>1.62469251351894</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-567113</x:v>
+        <x:v>-575626</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.95</x:v>
+        <x:v>23.9406557509746</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1924,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>4608178</x:v>
+        <x:v>4300883</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>24.204</x:v>
+        <x:v>23.9968285785417</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>5262931</x:v>
+        <x:v>4980669</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>24.178</x:v>
+        <x:v>23.9069930677946</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>9871109</x:v>
+        <x:v>9281552</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.59542864168697</x:v>
+        <x:v>1.42029163413205</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-654753</x:v>
+        <x:v>-679786</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.996</x:v>
+        <x:v>23.3386200489792</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1953,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>4008822</x:v>
+        <x:v>640958</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.979</x:v>
+        <x:v>23.9881697529685</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>4763805</x:v>
+        <x:v>1565233</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.888</x:v>
+        <x:v>23.765206583115</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>8772627</x:v>
+        <x:v>2206191</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.41788530332675</x:v>
+        <x:v>0.337598132359482</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-754983</x:v>
+        <x:v>-924275</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.406</x:v>
+        <x:v>23.610588068687</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1982,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>0</x:v>
+        <x:v>5930469</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>0</x:v>
+        <x:v>24.0601746543887</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>866623</x:v>
+        <x:v>6876456</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.462</x:v>
+        <x:v>24.0121451746932</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>866623</x:v>
+        <x:v>12806925</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.14006887734141</x:v>
+        <x:v>1.95975505351439</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-866623</x:v>
+        <x:v>-945987</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>24.462</x:v>
+        <x:v>23.7110444825904</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2011,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>5516470</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>24.051</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>6406672</x:v>
+        <x:v>996158</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.998</x:v>
+        <x:v>24.4497553375111</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>11923142</x:v>
+        <x:v>996158</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>1.92709068917189</x:v>
+        <x:v>0.152435161024117</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-890202</x:v>
+        <x:v>-996158</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.666</x:v>
+        <x:v>24.4497553375111</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2040,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>589771</x:v>
+        <x:v>1101210</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.947</x:v>
+        <x:v>24.2984041507017</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1549770</x:v>
+        <x:v>2487274</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.76</x:v>
+        <x:v>24.0127330259203</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>2139541</x:v>
+        <x:v>3588484</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>0.345805622393955</x:v>
+        <x:v>0.549120858711637</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-959999</x:v>
+        <x:v>-1386064</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.645</x:v>
+        <x:v>23.7857709957973</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2069,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>1097940</x:v>
+        <x:v>23553394</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>24.299</x:v>
+        <x:v>24.0562925312334</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>2485595</x:v>
+        <x:v>26642190</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>24.012</x:v>
+        <x:v>24.003812067474</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>3583535</x:v>
+        <x:v>50195584</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>0.579192710513854</x:v>
+        <x:v>7.6810826492781</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1387655</x:v>
+        <x:v>-3088796</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.786</x:v>
+        <x:v>23.6036260272737</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2098,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>22605431</x:v>
+        <x:v>8745838</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>24.044</x:v>
+        <x:v>24.0899890786311</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>25699163</x:v>
+        <x:v>14679842</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.99</x:v>
+        <x:v>23.9087294094196</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>48304594</x:v>
+        <x:v>23425680</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>7.80728211922899</x:v>
+        <x:v>3.58466960351614</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-3093732</x:v>
+        <x:v>-5934004</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.595</x:v>
+        <x:v>23.641579656427</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2127,57 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>8558079</x:v>
+        <x:v>17436885</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>24.088</x:v>
+        <x:v>24.1005503357919</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>14556761</x:v>
+        <x:v>29769994</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.907</x:v>
+        <x:v>23.8986558545262</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>23114840</x:v>
+        <x:v>47206879</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>3.73596095271682</x:v>
+        <x:v>7.22374181787527</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-5998682</x:v>
+        <x:v>-12333109</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.648</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:9">
-      <x:c r="A56" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B56" s="0">
-        <x:v>16807622</x:v>
-      </x:c>
-      <x:c r="C56" s="0">
-        <x:v>24.094</x:v>
-      </x:c>
-      <x:c r="D56" s="0">
-        <x:v>29230430</x:v>
-      </x:c>
-      <x:c r="E56" s="0">
-        <x:v>23.892</x:v>
-      </x:c>
-      <x:c r="F56" s="0">
-        <x:v>46038052</x:v>
-      </x:c>
-      <x:c r="G56" s="0">
-        <x:v>7.44094982319351</x:v>
-      </x:c>
-      <x:c r="H56" s="0">
-        <x:v>-12422808</x:v>
-      </x:c>
-      <x:c r="I56" s="0">
-        <x:v>23.618</x:v>
+        <x:v>23.6132119448061</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -55,12 +55,12 @@
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
@@ -73,57 +73,57 @@
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
@@ -142,49 +142,52 @@
     <x:t>GCM</x:t>
   </x:si>
   <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AKTIF </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
     <x:t>BLUPAY</x:t>
   </x:si>
   <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
   </x:si>
   <x:si>
     <x:t>BANK OF AMERICA</x:t>
@@ -550,7 +553,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I55"/>
+  <x:dimension ref="A1:I56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -587,28 +590,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>33324699</x:v>
+        <x:v>34456632</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>24.0419352352023</x:v>
+        <x:v>24.04</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>27326615</x:v>
+        <x:v>28534753</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>24.1025773612407</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>60651314</x:v>
+        <x:v>62991385</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.28105061236698</x:v>
+        <x:v>9.28789583057196</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>5998084</x:v>
+        <x:v>5921879</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.7656563383024</x:v>
+        <x:v>23.752</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +619,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>17221726</x:v>
+        <x:v>17946422</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>24.1967920974818</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>11626841</x:v>
+        <x:v>12329428</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>24.2833607793951</x:v>
+        <x:v>24.269</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>28848567</x:v>
+        <x:v>30275850</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.41449645132601</x:v>
+        <x:v>4.4640856996877</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>5594885</x:v>
+        <x:v>5616994</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24.0168920101367</x:v>
+        <x:v>24.017</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +648,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>16777144</x:v>
+        <x:v>17385231</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>24.0948454510736</x:v>
+        <x:v>24.093</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>12844415</x:v>
+        <x:v>13483760</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.2316360894215</x:v>
+        <x:v>24.222</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>29621559</x:v>
+        <x:v>30868991</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.53278206464273</x:v>
+        <x:v>4.5515426086101</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>3932729</x:v>
+        <x:v>3901471</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.6480829797581</x:v>
+        <x:v>23.651</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +677,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>45697252</x:v>
+        <x:v>47539758</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>24.0217167613274</x:v>
+        <x:v>24.022</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>43330279</x:v>
+        <x:v>44925178</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>24.0106708328615</x:v>
+        <x:v>24.011</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>89027531</x:v>
+        <x:v>92464936</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.6232666138951</x:v>
+        <x:v>13.633684884822</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2366973</x:v>
+        <x:v>2614580</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.2239257270589</x:v>
+        <x:v>24.201</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +706,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>6597931</x:v>
+        <x:v>6795254</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.2885055992753</x:v>
+        <x:v>24.28</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>4863515</x:v>
+        <x:v>5273004</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.338954810031</x:v>
+        <x:v>24.313</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>11461446</x:v>
+        <x:v>12068258</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.75386571867035</x:v>
+        <x:v>1.77942941182301</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1734416</x:v>
+        <x:v>1522250</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>24.1470398302508</x:v>
+        <x:v>24.167</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +735,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>17915999</x:v>
+        <x:v>2955799</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>24.1411210559481</x:v>
+        <x:v>24.097</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>16721296</x:v>
+        <x:v>1708304</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.1502926561661</x:v>
+        <x:v>24.2</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>34637295</x:v>
+        <x:v>4664103</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>5.30030541416606</x:v>
+        <x:v>0.687708371661588</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1194703</x:v>
+        <x:v>1247495</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>24.0127535520253</x:v>
+        <x:v>23.956</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +764,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>2848633</x:v>
+        <x:v>18330761</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>24.1014031888222</x:v>
+        <x:v>24.137</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1660102</x:v>
+        <x:v>17182660</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>24.2052721951032</x:v>
+        <x:v>24.146</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>4508735</x:v>
+        <x:v>35513421</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.689940497130045</x:v>
+        <x:v>5.23635025385212</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1188531</x:v>
+        <x:v>1148101</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.9563222905829</x:v>
+        <x:v>23.999</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +793,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>4741955</x:v>
+        <x:v>5026623</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>24.1263020099233</x:v>
+        <x:v>24.122</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>3717752</x:v>
+        <x:v>3948872</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>24.3046310363431</x:v>
+        <x:v>24.287</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>8459707</x:v>
+        <x:v>8975495</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.29453038449909</x:v>
+        <x:v>1.3234105360252</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>1024203</x:v>
+        <x:v>1077751</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.4789859069338</x:v>
+        <x:v>23.517</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +822,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>9224692</x:v>
+        <x:v>9628696</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>24.1239115714059</x:v>
+        <x:v>24.12</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8466003</x:v>
+        <x:v>8794877</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>24.2107989182608</x:v>
+        <x:v>24.204</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>17690695</x:v>
+        <x:v>18423573</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>2.70708455983241</x:v>
+        <x:v>2.71650205581189</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>758689</x:v>
+        <x:v>833819</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.1543594372162</x:v>
+        <x:v>23.243</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +851,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>2144414</x:v>
+        <x:v>2156668</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.9662925808854</x:v>
+        <x:v>23.967</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1445128</x:v>
+        <x:v>1464111</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>24.1160627406181</x:v>
+        <x:v>24.115</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>3589542</x:v>
+        <x:v>3620779</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.549282757125707</x:v>
+        <x:v>0.533873293586456</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>699286</x:v>
+        <x:v>692557</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.6567810914602</x:v>
+        <x:v>23.654</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +880,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>21508275</x:v>
+        <x:v>22485643</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>24.144007770572</x:v>
+        <x:v>24.139</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>20919756</x:v>
+        <x:v>21890931</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>24.2181528246992</x:v>
+        <x:v>24.209</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>42428031</x:v>
+        <x:v>44376574</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>6.49246779870384</x:v>
+        <x:v>6.54319628993184</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>588519</x:v>
+        <x:v>594712</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>21.5084149673693</x:v>
+        <x:v>21.581</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +909,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>578195</x:v>
+        <x:v>1107011</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>24.236328914475</x:v>
+        <x:v>24.124</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>208186</x:v>
+        <x:v>720190</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>24.3162616162972</x:v>
+        <x:v>24.231</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>786381</x:v>
+        <x:v>1827201</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.120334439277008</x:v>
+        <x:v>0.269415453391236</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>370009</x:v>
+        <x:v>386821</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>24.1913546855736</x:v>
+        <x:v>23.923</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +938,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>3104454</x:v>
+        <x:v>584924</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>24.1425672616146</x:v>
+        <x:v>24.233</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>2796967</x:v>
+        <x:v>223722</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>24.0467982356084</x:v>
+        <x:v>24.293</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>5901421</x:v>
+        <x:v>808646</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.90305359230775</x:v>
+        <x:v>0.119232492059171</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>307487</x:v>
+        <x:v>361202</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>25.0137026441231</x:v>
+        <x:v>24.195</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +967,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>1690588</x:v>
+        <x:v>3164865</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>24.1091377008618</x:v>
+        <x:v>24.139</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>1407787</x:v>
+        <x:v>2847746</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>24.155390248435</x:v>
+        <x:v>24.045</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>3098375</x:v>
+        <x:v>6012611</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.474122872112755</x:v>
+        <x:v>0.886541939627952</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>282801</x:v>
+        <x:v>317119</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.8788919266583</x:v>
+        <x:v>24.99</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +996,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>4559482</x:v>
+        <x:v>14169243</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>24.1086168662942</x:v>
+        <x:v>24.151</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>4290818</x:v>
+        <x:v>13863532</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>24.125621722086</x:v>
+        <x:v>24.177</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>8850300</x:v>
+        <x:v>28032775</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>1.35430012669852</x:v>
+        <x:v>4.13335083903714</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>268664</x:v>
+        <x:v>305711</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.8370332476516</x:v>
+        <x:v>22.941</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1025,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1468889</x:v>
+        <x:v>1575419</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>24.0219739966253</x:v>
+        <x:v>24.026</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1203139</x:v>
+        <x:v>1282963</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>24.1666706948365</x:v>
+        <x:v>24.156</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>2672028</x:v>
+        <x:v>2858382</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.408881942865438</x:v>
+        <x:v>0.421460081564835</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>265750</x:v>
+        <x:v>292456</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.3668837208429</x:v>
+        <x:v>23.454</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1054,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>912324</x:v>
+        <x:v>4707259</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>24.130913588607</x:v>
+        <x:v>24.105</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>666382</x:v>
+        <x:v>4444937</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>24.2501358863468</x:v>
+        <x:v>24.121</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1578706</x:v>
+        <x:v>9152196</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.241578447715864</x:v>
+        <x:v>1.34946458264058</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>245942</x:v>
+        <x:v>262322</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.8078797301671</x:v>
+        <x:v>23.827</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1083,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>13692406</x:v>
+        <x:v>3528505</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>24.1550065193752</x:v>
+        <x:v>23.943</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>13452895</x:v>
+        <x:v>3278317</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>24.1822644174899</x:v>
+        <x:v>24.031</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>27145301</x:v>
+        <x:v>6806822</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>4.15385744930334</x:v>
+        <x:v>1.00364603307651</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>239511</x:v>
+        <x:v>250188</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>22.6239802147045</x:v>
+        <x:v>22.793</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1112,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>648462</x:v>
+        <x:v>1843331</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>24.174848778734</x:v>
+        <x:v>24.104</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>480638</x:v>
+        <x:v>1643072</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>24.2382772170583</x:v>
+        <x:v>24.131</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>1129100</x:v>
+        <x:v>3486403</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.172778354751285</x:v>
+        <x:v>0.514059944663759</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>167824</x:v>
+        <x:v>200259</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.9931934866463</x:v>
+        <x:v>23.886</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1141,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>3238114</x:v>
+        <x:v>652714</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.9416626277536</x:v>
+        <x:v>24.174</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>3087189</x:v>
+        <x:v>490105</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>24.034577758836</x:v>
+        <x:v>24.234</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>6325303</x:v>
+        <x:v>1142819</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.967917319673514</x:v>
+        <x:v>0.16850532537423</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>150925</x:v>
+        <x:v>162609</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.0410724630288</x:v>
+        <x:v>23.992</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1170,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>762062</x:v>
+        <x:v>785722</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>24.0164935137161</x:v>
+        <x:v>24.014</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>651001</x:v>
+        <x:v>660348</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>24.1452545435118</x:v>
+        <x:v>24.143</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1413063</x:v>
+        <x:v>1446070</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.216231246390855</x:v>
+        <x:v>0.213218800058376</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>111061</x:v>
+        <x:v>125374</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.2617410879496</x:v>
+        <x:v>23.333</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1199,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>14967854</x:v>
+        <x:v>3687026</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.9912579145193</x:v>
+        <x:v>24.104</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>14872176</x:v>
+        <x:v>3568621</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.9914669558545</x:v>
+        <x:v>24.188</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>29840030</x:v>
+        <x:v>7255647</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>4.56621316900981</x:v>
+        <x:v>1.06982396909358</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>95678</x:v>
+        <x:v>118405</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.9587645562896</x:v>
+        <x:v>21.592</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1228,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>3614697</x:v>
+        <x:v>157443</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>24.1059766931259</x:v>
+        <x:v>24.65</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>3523382</x:v>
+        <x:v>80797</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>24.1900982094941</x:v>
+        <x:v>24.057</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>7138079</x:v>
+        <x:v>238240</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>1.09229080303312</x:v>
+        <x:v>0.0351277925175873</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>91315</x:v>
+        <x:v>76646</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>20.8601546859595</x:v>
+        <x:v>25.275</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1257,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>135581</x:v>
+        <x:v>184943</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>24.7652885799599</x:v>
+        <x:v>24.173</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>58083</x:v>
+        <x:v>108441</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>24.1043029689794</x:v>
+        <x:v>24.156</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>193664</x:v>
+        <x:v>293384</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0296350609286625</x:v>
+        <x:v>0.0432586143383976</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>77498</x:v>
+        <x:v>76502</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>25.2606823609941</x:v>
+        <x:v>24.197</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1286,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>169830</x:v>
+        <x:v>15132968</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>24.1953885165301</x:v>
+        <x:v>23.992</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>93285</x:v>
+        <x:v>15058725</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>24.1782261752709</x:v>
+        <x:v>23.992</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>263115</x:v>
+        <x:v>30191693</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0402626665577754</x:v>
+        <x:v>4.45167699571312</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>76545</x:v>
+        <x:v>74243</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>24.2163041740436</x:v>
+        <x:v>23.963</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1315,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>7281335</x:v>
+        <x:v>7352687</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>24.0378410092074</x:v>
+        <x:v>24.037</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>7228648</x:v>
+        <x:v>7285234</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>24.0920516985951</x:v>
+        <x:v>24.092</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>14509983</x:v>
+        <x:v>14637921</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>2.22036222673732</x:v>
+        <x:v>2.15831871968114</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>52687</x:v>
+        <x:v>67453</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>16.6001430681404</x:v>
+        <x:v>18.195</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1344,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>3370431</x:v>
+        <x:v>69966</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.7352808278131</x:v>
+        <x:v>24.426</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>3322562</x:v>
+        <x:v>21000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.7963753810148</x:v>
+        <x:v>24.312</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>6692993</x:v>
+        <x:v>90966</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>1.02418237437062</x:v>
+        <x:v>0.0134126711473928</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>47869</x:v>
+        <x:v>48966</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>19.4947401673637</x:v>
+        <x:v>24.475</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1373,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>66966</x:v>
+        <x:v>3388271</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>24.4455672910278</x:v>
+        <x:v>23.737</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>21000</x:v>
+        <x:v>3346345</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>24.3123811086019</x:v>
+        <x:v>23.798</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>87966</x:v>
+        <x:v>6734616</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0134608278753445</x:v>
+        <x:v>0.992999469163969</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>45966</x:v>
+        <x:v>41926</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.506414652794</x:v>
+        <x:v>18.84</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1402,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>130774</x:v>
+        <x:v>130888</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>24.3630088059572</x:v>
+        <x:v>24.363</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>90534</x:v>
+        <x:v>90714</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>24.2848552730866</x:v>
+        <x:v>24.284</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>221308</x:v>
+        <x:v>221602</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0338652308327848</x:v>
+        <x:v>0.0326745679880893</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>40240</x:v>
+        <x:v>40174</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>24.5388426018046</x:v>
+        <x:v>24.539</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1431,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>2544695</x:v>
+        <x:v>2559781</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>24.0096057316687</x:v>
+        <x:v>24.009</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2510047</x:v>
+        <x:v>2525602</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>24.0153931432544</x:v>
+        <x:v>24.015</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>5054742</x:v>
+        <x:v>5085383</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.773492167613336</x:v>
+        <x:v>0.74982487783943</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>34648</x:v>
+        <x:v>34179</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>23.5903412694057</x:v>
+        <x:v>23.574</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1460,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>41146</x:v>
+        <x:v>41147</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>24.672316040833</x:v>
+        <x:v>24.672</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>16986</x:v>
+        <x:v>16987</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>24.0878485026439</x:v>
+        <x:v>24.088</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>58132</x:v>
+        <x:v>58134</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00889553743548107</x:v>
+        <x:v>0.00857168859224908</x:v>
       </x:c>
       <x:c r="H32" s="0">
         <x:v>24160</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>25.0832334913165</x:v>
+        <x:v>25.083</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1489,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1059981</x:v>
+        <x:v>1082541</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.7333652916977</x:v>
+        <x:v>23.741</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>1041299</x:v>
+        <x:v>1064132</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>24.3007024033135</x:v>
+        <x:v>24.297</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>2101280</x:v>
+        <x:v>2146673</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.321544328466725</x:v>
+        <x:v>0.316520667172208</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>18682</x:v>
+        <x:v>18409</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>-7.88892177544624</x:v>
+        <x:v>-8.406</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1518,25 +1521,25 @@
         <x:v>111149</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>24.2269636903444</x:v>
+        <x:v>24.227</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>97061</x:v>
+        <x:v>98203</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>24.1769842966548</x:v>
+        <x:v>24.175</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>208210</x:v>
+        <x:v>209352</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0318609345875166</x:v>
+        <x:v>0.0308683412489168</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>14088</x:v>
+        <x:v>12946</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>24.5713028393301</x:v>
+        <x:v>24.622</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1547,25 +1550,25 @@
         <x:v>29229</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.8066670235299</x:v>
+        <x:v>23.807</x:v>
       </x:c>
       <x:c r="D35" s="0">
         <x:v>19470</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.1447667662156</x:v>
+        <x:v>24.145</x:v>
       </x:c>
       <x:c r="F35" s="0">
         <x:v>48699</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0074520707625833</x:v>
+        <x:v>0.00718052538538442</x:v>
       </x:c>
       <x:c r="H35" s="0">
         <x:v>9759</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.1321304941632</x:v>
+        <x:v>23.132</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1576,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>10517196</x:v>
+        <x:v>11218</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>24.1562125839914</x:v>
+        <x:v>23.713</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>10512514</x:v>
+        <x:v>7078</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>24.1596208929822</x:v>
+        <x:v>24.305</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>21029710</x:v>
+        <x:v>18296</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.21803090487702</x:v>
+        <x:v>0.00269769178937952</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>4682</x:v>
+        <x:v>4140</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>16.5035222846695</x:v>
+        <x:v>22.701</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1605,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>11218</x:v>
+        <x:v>8087</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.7129682352845</x:v>
+        <x:v>24.525</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>6933</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>24.3090436386027</x:v>
+        <x:v>24.55</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>18151</x:v>
+        <x:v>13087</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.0027775218466837</x:v>
+        <x:v>0.00192963994575917</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>4285</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>22.7485363166836</x:v>
+        <x:v>24.483</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1634,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>8087</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>24.5245555796552</x:v>
+        <x:v>23.299</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>5000</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>24.5500005722046</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>13087</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.00200261299143571</x:v>
+        <x:v>0.000114418934661047</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>3087</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>24.4833424397954</x:v>
+        <x:v>23.298</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1663,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>226358</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>24.0983549233532</x:v>
+        <x:v>24.043</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>224637</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.0166401583729</x:v>
+        <x:v>24.833</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>450995</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.0690126420166997</x:v>
+        <x:v>4.73305129203557E-05</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>1721</x:v>
+        <x:v>-39</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>34.7643396188048</x:v>
+        <x:v>27.692</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1692,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>775</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.2999992370605</x:v>
+        <x:v>24.339</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>1</x:v>
+        <x:v>1881</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>24.1399993896484</x:v>
+        <x:v>24.462</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>776</x:v>
+        <x:v>3221</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.000118745906728365</x:v>
+        <x:v>0.000474927047091793</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>774</x:v>
+        <x:v>-541</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.2989139655456</x:v>
+        <x:v>24.767</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1721,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>1340</x:v>
+        <x:v>134331</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>24.3394027823832</x:v>
+        <x:v>24.146</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>1881</x:v>
+        <x:v>137915</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>24.4618182975773</x:v>
+        <x:v>24.15</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>3221</x:v>
+        <x:v>272246</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.000492887326768123</x:v>
+        <x:v>0.0401418779455301</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-541</x:v>
+        <x:v>-3584</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>24.76502863096</x:v>
+        <x:v>24.318</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1750,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>133971</x:v>
+        <x:v>226968</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>24.1463113627855</x:v>
+        <x:v>24.098</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>137915</x:v>
+        <x:v>232325</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.1501759394169</x:v>
+        <x:v>24.018</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>271886</x:v>
+        <x:v>459293</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.0416048319545725</x:v>
+        <x:v>0.0677214120583455</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-3944</x:v>
+        <x:v>-5357</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>24.2814490621037</x:v>
+        <x:v>20.639</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1779,25 +1782,25 @@
         <x:v>1760009</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.8626256769488</x:v>
+        <x:v>23.863</x:v>
       </x:c>
       <x:c r="D43" s="0">
         <x:v>1854459</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>24.0090578733968</x:v>
+        <x:v>24.009</x:v>
       </x:c>
       <x:c r="F43" s="0">
         <x:v>3614468</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.553097010310129</x:v>
+        <x:v>0.532942755059851</x:v>
       </x:c>
       <x:c r="H43" s="0">
         <x:v>-94450</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>26.7377183671853</x:v>
+        <x:v>26.738</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1808,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>100</x:v>
+        <x:v>11238711</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.6800003051758</x:v>
+        <x:v>24.148</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>200001</x:v>
+        <x:v>11356137</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.15</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>200101</x:v>
+        <x:v>22594848</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.0306200704668203</x:v>
+        <x:v>3.33154437756222</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-199901</x:v>
+        <x:v>-117426</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>25.5009104505204</x:v>
+        <x:v>24.313</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1837,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>1619905</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>24.2652573552562</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>2059034</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>24.7145399275061</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>3678939</x:v>
+        <x:v>200101</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.562962561022351</x:v>
+        <x:v>0.0295043083049099</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-439129</x:v>
+        <x:v>-199901</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>26.3719004871604</x:v>
+        <x:v>25.501</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1866,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>3557306</x:v>
+        <x:v>1659971</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>24.1019141507018</x:v>
+        <x:v>24.26</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>4090212</x:v>
+        <x:v>2107639</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.2587724069056</x:v>
+        <x:v>24.7</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>7647518</x:v>
+        <x:v>3767610</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.17024672568491</x:v>
+        <x:v>0.555523095899879</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-532906</x:v>
+        <x:v>-447668</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>25.3058479060424</x:v>
+        <x:v>26.329</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1895,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>5020839</x:v>
+        <x:v>5201929</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>24.2082601617772</x:v>
+        <x:v>24.2</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>5596465</x:v>
+        <x:v>5705470</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>24.1807356339596</x:v>
+        <x:v>24.177</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>10617304</x:v>
+        <x:v>10907399</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>1.62469251351894</x:v>
+        <x:v>1.60826414111207</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-575626</x:v>
+        <x:v>-503541</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.9406557509746</x:v>
+        <x:v>23.935</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1924,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>4300883</x:v>
+        <x:v>3649538</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.9968285785417</x:v>
+        <x:v>24.098</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4980669</x:v>
+        <x:v>4156897</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.9069930677946</x:v>
+        <x:v>24.253</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>9281552</x:v>
+        <x:v>7806435</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.42029163413205</x:v>
+        <x:v>1.15103605180504</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-679786</x:v>
+        <x:v>-507359</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.3386200489792</x:v>
+        <x:v>25.371</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1953,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>640958</x:v>
+        <x:v>5033661</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.9881697529685</x:v>
+        <x:v>23.995</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1565233</x:v>
+        <x:v>5722447</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.765206583115</x:v>
+        <x:v>23.922</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>2206191</x:v>
+        <x:v>10756108</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.337598132359482</x:v>
+        <x:v>1.58595672481851</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-924275</x:v>
+        <x:v>-688786</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.610588068687</x:v>
+        <x:v>23.385</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1982,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>5930469</x:v>
+        <x:v>6206957</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>24.0601746543887</x:v>
+        <x:v>24.059</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>6876456</x:v>
+        <x:v>7065948</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.0121451746932</x:v>
+        <x:v>24.013</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>12806925</x:v>
+        <x:v>13272905</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.95975505351439</x:v>
+        <x:v>1.95705109530577</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-945987</x:v>
+        <x:v>-858991</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.7110444825904</x:v>
+        <x:v>23.679</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2011,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>0</x:v>
+        <x:v>653318</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>0</x:v>
+        <x:v>23.99</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>996158</x:v>
+        <x:v>1606212</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>24.4497553375111</x:v>
+        <x:v>23.774</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>996158</x:v>
+        <x:v>2259530</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>0.152435161024117</x:v>
+        <x:v>0.333161102364272</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-996158</x:v>
+        <x:v>-952894</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>24.4497553375111</x:v>
+        <x:v>23.625</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2040,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>1101210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>24.2984041507017</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>2487274</x:v>
+        <x:v>1067478</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>24.0127330259203</x:v>
+        <x:v>24.418</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>3588484</x:v>
+        <x:v>1067478</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>0.549120858711637</x:v>
+        <x:v>0.157396514863537</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1386064</x:v>
+        <x:v>-1067478</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.7857709957973</x:v>
+        <x:v>24.418</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2069,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>23553394</x:v>
+        <x:v>1101210</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>24.0562925312334</x:v>
+        <x:v>24.298</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>26642190</x:v>
+        <x:v>2488362</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>24.003812067474</x:v>
+        <x:v>24.013</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>50195584</x:v>
+        <x:v>3589572</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>7.6810826492781</x:v>
+        <x:v>0.529271912537529</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-3088796</x:v>
+        <x:v>-1387152</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.6036260272737</x:v>
+        <x:v>23.786</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2098,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>8745838</x:v>
+        <x:v>24687096</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>24.0899890786311</x:v>
+        <x:v>24.054</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>14679842</x:v>
+        <x:v>28078813</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.9087294094196</x:v>
+        <x:v>24.004</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>23425680</x:v>
+        <x:v>52765909</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>3.58466960351614</x:v>
+        <x:v>7.78017924510533</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-5934004</x:v>
+        <x:v>-3391717</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.641579656427</x:v>
+        <x:v>23.638</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2127,57 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>17436885</x:v>
+        <x:v>8870993</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>24.1005503357919</x:v>
+        <x:v>24.089</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>29769994</x:v>
+        <x:v>14800928</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.8986558545262</x:v>
+        <x:v>23.91</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>47206879</x:v>
+        <x:v>23671921</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>7.22374181787527</x:v>
+        <x:v>3.49035564716554</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-12333109</x:v>
+        <x:v>-5929935</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.6132119448061</x:v>
+        <x:v>23.642</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:9">
+      <x:c r="A56" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B56" s="0">
+        <x:v>17903841</x:v>
+      </x:c>
+      <x:c r="C56" s="0">
+        <x:v>24.099</x:v>
+      </x:c>
+      <x:c r="D56" s="0">
+        <x:v>30234461</x:v>
+      </x:c>
+      <x:c r="E56" s="0">
+        <x:v>23.901</x:v>
+      </x:c>
+      <x:c r="F56" s="0">
+        <x:v>48138302</x:v>
+      </x:c>
+      <x:c r="G56" s="0">
+        <x:v>7.09785210210275</x:v>
+      </x:c>
+      <x:c r="H56" s="0">
+        <x:v>-12330620</x:v>
+      </x:c>
+      <x:c r="I56" s="0">
+        <x:v>23.612</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -52,15 +52,18 @@
     <x:t>AK</x:t>
   </x:si>
   <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
@@ -70,7 +73,7 @@
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
-    <x:t>ZIRAAT</x:t>
+    <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
     <x:t>BTCTURK</x:t>
@@ -79,61 +82,61 @@
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
     <x:t>HSBC</x:t>
   </x:si>
   <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIZIM</x:t>
   </x:si>
   <x:si>
-    <x:t>AHLATCI</x:t>
+    <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
     <x:t>ANADOLU</x:t>
@@ -148,21 +151,15 @@
     <x:t>NCM INVESTMENT</x:t>
   </x:si>
   <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">ALLBATROSS </x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">AKTIF </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
@@ -172,31 +169,31 @@
     <x:t>BLUPAY</x:t>
   </x:si>
   <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
     <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
@@ -553,7 +550,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I56"/>
+  <x:dimension ref="A1:I55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -590,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>34456632</x:v>
+        <x:v>37166675</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>24.04</x:v>
+        <x:v>24.0088923918386</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>28534753</x:v>
+        <x:v>30672183</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>24.1</x:v>
+        <x:v>24.0631687793767</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>62991385</x:v>
+        <x:v>67838858</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.28789583057196</x:v>
+        <x:v>9.25642141548113</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>5921879</x:v>
+        <x:v>6494492</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.752</x:v>
+        <x:v>23.7525559006784</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -619,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>17946422</x:v>
+        <x:v>19717633</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>24.19</x:v>
+        <x:v>24.1326060403965</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>12329428</x:v>
+        <x:v>13377325</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>24.269</x:v>
+        <x:v>24.2180802589039</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>30275850</x:v>
+        <x:v>33094958</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.4640856996877</x:v>
+        <x:v>4.51571395815137</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>5616994</x:v>
+        <x:v>6340308</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24.017</x:v>
+        <x:v>23.9522652115134</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -648,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>17385231</x:v>
+        <x:v>18507982</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>24.093</x:v>
+        <x:v>24.061111836097</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>13483760</x:v>
+        <x:v>14111904</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.222</x:v>
+        <x:v>24.192937723928</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>30868991</x:v>
+        <x:v>32619886</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.5515426086101</x:v>
+        <x:v>4.45089171962407</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>3901471</x:v>
+        <x:v>4396078</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.651</x:v>
+        <x:v>23.6379359338984</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -677,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>47539758</x:v>
+        <x:v>52014874</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>24.022</x:v>
+        <x:v>23.98186837475</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>44925178</x:v>
+        <x:v>48998106</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>24.011</x:v>
+        <x:v>23.9738767149755</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>92464936</x:v>
+        <x:v>101012980</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.633684884822</x:v>
+        <x:v>13.7829370788283</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2614580</x:v>
+        <x:v>3016768</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.201</x:v>
+        <x:v>24.1116682774101</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -706,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>6795254</x:v>
+        <x:v>3638649</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.28</x:v>
+        <x:v>24.0113374034631</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>5273004</x:v>
+        <x:v>1851919</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.313</x:v>
+        <x:v>24.1479289775187</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>12068258</x:v>
+        <x:v>5490568</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.77942941182301</x:v>
+        <x:v>0.749172564466746</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1522250</x:v>
+        <x:v>1786730</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>24.167</x:v>
+        <x:v>23.8697622739061</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -735,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>2955799</x:v>
+        <x:v>7328102</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>24.097</x:v>
+        <x:v>24.2260182993309</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>1708304</x:v>
+        <x:v>5550260</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.2</x:v>
+        <x:v>24.2776240377982</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>4664103</x:v>
+        <x:v>12878362</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.687708371661588</x:v>
+        <x:v>1.75721628175283</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1247495</x:v>
+        <x:v>1777842</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.956</x:v>
+        <x:v>24.0649099072549</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -764,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>18330761</x:v>
+        <x:v>19792663</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>24.137</x:v>
+        <x:v>24.0957037904323</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>17182660</x:v>
+        <x:v>18434963</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>24.146</x:v>
+        <x:v>24.1068342725415</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>35513421</x:v>
+        <x:v>38227626</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>5.23635025385212</x:v>
+        <x:v>5.21605207401049</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1148101</x:v>
+        <x:v>1357700</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.999</x:v>
+        <x:v>23.9445731828932</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -793,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>5026623</x:v>
+        <x:v>24033460</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>24.122</x:v>
+        <x:v>24.1043293405446</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>3948872</x:v>
+        <x:v>22842309</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>24.287</x:v>
+        <x:v>24.184837565979</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>8975495</x:v>
+        <x:v>46875769</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.3234105360252</x:v>
+        <x:v>6.39606686832415</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>1077751</x:v>
+        <x:v>1191151</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.517</x:v>
+        <x:v>22.5604497128447</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -822,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>9628696</x:v>
+        <x:v>5540657</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>24.12</x:v>
+        <x:v>24.0692148896151</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8794877</x:v>
+        <x:v>4390726</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>24.204</x:v>
+        <x:v>24.2150882663549</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>18423573</x:v>
+        <x:v>9931383</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>2.71650205581189</x:v>
+        <x:v>1.35510928392316</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>833819</x:v>
+        <x:v>1149931</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.243</x:v>
+        <x:v>23.5122336203399</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -851,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>2156668</x:v>
+        <x:v>10254252</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.967</x:v>
+        <x:v>24.0867471373216</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1464111</x:v>
+        <x:v>9147035</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>24.115</x:v>
+        <x:v>24.181825599186</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>3620779</x:v>
+        <x:v>19401287</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.533873293586456</x:v>
+        <x:v>2.64725105594637</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>692557</x:v>
+        <x:v>1107217</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.654</x:v>
+        <x:v>23.3012768831444</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -880,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>22485643</x:v>
+        <x:v>2235129</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>24.139</x:v>
+        <x:v>23.9522486937003</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>21890931</x:v>
+        <x:v>1518181</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>24.209</x:v>
+        <x:v>24.0949345358447</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>44376574</x:v>
+        <x:v>3753310</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>6.54319628993184</x:v>
+        <x:v>0.51212859542741</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>594712</x:v>
+        <x:v>716948</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>21.581</x:v>
+        <x:v>23.6501027437673</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -909,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1107011</x:v>
+        <x:v>15206713</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>24.124</x:v>
+        <x:v>24.1107593042363</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>720190</x:v>
+        <x:v>14563244</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>24.231</x:v>
+        <x:v>24.1511697822689</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>1827201</x:v>
+        <x:v>29769957</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.269415453391236</x:v>
+        <x:v>4.06202692139588</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>386821</x:v>
+        <x:v>643469</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.923</x:v>
+        <x:v>23.1961734395795</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -938,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>584924</x:v>
+        <x:v>1239427</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>24.233</x:v>
+        <x:v>24.0663244323155</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>223722</x:v>
+        <x:v>818906</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>24.293</x:v>
+        <x:v>24.1432190714192</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>808646</x:v>
+        <x:v>2058333</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.119232492059171</x:v>
+        <x:v>0.28085374994655</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>361202</x:v>
+        <x:v>420521</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>24.195</x:v>
+        <x:v>23.9165828466874</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -967,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>3164865</x:v>
+        <x:v>609845</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>24.139</x:v>
+        <x:v>24.2019577900687</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>2847746</x:v>
+        <x:v>235111</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>24.045</x:v>
+        <x:v>24.2635324494139</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>6012611</x:v>
+        <x:v>844956</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.886541939627952</x:v>
+        <x:v>0.115291870236661</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>317119</x:v>
+        <x:v>374734</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>24.99</x:v>
+        <x:v>24.1633253741861</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -996,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>14169243</x:v>
+        <x:v>1656850</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>24.151</x:v>
+        <x:v>24.0033102966064</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>13863532</x:v>
+        <x:v>1311763</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>24.177</x:v>
+        <x:v>24.1451272580009</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>28032775</x:v>
+        <x:v>2968613</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>4.13335083903714</x:v>
+        <x:v>0.405058896296216</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>305711</x:v>
+        <x:v>345087</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>22.941</x:v>
+        <x:v>23.4642281441932</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1025,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1575419</x:v>
+        <x:v>4932677</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>24.026</x:v>
+        <x:v>24.0786319144866</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1282963</x:v>
+        <x:v>4633847</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>24.156</x:v>
+        <x:v>24.0971722868356</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>2858382</x:v>
+        <x:v>9566524</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.421460081564835</x:v>
+        <x:v>1.30532529933382</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>292456</x:v>
+        <x:v>298830</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.454</x:v>
+        <x:v>23.7911331734352</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1054,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>4707259</x:v>
+        <x:v>3544553</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>24.105</x:v>
+        <x:v>24.0742389517793</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>4444937</x:v>
+        <x:v>3249944</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>24.121</x:v>
+        <x:v>23.9768793639093</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>9152196</x:v>
+        <x:v>6794497</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.34946458264058</x:v>
+        <x:v>0.927090009950084</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>262322</x:v>
+        <x:v>294609</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.827</x:v>
+        <x:v>25.1482496182579</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1083,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>3528505</x:v>
+        <x:v>2074157</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.943</x:v>
+        <x:v>24.0414388784922</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>3278317</x:v>
+        <x:v>1866452</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>24.031</x:v>
+        <x:v>24.0560202900914</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>6806822</x:v>
+        <x:v>3940609</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.00364603307651</x:v>
+        <x:v>0.537685017304355</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>250188</x:v>
+        <x:v>207705</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>22.793</x:v>
+        <x:v>23.9104092699502</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1112,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>1843331</x:v>
+        <x:v>675572</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>24.104</x:v>
+        <x:v>24.1493951819502</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>1643072</x:v>
+        <x:v>494268</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>24.131</x:v>
+        <x:v>24.2285433135033</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>3486403</x:v>
+        <x:v>1169840</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.514059944663759</x:v>
+        <x:v>0.159621378483206</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>200259</x:v>
+        <x:v>181304</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.886</x:v>
+        <x:v>23.9336228399913</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1141,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>652714</x:v>
+        <x:v>4492739</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>24.174</x:v>
+        <x:v>23.8634824413475</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>490105</x:v>
+        <x:v>4338874</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>24.234</x:v>
+        <x:v>23.9242883626826</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1142819</x:v>
+        <x:v>8831613</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.16850532537423</x:v>
+        <x:v>1.20504875990751</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>162609</x:v>
+        <x:v>153865</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.992</x:v>
+        <x:v>22.1488024873163</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1170,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>785722</x:v>
+        <x:v>813161</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>24.014</x:v>
+        <x:v>24.0032805026186</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>660348</x:v>
+        <x:v>677630</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>24.143</x:v>
+        <x:v>24.1267001686458</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1446070</x:v>
+        <x:v>1490791</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.213218800058376</x:v>
+        <x:v>0.2034142399391</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>125374</x:v>
+        <x:v>135531</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.333</x:v>
+        <x:v>23.3862049384303</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1199,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>3687026</x:v>
+        <x:v>3790317</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>24.104</x:v>
+        <x:v>24.088550419374</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>3568621</x:v>
+        <x:v>3666415</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>24.188</x:v>
+        <x:v>24.1721336212675</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>7255647</x:v>
+        <x:v>7456732</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>1.06982396909358</x:v>
+        <x:v>1.01745011353675</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>118405</x:v>
+        <x:v>123902</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>21.592</x:v>
+        <x:v>21.6152190351307</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1228,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>157443</x:v>
+        <x:v>7898734</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>24.65</x:v>
+        <x:v>23.9987390329981</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>80797</x:v>
+        <x:v>7790190</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>24.057</x:v>
+        <x:v>24.0543597543815</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>238240</x:v>
+        <x:v>15688924</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0351277925175873</x:v>
+        <x:v>2.14070956352856</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>76646</x:v>
+        <x:v>108544</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>25.275</x:v>
+        <x:v>20.006846459354</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1257,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>184943</x:v>
+        <x:v>15958271</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>24.173</x:v>
+        <x:v>23.9667595842334</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>108441</x:v>
+        <x:v>15857285</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>24.156</x:v>
+        <x:v>23.9671074678127</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>293384</x:v>
+        <x:v>31815556</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0432586143383976</x:v>
+        <x:v>4.34114315284964</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>76502</x:v>
+        <x:v>100986</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>24.197</x:v>
+        <x:v>23.9121333086689</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1286,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>15132968</x:v>
+        <x:v>215053</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.992</x:v>
+        <x:v>24.1137812208325</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>15058725</x:v>
+        <x:v>123441</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.992</x:v>
+        <x:v>24.117870706452</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>30191693</x:v>
+        <x:v>338494</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>4.45167699571312</x:v>
+        <x:v>0.0461865544760773</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>74243</x:v>
+        <x:v>91612</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.963</x:v>
+        <x:v>24.108270914384</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1315,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>7352687</x:v>
+        <x:v>201152</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>24.037</x:v>
+        <x:v>24.4155840036921</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>7285234</x:v>
+        <x:v>109561</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>24.092</x:v>
+        <x:v>23.9129544777072</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>14637921</x:v>
+        <x:v>310713</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>2.15831871968114</x:v>
+        <x:v>0.0423959151445089</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>67453</x:v>
+        <x:v>91591</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>18.195</x:v>
+        <x:v>25.0168285964624</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1344,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>69966</x:v>
+        <x:v>76776</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>24.426</x:v>
+        <x:v>24.3573494018633</x:v>
       </x:c>
       <x:c r="D28" s="0">
         <x:v>21000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>24.312</x:v>
+        <x:v>24.3123811086019</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>90966</x:v>
+        <x:v>97776</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0134126711473928</x:v>
+        <x:v>0.0133412602600133</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>48966</x:v>
+        <x:v>55776</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.475</x:v>
+        <x:v>24.3742802351696</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1373,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>3388271</x:v>
+        <x:v>153285</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.737</x:v>
+        <x:v>24.252827503473</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3346345</x:v>
+        <x:v>99573</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.798</x:v>
+        <x:v>24.2245818614869</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>6734616</x:v>
+        <x:v>252858</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.992999469163969</x:v>
+        <x:v>0.0345017630791445</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>41926</x:v>
+        <x:v>53712</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>18.84</x:v>
+        <x:v>24.3051901656245</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1402,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>130888</x:v>
+        <x:v>1124794</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>24.363</x:v>
+        <x:v>23.7397971390111</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>90714</x:v>
+        <x:v>1082669</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>24.284</x:v>
+        <x:v>24.2867521763341</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>221602</x:v>
+        <x:v>2207463</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0326745679880893</x:v>
+        <x:v>0.301202119102333</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>40174</x:v>
+        <x:v>42125</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>24.539</x:v>
+        <x:v>9.6823190783945</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1431,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>2559781</x:v>
+        <x:v>2765505</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>24.009</x:v>
+        <x:v>23.9756375314872</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2525602</x:v>
+        <x:v>2726539</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>24.015</x:v>
+        <x:v>23.9824219426562</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>5085383</x:v>
+        <x:v>5492044</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.74982487783943</x:v>
+        <x:v>0.749373960516326</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>34179</x:v>
+        <x:v>38966</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>23.574</x:v>
+        <x:v>23.5009169637046</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1460,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>41147</x:v>
+        <x:v>3766782</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>24.672</x:v>
+        <x:v>23.7136974271204</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>16987</x:v>
+        <x:v>3731567</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>24.088</x:v>
+        <x:v>23.7660413671328</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>58134</x:v>
+        <x:v>7498349</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00857168859224908</x:v>
+        <x:v>1.02312863616235</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>24160</x:v>
+        <x:v>35215</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>25.083</x:v>
+        <x:v>18.1670576656438</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1489,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1082541</x:v>
+        <x:v>46065</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.741</x:v>
+        <x:v>24.5794636560654</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>1064132</x:v>
+        <x:v>17087</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>24.297</x:v>
+        <x:v>24.0849988122175</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>2146673</x:v>
+        <x:v>63152</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.316520667172208</x:v>
+        <x:v>0.00861691282053222</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>18409</x:v>
+        <x:v>28978</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>-8.406</x:v>
+        <x:v>24.871026938101</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1518,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>111149</x:v>
+        <x:v>248184</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>24.227</x:v>
+        <x:v>24.0405829414902</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>98203</x:v>
+        <x:v>232627</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>24.175</x:v>
+        <x:v>24.017756802662</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>209352</x:v>
+        <x:v>480811</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0308683412489168</x:v>
+        <x:v>0.0656053089395889</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>12946</x:v>
+        <x:v>15557</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>24.622</x:v>
+        <x:v>24.3819068598013</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1547,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>29229</x:v>
+        <x:v>114654</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.807</x:v>
+        <x:v>24.2054222883721</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>19470</x:v>
+        <x:v>101096</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.145</x:v>
+        <x:v>24.1572912193471</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>48699</x:v>
+        <x:v>215750</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00718052538538442</x:v>
+        <x:v>0.0294384808245159</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>9759</x:v>
+        <x:v>13558</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.132</x:v>
+        <x:v>24.5643143487163</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1576,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>11218</x:v>
+        <x:v>29235</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.713</x:v>
+        <x:v>23.8065616702267</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>7078</x:v>
+        <x:v>19470</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>24.305</x:v>
+        <x:v>24.1447667662156</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>18296</x:v>
+        <x:v>48705</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00269769178937952</x:v>
+        <x:v>0.00664566029459117</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>4140</x:v>
+        <x:v>9765</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>22.701</x:v>
+        <x:v>23.1322295433548</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1605,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>8087</x:v>
+        <x:v>12350</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>24.525</x:v>
+        <x:v>23.6840467400493</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>5000</x:v>
+        <x:v>7930</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>24.55</x:v>
+        <x:v>24.225230762727</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>13087</x:v>
+        <x:v>20280</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00192963994575917</x:v>
+        <x:v>0.00276714897391046</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>3087</x:v>
+        <x:v>4420</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>24.483</x:v>
+        <x:v>22.7130989346569</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1634,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>775</x:v>
+        <x:v>8087</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.299</x:v>
+        <x:v>24.5245555796552</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>1</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>24</x:v>
+        <x:v>24.5500005722046</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>776</x:v>
+        <x:v>13087</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000114418934661047</x:v>
+        <x:v>0.00178568435017585</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>774</x:v>
+        <x:v>3087</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.298</x:v>
+        <x:v>24.4833424397954</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1663,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>141</x:v>
+        <x:v>3340</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>24.043</x:v>
+        <x:v>24.1002397594338</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>180</x:v>
+        <x:v>1881</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.833</x:v>
+        <x:v>24.4618182975773</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>321</x:v>
+        <x:v>5221</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>4.73305129203557E-05</x:v>
+        <x:v>0.000712390768875074</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-39</x:v>
+        <x:v>1459</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>27.692</x:v>
+        <x:v>23.6340785323961</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1692,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>1340</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>24.339</x:v>
+        <x:v>23.2999992370605</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>1881</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>24.462</x:v>
+        <x:v>24.1399993896484</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>3221</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.000474927047091793</x:v>
+        <x:v>0.000105883017936613</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-541</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>24.767</x:v>
+        <x:v>23.2989139655456</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1721,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>134331</x:v>
+        <x:v>135739</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>24.146</x:v>
+        <x:v>24.1400334479178</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>137915</x:v>
+        <x:v>139173</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>24.15</x:v>
+        <x:v>24.1447289027144</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>272246</x:v>
+        <x:v>274912</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0401418779455301</x:v>
+        <x:v>0.0375109693646781</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-3584</x:v>
+        <x:v>-3434</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>24.318</x:v>
+        <x:v>24.3303306320759</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1750,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>226968</x:v>
+        <x:v>1760009</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>24.098</x:v>
+        <x:v>23.8626256769488</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>232325</x:v>
+        <x:v>1854603</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.018</x:v>
+        <x:v>24.0090525114639</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>459293</x:v>
+        <x:v>3614612</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.0677214120583455</x:v>
+        <x:v>0.493203643337497</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-5357</x:v>
+        <x:v>-94594</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>20.639</x:v>
+        <x:v>26.7334594145248</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1779,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>1760009</x:v>
+        <x:v>12235170</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.863</x:v>
+        <x:v>24.0986526486017</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>1854459</x:v>
+        <x:v>12346080</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>24.009</x:v>
+        <x:v>24.1073521856853</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>3614468</x:v>
+        <x:v>24581250</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.532942755059851</x:v>
+        <x:v>3.35404244156492</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-94450</x:v>
+        <x:v>-110910</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>26.738</x:v>
+        <x:v>25.0670520787458</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1808,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>11238711</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>24.148</x:v>
+        <x:v>23.6800003051758</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>11356137</x:v>
+        <x:v>200001</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>24.15</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>22594848</x:v>
+        <x:v>200101</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>3.33154437756222</x:v>
+        <x:v>0.0273032187785235</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-117426</x:v>
+        <x:v>-199901</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>24.313</x:v>
+        <x:v>25.5009104505204</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1837,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>100</x:v>
+        <x:v>4134539</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.68</x:v>
+        <x:v>24.024134269909</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>200001</x:v>
+        <x:v>4426750</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>25.5</x:v>
+        <x:v>24.2077375978149</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>200101</x:v>
+        <x:v>8561289</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.0295043083049099</x:v>
+        <x:v>1.16816381024166</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-199901</x:v>
+        <x:v>-292211</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>25.501</x:v>
+        <x:v>26.8055697114472</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1866,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>1659971</x:v>
+        <x:v>5619189</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>24.26</x:v>
+        <x:v>24.1522001965864</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>2107639</x:v>
+        <x:v>6089936</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.138289718176</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>3767610</x:v>
+        <x:v>11709125</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.555523095899879</x:v>
+        <x:v>1.59767718092403</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-447668</x:v>
+        <x:v>-470747</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>26.329</x:v>
+        <x:v>23.9722438224647</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1895,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>5201929</x:v>
+        <x:v>1813090</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>24.2</x:v>
+        <x:v>24.1972900715868</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>5705470</x:v>
+        <x:v>2400821</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>24.177</x:v>
+        <x:v>24.5702021519409</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>10907399</x:v>
+        <x:v>4213911</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>1.60826414111207</x:v>
+        <x:v>0.574976306696252</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-503541</x:v>
+        <x:v>-587731</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.935</x:v>
+        <x:v>25.7205977645071</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1924,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>3649538</x:v>
+        <x:v>6730407</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>24.098</x:v>
+        <x:v>24.0210105159806</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4156897</x:v>
+        <x:v>7455480</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>24.253</x:v>
+        <x:v>23.9920434422251</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>7806435</x:v>
+        <x:v>14185887</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.15103605180504</x:v>
+        <x:v>1.93562439132444</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-507359</x:v>
+        <x:v>-725073</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>25.371</x:v>
+        <x:v>23.7231599008804</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1953,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>5033661</x:v>
+        <x:v>684145</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.995</x:v>
+        <x:v>23.9729663840903</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>5722447</x:v>
+        <x:v>1615332</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.922</x:v>
+        <x:v>23.7729472153108</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>10756108</x:v>
+        <x:v>2299477</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.58595672481851</x:v>
+        <x:v>0.313757170664729</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-688786</x:v>
+        <x:v>-931187</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.385</x:v>
+        <x:v>23.6259927215038</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1982,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>6206957</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>24.059</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>7065948</x:v>
+        <x:v>1137935</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.013</x:v>
+        <x:v>24.3678587327946</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>13272905</x:v>
+        <x:v>1137935</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.95705109530577</x:v>
+        <x:v>0.155268030948067</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-858991</x:v>
+        <x:v>-1137935</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.679</x:v>
+        <x:v>24.3678587327946</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2011,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>653318</x:v>
+        <x:v>1168424</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.99</x:v>
+        <x:v>24.2533595449198</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>1606212</x:v>
+        <x:v>2546203</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.774</x:v>
+        <x:v>24.0004246171454</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2259530</x:v>
+        <x:v>3714627</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>0.333161102364272</x:v>
+        <x:v>0.506850408851582</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-952894</x:v>
+        <x:v>-1377779</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.625</x:v>
+        <x:v>23.7859234235215</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2040,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>0</x:v>
+        <x:v>26610017</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>0</x:v>
+        <x:v>24.0188512278435</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1067478</x:v>
+        <x:v>29861161</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>24.418</x:v>
+        <x:v>23.9787937524682</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>1067478</x:v>
+        <x:v>56471178</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>0.157396514863537</x:v>
+        <x:v>7.70533344468515</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1067478</x:v>
+        <x:v>-3251144</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>24.418</x:v>
+        <x:v>23.650930667747</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2069,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>1101210</x:v>
+        <x:v>5495707</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>24.298</x:v>
+        <x:v>23.9592310389548</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>2488362</x:v>
+        <x:v>9568121</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>24.013</x:v>
+        <x:v>23.7492436561418</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>3589572</x:v>
+        <x:v>15063828</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>0.529271912537529</x:v>
+        <x:v>2.05541697205935</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1387152</x:v>
+        <x:v>-4072414</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.786</x:v>
+        <x:v>23.4658664922196</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2098,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>24687096</x:v>
+        <x:v>9383367</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>24.054</x:v>
+        <x:v>24.0571851244238</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>28078813</x:v>
+        <x:v>15134552</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>24.004</x:v>
+        <x:v>23.9006103723697</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>52765909</x:v>
+        <x:v>24517919</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>7.78017924510533</x:v>
+        <x:v>3.34540110469772</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-3391717</x:v>
+        <x:v>-5751185</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.638</x:v>
+        <x:v>23.6451502608524</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2127,57 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>8870993</x:v>
+        <x:v>18783111</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>24.089</x:v>
+        <x:v>24.0742158463454</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>14800928</x:v>
+        <x:v>32987713</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.91</x:v>
+        <x:v>23.8732216347197</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>23671921</x:v>
+        <x:v>51770824</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>3.49035564716554</x:v>
+        <x:v>7.06398335848614</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-5929935</x:v>
+        <x:v>-14204602</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.642</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:9">
-      <x:c r="A56" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B56" s="0">
-        <x:v>17903841</x:v>
-      </x:c>
-      <x:c r="C56" s="0">
-        <x:v>24.099</x:v>
-      </x:c>
-      <x:c r="D56" s="0">
-        <x:v>30234461</x:v>
-      </x:c>
-      <x:c r="E56" s="0">
-        <x:v>23.901</x:v>
-      </x:c>
-      <x:c r="F56" s="0">
-        <x:v>48138302</x:v>
-      </x:c>
-      <x:c r="G56" s="0">
-        <x:v>7.09785210210275</x:v>
-      </x:c>
-      <x:c r="H56" s="0">
-        <x:v>-12330620</x:v>
-      </x:c>
-      <x:c r="I56" s="0">
-        <x:v>23.612</x:v>
+        <x:v>23.6074418129885</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,127 +40,127 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
     <x:t>DINAMIK</x:t>
   </x:si>
   <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
     <x:t>GCM</x:t>
   </x:si>
   <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALTERNATIF</x:t>
   </x:si>
   <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
     <x:t>PUSULA YAT.</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>37166675</x:v>
+        <x:v>20878176</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>24.0088923918386</x:v>
+        <x:v>24.0944807842817</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>30672183</x:v>
+        <x:v>14422104</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>24.0631687793767</x:v>
+        <x:v>24.1631140809629</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>67838858</x:v>
+        <x:v>35300280</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.25642141548113</x:v>
+        <x:v>4.60546182565582</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>6494492</x:v>
+        <x:v>6456072</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.7525559006784</x:v>
+        <x:v>23.9411620879291</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>19717633</x:v>
+        <x:v>38650663</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>24.1326060403965</x:v>
+        <x:v>23.9895109713796</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>13377325</x:v>
+        <x:v>32318217</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>24.2180802589039</x:v>
+        <x:v>24.0346694053628</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>33094958</x:v>
+        <x:v>70968880</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.51571395815137</x:v>
+        <x:v>9.25897663275047</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>6340308</x:v>
+        <x:v>6332446</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.9522652115134</x:v>
+        <x:v>23.7590407756841</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>18507982</x:v>
+        <x:v>19633975</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>24.061111836097</x:v>
+        <x:v>24.0253326888241</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>14111904</x:v>
+        <x:v>15184978</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.192937723928</x:v>
+        <x:v>24.1403988177794</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>32619886</x:v>
+        <x:v>34818953</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.45089171962407</x:v>
+        <x:v>4.54266535140243</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>4396078</x:v>
+        <x:v>4448997</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.6379359338984</x:v>
+        <x:v>23.6325977337924</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>52014874</x:v>
+        <x:v>53388971</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.98186837475</x:v>
+        <x:v>23.9702824128092</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>48998106</x:v>
+        <x:v>50179736</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.9738767149755</x:v>
+        <x:v>23.9641363778417</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>101012980</x:v>
+        <x:v>103568707</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.7829370788283</x:v>
+        <x:v>13.5121230319146</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>3016768</x:v>
+        <x:v>3209235</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.1116682774101</x:v>
+        <x:v>24.0663820789649</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>3638649</x:v>
+        <x:v>7934913</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.0113374034631</x:v>
+        <x:v>24.1640661835974</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1851919</x:v>
+        <x:v>5877879</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.1479289775187</x:v>
+        <x:v>24.2354125827359</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>5490568</x:v>
+        <x:v>13812792</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.749172564466746</x:v>
+        <x:v>1.80209013247839</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1786730</x:v>
+        <x:v>2057034</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.8697622739061</x:v>
+        <x:v>23.9601971657679</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>7328102</x:v>
+        <x:v>3901477</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>24.2260182993309</x:v>
+        <x:v>23.9711851912947</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>5550260</x:v>
+        <x:v>1947005</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.2776240377982</x:v>
+        <x:v>24.1138219567291</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>12878362</x:v>
+        <x:v>5848482</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.75721628175283</x:v>
+        <x:v>0.763023992700205</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1777842</x:v>
+        <x:v>1954472</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>24.0649099072549</x:v>
+        <x:v>23.8290933652237</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>19792663</x:v>
+        <x:v>20570086</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>24.0957037904323</x:v>
+        <x:v>24.0710020362119</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>18434963</x:v>
+        <x:v>19039397</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>24.1068342725415</x:v>
+        <x:v>24.0850523221661</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>38227626</x:v>
+        <x:v>39609483</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>5.21605207401049</x:v>
+        <x:v>5.16766331288203</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1357700</x:v>
+        <x:v>1530689</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.9445731828932</x:v>
+        <x:v>23.8962382714989</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>24033460</x:v>
+        <x:v>11044539</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>24.1043293405446</x:v>
+        <x:v>24.0447509888449</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>22842309</x:v>
+        <x:v>9669457</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>24.184837565979</x:v>
+        <x:v>24.1401130113124</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>46875769</x:v>
+        <x:v>20713996</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>6.39606686832415</x:v>
+        <x:v>2.70245782284977</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>1191151</x:v>
+        <x:v>1375082</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>22.5604497128447</x:v>
+        <x:v>23.3741735427853</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>5540657</x:v>
+        <x:v>5816477</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>24.0692148896151</x:v>
+        <x:v>24.0415894652744</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>4390726</x:v>
+        <x:v>4566870</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>24.2150882663549</x:v>
+        <x:v>24.1906443799734</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>9931383</x:v>
+        <x:v>10383347</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.35510928392316</x:v>
+        <x:v>1.35466654176788</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>1149931</x:v>
+        <x:v>1249607</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.5122336203399</x:v>
+        <x:v>23.4968466635043</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>10254252</x:v>
+        <x:v>25136217</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>24.0867471373216</x:v>
+        <x:v>24.0741494635259</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>9147035</x:v>
+        <x:v>24184234</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>24.181825599186</x:v>
+        <x:v>24.1433490165418</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>19401287</x:v>
+        <x:v>49320451</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2.64725105594637</x:v>
+        <x:v>6.4346077227894</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>1107217</x:v>
+        <x:v>951983</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.3012768831444</x:v>
+        <x:v>22.3161998122921</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2235129</x:v>
+        <x:v>2267286</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.9522486937003</x:v>
+        <x:v>23.9425036828394</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1518181</x:v>
+        <x:v>1531594</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>24.0949345358447</x:v>
+        <x:v>24.0876207570204</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>3753310</x:v>
+        <x:v>3798880</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.51212859542741</x:v>
+        <x:v>0.495622040965323</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>716948</x:v>
+        <x:v>735692</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.6501027437673</x:v>
+        <x:v>23.6403929624387</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>15206713</x:v>
+        <x:v>1833561</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>24.1107593042363</x:v>
+        <x:v>23.9361427214928</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>14563244</x:v>
+        <x:v>1338697</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>24.1511697822689</x:v>
+        <x:v>24.1290038662459</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>29769957</x:v>
+        <x:v>3172258</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>4.06202692139588</x:v>
+        <x:v>0.413869610103129</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>643469</x:v>
+        <x:v>494864</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.1961734395795</x:v>
+        <x:v>23.4144182964033</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1239427</x:v>
+        <x:v>1292252</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>24.0663244323155</x:v>
+        <x:v>24.0423458401931</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>818906</x:v>
+        <x:v>874372</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>24.1432190714192</x:v>
+        <x:v>24.0990669912188</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>2058333</x:v>
+        <x:v>2166624</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.28085374994655</x:v>
+        <x:v>0.282669262752299</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>420521</x:v>
+        <x:v>417880</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.9165828466874</x:v>
+        <x:v>23.9236625189894</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>609845</x:v>
+        <x:v>15826339</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>24.2019577900687</x:v>
+        <x:v>24.0861666190902</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>235111</x:v>
+        <x:v>15412350</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>24.2635324494139</x:v>
+        <x:v>24.1082400428832</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>844956</x:v>
+        <x:v>31238689</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.115291870236661</x:v>
+        <x:v>4.07556511373378</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>374734</x:v>
+        <x:v>413989</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>24.1633253741861</x:v>
+        <x:v>23.2643976030138</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>1656850</x:v>
+        <x:v>647879</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>24.0033102966064</x:v>
+        <x:v>24.1554312665448</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1311763</x:v>
+        <x:v>243128</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>24.1451272580009</x:v>
+        <x:v>24.2351640144328</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>2968613</x:v>
+        <x:v>891007</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.405058896296216</x:v>
+        <x:v>0.116245500740847</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>345087</x:v>
+        <x:v>404751</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.4642281441932</x:v>
+        <x:v>24.1075369722045</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>4932677</x:v>
+        <x:v>5229388</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>24.0786319144866</x:v>
+        <x:v>24.0435393063044</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>4633847</x:v>
+        <x:v>4883702</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>24.0971722868356</x:v>
+        <x:v>24.0678002715743</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>9566524</x:v>
+        <x:v>10113090</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>1.30532529933382</x:v>
+        <x:v>1.31940737961347</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>298830</x:v>
+        <x:v>345686</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.7911331734352</x:v>
+        <x:v>23.7007909028098</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>3544553</x:v>
+        <x:v>2349446</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>24.0742389517793</x:v>
+        <x:v>23.9855627269492</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>3249944</x:v>
+        <x:v>2128006</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.9768793639093</x:v>
+        <x:v>23.9979570301221</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>6794497</x:v>
+        <x:v>4477452</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.927090009950084</x:v>
+        <x:v>0.584152144464755</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>294609</x:v>
+        <x:v>221440</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>25.1482496182579</x:v>
+        <x:v>23.8664552869308</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>2074157</x:v>
+        <x:v>722232</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>24.0414388784922</x:v>
+        <x:v>24.0931192379807</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>1866452</x:v>
+        <x:v>502820</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>24.0560202900914</x:v>
+        <x:v>24.2159607898724</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>3940609</x:v>
+        <x:v>1225052</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.537685017304355</x:v>
+        <x:v>0.159826783822772</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>207705</x:v>
+        <x:v>219412</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.9104092699502</x:v>
+        <x:v>23.811606881673</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>675572</x:v>
+        <x:v>3595316</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>24.1493951819502</x:v>
+        <x:v>24.0647649999192</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>494268</x:v>
+        <x:v>3403839</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>24.2285433135033</x:v>
+        <x:v>23.9457118664324</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>1169840</x:v>
+        <x:v>6999155</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.159621378483206</x:v>
+        <x:v>0.913146897541551</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>181304</x:v>
+        <x:v>191477</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.9336228399913</x:v>
+        <x:v>26.1811429400093</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>4492739</x:v>
+        <x:v>848327</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.8634824413475</x:v>
+        <x:v>23.9762272957027</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>4338874</x:v>
+        <x:v>687063</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.9242883626826</x:v>
+        <x:v>24.1153885650165</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>8831613</x:v>
+        <x:v>1535390</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>1.20504875990751</x:v>
+        <x:v>0.200315125899672</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>153865</x:v>
+        <x:v>161264</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.1488024873163</x:v>
+        <x:v>23.3833326683925</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>813161</x:v>
+        <x:v>3938440</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>24.0032805026186</x:v>
+        <x:v>24.0674170155677</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>677630</x:v>
+        <x:v>3838059</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>24.1267001686458</x:v>
+        <x:v>24.1388617739505</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1490791</x:v>
+        <x:v>7776499</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.2034142399391</x:v>
+        <x:v>1.01456332022722</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>135531</x:v>
+        <x:v>100381</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.3862049384303</x:v>
+        <x:v>21.3357327534653</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>3790317</x:v>
+        <x:v>4604429</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>24.088550419374</x:v>
+        <x:v>23.8510572382935</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>3666415</x:v>
+        <x:v>4514029</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>24.1721336212675</x:v>
+        <x:v>23.9087516677882</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>7456732</x:v>
+        <x:v>9118458</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>1.01745011353675</x:v>
+        <x:v>1.18964241155724</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>123902</x:v>
+        <x:v>90400</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>21.6152190351307</x:v>
+        <x:v>20.9701465316789</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>7898734</x:v>
+        <x:v>216519</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.9987390329981</x:v>
+        <x:v>24.3500573320956</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>7790190</x:v>
+        <x:v>126952</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>24.0543597543815</x:v>
+        <x:v>23.8398125641918</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>15688924</x:v>
+        <x:v>343471</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>2.14070956352856</x:v>
+        <x:v>0.0448110490545636</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>108544</x:v>
+        <x:v>89567</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>20.006846459354</x:v>
+        <x:v>25.0732767519145</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>15958271</x:v>
+        <x:v>181215</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.9667595842334</x:v>
+        <x:v>24.1209715243546</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>15857285</x:v>
+        <x:v>114573</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.9671074678127</x:v>
+        <x:v>24.1043202677046</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>31815556</x:v>
+        <x:v>295788</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>4.34114315284964</x:v>
+        <x:v>0.0385900718772509</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>100986</x:v>
+        <x:v>66642</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.9121333086689</x:v>
+        <x:v>24.1495988828996</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>215053</x:v>
+        <x:v>79286</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>24.1137812208325</x:v>
+        <x:v>24.3248903665552</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>123441</x:v>
+        <x:v>21000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>24.117870706452</x:v>
+        <x:v>24.3123811086019</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>338494</x:v>
+        <x:v>100286</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0461865544760773</x:v>
+        <x:v>0.0130838436592492</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>91612</x:v>
+        <x:v>58286</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>24.108270914384</x:v>
+        <x:v>24.3293973565188</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>201152</x:v>
+        <x:v>1158792</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>24.4155840036921</x:v>
+        <x:v>23.7296291564529</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>109561</x:v>
+        <x:v>1101513</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.9129544777072</x:v>
+        <x:v>24.2706692766137</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>310713</x:v>
+        <x:v>2260305</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0423959151445089</x:v>
+        <x:v>0.294891383066621</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>91591</x:v>
+        <x:v>57279</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>25.0168285964624</x:v>
+        <x:v>13.3250703150156</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>76776</x:v>
+        <x:v>8287187</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>24.3573494018633</x:v>
+        <x:v>23.9724947415293</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>21000</x:v>
+        <x:v>8246251</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>24.3123811086019</x:v>
+        <x:v>24.0211453009486</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>97776</x:v>
+        <x:v>16533438</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0133412602600133</x:v>
+        <x:v>2.1570400448905</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>55776</x:v>
+        <x:v>40936</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.3742802351696</x:v>
+        <x:v>14.1722034511562</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>153285</x:v>
+        <x:v>50826</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>24.252827503473</x:v>
+        <x:v>24.4822585197424</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>99573</x:v>
+        <x:v>17295</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>24.2245818614869</x:v>
+        <x:v>24.0759152797579</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>252858</x:v>
+        <x:v>68121</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0345017630791445</x:v>
+        <x:v>0.00888742709761792</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>53712</x:v>
+        <x:v>33531</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.3051901656245</x:v>
+        <x:v>24.691846851004</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>1124794</x:v>
+        <x:v>3865608</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.7397971390111</x:v>
+        <x:v>23.7040759349266</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1082669</x:v>
+        <x:v>3842590</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>24.2867521763341</x:v>
+        <x:v>23.755989602133</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>2207463</x:v>
+        <x:v>7708198</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.301202119102333</x:v>
+        <x:v>1.00565240937456</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>42125</x:v>
+        <x:v>23018</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>9.6823190783945</x:v>
+        <x:v>15.0376870883455</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>2765505</x:v>
+        <x:v>255435</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.9756375314872</x:v>
+        <x:v>24.0194746936614</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2726539</x:v>
+        <x:v>234271</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.9824219426562</x:v>
+        <x:v>24.0133308515818</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>5492044</x:v>
+        <x:v>489706</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.749373960516326</x:v>
+        <x:v>0.0638896430508372</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>38966</x:v>
+        <x:v>21164</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>23.5009169637046</x:v>
+        <x:v>24.0874828219842</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>3766782</x:v>
+        <x:v>16330433</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.7136974271204</x:v>
+        <x:v>23.9554558879869</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>3731567</x:v>
+        <x:v>16313859</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.7660413671328</x:v>
+        <x:v>23.952712844254</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>7498349</x:v>
+        <x:v>32644292</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>1.02312863616235</x:v>
+        <x:v>4.25894753898727</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>35215</x:v>
+        <x:v>16574</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>18.1670576656438</x:v>
+        <x:v>26.6554455519499</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>46065</x:v>
+        <x:v>3014065</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>24.5794636560654</x:v>
+        <x:v>23.9331827244839</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>17087</x:v>
+        <x:v>2997624</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>24.0849988122175</x:v>
+        <x:v>23.9324932358592</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>63152</x:v>
+        <x:v>6011689</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00861691282053222</x:v>
+        <x:v>0.784316843866819</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>28978</x:v>
+        <x:v>16441</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>24.871026938101</x:v>
+        <x:v>24.0588945211644</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>248184</x:v>
+        <x:v>128215</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>24.0405829414902</x:v>
+        <x:v>24.1380164704243</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>232627</x:v>
+        <x:v>113240</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>24.017756802662</x:v>
+        <x:v>24.0711062637499</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>480811</x:v>
+        <x:v>241455</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0656053089395889</x:v>
+        <x:v>0.0315015004162496</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>15557</x:v>
+        <x:v>14975</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>24.3819068598013</x:v>
+        <x:v>24.643987208575</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>114654</x:v>
+        <x:v>241528</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>24.2054222883721</x:v>
+        <x:v>24.0385053325697</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>101096</x:v>
+        <x:v>230597</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>24.1572912193471</x:v>
+        <x:v>23.7826122893832</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>215750</x:v>
+        <x:v>472125</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0294384808245159</x:v>
+        <x:v>0.0615959325092536</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>13558</x:v>
+        <x:v>10931</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>24.5643143487163</x:v>
+        <x:v>29.4367459399867</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,10 +1573,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>29235</x:v>
+        <x:v>29318</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.8065616702267</x:v>
+        <x:v>23.8049768200919</x:v>
       </x:c>
       <x:c r="D36" s="0">
         <x:v>19470</x:v>
@@ -1585,16 +1585,16 @@
         <x:v>24.1447667662156</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>48705</x:v>
+        <x:v>48788</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00664566029459117</x:v>
+        <x:v>0.00636514134024138</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>9765</x:v>
+        <x:v>9848</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.1322295433548</x:v>
+        <x:v>23.133194706868</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>12350</x:v>
+        <x:v>1860684</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.6840467400493</x:v>
+        <x:v>23.848292344678</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>7930</x:v>
+        <x:v>1855153</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>24.225230762727</x:v>
+        <x:v>24.008838524296</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>20280</x:v>
+        <x:v>3715837</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00276714897391046</x:v>
+        <x:v>0.484787810574291</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>4420</x:v>
+        <x:v>5531</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>22.7130989346569</x:v>
+        <x:v>-30.0005101786882</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1646,7 +1646,7 @@
         <x:v>13087</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.00178568435017585</x:v>
+        <x:v>0.00170739945723823</x:v>
       </x:c>
       <x:c r="H38" s="0">
         <x:v>3087</x:v>
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>3340</x:v>
+        <x:v>142249</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>24.1002397594338</x:v>
+        <x:v>24.0983838003718</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>1881</x:v>
+        <x:v>139173</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.4618182975773</x:v>
+        <x:v>24.1447289027144</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>5221</x:v>
+        <x:v>281422</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.000712390768875074</x:v>
+        <x:v>0.0367158072938717</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>1459</x:v>
+        <x:v>3076</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.6340785323961</x:v>
+        <x:v>22.0015089862213</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>775</x:v>
+        <x:v>3840</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.2999992370605</x:v>
+        <x:v>24.0377086500327</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>1</x:v>
+        <x:v>1881</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>24.1399993896484</x:v>
+        <x:v>24.4618182975773</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>776</x:v>
+        <x:v>5721</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.000105883017936613</x:v>
+        <x:v>0.000746392014583934</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>774</x:v>
+        <x:v>1959</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.2989139655456</x:v>
+        <x:v>23.6304854509355</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>135739</x:v>
+        <x:v>12916</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>24.1400334479178</x:v>
+        <x:v>23.6687362419263</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>139173</x:v>
+        <x:v>11988</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>24.1447289027144</x:v>
+        <x:v>24.0186122198044</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>274912</x:v>
+        <x:v>24904</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0375109693646781</x:v>
+        <x:v>0.0032491079760878</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-3434</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>24.3303306320759</x:v>
+        <x:v>19.1490021656299</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>1760009</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.8626256769488</x:v>
+        <x:v>23.2999992370605</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>1854603</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.0090525114639</x:v>
+        <x:v>24.1399993896484</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>3614612</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.493203643337497</x:v>
+        <x:v>0.000101241077314653</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-94594</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>26.7334594145248</x:v>
+        <x:v>23.2989139655456</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>12235170</x:v>
+        <x:v>12967483</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>24.0986526486017</x:v>
+        <x:v>24.0667133978291</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>12346080</x:v>
+        <x:v>13124822</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>24.1073521856853</x:v>
+        <x:v>24.0721818828317</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>24581250</x:v>
+        <x:v>26092305</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>3.35404244156492</x:v>
+        <x:v>3.40414055131768</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-110910</x:v>
+        <x:v>-157339</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>25.0670520787458</x:v>
+        <x:v>24.5228806053806</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1820,7 +1820,7 @@
         <x:v>200101</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.0273032187785235</x:v>
+        <x:v>0.0261062381594581</x:v>
       </x:c>
       <x:c r="H44" s="0">
         <x:v>-199901</x:v>
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>4134539</x:v>
+        <x:v>4495121</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>24.024134269909</x:v>
+        <x:v>23.973422642649</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>4426750</x:v>
+        <x:v>4696337</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>24.2077375978149</x:v>
+        <x:v>24.1556853774643</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>8561289</x:v>
+        <x:v>9191458</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.16816381024166</x:v>
+        <x:v>1.19916637888195</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-292211</x:v>
+        <x:v>-201216</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>26.8055697114472</x:v>
+        <x:v>28.227394619203</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>5619189</x:v>
+        <x:v>6064384</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>24.1522001965864</x:v>
+        <x:v>24.1051803684461</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>6089936</x:v>
+        <x:v>6523552</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.138289718176</x:v>
+        <x:v>24.0935432341155</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>11709125</x:v>
+        <x:v>12587936</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.59767718092403</x:v>
+        <x:v>1.64228891985555</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-470747</x:v>
+        <x:v>-459168</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.9722438224647</x:v>
+        <x:v>23.9398477430526</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1813090</x:v>
+        <x:v>1910370</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>24.1972900715868</x:v>
+        <x:v>24.1574914440899</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2400821</x:v>
+        <x:v>2485751</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>24.5702021519409</x:v>
+        <x:v>24.5306646350452</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>4213911</x:v>
+        <x:v>4396121</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.574976306696252</x:v>
+        <x:v>0.573541270677283</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-587731</x:v>
+        <x:v>-575381</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.7205977645071</x:v>
+        <x:v>25.7696677804484</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>6730407</x:v>
+        <x:v>7153289</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>24.0210105159806</x:v>
+        <x:v>23.9815545026129</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>7455480</x:v>
+        <x:v>7894272</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.9920434422251</x:v>
+        <x:v>23.9595541259883</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>14185887</x:v>
+        <x:v>15047561</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.93562439132444</x:v>
+        <x:v>1.96318464767779</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-725073</x:v>
+        <x:v>-740983</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.7231599008804</x:v>
+        <x:v>23.7471672667689</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>684145</x:v>
+        <x:v>754441</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.9729663840903</x:v>
+        <x:v>23.9243947644239</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1615332</x:v>
+        <x:v>1654574</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.7729472153108</x:v>
+        <x:v>23.7611382312833</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>2299477</x:v>
+        <x:v>2409015</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.313757170664729</x:v>
+        <x:v>0.314292878694794</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-931187</x:v>
+        <x:v>-900133</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.6259927215038</x:v>
+        <x:v>23.6243057608382</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>0</x:v>
+        <x:v>7772</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>0</x:v>
+        <x:v>23.2399997711182</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1137935</x:v>
+        <x:v>1206456</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.3678587327946</x:v>
+        <x:v>24.3173276632822</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>1137935</x:v>
+        <x:v>1214228</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.155268030948067</x:v>
+        <x:v>0.158414627352599</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-1137935</x:v>
+        <x:v>-1198684</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>24.3678587327946</x:v>
+        <x:v>24.324312817316</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>1168424</x:v>
+        <x:v>1190288</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>24.2533595449198</x:v>
+        <x:v>24.240303953001</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2546203</x:v>
+        <x:v>2570397</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>24.0004246171454</x:v>
+        <x:v>23.9943469574921</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>3714627</x:v>
+        <x:v>3760685</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>0.506850408851582</x:v>
+        <x:v>0.49063891860961</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1377779</x:v>
+        <x:v>-1380109</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.7859234235215</x:v>
+        <x:v>23.7822190311686</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>26610017</x:v>
+        <x:v>27623118</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>24.0188512278435</x:v>
+        <x:v>23.998858756906</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>29861161</x:v>
+        <x:v>30933304</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.9787937524682</x:v>
+        <x:v>23.9617927208628</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>56471178</x:v>
+        <x:v>58556422</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>7.70533344468515</x:v>
+        <x:v>7.63958150382922</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-3251144</x:v>
+        <x:v>-3310186</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.650930667747</x:v>
+        <x:v>23.6524809518523</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>5495707</x:v>
+        <x:v>6009036</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>23.9592310389548</x:v>
+        <x:v>23.9164986116993</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>9568121</x:v>
+        <x:v>10539301</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.7492436561418</x:v>
+        <x:v>23.7235261152106</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>15063828</x:v>
+        <x:v>16548337</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>2.05541697205935</x:v>
+        <x:v>2.15898384748188</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-4072414</x:v>
+        <x:v>-4530265</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.4658664922196</x:v>
+        <x:v>23.4675634555405</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>9383367</x:v>
+        <x:v>9666738</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>24.0571851244238</x:v>
+        <x:v>24.0400355712796</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>15134552</x:v>
+        <x:v>15351273</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.9006103723697</x:v>
+        <x:v>23.8953494306095</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>24517919</x:v>
+        <x:v>25018011</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>3.34540110469772</x:v>
+        <x:v>3.2639824560694</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-5751185</x:v>
+        <x:v>-5684535</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.6451502608524</x:v>
+        <x:v>23.6493059083003</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>18783111</x:v>
+        <x:v>19424143</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>24.0742158463454</x:v>
+        <x:v>24.0530989708923</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>32987713</x:v>
+        <x:v>33923643</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.8732216347197</x:v>
+        <x:v>23.8611259449202</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>51770824</x:v>
+        <x:v>53347786</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>7.06398335848614</x:v>
+        <x:v>6.96003521519535</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-14204602</x:v>
+        <x:v>-14499500</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.6074418129885</x:v>
+        <x:v>23.6039507658709</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,166 +40,154 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUPAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -550,7 +538,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I55"/>
+  <x:dimension ref="A1:I51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -587,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>20878176</x:v>
+        <x:v>1676606</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>24.0944807842817</x:v>
+        <x:v>23.8586651539407</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>14422104</x:v>
+        <x:v>1108754</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>24.1631140809629</x:v>
+        <x:v>23.6888421502206</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>35300280</x:v>
+        <x:v>2785360</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>4.60546182565582</x:v>
+        <x:v>7.87671048869732</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>6456072</x:v>
+        <x:v>567852</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.9411620879291</x:v>
+        <x:v>24.1902514381604</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>38650663</x:v>
+        <x:v>1246901</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.9895109713796</x:v>
+        <x:v>23.7370386032282</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>32318217</x:v>
+        <x:v>871825</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>24.0346694053628</x:v>
+        <x:v>23.7553434209343</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>70968880</x:v>
+        <x:v>2118726</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>9.25897663275047</x:v>
+        <x:v>5.99153836734775</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>6332446</x:v>
+        <x:v>375076</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.7590407756841</x:v>
+        <x:v>23.694490965692</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +633,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>19633975</x:v>
+        <x:v>2336360</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>24.0253326888241</x:v>
+        <x:v>23.8138932563692</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>15184978</x:v>
+        <x:v>1970982</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>24.1403988177794</x:v>
+        <x:v>23.7914056488482</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>34818953</x:v>
+        <x:v>4307342</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.54266535140243</x:v>
+        <x:v>12.1807184384807</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>4448997</x:v>
+        <x:v>365378</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.6325977337924</x:v>
+        <x:v>23.9351996011605</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>53388971</x:v>
+        <x:v>724292</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.9702824128092</x:v>
+        <x:v>23.804213713838</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>50179736</x:v>
+        <x:v>469476</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.9641363778417</x:v>
+        <x:v>23.7504747770473</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>103568707</x:v>
+        <x:v>1193768</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.5121230319146</x:v>
+        <x:v>3.37585264621852</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>3209235</x:v>
+        <x:v>254816</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.0663820789649</x:v>
+        <x:v>23.903222963998</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>7934913</x:v>
+        <x:v>313613</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>24.1640661835974</x:v>
+        <x:v>23.8590206280491</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>5877879</x:v>
+        <x:v>103743</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>24.2354125827359</x:v>
+        <x:v>23.8345762108317</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>13812792</x:v>
+        <x:v>417356</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.80209013247839</x:v>
+        <x:v>1.18023967556106</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>2057034</x:v>
+        <x:v>209870</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.9601971657679</x:v>
+        <x:v>23.8711039995428</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>3901477</x:v>
+        <x:v>322787</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.9711851912947</x:v>
+        <x:v>23.7107987698153</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>1947005</x:v>
+        <x:v>220454</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>24.1138219567291</x:v>
+        <x:v>23.7345889723938</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>5848482</x:v>
+        <x:v>543241</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.763023992700205</x:v>
+        <x:v>1.53622945780453</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1954472</x:v>
+        <x:v>102333</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.8290933652237</x:v>
+        <x:v>23.6595479971491</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>20570086</x:v>
+        <x:v>102157</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>24.0710020362119</x:v>
+        <x:v>23.2508188229551</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>19039397</x:v>
+        <x:v>4222</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>24.0850523221661</x:v>
+        <x:v>23.8550732154973</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>39609483</x:v>
+        <x:v>106379</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>5.16766331288203</x:v>
+        <x:v>0.300828828258154</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1530689</x:v>
+        <x:v>97935</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.8962382714989</x:v>
+        <x:v>23.2247692794282</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>11044539</x:v>
+        <x:v>354627</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>24.0447509888449</x:v>
+        <x:v>23.7906210631341</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>9669457</x:v>
+        <x:v>298669</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>24.1401130113124</x:v>
+        <x:v>23.8776163002064</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>20713996</x:v>
+        <x:v>653296</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.70245782284977</x:v>
+        <x:v>1.84745363451188</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>1375082</x:v>
+        <x:v>55958</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.3741735427853</x:v>
+        <x:v>23.3262945957634</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>5816477</x:v>
+        <x:v>949875</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>24.0415894652744</x:v>
+        <x:v>23.8166480374984</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>4566870</x:v>
+        <x:v>900921</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>24.1906443799734</x:v>
+        <x:v>23.8742163307969</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>10383347</x:v>
+        <x:v>1850796</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.35466654176788</x:v>
+        <x:v>5.23385999139754</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>1249607</x:v>
+        <x:v>48954</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.4968466635043</x:v>
+        <x:v>22.7571945839148</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>25136217</x:v>
+        <x:v>279889</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>24.0741494635259</x:v>
+        <x:v>23.8259235922128</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>24184234</x:v>
+        <x:v>240103</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>24.1433490165418</x:v>
+        <x:v>23.8126932005473</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>49320451</x:v>
+        <x:v>519992</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>6.4346077227894</x:v>
+        <x:v>1.47048368628784</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>951983</x:v>
+        <x:v>39786</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.3161998122921</x:v>
+        <x:v>23.9057671736252</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2267286</x:v>
+        <x:v>433634</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.9425036828394</x:v>
+        <x:v>23.7964203711942</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1531594</x:v>
+        <x:v>402568</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>24.0876207570204</x:v>
+        <x:v>23.8372873104078</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>3798880</x:v>
+        <x:v>836202</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.495622040965323</x:v>
+        <x:v>2.36469291727808</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>735692</x:v>
+        <x:v>31066</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.6403929624387</x:v>
+        <x:v>23.2668471404822</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1833561</x:v>
+        <x:v>35954</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.9361427214928</x:v>
+        <x:v>23.8967216816576</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1338697</x:v>
+        <x:v>11675</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>24.1290038662459</x:v>
+        <x:v>23.7429310282803</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>3172258</x:v>
+        <x:v>47629</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.413869610103129</x:v>
+        <x:v>0.134689894256457</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>494864</x:v>
+        <x:v>24279</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.4144182964033</x:v>
+        <x:v>23.9706747224821</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1292252</x:v>
+        <x:v>109641</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>24.0423458401931</x:v>
+        <x:v>23.7814047395878</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>874372</x:v>
+        <x:v>89089</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>24.0990669912188</x:v>
+        <x:v>23.749590893233</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>2166624</x:v>
+        <x:v>198730</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.282669262752299</x:v>
+        <x:v>0.561987920921826</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>417880</x:v>
+        <x:v>20552</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.9236625189894</x:v>
+        <x:v>23.9193116954998</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>15826339</x:v>
+        <x:v>248498</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>24.0861666190902</x:v>
+        <x:v>23.8020312969182</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>15412350</x:v>
+        <x:v>231984</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>24.1082400428832</x:v>
+        <x:v>23.8206507249802</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>31238689</x:v>
+        <x:v>480482</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>4.07556511373378</x:v>
+        <x:v>1.35875348573623</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>413989</x:v>
+        <x:v>16514</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.2643976030138</x:v>
+        <x:v>23.5404708391531</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>647879</x:v>
+        <x:v>65282</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>24.1554312665448</x:v>
+        <x:v>23.6302701526952</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>243128</x:v>
+        <x:v>48943</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>24.2351640144328</x:v>
+        <x:v>23.94209667291</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>891007</x:v>
+        <x:v>114225</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.116245500740847</x:v>
+        <x:v>0.323016506150534</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>404751</x:v>
+        <x:v>16339</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>24.1075369722045</x:v>
+        <x:v>22.6962028671284</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>5229388</x:v>
+        <x:v>47871</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>24.0435393063044</x:v>
+        <x:v>23.7833028311507</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>4883702</x:v>
+        <x:v>32380</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>24.0678002715743</x:v>
+        <x:v>23.9373495993753</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>10113090</x:v>
+        <x:v>80251</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>1.31940737961347</x:v>
+        <x:v>0.226941542001195</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>345686</x:v>
+        <x:v>15491</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.7007909028098</x:v>
+        <x:v>23.4613071978727</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>2349446</x:v>
+        <x:v>242025</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.9855627269492</x:v>
+        <x:v>23.8267603646865</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>2128006</x:v>
+        <x:v>228850</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.9979570301221</x:v>
+        <x:v>23.8804071162938</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>4477452</x:v>
+        <x:v>470875</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.584152144464755</x:v>
+        <x:v>1.33158588166892</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>221440</x:v>
+        <x:v>13175</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.8664552869308</x:v>
+        <x:v>22.894915271303</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>722232</x:v>
+        <x:v>296850</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>24.0931192379807</x:v>
+        <x:v>23.7632705256825</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>502820</x:v>
+        <x:v>285053</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>24.2159607898724</x:v>
+        <x:v>23.8707935663677</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>1225052</x:v>
+        <x:v>581903</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.159826783822772</x:v>
+        <x:v>1.64556160191302</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>219412</x:v>
+        <x:v>11797</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.811606881673</x:v>
+        <x:v>21.1651722535427</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>3595316</x:v>
+        <x:v>35766</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>24.0647649999192</x:v>
+        <x:v>23.7670872051604</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>3403839</x:v>
+        <x:v>26671</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.9457118664324</x:v>
+        <x:v>23.7008047993158</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>6999155</x:v>
+        <x:v>62437</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.913146897541551</x:v>
+        <x:v>0.176565389315132</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>191477</x:v>
+        <x:v>9095</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>26.1811429400093</x:v>
+        <x:v>23.9614597226185</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>848327</x:v>
+        <x:v>6454</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.9762272957027</x:v>
+        <x:v>23.2399997711182</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>687063</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>24.1153885650165</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1535390</x:v>
+        <x:v>6454</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.200315125899672</x:v>
+        <x:v>0.0182512456178205</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>161264</x:v>
+        <x:v>6454</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.3833326683925</x:v>
+        <x:v>23.2399997711182</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1155,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>3938440</x:v>
+        <x:v>7667</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>24.0674170155677</x:v>
+        <x:v>23.6982029123382</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>3838059</x:v>
+        <x:v>4893</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>24.1388617739505</x:v>
+        <x:v>23.735025440577</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>7776499</x:v>
+        <x:v>12560</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.01456332022722</x:v>
+        <x:v>0.0355183831670012</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>100381</x:v>
+        <x:v>2774</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>21.3357327534653</x:v>
+        <x:v>23.6332524326437</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1184,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>4604429</x:v>
+        <x:v>2520</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.8510572382935</x:v>
+        <x:v>23.7360315171499</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>4514029</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.9087516677882</x:v>
+        <x:v>23.5235866086236</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>9118458</x:v>
+        <x:v>3970</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>1.18964241155724</x:v>
+        <x:v>0.0112267500933913</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>90400</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>20.9701465316789</x:v>
+        <x:v>24.0239241501995</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1213,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>216519</x:v>
+        <x:v>1242</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>24.3500573320956</x:v>
+        <x:v>23.8370212840573</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>126952</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.8398125641918</x:v>
+        <x:v>23.5945830543836</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>343471</x:v>
+        <x:v>1722</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0448110490545636</x:v>
+        <x:v>0.00486963820171783</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>89567</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>25.0732767519145</x:v>
+        <x:v>23.9897382791274</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1242,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>181215</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>24.1209715243546</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>114573</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>24.1043202677046</x:v>
+        <x:v>23.8999996185303</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>295788</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0385900718772509</x:v>
+        <x:v>5.65579349793012E-05</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>66642</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>24.1495988828996</x:v>
+        <x:v>23.8999996185303</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1271,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>79286</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>24.3248903665552</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>21000</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>24.3123811086019</x:v>
+        <x:v>23.4380483627319</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>100286</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0130838436592492</x:v>
+        <x:v>0.00115943766707567</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>58286</x:v>
+        <x:v>-410</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>24.3293973565188</x:v>
+        <x:v>23.4380483627319</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1300,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1158792</x:v>
+        <x:v>26811</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.7296291564529</x:v>
+        <x:v>23.5956143029236</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1101513</x:v>
+        <x:v>28078</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>24.2706692766137</x:v>
+        <x:v>23.878234839098</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>2260305</x:v>
+        <x:v>54889</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.294891383066621</x:v>
+        <x:v>0.155220424653943</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>57279</x:v>
+        <x:v>-1267</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>13.3250703150156</x:v>
+        <x:v>29.8587709049023</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>8287187</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.9724947415293</x:v>
+        <x:v>23.449431116988</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>8246251</x:v>
+        <x:v>1533</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>24.0211453009486</x:v>
+        <x:v>23.7596346898088</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>16533438</x:v>
+        <x:v>1656</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>2.1570400448905</x:v>
+        <x:v>0.00468299701628614</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>40936</x:v>
+        <x:v>-1410</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>14.1722034511562</x:v>
+        <x:v>23.7866950014804</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>50826</x:v>
+        <x:v>32954</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>24.4822585197424</x:v>
+        <x:v>23.2911620540889</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>17295</x:v>
+        <x:v>34385</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>24.0759152797579</x:v>
+        <x:v>23.9712078523268</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>68121</x:v>
+        <x:v>67339</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00888742709761792</x:v>
+        <x:v>0.190427739178558</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>33531</x:v>
+        <x:v>-1431</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.691846851004</x:v>
+        <x:v>39.6317454030845</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>3865608</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.7040759349266</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>3842590</x:v>
+        <x:v>2495</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.755989602133</x:v>
+        <x:v>23.887774855436</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>7708198</x:v>
+        <x:v>2495</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>1.00565240937456</x:v>
+        <x:v>0.00705560238866782</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>23018</x:v>
+        <x:v>-2495</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>15.0376870883455</x:v>
+        <x:v>23.887774855436</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1416,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>255435</x:v>
+        <x:v>41341</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>24.0194746936614</x:v>
+        <x:v>23.7891729397351</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>234271</x:v>
+        <x:v>44992</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>24.0133308515818</x:v>
+        <x:v>23.7649012589946</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>489706</x:v>
+        <x:v>86333</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0638896430508372</x:v>
+        <x:v>0.244140810028401</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>21164</x:v>
+        <x:v>-3651</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>24.0874828219842</x:v>
+        <x:v>23.4900681849082</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1445,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>16330433</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.9554558879869</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>16313859</x:v>
+        <x:v>6350</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.952712844254</x:v>
+        <x:v>23.8128127090574</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>32644292</x:v>
+        <x:v>6350</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>4.25894753898727</x:v>
+        <x:v>0.0179571443559281</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>16574</x:v>
+        <x:v>-6350</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>26.6554455519499</x:v>
+        <x:v>23.8128127090574</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>3014065</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.9331827244839</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>2997624</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.9324932358592</x:v>
+        <x:v>23.2753844627967</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>6011689</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.784316843866819</x:v>
+        <x:v>0.0183813288682729</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>16441</x:v>
+        <x:v>-6500</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>24.0588945211644</x:v>
+        <x:v>23.2753844627967</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>128215</x:v>
+        <x:v>143647</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>24.1380164704243</x:v>
+        <x:v>23.8059138296355</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>113240</x:v>
+        <x:v>151258</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>24.0711062637499</x:v>
+        <x:v>23.7945710525192</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>241455</x:v>
+        <x:v>294905</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0315015004162496</x:v>
+        <x:v>0.833960890753541</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>14975</x:v>
+        <x:v>-7611</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>24.643987208575</x:v>
+        <x:v>23.5804919690313</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>241528</x:v>
+        <x:v>78416</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>24.0385053325697</x:v>
+        <x:v>23.7856689973696</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>230597</x:v>
+        <x:v>86090</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.7826122893832</x:v>
+        <x:v>23.6918781016427</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>472125</x:v>
+        <x:v>164506</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0615959325092536</x:v>
+        <x:v>0.465205982585246</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>10931</x:v>
+        <x:v>-7674</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>29.4367459399867</x:v>
+        <x:v>22.7334852323018</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>29318</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.8049768200919</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>19470</x:v>
+        <x:v>7772</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>24.1447667662156</x:v>
+        <x:v>23.2399997711182</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>48788</x:v>
+        <x:v>7772</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00636514134024138</x:v>
+        <x:v>0.0219784135329564</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>9848</x:v>
+        <x:v>-7772</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.133194706868</x:v>
+        <x:v>23.2399997711182</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>1860684</x:v>
+        <x:v>281351</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.848292344678</x:v>
+        <x:v>23.6768840267033</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>1855153</x:v>
+        <x:v>296620</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>24.008838524296</x:v>
+        <x:v>23.7519607836008</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>3715837</x:v>
+        <x:v>577971</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.484787810574291</x:v>
+        <x:v>1.63444231189608</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>5531</x:v>
+        <x:v>-15269</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>-30.0005101786882</x:v>
+        <x:v>25.1353467702319</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1619,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>8087</x:v>
+        <x:v>85447</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>24.5245555796552</x:v>
+        <x:v>23.5736760814449</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>5000</x:v>
+        <x:v>101024</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>24.5500005722046</x:v>
+        <x:v>23.8680466340054</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>13087</x:v>
+        <x:v>186471</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.00170739945723823</x:v>
+        <x:v>0.527320734676264</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>3087</x:v>
+        <x:v>-15577</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>24.4833424397954</x:v>
+        <x:v>25.482804328339</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>142249</x:v>
+        <x:v>565034</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>24.0983838003718</x:v>
+        <x:v>23.7899374406747</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>139173</x:v>
+        <x:v>581084</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>24.1447289027144</x:v>
+        <x:v>23.695035640805</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>281422</x:v>
+        <x:v>1146118</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.0367158072938717</x:v>
+        <x:v>3.24110336613034</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>3076</x:v>
+        <x:v>-16050</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>22.0015089862213</x:v>
+        <x:v>20.3540547319216</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>3840</x:v>
+        <x:v>46411</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>24.0377086500327</x:v>
+        <x:v>23.8226046002763</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>1881</x:v>
+        <x:v>74896</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>24.4618182975773</x:v>
+        <x:v>23.8493020310664</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>5721</x:v>
+        <x:v>121307</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.000746392014583934</x:v>
+        <x:v>0.343043670926705</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>1959</x:v>
+        <x:v>-28485</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.6304854509355</x:v>
+        <x:v>23.8928005201096</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>12916</x:v>
+        <x:v>36837</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.6687362419263</x:v>
+        <x:v>23.7885530788528</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>11988</x:v>
+        <x:v>67439</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>24.0186122198044</x:v>
+        <x:v>23.8575923589733</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>24904</x:v>
+        <x:v>104276</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0032491079760878</x:v>
+        <x:v>0.294881761395081</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>928</x:v>
+        <x:v>-30602</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>19.1490021656299</x:v>
+        <x:v>23.9406980370924</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>775</x:v>
+        <x:v>89529</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.2999992370605</x:v>
+        <x:v>23.8804623101541</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>1</x:v>
+        <x:v>121347</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>24.1399993896484</x:v>
+        <x:v>23.7407396589505</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>776</x:v>
+        <x:v>210876</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.000101241077314653</x:v>
+        <x:v>0.596335554834756</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>774</x:v>
+        <x:v>-31818</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>23.2989139655456</x:v>
+        <x:v>23.3475902077089</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1764,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>12967483</x:v>
+        <x:v>51025</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>24.0667133978291</x:v>
+        <x:v>23.8671516762733</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>13124822</x:v>
+        <x:v>97016</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>24.0721818828317</x:v>
+        <x:v>23.7229067043626</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>26092305</x:v>
+        <x:v>148041</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>3.40414055131768</x:v>
+        <x:v>0.418644662613536</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-157339</x:v>
+        <x:v>-45991</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>24.5228806053806</x:v>
+        <x:v>23.5628732262529</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1793,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>100</x:v>
+        <x:v>23037</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.6800003051758</x:v>
+        <x:v>23.8059732075568</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>200001</x:v>
+        <x:v>82075</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>25.5</x:v>
+        <x:v>23.8856005153371</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>200101</x:v>
+        <x:v>105112</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.0261062381594581</x:v>
+        <x:v>0.297245883077215</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-199901</x:v>
+        <x:v>-59038</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>25.5009104505204</x:v>
+        <x:v>23.9166715931063</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>4495121</x:v>
+        <x:v>1279023</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.973422642649</x:v>
+        <x:v>23.7672337496755</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>4696337</x:v>
+        <x:v>1379328</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>24.1556853774643</x:v>
+        <x:v>23.8232790189017</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>9191458</x:v>
+        <x:v>2658351</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.19916637888195</x:v>
+        <x:v>7.51754215050802</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-201216</x:v>
+        <x:v>-100305</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>28.227394619203</x:v>
+        <x:v>24.5379312135234</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>6064384</x:v>
+        <x:v>480087</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>24.1051803684461</x:v>
+        <x:v>23.7914640899704</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>6523552</x:v>
+        <x:v>612382</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>24.0935432341155</x:v>
+        <x:v>23.7951806274662</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>12587936</x:v>
+        <x:v>1092469</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.64228891985555</x:v>
+        <x:v>3.08938953344511</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-459168</x:v>
+        <x:v>-132295</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.9398477430526</x:v>
+        <x:v>23.8086676174265</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1910370</x:v>
+        <x:v>1012220</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>24.1574914440899</x:v>
+        <x:v>23.8490878613912</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2485751</x:v>
+        <x:v>1175048</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>24.5306646350452</x:v>
+        <x:v>23.826922283764</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>4396121</x:v>
+        <x:v>2187268</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.573541270677283</x:v>
+        <x:v>6.18536806631531</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-575381</x:v>
+        <x:v>-162828</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.7696677804484</x:v>
+        <x:v>23.6891300061107</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>7153289</x:v>
+        <x:v>2537068</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.9815545026129</x:v>
+        <x:v>23.8443949266909</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>7894272</x:v>
+        <x:v>2805640</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.9595541259883</x:v>
+        <x:v>23.8522408404812</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>15047561</x:v>
+        <x:v>5342708</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.96318464767779</x:v>
+        <x:v>15.1086265838696</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-740983</x:v>
+        <x:v>-268572</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.7471672667689</x:v>
+        <x:v>23.9263573411149</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1938,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>754441</x:v>
+        <x:v>95553</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.9243947644239</x:v>
+        <x:v>23.7712589551277</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1654574</x:v>
+        <x:v>452207</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.7611382312833</x:v>
+        <x:v>23.6793759309501</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>2409015</x:v>
+        <x:v>547760</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.314292878694794</x:v>
+        <x:v>1.5490087232131</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-900133</x:v>
+        <x:v>-356654</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.6243057608382</x:v>
+        <x:v>23.6547590792976</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1967,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>7772</x:v>
+        <x:v>141410</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.2399997711182</x:v>
+        <x:v>23.7969962121203</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1206456</x:v>
+        <x:v>530456</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>24.3173276632822</x:v>
+        <x:v>23.8060405697136</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>1214228</x:v>
+        <x:v>671866</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.158414627352599</x:v>
+        <x:v>1.89996767714016</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-1198684</x:v>
+        <x:v>-389046</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>24.324312817316</x:v>
+        <x:v>23.8093280025808</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,144 +1996,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>1190288</x:v>
+        <x:v>793400</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>24.240303953001</x:v>
+        <x:v>23.899108503345</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2570397</x:v>
+        <x:v>1381105</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.9943469574921</x:v>
+        <x:v>23.8652947293453</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>3760685</x:v>
+        <x:v>2174505</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>0.49063891860961</x:v>
+        <x:v>6.14927562010827</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1380109</x:v>
+        <x:v>-587705</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.7822190311686</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:9">
-      <x:c r="A52" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B52" s="0">
-        <x:v>27623118</x:v>
-      </x:c>
-      <x:c r="C52" s="0">
-        <x:v>23.998858756906</x:v>
-      </x:c>
-      <x:c r="D52" s="0">
-        <x:v>30933304</x:v>
-      </x:c>
-      <x:c r="E52" s="0">
-        <x:v>23.9617927208628</x:v>
-      </x:c>
-      <x:c r="F52" s="0">
-        <x:v>58556422</x:v>
-      </x:c>
-      <x:c r="G52" s="0">
-        <x:v>7.63958150382922</x:v>
-      </x:c>
-      <x:c r="H52" s="0">
-        <x:v>-3310186</x:v>
-      </x:c>
-      <x:c r="I52" s="0">
-        <x:v>23.6524809518523</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:9">
-      <x:c r="A53" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B53" s="0">
-        <x:v>6009036</x:v>
-      </x:c>
-      <x:c r="C53" s="0">
-        <x:v>23.9164986116993</x:v>
-      </x:c>
-      <x:c r="D53" s="0">
-        <x:v>10539301</x:v>
-      </x:c>
-      <x:c r="E53" s="0">
-        <x:v>23.7235261152106</x:v>
-      </x:c>
-      <x:c r="F53" s="0">
-        <x:v>16548337</x:v>
-      </x:c>
-      <x:c r="G53" s="0">
-        <x:v>2.15898384748188</x:v>
-      </x:c>
-      <x:c r="H53" s="0">
-        <x:v>-4530265</x:v>
-      </x:c>
-      <x:c r="I53" s="0">
-        <x:v>23.4675634555405</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:9">
-      <x:c r="A54" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B54" s="0">
-        <x:v>9666738</x:v>
-      </x:c>
-      <x:c r="C54" s="0">
-        <x:v>24.0400355712796</x:v>
-      </x:c>
-      <x:c r="D54" s="0">
-        <x:v>15351273</x:v>
-      </x:c>
-      <x:c r="E54" s="0">
-        <x:v>23.8953494306095</x:v>
-      </x:c>
-      <x:c r="F54" s="0">
-        <x:v>25018011</x:v>
-      </x:c>
-      <x:c r="G54" s="0">
-        <x:v>3.2639824560694</x:v>
-      </x:c>
-      <x:c r="H54" s="0">
-        <x:v>-5684535</x:v>
-      </x:c>
-      <x:c r="I54" s="0">
-        <x:v>23.6493059083003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:9">
-      <x:c r="A55" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B55" s="0">
-        <x:v>19424143</x:v>
-      </x:c>
-      <x:c r="C55" s="0">
-        <x:v>24.0530989708923</x:v>
-      </x:c>
-      <x:c r="D55" s="0">
-        <x:v>33923643</x:v>
-      </x:c>
-      <x:c r="E55" s="0">
-        <x:v>23.8611259449202</x:v>
-      </x:c>
-      <x:c r="F55" s="0">
-        <x:v>53347786</x:v>
-      </x:c>
-      <x:c r="G55" s="0">
-        <x:v>6.96003521519535</x:v>
-      </x:c>
-      <x:c r="H55" s="0">
-        <x:v>-14499500</x:v>
-      </x:c>
-      <x:c r="I55" s="0">
-        <x:v>23.6039507658709</x:v>
+        <x:v>23.8196462351324</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,154 +40,154 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
-    <x:t>AK</x:t>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -575,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1676606</x:v>
+        <x:v>4673629</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.8586651539407</x:v>
+        <x:v>23.676</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>1108754</x:v>
+        <x:v>3990224</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.6888421502206</x:v>
+        <x:v>23.652</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2785360</x:v>
+        <x:v>8663853</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>7.87671048869732</x:v>
+        <x:v>10.6956193831614</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>567852</x:v>
+        <x:v>683405</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>24.1902514381604</x:v>
+        <x:v>23.819</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1246901</x:v>
+        <x:v>3120099</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.7370386032282</x:v>
+        <x:v>23.692</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>871825</x:v>
+        <x:v>2443114</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.7553434209343</x:v>
+        <x:v>23.588</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>2118726</x:v>
+        <x:v>5563213</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>5.99153836734775</x:v>
+        <x:v>6.86784607211775</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>375076</x:v>
+        <x:v>676985</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.694490965692</x:v>
+        <x:v>24.07</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,28 +633,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2336360</x:v>
+        <x:v>4633294</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.8138932563692</x:v>
+        <x:v>23.587</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1970982</x:v>
+        <x:v>4020490</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.7914056488482</x:v>
+        <x:v>23.617</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>4307342</x:v>
+        <x:v>8653784</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>12.1807184384807</x:v>
+        <x:v>10.6831890947471</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>365378</x:v>
+        <x:v>612804</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.9351996011605</x:v>
+        <x:v>23.391</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>724292</x:v>
+        <x:v>1056630</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.804213713838</x:v>
+        <x:v>23.688</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>469476</x:v>
+        <x:v>474708</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.7504747770473</x:v>
+        <x:v>23.741</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1193768</x:v>
+        <x:v>1531338</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>3.37585264621852</x:v>
+        <x:v>1.89045317308265</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>254816</x:v>
+        <x:v>581922</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.903222963998</x:v>
+        <x:v>23.645</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>313613</x:v>
+        <x:v>782100</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.8590206280491</x:v>
+        <x:v>23.622</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>103743</x:v>
+        <x:v>573473</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.8345762108317</x:v>
+        <x:v>23.705</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>417356</x:v>
+        <x:v>1355573</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.18023967556106</x:v>
+        <x:v>1.67346939682498</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>209870</x:v>
+        <x:v>208627</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.8711039995428</x:v>
+        <x:v>23.395</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>322787</x:v>
+        <x:v>806217</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.7107987698153</x:v>
+        <x:v>23.653</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>220454</x:v>
+        <x:v>657923</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.7345889723938</x:v>
+        <x:v>23.735</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>543241</x:v>
+        <x:v>1464140</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.53622945780453</x:v>
+        <x:v>1.8074965218895</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>102333</x:v>
+        <x:v>148294</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.6595479971491</x:v>
+        <x:v>23.291</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>102157</x:v>
+        <x:v>112277</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.2508188229551</x:v>
+        <x:v>23.272</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>4222</x:v>
+        <x:v>5224</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.8550732154973</x:v>
+        <x:v>23.796</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>106379</x:v>
+        <x:v>117501</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.300828828258154</x:v>
+        <x:v>0.145056243814484</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>97935</x:v>
+        <x:v>107053</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.2247692794282</x:v>
+        <x:v>23.247</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>354627</x:v>
+        <x:v>549275</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.7906210631341</x:v>
+        <x:v>23.695</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>298669</x:v>
+        <x:v>454981</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.8776163002064</x:v>
+        <x:v>23.565</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>653296</x:v>
+        <x:v>1004256</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.84745363451188</x:v>
+        <x:v>1.23976479509245</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>55958</x:v>
+        <x:v>94294</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.3262945957634</x:v>
+        <x:v>24.322</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>949875</x:v>
+        <x:v>667724</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.8166480374984</x:v>
+        <x:v>23.588</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>900921</x:v>
+        <x:v>586967</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.8742163307969</x:v>
+        <x:v>23.676</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1850796</x:v>
+        <x:v>1254691</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>5.23385999139754</x:v>
+        <x:v>1.54892948662427</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>48954</x:v>
+        <x:v>80757</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.7571945839148</x:v>
+        <x:v>22.951</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>279889</x:v>
+        <x:v>1812761</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.8259235922128</x:v>
+        <x:v>23.665</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>240103</x:v>
+        <x:v>1732846</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.8126932005473</x:v>
+        <x:v>23.693</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>519992</x:v>
+        <x:v>3545607</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.47048368628784</x:v>
+        <x:v>4.37708984146808</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>39786</x:v>
+        <x:v>79915</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.9057671736252</x:v>
+        <x:v>23.064</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>433634</x:v>
+        <x:v>1192162</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.7964203711942</x:v>
+        <x:v>23.682</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>402568</x:v>
+        <x:v>1115063</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.8372873104078</x:v>
+        <x:v>23.622</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>836202</x:v>
+        <x:v>2307225</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.36469291727808</x:v>
+        <x:v>2.84829399013517</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>31066</x:v>
+        <x:v>77099</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.2668471404822</x:v>
+        <x:v>24.555</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>35954</x:v>
+        <x:v>1169936</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.8967216816576</x:v>
+        <x:v>23.577</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>11675</x:v>
+        <x:v>1096900</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.7429310282803</x:v>
+        <x:v>23.593</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>47629</x:v>
+        <x:v>2266836</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.134689894256457</x:v>
+        <x:v>2.79843333676692</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>24279</x:v>
+        <x:v>73036</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.9706747224821</x:v>
+        <x:v>23.337</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>109641</x:v>
+        <x:v>456818</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.7814047395878</x:v>
+        <x:v>23.684</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>89089</x:v>
+        <x:v>405282</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.749590893233</x:v>
+        <x:v>23.677</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>198730</x:v>
+        <x:v>862100</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.561987920921826</x:v>
+        <x:v>1.06427168953853</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>20552</x:v>
+        <x:v>51536</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.9193116954998</x:v>
+        <x:v>23.739</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>248498</x:v>
+        <x:v>203677</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.8020312969182</x:v>
+        <x:v>23.616</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>231984</x:v>
+        <x:v>156309</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.8206507249802</x:v>
+        <x:v>23.62</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>480482</x:v>
+        <x:v>359986</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>1.35875348573623</x:v>
+        <x:v>0.444406575142346</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>16514</x:v>
+        <x:v>47368</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.5404708391531</x:v>
+        <x:v>23.602</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>65282</x:v>
+        <x:v>89236</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.6302701526952</x:v>
+        <x:v>23.538</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>48943</x:v>
+        <x:v>42735</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.94209667291</x:v>
+        <x:v>23.639</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>114225</x:v>
+        <x:v>131971</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.323016506150534</x:v>
+        <x:v>0.162919613896403</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>16339</x:v>
+        <x:v>46501</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>22.6962028671284</x:v>
+        <x:v>23.445</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>47871</x:v>
+        <x:v>117724</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.7833028311507</x:v>
+        <x:v>23.571</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>32380</x:v>
+        <x:v>71780</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.9373495993753</x:v>
+        <x:v>23.912</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>80251</x:v>
+        <x:v>189504</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.226941542001195</x:v>
+        <x:v>0.233944719005115</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>15491</x:v>
+        <x:v>45944</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.4613071978727</x:v>
+        <x:v>23.038</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>242025</x:v>
+        <x:v>164606</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.8267603646865</x:v>
+        <x:v>23.668</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>228850</x:v>
+        <x:v>119859</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.8804071162938</x:v>
+        <x:v>23.668</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>470875</x:v>
+        <x:v>284465</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.33158588166892</x:v>
+        <x:v>0.351175091247625</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>13175</x:v>
+        <x:v>44747</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.894915271303</x:v>
+        <x:v>23.669</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>296850</x:v>
+        <x:v>141771</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.7632705256825</x:v>
+        <x:v>23.646</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>285053</x:v>
+        <x:v>111281</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.8707935663677</x:v>
+        <x:v>23.604</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>581903</x:v>
+        <x:v>253052</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.64556160191302</x:v>
+        <x:v>0.312395406079462</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>11797</x:v>
+        <x:v>30490</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>21.1651722535427</x:v>
+        <x:v>23.8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>35766</x:v>
+        <x:v>205066</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.7670872051604</x:v>
+        <x:v>23.736</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>26671</x:v>
+        <x:v>175842</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.7008047993158</x:v>
+        <x:v>23.767</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>62437</x:v>
+        <x:v>380908</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.176565389315132</x:v>
+        <x:v>0.470235008373439</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>9095</x:v>
+        <x:v>29224</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.9614597226185</x:v>
+        <x:v>23.554</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>6454</x:v>
+        <x:v>550378</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.2399997711182</x:v>
+        <x:v>23.609</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>0</x:v>
+        <x:v>531318</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>0</x:v>
+        <x:v>23.619</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>6454</x:v>
+        <x:v>1081696</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0182512456178205</x:v>
+        <x:v>1.33536530505402</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>6454</x:v>
+        <x:v>19060</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.2399997711182</x:v>
+        <x:v>23.336</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1155,28 +1155,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>7667</x:v>
+        <x:v>471295</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.6982029123382</x:v>
+        <x:v>23.66</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>4893</x:v>
+        <x:v>453929</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.735025440577</x:v>
+        <x:v>23.685</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>12560</x:v>
+        <x:v>925224</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0355183831670012</x:v>
+        <x:v>1.14219894406866</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>2774</x:v>
+        <x:v>17366</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.6332524326437</x:v>
+        <x:v>23.005</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1184,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>2520</x:v>
+        <x:v>112091</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.7360315171499</x:v>
+        <x:v>23.614</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1450</x:v>
+        <x:v>99590</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.5235866086236</x:v>
+        <x:v>23.773</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>3970</x:v>
+        <x:v>211681</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0112267500933913</x:v>
+        <x:v>0.261322463186644</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>1070</x:v>
+        <x:v>12501</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>24.0239241501995</x:v>
+        <x:v>22.342</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,28 +1213,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>1242</x:v>
+        <x:v>520365</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.8370212840573</x:v>
+        <x:v>23.491</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>480</x:v>
+        <x:v>513802</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.5945830543836</x:v>
+        <x:v>23.536</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1722</x:v>
+        <x:v>1034167</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.00486963820171783</x:v>
+        <x:v>1.27669024516296</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>762</x:v>
+        <x:v>6563</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.9897382791274</x:v>
+        <x:v>20.016</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,28 +1242,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>0</x:v>
+        <x:v>6454</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>0</x:v>
+        <x:v>23.24</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>20</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.8999996185303</x:v>
+        <x:v>23.36</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>20</x:v>
+        <x:v>7908</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>5.65579349793012E-05</x:v>
+        <x:v>0.00976251075382286</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-20</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.8999996185303</x:v>
+        <x:v>23.205</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1271,28 +1271,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>0</x:v>
+        <x:v>9742</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0</x:v>
+        <x:v>23.568</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>410</x:v>
+        <x:v>6525</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.4380483627319</x:v>
+        <x:v>23.618</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>410</x:v>
+        <x:v>16267</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00115943766707567</x:v>
+        <x:v>0.0200817858412287</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-410</x:v>
+        <x:v>3217</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.4380483627319</x:v>
+        <x:v>23.466</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,28 +1300,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>26811</x:v>
+        <x:v>6760</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.5956143029236</x:v>
+        <x:v>23.326</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>28078</x:v>
+        <x:v>4314</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.878234839098</x:v>
+        <x:v>23.614</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>54889</x:v>
+        <x:v>11074</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.155220424653943</x:v>
+        <x:v>0.0136709716853609</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1267</x:v>
+        <x:v>2446</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>29.8587709049023</x:v>
+        <x:v>22.817</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>123</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.449431116988</x:v>
+        <x:v>23.731</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1533</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.7596346898088</x:v>
+        <x:v>23.524</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1656</x:v>
+        <x:v>4050</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00468299701628614</x:v>
+        <x:v>0.0049997684057894</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1410</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.7866950014804</x:v>
+        <x:v>24.026</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>32954</x:v>
+        <x:v>64510</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.2911620540889</x:v>
+        <x:v>23.485</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>34385</x:v>
+        <x:v>63548</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.9712078523268</x:v>
+        <x:v>23.534</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>67339</x:v>
+        <x:v>128058</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.190427739178558</x:v>
+        <x:v>0.158088973458908</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1431</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>39.6317454030845</x:v>
+        <x:v>20.284</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>0</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>0</x:v>
+        <x:v>23.267</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>2495</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.887774855436</x:v>
+        <x:v>23.448</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>2495</x:v>
+        <x:v>1795</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00705560238866782</x:v>
+        <x:v>0.00221594673787456</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-2495</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>23.887774855436</x:v>
+        <x:v>23.164</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1416,28 +1416,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>41341</x:v>
+        <x:v>66660</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.7891729397351</x:v>
+        <x:v>23.344</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>44992</x:v>
+        <x:v>67692</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.7649012589946</x:v>
+        <x:v>23.698</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>86333</x:v>
+        <x:v>134352</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.244140810028401</x:v>
+        <x:v>0.16585898391472</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-3651</x:v>
+        <x:v>-1032</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>23.4900681849082</x:v>
+        <x:v>46.571</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1445,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0</x:v>
+        <x:v>23.34</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>6350</x:v>
+        <x:v>10451</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.8128127090574</x:v>
+        <x:v>23.724</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>6350</x:v>
+        <x:v>16451</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0179571443559281</x:v>
+        <x:v>0.0203089358132448</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-6350</x:v>
+        <x:v>-4451</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.8128127090574</x:v>
+        <x:v>24.242</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>0</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0</x:v>
+        <x:v>23.415</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>6500</x:v>
+        <x:v>7772</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.2753844627967</x:v>
+        <x:v>23.24</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>6500</x:v>
+        <x:v>10458</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0183813288682729</x:v>
+        <x:v>0.012910513083394</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-6500</x:v>
+        <x:v>-5086</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.2753844627967</x:v>
+        <x:v>23.147</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>143647</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.8059138296355</x:v>
+        <x:v>23.395</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>151258</x:v>
+        <x:v>5861</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.7945710525192</x:v>
+        <x:v>23.731</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>294905</x:v>
+        <x:v>6084</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.833960890753541</x:v>
+        <x:v>0.00751076320514141</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-7611</x:v>
+        <x:v>-5638</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.5804919690313</x:v>
+        <x:v>23.744</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>78416</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.7856689973696</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>86090</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.6918781016427</x:v>
+        <x:v>23.275</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>164506</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.465205982585246</x:v>
+        <x:v>0.00802431966361262</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-7674</x:v>
+        <x:v>-6500</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>22.7334852323018</x:v>
+        <x:v>23.275</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>0</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0</x:v>
+        <x:v>23.357</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>7772</x:v>
+        <x:v>9868</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.2399997711182</x:v>
+        <x:v>23.626</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>7772</x:v>
+        <x:v>10358</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0219784135329564</x:v>
+        <x:v>0.0127870620116461</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-7772</x:v>
+        <x:v>-9378</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.2399997711182</x:v>
+        <x:v>23.64</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>281351</x:v>
+        <x:v>71905</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.6768840267033</x:v>
+        <x:v>23.511</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>296620</x:v>
+        <x:v>86621</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.7519607836008</x:v>
+        <x:v>23.616</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>577971</x:v>
+        <x:v>158526</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.63444231189608</x:v>
+        <x:v>0.195702045999054</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-15269</x:v>
+        <x:v>-14716</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>25.1353467702319</x:v>
+        <x:v>24.126</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,28 +1619,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>85447</x:v>
+        <x:v>107174</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.5736760814449</x:v>
+        <x:v>23.569</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>101024</x:v>
+        <x:v>131559</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.8680466340054</x:v>
+        <x:v>23.742</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>186471</x:v>
+        <x:v>238733</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.527320734676264</x:v>
+        <x:v>0.294718447115882</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-15577</x:v>
+        <x:v>-24385</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>25.482804328339</x:v>
+        <x:v>24.501</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>565034</x:v>
+        <x:v>97068</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.7899374406747</x:v>
+        <x:v>23.729</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>581084</x:v>
+        <x:v>126191</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.695035640805</x:v>
+        <x:v>23.662</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>1146118</x:v>
+        <x:v>223259</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>3.24110336613034</x:v>
+        <x:v>0.275615628273614</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-16050</x:v>
+        <x:v>-29123</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>20.3540547319216</x:v>
+        <x:v>23.437</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>46411</x:v>
+        <x:v>117793</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.8226046002763</x:v>
+        <x:v>23.5</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>74896</x:v>
+        <x:v>146939</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.8493020310664</x:v>
+        <x:v>23.561</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>121307</x:v>
+        <x:v>264732</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.343043670926705</x:v>
+        <x:v>0.326814491259615</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-28485</x:v>
+        <x:v>-29146</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.8928005201096</x:v>
+        <x:v>23.805</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>36837</x:v>
+        <x:v>165855</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.7885530788528</x:v>
+        <x:v>23.52</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>67439</x:v>
+        <x:v>197822</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.8575923589733</x:v>
+        <x:v>23.731</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>104276</x:v>
+        <x:v>363677</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.294881761395081</x:v>
+        <x:v>0.448963154200561</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-30602</x:v>
+        <x:v>-31967</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>23.9406980370924</x:v>
+        <x:v>24.825</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>89529</x:v>
+        <x:v>66368</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.8804623101541</x:v>
+        <x:v>23.678</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>121347</x:v>
+        <x:v>107463</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.7407396589505</x:v>
+        <x:v>23.734</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>210876</x:v>
+        <x:v>173831</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.596335554834756</x:v>
+        <x:v>0.214596232530068</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-31818</x:v>
+        <x:v>-41095</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>23.3475902077089</x:v>
+        <x:v>23.824</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,28 +1764,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>51025</x:v>
+        <x:v>2014071</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.8671516762733</x:v>
+        <x:v>23.65</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>97016</x:v>
+        <x:v>2055433</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.7229067043626</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>148041</x:v>
+        <x:v>4069504</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.418644662613536</x:v>
+        <x:v>5.02384630282311</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-45991</x:v>
+        <x:v>-41362</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>23.5628732262529</x:v>
+        <x:v>21.181</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,28 +1793,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>23037</x:v>
+        <x:v>1171430</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.8059732075568</x:v>
+        <x:v>23.602</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>82075</x:v>
+        <x:v>1235405</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.8856005153371</x:v>
+        <x:v>23.663</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>105112</x:v>
+        <x:v>2406835</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.297245883077215</x:v>
+        <x:v>2.97126360270324</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-59038</x:v>
+        <x:v>-63975</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>23.9166715931063</x:v>
+        <x:v>24.775</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>1279023</x:v>
+        <x:v>84149</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.7672337496755</x:v>
+        <x:v>23.519</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>1379328</x:v>
+        <x:v>182547</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>23.8232790189017</x:v>
+        <x:v>23.675</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>2658351</x:v>
+        <x:v>266696</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>7.51754215050802</x:v>
+        <x:v>0.329239070308743</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-100305</x:v>
+        <x:v>-98398</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>24.5379312135234</x:v>
+        <x:v>23.809</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>480087</x:v>
+        <x:v>6738275</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.7914640899704</x:v>
+        <x:v>23.624</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>612382</x:v>
+        <x:v>6952066</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.7951806274662</x:v>
+        <x:v>23.638</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>1092469</x:v>
+        <x:v>13690341</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>3.08938953344511</x:v>
+        <x:v>16.9008726904403</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-132295</x:v>
+        <x:v>-213791</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.8086676174265</x:v>
+        <x:v>24.096</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1012220</x:v>
+        <x:v>1246391</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.8490878613912</x:v>
+        <x:v>23.632</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1175048</x:v>
+        <x:v>1469800</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.826922283764</x:v>
+        <x:v>23.593</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>2187268</x:v>
+        <x:v>2716191</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>6.18536806631531</x:v>
+        <x:v>3.35316690021963</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-162828</x:v>
+        <x:v>-223409</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.6891300061107</x:v>
+        <x:v>23.372</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>2537068</x:v>
+        <x:v>2304701</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.8443949266909</x:v>
+        <x:v>23.652</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>2805640</x:v>
+        <x:v>2579040</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.8522408404812</x:v>
+        <x:v>23.656</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>5342708</x:v>
+        <x:v>4883741</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>15.1086265838696</x:v>
+        <x:v>6.02903060589095</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-268572</x:v>
+        <x:v>-274339</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.9263573411149</x:v>
+        <x:v>23.69</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,28 +1938,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>95553</x:v>
+        <x:v>2049300</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.7712589551277</x:v>
+        <x:v>23.669</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>452207</x:v>
+        <x:v>2532952</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.6793759309501</x:v>
+        <x:v>23.724</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>547760</x:v>
+        <x:v>4582252</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.5490087232131</x:v>
+        <x:v>5.65683920418896</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-356654</x:v>
+        <x:v>-483652</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.6547590792976</x:v>
+        <x:v>23.956</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,28 +1967,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>141410</x:v>
+        <x:v>184503</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.7969962121203</x:v>
+        <x:v>23.723</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>530456</x:v>
+        <x:v>727835</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>23.8060405697136</x:v>
+        <x:v>23.741</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>671866</x:v>
+        <x:v>912338</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.89996767714016</x:v>
+        <x:v>1.12629103896323</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-389046</x:v>
+        <x:v>-543332</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.8093280025808</x:v>
+        <x:v>23.747</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1996,28 +1996,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>793400</x:v>
+        <x:v>306367</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.899108503345</x:v>
+        <x:v>23.559</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>1381105</x:v>
+        <x:v>1950603</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.8652947293453</x:v>
+        <x:v>23.469</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2174505</x:v>
+        <x:v>2256970</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.14927562010827</x:v>
+        <x:v>2.78625365402827</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-587705</x:v>
+        <x:v>-1644236</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.8196462351324</x:v>
+        <x:v>23.452</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,151 +40,151 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
   </x:si>
   <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
+    <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
+    <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
+    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
@@ -575,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>4673629</x:v>
+        <x:v>6404199</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.676</x:v>
+        <x:v>23.626</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>3990224</x:v>
+        <x:v>5293473</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.652</x:v>
+        <x:v>23.639</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>8663853</x:v>
+        <x:v>11697672</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>10.6956193831614</x:v>
+        <x:v>10.6333618036898</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>683405</x:v>
+        <x:v>1110726</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.819</x:v>
+        <x:v>23.563</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>3120099</x:v>
+        <x:v>6374849</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.692</x:v>
+        <x:v>23.69</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>2443114</x:v>
+        <x:v>5743356</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.588</x:v>
+        <x:v>23.67</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>5563213</x:v>
+        <x:v>12118205</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>6.86784607211775</x:v>
+        <x:v>11.0156326982226</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>676985</x:v>
+        <x:v>631493</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24.07</x:v>
+        <x:v>23.87</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,28 +633,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>4633294</x:v>
+        <x:v>1141250</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.587</x:v>
+        <x:v>23.691</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>4020490</x:v>
+        <x:v>600470</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.617</x:v>
+        <x:v>23.747</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>8653784</x:v>
+        <x:v>1741720</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>10.6831890947471</x:v>
+        <x:v>1.58324997663831</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>612804</x:v>
+        <x:v>540780</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.391</x:v>
+        <x:v>23.63</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>1056630</x:v>
+        <x:v>4177803</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.688</x:v>
+        <x:v>23.693</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>474708</x:v>
+        <x:v>3696995</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.741</x:v>
+        <x:v>23.623</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1531338</x:v>
+        <x:v>7874798</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.89045317308265</x:v>
+        <x:v>7.15831118063259</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>581922</x:v>
+        <x:v>480808</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.645</x:v>
+        <x:v>24.228</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>782100</x:v>
+        <x:v>234893</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.622</x:v>
+        <x:v>23.669</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>573473</x:v>
+        <x:v>89104</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.705</x:v>
+        <x:v>23.617</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1355573</x:v>
+        <x:v>323997</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.67346939682498</x:v>
+        <x:v>0.29451820193882</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>208627</x:v>
+        <x:v>145789</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.395</x:v>
+        <x:v>23.701</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>806217</x:v>
+        <x:v>772917</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.653</x:v>
+        <x:v>23.71</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>657923</x:v>
+        <x:v>628375</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.735</x:v>
+        <x:v>23.617</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1464140</x:v>
+        <x:v>1401292</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.8074965218895</x:v>
+        <x:v>1.27379574573608</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>148294</x:v>
+        <x:v>144542</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.291</x:v>
+        <x:v>24.114</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>112277</x:v>
+        <x:v>1199157</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.272</x:v>
+        <x:v>23.682</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>5224</x:v>
+        <x:v>1073207</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.796</x:v>
+        <x:v>23.753</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>117501</x:v>
+        <x:v>2272364</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.145056243814484</x:v>
+        <x:v>2.06561344528037</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>107053</x:v>
+        <x:v>125950</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.247</x:v>
+        <x:v>23.073</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>549275</x:v>
+        <x:v>617538</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.695</x:v>
+        <x:v>23.711</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>454981</x:v>
+        <x:v>492821</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.565</x:v>
+        <x:v>23.783</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1004256</x:v>
+        <x:v>1110359</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.23976479509245</x:v>
+        <x:v>1.00933322279708</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>94294</x:v>
+        <x:v>124717</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>24.322</x:v>
+        <x:v>23.422</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>667724</x:v>
+        <x:v>954399</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.588</x:v>
+        <x:v>23.631</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>586967</x:v>
+        <x:v>836482</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.676</x:v>
+        <x:v>23.712</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1254691</x:v>
+        <x:v>1790881</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.54892948662427</x:v>
+        <x:v>1.62793807352042</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>80757</x:v>
+        <x:v>117917</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.951</x:v>
+        <x:v>23.054</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1812761</x:v>
+        <x:v>658546</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.665</x:v>
+        <x:v>23.712</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1732846</x:v>
+        <x:v>544976</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.693</x:v>
+        <x:v>23.692</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>3545607</x:v>
+        <x:v>1203522</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>4.37708984146808</x:v>
+        <x:v>1.09401980707788</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>79915</x:v>
+        <x:v>113570</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.064</x:v>
+        <x:v>23.806</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1192162</x:v>
+        <x:v>123220</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.682</x:v>
+        <x:v>23.311</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1115063</x:v>
+        <x:v>18225</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.622</x:v>
+        <x:v>23.753</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>2307225</x:v>
+        <x:v>141445</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.84829399013517</x:v>
+        <x:v>0.128575656790762</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>77099</x:v>
+        <x:v>104995</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>24.555</x:v>
+        <x:v>23.234</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1169936</x:v>
+        <x:v>1004354</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.577</x:v>
+        <x:v>23.611</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1096900</x:v>
+        <x:v>905154</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.593</x:v>
+        <x:v>23.634</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>2266836</x:v>
+        <x:v>1909508</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2.79843333676692</x:v>
+        <x:v>1.73577182118289</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>73036</x:v>
+        <x:v>99200</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.337</x:v>
+        <x:v>23.395</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>456818</x:v>
+        <x:v>1636976</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.684</x:v>
+        <x:v>23.637</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>405282</x:v>
+        <x:v>1540830</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.677</x:v>
+        <x:v>23.635</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>862100</x:v>
+        <x:v>3177806</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>1.06427168953853</x:v>
+        <x:v>2.88867399769256</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>51536</x:v>
+        <x:v>96146</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.739</x:v>
+        <x:v>23.662</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>203677</x:v>
+        <x:v>2881417</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.616</x:v>
+        <x:v>23.659</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>156309</x:v>
+        <x:v>2801958</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.62</x:v>
+        <x:v>23.626</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>359986</x:v>
+        <x:v>5683375</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.444406575142346</x:v>
+        <x:v>5.16627433570077</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>47368</x:v>
+        <x:v>79459</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.602</x:v>
+        <x:v>24.812</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>89236</x:v>
+        <x:v>1951206</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.538</x:v>
+        <x:v>23.671</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>42735</x:v>
+        <x:v>1879755</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.639</x:v>
+        <x:v>23.698</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>131971</x:v>
+        <x:v>3830961</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.162919613896403</x:v>
+        <x:v>3.48240182908405</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>46501</x:v>
+        <x:v>71451</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.445</x:v>
+        <x:v>22.955</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>117724</x:v>
+        <x:v>216502</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.571</x:v>
+        <x:v>23.783</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>71780</x:v>
+        <x:v>148691</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.912</x:v>
+        <x:v>23.681</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>189504</x:v>
+        <x:v>365193</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.233944719005115</x:v>
+        <x:v>0.331965992650067</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>45944</x:v>
+        <x:v>67811</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.038</x:v>
+        <x:v>24.005</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>164606</x:v>
+        <x:v>308664</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.668</x:v>
+        <x:v>23.633</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>119859</x:v>
+        <x:v>262974</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.668</x:v>
+        <x:v>23.627</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>284465</x:v>
+        <x:v>571638</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.351175091247625</x:v>
+        <x:v>0.519627638280303</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>44747</x:v>
+        <x:v>45690</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.669</x:v>
+        <x:v>23.664</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>141771</x:v>
+        <x:v>102612</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.646</x:v>
+        <x:v>23.56</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>111281</x:v>
+        <x:v>60067</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.604</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>253052</x:v>
+        <x:v>162679</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.312395406079462</x:v>
+        <x:v>0.147877685821799</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>30490</x:v>
+        <x:v>42545</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.8</x:v>
+        <x:v>23.39</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>205066</x:v>
+        <x:v>199235</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.736</x:v>
+        <x:v>23.668</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>175842</x:v>
+        <x:v>157286</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.767</x:v>
+        <x:v>23.672</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>380908</x:v>
+        <x:v>356521</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.470235008373439</x:v>
+        <x:v>0.324083012723668</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>29224</x:v>
+        <x:v>41949</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.554</x:v>
+        <x:v>23.653</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>550378</x:v>
+        <x:v>1670883</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.609</x:v>
+        <x:v>23.701</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>531318</x:v>
+        <x:v>1633437</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.619</x:v>
+        <x:v>23.652</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1081696</x:v>
+        <x:v>3304320</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>1.33536530505402</x:v>
+        <x:v>3.00367714833928</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>19060</x:v>
+        <x:v>37446</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.336</x:v>
+        <x:v>25.856</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1155,28 +1155,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>471295</x:v>
+        <x:v>632747</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.66</x:v>
+        <x:v>23.62</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>453929</x:v>
+        <x:v>607839</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.685</x:v>
+        <x:v>23.625</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>925224</x:v>
+        <x:v>1240586</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.14219894406866</x:v>
+        <x:v>1.12771154692936</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>17366</x:v>
+        <x:v>24908</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.005</x:v>
+        <x:v>23.485</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1184,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>112091</x:v>
+        <x:v>94460</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.614</x:v>
+        <x:v>23.47</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>99590</x:v>
+        <x:v>69701</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.773</x:v>
+        <x:v>23.701</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>211681</x:v>
+        <x:v>164161</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.261322463186644</x:v>
+        <x:v>0.149224846367339</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>12501</x:v>
+        <x:v>24759</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>22.342</x:v>
+        <x:v>22.82</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,28 +1213,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>520365</x:v>
+        <x:v>263847</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.491</x:v>
+        <x:v>23.742</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>513802</x:v>
+        <x:v>244295</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.536</x:v>
+        <x:v>23.746</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1034167</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>1.27669024516296</x:v>
+        <x:v>0.461908808321053</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>6563</x:v>
+        <x:v>19552</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>20.016</x:v>
+        <x:v>23.686</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,28 +1242,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>6454</x:v>
+        <x:v>545885</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.24</x:v>
+        <x:v>23.663</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>1454</x:v>
+        <x:v>538374</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.36</x:v>
+        <x:v>23.688</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>7908</x:v>
+        <x:v>1084259</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.00976251075382286</x:v>
+        <x:v>0.985607925740002</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>5000</x:v>
+        <x:v>7511</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.205</x:v>
+        <x:v>21.903</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1271,28 +1271,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>9742</x:v>
+        <x:v>6454</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.568</x:v>
+        <x:v>23.24</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>6525</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.618</x:v>
+        <x:v>23.36</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>16267</x:v>
+        <x:v>7908</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0200817858412287</x:v>
+        <x:v>0.0071884923037318</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>3217</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.466</x:v>
+        <x:v>23.205</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,28 +1300,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>6760</x:v>
+        <x:v>91250</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.326</x:v>
+        <x:v>23.522</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>4314</x:v>
+        <x:v>90288</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.614</x:v>
+        <x:v>23.562</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>11074</x:v>
+        <x:v>181538</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0136709716853609</x:v>
+        <x:v>0.165020803722163</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>2446</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>22.817</x:v>
+        <x:v>19.747</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>2550</x:v>
+        <x:v>1347</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.731</x:v>
+        <x:v>23.278</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1500</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.524</x:v>
+        <x:v>23.47</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>4050</x:v>
+        <x:v>1858</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0049997684057894</x:v>
+        <x:v>0.00168895026559606</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>1050</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.026</x:v>
+        <x:v>23.16</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>64510</x:v>
+        <x:v>7032</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.485</x:v>
+        <x:v>23.339</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>63548</x:v>
+        <x:v>9219</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.534</x:v>
+        <x:v>23.658</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>128058</x:v>
+        <x:v>16251</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.158088973458908</x:v>
+        <x:v>0.0147724062250816</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>962</x:v>
+        <x:v>-2187</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>20.284</x:v>
+        <x:v>24.684</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>1320</x:v>
+        <x:v>3953</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.267</x:v>
+        <x:v>23.518</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>475</x:v>
+        <x:v>7772</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.448</x:v>
+        <x:v>23.24</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1795</x:v>
+        <x:v>11725</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00221594673787456</x:v>
+        <x:v>0.0106582033714283</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>845</x:v>
+        <x:v>-3819</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>23.164</x:v>
+        <x:v>22.953</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1416,28 +1416,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>66660</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.344</x:v>
+        <x:v>23.393</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>67692</x:v>
+        <x:v>6271</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.698</x:v>
+        <x:v>23.734</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>134352</x:v>
+        <x:v>6495</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.16585898391472</x:v>
+        <x:v>0.00590405380788291</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1032</x:v>
+        <x:v>-6047</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>46.571</x:v>
+        <x:v>23.746</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1445,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.34</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>10451</x:v>
+        <x:v>7010</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.724</x:v>
+        <x:v>23.316</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>16451</x:v>
+        <x:v>7010</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0203089358132448</x:v>
+        <x:v>0.00637219664253413</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-4451</x:v>
+        <x:v>-7010</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>24.242</x:v>
+        <x:v>23.316</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>2686</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.415</x:v>
+        <x:v>23.34</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>7772</x:v>
+        <x:v>14451</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.24</x:v>
+        <x:v>23.751</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>10458</x:v>
+        <x:v>20451</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.012910513083394</x:v>
+        <x:v>0.0185902701193246</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-5086</x:v>
+        <x:v>-8451</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.147</x:v>
+        <x:v>24.042</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>223</x:v>
+        <x:v>9793</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.395</x:v>
+        <x:v>23.568</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>5861</x:v>
+        <x:v>22536</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.731</x:v>
+        <x:v>23.608</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>6084</x:v>
+        <x:v>32329</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00751076320514141</x:v>
+        <x:v>0.0293875528183289</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-5638</x:v>
+        <x:v>-12743</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.744</x:v>
+        <x:v>23.638</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>0</x:v>
+        <x:v>823922</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>0</x:v>
+        <x:v>23.601</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>6500</x:v>
+        <x:v>837836</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.275</x:v>
+        <x:v>23.692</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>6500</x:v>
+        <x:v>1661758</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00802431966361262</x:v>
+        <x:v>1.5105633021832</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-6500</x:v>
+        <x:v>-13914</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.275</x:v>
+        <x:v>29.034</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>490</x:v>
+        <x:v>1508001</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.357</x:v>
+        <x:v>23.623</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>9868</x:v>
+        <x:v>1525474</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.626</x:v>
+        <x:v>23.675</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>10358</x:v>
+        <x:v>3033475</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0127870620116461</x:v>
+        <x:v>2.75747492299732</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-9378</x:v>
+        <x:v>-17473</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.64</x:v>
+        <x:v>28.135</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>71905</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.511</x:v>
+        <x:v>23.731</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>86621</x:v>
+        <x:v>21789</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.616</x:v>
+        <x:v>23.641</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>158526</x:v>
+        <x:v>24339</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.195702045999054</x:v>
+        <x:v>0.0221245212671381</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-14716</x:v>
+        <x:v>-19239</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>24.126</x:v>
+        <x:v>23.63</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,28 +1619,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>107174</x:v>
+        <x:v>2510</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.569</x:v>
+        <x:v>23.633</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>131559</x:v>
+        <x:v>27686</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.742</x:v>
+        <x:v>23.745</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>238733</x:v>
+        <x:v>30196</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.294718447115882</x:v>
+        <x:v>0.0274486233691813</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-24385</x:v>
+        <x:v>-25176</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>24.501</x:v>
+        <x:v>23.756</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>97068</x:v>
+        <x:v>308692</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.729</x:v>
+        <x:v>23.648</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>126191</x:v>
+        <x:v>349521</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.662</x:v>
+        <x:v>23.697</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>223259</x:v>
+        <x:v>658213</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.275615628273614</x:v>
+        <x:v>0.598325630338419</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-29123</x:v>
+        <x:v>-40829</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.437</x:v>
+        <x:v>24.063</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>117793</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.5</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>146939</x:v>
+        <x:v>113046</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.561</x:v>
+        <x:v>23.732</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>264732</x:v>
+        <x:v>184796</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.326814491259615</x:v>
+        <x:v>0.16798237528584</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-29146</x:v>
+        <x:v>-41296</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.805</x:v>
+        <x:v>23.821</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>165855</x:v>
+        <x:v>126031</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.52</x:v>
+        <x:v>23.579</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>197822</x:v>
+        <x:v>168960</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.731</x:v>
+        <x:v>23.729</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>363677</x:v>
+        <x:v>294991</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.448963154200561</x:v>
+        <x:v>0.268151306673008</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-31967</x:v>
+        <x:v>-42929</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>24.825</x:v>
+        <x:v>24.169</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>66368</x:v>
+        <x:v>204732</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.678</x:v>
+        <x:v>23.541</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>107463</x:v>
+        <x:v>249189</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.734</x:v>
+        <x:v>23.728</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>173831</x:v>
+        <x:v>453921</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.214596232530068</x:v>
+        <x:v>0.412621094461588</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-41095</x:v>
+        <x:v>-44457</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>23.824</x:v>
+        <x:v>24.588</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,28 +1764,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>2014071</x:v>
+        <x:v>186660</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.65</x:v>
+        <x:v>23.545</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>2055433</x:v>
+        <x:v>234358</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.6</x:v>
+        <x:v>23.619</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>4069504</x:v>
+        <x:v>421018</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>5.02384630282311</x:v>
+        <x:v>0.382711766911046</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-41362</x:v>
+        <x:v>-47698</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>21.181</x:v>
+        <x:v>23.907</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,28 +1793,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1171430</x:v>
+        <x:v>88797</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.602</x:v>
+        <x:v>23.526</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>1235405</x:v>
+        <x:v>197028</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.663</x:v>
+        <x:v>23.678</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>2406835</x:v>
+        <x:v>285825</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2.97126360270324</x:v>
+        <x:v>0.259819273231429</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-63975</x:v>
+        <x:v>-108231</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>24.775</x:v>
+        <x:v>23.803</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>84149</x:v>
+        <x:v>3494405</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.519</x:v>
+        <x:v>23.671</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>182547</x:v>
+        <x:v>3710692</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>23.675</x:v>
+        <x:v>23.672</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>266696</x:v>
+        <x:v>7205097</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.329239070308743</x:v>
+        <x:v>6.54954278352821</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-98398</x:v>
+        <x:v>-216287</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.809</x:v>
+        <x:v>23.692</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>6738275</x:v>
+        <x:v>137227</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.624</x:v>
+        <x:v>23.621</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>6952066</x:v>
+        <x:v>374715</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.638</x:v>
+        <x:v>23.723</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>13690341</x:v>
+        <x:v>511942</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>16.9008726904403</x:v>
+        <x:v>0.46536306613013</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-213791</x:v>
+        <x:v>-237488</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>24.096</x:v>
+        <x:v>23.782</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1246391</x:v>
+        <x:v>1670809</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.632</x:v>
+        <x:v>23.66</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1469800</x:v>
+        <x:v>1982050</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.593</x:v>
+        <x:v>23.621</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>2716191</x:v>
+        <x:v>3652859</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>3.35316690021963</x:v>
+        <x:v>3.32050440163346</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-223409</x:v>
+        <x:v>-311241</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.372</x:v>
+        <x:v>23.409</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>2304701</x:v>
+        <x:v>8919094</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.652</x:v>
+        <x:v>23.646</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>2579040</x:v>
+        <x:v>9289965</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.656</x:v>
+        <x:v>23.661</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>4883741</x:v>
+        <x:v>18209059</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>6.02903060589095</x:v>
+        <x:v>16.5523116438667</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-274339</x:v>
+        <x:v>-370871</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.69</x:v>
+        <x:v>24.012</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,28 +1938,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>2049300</x:v>
+        <x:v>188165</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.669</x:v>
+        <x:v>23.723</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>2532952</x:v>
+        <x:v>735330</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.724</x:v>
+        <x:v>23.741</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>4582252</x:v>
+        <x:v>923495</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>5.65683920418896</x:v>
+        <x:v>0.839471004050935</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-483652</x:v>
+        <x:v>-547165</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.956</x:v>
+        <x:v>23.748</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,28 +1967,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>184503</x:v>
+        <x:v>2533328</x:v>
       </x:c>
       <x:c r="C50" s="0">
+        <x:v>23.676</x:v>
+      </x:c>
+      <x:c r="D50" s="0">
+        <x:v>3095618</x:v>
+      </x:c>
+      <x:c r="E50" s="0">
         <x:v>23.723</x:v>
       </x:c>
-      <x:c r="D50" s="0">
-        <x:v>727835</x:v>
-      </x:c>
-      <x:c r="E50" s="0">
-        <x:v>23.741</x:v>
-      </x:c>
       <x:c r="F50" s="0">
-        <x:v>912338</x:v>
+        <x:v>5628946</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.12629103896323</x:v>
+        <x:v>5.11679754667702</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-543332</x:v>
+        <x:v>-562290</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.747</x:v>
+        <x:v>23.934</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1996,28 +1996,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>306367</x:v>
+        <x:v>444295</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.559</x:v>
+        <x:v>23.616</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>1950603</x:v>
+        <x:v>2063966</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.469</x:v>
+        <x:v>23.484</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2256970</x:v>
+        <x:v>2508261</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.78625365402827</x:v>
+        <x:v>2.28004740696138</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1644236</x:v>
+        <x:v>-1619671</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.452</x:v>
+        <x:v>23.447</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,81 +40,93 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
+    <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
     <x:t>GCM</x:t>
   </x:si>
   <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
@@ -127,58 +139,46 @@
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALTERNATIF</x:t>
   </x:si>
   <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
-    <x:t>HSBC</x:t>
+    <x:t>TEB</x:t>
   </x:si>
   <x:si>
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
-    <x:t>OYAK</x:t>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>MIDAS</x:t>
+    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>GLOBAL</x:t>
@@ -575,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>6404199</x:v>
+        <x:v>7595288</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.626</x:v>
+        <x:v>23.676</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>5293473</x:v>
+        <x:v>7019091</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.639</x:v>
+        <x:v>23.662</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>11697672</x:v>
+        <x:v>14614379</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>10.6333618036898</x:v>
+        <x:v>11.302006053276</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1110726</x:v>
+        <x:v>576197</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.563</x:v>
+        <x:v>23.855</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>6374849</x:v>
+        <x:v>4775981</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.69</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>5743356</x:v>
+        <x:v>4242684</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.67</x:v>
+        <x:v>23.625</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>12118205</x:v>
+        <x:v>9018665</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>11.0156326982226</x:v>
+        <x:v>6.9745698002268</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>631493</x:v>
+        <x:v>533297</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.87</x:v>
+        <x:v>24.115</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,28 +633,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1141250</x:v>
+        <x:v>1193127</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.691</x:v>
+        <x:v>23.688</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>600470</x:v>
+        <x:v>672509</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.747</x:v>
+        <x:v>23.739</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1741720</x:v>
+        <x:v>1865636</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.58324997663831</x:v>
+        <x:v>1.44278654366427</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>540780</x:v>
+        <x:v>520618</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.63</x:v>
+        <x:v>23.621</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>4177803</x:v>
+        <x:v>6967005</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.693</x:v>
+        <x:v>23.621</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>3696995</x:v>
+        <x:v>6760540</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.623</x:v>
+        <x:v>23.625</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>7874798</x:v>
+        <x:v>13727545</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>7.15831118063259</x:v>
+        <x:v>10.6161744324969</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>480808</x:v>
+        <x:v>206465</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>24.228</x:v>
+        <x:v>23.487</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>234893</x:v>
+        <x:v>1160140</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.669</x:v>
+        <x:v>23.626</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>89104</x:v>
+        <x:v>974442</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.617</x:v>
+        <x:v>23.707</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>323997</x:v>
+        <x:v>2134582</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.29451820193882</x:v>
+        <x:v>1.65077549208311</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>145789</x:v>
+        <x:v>185698</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.701</x:v>
+        <x:v>23.197</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>772917</x:v>
+        <x:v>275842</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.71</x:v>
+        <x:v>23.659</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>628375</x:v>
+        <x:v>93042</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.617</x:v>
+        <x:v>23.618</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1401292</x:v>
+        <x:v>368884</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.27379574573608</x:v>
+        <x:v>0.285275836965544</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>144542</x:v>
+        <x:v>182800</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>24.114</x:v>
+        <x:v>23.68</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>1199157</x:v>
+        <x:v>1904087</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.682</x:v>
+        <x:v>23.681</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1073207</x:v>
+        <x:v>1731922</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.753</x:v>
+        <x:v>23.683</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>2272364</x:v>
+        <x:v>3636009</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.06561344528037</x:v>
+        <x:v>2.81190160237162</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>125950</x:v>
+        <x:v>172165</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.073</x:v>
+        <x:v>23.665</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>617538</x:v>
+        <x:v>1424017</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.711</x:v>
+        <x:v>23.677</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>492821</x:v>
+        <x:v>1267626</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.783</x:v>
+        <x:v>23.74</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1110359</x:v>
+        <x:v>2691643</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.00933322279708</x:v>
+        <x:v>2.08157770366145</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>124717</x:v>
+        <x:v>156391</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.422</x:v>
+        <x:v>23.165</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>954399</x:v>
+        <x:v>4461107</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.631</x:v>
+        <x:v>23.66</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>836482</x:v>
+        <x:v>4338838</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.712</x:v>
+        <x:v>23.664</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1790881</x:v>
+        <x:v>8799945</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.62793807352042</x:v>
+        <x:v>6.8054230466102</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>117917</x:v>
+        <x:v>122269</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.054</x:v>
+        <x:v>23.533</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>658546</x:v>
+        <x:v>124260</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.712</x:v>
+        <x:v>23.313</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>544976</x:v>
+        <x:v>18634</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.692</x:v>
+        <x:v>23.749</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>1203522</x:v>
+        <x:v>142894</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.09401980707788</x:v>
+        <x:v>0.1105068407612</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>113570</x:v>
+        <x:v>105626</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.806</x:v>
+        <x:v>23.237</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>123220</x:v>
+        <x:v>867549</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.311</x:v>
+        <x:v>23.699</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>18225</x:v>
+        <x:v>774197</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.753</x:v>
+        <x:v>23.624</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>141445</x:v>
+        <x:v>1641746</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.128575656790762</x:v>
+        <x:v>1.26964157901897</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>104995</x:v>
+        <x:v>93352</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.234</x:v>
+        <x:v>24.325</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1004354</x:v>
+        <x:v>1938262</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.611</x:v>
+        <x:v>23.664</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>905154</x:v>
+        <x:v>1845891</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.634</x:v>
+        <x:v>23.687</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>1909508</x:v>
+        <x:v>3784153</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.73577182118289</x:v>
+        <x:v>2.92646852203044</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>99200</x:v>
+        <x:v>92371</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.395</x:v>
+        <x:v>23.211</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1636976</x:v>
+        <x:v>1935152</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.637</x:v>
+        <x:v>23.631</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1540830</x:v>
+        <x:v>1856697</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.635</x:v>
+        <x:v>23.634</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>3177806</x:v>
+        <x:v>3791849</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>2.88867399769256</x:v>
+        <x:v>2.93242021102016</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>96146</x:v>
+        <x:v>78455</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.662</x:v>
+        <x:v>23.564</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>2881417</x:v>
+        <x:v>265856</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.659</x:v>
+        <x:v>23.765</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>2801958</x:v>
+        <x:v>197731</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.626</x:v>
+        <x:v>23.687</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>5683375</x:v>
+        <x:v>463587</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>5.16627433570077</x:v>
+        <x:v>0.358514246840052</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>79459</x:v>
+        <x:v>68125</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>24.812</x:v>
+        <x:v>23.992</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>1951206</x:v>
+        <x:v>3231079</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.671</x:v>
+        <x:v>23.649</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1879755</x:v>
+        <x:v>3169853</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.698</x:v>
+        <x:v>23.621</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>3830961</x:v>
+        <x:v>6400932</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>3.48240182908405</x:v>
+        <x:v>4.9501502739602</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>71451</x:v>
+        <x:v>61226</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>22.955</x:v>
+        <x:v>25.113</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>216502</x:v>
+        <x:v>1895939</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.783</x:v>
+        <x:v>23.686</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>148691</x:v>
+        <x:v>1835785</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.681</x:v>
+        <x:v>23.652</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>365193</x:v>
+        <x:v>3731724</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.331965992650067</x:v>
+        <x:v>2.88592264078792</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>67811</x:v>
+        <x:v>60154</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>24.005</x:v>
+        <x:v>24.731</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>308664</x:v>
+        <x:v>1005853</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.633</x:v>
+        <x:v>23.603</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>262974</x:v>
+        <x:v>951038</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.627</x:v>
+        <x:v>23.687</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>571638</x:v>
+        <x:v>1956891</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.519627638280303</x:v>
+        <x:v>1.51335844838849</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>45690</x:v>
+        <x:v>54815</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.664</x:v>
+        <x:v>22.134</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>102612</x:v>
+        <x:v>581464</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.56</x:v>
+        <x:v>23.646</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>60067</x:v>
+        <x:v>531305</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.68</x:v>
+        <x:v>23.651</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>162679</x:v>
+        <x:v>1112769</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.147877685821799</x:v>
+        <x:v>0.86055808282363</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>42545</x:v>
+        <x:v>50159</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.39</x:v>
+        <x:v>23.593</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>199235</x:v>
+        <x:v>121552</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.668</x:v>
+        <x:v>23.565</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>157286</x:v>
+        <x:v>75106</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.672</x:v>
+        <x:v>23.665</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>356521</x:v>
+        <x:v>196658</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.324083012723668</x:v>
+        <x:v>0.152085142066259</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>41949</x:v>
+        <x:v>46446</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.653</x:v>
+        <x:v>23.403</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>1670883</x:v>
+        <x:v>754058</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.701</x:v>
+        <x:v>23.706</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>1633437</x:v>
+        <x:v>710425</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.652</x:v>
+        <x:v>23.69</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>3304320</x:v>
+        <x:v>1464483</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>3.00367714833928</x:v>
+        <x:v>1.13255552842306</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>37446</x:v>
+        <x:v>43633</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>25.856</x:v>
+        <x:v>23.975</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1155,28 +1155,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>632747</x:v>
+        <x:v>228209</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.62</x:v>
+        <x:v>23.661</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>607839</x:v>
+        <x:v>193490</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.625</x:v>
+        <x:v>23.674</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1240586</x:v>
+        <x:v>421699</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.12771154692936</x:v>
+        <x:v>0.326120230675587</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>24908</x:v>
+        <x:v>34719</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.485</x:v>
+        <x:v>23.591</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1184,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>94460</x:v>
+        <x:v>759621</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.47</x:v>
+        <x:v>23.617</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>69701</x:v>
+        <x:v>725788</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.701</x:v>
+        <x:v>23.622</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>164161</x:v>
+        <x:v>1485409</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.149224846367339</x:v>
+        <x:v>1.14873861623478</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>24759</x:v>
+        <x:v>33833</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>22.82</x:v>
+        <x:v>23.517</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,28 +1213,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>263847</x:v>
+        <x:v>406396</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.742</x:v>
+        <x:v>23.667</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>244295</x:v>
+        <x:v>376374</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.746</x:v>
+        <x:v>23.692</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>508142</x:v>
+        <x:v>782770</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.461908808321053</x:v>
+        <x:v>0.605353896893113</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>19552</x:v>
+        <x:v>30022</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.686</x:v>
+        <x:v>23.349</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,28 +1242,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>545885</x:v>
+        <x:v>327928</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.663</x:v>
+        <x:v>23.713</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>538374</x:v>
+        <x:v>300833</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.688</x:v>
+        <x:v>23.725</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1084259</x:v>
+        <x:v>628761</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.985607925740002</x:v>
+        <x:v>0.486251289094384</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>7511</x:v>
+        <x:v>27095</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>21.903</x:v>
+        <x:v>23.576</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1271,28 +1271,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>6454</x:v>
+        <x:v>94611</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.24</x:v>
+        <x:v>23.47</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1454</x:v>
+        <x:v>69984</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.36</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>7908</x:v>
+        <x:v>164595</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0071884923037318</x:v>
+        <x:v>0.127289273553051</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>5000</x:v>
+        <x:v>24627</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.205</x:v>
+        <x:v>22.818</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,28 +1300,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>91250</x:v>
+        <x:v>1205718</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.522</x:v>
+        <x:v>23.622</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>90288</x:v>
+        <x:v>1186706</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.562</x:v>
+        <x:v>23.652</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>181538</x:v>
+        <x:v>2392424</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.165020803722163</x:v>
+        <x:v>1.8501771802964</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>962</x:v>
+        <x:v>19012</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>19.747</x:v>
+        <x:v>21.787</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>1347</x:v>
+        <x:v>563055</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.278</x:v>
+        <x:v>23.661</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>511</x:v>
+        <x:v>551239</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.47</x:v>
+        <x:v>23.684</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1858</x:v>
+        <x:v>1114294</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00168895026559606</x:v>
+        <x:v>0.861737439074843</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>836</x:v>
+        <x:v>11816</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.557</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>7032</x:v>
+        <x:v>6454</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.339</x:v>
+        <x:v>23.24</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>9219</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.658</x:v>
+        <x:v>23.36</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>16251</x:v>
+        <x:v>7908</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0147724062250816</x:v>
+        <x:v>0.00611563884235566</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-2187</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.684</x:v>
+        <x:v>23.205</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>3953</x:v>
+        <x:v>276285</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.518</x:v>
+        <x:v>23.552</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>7772</x:v>
+        <x:v>273779</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.24</x:v>
+        <x:v>23.622</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>11725</x:v>
+        <x:v>550064</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0106582033714283</x:v>
+        <x:v>0.425391093093263</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-3819</x:v>
+        <x:v>2506</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>22.953</x:v>
+        <x:v>15.946</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1416,28 +1416,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>224</x:v>
+        <x:v>263497</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.393</x:v>
+        <x:v>23.574</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>6271</x:v>
+        <x:v>262635</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.734</x:v>
+        <x:v>23.597</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>6495</x:v>
+        <x:v>526132</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00590405380788291</x:v>
+        <x:v>0.406883320107014</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-6047</x:v>
+        <x:v>862</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>23.746</x:v>
+        <x:v>16.679</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1445,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>0</x:v>
+        <x:v>1356</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0</x:v>
+        <x:v>23.281</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>7010</x:v>
+        <x:v>1811</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.316</x:v>
+        <x:v>23.563</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>7010</x:v>
+        <x:v>3167</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00637219664253413</x:v>
+        <x:v>0.00244919426071578</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-7010</x:v>
+        <x:v>-455</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.316</x:v>
+        <x:v>24.404</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>6000</x:v>
+        <x:v>8032</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.34</x:v>
+        <x:v>23.372</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>14451</x:v>
+        <x:v>9291</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.751</x:v>
+        <x:v>23.658</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>20451</x:v>
+        <x:v>17323</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0185902701193246</x:v>
+        <x:v>0.0133967136654182</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-8451</x:v>
+        <x:v>-1259</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>24.042</x:v>
+        <x:v>25.484</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>9793</x:v>
+        <x:v>5483</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.568</x:v>
+        <x:v>23.544</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>22536</x:v>
+        <x:v>7772</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.608</x:v>
+        <x:v>23.24</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>32329</x:v>
+        <x:v>13255</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0293875528183289</x:v>
+        <x:v>0.0102507325310349</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-12743</x:v>
+        <x:v>-2289</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.638</x:v>
+        <x:v>22.512</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>823922</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.601</x:v>
+        <x:v>23.48</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>837836</x:v>
+        <x:v>14451</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.692</x:v>
+        <x:v>23.751</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>1661758</x:v>
+        <x:v>24451</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>1.5105633021832</x:v>
+        <x:v>0.018909140785842</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-13914</x:v>
+        <x:v>-4451</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>29.034</x:v>
+        <x:v>24.359</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>1508001</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.623</x:v>
+        <x:v>23.393</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>1525474</x:v>
+        <x:v>6271</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.675</x:v>
+        <x:v>23.734</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>3033475</x:v>
+        <x:v>6495</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.75747492299732</x:v>
+        <x:v>0.00502289760762519</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-17473</x:v>
+        <x:v>-6047</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>28.135</x:v>
+        <x:v>23.746</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>2550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.731</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>21789</x:v>
+        <x:v>7010</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.641</x:v>
+        <x:v>23.316</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>24339</x:v>
+        <x:v>7010</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.0221245212671381</x:v>
+        <x:v>0.00542117201377253</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-19239</x:v>
+        <x:v>-7010</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>23.63</x:v>
+        <x:v>23.316</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,28 +1619,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>2510</x:v>
+        <x:v>240483</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.633</x:v>
+        <x:v>23.551</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>27686</x:v>
+        <x:v>252450</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.745</x:v>
+        <x:v>23.717</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>30196</x:v>
+        <x:v>492933</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.0274486233691813</x:v>
+        <x:v>0.381208927855198</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-25176</x:v>
+        <x:v>-11967</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.756</x:v>
+        <x:v>27.041</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>308692</x:v>
+        <x:v>22296</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.648</x:v>
+        <x:v>23.608</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>349521</x:v>
+        <x:v>37681</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.697</x:v>
+        <x:v>23.626</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>658213</x:v>
+        <x:v>59977</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.598325630338419</x:v>
+        <x:v>0.0463831146747554</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-40829</x:v>
+        <x:v>-15385</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>24.063</x:v>
+        <x:v>23.651</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>71750</x:v>
+        <x:v>2750</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.68</x:v>
+        <x:v>23.718</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>113046</x:v>
+        <x:v>21924</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.732</x:v>
+        <x:v>23.642</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>184796</x:v>
+        <x:v>24674</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.16798237528584</x:v>
+        <x:v>0.0190815974704456</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-41296</x:v>
+        <x:v>-19174</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.821</x:v>
+        <x:v>23.631</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>126031</x:v>
+        <x:v>3386</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.579</x:v>
+        <x:v>23.61</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>168960</x:v>
+        <x:v>28431</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.729</x:v>
+        <x:v>23.742</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>294991</x:v>
+        <x:v>31817</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.268151306673008</x:v>
+        <x:v>0.0246056248162911</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-42929</x:v>
+        <x:v>-25045</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>24.169</x:v>
+        <x:v>23.76</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>204732</x:v>
+        <x:v>78401</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.541</x:v>
+        <x:v>23.65</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>249189</x:v>
+        <x:v>108588</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.728</x:v>
+        <x:v>23.71</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>453921</x:v>
+        <x:v>186989</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.412621094461588</x:v>
+        <x:v>0.144607636759388</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-44457</x:v>
+        <x:v>-30187</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>24.588</x:v>
+        <x:v>23.865</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,28 +1764,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>186660</x:v>
+        <x:v>151098</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.545</x:v>
+        <x:v>23.585</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>234358</x:v>
+        <x:v>191310</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.619</x:v>
+        <x:v>23.713</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>421018</x:v>
+        <x:v>342408</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.382711766911046</x:v>
+        <x:v>0.264800665747764</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-47698</x:v>
+        <x:v>-40212</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>23.907</x:v>
+        <x:v>24.196</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,28 +1793,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>88797</x:v>
+        <x:v>1624079</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.526</x:v>
+        <x:v>23.613</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>197028</x:v>
+        <x:v>1680283</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.678</x:v>
+        <x:v>23.669</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>285825</x:v>
+        <x:v>3304362</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.259819273231429</x:v>
+        <x:v>2.55542293834143</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-108231</x:v>
+        <x:v>-56204</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>23.803</x:v>
+        <x:v>25.3</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>3494405</x:v>
+        <x:v>103745</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.671</x:v>
+        <x:v>23.529</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>3710692</x:v>
+        <x:v>199521</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>23.672</x:v>
+        <x:v>23.676</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>7205097</x:v>
+        <x:v>303266</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>6.54954278352821</x:v>
+        <x:v>0.234530264183843</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-216287</x:v>
+        <x:v>-95776</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.692</x:v>
+        <x:v>23.835</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>137227</x:v>
+        <x:v>10138555</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.621</x:v>
+        <x:v>23.642</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>374715</x:v>
+        <x:v>10266647</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.723</x:v>
+        <x:v>23.65</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>511942</x:v>
+        <x:v>20405202</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.46536306613013</x:v>
+        <x:v>15.7803295317796</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-237488</x:v>
+        <x:v>-128092</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.782</x:v>
+        <x:v>24.272</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1670809</x:v>
+        <x:v>174308</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.66</x:v>
+        <x:v>23.621</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1982050</x:v>
+        <x:v>377413</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.621</x:v>
+        <x:v>23.723</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>3652859</x:v>
+        <x:v>551721</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>3.32050440163346</x:v>
+        <x:v>0.426672531328187</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-311241</x:v>
+        <x:v>-203105</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.409</x:v>
+        <x:v>23.81</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>8919094</x:v>
+        <x:v>1975827</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.646</x:v>
+        <x:v>23.653</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>9289965</x:v>
+        <x:v>2214438</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.661</x:v>
+        <x:v>23.615</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>18209059</x:v>
+        <x:v>4190265</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>16.5523116438667</x:v>
+        <x:v>3.24053457179608</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-370871</x:v>
+        <x:v>-238611</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>24.012</x:v>
+        <x:v>23.296</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,28 +1938,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>188165</x:v>
+        <x:v>195442</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.723</x:v>
+        <x:v>23.716</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>735330</x:v>
+        <x:v>737096</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>23.741</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>923495</x:v>
+        <x:v>932538</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.839471004050935</x:v>
+        <x:v>0.721176734290928</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-547165</x:v>
+        <x:v>-541654</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.748</x:v>
+        <x:v>23.749</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,28 +1967,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2533328</x:v>
+        <x:v>2738424</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.676</x:v>
+        <x:v>23.664</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>3095618</x:v>
+        <x:v>3390267</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>23.723</x:v>
+        <x:v>23.71</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>5628946</x:v>
+        <x:v>6128691</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.11679754667702</x:v>
+        <x:v>4.73961314269038</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-562290</x:v>
+        <x:v>-651843</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.934</x:v>
+        <x:v>23.9</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1996,28 +1996,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>444295</x:v>
+        <x:v>570635</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.616</x:v>
+        <x:v>23.612</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2063966</x:v>
+        <x:v>2091623</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.484</x:v>
+        <x:v>23.485</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2508261</x:v>
+        <x:v>2662258</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.28004740696138</x:v>
+        <x:v>2.0588528620602</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1619671</x:v>
+        <x:v>-1520988</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.447</x:v>
+        <x:v>23.437</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -43,145 +43,148 @@
     <x:t>IS</x:t>
   </x:si>
   <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
+    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>YAPI KREDI</x:t>
@@ -538,7 +541,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I51"/>
+  <x:dimension ref="A1:I52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -575,28 +578,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>7595288</x:v>
+        <x:v>9438988</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.676</x:v>
+        <x:v>23.65</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>7019091</x:v>
+        <x:v>7714149</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.662</x:v>
+        <x:v>23.651</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>14614379</x:v>
+        <x:v>17153137</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>11.302006053276</x:v>
+        <x:v>11.8050152986353</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>576197</x:v>
+        <x:v>1724839</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.855</x:v>
+        <x:v>23.644</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +607,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>4775981</x:v>
+        <x:v>1265154</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.68</x:v>
+        <x:v>23.679</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>4242684</x:v>
+        <x:v>725378</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.625</x:v>
+        <x:v>23.726</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>9018665</x:v>
+        <x:v>1990532</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>6.9745698002268</x:v>
+        <x:v>1.36991039670605</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>533297</x:v>
+        <x:v>539776</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24.115</x:v>
+        <x:v>23.617</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,28 +636,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1193127</x:v>
+        <x:v>5297384</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.688</x:v>
+        <x:v>23.643</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>672509</x:v>
+        <x:v>4966931</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.739</x:v>
+        <x:v>23.649</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1865636</x:v>
+        <x:v>10264315</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.44278654366427</x:v>
+        <x:v>7.06403706826407</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>520618</x:v>
+        <x:v>330453</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.621</x:v>
+        <x:v>23.542</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +665,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>6967005</x:v>
+        <x:v>7511319</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.621</x:v>
+        <x:v>23.615</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>6760540</x:v>
+        <x:v>7182388</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.625</x:v>
+        <x:v>23.62</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>13727545</x:v>
+        <x:v>14693707</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>10.6161744324969</x:v>
+        <x:v>10.1124031090444</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>206465</x:v>
+        <x:v>328931</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.487</x:v>
+        <x:v>23.495</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +694,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>1160140</x:v>
+        <x:v>1349191</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.626</x:v>
+        <x:v>23.616</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>974442</x:v>
+        <x:v>1152107</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.707</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>2134582</x:v>
+        <x:v>2501298</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.65077549208311</x:v>
+        <x:v>1.72142629983343</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>185698</x:v>
+        <x:v>197084</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.197</x:v>
+        <x:v>23.238</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +723,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>275842</x:v>
+        <x:v>297571</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.659</x:v>
+        <x:v>23.652</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>93042</x:v>
+        <x:v>101315</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.618</x:v>
+        <x:v>23.613</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>368884</x:v>
+        <x:v>398886</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.285275836965544</x:v>
+        <x:v>0.274518610351649</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>182800</x:v>
+        <x:v>196256</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.68</x:v>
+        <x:v>23.673</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +752,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>1904087</x:v>
+        <x:v>5242788</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.681</x:v>
+        <x:v>23.667</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1731922</x:v>
+        <x:v>5047130</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.683</x:v>
+        <x:v>23.612</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>3636009</x:v>
+        <x:v>10289918</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.81190160237162</x:v>
+        <x:v>7.08165739081446</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>172165</x:v>
+        <x:v>195658</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.665</x:v>
+        <x:v>25.085</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +781,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>1424017</x:v>
+        <x:v>476836</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.677</x:v>
+        <x:v>23.671</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1267626</x:v>
+        <x:v>337212</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.74</x:v>
+        <x:v>23.706</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>2691643</x:v>
+        <x:v>814048</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.08157770366145</x:v>
+        <x:v>0.56023857874064</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>156391</x:v>
+        <x:v>139624</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.165</x:v>
+        <x:v>23.586</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +810,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>4461107</x:v>
+        <x:v>125262</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.66</x:v>
+        <x:v>23.315</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>4338838</x:v>
+        <x:v>19604</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.664</x:v>
+        <x:v>23.739</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>8799945</x:v>
+        <x:v>144866</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>6.8054230466102</x:v>
+        <x:v>0.0996986933790656</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>122269</x:v>
+        <x:v>105658</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.533</x:v>
+        <x:v>23.236</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +839,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>124260</x:v>
+        <x:v>917781</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.313</x:v>
+        <x:v>23.691</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>18634</x:v>
+        <x:v>812349</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.749</x:v>
+        <x:v>23.62</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>142894</x:v>
+        <x:v>1730130</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.1105068407612</x:v>
+        <x:v>1.19069830309336</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>105626</x:v>
+        <x:v>105432</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.237</x:v>
+        <x:v>24.239</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +868,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>867549</x:v>
+        <x:v>1939968</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.699</x:v>
+        <x:v>23.631</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>774197</x:v>
+        <x:v>1864237</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.624</x:v>
+        <x:v>23.634</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>1641746</x:v>
+        <x:v>3804205</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>1.26964157901897</x:v>
+        <x:v>2.61810409513694</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>93352</x:v>
+        <x:v>75731</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>24.325</x:v>
+        <x:v>23.567</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +897,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1938262</x:v>
+        <x:v>1320752</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.664</x:v>
+        <x:v>23.614</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1845891</x:v>
+        <x:v>1246903</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.687</x:v>
+        <x:v>23.645</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>3784153</x:v>
+        <x:v>2567655</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2.92646852203044</x:v>
+        <x:v>1.76709406312195</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>92371</x:v>
+        <x:v>73849</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.211</x:v>
+        <x:v>23.098</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +926,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1935152</x:v>
+        <x:v>760659</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.631</x:v>
+        <x:v>23.622</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1856697</x:v>
+        <x:v>690953</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.634</x:v>
+        <x:v>23.623</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>3791849</x:v>
+        <x:v>1451612</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>2.93242021102016</x:v>
+        <x:v>0.999018539155993</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>78455</x:v>
+        <x:v>69706</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.564</x:v>
+        <x:v>23.62</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +955,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>265856</x:v>
+        <x:v>1948262</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.765</x:v>
+        <x:v>23.664</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>197731</x:v>
+        <x:v>1881891</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.687</x:v>
+        <x:v>23.684</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>463587</x:v>
+        <x:v>3830153</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.358514246840052</x:v>
+        <x:v>2.6359618512412</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>68125</x:v>
+        <x:v>66371</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.992</x:v>
+        <x:v>23.09</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +984,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>3231079</x:v>
+        <x:v>313306</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.649</x:v>
+        <x:v>23.735</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>3169853</x:v>
+        <x:v>247620</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.621</x:v>
+        <x:v>23.659</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>6400932</x:v>
+        <x:v>560926</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>4.9501502739602</x:v>
+        <x:v>0.386036677221334</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>61226</x:v>
+        <x:v>65686</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>25.113</x:v>
+        <x:v>24.021</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1013,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1895939</x:v>
+        <x:v>130260</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.686</x:v>
+        <x:v>23.563</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1835785</x:v>
+        <x:v>77993</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.652</x:v>
+        <x:v>23.661</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>3731724</x:v>
+        <x:v>208253</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.88592264078792</x:v>
+        <x:v>0.143322463464654</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>60154</x:v>
+        <x:v>52267</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>24.731</x:v>
+        <x:v>23.418</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1042,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>1005853</x:v>
+        <x:v>2747412</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.603</x:v>
+        <x:v>23.639</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>951038</x:v>
+        <x:v>2713123</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.687</x:v>
+        <x:v>23.634</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1956891</x:v>
+        <x:v>5460535</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.51335844838849</x:v>
+        <x:v>3.75801226409686</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>54815</x:v>
+        <x:v>34289</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.134</x:v>
+        <x:v>24.016</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1071,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>581464</x:v>
+        <x:v>447446</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.646</x:v>
+        <x:v>23.656</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>531305</x:v>
+        <x:v>422842</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.651</x:v>
+        <x:v>23.677</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>1112769</x:v>
+        <x:v>870288</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.86055808282363</x:v>
+        <x:v>0.5989436890884</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>50159</x:v>
+        <x:v>24604</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.593</x:v>
+        <x:v>23.286</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1100,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>121552</x:v>
+        <x:v>95228</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.565</x:v>
+        <x:v>23.471</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>75106</x:v>
+        <x:v>71627</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.665</x:v>
+        <x:v>23.697</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>196658</x:v>
+        <x:v>166855</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.152085142066259</x:v>
+        <x:v>0.114831813425952</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>46446</x:v>
+        <x:v>23601</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.403</x:v>
+        <x:v>22.786</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1129,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>754058</x:v>
+        <x:v>570258</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.706</x:v>
+        <x:v>23.659</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>710425</x:v>
+        <x:v>551819</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.69</x:v>
+        <x:v>23.684</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1464483</x:v>
+        <x:v>1122077</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>1.13255552842306</x:v>
+        <x:v>0.772228202412586</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>43633</x:v>
+        <x:v>18439</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.975</x:v>
+        <x:v>22.915</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1155,28 +1158,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>228209</x:v>
+        <x:v>784662</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.661</x:v>
+        <x:v>23.615</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>193490</x:v>
+        <x:v>775844</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.674</x:v>
+        <x:v>23.617</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>421699</x:v>
+        <x:v>1560506</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.326120230675587</x:v>
+        <x:v>1.0739608273176</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>34719</x:v>
+        <x:v>8818</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.591</x:v>
+        <x:v>23.476</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1187,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>759621</x:v>
+        <x:v>1825022</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.617</x:v>
+        <x:v>23.606</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>725788</x:v>
+        <x:v>1818447</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.622</x:v>
+        <x:v>23.661</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1485409</x:v>
+        <x:v>3643469</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>1.14873861623478</x:v>
+        <x:v>2.50748345827959</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>33833</x:v>
+        <x:v>6575</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.517</x:v>
+        <x:v>8.59</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,28 +1216,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>406396</x:v>
+        <x:v>1559810</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.667</x:v>
+        <x:v>23.666</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>376374</x:v>
+        <x:v>1553375</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.692</x:v>
+        <x:v>23.704</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>782770</x:v>
+        <x:v>3113185</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.605353896893113</x:v>
+        <x:v>2.14253500992163</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>30022</x:v>
+        <x:v>6435</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.349</x:v>
+        <x:v>14.413</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,28 +1245,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>327928</x:v>
+        <x:v>1146815</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.713</x:v>
+        <x:v>23.596</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>300833</x:v>
+        <x:v>1141482</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.725</x:v>
+        <x:v>23.663</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>628761</x:v>
+        <x:v>2288297</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.486251289094384</x:v>
+        <x:v>1.57483620009689</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>27095</x:v>
+        <x:v>5333</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.576</x:v>
+        <x:v>9.247</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1271,28 +1274,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>94611</x:v>
+        <x:v>6454</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.47</x:v>
+        <x:v>23.24</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>69984</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.7</x:v>
+        <x:v>23.36</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>164595</x:v>
+        <x:v>7908</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.127289273553051</x:v>
+        <x:v>0.00544238998275407</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>24627</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>22.818</x:v>
+        <x:v>23.205</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,28 +1303,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1205718</x:v>
+        <x:v>398497</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.622</x:v>
+        <x:v>23.561</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1186706</x:v>
+        <x:v>397635</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.652</x:v>
+        <x:v>23.581</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>2392424</x:v>
+        <x:v>796132</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>1.8501771802964</x:v>
+        <x:v>0.547908551055888</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>19012</x:v>
+        <x:v>862</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>21.787</x:v>
+        <x:v>14.171</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1332,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>563055</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.661</x:v>
+        <x:v>23.553</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>551239</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.684</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1114294</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.861737439074843</x:v>
+        <x:v>0.000432197889373995</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>11816</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>22.557</x:v>
+        <x:v>23.553</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1361,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>6454</x:v>
+        <x:v>9156</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.24</x:v>
+        <x:v>23.392</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1454</x:v>
+        <x:v>9352</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.36</x:v>
+        <x:v>23.657</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>7908</x:v>
+        <x:v>18508</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00611563884235566</x:v>
+        <x:v>0.0127374498989393</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>5000</x:v>
+        <x:v>-196</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.205</x:v>
+        <x:v>36.026</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1390,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>276285</x:v>
+        <x:v>237127</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.552</x:v>
+        <x:v>23.657</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>273779</x:v>
+        <x:v>237365</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.622</x:v>
+        <x:v>23.649</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>550064</x:v>
+        <x:v>474492</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.425391093093263</x:v>
+        <x:v>0.32655165752364</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>2506</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>15.946</x:v>
+        <x:v>15.214</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1416,28 +1419,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>263497</x:v>
+        <x:v>1651</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.574</x:v>
+        <x:v>23.323</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>262635</x:v>
+        <x:v>1934</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.597</x:v>
+        <x:v>23.56</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>526132</x:v>
+        <x:v>3585</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.406883320107014</x:v>
+        <x:v>0.00246724432070983</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>862</x:v>
+        <x:v>-283</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>16.679</x:v>
+        <x:v>24.943</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1448,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1356</x:v>
+        <x:v>5001</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.281</x:v>
+        <x:v>23.5</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1811</x:v>
+        <x:v>7010</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.563</x:v>
+        <x:v>23.316</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>3167</x:v>
+        <x:v>12011</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00244919426071578</x:v>
+        <x:v>0.00826612874087748</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-455</x:v>
+        <x:v>-2009</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>24.404</x:v>
+        <x:v>22.86</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1477,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>8032</x:v>
+        <x:v>5483</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.372</x:v>
+        <x:v>23.544</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>9291</x:v>
+        <x:v>7772</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.658</x:v>
+        <x:v>23.24</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>17323</x:v>
+        <x:v>13255</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0133967136654182</x:v>
+        <x:v>0.00912226596122978</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-1259</x:v>
+        <x:v>-2289</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>25.484</x:v>
+        <x:v>22.512</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1506,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>5483</x:v>
+        <x:v>265903</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.544</x:v>
+        <x:v>23.549</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>7772</x:v>
+        <x:v>271311</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.24</x:v>
+        <x:v>23.705</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>13255</x:v>
+        <x:v>537214</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0102507325310349</x:v>
+        <x:v>0.369717765831467</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-2289</x:v>
+        <x:v>-5408</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>22.512</x:v>
+        <x:v>31.373</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1535,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>10000</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.48</x:v>
+        <x:v>23.462</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>14451</x:v>
+        <x:v>6271</x:v>
       </x:c>
       <x:c r="E35" s="0">
+        <x:v>23.734</x:v>
+      </x:c>
+      <x:c r="F35" s="0">
+        <x:v>6650</x:v>
+      </x:c>
+      <x:c r="G35" s="0">
+        <x:v>0.00457661777760679</x:v>
+      </x:c>
+      <x:c r="H35" s="0">
+        <x:v>-5892</x:v>
+      </x:c>
+      <x:c r="I35" s="0">
         <x:v>23.751</x:v>
-      </x:c>
-      <x:c r="F35" s="0">
-        <x:v>24451</x:v>
-      </x:c>
-      <x:c r="G35" s="0">
-        <x:v>0.018909140785842</x:v>
-      </x:c>
-      <x:c r="H35" s="0">
-        <x:v>-4451</x:v>
-      </x:c>
-      <x:c r="I35" s="0">
-        <x:v>24.359</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1564,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>224</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.393</x:v>
+        <x:v>23.48</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>6271</x:v>
+        <x:v>19251</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.734</x:v>
+        <x:v>23.697</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>6495</x:v>
+        <x:v>29251</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00502289760762519</x:v>
+        <x:v>0.0201309243026731</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-6047</x:v>
+        <x:v>-9251</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.746</x:v>
+        <x:v>23.931</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1593,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>0</x:v>
+        <x:v>26846</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0</x:v>
+        <x:v>23.599</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>7010</x:v>
+        <x:v>40181</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.316</x:v>
+        <x:v>23.621</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>7010</x:v>
+        <x:v>67027</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00542117201377253</x:v>
+        <x:v>0.0461288661322783</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-7010</x:v>
+        <x:v>-13335</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>23.316</x:v>
+        <x:v>23.665</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,28 +1622,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>240483</x:v>
+        <x:v>2750</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.551</x:v>
+        <x:v>23.718</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>252450</x:v>
+        <x:v>21924</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.717</x:v>
+        <x:v>23.642</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>492933</x:v>
+        <x:v>24674</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.381208927855198</x:v>
+        <x:v>0.0169809724879203</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-11967</x:v>
+        <x:v>-19174</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>27.041</x:v>
+        <x:v>23.631</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1651,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>22296</x:v>
+        <x:v>821236</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.608</x:v>
+        <x:v>23.692</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>37681</x:v>
+        <x:v>840707</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.626</x:v>
+        <x:v>23.664</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>59977</x:v>
+        <x:v>1661943</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.0463831146747554</x:v>
+        <x:v>1.1437711096495</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-15385</x:v>
+        <x:v>-19471</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.651</x:v>
+        <x:v>22.47</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1680,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>2750</x:v>
+        <x:v>2071123</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.718</x:v>
+        <x:v>23.675</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>21924</x:v>
+        <x:v>2092959</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.642</x:v>
+        <x:v>23.639</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>24674</x:v>
+        <x:v>4164082</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.0190815974704456</x:v>
+        <x:v>2.86577619678383</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-19174</x:v>
+        <x:v>-21836</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.631</x:v>
+        <x:v>20.23</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1709,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>3386</x:v>
+        <x:v>5890</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.61</x:v>
+        <x:v>23.585</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>28431</x:v>
+        <x:v>28593</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.742</x:v>
+        <x:v>23.741</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>31817</x:v>
+        <x:v>34483</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0246056248162911</x:v>
+        <x:v>0.0237316557631902</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-25045</x:v>
+        <x:v>-22703</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>23.76</x:v>
+        <x:v>23.781</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1738,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>78401</x:v>
+        <x:v>80079</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.65</x:v>
+        <x:v>23.648</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>108588</x:v>
+        <x:v>112840</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.71</x:v>
+        <x:v>23.704</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>186989</x:v>
+        <x:v>192919</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.144607636759388</x:v>
+        <x:v>0.132769402261372</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-30187</x:v>
+        <x:v>-32761</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>23.865</x:v>
+        <x:v>23.839</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,28 +1767,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>151098</x:v>
+        <x:v>306555</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.585</x:v>
+        <x:v>23.549</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>191310</x:v>
+        <x:v>345974</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.713</x:v>
+        <x:v>23.611</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>342408</x:v>
+        <x:v>652529</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.264800665747764</x:v>
+        <x:v>0.449079070947968</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-40212</x:v>
+        <x:v>-39419</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>24.196</x:v>
+        <x:v>24.095</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,28 +1796,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1624079</x:v>
+        <x:v>166986</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.613</x:v>
+        <x:v>23.579</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>1680283</x:v>
+        <x:v>209469</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.669</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>3304362</x:v>
+        <x:v>376455</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2.55542293834143</x:v>
+        <x:v>0.259081300070521</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-56204</x:v>
+        <x:v>-42483</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>25.3</x:v>
+        <x:v>24.175</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1825,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>103745</x:v>
+        <x:v>115438</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.529</x:v>
+        <x:v>23.53</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>199521</x:v>
+        <x:v>202394</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>23.676</x:v>
+        <x:v>23.674</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>303266</x:v>
+        <x:v>317832</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.234530264183843</x:v>
+        <x:v>0.218736177668018</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-95776</x:v>
+        <x:v>-86956</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.835</x:v>
+        <x:v>23.865</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1854,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>10138555</x:v>
+        <x:v>196651</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.642</x:v>
+        <x:v>23.613</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>10266647</x:v>
+        <x:v>384390</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.65</x:v>
+        <x:v>23.72</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>20405202</x:v>
+        <x:v>581041</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>15.7803295317796</x:v>
+        <x:v>0.399880085732095</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-128092</x:v>
+        <x:v>-187739</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>24.272</x:v>
+        <x:v>23.831</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1883,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>174308</x:v>
+        <x:v>10739727</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.621</x:v>
+        <x:v>23.637</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>377413</x:v>
+        <x:v>10951928</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.723</x:v>
+        <x:v>23.643</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>551721</x:v>
+        <x:v>21691655</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.426672531328187</x:v>
+        <x:v>14.9284832930396</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-203105</x:v>
+        <x:v>-212201</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.81</x:v>
+        <x:v>23.993</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1912,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>1975827</x:v>
+        <x:v>3781282</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.653</x:v>
+        <x:v>23.635</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>2214438</x:v>
+        <x:v>4052014</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.615</x:v>
+        <x:v>23.604</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>4190265</x:v>
+        <x:v>7833296</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>3.24053457179608</x:v>
+        <x:v>5.39097770388815</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-238611</x:v>
+        <x:v>-270732</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.296</x:v>
+        <x:v>23.179</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,28 +1941,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>195442</x:v>
+        <x:v>219844</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.716</x:v>
+        <x:v>23.693</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>737096</x:v>
+        <x:v>737584</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.741</x:v>
+        <x:v>23.74</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>932538</x:v>
+        <x:v>957428</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.721176734290928</x:v>
+        <x:v>0.65891458730504</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-541654</x:v>
+        <x:v>-517740</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.749</x:v>
+        <x:v>23.76</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,28 +1970,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2738424</x:v>
+        <x:v>2148929</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.664</x:v>
+        <x:v>23.645</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>3390267</x:v>
+        <x:v>2777724</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>23.71</x:v>
+        <x:v>23.599</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>6128691</x:v>
+        <x:v>4926653</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>4.73961314269038</x:v>
+        <x:v>3.39058762464659</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-651843</x:v>
+        <x:v>-628795</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.9</x:v>
+        <x:v>23.442</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1996,28 +1999,57 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>570635</x:v>
+        <x:v>2897925</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.612</x:v>
+        <x:v>23.658</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2091623</x:v>
+        <x:v>3619791</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.485</x:v>
+        <x:v>23.699</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2662258</x:v>
+        <x:v>6517716</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.0588528620602</x:v>
+        <x:v>4.4855781827056</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1520988</x:v>
+        <x:v>-721866</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.437</x:v>
+        <x:v>23.866</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
+      <x:c r="A52" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B52" s="0">
+        <x:v>618231</x:v>
+      </x:c>
+      <x:c r="C52" s="0">
+        <x:v>23.607</x:v>
+      </x:c>
+      <x:c r="D52" s="0">
+        <x:v>2157359</x:v>
+      </x:c>
+      <x:c r="E52" s="0">
+        <x:v>23.486</x:v>
+      </x:c>
+      <x:c r="F52" s="0">
+        <x:v>2775590</x:v>
+      </x:c>
+      <x:c r="G52" s="0">
+        <x:v>1.91019767478912</x:v>
+      </x:c>
+      <x:c r="H52" s="0">
+        <x:v>-1539128</x:v>
+      </x:c>
+      <x:c r="I52" s="0">
+        <x:v>23.438</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -46,118 +46,121 @@
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
+    <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
@@ -166,9 +169,6 @@
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
@@ -184,10 +184,10 @@
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
@@ -578,28 +578,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>9438988</x:v>
+        <x:v>10872653</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.65</x:v>
+        <x:v>23.6458911029338</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>7714149</x:v>
+        <x:v>9363134</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.651</x:v>
+        <x:v>23.6441289355252</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>17153137</x:v>
+        <x:v>20235787</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>11.8050152986353</x:v>
+        <x:v>11.7983449912501</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1724839</x:v>
+        <x:v>1509519</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.644</x:v>
+        <x:v>23.6568213459956</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -607,28 +607,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1265154</x:v>
+        <x:v>1378367</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.679</x:v>
+        <x:v>23.6765622178246</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>725378</x:v>
+        <x:v>832227</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.726</x:v>
+        <x:v>23.7128075017488</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1990532</x:v>
+        <x:v>2210594</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>1.36991039670605</x:v>
+        <x:v>1.2888725626331</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>539776</x:v>
+        <x:v>546140</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.617</x:v>
+        <x:v>23.6213304019819</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -636,28 +636,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>5297384</x:v>
+        <x:v>2705253</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.643</x:v>
+        <x:v>23.633796643114</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>4966931</x:v>
+        <x:v>2206938</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.649</x:v>
+        <x:v>23.6324272074738</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>10264315</x:v>
+        <x:v>4912191</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.06403706826407</x:v>
+        <x:v>2.86402125506233</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>330453</x:v>
+        <x:v>498315</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.542</x:v>
+        <x:v>23.6398616011282</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -665,28 +665,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>7511319</x:v>
+        <x:v>2390253</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.615</x:v>
+        <x:v>23.6348429714629</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>7182388</x:v>
+        <x:v>1905976</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.62</x:v>
+        <x:v>23.692654776196</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>14693707</x:v>
+        <x:v>4296229</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>10.1124031090444</x:v>
+        <x:v>2.50488858690861</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>328931</x:v>
+        <x:v>484277</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.495</x:v>
+        <x:v>23.4073122146068</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -694,28 +694,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>1349191</x:v>
+        <x:v>8748002</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.616</x:v>
+        <x:v>23.6173742937469</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1152107</x:v>
+        <x:v>8425415</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.68</x:v>
+        <x:v>23.6184251105106</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>2501298</x:v>
+        <x:v>17173417</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.72142629983343</x:v>
+        <x:v>10.0128499299088</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>197084</x:v>
+        <x:v>322587</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.238</x:v>
+        <x:v>23.5899287757206</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -723,28 +723,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>297571</x:v>
+        <x:v>228368</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.652</x:v>
+        <x:v>23.4809618472118</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>101315</x:v>
+        <x:v>22665</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.613</x:v>
+        <x:v>23.7197553026631</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>398886</x:v>
+        <x:v>251033</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.274518610351649</x:v>
+        <x:v>0.146363170268026</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>196256</x:v>
+        <x:v>205703</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.673</x:v>
+        <x:v>23.4546508373198</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -752,28 +752,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>5242788</x:v>
+        <x:v>299611</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.667</x:v>
+        <x:v>23.6520236385339</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>5047130</x:v>
+        <x:v>102905</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.612</x:v>
+        <x:v>23.6127228975933</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>10289918</x:v>
+        <x:v>402516</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>7.08165739081446</x:v>
+        <x:v>0.234684355617009</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>195658</x:v>
+        <x:v>196706</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>25.085</x:v>
+        <x:v>23.6725834727356</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -781,28 +781,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>476836</x:v>
+        <x:v>1150240</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.671</x:v>
+        <x:v>23.6068910093811</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>337212</x:v>
+        <x:v>960476</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.706</x:v>
+        <x:v>23.6077720180907</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>814048</x:v>
+        <x:v>2110716</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.56023857874064</x:v>
+        <x:v>1.23063933943125</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>139624</x:v>
+        <x:v>189764</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.586</x:v>
+        <x:v>23.6024318510509</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -810,28 +810,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>125262</x:v>
+        <x:v>659263</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.315</x:v>
+        <x:v>23.6214666359966</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>19604</x:v>
+        <x:v>488329</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.739</x:v>
+        <x:v>23.6685247592166</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>144866</x:v>
+        <x:v>1147592</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.0996986933790656</x:v>
+        <x:v>0.669096108058399</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>105658</x:v>
+        <x:v>170934</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.236</x:v>
+        <x:v>23.4870296822374</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -839,28 +839,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>917781</x:v>
+        <x:v>1570874</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.691</x:v>
+        <x:v>23.6126845316078</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>812349</x:v>
+        <x:v>1453743</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.62</x:v>
+        <x:v>23.6667235776226</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>1730130</x:v>
+        <x:v>3024617</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.19069830309336</x:v>
+        <x:v>1.76348341838151</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>105432</x:v>
+        <x:v>117131</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>24.239</x:v>
+        <x:v>22.9419920174929</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -868,28 +868,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1939968</x:v>
+        <x:v>528284</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.631</x:v>
+        <x:v>23.667895615688</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1864237</x:v>
+        <x:v>414248</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.634</x:v>
+        <x:v>23.6990240220388</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>3804205</x:v>
+        <x:v>942532</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.61810409513694</x:v>
+        <x:v>0.549537198691258</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>75731</x:v>
+        <x:v>114036</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.567</x:v>
+        <x:v>23.5548183411959</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -897,28 +897,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1320752</x:v>
+        <x:v>6290772</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.614</x:v>
+        <x:v>23.6357162784809</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1246903</x:v>
+        <x:v>6186175</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.645</x:v>
+        <x:v>23.6450360043818</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>2567655</x:v>
+        <x:v>12476947</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.76709406312195</x:v>
+        <x:v>7.27460341144842</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>73849</x:v>
+        <x:v>104597</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.098</x:v>
+        <x:v>23.0845202080888</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -926,28 +926,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>760659</x:v>
+        <x:v>1262953</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.622</x:v>
+        <x:v>23.6681218816442</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>690953</x:v>
+        <x:v>1176628</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.623</x:v>
+        <x:v>23.606380831562</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1451612</x:v>
+        <x:v>2439581</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.999018539155993</x:v>
+        <x:v>1.42238195490489</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>69706</x:v>
+        <x:v>86325</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.62</x:v>
+        <x:v>24.5096654469622</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -955,28 +955,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>1948262</x:v>
+        <x:v>336307</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.664</x:v>
+        <x:v>23.7305709382758</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>1881891</x:v>
+        <x:v>270657</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.684</x:v>
+        <x:v>23.6586106813027</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>3830153</x:v>
+        <x:v>606964</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.6359618512412</x:v>
+        <x:v>0.353886442334521</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>66371</x:v>
+        <x:v>65650</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.09</x:v>
+        <x:v>24.0272434024273</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -984,28 +984,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>313306</x:v>
+        <x:v>2055310</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.735</x:v>
+        <x:v>23.6677562652634</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>247620</x:v>
+        <x:v>1993394</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.659</x:v>
+        <x:v>23.6909237250831</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>560926</x:v>
+        <x:v>4048704</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.386036677221334</x:v>
+        <x:v>2.36057073339695</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>65686</x:v>
+        <x:v>61916</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>24.021</x:v>
+        <x:v>22.9218767607764</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1013,28 +1013,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>130260</x:v>
+        <x:v>138642</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.563</x:v>
+        <x:v>23.5642751969781</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>77993</x:v>
+        <x:v>93224</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.661</x:v>
+        <x:v>23.658063209017</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>208253</x:v>
+        <x:v>231866</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.143322463464654</x:v>
+        <x:v>0.135187974638259</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>52267</x:v>
+        <x:v>45418</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.418</x:v>
+        <x:v>23.3717679612057</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1042,28 +1042,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>2747412</x:v>
+        <x:v>1367003</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.639</x:v>
+        <x:v>23.6140191205428</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>2713123</x:v>
+        <x:v>1325132</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.634</x:v>
+        <x:v>23.643206974418</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>5460535</x:v>
+        <x:v>2692135</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>3.75801226409686</x:v>
+        <x:v>1.56963193440508</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>34289</x:v>
+        <x:v>41871</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>24.016</x:v>
+        <x:v>22.6902829026029</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1071,28 +1071,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>447446</x:v>
+        <x:v>2147909</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.656</x:v>
+        <x:v>23.616266837295</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>422842</x:v>
+        <x:v>2122730</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.677</x:v>
+        <x:v>23.6588227077209</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>870288</x:v>
+        <x:v>4270639</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.5989436890884</x:v>
+        <x:v>2.48996850258839</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>24604</x:v>
+        <x:v>25179</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.286</x:v>
+        <x:v>20.0285698346676</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1100,28 +1100,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>95228</x:v>
+        <x:v>96247</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.471</x:v>
+        <x:v>23.471626025125</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>71627</x:v>
+        <x:v>73169</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.697</x:v>
+        <x:v>23.6960517529979</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>166855</x:v>
+        <x:v>169416</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.114831813425952</x:v>
+        <x:v>0.0987769052440429</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>23601</x:v>
+        <x:v>23078</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.786</x:v>
+        <x:v>22.7600823002472</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1129,28 +1129,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>570258</x:v>
+        <x:v>1313109</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.659</x:v>
+        <x:v>23.5978468665971</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>551819</x:v>
+        <x:v>1300107</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.684</x:v>
+        <x:v>23.6548116172329</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1122077</x:v>
+        <x:v>2613216</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.772228202412586</x:v>
+        <x:v>1.5236187208659</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>18439</x:v>
+        <x:v>13002</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.915</x:v>
+        <x:v>17.9017792573948</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1158,28 +1158,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>784662</x:v>
+        <x:v>882147</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.615</x:v>
+        <x:v>23.6173806321956</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>775844</x:v>
+        <x:v>870029</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.617</x:v>
+        <x:v>23.6196212019847</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1560506</x:v>
+        <x:v>1752176</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.0739608273176</x:v>
+        <x:v>1.02159490675548</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>8818</x:v>
+        <x:v>12118</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.476</x:v>
+        <x:v>23.4565157458262</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1187,28 +1187,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>1825022</x:v>
+        <x:v>19665</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.606</x:v>
+        <x:v>23.4711634581852</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1818447</x:v>
+        <x:v>9664</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.661</x:v>
+        <x:v>23.6551787148643</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>3643469</x:v>
+        <x:v>29329</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.50748345827959</x:v>
+        <x:v>0.0171000841355157</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>6575</x:v>
+        <x:v>10001</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.59</x:v>
+        <x:v>23.2933488955868</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1216,28 +1216,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>1559810</x:v>
+        <x:v>578071</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.666</x:v>
+        <x:v>23.6629900465622</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>1553375</x:v>
+        <x:v>568783</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.704</x:v>
+        <x:v>23.6876158182875</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>3113185</x:v>
+        <x:v>1146854</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>2.14253500992163</x:v>
+        <x:v>0.668665821922083</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>6435</x:v>
+        <x:v>9288</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>14.413</x:v>
+        <x:v>22.1549452232144</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1245,28 +1245,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>1146815</x:v>
+        <x:v>893900</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.596</x:v>
+        <x:v>23.6832431127145</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>1141482</x:v>
+        <x:v>885333</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.663</x:v>
+        <x:v>23.6598958140443</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>2288297</x:v>
+        <x:v>1779233</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>1.57483620009689</x:v>
+        <x:v>1.03737031595643</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>5333</x:v>
+        <x:v>8567</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>9.247</x:v>
+        <x:v>26.0960053367877</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1274,28 +1274,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>6454</x:v>
+        <x:v>6954</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.24</x:v>
+        <x:v>23.2644461438956</x:v>
       </x:c>
       <x:c r="D26" s="0">
         <x:v>1454</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.36</x:v>
+        <x:v>23.3600006103516</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>7908</x:v>
+        <x:v>8408</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00544238998275407</x:v>
+        <x:v>0.00490223012756713</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>5000</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.205</x:v>
+        <x:v>23.2391850176724</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1303,28 +1303,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>398497</x:v>
+        <x:v>10001</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.561</x:v>
+        <x:v>23.5300027326445</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>397635</x:v>
+        <x:v>7010</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.581</x:v>
+        <x:v>23.3164620664763</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>796132</x:v>
+        <x:v>17011</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.547908551055888</x:v>
+        <x:v>0.00991815374643726</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>862</x:v>
+        <x:v>2991</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>14.171</x:v>
+        <x:v>24.0304775136006</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1332,28 +1332,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>628</x:v>
+        <x:v>603497</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.553</x:v>
+        <x:v>23.5686152182389</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>0</x:v>
+        <x:v>602745</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>0</x:v>
+        <x:v>23.5863545652642</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>628</x:v>
+        <x:v>1206242</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.000432197889373995</x:v>
+        <x:v>0.703291611981069</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>628</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.553</x:v>
+        <x:v>9.35012755495436</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1361,28 +1361,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>9156</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.392</x:v>
+        <x:v>23.5526433112515</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>9352</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.657</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>18508</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0127374498989393</x:v>
+        <x:v>0.000366151346350161</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-196</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>36.026</x:v>
+        <x:v>23.5526433112515</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1390,28 +1390,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>237127</x:v>
+        <x:v>7502</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.657</x:v>
+        <x:v>23.5731698445275</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>237365</x:v>
+        <x:v>7772</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.649</x:v>
+        <x:v>23.2399997711182</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>474492</x:v>
+        <x:v>15274</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.32655165752364</x:v>
+        <x:v>0.00890540710852288</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-238</x:v>
+        <x:v>-270</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>15.214</x:v>
+        <x:v>13.9828075832791</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1422,25 +1422,25 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.323</x:v>
+        <x:v>23.323816129614</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1934</x:v>
+        <x:v>2222</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.56</x:v>
+        <x:v>23.5604321551044</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>3585</x:v>
+        <x:v>3873</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00246724432070983</x:v>
+        <x:v>0.00225812765034104</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-283</x:v>
+        <x:v>-571</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>24.943</x:v>
+        <x:v>24.2445881237291</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1448,28 +1448,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>5001</x:v>
+        <x:v>269083</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.5</x:v>
+        <x:v>23.6483261545975</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>7010</x:v>
+        <x:v>274603</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.316</x:v>
+        <x:v>23.6373106380807</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>12011</x:v>
+        <x:v>543686</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00826612874087748</x:v>
+        <x:v>0.316992612884926</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-2009</x:v>
+        <x:v>-5520</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>22.86</x:v>
+        <x:v>23.1003381324851</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1477,28 +1477,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>5483</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.544</x:v>
+        <x:v>23.4634826831264</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>7772</x:v>
+        <x:v>6271</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.24</x:v>
+        <x:v>23.7336531562909</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>13255</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00912226596122978</x:v>
+        <x:v>0.00387723957520473</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-2289</x:v>
+        <x:v>-5892</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>22.512</x:v>
+        <x:v>23.7510317390012</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1506,28 +1506,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>265903</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.549</x:v>
+        <x:v>23.4799999237061</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>271311</x:v>
+        <x:v>19251</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.705</x:v>
+        <x:v>23.6966220243808</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>537214</x:v>
+        <x:v>29251</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.369717765831467</x:v>
+        <x:v>0.0170546067389945</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-5408</x:v>
+        <x:v>-9251</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>31.373</x:v>
+        <x:v>23.9307827644897</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1535,28 +1535,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>379</x:v>
+        <x:v>45877</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.462</x:v>
+        <x:v>23.5859684703744</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>6271</x:v>
+        <x:v>56719</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.734</x:v>
+        <x:v>23.6020998092466</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>6650</x:v>
+        <x:v>102596</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00457661777760679</x:v>
+        <x:v>0.0598179355575496</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-5892</x:v>
+        <x:v>-10842</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.751</x:v>
+        <x:v>23.670358196393</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1564,28 +1564,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>10000</x:v>
+        <x:v>2495010</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.48</x:v>
+        <x:v>23.6711151357325</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>19251</x:v>
+        <x:v>2514162</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.697</x:v>
+        <x:v>23.6289539073523</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>29251</x:v>
+        <x:v>5009172</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0201309243026731</x:v>
+        <x:v>2.9205654011139</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-9251</x:v>
+        <x:v>-19152</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.931</x:v>
+        <x:v>18.1364368636507</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1593,28 +1593,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>26846</x:v>
+        <x:v>2750</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.599</x:v>
+        <x:v>23.7184724703702</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>40181</x:v>
+        <x:v>22069</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.621</x:v>
+        <x:v>23.6420078527361</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>67027</x:v>
+        <x:v>24819</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.0461288661322783</x:v>
+        <x:v>0.0144705577469182</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-13335</x:v>
+        <x:v>-19319</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>23.665</x:v>
+        <x:v>23.6311233505106</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1622,28 +1622,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>2750</x:v>
+        <x:v>6755</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.718</x:v>
+        <x:v>23.5794527202073</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>21924</x:v>
+        <x:v>28654</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.642</x:v>
+        <x:v>23.7402350867777</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>24674</x:v>
+        <x:v>35409</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.0169809724879203</x:v>
+        <x:v>0.0206449888899886</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-19174</x:v>
+        <x:v>-21899</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.631</x:v>
+        <x:v>23.7898302685752</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1651,28 +1651,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>821236</x:v>
+        <x:v>2991972</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.692</x:v>
+        <x:v>23.637085968762</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>840707</x:v>
+        <x:v>3015934</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.664</x:v>
+        <x:v>23.6355895018664</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>1661943</x:v>
+        <x:v>6007906</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>1.1437711096495</x:v>
+        <x:v>3.50287081312932</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-19471</x:v>
+        <x:v>-23962</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>22.47</x:v>
+        <x:v>23.4487358564806</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1680,28 +1680,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>2071123</x:v>
+        <x:v>278765</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.675</x:v>
+        <x:v>23.549609496188</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>2092959</x:v>
+        <x:v>304168</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.639</x:v>
+        <x:v>23.704814779881</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>4164082</x:v>
+        <x:v>582933</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.86577619678383</x:v>
+        <x:v>0.339875322901176</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-21836</x:v>
+        <x:v>-25403</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>20.23</x:v>
+        <x:v>25.4079916057955</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1709,28 +1709,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>5890</x:v>
+        <x:v>6116733</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.585</x:v>
+        <x:v>23.6627158044095</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>28593</x:v>
+        <x:v>6145869</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.741</x:v>
+        <x:v>23.6087722151933</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>34483</x:v>
+        <x:v>12262602</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0237316557631902</x:v>
+        <x:v>7.14963094276462</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-22703</x:v>
+        <x:v>-29136</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>23.781</x:v>
+        <x:v>12.2840010627556</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1738,28 +1738,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>80079</x:v>
+        <x:v>192336</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.648</x:v>
+        <x:v>23.582227555639</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>112840</x:v>
+        <x:v>229824</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.704</x:v>
+        <x:v>23.6952989486906</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>192919</x:v>
+        <x:v>422160</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.132769402261372</x:v>
+        <x:v>0.246137663017809</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-32761</x:v>
+        <x:v>-37488</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>23.839</x:v>
+        <x:v>24.27542324057</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1767,28 +1767,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>306555</x:v>
+        <x:v>106177</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.549</x:v>
+        <x:v>23.6483921983817</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>345974</x:v>
+        <x:v>146607</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.611</x:v>
+        <x:v>23.7016367778648</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>652529</x:v>
+        <x:v>252784</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.449079070947968</x:v>
+        <x:v>0.147384079515572</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-39419</x:v>
+        <x:v>-40430</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>24.095</x:v>
+        <x:v>23.8414673421927</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1796,28 +1796,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>166986</x:v>
+        <x:v>328749</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.579</x:v>
+        <x:v>23.5528565754303</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>209469</x:v>
+        <x:v>390773</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.7</x:v>
+        <x:v>23.6158853456064</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>376455</x:v>
+        <x:v>719522</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.259081300070521</x:v>
+        <x:v>0.419512657688791</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-42483</x:v>
+        <x:v>-62024</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>24.175</x:v>
+        <x:v>23.9499599806927</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1825,28 +1825,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>115438</x:v>
+        <x:v>136559</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.53</x:v>
+        <x:v>23.5542061546445</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>202394</x:v>
+        <x:v>216052</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>23.674</x:v>
+        <x:v>23.6712858739988</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>317832</x:v>
+        <x:v>352611</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.218736177668018</x:v>
+        <x:v>0.205587567496619</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-86956</x:v>
+        <x:v>-79493</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.865</x:v>
+        <x:v>23.8724141418375</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1854,28 +1854,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>196651</x:v>
+        <x:v>204247</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.613</x:v>
+        <x:v>23.6126149200192</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>384390</x:v>
+        <x:v>390004</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.72</x:v>
+        <x:v>23.7183334043633</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>581041</x:v>
+        <x:v>594251</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.399880085732095</x:v>
+        <x:v>0.346474209745111</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-187739</x:v>
+        <x:v>-185757</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.831</x:v>
+        <x:v>23.8345749633453</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1883,28 +1883,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>10739727</x:v>
+        <x:v>12653123</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.637</x:v>
+        <x:v>23.637402283656</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>10951928</x:v>
+        <x:v>13035180</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.643</x:v>
+        <x:v>23.6460339193696</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>21691655</x:v>
+        <x:v>25688303</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>14.9284832930396</x:v>
+        <x:v>14.9773992498422</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-212201</x:v>
+        <x:v>-382057</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.993</x:v>
+        <x:v>23.9319000293365</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1912,28 +1912,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>3781282</x:v>
+        <x:v>4333860</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.635</x:v>
+        <x:v>23.6348707898017</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4052014</x:v>
+        <x:v>4741610</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.604</x:v>
+        <x:v>23.6101044077975</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>7833296</x:v>
+        <x:v>9075470</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.39097770388815</x:v>
+        <x:v>5.29139420264411</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-270732</x:v>
+        <x:v>-407750</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.179</x:v>
+        <x:v>23.3468695032902</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1941,28 +1941,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>219844</x:v>
+        <x:v>226880</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.693</x:v>
+        <x:v>23.6888438462959</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>737584</x:v>
+        <x:v>760917</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.74</x:v>
+        <x:v>23.7375273399903</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>957428</x:v>
+        <x:v>987797</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.65891458730504</x:v>
+        <x:v>0.575928664762182</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-517740</x:v>
+        <x:v>-534037</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.76</x:v>
+        <x:v>23.7582100100101</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1970,28 +1970,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2148929</x:v>
+        <x:v>3490740</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.645</x:v>
+        <x:v>23.6570016639057</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2777724</x:v>
+        <x:v>4067419</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>23.599</x:v>
+        <x:v>23.6961613546415</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>4926653</x:v>
+        <x:v>7558159</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>3.39058762464659</x:v>
+        <x:v>4.40673581811877</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-628795</x:v>
+        <x:v>-576679</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.442</x:v>
+        <x:v>23.9332018899119</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1999,28 +1999,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2897925</x:v>
+        <x:v>2604322</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.658</x:v>
+        <x:v>23.6468010765501</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>3619791</x:v>
+        <x:v>3398149</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.699</x:v>
+        <x:v>23.6034588979939</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>6517716</x:v>
+        <x:v>6002471</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>4.4855781827056</x:v>
+        <x:v>3.49970197146146</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-721866</x:v>
+        <x:v>-793827</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.866</x:v>
+        <x:v>23.4612654614622</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2028,28 +2028,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>618231</x:v>
+        <x:v>719135</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.607</x:v>
+        <x:v>23.6065609861004</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>2157359</x:v>
+        <x:v>2320369</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.486</x:v>
+        <x:v>23.494289045404</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>2775590</x:v>
+        <x:v>3039504</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>1.91019767478912</x:v>
+        <x:v>1.77216318763806</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1539128</x:v>
+        <x:v>-1601234</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.438</x:v>
+        <x:v>23.4438662576835</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -52,139 +52,142 @@
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
+    <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
+    <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
+    <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
@@ -541,7 +544,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I52"/>
+  <x:dimension ref="A1:I53"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -578,28 +581,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>10872653</x:v>
+        <x:v>13204664</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.6458911029338</x:v>
+        <x:v>23.6121962864324</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>9363134</x:v>
+        <x:v>10475553</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.6441289355252</x:v>
+        <x:v>23.6209278178224</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>20235787</x:v>
+        <x:v>23680217</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>11.7983449912501</x:v>
+        <x:v>11.784033235128</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1509519</x:v>
+        <x:v>2729111</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.6568213459956</x:v>
+        <x:v>23.578680749744</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -607,28 +610,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1378367</x:v>
+        <x:v>1650244</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.6765622178246</x:v>
+        <x:v>23.6314488958033</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>832227</x:v>
+        <x:v>1066091</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.7128075017488</x:v>
+        <x:v>23.6459546782437</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>2210594</x:v>
+        <x:v>2716335</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>1.2888725626331</x:v>
+        <x:v>1.35173516010184</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>546140</x:v>
+        <x:v>584153</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.6213304019819</x:v>
+        <x:v>23.6049755504508</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -636,28 +639,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2705253</x:v>
+        <x:v>3339361</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.633796643114</x:v>
+        <x:v>23.6121406144223</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>2206938</x:v>
+        <x:v>2943990</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.6324272074738</x:v>
+        <x:v>23.5957396470771</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>4912191</x:v>
+        <x:v>6283351</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.86402125506233</x:v>
+        <x:v>3.1267963892381</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>498315</x:v>
+        <x:v>395371</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.6398616011282</x:v>
+        <x:v>23.7342646039274</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -665,28 +668,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>2390253</x:v>
+        <x:v>2784960</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.6348429714629</x:v>
+        <x:v>23.6058720628352</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1905976</x:v>
+        <x:v>2426366</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.692654776196</x:v>
+        <x:v>23.6299786143894</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>4296229</x:v>
+        <x:v>5211326</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.50488858690861</x:v>
+        <x:v>2.59332246757226</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>484277</x:v>
+        <x:v>358594</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.4073122146068</x:v>
+        <x:v>23.4427591354905</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -694,28 +697,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>8748002</x:v>
+        <x:v>372774</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.6173742937469</x:v>
+        <x:v>23.5913318211205</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>8425415</x:v>
+        <x:v>144790</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.6184251105106</x:v>
+        <x:v>23.5571018137057</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>17173417</x:v>
+        <x:v>517564</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>10.0128499299088</x:v>
+        <x:v>0.257556397279036</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>322587</x:v>
+        <x:v>227984</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.5899287757206</x:v>
+        <x:v>23.6130709026946</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -723,28 +726,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>228368</x:v>
+        <x:v>265802</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.4809618472118</x:v>
+        <x:v>23.4739481179915</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>22665</x:v>
+        <x:v>65448</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.7197553026631</x:v>
+        <x:v>23.4996188745101</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>251033</x:v>
+        <x:v>331250</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.146363170268026</x:v>
+        <x:v>0.164840592851668</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>205703</x:v>
+        <x:v>200354</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.4546508373198</x:v>
+        <x:v>23.4655624622391</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -752,28 +755,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>299611</x:v>
+        <x:v>7736696</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.6520236385339</x:v>
+        <x:v>23.5933696227755</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>102905</x:v>
+        <x:v>7556996</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.6127228975933</x:v>
+        <x:v>23.6032359522409</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>402516</x:v>
+        <x:v>15293692</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.234684355617009</x:v>
+        <x:v>7.61063020730811</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>196706</x:v>
+        <x:v>179700</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.6725834727356</x:v>
+        <x:v>23.1784569221373</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -781,28 +784,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>1150240</x:v>
+        <x:v>636736</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.6068910093811</x:v>
+        <x:v>23.6237443723664</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>960476</x:v>
+        <x:v>467125</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.6077720180907</x:v>
+        <x:v>23.6670168588264</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>2110716</x:v>
+        <x:v>1103861</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.23063933943125</x:v>
+        <x:v>0.549316533330823</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>189764</x:v>
+        <x:v>169611</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.6024318510509</x:v>
+        <x:v>23.5045677845413</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -810,28 +813,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>659263</x:v>
+        <x:v>10014273</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.6214666359966</x:v>
+        <x:v>23.5915963384155</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>488329</x:v>
+        <x:v>9868119</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.6685247592166</x:v>
+        <x:v>23.5889444576704</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1147592</x:v>
+        <x:v>19882392</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.669096108058399</x:v>
+        <x:v>9.89411406668456</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>170934</x:v>
+        <x:v>146154</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.4870296822374</x:v>
+        <x:v>23.7706477141353</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -839,28 +842,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1570874</x:v>
+        <x:v>1724633</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.6126845316078</x:v>
+        <x:v>23.591472198892</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1453743</x:v>
+        <x:v>1586460</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.6667235776226</x:v>
+        <x:v>23.642009909483</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>3024617</x:v>
+        <x:v>3311093</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.76348341838151</x:v>
+        <x:v>1.64770576032304</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>117131</x:v>
+        <x:v>138173</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.9419920174929</x:v>
+        <x:v>23.011213708852</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -868,28 +871,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>528284</x:v>
+        <x:v>3194243</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.667895615688</x:v>
+        <x:v>23.5671392552488</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>414248</x:v>
+        <x:v>3071157</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.6990240220388</x:v>
+        <x:v>23.6033565604485</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>942532</x:v>
+        <x:v>6265400</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.549537198691258</x:v>
+        <x:v>3.11786339759348</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>114036</x:v>
+        <x:v>123086</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.5548183411959</x:v>
+        <x:v>22.6634700289748</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -897,28 +900,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>6290772</x:v>
+        <x:v>1326231</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.6357162784809</x:v>
+        <x:v>23.6541493327598</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>6186175</x:v>
+        <x:v>1209968</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.6450360043818</x:v>
+        <x:v>23.6010183607036</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>12476947</x:v>
+        <x:v>2536199</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>7.27460341144842</x:v>
+        <x:v>1.26209372603715</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>104597</x:v>
+        <x:v>116263</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.0845202080888</x:v>
+        <x:v>24.2070920230133</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -926,28 +929,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1262953</x:v>
+        <x:v>820068</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.6681218816442</x:v>
+        <x:v>23.5739075854174</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1176628</x:v>
+        <x:v>723540</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.606380831562</x:v>
+        <x:v>23.5832980166885</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>2439581</x:v>
+        <x:v>1543608</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>1.42238195490489</x:v>
+        <x:v>0.768148702945139</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>86325</x:v>
+        <x:v>96528</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>24.5096654469622</x:v>
+        <x:v>23.5035202092996</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -955,28 +958,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>336307</x:v>
+        <x:v>387011</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.7305709382758</x:v>
+        <x:v>23.6775626241971</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>270657</x:v>
+        <x:v>318047</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.6586106813027</x:v>
+        <x:v>23.6116496394799</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>606964</x:v>
+        <x:v>705058</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.353886442334521</x:v>
+        <x:v>0.35085940744094</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>65650</x:v>
+        <x:v>68964</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>24.0272434024273</x:v>
+        <x:v>23.9815390039075</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -984,28 +987,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>2055310</x:v>
+        <x:v>173955</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.6677562652634</x:v>
+        <x:v>23.5294623896279</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1993394</x:v>
+        <x:v>121947</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.6909237250831</x:v>
+        <x:v>23.5904819507107</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>4048704</x:v>
+        <x:v>295902</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>2.36057073339695</x:v>
+        <x:v>0.147250297678473</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>61916</x:v>
+        <x:v>52008</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>22.9218767607764</x:v>
+        <x:v>23.3863853165744</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1013,28 +1016,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>138642</x:v>
+        <x:v>1201126</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.5642751969781</x:v>
+        <x:v>23.6009344439583</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>93224</x:v>
+        <x:v>1152489</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.658063209017</x:v>
+        <x:v>23.5927536016462</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>231866</x:v>
+        <x:v>2353615</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.135187974638259</x:v>
+        <x:v>1.17123408888929</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>45418</x:v>
+        <x:v>48637</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.3717679612057</x:v>
+        <x:v>23.7947854375526</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1042,28 +1045,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>1367003</x:v>
+        <x:v>1119153</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.6140191205428</x:v>
+        <x:v>23.5803003860301</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>1325132</x:v>
+        <x:v>1091380</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.643206974418</x:v>
+        <x:v>23.5820316571252</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>2692135</x:v>
+        <x:v>2210533</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.56963193440508</x:v>
+        <x:v>1.10003191015298</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>41871</x:v>
+        <x:v>27773</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.6902829026029</x:v>
+        <x:v>23.512267597072</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1071,28 +1074,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>2147909</x:v>
+        <x:v>2173017</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.616266837295</x:v>
+        <x:v>23.6569162838058</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>2122730</x:v>
+        <x:v>2152071</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.6588227077209</x:v>
+        <x:v>23.6715534558299</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>4270639</x:v>
+        <x:v>4325088</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>2.48996850258839</x:v>
+        <x:v>2.15230209828116</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>25179</x:v>
+        <x:v>20946</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>20.0285698346676</x:v>
+        <x:v>22.1530380524025</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1100,28 +1103,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>96247</x:v>
+        <x:v>27001</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.471626025125</x:v>
+        <x:v>23.5051871220238</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>73169</x:v>
+        <x:v>7010</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.6960517529979</x:v>
+        <x:v>23.3164620664763</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>169416</x:v>
+        <x:v>34011</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0987769052440429</x:v>
+        <x:v>0.016924961218047</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>23078</x:v>
+        <x:v>19991</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.7600823002472</x:v>
+        <x:v>23.5713650340537</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1129,28 +1132,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>1313109</x:v>
+        <x:v>1426525</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.5978468665971</x:v>
+        <x:v>23.6042665824891</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>1300107</x:v>
+        <x:v>1411345</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.6548116172329</x:v>
+        <x:v>23.6261962285409</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>2613216</x:v>
+        <x:v>2837870</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>1.5236187208659</x:v>
+        <x:v>1.41221486259913</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>13002</x:v>
+        <x:v>15180</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>17.9017792573948</x:v>
+        <x:v>21.565380132748</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1158,28 +1161,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>882147</x:v>
+        <x:v>24493</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.6173806321956</x:v>
+        <x:v>23.4344388556618</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>870029</x:v>
+        <x:v>10157</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.6196212019847</x:v>
+        <x:v>23.6490840956934</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1752176</x:v>
+        <x:v>34650</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.02159490675548</x:v>
+        <x:v>0.0172429480522575</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>12118</x:v>
+        <x:v>14336</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.4565157458262</x:v>
+        <x:v>23.2823635415573</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1187,28 +1190,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>19665</x:v>
+        <x:v>595344</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.4711634581852</x:v>
+        <x:v>23.6560013371976</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>9664</x:v>
+        <x:v>582030</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.6551787148643</x:v>
+        <x:v>23.6817932558398</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>29329</x:v>
+        <x:v>1177374</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0171000841355157</x:v>
+        <x:v>0.585898952960422</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>10001</x:v>
+        <x:v>13314</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.2933488955868</x:v>
+        <x:v>22.5284911668997</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1216,28 +1219,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>578071</x:v>
+        <x:v>40598</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.6629900465622</x:v>
+        <x:v>23.492019490389</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>568783</x:v>
+        <x:v>29085</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.6876158182875</x:v>
+        <x:v>23.7340806596771</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1146854</x:v>
+        <x:v>69683</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.668665821922083</x:v>
+        <x:v>0.0346764891522499</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>9288</x:v>
+        <x:v>11513</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>22.1549452232144</x:v>
+        <x:v>22.8805064956226</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1245,28 +1248,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>893900</x:v>
+        <x:v>106430</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.6832431127145</x:v>
+        <x:v>23.4710040936465</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>885333</x:v>
+        <x:v>95318</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.6598958140443</x:v>
+        <x:v>23.6329821407696</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1779233</x:v>
+        <x:v>201748</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>1.03737031595643</x:v>
+        <x:v>0.100396256382304</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>8567</x:v>
+        <x:v>11112</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>26.0960053367877</x:v>
+        <x:v>22.0815671339921</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1274,28 +1277,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>6954</x:v>
+        <x:v>28000</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.2644461438956</x:v>
+        <x:v>23.5014290809631</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1454</x:v>
+        <x:v>19251</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.3600006103516</x:v>
+        <x:v>23.6966220243808</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>8408</x:v>
+        <x:v>47251</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00490223012756713</x:v>
+        <x:v>0.0235136086123295</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>5500</x:v>
+        <x:v>8749</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.2391850176724</x:v>
+        <x:v>23.0719332124372</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1303,28 +1306,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>10001</x:v>
+        <x:v>10300</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.5300027326445</x:v>
+        <x:v>23.4543028877777</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>7010</x:v>
+        <x:v>2222</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.3164620664763</x:v>
+        <x:v>23.5604321551044</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>17011</x:v>
+        <x:v>12522</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00991815374643726</x:v>
+        <x:v>0.00623134763377686</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>2991</x:v>
+        <x:v>8078</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>24.0304775136006</x:v>
+        <x:v>23.4251101133286</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1332,28 +1335,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>603497</x:v>
+        <x:v>75312</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.5686152182389</x:v>
+        <x:v>23.5090740182634</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>602745</x:v>
+        <x:v>69219</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.5863545652642</x:v>
+        <x:v>23.5851066412561</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1206242</x:v>
+        <x:v>144531</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.703291611981069</x:v>
+        <x:v>0.0719232474730397</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>752</x:v>
+        <x:v>6093</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>9.35012755495436</x:v>
+        <x:v>22.6453119747826</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1361,28 +1364,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>628</x:v>
+        <x:v>6954</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.5526433112515</x:v>
+        <x:v>23.2644461438956</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>0</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>0</x:v>
+        <x:v>23.3600006103516</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>628</x:v>
+        <x:v>8408</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.000366151346350161</x:v>
+        <x:v>0.00418408967455645</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>628</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.5526433112515</x:v>
+        <x:v>23.2391850176724</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1390,28 +1393,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>7502</x:v>
+        <x:v>367081</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.5731698445275</x:v>
+        <x:v>23.5182491202894</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>7772</x:v>
+        <x:v>365874</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.2399997711182</x:v>
+        <x:v>23.6552598738383</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>15274</x:v>
+        <x:v>732955</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00890540710852288</x:v>
+        <x:v>0.364741846742926</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-270</x:v>
+        <x:v>1207</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>13.9828075832791</x:v>
+        <x:v>-18.013376765342</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1419,28 +1422,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>1651</x:v>
+        <x:v>8622</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.323816129614</x:v>
+        <x:v>23.5623428928302</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2222</x:v>
+        <x:v>7772</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.5604321551044</x:v>
+        <x:v>23.2399997711182</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>3873</x:v>
+        <x:v>16394</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00225812765034104</x:v>
+        <x:v>0.0081581786542196</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-571</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>24.2445881237291</x:v>
+        <x:v>26.509696706884</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1448,28 +1451,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>269083</x:v>
+        <x:v>822947</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.6483261545975</x:v>
+        <x:v>23.5318488621688</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>274603</x:v>
+        <x:v>822210</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.6373106380807</x:v>
+        <x:v>23.5483444148472</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>543686</x:v>
+        <x:v>1645157</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.316992612884926</x:v>
+        <x:v>0.818682732721725</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-5520</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.1003381324851</x:v>
+        <x:v>5.12912380420369</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1477,28 +1480,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>379</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.4634826831264</x:v>
+        <x:v>23.5526433112515</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>6271</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.7336531562909</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>6650</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00387723957520473</x:v>
+        <x:v>0.000312512882447841</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-5892</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.7510317390012</x:v>
+        <x:v>23.5526433112515</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1506,28 +1509,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>10000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.4799999237061</x:v>
+        <x:v>23.5599994659424</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>19251</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.6966220243808</x:v>
+        <x:v>23.4799995422363</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>29251</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0170546067389945</x:v>
+        <x:v>0.00049763197842013</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-9251</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.9307827644897</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1535,28 +1538,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>45877</x:v>
+        <x:v>315385</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.5859684703744</x:v>
+        <x:v>23.6072675424313</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>56719</x:v>
+        <x:v>319156</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.6020998092466</x:v>
+        <x:v>23.6093234414541</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>102596</x:v>
+        <x:v>634541</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0598179355575496</x:v>
+        <x:v>0.315767893218687</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-10842</x:v>
+        <x:v>-3771</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.670358196393</x:v>
+        <x:v>23.7812671469175</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1564,28 +1567,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>2495010</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.6711151357325</x:v>
+        <x:v>23.4760966095076</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>2514162</x:v>
+        <x:v>6771</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.6289539073523</x:v>
+        <x:v>23.7075378117683</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>5009172</x:v>
+        <x:v>7350</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.9205654011139</x:v>
+        <x:v>0.00365759504138795</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-19152</x:v>
+        <x:v>-6192</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>18.1364368636507</x:v>
+        <x:v>23.7291793582975</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1593,28 +1596,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>2750</x:v>
+        <x:v>245527</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.7184724703702</x:v>
+        <x:v>23.540762991299</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>22069</x:v>
+        <x:v>257438</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.6420078527361</x:v>
+        <x:v>23.662678003113</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>24819</x:v>
+        <x:v>502965</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.0144705577469182</x:v>
+        <x:v>0.25029146802608</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-19319</x:v>
+        <x:v>-11911</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>23.6311233505106</x:v>
+        <x:v>26.1757690202939</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1622,28 +1625,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>6755</x:v>
+        <x:v>6805</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.5794527202073</x:v>
+        <x:v>23.4855251606556</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>28654</x:v>
+        <x:v>22129</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.7402350867777</x:v>
+        <x:v>23.6411347681197</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>35409</x:v>
+        <x:v>28934</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.0206449888899886</x:v>
+        <x:v>0.014398483663608</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-21899</x:v>
+        <x:v>-15324</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.7898302685752</x:v>
+        <x:v>23.7102370507348</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1651,28 +1654,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>2991972</x:v>
+        <x:v>3032964</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.637085968762</x:v>
+        <x:v>23.6349758680076</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>3015934</x:v>
+        <x:v>3059789</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.6355895018664</x:v>
+        <x:v>23.6337794159938</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>6007906</x:v>
+        <x:v>6092753</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>3.50287081312932</x:v>
+        <x:v>3.03194872941518</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-23962</x:v>
+        <x:v>-26825</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.4487358564806</x:v>
+        <x:v>23.4985027753362</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1680,28 +1683,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>278765</x:v>
+        <x:v>455608</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.549609496188</x:v>
+        <x:v>23.4979660685463</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>304168</x:v>
+        <x:v>486096</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.704814779881</x:v>
+        <x:v>23.5696450394814</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>582933</x:v>
+        <x:v>941704</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.339875322901176</x:v>
+        <x:v>0.46862202460615</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-25403</x:v>
+        <x:v>-30488</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>25.4079916057955</x:v>
+        <x:v>24.6408045970058</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1709,28 +1712,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>6116733</x:v>
+        <x:v>122181</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.6627158044095</x:v>
+        <x:v>23.6222904049464</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>6145869</x:v>
+        <x:v>171895</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.6087722151933</x:v>
+        <x:v>23.6613924816359</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>12262602</x:v>
+        <x:v>294076</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>7.14963094276462</x:v>
+        <x:v>0.146341621685878</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-29136</x:v>
+        <x:v>-49714</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>12.2840010627556</x:v>
+        <x:v>23.7574927920515</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1738,28 +1741,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>192336</x:v>
+        <x:v>979658</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.582227555639</x:v>
+        <x:v>23.6573563641515</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>229824</x:v>
+        <x:v>1044721</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.6952989486906</x:v>
+        <x:v>23.632454301816</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>422160</x:v>
+        <x:v>2024379</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.246137663017809</x:v>
+        <x:v>1.00739572684216</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-37488</x:v>
+        <x:v>-65063</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>24.27542324057</x:v>
+        <x:v>23.2575022617403</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1767,28 +1770,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>106177</x:v>
+        <x:v>1578497</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.6483921983817</x:v>
+        <x:v>23.5652084123299</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>146607</x:v>
+        <x:v>1654369</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.7016367778648</x:v>
+        <x:v>23.5948113509247</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>252784</x:v>
+        <x:v>3232866</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.147384079515572</x:v>
+        <x:v>1.60877750354717</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-40430</x:v>
+        <x:v>-75872</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>23.8414673421927</x:v>
+        <x:v>24.2106927006067</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1796,28 +1799,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>328749</x:v>
+        <x:v>148993</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.5528565754303</x:v>
+        <x:v>23.5446592492246</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>390773</x:v>
+        <x:v>228364</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.6158853456064</x:v>
+        <x:v>23.6598345451808</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>719522</x:v>
+        <x:v>377357</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.419512657688791</x:v>
+        <x:v>0.187784910480685</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-62024</x:v>
+        <x:v>-79371</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>23.9499599806927</x:v>
+        <x:v>23.8760383585435</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1825,28 +1828,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>136559</x:v>
+        <x:v>314895</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.5542061546445</x:v>
+        <x:v>23.5527974163082</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>216052</x:v>
+        <x:v>479452</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>23.6712858739988</x:v>
+        <x:v>23.66320170488</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>352611</x:v>
+        <x:v>794347</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.205587567496619</x:v>
+        <x:v>0.395292469162095</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-79493</x:v>
+        <x:v>-164557</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.8724141418375</x:v>
+        <x:v>23.8744704959362</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1854,28 +1857,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>204247</x:v>
+        <x:v>14472681</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.6126149200192</x:v>
+        <x:v>23.6050480590677</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>390004</x:v>
+        <x:v>14812147</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.7183334043633</x:v>
+        <x:v>23.6137003367213</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>594251</x:v>
+        <x:v>29284828</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.346474209745111</x:v>
+        <x:v>14.5730668953332</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-185757</x:v>
+        <x:v>-339466</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.8345749633453</x:v>
+        <x:v>23.982578676244</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1883,28 +1886,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>12653123</x:v>
+        <x:v>7054366</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.637402283656</x:v>
+        <x:v>23.6284327513872</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>13035180</x:v>
+        <x:v>7402645</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.6460339193696</x:v>
+        <x:v>23.5755243137407</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>25688303</x:v>
+        <x:v>14457011</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>14.9773992498422</x:v>
+        <x:v>7.19427098597158</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-382057</x:v>
+        <x:v>-348279</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.9319000293365</x:v>
+        <x:v>22.5038677290867</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1912,28 +1915,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>4333860</x:v>
+        <x:v>2838053</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.6348707898017</x:v>
+        <x:v>23.6353011961796</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4741610</x:v>
+        <x:v>3259177</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.6101044077975</x:v>
+        <x:v>23.5834423389788</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>9075470</x:v>
+        <x:v>6097230</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.29139420264411</x:v>
+        <x:v>3.03417662778257</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-407750</x:v>
+        <x:v>-421124</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.3468695032902</x:v>
+        <x:v>23.2339533873749</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1941,28 +1944,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>226880</x:v>
+        <x:v>4037503</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.6888438462959</x:v>
+        <x:v>23.6184173702533</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>760917</x:v>
+        <x:v>4514268</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.7375273399903</x:v>
+        <x:v>23.6676551035036</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>987797</x:v>
+        <x:v>8551771</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.575928664762182</x:v>
+        <x:v>4.25563472172589</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-534037</x:v>
+        <x:v>-476765</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.7582100100101</x:v>
+        <x:v>24.0846267681833</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1970,28 +1973,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>3490740</x:v>
+        <x:v>5150625</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.6570016639057</x:v>
+        <x:v>23.5997084756743</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>4067419</x:v>
+        <x:v>5735288</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>23.6961613546415</x:v>
+        <x:v>23.5768554802909</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>7558159</x:v>
+        <x:v>10885913</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>4.40673581811877</x:v>
+        <x:v>5.41717842309941</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-576679</x:v>
+        <x:v>-584663</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.9332018899119</x:v>
+        <x:v>23.3755305985274</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1999,28 +2002,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2604322</x:v>
+        <x:v>231183</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.6468010765501</x:v>
+        <x:v>23.6833204511797</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>3398149</x:v>
+        <x:v>835671</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.6034588979939</x:v>
+        <x:v>23.7147271241916</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>6002471</x:v>
+        <x:v>1066854</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>3.49970197146146</x:v>
+        <x:v>0.530900666705429</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-793827</x:v>
+        <x:v>-604488</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.4612654614622</x:v>
+        <x:v>23.7267384277856</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2028,28 +2031,57 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>719135</x:v>
+        <x:v>3002996</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.6065609861004</x:v>
+        <x:v>23.6129217421233</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>2320369</x:v>
+        <x:v>3912436</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.494289045404</x:v>
+        <x:v>23.5767988843651</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>3039504</x:v>
+        <x:v>6915432</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>1.77216318763806</x:v>
+        <x:v>3.44134010778987</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1601234</x:v>
+        <x:v>-909440</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.4438662576835</x:v>
+        <x:v>23.4575202102836</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:9">
+      <x:c r="A53" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B53" s="0">
+        <x:v>821677</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>23.5822580176954</x:v>
+      </x:c>
+      <x:c r="D53" s="0">
+        <x:v>2409062</x:v>
+      </x:c>
+      <x:c r="E53" s="0">
+        <x:v>23.4917470895451</x:v>
+      </x:c>
+      <x:c r="F53" s="0">
+        <x:v>3230739</x:v>
+      </x:c>
+      <x:c r="G53" s="0">
+        <x:v>1.60771904032907</x:v>
+      </x:c>
+      <x:c r="H53" s="0">
+        <x:v>-1587385</x:v>
+      </x:c>
+      <x:c r="I53" s="0">
+        <x:v>23.4448959803877</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -52,123 +52,126 @@
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PAPARA </x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
@@ -178,16 +181,16 @@
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
-    <x:t>YAPI KREDI</x:t>
+    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
@@ -544,7 +547,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I53"/>
+  <x:dimension ref="A1:I54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -581,28 +584,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>13204664</x:v>
+        <x:v>13838855</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.6121962864324</x:v>
+        <x:v>23.6042254443202</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>10475553</x:v>
+        <x:v>11247306</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.6209278178224</x:v>
+        <x:v>23.6093098317309</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>23680217</x:v>
+        <x:v>25086161</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>11.784033235128</x:v>
+        <x:v>11.3918311567625</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2729111</x:v>
+        <x:v>2591549</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.578680749744</x:v>
+        <x:v>23.5821592356435</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -610,28 +613,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1650244</x:v>
+        <x:v>1686176</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.6314488958033</x:v>
+        <x:v>23.6258300937835</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1066091</x:v>
+        <x:v>1219691</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.6459546782437</x:v>
+        <x:v>23.619138683043</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>2716335</x:v>
+        <x:v>2905867</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>1.35173516010184</x:v>
+        <x:v>1.31957800270866</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>584153</x:v>
+        <x:v>466485</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.6049755504508</x:v>
+        <x:v>23.6433257334237</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -639,28 +642,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>3339361</x:v>
+        <x:v>3522334</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.6121406144223</x:v>
+        <x:v>23.6033093648532</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>2943990</x:v>
+        <x:v>3162707</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.5957396470771</x:v>
+        <x:v>23.5851132597133</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>6283351</x:v>
+        <x:v>6685041</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>3.1267963892381</x:v>
+        <x:v>3.03573186618848</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>395371</x:v>
+        <x:v>359627</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.7342646039274</x:v>
+        <x:v>23.7633333594327</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -668,28 +671,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>2784960</x:v>
+        <x:v>2967486</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.6058720628352</x:v>
+        <x:v>23.5975714037613</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>2426366</x:v>
+        <x:v>2665635</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.6299786143894</x:v>
+        <x:v>23.6078089160863</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>5211326</x:v>
+        <x:v>5633121</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.59332246757226</x:v>
+        <x:v>2.55804637934091</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>358594</x:v>
+        <x:v>301851</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.4427591354905</x:v>
+        <x:v>23.5071643116315</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -697,28 +700,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>372774</x:v>
+        <x:v>10864140</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.5913318211205</x:v>
+        <x:v>23.5804562412825</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>144790</x:v>
+        <x:v>10628286</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.5571018137057</x:v>
+        <x:v>23.5797706545777</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>517564</x:v>
+        <x:v>21492426</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.257556397279036</x:v>
+        <x:v>9.7598866618616</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>227984</x:v>
+        <x:v>235854</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.6130709026946</x:v>
+        <x:v>23.6113508268189</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -726,28 +729,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>265802</x:v>
+        <x:v>399201</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.4739481179915</x:v>
+        <x:v>23.5725070044008</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>65448</x:v>
+        <x:v>176140</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.4996188745101</x:v>
+        <x:v>23.5577084987567</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>331250</x:v>
+        <x:v>575341</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.164840592851668</x:v>
+        <x:v>0.261267059936468</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>200354</x:v>
+        <x:v>223061</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.4655624622391</x:v>
+        <x:v>23.584192636511</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -755,28 +758,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>7736696</x:v>
+        <x:v>754276</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.5933696227755</x:v>
+        <x:v>23.5979438442921</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>7556996</x:v>
+        <x:v>547544</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.6032359522409</x:v>
+        <x:v>23.6348149874692</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>15293692</x:v>
+        <x:v>1301820</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>7.61063020730811</x:v>
+        <x:v>0.591167123438958</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>179700</x:v>
+        <x:v>206732</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.1784569221373</x:v>
+        <x:v>23.5002880715052</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -784,28 +787,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>636736</x:v>
+        <x:v>267812</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.6237443723664</x:v>
+        <x:v>23.4733139567989</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>467125</x:v>
+        <x:v>65883</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.6670168588264</x:v>
+        <x:v>23.4993132661062</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1103861</x:v>
+        <x:v>333695</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.549316533330823</x:v>
+        <x:v>0.151533632342384</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>169611</x:v>
+        <x:v>201929</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.5045677845413</x:v>
+        <x:v>23.4648312104123</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -813,28 +816,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>10014273</x:v>
+        <x:v>8864861</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.5915963384155</x:v>
+        <x:v>23.5720511480597</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>9868119</x:v>
+        <x:v>8708433</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.5889444576704</x:v>
+        <x:v>23.5811401929833</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>19882392</x:v>
+        <x:v>17573294</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>9.89411406668456</x:v>
+        <x:v>7.98017672437595</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>146154</x:v>
+        <x:v>156428</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.7706477141353</x:v>
+        <x:v>23.0660590062978</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -842,28 +845,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1724633</x:v>
+        <x:v>1443092</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.591472198892</x:v>
+        <x:v>23.6344770233415</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1586460</x:v>
+        <x:v>1312205</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.642009909483</x:v>
+        <x:v>23.5858652201507</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>3311093</x:v>
+        <x:v>2755297</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.64770576032304</x:v>
+        <x:v>1.25120293259436</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>138173</x:v>
+        <x:v>130887</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.011213708852</x:v>
+        <x:v>24.1218336837133</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -871,28 +874,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>3194243</x:v>
+        <x:v>3563064</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.5671392552488</x:v>
+        <x:v>23.5548223885084</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>3071157</x:v>
+        <x:v>3438715</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.6033565604485</x:v>
+        <x:v>23.5900950173286</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>6265400</x:v>
+        <x:v>7001779</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>3.11786339759348</x:v>
+        <x:v>3.17956518595912</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>123086</x:v>
+        <x:v>124349</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>22.6634700289748</x:v>
+        <x:v>22.5794022579623</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -900,28 +903,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1326231</x:v>
+        <x:v>488159</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.6541493327598</x:v>
+        <x:v>23.4927124481646</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1209968</x:v>
+        <x:v>377582</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.6010183607036</x:v>
+        <x:v>23.6468003534258</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>2536199</x:v>
+        <x:v>865741</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.26209372603715</x:v>
+        <x:v>0.393140078208329</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>116263</x:v>
+        <x:v>110577</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>24.2070920230133</x:v>
+        <x:v>22.9665558383422</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -929,28 +932,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>820068</x:v>
+        <x:v>1305584</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.5739075854174</x:v>
+        <x:v>23.5952016681951</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>723540</x:v>
+        <x:v>1196276</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.5832980166885</x:v>
+        <x:v>23.5908142647347</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1543608</x:v>
+        <x:v>2501860</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.768148702945139</x:v>
+        <x:v>1.13611511533621</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>96528</x:v>
+        <x:v>109308</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.5035202092996</x:v>
+        <x:v>23.6432177828622</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -958,28 +961,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>387011</x:v>
+        <x:v>229721</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.6775626241971</x:v>
+        <x:v>23.4955916498485</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>318047</x:v>
+        <x:v>127723</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.6116496394799</x:v>
+        <x:v>23.5864500768392</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>705058</x:v>
+        <x:v>357444</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.35085940744094</x:v>
+        <x:v>0.162318247738178</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>68964</x:v>
+        <x:v>101998</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.9815390039075</x:v>
+        <x:v>23.3818177437861</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -987,28 +990,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>173955</x:v>
+        <x:v>892006</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.5294623896279</x:v>
+        <x:v>23.5596313850118</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>121947</x:v>
+        <x:v>793143</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.5904819507107</x:v>
+        <x:v>23.5715008962522</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>295902</x:v>
+        <x:v>1685149</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.147250297678473</x:v>
+        <x:v>0.765239961666003</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>52008</x:v>
+        <x:v>98863</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.3863853165744</x:v>
+        <x:v>23.4644064803081</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1016,28 +1019,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1201126</x:v>
+        <x:v>1016558</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.6009344439583</x:v>
+        <x:v>23.4927139938944</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1152489</x:v>
+        <x:v>953321</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.5927536016462</x:v>
+        <x:v>23.5146322278006</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>2353615</x:v>
+        <x:v>1969879</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>1.17123408888929</x:v>
+        <x:v>0.894538186502597</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>48637</x:v>
+        <x:v>63237</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.7947854375526</x:v>
+        <x:v>23.1622885678659</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1045,28 +1048,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>1119153</x:v>
+        <x:v>1834069</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.5803003860301</x:v>
+        <x:v>23.5108118118198</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>1091380</x:v>
+        <x:v>1774791</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.5820316571252</x:v>
+        <x:v>23.5125529574631</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>2210533</x:v>
+        <x:v>3608860</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.10003191015298</x:v>
+        <x:v>1.63881288126924</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>27773</x:v>
+        <x:v>59278</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.512267597072</x:v>
+        <x:v>23.458681685677</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1074,28 +1077,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>2173017</x:v>
+        <x:v>550256</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.6569162838058</x:v>
+        <x:v>23.4788468786063</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>2152071</x:v>
+        <x:v>527253</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.6715534558299</x:v>
+        <x:v>23.5616811174923</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>4325088</x:v>
+        <x:v>1077509</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>2.15230209828116</x:v>
+        <x:v>0.489305661312307</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>20946</x:v>
+        <x:v>23003</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>22.1530380524025</x:v>
+        <x:v>21.5801988346382</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1103,28 +1106,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>27001</x:v>
+        <x:v>2207407</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.5051871220238</x:v>
+        <x:v>23.6552256344495</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>7010</x:v>
+        <x:v>2186461</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.3164620664763</x:v>
+        <x:v>23.6696057802744</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>34011</x:v>
+        <x:v>4393868</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.016924961218047</x:v>
+        <x:v>1.99529144300325</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>19991</x:v>
+        <x:v>20946</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.5713650340537</x:v>
+        <x:v>22.1541453317529</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1132,28 +1135,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>1426525</x:v>
+        <x:v>27001</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.6042665824891</x:v>
+        <x:v>23.5051871220238</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>1411345</x:v>
+        <x:v>7010</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.6261962285409</x:v>
+        <x:v>23.3164620664763</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>2837870</x:v>
+        <x:v>34011</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>1.41221486259913</x:v>
+        <x:v>0.0154446736378934</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>15180</x:v>
+        <x:v>19991</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>21.565380132748</x:v>
+        <x:v>23.5713650340537</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,22 +1170,22 @@
         <x:v>23.4344388556618</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>10157</x:v>
+        <x:v>10447</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.6490840956934</x:v>
+        <x:v>23.643280084069</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>34650</x:v>
+        <x:v>34940</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0172429480522575</x:v>
+        <x:v>0.0158665401460703</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>14336</x:v>
+        <x:v>14046</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.2823635415573</x:v>
+        <x:v>23.2791089173754</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1190,28 +1193,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>595344</x:v>
+        <x:v>1477689</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.6560013371976</x:v>
+        <x:v>23.6013837003864</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>582030</x:v>
+        <x:v>1464793</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.6817932558398</x:v>
+        <x:v>23.6200446170131</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1177374</x:v>
+        <x:v>2942482</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.585898952960422</x:v>
+        <x:v>1.33620517407238</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>13314</x:v>
+        <x:v>12896</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>22.5284911668997</x:v>
+        <x:v>21.4817822698328</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1219,28 +1222,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>40598</x:v>
+        <x:v>41911</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.492019490389</x:v>
+        <x:v>23.4906751532979</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>29085</x:v>
+        <x:v>29242</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.7340806596771</x:v>
+        <x:v>23.7334483312799</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>69683</x:v>
+        <x:v>71153</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0346764891522499</x:v>
+        <x:v>0.032311160017554</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>11513</x:v>
+        <x:v>12669</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>22.8805064956226</x:v>
+        <x:v>22.9303173294326</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1248,28 +1251,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>106430</x:v>
+        <x:v>604616</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.4710040936465</x:v>
+        <x:v>23.6522693699334</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>95318</x:v>
+        <x:v>592832</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.6329821407696</x:v>
+        <x:v>23.677546770941</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>201748</x:v>
+        <x:v>1197448</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.100396256382304</x:v>
+        <x:v>0.543770943469706</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>11112</x:v>
+        <x:v>11784</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>22.0815671339921</x:v>
+        <x:v>22.3806084573309</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1277,28 +1280,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>28000</x:v>
+        <x:v>107805</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.5014290809631</x:v>
+        <x:v>23.4704398334306</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>19251</x:v>
+        <x:v>97029</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.6966220243808</x:v>
+        <x:v>23.6306835267305</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>47251</x:v>
+        <x:v>204834</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0235136086123295</x:v>
+        <x:v>0.093016796917005</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>8749</x:v>
+        <x:v>10776</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.0719332124372</x:v>
+        <x:v>22.0275774246335</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1306,28 +1309,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>10300</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.4543028877777</x:v>
+        <x:v>23.488000424703</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>2222</x:v>
+        <x:v>21251</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.5604321551044</x:v>
+        <x:v>23.6743526780057</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>12522</x:v>
+        <x:v>51251</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00623134763377686</x:v>
+        <x:v>0.023273498827311</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>8078</x:v>
+        <x:v>8749</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>23.4251101133286</x:v>
+        <x:v>23.0353576386775</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1335,28 +1338,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>75312</x:v>
+        <x:v>10300</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.5090740182634</x:v>
+        <x:v>23.4543028877777</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>69219</x:v>
+        <x:v>3522</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.5851066412561</x:v>
+        <x:v>23.5693584005647</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>144531</x:v>
+        <x:v>13822</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0719232474730397</x:v>
+        <x:v>0.00627668339722333</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>6093</x:v>
+        <x:v>6778</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>22.6453119747826</x:v>
+        <x:v>23.3945174767367</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1379,7 +1382,7 @@
         <x:v>8408</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00418408967455645</x:v>
+        <x:v>0.00381814165850483</x:v>
       </x:c>
       <x:c r="H29" s="0">
         <x:v>5500</x:v>
@@ -1393,28 +1396,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>367081</x:v>
+        <x:v>8987</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.5182491202894</x:v>
+        <x:v>23.5560432263021</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>365874</x:v>
+        <x:v>7772</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.6552598738383</x:v>
+        <x:v>23.2399997711182</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>732955</x:v>
+        <x:v>16759</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.364741846742926</x:v>
+        <x:v>0.0076103991502001</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>1207</x:v>
+        <x:v>1215</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>-18.013376765342</x:v>
+        <x:v>25.5776808671991</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1422,28 +1425,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>8622</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.5623428928302</x:v>
+        <x:v>23.5526433112515</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>7772</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.2399997711182</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>16394</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0081581786542196</x:v>
+        <x:v>0.000285179943094794</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>850</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>26.509696706884</x:v>
+        <x:v>23.5526433112515</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1451,28 +1454,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>822947</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.5318488621688</x:v>
+        <x:v>23.5599994659424</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>822210</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.5483444148472</x:v>
+        <x:v>23.4799995422363</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>1645157</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.818682732721725</x:v>
+        <x:v>0.000454108189641393</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>737</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>5.12912380420369</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1480,28 +1483,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>628</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.5526433112515</x:v>
+        <x:v>23.5600001017253</x:v>
       </x:c>
       <x:c r="D33" s="0">
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="E33" s="0">
+        <x:v>23.5400002797445</x:v>
+      </x:c>
+      <x:c r="F33" s="0">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="G33" s="0">
+        <x:v>0.00681162284462089</x:v>
+      </x:c>
+      <x:c r="H33" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="0">
+      <x:c r="I33" s="0">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="F33" s="0">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="G33" s="0">
-        <x:v>0.000312512882447841</x:v>
-      </x:c>
-      <x:c r="H33" s="0">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="I33" s="0">
-        <x:v>23.5526433112515</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1509,28 +1512,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>500</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.5599994659424</x:v>
+        <x:v>23.4822335518677</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>500</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.4799995422363</x:v>
+        <x:v>23.6949070121593</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>1000</x:v>
+        <x:v>7840</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00049763197842013</x:v>
+        <x:v>0.00356020820678852</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>0</x:v>
+        <x:v>-6282</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0</x:v>
+        <x:v>23.7212796045769</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1538,28 +1541,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>315385</x:v>
+        <x:v>82312</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.6072675424313</x:v>
+        <x:v>23.4940880980433</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>319156</x:v>
+        <x:v>90839</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.6093234414541</x:v>
+        <x:v>23.5298449359732</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>634541</x:v>
+        <x:v>173151</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.315767893218687</x:v>
+        <x:v>0.0786292871445968</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-3771</x:v>
+        <x:v>-8527</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.7812671469175</x:v>
+        <x:v>23.8750093365465</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1567,28 +1570,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>579</x:v>
+        <x:v>1900159</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.4760966095076</x:v>
+        <x:v>23.5447227604811</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>6771</x:v>
+        <x:v>1911250</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.7075378117683</x:v>
+        <x:v>23.5716248229462</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>7350</x:v>
+        <x:v>3811409</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00365759504138795</x:v>
+        <x:v>1.73079204097291</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-6192</x:v>
+        <x:v>-11091</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.7291793582975</x:v>
+        <x:v>28.1806047266055</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1596,28 +1599,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>245527</x:v>
+        <x:v>3049240</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.540762991299</x:v>
+        <x:v>23.6347891785313</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>257438</x:v>
+        <x:v>3063079</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.662678003113</x:v>
+        <x:v>23.633742840519</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>502965</x:v>
+        <x:v>6112319</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.25029146802608</x:v>
+        <x:v>2.77565411560069</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-11911</x:v>
+        <x:v>-13839</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>26.1757690202939</x:v>
+        <x:v>23.4031961449172</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1625,28 +1628,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>6805</x:v>
+        <x:v>8160</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.4855251606556</x:v>
+        <x:v>23.480318331251</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>22129</x:v>
+        <x:v>22169</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.6411347681197</x:v>
+        <x:v>23.6409342456635</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>28934</x:v>
+        <x:v>30329</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.014398483663608</x:v>
+        <x:v>0.0137726472836338</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-15324</x:v>
+        <x:v>-14009</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.7102370507348</x:v>
+        <x:v>23.7344902354991</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1654,28 +1657,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>3032964</x:v>
+        <x:v>329803</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.6349758680076</x:v>
+        <x:v>23.5993507916033</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>3059789</x:v>
+        <x:v>343938</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.6337794159938</x:v>
+        <x:v>23.6047957947754</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>6092753</x:v>
+        <x:v>673741</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>3.03194872941518</x:v>
+        <x:v>0.305951305797181</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-26825</x:v>
+        <x:v>-14135</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.4985027753362</x:v>
+        <x:v>23.7318406041958</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1683,28 +1686,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>455608</x:v>
+        <x:v>281560</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.4979660685463</x:v>
+        <x:v>23.5213050026398</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>486096</x:v>
+        <x:v>306140</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.5696450394814</x:v>
+        <x:v>23.6356834322901</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>941704</x:v>
+        <x:v>587700</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.46862202460615</x:v>
+        <x:v>0.266879383052246</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-30488</x:v>
+        <x:v>-24580</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>24.6408045970058</x:v>
+        <x:v>24.9458701960142</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1712,28 +1715,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>122181</x:v>
+        <x:v>443056</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.6222904049464</x:v>
+        <x:v>23.6600939779274</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>171895</x:v>
+        <x:v>467662</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.6613924816359</x:v>
+        <x:v>23.5267818735736</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>294076</x:v>
+        <x:v>910718</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.146341621685878</x:v>
+        <x:v>0.41356450225383</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-49714</x:v>
+        <x:v>-24606</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>23.7574927920515</x:v>
+        <x:v>21.1263621504749</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1741,28 +1744,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>979658</x:v>
+        <x:v>1124485</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.6573563641515</x:v>
+        <x:v>23.6467729065567</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>1044721</x:v>
+        <x:v>1166308</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.632454301816</x:v>
+        <x:v>23.6150457029357</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>2024379</x:v>
+        <x:v>2290793</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.00739572684216</x:v>
+        <x:v>1.04026786207317</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-65063</x:v>
+        <x:v>-41823</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>23.2575022617403</x:v>
+        <x:v>22.7620039660024</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1770,28 +1773,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>1578497</x:v>
+        <x:v>133412</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.5652084123299</x:v>
+        <x:v>23.6007936673983</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>1654369</x:v>
+        <x:v>181681</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.5948113509247</x:v>
+        <x:v>23.6491028666145</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>3232866</x:v>
+        <x:v>315093</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.60877750354717</x:v>
+        <x:v>0.143086311798675</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-75872</x:v>
+        <x:v>-48269</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>24.2106927006067</x:v>
+        <x:v>23.7826259743199</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1799,28 +1802,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>148993</x:v>
+        <x:v>163442</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.5446592492246</x:v>
+        <x:v>23.5337730153592</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>228364</x:v>
+        <x:v>235872</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.6598345451808</x:v>
+        <x:v>23.6533028950136</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>377357</x:v>
+        <x:v>399314</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.187784910480685</x:v>
+        <x:v>0.181331757638463</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-79371</x:v>
+        <x:v>-72430</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>23.8760383585435</x:v>
+        <x:v>23.9230281827464</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1828,28 +1831,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>314895</x:v>
+        <x:v>1896990</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.5527974163082</x:v>
+        <x:v>23.5746287099895</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>479452</x:v>
+        <x:v>1969771</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>23.66320170488</x:v>
+        <x:v>23.580495074056</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>794347</x:v>
+        <x:v>3866761</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.395292469162095</x:v>
+        <x:v>1.75592783748594</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-164557</x:v>
+        <x:v>-72781</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.8744704959362</x:v>
+        <x:v>23.7333980840505</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1857,28 +1860,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>14472681</x:v>
+        <x:v>380665</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.6050480590677</x:v>
+        <x:v>23.5273789926308</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>14812147</x:v>
+        <x:v>538167</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.6137003367213</x:v>
+        <x:v>23.6385815400488</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>29284828</x:v>
+        <x:v>918832</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>14.5730668953332</x:v>
+        <x:v>0.41724913610458</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-339466</x:v>
+        <x:v>-157502</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.982578676244</x:v>
+        <x:v>23.9073458586788</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1886,28 +1889,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>7054366</x:v>
+        <x:v>15726497</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.6284327513872</x:v>
+        <x:v>23.5913359145926</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>7402645</x:v>
+        <x:v>15953674</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.5755243137407</x:v>
+        <x:v>23.6015634562079</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>14457011</x:v>
+        <x:v>31680171</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>7.19427098597158</x:v>
+        <x:v>14.3862251003397</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-348279</x:v>
+        <x:v>-227177</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>22.5038677290867</x:v>
+        <x:v>24.3095726408092</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1915,28 +1918,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>2838053</x:v>
+        <x:v>7894851</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.6353011961796</x:v>
+        <x:v>23.6095961124618</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>3259177</x:v>
+        <x:v>8156745</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.5834423389788</x:v>
+        <x:v>23.5637338817414</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>6097230</x:v>
+        <x:v>16051596</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>3.03417662778257</x:v>
+        <x:v>7.28916120041502</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-421124</x:v>
+        <x:v>-261894</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.2339533873749</x:v>
+        <x:v>22.1812070652993</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1944,28 +1947,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>4037503</x:v>
+        <x:v>4515597</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.6184173702533</x:v>
+        <x:v>23.601081567463</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>4514268</x:v>
+        <x:v>4873266</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.6676551035036</x:v>
+        <x:v>23.6547460738336</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>8551771</x:v>
+        <x:v>9388863</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>4.25563472172589</x:v>
+        <x:v>4.26355957972105</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-476765</x:v>
+        <x:v>-357669</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>24.0846267681833</x:v>
+        <x:v>24.3322643490362</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1973,28 +1976,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>5150625</x:v>
+        <x:v>3227554</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.5997084756743</x:v>
+        <x:v>23.612644025983</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>5735288</x:v>
+        <x:v>3606963</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>23.5768554802909</x:v>
+        <x:v>23.5662640790694</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>10885913</x:v>
+        <x:v>6834517</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.41717842309941</x:v>
+        <x:v>3.10361014194332</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-584663</x:v>
+        <x:v>-379409</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.3755305985274</x:v>
+        <x:v>23.1717194499727</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2002,28 +2005,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>231183</x:v>
+        <x:v>244200</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.6833204511797</x:v>
+        <x:v>23.6711859517015</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>835671</x:v>
+        <x:v>838725</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.7147271241916</x:v>
+        <x:v>23.7133367330224</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1066854</x:v>
+        <x:v>1082925</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>0.530900666705429</x:v>
+        <x:v>0.491765111267405</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-604488</x:v>
+        <x:v>-594525</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.7267384277856</x:v>
+        <x:v>23.73065008536</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2031,28 +2034,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>3002996</x:v>
+        <x:v>5495911</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.6129217421233</x:v>
+        <x:v>23.5892462145064</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>3912436</x:v>
+        <x:v>6329472</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.5767988843651</x:v>
+        <x:v>23.5669225953061</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>6915432</x:v>
+        <x:v>11825383</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>3.44134010778987</x:v>
+        <x:v>5.3700032659461</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-909440</x:v>
+        <x:v>-833561</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.4575202102836</x:v>
+        <x:v>23.4197364573715</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2060,28 +2063,57 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>821677</x:v>
+        <x:v>3287533</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>23.5822580176954</x:v>
+        <x:v>23.5971326256579</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>2409062</x:v>
+        <x:v>4206617</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.4917470895451</x:v>
+        <x:v>23.566752740481</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>3230739</x:v>
+        <x:v>7494150</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>1.60771904032907</x:v>
+        <x:v>3.40315488940104</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1587385</x:v>
+        <x:v>-919084</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.4448959803877</x:v>
+        <x:v>23.4580848983087</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:9">
+      <x:c r="A54" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B54" s="0">
+        <x:v>876273</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>23.5732059144207</x:v>
+      </x:c>
+      <x:c r="D54" s="0">
+        <x:v>2484074</x:v>
+      </x:c>
+      <x:c r="E54" s="0">
+        <x:v>23.4913639671398</x:v>
+      </x:c>
+      <x:c r="F54" s="0">
+        <x:v>3360347</x:v>
+      </x:c>
+      <x:c r="G54" s="0">
+        <x:v>1.52596109273688</x:v>
+      </x:c>
+      <x:c r="H54" s="0">
+        <x:v>-1607801</x:v>
+      </x:c>
+      <x:c r="I54" s="0">
+        <x:v>23.4467590137472</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,151 +40,154 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PAPARA </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PAPARA </x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
   </x:si>
   <x:si>
     <x:t>GLOBAL</x:t>
@@ -547,7 +550,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I54"/>
+  <x:dimension ref="A1:I55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -584,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>13838855</x:v>
+        <x:v>6672022</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.6042254443202</x:v>
+        <x:v>23.2636798351155</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>11247306</x:v>
+        <x:v>4824860</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.6093098317309</x:v>
+        <x:v>23.3885234806712</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>25086161</x:v>
+        <x:v>11496882</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>11.3918311567625</x:v>
+        <x:v>4.18056271686233</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2591549</x:v>
+        <x:v>1847162</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.5821592356435</x:v>
+        <x:v>22.9375833088247</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -613,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1686176</x:v>
+        <x:v>16112863</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.6258300937835</x:v>
+        <x:v>23.5088019990496</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1219691</x:v>
+        <x:v>14783374</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.619138683043</x:v>
+        <x:v>23.4630127760081</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>2905867</x:v>
+        <x:v>30896237</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>1.31957800270866</x:v>
+        <x:v>11.2346683643045</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>466485</x:v>
+        <x:v>1329489</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.6433257334237</x:v>
+        <x:v>24.0179594342684</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -642,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>3522334</x:v>
+        <x:v>11016270</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.6033093648532</x:v>
+        <x:v>23.4561605552198</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>3162707</x:v>
+        <x:v>10445390</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.5851132597133</x:v>
+        <x:v>23.482555502044</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>6685041</x:v>
+        <x:v>21461660</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>3.03573186618848</x:v>
+        <x:v>7.80401291741322</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>359627</x:v>
+        <x:v>570880</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.7633333594327</x:v>
+        <x:v>22.9732122760583</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -671,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>2967486</x:v>
+        <x:v>1934049</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.5975714037613</x:v>
+        <x:v>23.535947271035</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>2665635</x:v>
+        <x:v>1417573</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.6078089160863</x:v>
+        <x:v>23.522594136287</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>5633121</x:v>
+        <x:v>3351622</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.55804637934091</x:v>
+        <x:v>1.21873617335688</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>301851</x:v>
+        <x:v>516476</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.5071643116315</x:v>
+        <x:v>23.5725976541779</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -700,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>10864140</x:v>
+        <x:v>3506406</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.5804562412825</x:v>
+        <x:v>23.4973370996054</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>10628286</x:v>
+        <x:v>3159248</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.5797706545777</x:v>
+        <x:v>23.5079304088009</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>21492426</x:v>
+        <x:v>6665654</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>9.7598866618616</x:v>
+        <x:v>2.42380365353878</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>235854</x:v>
+        <x:v>347158</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.6113508268189</x:v>
+        <x:v>23.400934623243</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -729,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>399201</x:v>
+        <x:v>750258</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.5725070044008</x:v>
+        <x:v>23.3608795414943</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>176140</x:v>
+        <x:v>430162</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.5577084987567</x:v>
+        <x:v>23.5649465632594</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>575341</x:v>
+        <x:v>1180420</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.261267059936468</x:v>
+        <x:v>0.429231146517693</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>223061</x:v>
+        <x:v>320096</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.584192636511</x:v>
+        <x:v>23.0866434428974</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -758,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>754276</x:v>
+        <x:v>1826863</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.5979438442921</x:v>
+        <x:v>23.470858695221</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>547544</x:v>
+        <x:v>1635978</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.6348149874692</x:v>
+        <x:v>23.4435998242309</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1301820</x:v>
+        <x:v>3462841</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.591167123438958</x:v>
+        <x:v>1.25917826929269</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>206732</x:v>
+        <x:v>190885</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.5002880715052</x:v>
+        <x:v>23.7044805787878</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -787,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>267812</x:v>
+        <x:v>1184305</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.4733139567989</x:v>
+        <x:v>23.4207607022829</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>65883</x:v>
+        <x:v>1004474</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.4993132661062</x:v>
+        <x:v>23.4347531986303</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>333695</x:v>
+        <x:v>2188779</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.151533632342384</x:v>
+        <x:v>0.795896477223234</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>201929</x:v>
+        <x:v>179831</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.4648312104123</x:v>
+        <x:v>23.3426034392077</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -816,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>8864861</x:v>
+        <x:v>900994</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.5720511480597</x:v>
+        <x:v>23.4805471894791</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8708433</x:v>
+        <x:v>749623</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.5811401929833</x:v>
+        <x:v>23.4506889442076</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>17573294</x:v>
+        <x:v>1650617</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>7.98017672437595</x:v>
+        <x:v>0.600206898706896</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>156428</x:v>
+        <x:v>151371</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.0660590062978</x:v>
+        <x:v>23.628411888762</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -845,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1443092</x:v>
+        <x:v>1333543</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.6344770233415</x:v>
+        <x:v>23.5809326196605</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1312205</x:v>
+        <x:v>1248071</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.5858652201507</x:v>
+        <x:v>23.5599743138357</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2755297</x:v>
+        <x:v>2581614</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.25120293259436</x:v>
+        <x:v>0.938741411604452</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>130887</x:v>
+        <x:v>85472</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>24.1218336837133</x:v>
+        <x:v>23.8869679728638</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -874,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>3563064</x:v>
+        <x:v>480895</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.5548223885084</x:v>
+        <x:v>23.2591157664742</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>3438715</x:v>
+        <x:v>397288</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.5900950173286</x:v>
+        <x:v>23.4808026615212</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>7001779</x:v>
+        <x:v>878183</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>3.17956518595912</x:v>
+        <x:v>0.319329980805431</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>124349</x:v>
+        <x:v>83607</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>22.5794022579623</x:v>
+        <x:v>22.2056926899444</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -903,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>488159</x:v>
+        <x:v>272309</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.4927124481646</x:v>
+        <x:v>23.4084395104323</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>377582</x:v>
+        <x:v>201527</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.6468003534258</x:v>
+        <x:v>23.3739802178774</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>865741</x:v>
+        <x:v>473836</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.393140078208329</x:v>
+        <x:v>0.172298986412766</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>110577</x:v>
+        <x:v>70782</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>22.9665558383422</x:v>
+        <x:v>23.5065502992021</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -932,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1305584</x:v>
+        <x:v>1252623</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.5952016681951</x:v>
+        <x:v>23.3786577455173</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1196276</x:v>
+        <x:v>1189286</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.5908142647347</x:v>
+        <x:v>23.3898864161986</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>2501860</x:v>
+        <x:v>2441909</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>1.13611511533621</x:v>
+        <x:v>0.887941071620163</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>109308</x:v>
+        <x:v>63337</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.6432177828622</x:v>
+        <x:v>23.1678157283733</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -961,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>229721</x:v>
+        <x:v>638154</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.4955916498485</x:v>
+        <x:v>23.4171787427599</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>127723</x:v>
+        <x:v>583349</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.5864500768392</x:v>
+        <x:v>23.501063795245</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>357444</x:v>
+        <x:v>1221503</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.162318247738178</x:v>
+        <x:v>0.44416998455194</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>101998</x:v>
+        <x:v>54805</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.3818177437861</x:v>
+        <x:v>22.5242992339175</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -990,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>892006</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.5596313850118</x:v>
+        <x:v>22.9379997253418</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>793143</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.5715008962522</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>1685149</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.765239961666003</x:v>
+        <x:v>0.0181812891393611</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>98863</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.4644064803081</x:v>
+        <x:v>22.9379997253418</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1019,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1016558</x:v>
+        <x:v>2827976</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.4927139938944</x:v>
+        <x:v>23.3361356935062</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>953321</x:v>
+        <x:v>2790986</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.5146322278006</x:v>
+        <x:v>23.3254994723824</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>1969879</x:v>
+        <x:v>5618962</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.894538186502597</x:v>
+        <x:v>2.04319945570166</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>63237</x:v>
+        <x:v>36990</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.1622885678659</x:v>
+        <x:v>24.1386645999526</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1048,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>1834069</x:v>
+        <x:v>58750</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.5108118118198</x:v>
+        <x:v>23.2057025016622</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>1774791</x:v>
+        <x:v>25251</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.5125529574631</x:v>
+        <x:v>23.5532718763593</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>3608860</x:v>
+        <x:v>84001</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.63881288126924</x:v>
+        <x:v>0.0305449293799095</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>59278</x:v>
+        <x:v>33499</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.458681685677</x:v>
+        <x:v>22.9437103741219</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1077,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>550256</x:v>
+        <x:v>378614</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.4788468786063</x:v>
+        <x:v>23.0563857295229</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>527253</x:v>
+        <x:v>354105</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.5616811174923</x:v>
+        <x:v>23.0765432152809</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>1077509</x:v>
+        <x:v>732719</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.489305661312307</x:v>
+        <x:v>0.266435519938071</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>23003</x:v>
+        <x:v>24509</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>21.5801988346382</x:v>
+        <x:v>22.7651512240628</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1106,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>2207407</x:v>
+        <x:v>12560742</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.6552256344495</x:v>
+        <x:v>23.4900493899247</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>2186461</x:v>
+        <x:v>12539711</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.6696057802744</x:v>
+        <x:v>23.4812635219806</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>4393868</x:v>
+        <x:v>25100453</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>1.99529144300325</x:v>
+        <x:v>9.12717187043888</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>20946</x:v>
+        <x:v>21031</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.1541453317529</x:v>
+        <x:v>28.7286136476285</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1141,22 +1144,22 @@
         <x:v>23.5051871220238</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>7010</x:v>
+        <x:v>9010</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.3164620664763</x:v>
+        <x:v>23.2062595422472</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>34011</x:v>
+        <x:v>36011</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0154446736378934</x:v>
+        <x:v>0.0130945280639507</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>19991</x:v>
+        <x:v>17991</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.5713650340537</x:v>
+        <x:v>23.6548918351464</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1164,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>24493</x:v>
+        <x:v>64546</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.4344388556618</x:v>
+        <x:v>23.265324369693</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>10447</x:v>
+        <x:v>47691</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.643280084069</x:v>
+        <x:v>23.4526756811581</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>34940</x:v>
+        <x:v>112237</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0158665401460703</x:v>
+        <x:v>0.0408122669826895</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>14046</x:v>
+        <x:v>16855</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.2791089173754</x:v>
+        <x:v>22.7352163070955</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1193,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>1477689</x:v>
+        <x:v>4173563</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.6013837003864</x:v>
+        <x:v>23.4831950807289</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1464793</x:v>
+        <x:v>4161142</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.6200446170131</x:v>
+        <x:v>23.4285327267002</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>2942482</x:v>
+        <x:v>8334705</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>1.33620517407238</x:v>
+        <x:v>3.03071362992558</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>12896</x:v>
+        <x:v>12421</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>21.4817822698328</x:v>
+        <x:v>41.795554566082</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1222,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>41911</x:v>
+        <x:v>11454</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.4906751532979</x:v>
+        <x:v>23.1317409174343</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>29242</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.7334483312799</x:v>
+        <x:v>23.3600006103516</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>71153</x:v>
+        <x:v>12908</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.032311160017554</x:v>
+        <x:v>0.00469368160421747</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>12669</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>22.9303173294326</x:v>
+        <x:v>23.0985519580841</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1251,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>604616</x:v>
+        <x:v>5075</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.6522693699334</x:v>
+        <x:v>23.1034372553332</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>592832</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.677546770941</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1197448</x:v>
+        <x:v>5075</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.543770943469706</x:v>
+        <x:v>0.00184540084764515</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>11784</x:v>
+        <x:v>5075</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>22.3806084573309</x:v>
+        <x:v>23.1034372553332</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1280,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>107805</x:v>
+        <x:v>11700</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.4704398334306</x:v>
+        <x:v>23.4238735736945</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>97029</x:v>
+        <x:v>6780</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.6306835267305</x:v>
+        <x:v>23.2573216128842</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>204834</x:v>
+        <x:v>18480</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.093016796917005</x:v>
+        <x:v>0.00671980446590787</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>10776</x:v>
+        <x:v>4920</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>22.0275774246335</x:v>
+        <x:v>23.653390300177</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1309,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>30000</x:v>
+        <x:v>677273</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.488000424703</x:v>
+        <x:v>23.5637968911833</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>21251</x:v>
+        <x:v>672720</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.6743526780057</x:v>
+        <x:v>23.5788307313758</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>51251</x:v>
+        <x:v>1349993</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.023273498827311</x:v>
+        <x:v>0.490892261382271</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>8749</x:v>
+        <x:v>4553</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>23.0353576386775</x:v>
+        <x:v>21.342499949763</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1338,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>10300</x:v>
+        <x:v>1774001</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.4543028877777</x:v>
+        <x:v>23.4763413637907</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>3522</x:v>
+        <x:v>1773160</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.5693584005647</x:v>
+        <x:v>23.4964302585122</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>13822</x:v>
+        <x:v>3547161</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00627668339722333</x:v>
+        <x:v>1.28983919529731</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>6778</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.3945174767367</x:v>
+        <x:v>-18.8789791646951</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1367,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>6954</x:v>
+        <x:v>2628843</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.2644461438956</x:v>
+        <x:v>23.5324761505318</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1454</x:v>
+        <x:v>2628331</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.3600006103516</x:v>
+        <x:v>23.5384516541292</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>8408</x:v>
+        <x:v>5257174</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00381814165850483</x:v>
+        <x:v>1.91164401099863</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>5500</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.2391850176724</x:v>
+        <x:v>-7.1425264775753</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1396,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>8987</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.5560432263021</x:v>
+        <x:v>23.5599994659424</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>7772</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.2399997711182</x:v>
+        <x:v>23.4799995422363</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>16759</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0076103991502001</x:v>
+        <x:v>0.000363625782787222</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>1215</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>25.5776808671991</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1425,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>628</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.5526433112515</x:v>
+        <x:v>23.5600001017253</x:v>
       </x:c>
       <x:c r="D31" s="0">
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="E31" s="0">
+        <x:v>23.5400002797445</x:v>
+      </x:c>
+      <x:c r="F31" s="0">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="G31" s="0">
+        <x:v>0.00545438674180833</x:v>
+      </x:c>
+      <x:c r="H31" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="0">
+      <x:c r="I31" s="0">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="F31" s="0">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="G31" s="0">
-        <x:v>0.000285179943094794</x:v>
-      </x:c>
-      <x:c r="H31" s="0">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="I31" s="0">
-        <x:v>23.5526433112515</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1454,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>500</x:v>
+        <x:v>9056</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.5599994659424</x:v>
+        <x:v>23.5522703715853</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>500</x:v>
+        <x:v>9859</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.4799995422363</x:v>
+        <x:v>23.1562022518611</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>1000</x:v>
+        <x:v>18915</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.000454108189641393</x:v>
+        <x:v>0.00687798168142031</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>0</x:v>
+        <x:v>-803</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0</x:v>
+        <x:v>18.689461414722</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1483,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>7500</x:v>
+        <x:v>108790</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.5600001017253</x:v>
+        <x:v>23.324864958998</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>7500</x:v>
+        <x:v>111242</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.5400002797445</x:v>
+        <x:v>23.3941037540213</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>15000</x:v>
+        <x:v>220032</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00681162284462089</x:v>
+        <x:v>0.0800093082382381</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>0</x:v>
+        <x:v>-2452</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0</x:v>
+        <x:v>26.4660811237565</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1512,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>779</x:v>
+        <x:v>1704</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.4822335518677</x:v>
+        <x:v>23.1544364147903</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>7061</x:v>
+        <x:v>7855</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.6949070121593</x:v>
+        <x:v>23.6098483454111</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>7840</x:v>
+        <x:v>9559</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00356020820678852</x:v>
+        <x:v>0.00347589885766306</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-6282</x:v>
+        <x:v>-6151</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.7212796045769</x:v>
+        <x:v>23.736010258885</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1541,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>82312</x:v>
+        <x:v>33070</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.4940880980433</x:v>
+        <x:v>23.2521526933618</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>90839</x:v>
+        <x:v>39912</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.5298449359732</x:v>
+        <x:v>23.1105527434327</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>173151</x:v>
+        <x:v>72982</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0786292871445968</x:v>
+        <x:v>0.0265381368793771</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-8527</x:v>
+        <x:v>-6842</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.8750093365465</x:v>
+        <x:v>22.4261460868771</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1570,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>1900159</x:v>
+        <x:v>8649</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.5447227604811</x:v>
+        <x:v>23.4484168709958</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>1911250</x:v>
+        <x:v>22907</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.5716248229462</x:v>
+        <x:v>23.6176047113433</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>3811409</x:v>
+        <x:v>31556</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>1.73079204097291</x:v>
+        <x:v>0.0114745752016336</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-11091</x:v>
+        <x:v>-14258</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>28.1806047266055</x:v>
+        <x:v>23.7202352086898</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1599,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>3049240</x:v>
+        <x:v>475593</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.6347891785313</x:v>
+        <x:v>23.4958504393165</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>3063079</x:v>
+        <x:v>496839</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.633742840519</x:v>
+        <x:v>23.1470053978033</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>6112319</x:v>
+        <x:v>972432</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2.77565411560069</x:v>
+        <x:v>0.353601347207344</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-13839</x:v>
+        <x:v>-21246</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>23.4031961449172</x:v>
+        <x:v>15.3380879625968</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1628,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>8160</x:v>
+        <x:v>374101</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.480318331251</x:v>
+        <x:v>23.5142663964116</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>22169</x:v>
+        <x:v>397203</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.6409342456635</x:v>
+        <x:v>23.5109296655949</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>30329</x:v>
+        <x:v>771304</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.0137726472836338</x:v>
+        <x:v>0.280466020766916</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-14009</x:v>
+        <x:v>-23102</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.7344902354991</x:v>
+        <x:v>23.4568964937798</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1657,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>329803</x:v>
+        <x:v>185888</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.5993507916033</x:v>
+        <x:v>23.3745449519666</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>343938</x:v>
+        <x:v>209560</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.6047957947754</x:v>
+        <x:v>23.5703329466026</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>673741</x:v>
+        <x:v>395448</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.305951305797181</x:v>
+        <x:v>0.143795088551642</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-14135</x:v>
+        <x:v>-23672</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.7318406041958</x:v>
+        <x:v>25.1077881150247</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1686,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>281560</x:v>
+        <x:v>2303356</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.5213050026398</x:v>
+        <x:v>23.430291861624</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>306140</x:v>
+        <x:v>2338564</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.6356834322901</x:v>
+        <x:v>23.466255312383</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>587700</x:v>
+        <x:v>4641920</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.266879383052246</x:v>
+        <x:v>1.68792179363566</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-24580</x:v>
+        <x:v>-35208</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>24.9458701960142</x:v>
+        <x:v>25.8190339446962</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1715,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>443056</x:v>
+        <x:v>585194</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.6600939779274</x:v>
+        <x:v>23.4666576877138</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>467662</x:v>
+        <x:v>633238</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.5267818735736</x:v>
+        <x:v>23.3569869155778</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>910718</x:v>
+        <x:v>1218432</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.41356450225383</x:v>
+        <x:v>0.443053289773001</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-24606</x:v>
+        <x:v>-48044</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>21.1263621504749</x:v>
+        <x:v>22.0211556394693</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1744,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>1124485</x:v>
+        <x:v>3225108</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.6467729065567</x:v>
+        <x:v>23.5914576972727</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>1166308</x:v>
+        <x:v>3276229</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.6150457029357</x:v>
+        <x:v>23.5792017751644</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>2290793</x:v>
+        <x:v>6501337</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.04026786207317</x:v>
+        <x:v>2.36405375578853</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-41823</x:v>
+        <x:v>-51121</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>22.7620039660024</x:v>
+        <x:v>22.8060034332168</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1773,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>133412</x:v>
+        <x:v>204529</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.6007936673983</x:v>
+        <x:v>23.4313680957116</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>181681</x:v>
+        <x:v>260742</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.6491028666145</x:v>
+        <x:v>23.5858674878578</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>315093</x:v>
+        <x:v>465271</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.143086311798675</x:v>
+        <x:v>0.169184531583194</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-48269</x:v>
+        <x:v>-56213</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>23.7826259743199</x:v>
+        <x:v>24.1480080278801</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1802,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>163442</x:v>
+        <x:v>1235797</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.5337730153592</x:v>
+        <x:v>23.5810025221955</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>235872</x:v>
+        <x:v>1302113</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.6533028950136</x:v>
+        <x:v>23.5503442462873</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>399314</x:v>
+        <x:v>2537910</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.181331757638463</x:v>
+        <x:v>0.922849510393519</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-72430</x:v>
+        <x:v>-66316</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>23.9230281827464</x:v>
+        <x:v>22.9790280421656</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1831,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>1896990</x:v>
+        <x:v>2254016</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.5746287099895</x:v>
+        <x:v>23.4708265562282</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>1969771</x:v>
+        <x:v>2366004</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>23.580495074056</x:v>
+        <x:v>23.469871893313</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>3866761</x:v>
+        <x:v>4620020</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.75592783748594</x:v>
+        <x:v>1.67995838899262</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-72781</x:v>
+        <x:v>-111988</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.7333980840505</x:v>
+        <x:v>23.4506571070358</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1860,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>380665</x:v>
+        <x:v>667145</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.5273789926308</x:v>
+        <x:v>23.2967653686214</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>538167</x:v>
+        <x:v>820919</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.6385815400488</x:v>
+        <x:v>23.3936000040463</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>918832</x:v>
+        <x:v>1488064</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.41724913610458</x:v>
+        <x:v>0.541098436837485</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-157502</x:v>
+        <x:v>-153774</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.9073458586788</x:v>
+        <x:v>23.8137148664452</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1889,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>15726497</x:v>
+        <x:v>5966898</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.5913359145926</x:v>
+        <x:v>23.4398171633986</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>15953674</x:v>
+        <x:v>6150847</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.6015634562079</x:v>
+        <x:v>23.4951803145649</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>31680171</x:v>
+        <x:v>12117745</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>14.3862251003397</x:v>
+        <x:v>4.40632451124095</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-227177</x:v>
+        <x:v>-183949</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>24.3095726408092</x:v>
+        <x:v>25.2910382750203</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1918,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>7894851</x:v>
+        <x:v>324117</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.6095961124618</x:v>
+        <x:v>23.3758899965587</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>8156745</x:v>
+        <x:v>518044</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.5637338817414</x:v>
+        <x:v>22.9927144214145</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>16051596</x:v>
+        <x:v>842161</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>7.28916120041502</x:v>
+        <x:v>0.30623145285787</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-261894</x:v>
+        <x:v>-193927</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>22.1812070652993</x:v>
+        <x:v>22.352299637042</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1947,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>4515597</x:v>
+        <x:v>20309960</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.601081567463</x:v>
+        <x:v>23.4320804241148</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>4873266</x:v>
+        <x:v>20513757</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.6547460738336</x:v>
+        <x:v>23.438616062361</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>9388863</x:v>
+        <x:v>40823717</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>4.26355957972105</x:v>
+        <x:v>14.844556050409</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-357669</x:v>
+        <x:v>-203797</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>24.3322643490362</x:v>
+        <x:v>24.0899433701985</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1976,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>3227554</x:v>
+        <x:v>4110638</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.612644025983</x:v>
+        <x:v>23.4711108810886</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>3606963</x:v>
+        <x:v>4498832</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>23.5662640790694</x:v>
+        <x:v>23.4488757984536</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>6834517</x:v>
+        <x:v>8609470</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>3.10361014194332</x:v>
+        <x:v>3.13062526813311</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-379409</x:v>
+        <x:v>-388194</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.1717194499727</x:v>
+        <x:v>23.2134255451972</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2005,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>244200</x:v>
+        <x:v>9646398</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.6711859517015</x:v>
+        <x:v>23.4956684121239</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>838725</x:v>
+        <x:v>10156278</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.7133367330224</x:v>
+        <x:v>23.4361554688431</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1082925</x:v>
+        <x:v>19802676</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>0.491765111267405</x:v>
+        <x:v>7.20076356178174</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-594525</x:v>
+        <x:v>-509880</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.73065008536</x:v>
+        <x:v>22.3102326300618</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2034,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>5495911</x:v>
+        <x:v>664759</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.5892462145064</x:v>
+        <x:v>23.1939679074686</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>6329472</x:v>
+        <x:v>1245305</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.5669225953061</x:v>
+        <x:v>23.4526574395277</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>11825383</x:v>
+        <x:v>1910064</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>5.3700032659461</x:v>
+        <x:v>0.694548517173693</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-833561</x:v>
+        <x:v>-580546</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.4197364573715</x:v>
+        <x:v>23.7488720282804</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2063,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>3287533</x:v>
+        <x:v>6649010</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>23.5971326256579</x:v>
+        <x:v>23.4751587147339</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>4206617</x:v>
+        <x:v>7430471</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.566752740481</x:v>
+        <x:v>23.4673178528168</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>7494150</x:v>
+        <x:v>14079481</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>3.40315488940104</x:v>
+        <x:v>5.11966229986282</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-919084</x:v>
+        <x:v>-781461</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.4580848983087</x:v>
+        <x:v>23.400604390091</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2092,28 +2095,57 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>876273</x:v>
+        <x:v>3957183</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>23.5732059144207</x:v>
+        <x:v>23.4772988098892</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>2484074</x:v>
+        <x:v>4961282</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.4913639671398</x:v>
+        <x:v>23.4692266170621</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>3360347</x:v>
+        <x:v>8918465</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>1.52596109273688</x:v>
+        <x:v>3.24298381688544</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-1607801</x:v>
+        <x:v>-1004099</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.4467590137472</x:v>
+        <x:v>23.4374138732704</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:9">
+      <x:c r="A55" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B55" s="0">
+        <x:v>1063950</x:v>
+      </x:c>
+      <x:c r="C55" s="0">
+        <x:v>23.4594826096967</x:v>
+      </x:c>
+      <x:c r="D55" s="0">
+        <x:v>2647455</x:v>
+      </x:c>
+      <x:c r="E55" s="0">
+        <x:v>23.4547498103365</x:v>
+      </x:c>
+      <x:c r="F55" s="0">
+        <x:v>3711405</x:v>
+      </x:c>
+      <x:c r="G55" s="0">
+        <x:v>1.34956254836541</x:v>
+      </x:c>
+      <x:c r="H55" s="0">
+        <x:v>-1583505</x:v>
+      </x:c>
+      <x:c r="I55" s="0">
+        <x:v>23.4515698633964</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -46,142 +46,142 @@
     <x:t>IS</x:t>
   </x:si>
   <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
     <x:t>HSBC</x:t>
   </x:si>
   <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PAPARA </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PAPARA </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
+    <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>AHLATCI</x:t>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>HALK</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>6672022</x:v>
+        <x:v>7255077</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.2636798351155</x:v>
+        <x:v>23.2426450143119</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>4824860</x:v>
+        <x:v>5146049</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.3885234806712</x:v>
+        <x:v>23.362980994757</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>11496882</x:v>
+        <x:v>12401126</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>4.18056271686233</x:v>
+        <x:v>4.27364984363446</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1847162</x:v>
+        <x:v>2109028</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>22.9375833088247</x:v>
+        <x:v>22.9490240420755</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>16112863</x:v>
+        <x:v>16797624</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.5088019990496</x:v>
+        <x:v>23.4875192675927</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>14783374</x:v>
+        <x:v>15469383</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.4630127760081</x:v>
+        <x:v>23.4415055097204</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>30896237</x:v>
+        <x:v>32267007</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>11.2346683643045</x:v>
+        <x:v>11.1197877854077</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1329489</x:v>
+        <x:v>1328241</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24.0179594342684</x:v>
+        <x:v>24.0234193367786</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>11016270</x:v>
+        <x:v>4351823</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.4561605552198</x:v>
+        <x:v>23.400950592199</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>10445390</x:v>
+        <x:v>3516496</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.482555502044</x:v>
+        <x:v>23.4561836064407</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>21461660</x:v>
+        <x:v>7868319</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.80401291741322</x:v>
+        <x:v>2.71156347125382</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>570880</x:v>
+        <x:v>835327</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>22.9732122760583</x:v>
+        <x:v>23.168434854471</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>1934049</x:v>
+        <x:v>11655374</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.535947271035</x:v>
+        <x:v>23.4300601159712</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1417573</x:v>
+        <x:v>11178246</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.522594136287</x:v>
+        <x:v>23.4510171560953</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>3351622</x:v>
+        <x:v>22833620</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.21873617335688</x:v>
+        <x:v>7.86887388633973</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>516476</x:v>
+        <x:v>477128</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.5725976541779</x:v>
+        <x:v>22.9390745734335</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>3506406</x:v>
+        <x:v>1960493</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.4973370996054</x:v>
+        <x:v>23.5282537578608</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>3159248</x:v>
+        <x:v>1496899</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.5079304088009</x:v>
+        <x:v>23.4963122566616</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>6665654</x:v>
+        <x:v>3457392</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2.42380365353878</x:v>
+        <x:v>1.19147912699081</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>347158</x:v>
+        <x:v>463594</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.400934623243</x:v>
+        <x:v>23.6313896940544</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>750258</x:v>
+        <x:v>763002</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.3608795414943</x:v>
+        <x:v>23.353923241568</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>430162</x:v>
+        <x:v>486362</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.5649465632594</x:v>
+        <x:v>23.4991391971051</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1180420</x:v>
+        <x:v>1249364</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.429231146517693</x:v>
+        <x:v>0.430553182287038</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>320096</x:v>
+        <x:v>276640</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.0866434428974</x:v>
+        <x:v>23.0986184318263</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>1826863</x:v>
+        <x:v>994941</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.470858695221</x:v>
+        <x:v>23.4358820106942</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1635978</x:v>
+        <x:v>842414</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.4435998242309</x:v>
+        <x:v>23.4006701158855</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>3462841</x:v>
+        <x:v>1837355</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.25917826929269</x:v>
+        <x:v>0.633185398523569</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>190885</x:v>
+        <x:v>152527</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.7044805787878</x:v>
+        <x:v>23.6303590092151</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>1184305</x:v>
+        <x:v>2040058</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.4207607022829</x:v>
+        <x:v>23.414999149355</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1004474</x:v>
+        <x:v>1936959</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.4347531986303</x:v>
+        <x:v>23.4537920530394</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>2188779</x:v>
+        <x:v>3977017</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.795896477223234</x:v>
+        <x:v>1.37055119673662</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>179831</x:v>
+        <x:v>103099</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.3426034392077</x:v>
+        <x:v>22.6861825368988</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>900994</x:v>
+        <x:v>1894217</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.4805471894791</x:v>
+        <x:v>23.4541957602849</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>749623</x:v>
+        <x:v>1803921</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.4506889442076</x:v>
+        <x:v>23.4013676133184</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1650617</x:v>
+        <x:v>3698138</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.600206898706896</x:v>
+        <x:v>1.2744445049134</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>151371</x:v>
+        <x:v>90296</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.628411888762</x:v>
+        <x:v>24.5095891742127</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1333543</x:v>
+        <x:v>1356691</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.5809326196605</x:v>
+        <x:v>23.5714914793909</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1248071</x:v>
+        <x:v>1269215</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.5599743138357</x:v>
+        <x:v>23.5491712111745</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2581614</x:v>
+        <x:v>2625906</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.938741411604452</x:v>
+        <x:v>0.904934178259199</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>85472</x:v>
+        <x:v>87476</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.8869679728638</x:v>
+        <x:v>23.8953428126051</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>480895</x:v>
+        <x:v>1301163</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.2591157664742</x:v>
+        <x:v>23.3785258511148</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>397288</x:v>
+        <x:v>1222868</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.4808026615212</x:v>
+        <x:v>23.3469128571676</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>878183</x:v>
+        <x:v>2524031</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.319329980805431</x:v>
+        <x:v>0.869826230979229</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>83607</x:v>
+        <x:v>78295</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>22.2056926899444</x:v>
+        <x:v>23.8722804801751</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>272309</x:v>
+        <x:v>567965</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.4084395104323</x:v>
+        <x:v>23.2120304304558</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>201527</x:v>
+        <x:v>492995</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.3739802178774</x:v>
+        <x:v>23.3940130748773</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>473836</x:v>
+        <x:v>1060960</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.172298986412766</x:v>
+        <x:v>0.365625793827304</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>70782</x:v>
+        <x:v>74970</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.5065502992021</x:v>
+        <x:v>22.0153313003159</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1252623</x:v>
+        <x:v>281999</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.3786577455173</x:v>
+        <x:v>23.3918161797322</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1189286</x:v>
+        <x:v>212171</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.3898864161986</x:v>
+        <x:v>23.3548535290085</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>2441909</x:v>
+        <x:v>494170</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.887941071620163</x:v>
+        <x:v>0.170299821421768</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>63337</x:v>
+        <x:v>69828</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.1678157283733</x:v>
+        <x:v>23.5041264645278</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>638154</x:v>
+        <x:v>13209959</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.4171787427599</x:v>
+        <x:v>23.466325134343</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>583349</x:v>
+        <x:v>13145206</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.501063795245</x:v>
+        <x:v>23.4600765125299</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1221503</x:v>
+        <x:v>26355165</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.44416998455194</x:v>
+        <x:v>9.0824612846616</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>54805</x:v>
+        <x:v>64753</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>22.5242992339175</x:v>
+        <x:v>24.7348288476763</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>50000</x:v>
+        <x:v>1263734</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>22.9379997253418</x:v>
+        <x:v>23.3755043595007</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>0</x:v>
+        <x:v>1203163</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>0</x:v>
+        <x:v>23.3858780778851</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>50000</x:v>
+        <x:v>2466897</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0181812891393611</x:v>
+        <x:v>0.850136832599904</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>50000</x:v>
+        <x:v>60571</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>22.9379997253418</x:v>
+        <x:v>23.1694441304727</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>2827976</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.3361356935062</x:v>
+        <x:v>22.9379997253418</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>2790986</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.3254994723824</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>5618962</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.04319945570166</x:v>
+        <x:v>0.0172308943705372</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>36990</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>24.1386645999526</x:v>
+        <x:v>22.9379997253418</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>58750</x:v>
+        <x:v>679142</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.2057025016622</x:v>
+        <x:v>23.3916546646467</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>25251</x:v>
+        <x:v>639831</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.5532718763593</x:v>
+        <x:v>23.4572236533756</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>84001</x:v>
+        <x:v>1318973</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0305449293799095</x:v>
+        <x:v>0.454541688811812</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>33499</x:v>
+        <x:v>39311</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.9437103741219</x:v>
+        <x:v>22.3244451907732</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>378614</x:v>
+        <x:v>2973866</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.0563857295229</x:v>
+        <x:v>23.3172379235951</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>354105</x:v>
+        <x:v>2936730</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.0765432152809</x:v>
+        <x:v>23.3077208149762</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>732719</x:v>
+        <x:v>5910596</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.266435519938071</x:v>
+        <x:v>2.0368971068584</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>24509</x:v>
+        <x:v>37136</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>22.7651512240628</x:v>
+        <x:v>24.0698547480898</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>12560742</x:v>
+        <x:v>58750</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.4900493899247</x:v>
+        <x:v>23.2057025016622</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>12539711</x:v>
+        <x:v>25251</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.4812635219806</x:v>
+        <x:v>23.5532718763593</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>25100453</x:v>
+        <x:v>84001</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>9.12717187043888</x:v>
+        <x:v>0.02894824716039</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>21031</x:v>
+        <x:v>33499</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>28.7286136476285</x:v>
+        <x:v>22.9437103741219</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>27001</x:v>
+        <x:v>36274</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.5051871220238</x:v>
+        <x:v>23.1378772808369</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>9010</x:v>
+        <x:v>10148</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.2062595422472</x:v>
+        <x:v>23.1525146076893</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>36011</x:v>
+        <x:v>46422</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0130945280639507</x:v>
+        <x:v>0.0159978515693816</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>17991</x:v>
+        <x:v>26126</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.6548918351464</x:v>
+        <x:v>23.1321917724201</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>64546</x:v>
+        <x:v>379041</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.265324369693</x:v>
+        <x:v>23.0563284886072</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>47691</x:v>
+        <x:v>354307</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.4526756811581</x:v>
+        <x:v>23.0764809480371</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>112237</x:v>
+        <x:v>733348</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0408122669826895</x:v>
+        <x:v>0.252724838496895</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>16855</x:v>
+        <x:v>24734</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>22.7352163070955</x:v>
+        <x:v>22.767650658768</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>4173563</x:v>
+        <x:v>27001</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.4831950807289</x:v>
+        <x:v>23.5051871220238</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>4161142</x:v>
+        <x:v>9010</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.4285327267002</x:v>
+        <x:v>23.2062595422472</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>8334705</x:v>
+        <x:v>36011</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>3.03071362992558</x:v>
+        <x:v>0.0124100347435483</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>12421</x:v>
+        <x:v>17991</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>41.795554566082</x:v>
+        <x:v>23.6548918351464</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>11454</x:v>
+        <x:v>65309</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.1317409174343</x:v>
+        <x:v>23.2625238056174</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>1454</x:v>
+        <x:v>49884</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.3600006103516</x:v>
+        <x:v>23.4354112489156</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>12908</x:v>
+        <x:v>115193</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.00469368160421747</x:v>
+        <x:v>0.0396975683045059</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>10000</x:v>
+        <x:v>15425</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.0985519580841</x:v>
+        <x:v>22.7034108577091</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>5075</x:v>
+        <x:v>124490</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.1034372553332</x:v>
+        <x:v>23.2712832588988</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>0</x:v>
+        <x:v>111242</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>0</x:v>
+        <x:v>23.3941037540213</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>5075</x:v>
+        <x:v>235732</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.00184540084764515</x:v>
+        <x:v>0.0812374638351096</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>5075</x:v>
+        <x:v>13248</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.1034372553332</x:v>
+        <x:v>22.2399730597429</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>11700</x:v>
+        <x:v>11454</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.4238735736945</x:v>
+        <x:v>23.1317409174343</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>6780</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.2573216128842</x:v>
+        <x:v>23.3600006103516</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>18480</x:v>
+        <x:v>12908</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00671980446590787</x:v>
+        <x:v>0.00444832769069789</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>4920</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.653390300177</x:v>
+        <x:v>23.0985519580841</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>677273</x:v>
+        <x:v>9037</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.5637968911833</x:v>
+        <x:v>23.0580883114768</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>672720</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.5788307313758</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1349993</x:v>
+        <x:v>9037</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.490892261382271</x:v>
+        <x:v>0.0031143118485309</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>4553</x:v>
+        <x:v>9037</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>21.342499949763</x:v>
+        <x:v>23.0580883114768</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>1774001</x:v>
+        <x:v>2881580</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.4763413637907</x:v>
+        <x:v>23.4904387423318</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1773160</x:v>
+        <x:v>2880058</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.4964302585122</x:v>
+        <x:v>23.4941108301037</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>3547161</x:v>
+        <x:v>5761638</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>1.28983919529731</x:v>
+        <x:v>1.98556351558547</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>841</x:v>
+        <x:v>1522</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>-18.8789791646951</x:v>
+        <x:v>16.5418015779553</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>2628843</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.5324761505318</x:v>
+        <x:v>23.5599994659424</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>2628331</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.5384516541292</x:v>
+        <x:v>23.4799995422363</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>5257174</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>1.91164401099863</x:v>
+        <x:v>0.000344617887410745</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>512</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>-7.1425264775753</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,22 +1399,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>500</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.5599994659424</x:v>
+        <x:v>23.5600001017253</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>500</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.4799995422363</x:v>
+        <x:v>23.5400002797445</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.000363625782787222</x:v>
+        <x:v>0.00516926831116117</x:v>
       </x:c>
       <x:c r="H30" s="0">
         <x:v>0</x:v>
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>7500</x:v>
+        <x:v>11700</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.5600001017253</x:v>
+        <x:v>23.4238735736945</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>7500</x:v>
+        <x:v>13325</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.5400002797445</x:v>
+        <x:v>23.1217590728531</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>15000</x:v>
+        <x:v>25025</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00545438674180833</x:v>
+        <x:v>0.00862406263245388</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>0</x:v>
+        <x:v>-1625</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0</x:v>
+        <x:v>20.946534666795</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>9056</x:v>
+        <x:v>1704</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.5522703715853</x:v>
+        <x:v>23.1544364147903</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>9859</x:v>
+        <x:v>7965</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.1562022518611</x:v>
+        <x:v>23.6014260832648</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>18915</x:v>
+        <x:v>9669</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00687798168142031</x:v>
+        <x:v>0.00333211035337449</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-803</x:v>
+        <x:v>-6261</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>18.689461414722</x:v>
+        <x:v>23.7230792369273</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>108790</x:v>
+        <x:v>712691</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.324864958998</x:v>
+        <x:v>23.5349120346404</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>111242</x:v>
+        <x:v>719185</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.3941037540213</x:v>
+        <x:v>23.5401437819085</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>220032</x:v>
+        <x:v>1431876</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0800093082382381</x:v>
+        <x:v>0.493450082154147</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-2452</x:v>
+        <x:v>-6494</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>26.4660811237565</x:v>
+        <x:v>24.114307501076</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>1704</x:v>
+        <x:v>33151</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.1544364147903</x:v>
+        <x:v>23.2514388553985</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>7855</x:v>
+        <x:v>40989</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.6098483454111</x:v>
+        <x:v>23.108965347172</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>9559</x:v>
+        <x:v>74140</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00347589885766306</x:v>
+        <x:v>0.0255499701726326</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-6151</x:v>
+        <x:v>-7838</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.736010258885</x:v>
+        <x:v>22.5063703903954</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>33070</x:v>
+        <x:v>483583</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.2521526933618</x:v>
+        <x:v>23.4872430900269</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>39912</x:v>
+        <x:v>497893</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.1105527434327</x:v>
+        <x:v>23.1468657217183</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>72982</x:v>
+        <x:v>981476</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0265381368793771</x:v>
+        <x:v>0.338234185664348</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-6842</x:v>
+        <x:v>-14310</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>22.4261460868771</x:v>
+        <x:v>11.6443703409511</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>8649</x:v>
+        <x:v>8669</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.4484168709958</x:v>
+        <x:v>23.4470132103235</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>22907</x:v>
+        <x:v>23007</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.6176047113433</x:v>
+        <x:v>23.6151810783386</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>31556</x:v>
+        <x:v>31676</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0114745752016336</x:v>
+        <x:v>0.0109161162016227</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-14258</x:v>
+        <x:v>-14338</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.7202352086898</x:v>
+        <x:v>23.716858247248</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>475593</x:v>
+        <x:v>392770</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.4958504393165</x:v>
+        <x:v>23.4934255467063</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>496839</x:v>
+        <x:v>417393</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.1470053978033</x:v>
+        <x:v>23.4850006476812</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>972432</x:v>
+        <x:v>810163</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.353601347207344</x:v>
+        <x:v>0.279196661518351</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-21246</x:v>
+        <x:v>-24623</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>15.3380879625968</x:v>
+        <x:v>23.3506121657707</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>374101</x:v>
+        <x:v>250134</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.5142663964116</x:v>
+        <x:v>23.3502810734718</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>397203</x:v>
+        <x:v>286959</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.5109296655949</x:v>
+        <x:v>23.5311238816091</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>771304</x:v>
+        <x:v>537093</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.280466020766916</x:v>
+        <x:v>0.185091855003099</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-23102</x:v>
+        <x:v>-36825</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.4568964937798</x:v>
+        <x:v>24.7594995766696</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>185888</x:v>
+        <x:v>648417</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.3745449519666</x:v>
+        <x:v>23.4237668336968</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>209560</x:v>
+        <x:v>688106</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.5703329466026</x:v>
+        <x:v>23.3317784878463</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>395448</x:v>
+        <x:v>1336523</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.143795088551642</x:v>
+        <x:v>0.460589732735871</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-23672</x:v>
+        <x:v>-39689</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>25.1077881150247</x:v>
+        <x:v>21.8289236098858</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>2303356</x:v>
+        <x:v>191429</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.430291861624</x:v>
+        <x:v>23.3608476738242</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>2338564</x:v>
+        <x:v>236660</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.466255312383</x:v>
+        <x:v>23.5120579312541</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>4641920</x:v>
+        <x:v>428089</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>1.68792179363566</x:v>
+        <x:v>0.147527126803778</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-35208</x:v>
+        <x:v>-45231</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>25.8190339446962</x:v>
+        <x:v>24.1520178784044</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>585194</x:v>
+        <x:v>1309756</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.4666576877138</x:v>
+        <x:v>23.5486361532514</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>633238</x:v>
+        <x:v>1359765</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.3569869155778</x:v>
+        <x:v>23.5241910062211</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>1218432</x:v>
+        <x:v>2669521</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.443053289773001</x:v>
+        <x:v>0.919964687418618</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-48044</x:v>
+        <x:v>-50009</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>22.0211556394693</x:v>
+        <x:v>22.8839626874441</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>3225108</x:v>
+        <x:v>3239738</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.5914576972727</x:v>
+        <x:v>23.5888767807859</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>3276229</x:v>
+        <x:v>3292390</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.5792017751644</x:v>
+        <x:v>23.5763595602686</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>6501337</x:v>
+        <x:v>6532128</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>2.36405375578853</x:v>
+        <x:v>2.25108815165657</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-51121</x:v>
+        <x:v>-52652</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>22.8060034332168</x:v>
+        <x:v>22.8061606131416</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>204529</x:v>
+        <x:v>4284026</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.4313680957116</x:v>
+        <x:v>23.4714207339905</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>260742</x:v>
+        <x:v>4344123</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.5858674878578</x:v>
+        <x:v>23.4112828443893</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>465271</x:v>
+        <x:v>8628149</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.169184531583194</x:v>
+        <x:v>2.97341448064513</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-56213</x:v>
+        <x:v>-60097</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>24.1480080278801</x:v>
+        <x:v>19.1243420214372</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1235797</x:v>
+        <x:v>2395099</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.5810025221955</x:v>
+        <x:v>23.4140588148338</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>1302113</x:v>
+        <x:v>2500982</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.5503442462873</x:v>
+        <x:v>23.435560551322</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>2537910</x:v>
+        <x:v>4896081</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.922849510393519</x:v>
+        <x:v>1.68727709081189</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-66316</x:v>
+        <x:v>-105883</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>22.9790280421656</x:v>
+        <x:v>23.9219350171098</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>2254016</x:v>
+        <x:v>742418</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.4708265562282</x:v>
+        <x:v>23.2675665603941</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>2366004</x:v>
+        <x:v>879806</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>23.469871893313</x:v>
+        <x:v>23.3670044755789</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>4620020</x:v>
+        <x:v>1622224</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.67995838899262</x:v>
+        <x:v>0.559047407787008</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-111988</x:v>
+        <x:v>-137388</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.4506571070358</x:v>
+        <x:v>23.9043476068252</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>667145</x:v>
+        <x:v>2342468</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.2967653686214</x:v>
+        <x:v>23.4524021312174</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>820919</x:v>
+        <x:v>2492511</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.3936000040463</x:v>
+        <x:v>23.4452442599149</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>1488064</x:v>
+        <x:v>4834979</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.541098436837485</x:v>
+        <x:v>1.66622024865532</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-153774</x:v>
+        <x:v>-150043</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.8137148664452</x:v>
+        <x:v>23.3334957313305</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>5966898</x:v>
+        <x:v>332815</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.4398171633986</x:v>
+        <x:v>23.3639105694216</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>6150847</x:v>
+        <x:v>523417</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.4951803145649</x:v>
+        <x:v>22.9939601006542</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>12117745</x:v>
+        <x:v>856232</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.40632451124095</x:v>
+        <x:v>0.295072862973477</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-183949</x:v>
+        <x:v>-190602</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.2910382750203</x:v>
+        <x:v>22.3479801777636</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>324117</x:v>
+        <x:v>20725612</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.3758899965587</x:v>
+        <x:v>23.4236677905893</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>518044</x:v>
+        <x:v>20917822</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>22.9927144214145</x:v>
+        <x:v>23.4305498297201</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>842161</x:v>
+        <x:v>41643434</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0.30623145285787</x:v>
+        <x:v>14.3510722496088</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-193927</x:v>
+        <x:v>-192210</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>22.352299637042</x:v>
+        <x:v>24.1726260629754</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>20309960</x:v>
+        <x:v>6299168</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.4320804241148</x:v>
+        <x:v>23.4143137536793</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>20513757</x:v>
+        <x:v>6600230</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.438616062361</x:v>
+        <x:v>23.4614527257615</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>40823717</x:v>
+        <x:v>12899398</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>14.844556050409</x:v>
+        <x:v>4.44536328763038</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-203797</x:v>
+        <x:v>-301062</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>24.0899433701985</x:v>
+        <x:v>24.4477489188826</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>4110638</x:v>
+        <x:v>4294876</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.4711108810886</x:v>
+        <x:v>23.4499579553327</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>4498832</x:v>
+        <x:v>4755337</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>23.4488757984536</x:v>
+        <x:v>23.4238854784208</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>8609470</x:v>
+        <x:v>9050213</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>3.13062526813311</x:v>
+        <x:v>3.11886528467726</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-388194</x:v>
+        <x:v>-460461</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.2134255451972</x:v>
+        <x:v>23.1806986388207</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>9646398</x:v>
+        <x:v>10191934</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.4956684121239</x:v>
+        <x:v>23.468755289444</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>10156278</x:v>
+        <x:v>10720576</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.4361554688431</x:v>
+        <x:v>23.4125335992344</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>19802676</x:v>
+        <x:v>20912510</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>7.20076356178174</x:v>
+        <x:v>7.20682501665607</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-509880</x:v>
+        <x:v>-528642</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>22.3102326300618</x:v>
+        <x:v>22.3286095901994</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>664759</x:v>
+        <x:v>670461</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.1939679074686</x:v>
+        <x:v>23.1914981036379</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1245305</x:v>
+        <x:v>1249082</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>23.4526574395277</x:v>
+        <x:v>23.4512886207005</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>1910064</x:v>
+        <x:v>1919543</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>0.694548517173693</x:v>
+        <x:v>0.661508853454083</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-580546</x:v>
+        <x:v>-578621</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>23.7488720282804</x:v>
+        <x:v>23.7523136610297</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>6649010</x:v>
+        <x:v>7253604</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>23.4751587147339</x:v>
+        <x:v>23.4343384084529</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>7430471</x:v>
+        <x:v>8000344</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>23.4673178528168</x:v>
+        <x:v>23.4324035204387</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>14079481</x:v>
+        <x:v>15253948</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>5.11966229986282</x:v>
+        <x:v>5.25678333443335</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-781461</x:v>
+        <x:v>-746740</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>23.400604390091</x:v>
+        <x:v>23.4136086099746</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>3957183</x:v>
+        <x:v>4155988</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>23.4772988098892</x:v>
+        <x:v>23.4540943272481</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>4961282</x:v>
+        <x:v>5336290</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>23.4692266170621</x:v>
+        <x:v>23.4333323980421</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>8918465</x:v>
+        <x:v>9492278</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>3.24298381688544</x:v>
+        <x:v>3.27120879107549</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-1004099</x:v>
+        <x:v>-1180302</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>23.4374138732704</x:v>
+        <x:v>23.3602271007225</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>1063950</x:v>
+        <x:v>1117957</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>23.4594826096967</x:v>
+        <x:v>23.4370215381772</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>2647455</x:v>
+        <x:v>2735813</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>23.4547498103365</x:v>
+        <x:v>23.4417941854745</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>3711405</x:v>
+        <x:v>3853770</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>1.34956254836541</x:v>
+        <x:v>1.32807807596691</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-1583505</x:v>
+        <x:v>-1617856</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.4515698633964</x:v>
+        <x:v>23.4450921393435</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,166 +40,121 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PAPARA </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
+    <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -550,7 +505,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I55"/>
+  <x:dimension ref="A1:I40"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -587,28 +542,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>7255077</x:v>
+        <x:v>259015</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.2426450143119</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>5146049</x:v>
+        <x:v>27388</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.362980994757</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>12401126</x:v>
+        <x:v>286403</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>4.27364984363446</x:v>
+        <x:v>27.577730060759</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2109028</x:v>
+        <x:v>231627</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>22.9490240420755</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +571,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>16797624</x:v>
+        <x:v>52000</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.4875192675927</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>15469383</x:v>
+        <x:v>2243</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.4415055097204</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>32267007</x:v>
+        <x:v>54243</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>11.1197877854077</x:v>
+        <x:v>5.22305566521911</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1328241</x:v>
+        <x:v>49757</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24.0234193367786</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +600,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>4351823</x:v>
+        <x:v>40800</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.400950592199</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>3516496</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.4561836064407</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>7868319</x:v>
+        <x:v>40800</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.71156347125382</x:v>
+        <x:v>3.92862989032575</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>835327</x:v>
+        <x:v>40800</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.168434854471</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +629,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>11655374</x:v>
+        <x:v>20600</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.4300601159712</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>11178246</x:v>
+        <x:v>1325</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.4510171560953</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>22833620</x:v>
+        <x:v>21925</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>7.86887388633973</x:v>
+        <x:v>2.11115711630863</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>477128</x:v>
+        <x:v>19275</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>22.9390745734335</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +658,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>1960493</x:v>
+        <x:v>20864</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.5282537578608</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1496899</x:v>
+        <x:v>2212</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.4963122566616</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>3457392</x:v>
+        <x:v>23076</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.19147912699081</x:v>
+        <x:v>2.22198684679306</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>463594</x:v>
+        <x:v>18652</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.6313896940544</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +687,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>763002</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.353923241568</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>486362</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.4991391971051</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1249364</x:v>
+        <x:v>18685</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.430553182287038</x:v>
+        <x:v>1.79917768384158</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>276640</x:v>
+        <x:v>17315</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.0986184318263</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +716,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>994941</x:v>
+        <x:v>18144</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.4358820106942</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>842414</x:v>
+        <x:v>5126</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.4006701158855</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1837355</x:v>
+        <x:v>23270</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.633185398523569</x:v>
+        <x:v>2.24066709676177</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>152527</x:v>
+        <x:v>13018</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.6303590092151</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +745,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>2040058</x:v>
+        <x:v>3865</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.414999149355</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1936959</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.4537920530394</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>3977017</x:v>
+        <x:v>5325</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.37055119673662</x:v>
+        <x:v>0.512743974656486</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>103099</x:v>
+        <x:v>2405</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>22.6861825368988</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +774,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1894217</x:v>
+        <x:v>5207</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.4541957602849</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1803921</x:v>
+        <x:v>4845</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.4013676133184</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>3698138</x:v>
+        <x:v>10052</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.2744445049134</x:v>
+        <x:v>0.967906560234177</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>90296</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>24.5095891742127</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +803,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1356691</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.5714914793909</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1269215</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.5491712111745</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2625906</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.904934178259199</x:v>
+        <x:v>0.0288869844876893</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>87476</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.8953428126051</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +832,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1301163</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.3785258511148</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1222868</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.3469128571676</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>2524031</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.869826230979229</x:v>
+        <x:v>0.000674029638046084</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>78295</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.8722804801751</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +861,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>567965</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.2120304304558</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>492995</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.3940130748773</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>1060960</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.365625793827304</x:v>
+        <x:v>0.000962899482922978</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>74970</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>22.0153313003159</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +890,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>281999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.3918161797322</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>212171</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.3548535290085</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>494170</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.170299821421768</x:v>
+        <x:v>0.000962899482922978</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>69828</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.5041264645278</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +919,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>13209959</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.466325134343</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>13145206</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.4600765125299</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>26355165</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>9.0824612846616</x:v>
+        <x:v>0.0337977718505965</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>64753</x:v>
+        <x:v>-91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>24.7348288476763</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +948,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>1263734</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.3755043595007</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1203163</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.3858780778851</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>2466897</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.850136832599904</x:v>
+        <x:v>0.00962899482922978</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>60571</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.1694441304727</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +977,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>50000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>22.9379997253418</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>0</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>0</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>50000</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0172308943705372</x:v>
+        <x:v>0.0139620425023832</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>50000</x:v>
+        <x:v>-145</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.9379997253418</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1006,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>679142</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.3916546646467</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>639831</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.4572236533756</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1318973</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.454541688811812</x:v>
+        <x:v>0.0234947473833207</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>39311</x:v>
+        <x:v>-244</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.3244451907732</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1035,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>2973866</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.3172379235951</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>2936730</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.3077208149762</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>5910596</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>2.0368971068584</x:v>
+        <x:v>0.0392862989032575</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>37136</x:v>
+        <x:v>-318</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>24.0698547480898</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1064,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>58750</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.2057025016622</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>25251</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.5532718763593</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>84001</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.02894824716039</x:v>
+        <x:v>0.0358198607647348</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>33499</x:v>
+        <x:v>-366</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.9437103741219</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1093,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>36274</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.1378772808369</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>10148</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.1525146076893</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>46422</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0159978515693816</x:v>
+        <x:v>0.035242121074981</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>26126</x:v>
+        <x:v>-366</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.1321917724201</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1122,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>379041</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.0563284886072</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>354307</x:v>
+        <x:v>1632</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.0764809480371</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>733348</x:v>
+        <x:v>2832</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.252724838496895</x:v>
+        <x:v>0.272693133563787</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>24734</x:v>
+        <x:v>-432</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>22.767650658768</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1151,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>27001</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.5051871220238</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>9010</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.2062595422472</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>36011</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0124100347435483</x:v>
+        <x:v>0.049781903267118</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>17991</x:v>
+        <x:v>-517</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.6548918351464</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1180,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>65309</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.2625238056174</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>49884</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.4354112489156</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>115193</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0396975683045059</x:v>
+        <x:v>0.0616255669070706</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>15425</x:v>
+        <x:v>-640</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>22.7034108577091</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1209,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>124490</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.2712832588988</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>111242</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.3941037540213</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>235732</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0812374638351096</x:v>
+        <x:v>0.0655734547870548</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>13248</x:v>
+        <x:v>-661</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>22.2399730597429</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1238,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>11454</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.1317409174343</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1454</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.3600006103516</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>12908</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00444832769069789</x:v>
+        <x:v>0.0755876094094538</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>10000</x:v>
+        <x:v>-785</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.0985519580841</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1267,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>9037</x:v>
+        <x:v>2734</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.0580883114768</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>0</x:v>
+        <x:v>4011</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>0</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>9037</x:v>
+        <x:v>6745</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0031143118485309</x:v>
+        <x:v>0.649475701231548</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>9037</x:v>
+        <x:v>-1277</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>23.0580883114768</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1296,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>2881580</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.4904387423318</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2880058</x:v>
+        <x:v>2137</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.4941108301037</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>5761638</x:v>
+        <x:v>2137</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>1.98556351558547</x:v>
+        <x:v>0.20577161950064</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>1522</x:v>
+        <x:v>-2137</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>16.5418015779553</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1325,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>500</x:v>
+        <x:v>1294</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.5599994659424</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>500</x:v>
+        <x:v>4073</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.4799995422363</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1000</x:v>
+        <x:v>5367</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.000344617887410745</x:v>
+        <x:v>0.516788152484762</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>0</x:v>
+        <x:v>-2779</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1354,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>7500</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.5600001017253</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>7500</x:v>
+        <x:v>5875</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.5400002797445</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>15000</x:v>
+        <x:v>6492</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00516926831116117</x:v>
+        <x:v>0.625114344313597</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>0</x:v>
+        <x:v>-5258</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1383,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>11700</x:v>
+        <x:v>6296</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.4238735736945</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>13325</x:v>
+        <x:v>15526</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.1217590728531</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>25025</x:v>
+        <x:v>21822</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00862406263245388</x:v>
+        <x:v>2.10123925163452</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1625</x:v>
+        <x:v>-9230</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>20.946534666795</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1412,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1704</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.1544364147903</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>7965</x:v>
+        <x:v>17350</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.6014260832648</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>9669</x:v>
+        <x:v>17850</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00333211035337449</x:v>
+        <x:v>1.71877557701752</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-6261</x:v>
+        <x:v>-16850</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.7230792369273</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1441,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>712691</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.5349120346404</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>719185</x:v>
+        <x:v>16870</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.5401437819085</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>1431876</x:v>
+        <x:v>16873</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.493450082154147</x:v>
+        <x:v>1.62470029753594</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-6494</x:v>
+        <x:v>-16867</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>24.114307501076</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1470,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>33151</x:v>
+        <x:v>15429</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.2514388553985</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>40989</x:v>
+        <x:v>32469</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.108965347172</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>74140</x:v>
+        <x:v>47898</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0255499701726326</x:v>
+        <x:v>4.61209594330448</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-7838</x:v>
+        <x:v>-17040</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>22.5063703903954</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1499,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>483583</x:v>
+        <x:v>35279</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.4872430900269</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>497893</x:v>
+        <x:v>57430</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.1468657217183</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>981476</x:v>
+        <x:v>92709</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.338234185664348</x:v>
+        <x:v>8.92694481623064</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-14310</x:v>
+        <x:v>-22151</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>11.6443703409511</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1528,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>8669</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.4470132103235</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>23007</x:v>
+        <x:v>27218</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.6151810783386</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>31676</x:v>
+        <x:v>27218</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0109161162016227</x:v>
+        <x:v>2.62081981261976</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-14338</x:v>
+        <x:v>-27218</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.716858247248</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1557,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>392770</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.4934255467063</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>417393</x:v>
+        <x:v>28025</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.4850006476812</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>810163</x:v>
+        <x:v>28170</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.279196661518351</x:v>
+        <x:v>2.71248784339403</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-24623</x:v>
+        <x:v>-27880</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>23.3506121657707</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1586,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>250134</x:v>
+        <x:v>10914</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.3502810734718</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>286959</x:v>
+        <x:v>62716</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.5311238816091</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>537093</x:v>
+        <x:v>73630</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.185091855003099</x:v>
+        <x:v>7.08982889276188</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-36825</x:v>
+        <x:v>-51802</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>24.7594995766696</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1615,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>648417</x:v>
+        <x:v>1942</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.4237668336968</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>688106</x:v>
+        <x:v>72743</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.3317784878463</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>1336523</x:v>
+        <x:v>74685</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.460589732735871</x:v>
+        <x:v>7.19141478821026</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-39689</x:v>
+        <x:v>-70801</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>21.8289236098858</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,463 +1644,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>191429</x:v>
+        <x:v>3929</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.3608476738242</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>236660</x:v>
+        <x:v>121458</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.5120579312541</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>428089</x:v>
+        <x:v>125387</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.147527126803778</x:v>
+        <x:v>12.0735077465263</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-45231</x:v>
+        <x:v>-117529</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>24.1520178784044</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:9">
-      <x:c r="A41" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B41" s="0">
-        <x:v>1309756</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>23.5486361532514</x:v>
-      </x:c>
-      <x:c r="D41" s="0">
-        <x:v>1359765</x:v>
-      </x:c>
-      <x:c r="E41" s="0">
-        <x:v>23.5241910062211</x:v>
-      </x:c>
-      <x:c r="F41" s="0">
-        <x:v>2669521</x:v>
-      </x:c>
-      <x:c r="G41" s="0">
-        <x:v>0.919964687418618</x:v>
-      </x:c>
-      <x:c r="H41" s="0">
-        <x:v>-50009</x:v>
-      </x:c>
-      <x:c r="I41" s="0">
-        <x:v>22.8839626874441</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:9">
-      <x:c r="A42" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B42" s="0">
-        <x:v>3239738</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>23.5888767807859</x:v>
-      </x:c>
-      <x:c r="D42" s="0">
-        <x:v>3292390</x:v>
-      </x:c>
-      <x:c r="E42" s="0">
-        <x:v>23.5763595602686</x:v>
-      </x:c>
-      <x:c r="F42" s="0">
-        <x:v>6532128</x:v>
-      </x:c>
-      <x:c r="G42" s="0">
-        <x:v>2.25108815165657</x:v>
-      </x:c>
-      <x:c r="H42" s="0">
-        <x:v>-52652</x:v>
-      </x:c>
-      <x:c r="I42" s="0">
-        <x:v>22.8061606131416</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:9">
-      <x:c r="A43" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B43" s="0">
-        <x:v>4284026</x:v>
-      </x:c>
-      <x:c r="C43" s="0">
-        <x:v>23.4714207339905</x:v>
-      </x:c>
-      <x:c r="D43" s="0">
-        <x:v>4344123</x:v>
-      </x:c>
-      <x:c r="E43" s="0">
-        <x:v>23.4112828443893</x:v>
-      </x:c>
-      <x:c r="F43" s="0">
-        <x:v>8628149</x:v>
-      </x:c>
-      <x:c r="G43" s="0">
-        <x:v>2.97341448064513</x:v>
-      </x:c>
-      <x:c r="H43" s="0">
-        <x:v>-60097</x:v>
-      </x:c>
-      <x:c r="I43" s="0">
-        <x:v>19.1243420214372</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:9">
-      <x:c r="A44" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B44" s="0">
-        <x:v>2395099</x:v>
-      </x:c>
-      <x:c r="C44" s="0">
-        <x:v>23.4140588148338</x:v>
-      </x:c>
-      <x:c r="D44" s="0">
-        <x:v>2500982</x:v>
-      </x:c>
-      <x:c r="E44" s="0">
-        <x:v>23.435560551322</x:v>
-      </x:c>
-      <x:c r="F44" s="0">
-        <x:v>4896081</x:v>
-      </x:c>
-      <x:c r="G44" s="0">
-        <x:v>1.68727709081189</x:v>
-      </x:c>
-      <x:c r="H44" s="0">
-        <x:v>-105883</x:v>
-      </x:c>
-      <x:c r="I44" s="0">
-        <x:v>23.9219350171098</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:9">
-      <x:c r="A45" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B45" s="0">
-        <x:v>742418</x:v>
-      </x:c>
-      <x:c r="C45" s="0">
-        <x:v>23.2675665603941</x:v>
-      </x:c>
-      <x:c r="D45" s="0">
-        <x:v>879806</x:v>
-      </x:c>
-      <x:c r="E45" s="0">
-        <x:v>23.3670044755789</x:v>
-      </x:c>
-      <x:c r="F45" s="0">
-        <x:v>1622224</x:v>
-      </x:c>
-      <x:c r="G45" s="0">
-        <x:v>0.559047407787008</x:v>
-      </x:c>
-      <x:c r="H45" s="0">
-        <x:v>-137388</x:v>
-      </x:c>
-      <x:c r="I45" s="0">
-        <x:v>23.9043476068252</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:9">
-      <x:c r="A46" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B46" s="0">
-        <x:v>2342468</x:v>
-      </x:c>
-      <x:c r="C46" s="0">
-        <x:v>23.4524021312174</x:v>
-      </x:c>
-      <x:c r="D46" s="0">
-        <x:v>2492511</x:v>
-      </x:c>
-      <x:c r="E46" s="0">
-        <x:v>23.4452442599149</x:v>
-      </x:c>
-      <x:c r="F46" s="0">
-        <x:v>4834979</x:v>
-      </x:c>
-      <x:c r="G46" s="0">
-        <x:v>1.66622024865532</x:v>
-      </x:c>
-      <x:c r="H46" s="0">
-        <x:v>-150043</x:v>
-      </x:c>
-      <x:c r="I46" s="0">
-        <x:v>23.3334957313305</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:9">
-      <x:c r="A47" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B47" s="0">
-        <x:v>332815</x:v>
-      </x:c>
-      <x:c r="C47" s="0">
-        <x:v>23.3639105694216</x:v>
-      </x:c>
-      <x:c r="D47" s="0">
-        <x:v>523417</x:v>
-      </x:c>
-      <x:c r="E47" s="0">
-        <x:v>22.9939601006542</x:v>
-      </x:c>
-      <x:c r="F47" s="0">
-        <x:v>856232</x:v>
-      </x:c>
-      <x:c r="G47" s="0">
-        <x:v>0.295072862973477</x:v>
-      </x:c>
-      <x:c r="H47" s="0">
-        <x:v>-190602</x:v>
-      </x:c>
-      <x:c r="I47" s="0">
-        <x:v>22.3479801777636</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:9">
-      <x:c r="A48" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B48" s="0">
-        <x:v>20725612</x:v>
-      </x:c>
-      <x:c r="C48" s="0">
-        <x:v>23.4236677905893</x:v>
-      </x:c>
-      <x:c r="D48" s="0">
-        <x:v>20917822</x:v>
-      </x:c>
-      <x:c r="E48" s="0">
-        <x:v>23.4305498297201</x:v>
-      </x:c>
-      <x:c r="F48" s="0">
-        <x:v>41643434</x:v>
-      </x:c>
-      <x:c r="G48" s="0">
-        <x:v>14.3510722496088</x:v>
-      </x:c>
-      <x:c r="H48" s="0">
-        <x:v>-192210</x:v>
-      </x:c>
-      <x:c r="I48" s="0">
-        <x:v>24.1726260629754</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:9">
-      <x:c r="A49" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B49" s="0">
-        <x:v>6299168</x:v>
-      </x:c>
-      <x:c r="C49" s="0">
-        <x:v>23.4143137536793</x:v>
-      </x:c>
-      <x:c r="D49" s="0">
-        <x:v>6600230</x:v>
-      </x:c>
-      <x:c r="E49" s="0">
-        <x:v>23.4614527257615</x:v>
-      </x:c>
-      <x:c r="F49" s="0">
-        <x:v>12899398</x:v>
-      </x:c>
-      <x:c r="G49" s="0">
-        <x:v>4.44536328763038</x:v>
-      </x:c>
-      <x:c r="H49" s="0">
-        <x:v>-301062</x:v>
-      </x:c>
-      <x:c r="I49" s="0">
-        <x:v>24.4477489188826</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:9">
-      <x:c r="A50" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B50" s="0">
-        <x:v>4294876</x:v>
-      </x:c>
-      <x:c r="C50" s="0">
-        <x:v>23.4499579553327</x:v>
-      </x:c>
-      <x:c r="D50" s="0">
-        <x:v>4755337</x:v>
-      </x:c>
-      <x:c r="E50" s="0">
-        <x:v>23.4238854784208</x:v>
-      </x:c>
-      <x:c r="F50" s="0">
-        <x:v>9050213</x:v>
-      </x:c>
-      <x:c r="G50" s="0">
-        <x:v>3.11886528467726</x:v>
-      </x:c>
-      <x:c r="H50" s="0">
-        <x:v>-460461</x:v>
-      </x:c>
-      <x:c r="I50" s="0">
-        <x:v>23.1806986388207</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:9">
-      <x:c r="A51" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B51" s="0">
-        <x:v>10191934</x:v>
-      </x:c>
-      <x:c r="C51" s="0">
-        <x:v>23.468755289444</x:v>
-      </x:c>
-      <x:c r="D51" s="0">
-        <x:v>10720576</x:v>
-      </x:c>
-      <x:c r="E51" s="0">
-        <x:v>23.4125335992344</x:v>
-      </x:c>
-      <x:c r="F51" s="0">
-        <x:v>20912510</x:v>
-      </x:c>
-      <x:c r="G51" s="0">
-        <x:v>7.20682501665607</x:v>
-      </x:c>
-      <x:c r="H51" s="0">
-        <x:v>-528642</x:v>
-      </x:c>
-      <x:c r="I51" s="0">
-        <x:v>22.3286095901994</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:9">
-      <x:c r="A52" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B52" s="0">
-        <x:v>670461</x:v>
-      </x:c>
-      <x:c r="C52" s="0">
-        <x:v>23.1914981036379</x:v>
-      </x:c>
-      <x:c r="D52" s="0">
-        <x:v>1249082</x:v>
-      </x:c>
-      <x:c r="E52" s="0">
-        <x:v>23.4512886207005</x:v>
-      </x:c>
-      <x:c r="F52" s="0">
-        <x:v>1919543</x:v>
-      </x:c>
-      <x:c r="G52" s="0">
-        <x:v>0.661508853454083</x:v>
-      </x:c>
-      <x:c r="H52" s="0">
-        <x:v>-578621</x:v>
-      </x:c>
-      <x:c r="I52" s="0">
-        <x:v>23.7523136610297</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:9">
-      <x:c r="A53" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B53" s="0">
-        <x:v>7253604</x:v>
-      </x:c>
-      <x:c r="C53" s="0">
-        <x:v>23.4343384084529</x:v>
-      </x:c>
-      <x:c r="D53" s="0">
-        <x:v>8000344</x:v>
-      </x:c>
-      <x:c r="E53" s="0">
-        <x:v>23.4324035204387</x:v>
-      </x:c>
-      <x:c r="F53" s="0">
-        <x:v>15253948</x:v>
-      </x:c>
-      <x:c r="G53" s="0">
-        <x:v>5.25678333443335</x:v>
-      </x:c>
-      <x:c r="H53" s="0">
-        <x:v>-746740</x:v>
-      </x:c>
-      <x:c r="I53" s="0">
-        <x:v>23.4136086099746</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:9">
-      <x:c r="A54" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B54" s="0">
-        <x:v>4155988</x:v>
-      </x:c>
-      <x:c r="C54" s="0">
-        <x:v>23.4540943272481</x:v>
-      </x:c>
-      <x:c r="D54" s="0">
-        <x:v>5336290</x:v>
-      </x:c>
-      <x:c r="E54" s="0">
-        <x:v>23.4333323980421</x:v>
-      </x:c>
-      <x:c r="F54" s="0">
-        <x:v>9492278</x:v>
-      </x:c>
-      <x:c r="G54" s="0">
-        <x:v>3.27120879107549</x:v>
-      </x:c>
-      <x:c r="H54" s="0">
-        <x:v>-1180302</x:v>
-      </x:c>
-      <x:c r="I54" s="0">
-        <x:v>23.3602271007225</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:9">
-      <x:c r="A55" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B55" s="0">
-        <x:v>1117957</x:v>
-      </x:c>
-      <x:c r="C55" s="0">
-        <x:v>23.4370215381772</x:v>
-      </x:c>
-      <x:c r="D55" s="0">
-        <x:v>2735813</x:v>
-      </x:c>
-      <x:c r="E55" s="0">
-        <x:v>23.4417941854745</x:v>
-      </x:c>
-      <x:c r="F55" s="0">
-        <x:v>3853770</x:v>
-      </x:c>
-      <x:c r="G55" s="0">
-        <x:v>1.32807807596691</x:v>
-      </x:c>
-      <x:c r="H55" s="0">
-        <x:v>-1617856</x:v>
-      </x:c>
-      <x:c r="I55" s="0">
-        <x:v>23.4450921393435</x:v>
+        <x:v>23.1399993896484</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,121 +40,148 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
     <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -505,7 +532,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I40"/>
+  <x:dimension ref="A1:I49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -542,28 +569,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>259015</x:v>
+        <x:v>1566952</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0105513771085</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>27388</x:v>
+        <x:v>1113885</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9912156166613</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>286403</x:v>
+        <x:v>2680837</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>27.577730060759</x:v>
+        <x:v>8.69322139787068</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>231627</x:v>
+        <x:v>453067</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.05808918835</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -571,28 +598,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>52000</x:v>
+        <x:v>1617252</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.1246495889317</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>2243</x:v>
+        <x:v>1194441</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0805942330211</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>54243</x:v>
+        <x:v>2811693</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>5.22305566521911</x:v>
+        <x:v>9.11755162728775</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>49757</x:v>
+        <x:v>422811</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.2491059615644</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -600,28 +627,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>40800</x:v>
+        <x:v>361670</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.1476373397408</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>0</x:v>
+        <x:v>102830</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>0</x:v>
+        <x:v>23.0713145400999</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>40800</x:v>
+        <x:v>464500</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>3.92862989032575</x:v>
+        <x:v>1.50624649663927</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>40800</x:v>
+        <x:v>258840</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.1779582850625</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -629,28 +656,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>20600</x:v>
+        <x:v>2140651</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.990949976667</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1325</x:v>
+        <x:v>1991237</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0204814459431</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>21925</x:v>
+        <x:v>4131888</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.11115711630863</x:v>
+        <x:v>13.3985830452225</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>19275</x:v>
+        <x:v>149414</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.5973847532821</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -658,28 +685,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>20864</x:v>
+        <x:v>105942</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9066585766466</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>2212</x:v>
+        <x:v>11017</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9356342451406</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>23076</x:v>
+        <x:v>116959</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2.22198684679306</x:v>
+        <x:v>0.379266058127949</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>18652</x:v>
+        <x:v>94925</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9032956591876</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -687,28 +714,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>18000</x:v>
+        <x:v>247723</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0485830810209</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>685</x:v>
+        <x:v>157233</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0650419069876</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>18685</x:v>
+        <x:v>404956</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.79917768384158</x:v>
+        <x:v>1.31316158513036</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>17315</x:v>
+        <x:v>90490</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0199846659119</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -716,28 +743,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>18144</x:v>
+        <x:v>565606</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0036578744821</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>5126</x:v>
+        <x:v>479300</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9896255712352</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>23270</x:v>
+        <x:v>1044906</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.24066709676177</x:v>
+        <x:v>3.38834446031723</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>13018</x:v>
+        <x:v>86306</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0815862102436</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -745,28 +772,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>3865</x:v>
+        <x:v>278967</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9793024013575</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1460</x:v>
+        <x:v>209622</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0019899857029</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>5325</x:v>
+        <x:v>488589</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.512743974656486</x:v>
+        <x:v>1.58436053723678</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>2405</x:v>
+        <x:v>69345</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.910720429973</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -774,28 +801,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>5207</x:v>
+        <x:v>452664</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0422604369655</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>4845</x:v>
+        <x:v>394763</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.061699130611</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>10052</x:v>
+        <x:v>847427</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.967906560234177</x:v>
+        <x:v>2.74797405792794</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>362</x:v>
+        <x:v>57901</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9097294440712</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -803,28 +830,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>300</x:v>
+        <x:v>880004</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0426455108315</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>0</x:v>
+        <x:v>831327</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>0</x:v>
+        <x:v>23.0320142423275</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>300</x:v>
+        <x:v>1711331</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.0288869844876893</x:v>
+        <x:v>5.54937852172267</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>300</x:v>
+        <x:v>48677</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.2242109432048</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -832,28 +859,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>0</x:v>
+        <x:v>74488</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>0</x:v>
+        <x:v>22.9244459496573</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>7</x:v>
+        <x:v>27617</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.2026301613715</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>7</x:v>
+        <x:v>102105</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.000674029638046084</x:v>
+        <x:v>0.331098597501298</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-7</x:v>
+        <x:v>46871</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.7605362106948</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -861,28 +888,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>0</x:v>
+        <x:v>39936</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>0</x:v>
+        <x:v>23.1012628182578</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>10</x:v>
+        <x:v>8106</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0897954380309</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>10</x:v>
+        <x:v>48042</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.000962899482922978</x:v>
+        <x:v>0.155787070380073</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-10</x:v>
+        <x:v>31830</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.1041831633448</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -890,28 +917,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>0</x:v>
+        <x:v>415924</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>0</x:v>
+        <x:v>23.0146558252682</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>10</x:v>
+        <x:v>387602</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0819364842068</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>10</x:v>
+        <x:v>803526</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.000962899482922978</x:v>
+        <x:v>2.60561511831769</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-10</x:v>
+        <x:v>28322</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.093883352776</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -919,28 +946,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>130</x:v>
+        <x:v>31020</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0549967819302</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>221</x:v>
+        <x:v>6055</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.007946877515</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>351</x:v>
+        <x:v>37075</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0337977718505965</x:v>
+        <x:v>0.1202240879718</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-91</x:v>
+        <x:v>24965</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0664082448277</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -948,28 +975,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>0</x:v>
+        <x:v>75691</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>0</x:v>
+        <x:v>23.0096481851064</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>100</x:v>
+        <x:v>52240</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.985786906939</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>100</x:v>
+        <x:v>127931</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.00962899482922978</x:v>
+        <x:v>0.414845254169125</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-100</x:v>
+        <x:v>23451</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0628021304162</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -977,28 +1004,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>0</x:v>
+        <x:v>284238</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>0</x:v>
+        <x:v>22.9754350121293</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>145</x:v>
+        <x:v>271616</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0434266510055</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>145</x:v>
+        <x:v>555854</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0139620425023832</x:v>
+        <x:v>1.80248254067368</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-145</x:v>
+        <x:v>12622</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>21.5123057944936</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1006,28 +1033,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>0</x:v>
+        <x:v>56587</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>0</x:v>
+        <x:v>22.9336530493399</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>244</x:v>
+        <x:v>44073</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0045985713771</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>244</x:v>
+        <x:v>100660</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0234947473833207</x:v>
+        <x:v>0.326412857592484</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-244</x:v>
+        <x:v>12514</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.683790336159</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1035,28 +1062,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>45</x:v>
+        <x:v>74275</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0180261986218</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>363</x:v>
+        <x:v>67039</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.002139688301</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>408</x:v>
+        <x:v>141314</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0392862989032575</x:v>
+        <x:v>0.458242663995871</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-318</x:v>
+        <x:v>7236</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.1652091402188</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1064,28 +1091,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>3</x:v>
+        <x:v>614912</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0687941493347</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>369</x:v>
+        <x:v>607714</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0713389738109</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>372</x:v>
+        <x:v>1222626</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0358198607647348</x:v>
+        <x:v>3.96464182820255</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-366</x:v>
+        <x:v>7198</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.8539392644082</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1093,28 +1120,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>0</x:v>
+        <x:v>83447</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0</x:v>
+        <x:v>23.0274572737577</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>366</x:v>
+        <x:v>77364</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9216641089606</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>366</x:v>
+        <x:v>160811</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.035242121074981</x:v>
+        <x:v>0.521466104135754</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-366</x:v>
+        <x:v>6083</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>24.3729418046416</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1122,28 +1149,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>1200</x:v>
+        <x:v>69723</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0016400923857</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>1632</x:v>
+        <x:v>65082</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0129698590147</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>2832</x:v>
+        <x:v>134805</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.272693133563787</x:v>
+        <x:v>0.437135756683438</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-432</x:v>
+        <x:v>4641</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.842759706316</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1151,28 +1178,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>0</x:v>
+        <x:v>29211</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0</x:v>
+        <x:v>22.8958182102937</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>517</x:v>
+        <x:v>25595</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9757306666224</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>517</x:v>
+        <x:v>54806</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.049781903267118</x:v>
+        <x:v>0.177720872970531</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-517</x:v>
+        <x:v>3616</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.3301768055004</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1180,28 +1207,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>0</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0</x:v>
+        <x:v>23.0622225867377</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>640</x:v>
+        <x:v>6010</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.206555383971</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>640</x:v>
+        <x:v>15010</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0616255669070706</x:v>
+        <x:v>0.0486733259732087</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-640</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.7721088371149</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1209,28 +1236,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>10</x:v>
+        <x:v>104366</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9833213156712</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>671</x:v>
+        <x:v>102166</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9821555112039</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>681</x:v>
+        <x:v>206532</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0655734547870548</x:v>
+        <x:v>0.669726806122501</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-661</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0374602153084</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1238,28 +1265,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
+        <x:v>1300</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>23.1599998474121</x:v>
+      </x:c>
+      <x:c r="D26" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C26" s="0">
+      <x:c r="E26" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D26" s="0">
-        <x:v>785</x:v>
-      </x:c>
-      <x:c r="E26" s="0">
-        <x:v>23.1399993896484</x:v>
-      </x:c>
       <x:c r="F26" s="0">
-        <x:v>785</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0755876094094538</x:v>
+        <x:v>0.00421554455464166</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-785</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.1599998474121</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1267,28 +1294,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>2734</x:v>
+        <x:v>2103</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9699856372204</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>4011</x:v>
+        <x:v>1062</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9971182440634</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>6745</x:v>
+        <x:v>3165</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.649475701231548</x:v>
+        <x:v>0.0102632296272622</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1277</x:v>
+        <x:v>1041</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9423056867235</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1296,28 +1323,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>22.8076929679284</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2137</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0400004916721</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>2137</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.20577161950064</x:v>
+        <x:v>0.00113495430317276</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-2137</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.6847066318288</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1325,28 +1352,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1294</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.2366663614909</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>4073</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>5367</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.516788152484762</x:v>
+        <x:v>3.8912718965923E-05</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-2779</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.2366663614909</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1354,28 +1381,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>617</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.8199996948242</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>5875</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9572412819698</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>6492</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.625114344313597</x:v>
+        <x:v>0.000632331683196249</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-5258</x:v>
+        <x:v>-95</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0294736962569</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1383,28 +1410,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>6296</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.8484204944811</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>15526</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.7800006866455</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>21822</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>2.10123925163452</x:v>
+        <x:v>0.000531807159200948</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-9230</x:v>
+        <x:v>-126</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.7696834140354</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1412,28 +1439,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9266668955485</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>17350</x:v>
+        <x:v>4965</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.038690981524</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>17850</x:v>
+        <x:v>7965</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>1.71877557701752</x:v>
+        <x:v>0.0258283172136314</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-16850</x:v>
+        <x:v>-1965</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.2097201204179</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1441,28 +1468,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>3</x:v>
+        <x:v>28571</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.933047458675</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>16870</x:v>
+        <x:v>30872</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0247168960458</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>16873</x:v>
+        <x:v>59443</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.62470029753594</x:v>
+        <x:v>0.19275739612428</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-16867</x:v>
+        <x:v>-2301</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>24.1629557031385</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1470,28 +1497,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>15429</x:v>
+        <x:v>11251</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.1754908327335</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>32469</x:v>
+        <x:v>13616</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9802775538486</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>47898</x:v>
+        <x:v>24867</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>4.61209594330448</x:v>
+        <x:v>0.080636881877134</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-17040</x:v>
+        <x:v>-2365</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.0515906190771</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1499,28 +1526,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>35279</x:v>
+        <x:v>60912</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.1395564289083</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>57430</x:v>
+        <x:v>63756</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0686672207881</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>92709</x:v>
+        <x:v>124668</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>8.92694481623064</x:v>
+        <x:v>0.404264237336974</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-22151</x:v>
+        <x:v>-2844</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>21.5503819025686</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1528,28 +1555,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>0</x:v>
+        <x:v>33480</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0</x:v>
+        <x:v>22.9745126716267</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>27218</x:v>
+        <x:v>42530</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0848506152532</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>27218</x:v>
+        <x:v>76010</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.62081981261976</x:v>
+        <x:v>0.246479647383317</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-27218</x:v>
+        <x:v>-9050</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.4930400464811</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1557,28 +1584,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>145</x:v>
+        <x:v>37446</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.1770981969611</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>28025</x:v>
+        <x:v>49315</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9493195732261</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>28170</x:v>
+        <x:v>86761</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2.71248784339403</x:v>
+        <x:v>0.281342200850204</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-27880</x:v>
+        <x:v>-11869</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.2306913531251</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1586,28 +1613,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>10914</x:v>
+        <x:v>174522</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.8903343016836</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>62716</x:v>
+        <x:v>190657</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9411006408318</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>73630</x:v>
+        <x:v>365179</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>7.08982889276188</x:v>
+        <x:v>1.18417564993807</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-51802</x:v>
+        <x:v>-16135</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.4902077397363</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1615,28 +1642,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>1942</x:v>
+        <x:v>50999</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0579843325705</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>72743</x:v>
+        <x:v>70909</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.9950759049913</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>74685</x:v>
+        <x:v>121908</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>7.19141478821026</x:v>
+        <x:v>0.395314311974812</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-70801</x:v>
+        <x:v>-19910</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>22.8339374369799</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1644,28 +1671,289 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>3929</x:v>
+        <x:v>968305</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0018854185349</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>121458</x:v>
+        <x:v>989123</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.0201312413483</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>125387</x:v>
+        <x:v>1957428</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>12.0735077465263</x:v>
+        <x:v>6.3474038050024</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-117529</x:v>
+        <x:v>-20818</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.1399993896484</x:v>
+        <x:v>23.868796889314</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:9">
+      <x:c r="A41" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>66000</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>22.9738818904703</x:v>
+      </x:c>
+      <x:c r="D41" s="0">
+        <x:v>93373</x:v>
+      </x:c>
+      <x:c r="E41" s="0">
+        <x:v>22.9975287277382</x:v>
+      </x:c>
+      <x:c r="F41" s="0">
+        <x:v>159373</x:v>
+      </x:c>
+      <x:c r="G41" s="0">
+        <x:v>0.516803063313004</x:v>
+      </x:c>
+      <x:c r="H41" s="0">
+        <x:v>-27373</x:v>
+      </x:c>
+      <x:c r="I41" s="0">
+        <x:v>23.054544446135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:9">
+      <x:c r="A42" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B42" s="0">
+        <x:v>95589</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>22.9982510620896</x:v>
+      </x:c>
+      <x:c r="D42" s="0">
+        <x:v>158764</x:v>
+      </x:c>
+      <x:c r="E42" s="0">
+        <x:v>22.9836104880451</x:v>
+      </x:c>
+      <x:c r="F42" s="0">
+        <x:v>254353</x:v>
+      </x:c>
+      <x:c r="G42" s="0">
+        <x:v>0.824797233928285</x:v>
+      </x:c>
+      <x:c r="H42" s="0">
+        <x:v>-63175</x:v>
+      </x:c>
+      <x:c r="I42" s="0">
+        <x:v>22.9614580886412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:9">
+      <x:c r="A43" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B43" s="0">
+        <x:v>864624</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>23.0031039990826</x:v>
+      </x:c>
+      <x:c r="D43" s="0">
+        <x:v>973712</x:v>
+      </x:c>
+      <x:c r="E43" s="0">
+        <x:v>23.0241889993104</x:v>
+      </x:c>
+      <x:c r="F43" s="0">
+        <x:v>1838336</x:v>
+      </x:c>
+      <x:c r="G43" s="0">
+        <x:v>5.96122101107826</x:v>
+      </x:c>
+      <x:c r="H43" s="0">
+        <x:v>-109088</x:v>
+      </x:c>
+      <x:c r="I43" s="0">
+        <x:v>23.1913072638024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
+      <x:c r="A44" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>171795</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>22.9414055000393</x:v>
+      </x:c>
+      <x:c r="D44" s="0">
+        <x:v>349887</x:v>
+      </x:c>
+      <x:c r="E44" s="0">
+        <x:v>23.0053290838358</x:v>
+      </x:c>
+      <x:c r="F44" s="0">
+        <x:v>521682</x:v>
+      </x:c>
+      <x:c r="G44" s="0">
+        <x:v>1.69167208796505</x:v>
+      </x:c>
+      <x:c r="H44" s="0">
+        <x:v>-178092</x:v>
+      </x:c>
+      <x:c r="I44" s="0">
+        <x:v>23.066992449278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
+      <x:c r="A45" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B45" s="0">
+        <x:v>1247268</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>23.018440832367</x:v>
+      </x:c>
+      <x:c r="D45" s="0">
+        <x:v>1492727</x:v>
+      </x:c>
+      <x:c r="E45" s="0">
+        <x:v>22.9598072795087</x:v>
+      </x:c>
+      <x:c r="F45" s="0">
+        <x:v>2739995</x:v>
+      </x:c>
+      <x:c r="G45" s="0">
+        <x:v>8.88505461691952</x:v>
+      </x:c>
+      <x:c r="H45" s="0">
+        <x:v>-245459</x:v>
+      </x:c>
+      <x:c r="I45" s="0">
+        <x:v>22.6618685027412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:9">
+      <x:c r="A46" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B46" s="0">
+        <x:v>109345</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>22.9850784946291</x:v>
+      </x:c>
+      <x:c r="D46" s="0">
+        <x:v>356386</x:v>
+      </x:c>
+      <x:c r="E46" s="0">
+        <x:v>23.1927322714205</x:v>
+      </x:c>
+      <x:c r="F46" s="0">
+        <x:v>465731</x:v>
+      </x:c>
+      <x:c r="G46" s="0">
+        <x:v>1.51023829305986</x:v>
+      </x:c>
+      <x:c r="H46" s="0">
+        <x:v>-247041</x:v>
+      </x:c>
+      <x:c r="I46" s="0">
+        <x:v>23.284643744509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
+      <x:c r="A47" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B47" s="0">
+        <x:v>497862</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>22.9932375999917</x:v>
+      </x:c>
+      <x:c r="D47" s="0">
+        <x:v>747825</x:v>
+      </x:c>
+      <x:c r="E47" s="0">
+        <x:v>23.0044424441078</x:v>
+      </x:c>
+      <x:c r="F47" s="0">
+        <x:v>1245687</x:v>
+      </x:c>
+      <x:c r="G47" s="0">
+        <x:v>4.03942234587531</x:v>
+      </x:c>
+      <x:c r="H47" s="0">
+        <x:v>-249963</x:v>
+      </x:c>
+      <x:c r="I47" s="0">
+        <x:v>23.026759611454</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
+      <x:c r="A48" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B48" s="0">
+        <x:v>266702</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>23.0288541213198</x:v>
+      </x:c>
+      <x:c r="D48" s="0">
+        <x:v>567209</x:v>
+      </x:c>
+      <x:c r="E48" s="0">
+        <x:v>22.9498708101798</x:v>
+      </x:c>
+      <x:c r="F48" s="0">
+        <x:v>833911</x:v>
+      </x:c>
+      <x:c r="G48" s="0">
+        <x:v>2.70414536546599</x:v>
+      </x:c>
+      <x:c r="H48" s="0">
+        <x:v>-300507</x:v>
+      </x:c>
+      <x:c r="I48" s="0">
+        <x:v>22.8797725860198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
+      <x:c r="A49" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B49" s="0">
+        <x:v>547459</x:v>
+      </x:c>
+      <x:c r="C49" s="0">
+        <x:v>23.0296864777372</x:v>
+      </x:c>
+      <x:c r="D49" s="0">
+        <x:v>988121</x:v>
+      </x:c>
+      <x:c r="E49" s="0">
+        <x:v>23.0811425090989</x:v>
+      </x:c>
+      <x:c r="F49" s="0">
+        <x:v>1535580</x:v>
+      </x:c>
+      <x:c r="G49" s="0">
+        <x:v>4.97946608247434</x:v>
+      </x:c>
+      <x:c r="H49" s="0">
+        <x:v>-440662</x:v>
+      </x:c>
+      <x:c r="I49" s="0">
+        <x:v>23.145069209094</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -46,142 +46,151 @@
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -532,7 +541,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I49"/>
+  <x:dimension ref="A1:I52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -569,28 +578,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1566952</x:v>
+        <x:v>2612437</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.0105513771085</x:v>
+        <x:v>23.0195377793721</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>1113885</x:v>
+        <x:v>2061555</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>22.9912156166613</x:v>
+        <x:v>23.0009676266976</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2680837</x:v>
+        <x:v>4673992</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>8.69322139787068</x:v>
+        <x:v>6.25776330822619</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>453067</x:v>
+        <x:v>550882</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.05808918835</x:v>
+        <x:v>23.0890325007405</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -598,28 +607,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1617252</x:v>
+        <x:v>3599419</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.1246495889317</x:v>
+        <x:v>23.0832428843835</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1194441</x:v>
+        <x:v>3319043</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.0805942330211</x:v>
+        <x:v>23.0597574987041</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>2811693</x:v>
+        <x:v>6918462</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>9.11755162728775</x:v>
+        <x:v>9.26276674263824</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>422811</x:v>
+        <x:v>280376</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.2491059615644</x:v>
+        <x:v>23.3612588520182</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -627,28 +636,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>361670</x:v>
+        <x:v>5405847</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.1476373397408</x:v>
+        <x:v>23.0239685977323</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>102830</x:v>
+        <x:v>5153804</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.0713145400999</x:v>
+        <x:v>23.0326804352596</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>464500</x:v>
+        <x:v>10559651</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.50624649663927</x:v>
+        <x:v>14.1377641586622</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>258840</x:v>
+        <x:v>252043</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.1779582850625</x:v>
+        <x:v>22.8458279507189</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -656,28 +665,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>2140651</x:v>
+        <x:v>810049</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>22.990949976667</x:v>
+        <x:v>23.0596222691977</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1991237</x:v>
+        <x:v>562123</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.0204814459431</x:v>
+        <x:v>23.079237942608</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>4131888</x:v>
+        <x:v>1372172</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.3985830452225</x:v>
+        <x:v>1.83712928780694</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>149414</x:v>
+        <x:v>247926</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>22.5973847532821</x:v>
+        <x:v>23.0151476227933</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -685,28 +694,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>105942</x:v>
+        <x:v>1027067</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>22.9066585766466</x:v>
+        <x:v>22.9936792552723</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>11017</x:v>
+        <x:v>807574</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>22.9356342451406</x:v>
+        <x:v>23.0171442782968</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>116959</x:v>
+        <x:v>1834641</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.379266058127949</x:v>
+        <x:v>2.45630483183698</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>94925</x:v>
+        <x:v>219493</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>22.9032956591876</x:v>
+        <x:v>22.9073451010896</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -714,28 +723,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>247723</x:v>
+        <x:v>803930</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.0485830810209</x:v>
+        <x:v>23.0848803849356</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>157233</x:v>
+        <x:v>587050</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.0650419069876</x:v>
+        <x:v>23.0398441228565</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>404956</x:v>
+        <x:v>1390980</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.31316158513036</x:v>
+        <x:v>1.86231033482224</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>90490</x:v>
+        <x:v>216880</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.0199846659119</x:v>
+        <x:v>23.2067843763294</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -743,28 +752,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>565606</x:v>
+        <x:v>2235724</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.0036578744821</x:v>
+        <x:v>23.0387291889683</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>479300</x:v>
+        <x:v>2054781</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>22.9896255712352</x:v>
+        <x:v>23.0409856832324</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1044906</x:v>
+        <x:v>4290505</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>3.38834446031723</x:v>
+        <x:v>5.7443326310274</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>86306</x:v>
+        <x:v>180943</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.0815862102436</x:v>
+        <x:v>23.0131045362295</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -772,28 +781,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>278967</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>22.9793024013575</x:v>
+        <x:v>23.17200050354</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>209622</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>23.0019899857029</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>488589</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.58436053723678</x:v>
+        <x:v>0.200827150802554</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>69345</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>22.910720429973</x:v>
+        <x:v>23.17200050354</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -801,28 +810,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>452664</x:v>
+        <x:v>1546792</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.0422604369655</x:v>
+        <x:v>23.0556386298264</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>394763</x:v>
+        <x:v>1427144</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.061699130611</x:v>
+        <x:v>23.0483232791042</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>847427</x:v>
+        <x:v>2973936</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>2.74797405792794</x:v>
+        <x:v>3.98164729032762</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>57901</x:v>
+        <x:v>119648</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.9097294440712</x:v>
+        <x:v>23.1428950728182</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -830,28 +839,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>880004</x:v>
+        <x:v>726108</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.0426455108315</x:v>
+        <x:v>22.9814718674599</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>831327</x:v>
+        <x:v>639164</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>23.0320142423275</x:v>
+        <x:v>22.9931974267504</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>1711331</x:v>
+        <x:v>1365272</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>5.54937852172267</x:v>
+        <x:v>1.82789123887003</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>48677</x:v>
+        <x:v>86944</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.2242109432048</x:v>
+        <x:v>22.8952720678375</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -859,28 +868,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>74488</x:v>
+        <x:v>2473202</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>22.9244459496573</x:v>
+        <x:v>23.0166914181582</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>27617</x:v>
+        <x:v>2420255</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.2026301613715</x:v>
+        <x:v>23.0393632687917</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>102105</x:v>
+        <x:v>4893457</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.331098597501298</x:v>
+        <x:v>6.55159351256541</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>46871</x:v>
+        <x:v>52947</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>22.7605362106948</x:v>
+        <x:v>21.980340730584</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -888,28 +897,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>39936</x:v>
+        <x:v>1227500</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.1012628182578</x:v>
+        <x:v>23.0187430342867</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>8106</x:v>
+        <x:v>1179560</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.0897954380309</x:v>
+        <x:v>23.004742138181</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>48042</x:v>
+        <x:v>2407060</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.155787070380073</x:v>
+        <x:v>3.2226866774053</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>31830</x:v>
+        <x:v>47940</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.1041831633448</x:v>
+        <x:v>23.3632340023803</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -917,28 +926,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>415924</x:v>
+        <x:v>49126</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.0146558252682</x:v>
+        <x:v>23.0784193704878</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>387602</x:v>
+        <x:v>12986</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.0819364842068</x:v>
+        <x:v>23.0734270315554</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>803526</x:v>
+        <x:v>62112</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>2.60561511831769</x:v>
+        <x:v>0.0831585066043214</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>28322</x:v>
+        <x:v>36140</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>22.093883352776</x:v>
+        <x:v>23.0802132419149</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -946,28 +955,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>31020</x:v>
+        <x:v>134326</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>23.0549967819302</x:v>
+        <x:v>22.9732788212681</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>6055</x:v>
+        <x:v>98357</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.007946877515</x:v>
+        <x:v>22.9991803384066</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>37075</x:v>
+        <x:v>232683</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.1202240879718</x:v>
+        <x:v>0.311527092867937</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>24965</x:v>
+        <x:v>35969</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.0664082448277</x:v>
+        <x:v>22.9024512886375</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -975,28 +984,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>75691</x:v>
+        <x:v>42184</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.0096481851064</x:v>
+        <x:v>23.0351244544205</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>52240</x:v>
+        <x:v>6628</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>22.985786906939</x:v>
+        <x:v>23.0218559217942</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>127931</x:v>
+        <x:v>48812</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.414845254169125</x:v>
+        <x:v>0.0653518325664949</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>23451</x:v>
+        <x:v>35556</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.0628021304162</x:v>
+        <x:v>23.0375978438414</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1004,28 +1013,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>284238</x:v>
+        <x:v>97040</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>22.9754350121293</x:v>
+        <x:v>22.9480752350177</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>271616</x:v>
+        <x:v>62723</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.0434266510055</x:v>
+        <x:v>23.1056780559916</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>555854</x:v>
+        <x:v>159763</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>1.80248254067368</x:v>
+        <x:v>0.213898320624456</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>12622</x:v>
+        <x:v>34317</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>21.5123057944936</x:v>
+        <x:v>22.6600162048011</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1033,28 +1042,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>56587</x:v>
+        <x:v>119878</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>22.9336530493399</x:v>
+        <x:v>23.0267558638566</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>44073</x:v>
+        <x:v>87169</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.0045985713771</x:v>
+        <x:v>23.0412090639882</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>100660</x:v>
+        <x:v>207047</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.326412857592484</x:v>
+        <x:v>0.277204393948109</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>12514</x:v>
+        <x:v>32709</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.683790336159</x:v>
+        <x:v>22.988238299814</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1062,28 +1071,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>74275</x:v>
+        <x:v>253935</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.0180261986218</x:v>
+        <x:v>23.0412286278497</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>67039</x:v>
+        <x:v>226261</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>23.002139688301</x:v>
+        <x:v>22.9554757698752</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>141314</x:v>
+        <x:v>480196</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.458242663995871</x:v>
+        <x:v>0.642909296711886</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>7236</x:v>
+        <x:v>27674</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.1652091402188</x:v>
+        <x:v>23.7423389623937</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1091,28 +1100,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>614912</x:v>
+        <x:v>139618</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.0687941493347</x:v>
+        <x:v>23.0070579543262</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>607714</x:v>
+        <x:v>114326</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.0713389738109</x:v>
+        <x:v>23.0242726655803</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>1222626</x:v>
+        <x:v>253944</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>3.96464182820255</x:v>
+        <x:v>0.339992333222691</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>7198</x:v>
+        <x:v>25292</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.8539392644082</x:v>
+        <x:v>22.9292432667239</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1120,28 +1129,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>83447</x:v>
+        <x:v>483974</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.0274572737577</x:v>
+        <x:v>23.0394991977465</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>77364</x:v>
+        <x:v>461223</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>22.9216641089606</x:v>
+        <x:v>23.0249767323854</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>160811</x:v>
+        <x:v>945197</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.521466104135754</x:v>
+        <x:v>1.26547480304747</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>6083</x:v>
+        <x:v>22751</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>24.3729418046416</x:v>
+        <x:v>23.3339080167526</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1149,28 +1158,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>69723</x:v>
+        <x:v>507847</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.0016400923857</x:v>
+        <x:v>22.9946965125156</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>65082</x:v>
+        <x:v>486833</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.0129698590147</x:v>
+        <x:v>23.0057841576306</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>134805</x:v>
+        <x:v>994680</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.437135756683438</x:v>
+        <x:v>1.33172500240189</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>4641</x:v>
+        <x:v>21014</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>22.842759706316</x:v>
+        <x:v>22.7378281612111</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1178,28 +1187,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>29211</x:v>
+        <x:v>720717</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>22.8958182102937</x:v>
+        <x:v>23.0721648030504</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>25595</x:v>
+        <x:v>703562</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>22.9757306666224</x:v>
+        <x:v>23.0736976640788</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>54806</x:v>
+        <x:v>1424279</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.177720872970531</x:v>
+        <x:v>1.90689262345273</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>3616</x:v>
+        <x:v>17155</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>22.3301768055004</x:v>
+        <x:v>23.0092990046929</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1207,28 +1216,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>9000</x:v>
+        <x:v>81893</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.0622225867377</x:v>
+        <x:v>22.9603556712103</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>6010</x:v>
+        <x:v>65815</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.206555383971</x:v>
+        <x:v>23.0107878244712</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>15010</x:v>
+        <x:v>147708</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0486733259732087</x:v>
+        <x:v>0.19775851193829</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>2990</x:v>
+        <x:v>16078</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>22.7721088371149</x:v>
+        <x:v>22.753912570895</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1236,28 +1245,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>104366</x:v>
+        <x:v>618092</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>22.9833213156712</x:v>
+        <x:v>23.0564515163414</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>102166</x:v>
+        <x:v>603517</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>22.9821555112039</x:v>
+        <x:v>23.0851762345608</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>206532</x:v>
+        <x:v>1221609</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.669726806122501</x:v>
+        <x:v>1.63554836576504</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>2200</x:v>
+        <x:v>14575</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.0374602153084</x:v>
+        <x:v>21.8670274500904</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1265,28 +1274,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>1300</x:v>
+        <x:v>40908</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.1599998474121</x:v>
+        <x:v>23.081415601428</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>0</x:v>
+        <x:v>35232</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>0</x:v>
+        <x:v>22.9730699307046</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1300</x:v>
+        <x:v>76140</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00421554455464166</x:v>
+        <x:v>0.101939861747376</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>1300</x:v>
+        <x:v>5676</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.1599998474121</x:v>
+        <x:v>23.7539375660031</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1294,28 +1303,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>2103</x:v>
+        <x:v>3019</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>22.9699856372204</x:v>
+        <x:v>23.0056709000195</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1062</x:v>
+        <x:v>924</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>22.9971182440634</x:v>
+        <x:v>23.0032907007061</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>3165</x:v>
+        <x:v>3943</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0102632296272622</x:v>
+        <x:v>0.00527907637076312</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>1041</x:v>
+        <x:v>2095</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>22.9423056867235</x:v>
+        <x:v>23.0067206872107</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1323,28 +1332,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>260</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>22.8076929679284</x:v>
+        <x:v>23.046000289917</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>90</x:v>
+        <x:v>8180</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.0400004916721</x:v>
+        <x:v>23.2055496924664</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>350</x:v>
+        <x:v>18180</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00113495430317276</x:v>
+        <x:v>0.0243402506772695</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>170</x:v>
+        <x:v>1820</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>22.6847066318288</x:v>
+        <x:v>22.3289046235137</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1352,10 +1361,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>12</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.2366663614909</x:v>
+        <x:v>23.1599998474121</x:v>
       </x:c>
       <x:c r="D29" s="0">
         <x:v>0</x:v>
@@ -1364,16 +1373,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>12</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>3.8912718965923E-05</x:v>
+        <x:v>0.00174050197362213</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>12</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.2366663614909</x:v>
+        <x:v>23.1599998474121</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1381,28 +1390,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>50</x:v>
+        <x:v>59124</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>22.8199996948242</x:v>
+        <x:v>22.9439778869912</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>145</x:v>
+        <x:v>58079</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>22.9572412819698</x:v>
+        <x:v>23.0157925823458</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>195</x:v>
+        <x:v>117203</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.000632331683196249</x:v>
+        <x:v>0.156916963703411</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-95</x:v>
+        <x:v>1045</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>23.0294736962569</x:v>
+        <x:v>18.952661435798</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1410,28 +1419,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>19</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>22.8484204944811</x:v>
+        <x:v>22.8981099672844</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>145</x:v>
+        <x:v>1407</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>22.7800006866455</x:v>
+        <x:v>23.0492682019785</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>164</x:v>
+        <x:v>3852</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.000531807159200948</x:v>
+        <x:v>0.00515724123260957</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-126</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>22.7696834140354</x:v>
+        <x:v>22.6932162907771</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1439,28 +1448,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>3000</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>22.9266668955485</x:v>
+        <x:v>23.0400009155273</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>4965</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>23.038690981524</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>7965</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0258283172136314</x:v>
+        <x:v>0.000183422131066332</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-1965</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.2097201204179</x:v>
+        <x:v>23.0400009155273</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1468,28 +1477,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>28571</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>22.933047458675</x:v>
+        <x:v>22.8367350720108</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>30872</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.0247168960458</x:v>
+        <x:v>23.0727274555805</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>59443</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.19275739612428</x:v>
+        <x:v>0.00110722702475808</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-2301</x:v>
+        <x:v>-141</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>24.1629557031385</x:v>
+        <x:v>23.6468082184487</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1497,28 +1506,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>11251</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.1754908327335</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>13616</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>22.9802775538486</x:v>
+        <x:v>23.0799999237061</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>24867</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.080636881877134</x:v>
+        <x:v>0.000194132912442468</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-2365</x:v>
+        <x:v>-145</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>22.0515906190771</x:v>
+        <x:v>23.0799999237061</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1526,28 +1535,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>60912</x:v>
+        <x:v>2817</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>23.1395564289083</x:v>
+        <x:v>22.9677242973742</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>63756</x:v>
+        <x:v>4716</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.0686672207881</x:v>
+        <x:v>23.0801012934619</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>124668</x:v>
+        <x:v>7533</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.404264237336974</x:v>
+        <x:v>0.0100855395133042</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-2844</x:v>
+        <x:v>-1899</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>21.5503819025686</x:v>
+        <x:v>23.2468027141987</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1555,28 +1564,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>33480</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>22.9745126716267</x:v>
+        <x:v>22.9528957057644</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>42530</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.0848506152532</x:v>
+        <x:v>23.03059830419</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>76010</x:v>
+        <x:v>3237</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.246479647383317</x:v>
+        <x:v>0.0043338499143191</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-9050</x:v>
+        <x:v>-2719</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.4930400464811</x:v>
+        <x:v>23.0379999124991</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1584,28 +1593,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>37446</x:v>
+        <x:v>63206</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.1770981969611</x:v>
+        <x:v>23.136354465</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>49315</x:v>
+        <x:v>67353</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>22.9493195732261</x:v>
+        <x:v>23.0658293970957</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>86761</x:v>
+        <x:v>130559</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.281342200850204</x:v>
+        <x:v>0.174798613210871</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-11869</x:v>
+        <x:v>-4147</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>22.2306913531251</x:v>
+        <x:v>21.990930086278</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1613,28 +1622,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>174522</x:v>
+        <x:v>228356</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>22.8903343016836</x:v>
+        <x:v>23.0220582943711</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>190657</x:v>
+        <x:v>233304</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>22.9411006408318</x:v>
+        <x:v>23.0522956500936</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>365179</x:v>
+        <x:v>461660</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>1.18417564993807</x:v>
+        <x:v>0.618092416263379</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-16135</x:v>
+        <x:v>-4948</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.4902077397363</x:v>
+        <x:v>24.4477850606389</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1642,28 +1651,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>50999</x:v>
+        <x:v>425000</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>23.0579843325705</x:v>
+        <x:v>22.9901769860346</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>70909</x:v>
+        <x:v>431317</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>22.9950759049913</x:v>
+        <x:v>23.0019519115089</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>121908</x:v>
+        <x:v>856317</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.395314311974812</x:v>
+        <x:v>1.1464780219586</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-19910</x:v>
+        <x:v>-6317</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>22.8339374369799</x:v>
+        <x:v>23.7941544327306</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1671,28 +1680,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>968305</x:v>
+        <x:v>174427</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.0018854185349</x:v>
+        <x:v>23.0188951194606</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>989123</x:v>
+        <x:v>184313</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.0201312413483</x:v>
+        <x:v>23.0072484901079</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>1957428</x:v>
+        <x:v>358740</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>6.3474038050024</x:v>
+        <x:v>0.480298213859387</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-20818</x:v>
+        <x:v>-9886</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.868796889314</x:v>
+        <x:v>22.801757227909</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1700,28 +1709,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>66000</x:v>
+        <x:v>72904</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>22.9738818904703</x:v>
+        <x:v>23.1405915593415</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>93373</x:v>
+        <x:v>85793</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>22.9975287277382</x:v>
+        <x:v>22.9888612281366</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>159373</x:v>
+        <x:v>158697</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.516803063313004</x:v>
+        <x:v>0.212471109006086</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-27373</x:v>
+        <x:v>-12889</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>23.054544446135</x:v>
+        <x:v>22.1306295525862</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1729,28 +1738,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>95589</x:v>
+        <x:v>96024</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>22.9982510620896</x:v>
+        <x:v>23.0065832459846</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>158764</x:v>
+        <x:v>123760</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>22.9836104880451</x:v>
+        <x:v>23.0267482483086</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>254353</x:v>
+        <x:v>219784</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.824797233928285</x:v>
+        <x:v>0.294257296746589</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-63175</x:v>
+        <x:v>-27736</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>22.9614580886412</x:v>
+        <x:v>23.0965609171565</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1758,28 +1767,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>864624</x:v>
+        <x:v>106039</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>23.0031039990826</x:v>
+        <x:v>22.9668303901152</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>973712</x:v>
+        <x:v>157968</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.0241889993104</x:v>
+        <x:v>23.1079905953896</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>1838336</x:v>
+        <x:v>264007</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>5.96122101107826</x:v>
+        <x:v>0.353465157346198</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-109088</x:v>
+        <x:v>-51929</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>23.1913072638024</x:v>
+        <x:v>23.3962396856298</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1787,28 +1796,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>171795</x:v>
+        <x:v>1913034</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>22.9414055000393</x:v>
+        <x:v>23.0180737371652</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>349887</x:v>
+        <x:v>1998501</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.0053290838358</x:v>
+        <x:v>23.0342446978675</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>521682</x:v>
+        <x:v>3911535</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.69167208796505</x:v>
+        <x:v>5.23694952876311</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-178092</x:v>
+        <x:v>-85467</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>23.066992449278</x:v>
+        <x:v>23.3962042569509</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1816,28 +1825,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>1247268</x:v>
+        <x:v>281720</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23.018440832367</x:v>
+        <x:v>22.98831706892</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>1492727</x:v>
+        <x:v>373192</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>22.9598072795087</x:v>
+        <x:v>22.9931886537903</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>2739995</x:v>
+        <x:v>654912</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>8.88505461691952</x:v>
+        <x:v>0.876827406576013</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-245459</x:v>
+        <x:v>-91472</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>22.6618685027412</x:v>
+        <x:v>23.0081924023652</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1845,28 +1854,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>109345</x:v>
+        <x:v>192911</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>22.9850784946291</x:v>
+        <x:v>23.0013664443903</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>356386</x:v>
+        <x:v>321918</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.1927322714205</x:v>
+        <x:v>23.0026992536229</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>465731</x:v>
+        <x:v>514829</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.51023829305986</x:v>
+        <x:v>0.689277608136852</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-247041</x:v>
+        <x:v>-129007</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.284643744509</x:v>
+        <x:v>23.0046922738612</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1874,28 +1883,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>497862</x:v>
+        <x:v>1095878</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>22.9932375999917</x:v>
+        <x:v>23.0166700422819</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>747825</x:v>
+        <x:v>1329609</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.0044424441078</x:v>
+        <x:v>23.024062818275</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1245687</x:v>
+        <x:v>2425487</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.03942234587531</x:v>
+        <x:v>3.24735762345755</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-249963</x:v>
+        <x:v>-233731</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.026759611454</x:v>
+        <x:v>23.0587248039326</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1903,28 +1912,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>266702</x:v>
+        <x:v>1200765</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.0288541213198</x:v>
+        <x:v>23.0152472412961</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>567209</x:v>
+        <x:v>1471970</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>22.9498708101798</x:v>
+        <x:v>23.0910231901368</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>833911</x:v>
+        <x:v>2672735</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>2.70414536546599</x:v>
+        <x:v>3.57838503266842</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-300507</x:v>
+        <x:v>-271205</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>22.8797725860198</x:v>
+        <x:v>23.4265225622344</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1932,28 +1941,115 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>547459</x:v>
+        <x:v>182760</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.0296864777372</x:v>
+        <x:v>23.0034990225508</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>988121</x:v>
+        <x:v>462178</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.0811425090989</x:v>
+        <x:v>23.1549551822391</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>1535580</x:v>
+        <x:v>644938</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>4.97946608247434</x:v>
+        <x:v>0.863473739895315</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-440662</x:v>
+        <x:v>-279418</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.145069209094</x:v>
+        <x:v>23.2540186919078</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
+      <x:c r="A50" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B50" s="0">
+        <x:v>877254</x:v>
+      </x:c>
+      <x:c r="C50" s="0">
+        <x:v>23.0186985850585</x:v>
+      </x:c>
+      <x:c r="D50" s="0">
+        <x:v>1294086</x:v>
+      </x:c>
+      <x:c r="E50" s="0">
+        <x:v>22.9913208162032</x:v>
+      </x:c>
+      <x:c r="F50" s="0">
+        <x:v>2171340</x:v>
+      </x:c>
+      <x:c r="G50" s="0">
+        <x:v>2.90709350415744</x:v>
+      </x:c>
+      <x:c r="H50" s="0">
+        <x:v>-416832</x:v>
+      </x:c>
+      <x:c r="I50" s="0">
+        <x:v>22.9337022618711</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
+      <x:c r="A51" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B51" s="0">
+        <x:v>1785675</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>23.0284077670114</x:v>
+      </x:c>
+      <x:c r="D51" s="0">
+        <x:v>2318770</x:v>
+      </x:c>
+      <x:c r="E51" s="0">
+        <x:v>23.0233339662163</x:v>
+      </x:c>
+      <x:c r="F51" s="0">
+        <x:v>4104445</x:v>
+      </x:c>
+      <x:c r="G51" s="0">
+        <x:v>5.49522663317191</x:v>
+      </x:c>
+      <x:c r="H51" s="0">
+        <x:v>-533095</x:v>
+      </x:c>
+      <x:c r="I51" s="0">
+        <x:v>23.0063385728347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
+      <x:c r="A52" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B52" s="0">
+        <x:v>2662538</x:v>
+      </x:c>
+      <x:c r="C52" s="0">
+        <x:v>23.0305523710266</x:v>
+      </x:c>
+      <x:c r="D52" s="0">
+        <x:v>3237918</x:v>
+      </x:c>
+      <x:c r="E52" s="0">
+        <x:v>22.9933668473576</x:v>
+      </x:c>
+      <x:c r="F52" s="0">
+        <x:v>5900456</x:v>
+      </x:c>
+      <x:c r="G52" s="0">
+        <x:v>7.89981177943888</x:v>
+      </x:c>
+      <x:c r="H52" s="0">
+        <x:v>-575380</x:v>
+      </x:c>
+      <x:c r="I52" s="0">
+        <x:v>22.8212929660641</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,148 +40,154 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
+    <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
+    <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
+    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
@@ -541,7 +547,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I52"/>
+  <x:dimension ref="A1:I54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -578,28 +584,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>2612437</x:v>
+        <x:v>5157554</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>23.0195377793721</x:v>
+        <x:v>22.9787228450416</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>2061555</x:v>
+        <x:v>4576741</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>23.0009676266976</x:v>
+        <x:v>22.9760777476513</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>4673992</x:v>
+        <x:v>9734295</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>6.25776330822619</x:v>
+        <x:v>8.5220476919748</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>550882</x:v>
+        <x:v>580813</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>23.0890325007405</x:v>
+        <x:v>22.9995659144543</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -607,28 +613,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>3599419</x:v>
+        <x:v>5020927</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>23.0832428843835</x:v>
+        <x:v>22.8713464725525</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>3319043</x:v>
+        <x:v>4536168</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>23.0597574987041</x:v>
+        <x:v>22.8850457702788</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>6918462</x:v>
+        <x:v>9557095</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>9.26276674263824</x:v>
+        <x:v>8.36691505514615</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>280376</x:v>
+        <x:v>484759</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.3612588520182</x:v>
+        <x:v>22.7431542863974</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -636,28 +642,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>5405847</x:v>
+        <x:v>943616</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.0239685977323</x:v>
+        <x:v>23.0120988915767</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>5153804</x:v>
+        <x:v>633348</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.0326804352596</x:v>
+        <x:v>23.0384842640978</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>10559651</x:v>
+        <x:v>1576964</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>14.1377641586622</x:v>
+        <x:v>1.38057891367863</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>252043</x:v>
+        <x:v>310268</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>22.8458279507189</x:v>
+        <x:v>22.9582386065472</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -665,28 +671,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>810049</x:v>
+        <x:v>4318178</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>23.0596222691977</x:v>
+        <x:v>22.9051066466749</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>562123</x:v>
+        <x:v>4011301</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>23.079237942608</x:v>
+        <x:v>22.8695931195152</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1372172</x:v>
+        <x:v>8329479</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.83712928780694</x:v>
+        <x:v>7.29217855913577</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>247926</x:v>
+        <x:v>306877</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.0151476227933</x:v>
+        <x:v>23.3693168905483</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -694,28 +700,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>1027067</x:v>
+        <x:v>1066132</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>22.9936792552723</x:v>
+        <x:v>22.9975677871914</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>807574</x:v>
+        <x:v>773672</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>23.0171442782968</x:v>
+        <x:v>22.9693736602913</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1834641</x:v>
+        <x:v>1839804</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2.45630483183698</x:v>
+        <x:v>1.61068648853214</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>219493</x:v>
+        <x:v>292460</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>22.9073451010896</x:v>
+        <x:v>23.0721523681499</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -723,28 +729,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>803930</x:v>
+        <x:v>7282416</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>23.0848803849356</x:v>
+        <x:v>22.9500589705202</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>587050</x:v>
+        <x:v>7035138</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>23.0398441228565</x:v>
+        <x:v>22.9514385882818</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1390980</x:v>
+        <x:v>14317554</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.86231033482224</x:v>
+        <x:v>12.5345367096872</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>216880</x:v>
+        <x:v>247278</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.2067843763294</x:v>
+        <x:v>22.9108084050002</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -752,28 +758,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>2235724</x:v>
+        <x:v>210000</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.0387291889683</x:v>
+        <x:v>23.0733338310605</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>2054781</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>23.0409856832324</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>4290505</x:v>
+        <x:v>210000</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>5.7443326310274</x:v>
+        <x:v>0.183847933036209</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>180943</x:v>
+        <x:v>210000</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.0131045362295</x:v>
+        <x:v>23.0733338310605</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -781,28 +787,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>150000</x:v>
+        <x:v>1940018</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>23.17200050354</x:v>
+        <x:v>22.9130189374995</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>0</x:v>
+        <x:v>1798493</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>0</x:v>
+        <x:v>22.9075277797151</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>150000</x:v>
+        <x:v>3738511</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.200827150802554</x:v>
+        <x:v>3.27294057134825</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>150000</x:v>
+        <x:v>141525</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.17200050354</x:v>
+        <x:v>22.9828003106642</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -810,28 +816,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1546792</x:v>
+        <x:v>752597</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>23.0556386298264</x:v>
+        <x:v>22.9912463750739</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1427144</x:v>
+        <x:v>659667</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.0483232791042</x:v>
+        <x:v>23.0505112478889</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>2973936</x:v>
+        <x:v>1412264</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>3.98164729032762</x:v>
+        <x:v>1.23638960619738</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>119648</x:v>
+        <x:v>92930</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.1428950728182</x:v>
+        <x:v>22.5705525102803</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -839,28 +845,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>726108</x:v>
+        <x:v>798619</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>22.9814718674599</x:v>
+        <x:v>22.9027313426524</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>639164</x:v>
+        <x:v>707439</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>22.9931974267504</x:v>
+        <x:v>22.9214020398089</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>1365272</x:v>
+        <x:v>1506058</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.82789123887003</x:v>
+        <x:v>1.31850309682213</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>86944</x:v>
+        <x:v>91180</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.8952720678375</x:v>
+        <x:v>22.7578708543252</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -868,28 +874,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2473202</x:v>
+        <x:v>200970</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.0166914181582</x:v>
+        <x:v>22.8734650415752</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>2420255</x:v>
+        <x:v>120906</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>23.0393632687917</x:v>
+        <x:v>22.9239123402175</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>4893457</x:v>
+        <x:v>321876</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>6.55159351256541</x:v>
+        <x:v>0.281791606161728</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>52947</x:v>
+        <x:v>80064</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>21.980340730584</x:v>
+        <x:v>22.7972837230094</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -897,28 +903,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1227500</x:v>
+        <x:v>712726</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>23.0187430342867</x:v>
+        <x:v>22.9458254782926</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1179560</x:v>
+        <x:v>635348</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>23.004742138181</x:v>
+        <x:v>22.9427400531128</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>2407060</x:v>
+        <x:v>1348074</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>3.2226866774053</x:v>
+        <x:v>1.18019342133264</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>47940</x:v>
+        <x:v>77378</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.3632340023803</x:v>
+        <x:v>22.9711597944693</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -926,28 +932,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>49126</x:v>
+        <x:v>264134</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>23.0784193704878</x:v>
+        <x:v>22.829361775325</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>12986</x:v>
+        <x:v>188001</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.0734270315554</x:v>
+        <x:v>23.0437394828483</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>62112</x:v>
+        <x:v>452135</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0831585066043214</x:v>
+        <x:v>0.395828977158698</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>36140</x:v>
+        <x:v>76133</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>23.0802132419149</x:v>
+        <x:v>22.2999826179017</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -955,28 +961,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>134326</x:v>
+        <x:v>710722</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>22.9732788212681</x:v>
+        <x:v>22.8707480530315</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>98357</x:v>
+        <x:v>652208</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>22.9991803384066</x:v>
+        <x:v>22.9010089467576</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>232683</x:v>
+        <x:v>1362930</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.311527092867937</x:v>
+        <x:v>1.19319934939543</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>35969</x:v>
+        <x:v>58514</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>22.9024512886375</x:v>
+        <x:v>22.5334544655939</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -984,28 +990,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>42184</x:v>
+        <x:v>56495</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>23.0351244544205</x:v>
+        <x:v>22.7263908107362</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>6628</x:v>
+        <x:v>5106</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.0218559217942</x:v>
+        <x:v>23.0518523106797</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>48812</x:v>
+        <x:v>61601</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0653518325664949</x:v>
+        <x:v>0.0539296024903026</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>35556</x:v>
+        <x:v>51389</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>23.0375978438414</x:v>
+        <x:v>22.6940530260213</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1013,28 +1019,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>97040</x:v>
+        <x:v>1624568</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>22.9480752350177</x:v>
+        <x:v>23.0380613820629</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>62723</x:v>
+        <x:v>1580785</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.1056780559916</x:v>
+        <x:v>23.0185497632155</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>159763</x:v>
+        <x:v>3205353</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.213898320624456</x:v>
+        <x:v>2.80617868429244</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>34317</x:v>
+        <x:v>43783</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.6600162048011</x:v>
+        <x:v>23.7425282847339</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1042,28 +1048,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>119878</x:v>
+        <x:v>558525</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>23.0267558638566</x:v>
+        <x:v>22.839415866952</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>87169</x:v>
+        <x:v>515156</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>23.0412090639882</x:v>
+        <x:v>22.8984536922368</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>207047</x:v>
+        <x:v>1073681</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.277204393948109</x:v>
+        <x:v>0.939971583763097</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>32709</x:v>
+        <x:v>43369</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.988238299814</x:v>
+        <x:v>22.1381386891892</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1071,28 +1077,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>253935</x:v>
+        <x:v>256721</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>23.0412286278497</x:v>
+        <x:v>22.859271682443</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>226261</x:v>
+        <x:v>214657</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>22.9554757698752</x:v>
+        <x:v>22.8565571737164</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>480196</x:v>
+        <x:v>471378</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.642909296711886</x:v>
+        <x:v>0.412675576089249</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>27674</x:v>
+        <x:v>42064</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>23.7423389623937</x:v>
+        <x:v>22.8731241049355</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1100,28 +1106,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>139618</x:v>
+        <x:v>126255</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>23.0070579543262</x:v>
+        <x:v>22.822107502437</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>114326</x:v>
+        <x:v>87020</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>23.0242726655803</x:v>
+        <x:v>22.9176339711466</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>253944</x:v>
+        <x:v>213275</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.339992333222691</x:v>
+        <x:v>0.186715085325226</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>25292</x:v>
+        <x:v>39235</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.9292432667239</x:v>
+        <x:v>22.6102376590037</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1129,28 +1135,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>483974</x:v>
+        <x:v>122853</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.0394991977465</x:v>
+        <x:v>23.0201761430744</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>461223</x:v>
+        <x:v>88645</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.0249767323854</x:v>
+        <x:v>23.0355094321616</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>945197</x:v>
+        <x:v>211498</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>1.26547480304747</x:v>
+        <x:v>0.185159381625201</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>22751</x:v>
+        <x:v>34208</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.3339080167526</x:v>
+        <x:v>22.9804421799332</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1158,28 +1164,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>507847</x:v>
+        <x:v>42234</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>22.9946965125156</x:v>
+        <x:v>23.0346803522451</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>486833</x:v>
+        <x:v>8228</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>23.0057841576306</x:v>
+        <x:v>22.9590473156504</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>994680</x:v>
+        <x:v>50462</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.33172500240189</x:v>
+        <x:v>0.0441777828422533</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>21014</x:v>
+        <x:v>34006</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>22.7378281612111</x:v>
+        <x:v>23.0529803176953</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1187,28 +1193,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>720717</x:v>
+        <x:v>1996423</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>23.0721648030504</x:v>
+        <x:v>22.8098395150132</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>703562</x:v>
+        <x:v>1962544</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>23.0736976640788</x:v>
+        <x:v>22.8144724041848</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1424279</x:v>
+        <x:v>3958967</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>1.90689262345273</x:v>
+        <x:v>3.46594238051697</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>17155</x:v>
+        <x:v>33879</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>23.0092990046929</x:v>
+        <x:v>22.5414653349529</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1216,28 +1222,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>81893</x:v>
+        <x:v>277600</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>22.9603556712103</x:v>
+        <x:v>23.0133952028126</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>65815</x:v>
+        <x:v>251931</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.0107878244712</x:v>
+        <x:v>22.927644206956</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>147708</x:v>
+        <x:v>529531</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.19775851193829</x:v>
+        <x:v>0.463586570612367</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>16078</x:v>
+        <x:v>25669</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>22.753912570895</x:v>
+        <x:v>23.8550070356517</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1245,28 +1251,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>618092</x:v>
+        <x:v>24015</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>23.0564515163414</x:v>
+        <x:v>22.6750033138544</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>603517</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>23.0851762345608</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1221609</x:v>
+        <x:v>24015</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>1.63554836576504</x:v>
+        <x:v>0.0210243243422122</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>14575</x:v>
+        <x:v>24015</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>21.8670274500904</x:v>
+        <x:v>22.6750033138544</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1274,28 +1280,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>40908</x:v>
+        <x:v>334220</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>23.081415601428</x:v>
+        <x:v>22.9223594091474</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>35232</x:v>
+        <x:v>313489</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>22.9730699307046</x:v>
+        <x:v>22.9655437870435</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>76140</x:v>
+        <x:v>647709</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.101939861747376</x:v>
+        <x:v>0.567047432661667</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>5676</x:v>
+        <x:v>20731</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>23.7539375660031</x:v>
+        <x:v>22.269336041134</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1303,28 +1309,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>3019</x:v>
+        <x:v>21400</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.0056709000195</x:v>
+        <x:v>22.8308409664118</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>924</x:v>
+        <x:v>8180</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.0032907007061</x:v>
+        <x:v>23.2055496924664</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>3943</x:v>
+        <x:v>29580</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00527907637076312</x:v>
+        <x:v>0.0258962945676718</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>2095</x:v>
+        <x:v>13220</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>23.0067206872107</x:v>
+        <x:v>22.5989863991557</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1332,28 +1338,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>10000</x:v>
+        <x:v>742856</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.046000289917</x:v>
+        <x:v>23.0635839045797</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>8180</x:v>
+        <x:v>731001</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.2055496924664</x:v>
+        <x:v>23.0613690850012</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>18180</x:v>
+        <x:v>1473857</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0243402506772695</x:v>
+        <x:v>1.2903122049569</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>1820</x:v>
+        <x:v>11855</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>22.3289046235137</x:v>
+        <x:v>23.2001537339087</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1361,28 +1367,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1300</x:v>
+        <x:v>130349</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>23.1599998474121</x:v>
+        <x:v>22.8968126547376</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>0</x:v>
+        <x:v>121667</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>0</x:v>
+        <x:v>22.8653621020645</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1300</x:v>
+        <x:v>252016</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00174050197362213</x:v>
+        <x:v>0.220631527105016</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>1300</x:v>
+        <x:v>8682</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.1599998474121</x:v>
+        <x:v>23.3375514697655</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1390,28 +1396,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>59124</x:v>
+        <x:v>9549</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>22.9439778869912</x:v>
+        <x:v>22.7710842270791</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>58079</x:v>
+        <x:v>3385</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.0157925823458</x:v>
+        <x:v>22.9954096006678</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>117203</x:v>
+        <x:v>12934</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.156916963703411</x:v>
+        <x:v>0.0113232817423349</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>1045</x:v>
+        <x:v>6164</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>18.952661435798</x:v>
+        <x:v>22.6478945142955</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1419,28 +1425,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>2445</x:v>
+        <x:v>43393</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>22.8981099672844</x:v>
+        <x:v>23.0614871021855</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1407</x:v>
+        <x:v>37394</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>23.0492682019785</x:v>
+        <x:v>22.9577386629303</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>3852</x:v>
+        <x:v>80787</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00515724123260957</x:v>
+        <x:v>0.0707262998390298</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>1038</x:v>
+        <x:v>5999</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>22.6932162907771</x:v>
+        <x:v>23.7081897422102</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1448,28 +1454,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>137</x:v>
+        <x:v>1154421</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>23.0400009155273</x:v>
+        <x:v>22.9750976615982</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>0</x:v>
+        <x:v>1150141</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>0</x:v>
+        <x:v>22.9555116953468</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>137</x:v>
+        <x:v>2304562</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.000183422131066332</x:v>
+        <x:v>2.01756647739901</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>137</x:v>
+        <x:v>4280</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>23.0400009155273</x:v>
+        <x:v>28.2383272901874</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1477,28 +1483,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>343</x:v>
+        <x:v>1994</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>22.8367350720108</x:v>
+        <x:v>23.0326979684017</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>484</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>23.0727274555805</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>827</x:v>
+        <x:v>1994</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00110722702475808</x:v>
+        <x:v>0.0017456798974962</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-141</x:v>
+        <x:v>1994</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.6468082184487</x:v>
+        <x:v>23.0326979684017</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1506,28 +1512,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>0</x:v>
+        <x:v>3024</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>0</x:v>
+        <x:v>23.005264698513</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>145</x:v>
+        <x:v>1339</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>23.0799999237061</x:v>
+        <x:v>22.9084693789037</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>145</x:v>
+        <x:v>4363</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.000194132912442468</x:v>
+        <x:v>0.0038196596754142</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-145</x:v>
+        <x:v>1685</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.0799999237061</x:v>
+        <x:v>23.0821839465586</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1535,28 +1541,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>2817</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>22.9677242973742</x:v>
+        <x:v>22.6003582311672</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>4716</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>23.0801012934619</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>7533</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0100855395133042</x:v>
+        <x:v>0.000440359572939111</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-1899</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>23.2468027141987</x:v>
+        <x:v>22.6003582311672</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1564,28 +1570,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>259</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>22.9528957057644</x:v>
+        <x:v>23.0400009155273</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>2978</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>23.03059830419</x:v>
+        <x:v>22.7800006866455</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>3237</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0043338499143191</x:v>
+        <x:v>0.000239877779294864</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-2719</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>23.0379999124991</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1593,28 +1599,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>63206</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>23.136354465</x:v>
+        <x:v>22.792051310417</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>67353</x:v>
+        <x:v>904</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>23.0658293970957</x:v>
+        <x:v>22.9325224762469</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>130559</x:v>
+        <x:v>1684</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.174798613210871</x:v>
+        <x:v>0.00147428532968084</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-4147</x:v>
+        <x:v>-124</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.990930086278</x:v>
+        <x:v>23.8161314225966</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1622,28 +1628,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>228356</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>23.0220582943711</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>233304</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>23.0522956500936</x:v>
+        <x:v>22.8408306016229</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>461660</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.618092416263379</x:v>
+        <x:v>0.000253009774511736</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-4948</x:v>
+        <x:v>-289</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>24.4477850606389</x:v>
+        <x:v>22.8408306016229</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1651,28 +1657,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>425000</x:v>
+        <x:v>195255</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>22.9901769860346</x:v>
+        <x:v>22.923368650258</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>431317</x:v>
+        <x:v>195821</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>23.0019519115089</x:v>
+        <x:v>22.8998709091161</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>856317</x:v>
+        <x:v>391076</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>1.1464780219586</x:v>
+        <x:v>0.342373877428898</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-6317</x:v>
+        <x:v>-566</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.7941544327306</x:v>
+        <x:v>14.7937729468194</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1680,28 +1686,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>174427</x:v>
+        <x:v>121185</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>23.0188951194606</x:v>
+        <x:v>22.8757101650358</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>184313</x:v>
+        <x:v>121913</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>23.0072484901079</x:v>
+        <x:v>22.7892773058524</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>358740</x:v>
+        <x:v>243098</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.480298213859387</x:v>
+        <x:v>0.212824118215412</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-9886</x:v>
+        <x:v>-728</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>22.801757227909</x:v>
+        <x:v>8.40141186609373</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1709,28 +1715,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>72904</x:v>
+        <x:v>72210</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.1405915593415</x:v>
+        <x:v>23.0819019632481</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>85793</x:v>
+        <x:v>73237</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>22.9888612281366</x:v>
+        <x:v>23.0402764738203</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>158697</x:v>
+        <x:v>145447</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.212471109006086</x:v>
+        <x:v>0.127333953887226</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-12889</x:v>
+        <x:v>-1027</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>22.1306295525862</x:v>
+        <x:v>20.1135222463784</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1738,28 +1744,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>96024</x:v>
+        <x:v>618265</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>23.0065832459846</x:v>
+        <x:v>22.846738568961</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>123760</x:v>
+        <x:v>620181</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>23.0267482483086</x:v>
+        <x:v>22.9001752485257</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>219784</x:v>
+        <x:v>1238446</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.294257296746589</x:v>
+        <x:v>1.08421779655696</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-27736</x:v>
+        <x:v>-1916</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>23.0965609171565</x:v>
+        <x:v>40.1434052543003</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1767,28 +1773,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>106039</x:v>
+        <x:v>3588746</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>22.9668303901152</x:v>
+        <x:v>22.9271419534477</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>157968</x:v>
+        <x:v>3598117</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>23.1079905953896</x:v>
+        <x:v>22.9146724646706</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>264007</x:v>
+        <x:v>7186863</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.353465157346198</x:v>
+        <x:v>6.29185670268767</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-51929</x:v>
+        <x:v>-9371</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>23.3962396856298</x:v>
+        <x:v>18.1393199973981</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1796,28 +1802,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1913034</x:v>
+        <x:v>13326</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>23.0180737371652</x:v>
+        <x:v>22.7795396594695</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>1998501</x:v>
+        <x:v>26425</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>23.0342446978675</x:v>
+        <x:v>22.8216448345924</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>3911535</x:v>
+        <x:v>39751</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>5.23694952876311</x:v>
+        <x:v>0.0348006627910589</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-85467</x:v>
+        <x:v>-13099</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>23.3962042569509</x:v>
+        <x:v>22.8644796741747</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1825,28 +1831,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>281720</x:v>
+        <x:v>189894</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>22.98831706892</x:v>
+        <x:v>22.8546378025505</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>373192</x:v>
+        <x:v>214665</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>22.9931886537903</x:v>
+        <x:v>22.8989931335407</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>654912</x:v>
+        <x:v>404559</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.876827406576013</x:v>
+        <x:v>0.354177790196171</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-91472</x:v>
+        <x:v>-24771</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.0081924023652</x:v>
+        <x:v>23.2390202306718</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1854,28 +1860,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>192911</x:v>
+        <x:v>117291</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>23.0013664443903</x:v>
+        <x:v>22.9196369083557</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>321918</x:v>
+        <x:v>149901</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>23.0026992536229</x:v>
+        <x:v>22.9456401661472</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>514829</x:v>
+        <x:v>267192</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.689277608136852</x:v>
+        <x:v>0.233917604399099</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-129007</x:v>
+        <x:v>-32610</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.0046922738612</x:v>
+        <x:v>23.0391681670558</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1883,28 +1889,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1095878</x:v>
+        <x:v>233696</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>23.0166700422819</x:v>
+        <x:v>22.9492861057461</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1329609</x:v>
+        <x:v>298033</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>23.024062818275</x:v>
+        <x:v>22.8784204298789</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>2425487</x:v>
+        <x:v>531729</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>3.24735762345755</x:v>
+        <x:v>0.465510845644812</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-233731</x:v>
+        <x:v>-64337</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.0587248039326</x:v>
+        <x:v>22.6210098420762</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1912,28 +1918,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>1200765</x:v>
+        <x:v>2020726</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>23.0152472412961</x:v>
+        <x:v>22.8820002837628</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1471970</x:v>
+        <x:v>2087488</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>23.0910231901368</x:v>
+        <x:v>22.9140063919963</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>2672735</x:v>
+        <x:v>4108214</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>3.57838503266842</x:v>
+        <x:v>3.5966031065258</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-271205</x:v>
+        <x:v>-66762</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.4265225622344</x:v>
+        <x:v>23.8827547078964</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1941,28 +1947,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>182760</x:v>
+        <x:v>2260138</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>23.0034990225508</x:v>
+        <x:v>22.9749318397379</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>462178</x:v>
+        <x:v>2338334</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>23.1549551822391</x:v>
+        <x:v>22.9925085023121</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>644938</x:v>
+        <x:v>4598472</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.863473739895315</x:v>
+        <x:v>4.02580748726135</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-279418</x:v>
+        <x:v>-78196</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.2540186919078</x:v>
+        <x:v>23.5005355496938</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1970,28 +1976,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>877254</x:v>
+        <x:v>483971</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>23.0186985850585</x:v>
+        <x:v>22.8437945214852</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1294086</x:v>
+        <x:v>610174</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>22.9913208162032</x:v>
+        <x:v>23.0600288184972</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>2171340</x:v>
+        <x:v>1094145</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>2.90709350415744</x:v>
+        <x:v>0.957887127104302</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-416832</x:v>
+        <x:v>-126203</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>22.9337022618711</x:v>
+        <x:v>23.8892573547381</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1999,28 +2005,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>1785675</x:v>
+        <x:v>1704762</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>23.0284077670114</x:v>
+        <x:v>22.9293076665326</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2318770</x:v>
+        <x:v>2025474</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>23.0233339662163</x:v>
+        <x:v>22.9902929355357</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>4104445</x:v>
+        <x:v>3730236</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>5.49522663317191</x:v>
+        <x:v>3.26569608732028</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-533095</x:v>
+        <x:v>-320712</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.0063385728347</x:v>
+        <x:v>23.3144634347882</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2028,28 +2034,86 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>2662538</x:v>
+        <x:v>1566558</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>23.0305523710266</x:v>
+        <x:v>22.8940151310113</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>3237918</x:v>
+        <x:v>2089806</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>22.9933668473576</x:v>
+        <x:v>22.8938578547635</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>5900456</x:v>
+        <x:v>3656364</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>7.89981177943888</x:v>
+        <x:v>3.20102363727622</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-575380</x:v>
+        <x:v>-523248</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>22.8212929660641</x:v>
+        <x:v>22.8933869836579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:9">
+      <x:c r="A53" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B53" s="0">
+        <x:v>3144912</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>22.9052735675133</x:v>
+      </x:c>
+      <x:c r="D53" s="0">
+        <x:v>3948651</x:v>
+      </x:c>
+      <x:c r="E53" s="0">
+        <x:v>22.906536050832</x:v>
+      </x:c>
+      <x:c r="F53" s="0">
+        <x:v>7093563</x:v>
+      </x:c>
+      <x:c r="G53" s="0">
+        <x:v>6.21017569243873</x:v>
+      </x:c>
+      <x:c r="H53" s="0">
+        <x:v>-803739</x:v>
+      </x:c>
+      <x:c r="I53" s="0">
+        <x:v>22.911475961598</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:9">
+      <x:c r="A54" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B54" s="0">
+        <x:v>3874559</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>22.9353785754317</x:v>
+      </x:c>
+      <x:c r="D54" s="0">
+        <x:v>5303770</x:v>
+      </x:c>
+      <x:c r="E54" s="0">
+        <x:v>22.8887106307554</x:v>
+      </x:c>
+      <x:c r="F54" s="0">
+        <x:v>9178329</x:v>
+      </x:c>
+      <x:c r="G54" s="0">
+        <x:v>8.03531816845856</x:v>
+      </x:c>
+      <x:c r="H54" s="0">
+        <x:v>-1429211</x:v>
+      </x:c>
+      <x:c r="I54" s="0">
+        <x:v>22.7621948783178</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,154 +40,154 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
-    <x:t>MIDAS</x:t>
+    <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
+    <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
+    <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
+    <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
@@ -584,28 +584,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>5157554</x:v>
+        <x:v>6310599</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>22.9787228450416</x:v>
+        <x:v>22.8158618226834</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>4576741</x:v>
+        <x:v>5390482</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>22.9760777476513</x:v>
+        <x:v>22.836258622425</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>9734295</x:v>
+        <x:v>11701081</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>8.5220476919748</x:v>
+        <x:v>8.13224564796862</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>580813</x:v>
+        <x:v>920117</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>22.9995659144543</x:v>
+        <x:v>22.6963676911059</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -613,28 +613,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>5020927</x:v>
+        <x:v>5974030</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>22.8713464725525</x:v>
+        <x:v>22.92378482659</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>4536168</x:v>
+        <x:v>5539227</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>22.8850457702788</x:v>
+        <x:v>22.9091105456292</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>9557095</x:v>
+        <x:v>11513257</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>8.36691505514615</x:v>
+        <x:v>8.00170805861392</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>484759</x:v>
+        <x:v>434803</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>22.7431542863974</x:v>
+        <x:v>23.1107296574754</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -642,28 +642,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>943616</x:v>
+        <x:v>1426663</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>23.0120988915767</x:v>
+        <x:v>22.8897385507444</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>633348</x:v>
+        <x:v>1060859</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>23.0384842640978</x:v>
+        <x:v>22.8650905683666</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1576964</x:v>
+        <x:v>2487522</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.38057891367863</x:v>
+        <x:v>1.72882658950282</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>310268</x:v>
+        <x:v>365804</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>22.9582386065472</x:v>
+        <x:v>22.9612195458603</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -671,28 +671,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>4318178</x:v>
+        <x:v>1138644</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>22.9051066466749</x:v>
+        <x:v>22.9431128656538</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>4011301</x:v>
+        <x:v>808196</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>22.8695931195152</x:v>
+        <x:v>22.9495506556795</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>8329479</x:v>
+        <x:v>1946840</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>7.29217855913577</x:v>
+        <x:v>1.35305286044009</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>306877</x:v>
+        <x:v>330448</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>23.3693168905483</x:v>
+        <x:v>22.9273675860709</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -700,28 +700,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>1066132</x:v>
+        <x:v>213000</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>22.9975677871914</x:v>
+        <x:v>23.0657281920384</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>773672</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>22.9693736602913</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1839804</x:v>
+        <x:v>213000</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.61068648853214</x:v>
+        <x:v>0.148034897204567</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>292460</x:v>
+        <x:v>213000</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.0721523681499</x:v>
+        <x:v>23.0657281920384</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -729,28 +729,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>7282416</x:v>
+        <x:v>2452823</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>22.9500589705202</x:v>
+        <x:v>22.8214714308906</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>7035138</x:v>
+        <x:v>2294327</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>22.9514385882818</x:v>
+        <x:v>22.9395145694645</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>14317554</x:v>
+        <x:v>4747150</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>12.5345367096872</x:v>
+        <x:v>3.29926695898902</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>247278</x:v>
+        <x:v>158496</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>22.9108084050002</x:v>
+        <x:v>21.1127244593903</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -758,28 +758,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>210000</x:v>
+        <x:v>732947</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>23.0733338310605</x:v>
+        <x:v>22.7853628012422</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>0</x:v>
+        <x:v>601767</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>0</x:v>
+        <x:v>22.8538644350575</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>210000</x:v>
+        <x:v>1334714</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.183847933036209</x:v>
+        <x:v>0.927625585856793</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>210000</x:v>
+        <x:v>131180</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.0733338310605</x:v>
+        <x:v>22.471122652773</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -787,28 +787,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>1940018</x:v>
+        <x:v>952441</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>22.9130189374995</x:v>
+        <x:v>22.9019914058254</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1798493</x:v>
+        <x:v>837008</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>22.9075277797151</x:v>
+        <x:v>22.9590943235988</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>3738511</x:v>
+        <x:v>1789449</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>3.27294057134825</x:v>
+        <x:v>1.2436661913982</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>141525</x:v>
+        <x:v>115433</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>22.9828003106642</x:v>
+        <x:v>22.4879365081812</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -816,28 +816,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>752597</x:v>
+        <x:v>1786310</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>22.9912463750739</x:v>
+        <x:v>22.9962395395159</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>659667</x:v>
+        <x:v>1677099</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>23.0505112478889</x:v>
+        <x:v>22.9924350865536</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1412264</x:v>
+        <x:v>3463409</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.23638960619738</x:v>
+        <x:v>2.40706758353227</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>92930</x:v>
+        <x:v>109211</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.5705525102803</x:v>
+        <x:v>23.0546626311331</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -845,28 +845,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>798619</x:v>
+        <x:v>322258</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>22.9027313426524</x:v>
+        <x:v>22.7800185341381</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>707439</x:v>
+        <x:v>221218</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>22.9214020398089</x:v>
+        <x:v>22.9753241322632</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>1506058</x:v>
+        <x:v>543476</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.31850309682213</x:v>
+        <x:v>0.377715557714317</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>91180</x:v>
+        <x:v>101040</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.7578708543252</x:v>
+        <x:v>22.352414478259</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -874,28 +874,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>200970</x:v>
+        <x:v>1004979</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>22.8734650415752</x:v>
+        <x:v>22.8360498345917</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>120906</x:v>
+        <x:v>911669</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>22.9239123402175</x:v>
+        <x:v>22.8393888499527</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>321876</x:v>
+        <x:v>1916648</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.281791606161728</x:v>
+        <x:v>1.33206943501098</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>80064</x:v>
+        <x:v>93310</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>22.7972837230094</x:v>
+        <x:v>22.8034265702566</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -903,28 +903,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>712726</x:v>
+        <x:v>9116320</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>22.9458254782926</x:v>
+        <x:v>22.8773821659517</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>635348</x:v>
+        <x:v>9026648</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>22.9427400531128</x:v>
+        <x:v>22.8681150696536</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>1348074</x:v>
+        <x:v>18142968</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.18019342133264</x:v>
+        <x:v>12.6093540040646</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>77378</x:v>
+        <x:v>89672</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>22.9711597944693</x:v>
+        <x:v>23.8102354118301</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -932,28 +932,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>264134</x:v>
+        <x:v>852797</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>22.829361775325</x:v>
+        <x:v>22.8215260464272</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>188001</x:v>
+        <x:v>780702</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>23.0437394828483</x:v>
+        <x:v>22.8550614396967</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>452135</x:v>
+        <x:v>1633499</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.395828977158698</x:v>
+        <x:v>1.13528101666086</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>76133</x:v>
+        <x:v>72095</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>22.2999826179017</x:v>
+        <x:v>22.4583781360828</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -961,28 +961,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>710722</x:v>
+        <x:v>146119</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>22.8707480530315</x:v>
+        <x:v>22.9496414322231</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>652208</x:v>
+        <x:v>89896</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>22.9010089467576</x:v>
+        <x:v>23.0290846552853</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1362930</x:v>
+        <x:v>236015</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>1.19319934939543</x:v>
+        <x:v>0.164030311097352</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>58514</x:v>
+        <x:v>56223</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>22.5334544655939</x:v>
+        <x:v>22.8226181858579</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -990,28 +990,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>56495</x:v>
+        <x:v>57287</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>22.7263908107362</x:v>
+        <x:v>22.7240726247474</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>5106</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>23.0518523106797</x:v>
+        <x:v>22.9915474472046</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>61601</x:v>
+        <x:v>63037</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0539296024903026</x:v>
+        <x:v>0.0438106845778606</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>51389</x:v>
+        <x:v>51537</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>22.6940530260213</x:v>
+        <x:v>22.6942303710437</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1019,28 +1019,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1624568</x:v>
+        <x:v>409462</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>23.0380613820629</x:v>
+        <x:v>22.8614189191913</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1580785</x:v>
+        <x:v>359439</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>23.0185497632155</x:v>
+        <x:v>22.9170451120932</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>3205353</x:v>
+        <x:v>768901</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.80617868429244</x:v>
+        <x:v>0.534385823922484</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>43783</x:v>
+        <x:v>50023</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>23.7425282847339</x:v>
+        <x:v>22.4617183184587</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1048,28 +1048,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>558525</x:v>
+        <x:v>695520</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>22.839415866952</x:v>
+        <x:v>22.815129390387</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>515156</x:v>
+        <x:v>655454</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>22.8984536922368</x:v>
+        <x:v>22.882433298388</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1073681</x:v>
+        <x:v>1350974</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.939971583763097</x:v>
+        <x:v>0.938926278009593</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>43369</x:v>
+        <x:v>40066</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.1381386891892</x:v>
+        <x:v>21.7140807278091</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1077,28 +1077,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>256721</x:v>
+        <x:v>387727</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>22.859271682443</x:v>
+        <x:v>22.7722535150297</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>214657</x:v>
+        <x:v>347673</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>22.8565571737164</x:v>
+        <x:v>22.7527771875122</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>471378</x:v>
+        <x:v>735400</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.412675576089249</x:v>
+        <x:v>0.511102645090323</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>42064</x:v>
+        <x:v>40054</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>22.8731241049355</x:v>
+        <x:v>22.9413101190384</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1106,28 +1106,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>126255</x:v>
+        <x:v>331300</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>22.822107502437</x:v>
+        <x:v>22.941021785857</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>87020</x:v>
+        <x:v>293136</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>22.9176339711466</x:v>
+        <x:v>22.8756182943328</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>213275</x:v>
+        <x:v>624436</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.186715085325226</x:v>
+        <x:v>0.4339827186424</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>39235</x:v>
+        <x:v>38164</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.6102376590037</x:v>
+        <x:v>23.4433831183019</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1135,28 +1135,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>122853</x:v>
+        <x:v>168744</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>23.0201761430744</x:v>
+        <x:v>22.7978495710103</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>88645</x:v>
+        <x:v>130595</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>23.0355094321616</x:v>
+        <x:v>22.7756776749008</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>211498</x:v>
+        <x:v>299339</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.185159381625201</x:v>
+        <x:v>0.208040460536704</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>34208</x:v>
+        <x:v>38149</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.9804421799332</x:v>
+        <x:v>22.8737503488135</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1164,28 +1164,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>42234</x:v>
+        <x:v>42599</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.0346803522451</x:v>
+        <x:v>23.0311601169065</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>8228</x:v>
+        <x:v>10669</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>22.9590473156504</x:v>
+        <x:v>22.8849676734495</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>50462</x:v>
+        <x:v>53268</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0441777828422533</x:v>
+        <x:v>0.0370212342924549</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>34006</x:v>
+        <x:v>31930</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.0529803176953</x:v>
+        <x:v>23.0800084469798</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1193,28 +1193,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>1996423</x:v>
+        <x:v>28565</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>22.8098395150132</x:v>
+        <x:v>22.6630564088185</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1962544</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>22.8144724041848</x:v>
+        <x:v>22.5799999237061</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>3958967</x:v>
+        <x:v>29193</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>3.46594238051697</x:v>
+        <x:v>0.0202891209112344</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>33879</x:v>
+        <x:v>27937</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>22.5414653349529</x:v>
+        <x:v>22.6649234479656</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1222,28 +1222,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>277600</x:v>
+        <x:v>758294</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.0133952028126</x:v>
+        <x:v>23.0535045783472</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>251931</x:v>
+        <x:v>734401</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>22.927644206956</x:v>
+        <x:v>23.0593257162754</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>529531</x:v>
+        <x:v>1492695</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.463586570612367</x:v>
+        <x:v>1.03742230461395</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>25669</x:v>
+        <x:v>23893</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>23.8550070356517</x:v>
+        <x:v>22.8745798089328</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1251,28 +1251,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>24015</x:v>
+        <x:v>21826</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>22.6750033138544</x:v>
+        <x:v>22.6065393565152</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>0</x:v>
+        <x:v>904</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>0</x:v>
+        <x:v>22.9325224762469</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>24015</x:v>
+        <x:v>22730</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0210243243422122</x:v>
+        <x:v>0.0157973390303278</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>24015</x:v>
+        <x:v>20922</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>22.6750033138544</x:v>
+        <x:v>22.5924542432259</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1280,28 +1280,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>334220</x:v>
+        <x:v>5333202</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>22.9223594091474</x:v>
+        <x:v>22.8435975218312</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>313489</x:v>
+        <x:v>5312653</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>22.9655437870435</x:v>
+        <x:v>22.7992659859032</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>647709</x:v>
+        <x:v>10645855</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.567047432661667</x:v>
+        <x:v>7.39886408722878</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>20731</x:v>
+        <x:v>20549</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>22.269336041134</x:v>
+        <x:v>34.3048884529018</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1309,28 +1309,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>21400</x:v>
+        <x:v>60446</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>22.8308409664118</x:v>
+        <x:v>22.9342144016427</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>8180</x:v>
+        <x:v>41541</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>23.2055496924664</x:v>
+        <x:v>22.9265718001623</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>29580</x:v>
+        <x:v>101987</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0258962945676718</x:v>
+        <x:v>0.0708809157802921</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>13220</x:v>
+        <x:v>18905</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>22.5989863991557</x:v>
+        <x:v>22.9510079117245</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1338,28 +1338,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>742856</x:v>
+        <x:v>2463473</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>23.0635839045797</x:v>
+        <x:v>22.8418930074645</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>731001</x:v>
+        <x:v>2449971</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>23.0613690850012</x:v>
+        <x:v>22.8201851551451</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1473857</x:v>
+        <x:v>4913444</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>1.2903122049569</x:v>
+        <x:v>3.41484120873426</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>11855</x:v>
+        <x:v>13502</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.2001537339087</x:v>
+        <x:v>26.7808360273689</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1367,28 +1367,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>130349</x:v>
+        <x:v>21411</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>22.8968126547376</x:v>
+        <x:v>22.8306887434541</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>121667</x:v>
+        <x:v>8180</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>22.8653621020645</x:v>
+        <x:v>23.2055496924664</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>252016</x:v>
+        <x:v>29591</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.220631527105016</x:v>
+        <x:v>0.0205657307191566</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>8682</x:v>
+        <x:v>13231</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.3375514697655</x:v>
+        <x:v>22.5989328245576</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1396,28 +1396,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>9549</x:v>
+        <x:v>171594</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>22.7710842270791</x:v>
+        <x:v>22.8210963915879</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>3385</x:v>
+        <x:v>162285</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>22.9954096006678</x:v>
+        <x:v>22.79613375745</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>12934</x:v>
+        <x:v>333879</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0113232817423349</x:v>
+        <x:v>0.232045743867435</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>6164</x:v>
+        <x:v>9309</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>22.6478945142955</x:v>
+        <x:v>23.2562732184301</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1425,28 +1425,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>43393</x:v>
+        <x:v>104882</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>23.0614871021855</x:v>
+        <x:v>22.9269468830842</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>37394</x:v>
+        <x:v>98914</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>22.9577386629303</x:v>
+        <x:v>22.9278368745009</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>80787</x:v>
+        <x:v>203796</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0707262998390298</x:v>
+        <x:v>0.141638121646488</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>5999</x:v>
+        <x:v>5968</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>23.7081897422102</x:v>
+        <x:v>22.9121961104646</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1454,28 +1454,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1154421</x:v>
+        <x:v>9831</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>22.9750976615982</x:v>
+        <x:v>22.7662804589705</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1150141</x:v>
+        <x:v>3917</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>22.9555116953468</x:v>
+        <x:v>22.9466892220032</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>2304562</x:v>
+        <x:v>13748</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>2.01756647739901</x:v>
+        <x:v>0.00955485336510982</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>4280</x:v>
+        <x:v>5914</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>28.2383272901874</x:v>
+        <x:v>22.6467909214664</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1489,22 +1489,22 @@
         <x:v>23.0326979684017</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>0</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>0</x:v>
+        <x:v>22.6000003814697</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>1994</x:v>
+        <x:v>2139</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0017456798974962</x:v>
+        <x:v>0.0014866039677022</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>1994</x:v>
+        <x:v>1849</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.0326979684017</x:v>
+        <x:v>23.0666304454731</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1512,28 +1512,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>3024</x:v>
+        <x:v>3039</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.005264698513</x:v>
+        <x:v>23.0030340431316</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>1339</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>22.9084693789037</x:v>
+        <x:v>22.8870485805643</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>4363</x:v>
+        <x:v>4489</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0038196596754142</x:v>
+        <x:v>0.00311985283357419</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1685</x:v>
+        <x:v>1589</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.0821839465586</x:v>
+        <x:v>23.108873514952</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1541,10 +1541,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>503</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>22.6003582311672</x:v>
+        <x:v>22.6129223105096</x:v>
       </x:c>
       <x:c r="D35" s="0">
         <x:v>0</x:v>
@@ -1553,16 +1553,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>503</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000440359572939111</x:v>
+        <x:v>0.000518469639974682</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>503</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>22.6003582311672</x:v>
+        <x:v>22.6129223105096</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1585,7 +1585,7 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.000239877779294864</x:v>
+        <x:v>0.0001904298677655</x:v>
       </x:c>
       <x:c r="H36" s="0">
         <x:v>0</x:v>
@@ -1599,28 +1599,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>780</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>22.792051310417</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>904</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>22.9325224762469</x:v>
+        <x:v>22.8401380802023</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>1684</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00147428532968084</x:v>
+        <x:v>0.000201549860043777</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-124</x:v>
+        <x:v>-290</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>23.8161314225966</x:v>
+        <x:v>22.8401380802023</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1628,28 +1628,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>0</x:v>
+        <x:v>902261</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0</x:v>
+        <x:v>22.8744360406874</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>289</x:v>
+        <x:v>902859</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>22.8408306016229</x:v>
+        <x:v>22.8328819413804</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>289</x:v>
+        <x:v>1805120</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000253009774511736</x:v>
+        <x:v>1.25455752883525</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-289</x:v>
+        <x:v>-598</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>22.8408306016229</x:v>
+        <x:v>-39.8638458092476</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1657,28 +1657,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>195255</x:v>
+        <x:v>4091287</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>22.923368650258</x:v>
+        <x:v>22.8867197437261</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>195821</x:v>
+        <x:v>4092999</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>22.8998709091161</x:v>
+        <x:v>22.8766208611801</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>391076</x:v>
+        <x:v>8184286</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.342373877428898</x:v>
+        <x:v>5.68807482020084</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-566</x:v>
+        <x:v>-1712</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>14.7937729468194</x:v>
+        <x:v>-1.25739016376923</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1686,28 +1686,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>121185</x:v>
+        <x:v>1373512</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>22.8757101650358</x:v>
+        <x:v>22.9141573134097</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>121913</x:v>
+        <x:v>1377944</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>22.7892773058524</x:v>
+        <x:v>22.895479615901</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>243098</x:v>
+        <x:v>2751456</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.212824118215412</x:v>
+        <x:v>1.91226059212624</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-728</x:v>
+        <x:v>-4432</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>8.40141186609373</x:v>
+        <x:v>17.1071128152338</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1715,28 +1715,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>72210</x:v>
+        <x:v>44372</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>23.0819019632481</x:v>
+        <x:v>22.6479277068733</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>73237</x:v>
+        <x:v>53306</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>23.0402764738203</x:v>
+        <x:v>22.6927444405553</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>145447</x:v>
+        <x:v>97678</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.127333953887226</x:v>
+        <x:v>0.0678861628598485</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-1027</x:v>
+        <x:v>-8934</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>20.1135222463784</x:v>
+        <x:v>22.9153332145576</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1744,28 +1744,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>618265</x:v>
+        <x:v>230856</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>22.846738568961</x:v>
+        <x:v>22.8360136533001</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>620181</x:v>
+        <x:v>249525</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>22.9001752485257</x:v>
+        <x:v>22.7335328157588</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>1238446</x:v>
+        <x:v>480381</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.08421779655696</x:v>
+        <x:v>0.333864563164447</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-1916</x:v>
+        <x:v>-18669</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>40.1434052543003</x:v>
+        <x:v>21.4662814240699</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1773,28 +1773,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>3588746</x:v>
+        <x:v>526697</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>22.9271419534477</x:v>
+        <x:v>22.6852575094944</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>3598117</x:v>
+        <x:v>555251</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>22.9146724646706</x:v>
+        <x:v>22.7061128718682</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>7186863</x:v>
+        <x:v>1081948</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>6.29185670268767</x:v>
+        <x:v>0.751953337843602</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-9371</x:v>
+        <x:v>-28554</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>18.1393199973981</x:v>
+        <x:v>23.090803521032</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1802,28 +1802,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>13326</x:v>
+        <x:v>147746</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>22.7795396594695</x:v>
+        <x:v>22.7870006166115</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>26425</x:v>
+        <x:v>176525</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>22.8216448345924</x:v>
+        <x:v>22.75364973867</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>39751</x:v>
+        <x:v>324271</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.0348006627910589</x:v>
+        <x:v>0.22536818850433</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-13099</x:v>
+        <x:v>-28779</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>22.8644796741747</x:v>
+        <x:v>22.5824325729466</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1831,28 +1831,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>189894</x:v>
+        <x:v>3293907</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>22.8546378025505</x:v>
+        <x:v>22.7174396301957</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>214665</x:v>
+        <x:v>3325906</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>22.8989931335407</x:v>
+        <x:v>22.7192112393194</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>404559</x:v>
+        <x:v>6619813</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.354177790196171</x:v>
+        <x:v>4.60076684022751</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-24771</x:v>
+        <x:v>-31999</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>23.2390202306718</x:v>
+        <x:v>22.9015768036782</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1860,28 +1860,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>117291</x:v>
+        <x:v>2454713</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>22.9196369083557</x:v>
+        <x:v>22.9422589562513</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>149901</x:v>
+        <x:v>2494306</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>22.9456401661472</x:v>
+        <x:v>22.9662890056371</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>267192</x:v>
+        <x:v>4949019</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.233917604399099</x:v>
+        <x:v>3.4395658165655</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-32610</x:v>
+        <x:v>-39593</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23.0391681670558</x:v>
+        <x:v>24.4561199004401</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1889,28 +1889,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>233696</x:v>
+        <x:v>226189</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>22.9492861057461</x:v>
+        <x:v>22.8779531799091</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>298033</x:v>
+        <x:v>269185</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>22.8784204298789</x:v>
+        <x:v>22.8099670838554</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>531729</x:v>
+        <x:v>495374</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.465510845644812</x:v>
+        <x:v>0.344284690928711</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-64337</x:v>
+        <x:v>-42996</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>22.6210098420762</x:v>
+        <x:v>22.4523127187916</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1918,28 +1918,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>2020726</x:v>
+        <x:v>321167</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>22.8820002837628</x:v>
+        <x:v>22.842320261663</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>2087488</x:v>
+        <x:v>368220</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>22.9140063919963</x:v>
+        <x:v>22.8236734051544</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>4108214</x:v>
+        <x:v>689387</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>3.5966031065258</x:v>
+        <x:v>0.47912363229655</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-66762</x:v>
+        <x:v>-47053</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.8827547078964</x:v>
+        <x:v>22.6963966116602</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1947,28 +1947,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>2260138</x:v>
+        <x:v>771519</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>22.9749318397379</x:v>
+        <x:v>22.7330485519473</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>2338334</x:v>
+        <x:v>890618</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>22.9925085023121</x:v>
+        <x:v>22.908963644086</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>4598472</x:v>
+        <x:v>1662137</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>4.02580748726135</x:v>
+        <x:v>1.15518441283994</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-78196</x:v>
+        <x:v>-119099</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.5005355496938</x:v>
+        <x:v>24.048535227154</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1976,28 +1976,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>483971</x:v>
+        <x:v>120008</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>22.8437945214852</x:v>
+        <x:v>22.9127472506452</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>610174</x:v>
+        <x:v>246487</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>23.0600288184972</x:v>
+        <x:v>22.7793187882256</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>1094145</x:v>
+        <x:v>366495</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.957887127104302</x:v>
+        <x:v>0.254713848126704</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-126203</x:v>
+        <x:v>-126479</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.8892573547381</x:v>
+        <x:v>22.6527168786748</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2005,28 +2005,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>1704762</x:v>
+        <x:v>2596712</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>22.9293076665326</x:v>
+        <x:v>22.8154864070919</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2025474</x:v>
+        <x:v>2787219</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>22.9902929355357</x:v>
+        <x:v>22.8365844273948</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>3730236</x:v>
+        <x:v>5383931</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>3.26569608732028</x:v>
+        <x:v>3.74182944667363</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-320712</x:v>
+        <x:v>-190507</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.3144634347882</x:v>
+        <x:v>23.1241616948805</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2034,28 +2034,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>1566558</x:v>
+        <x:v>2042500</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>22.8940151310113</x:v>
+        <x:v>22.8198812236791</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>2089806</x:v>
+        <x:v>2636741</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>22.8938578547635</x:v>
+        <x:v>22.8274817225189</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>3656364</x:v>
+        <x:v>4679241</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>3.20102363727622</x:v>
+        <x:v>3.25207023676243</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-523248</x:v>
+        <x:v>-594241</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>22.8933869836579</x:v>
+        <x:v>22.8536058352616</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2063,28 +2063,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>3144912</x:v>
+        <x:v>4395731</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>22.9052735675133</x:v>
+        <x:v>22.8123079570008</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>3948651</x:v>
+        <x:v>5201041</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>22.906536050832</x:v>
+        <x:v>22.8294066836734</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>7093563</x:v>
+        <x:v>9596772</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>6.21017569243873</x:v>
+        <x:v>6.66975190852428</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-803739</x:v>
+        <x:v>-805310</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>22.911475961598</x:v>
+        <x:v>22.922738944412</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2092,28 +2092,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>3874559</x:v>
+        <x:v>4901310</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>22.9353785754317</x:v>
+        <x:v>22.8603089653037</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>5303770</x:v>
+        <x:v>6457134</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>22.8887106307554</x:v>
+        <x:v>22.8334115724704</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>9178329</x:v>
+        <x:v>11358444</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>8.03531816845856</x:v>
+        <x:v>7.89411309832786</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-1429211</x:v>
+        <x:v>-1555824</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>22.7621948783178</x:v>
+        <x:v>22.7486767564066</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -43,157 +43,157 @@
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
   </x:si>
   <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
@@ -584,28 +584,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>6310599</x:v>
+        <x:v>7176543</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>22.8158618226834</x:v>
+        <x:v>22.757394597171</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>5390482</x:v>
+        <x:v>6384841</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>22.836258622425</x:v>
+        <x:v>22.7605136104149</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>11701081</x:v>
+        <x:v>13561384</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>8.13224564796862</x:v>
+        <x:v>7.6797758803469</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>920117</x:v>
+        <x:v>791702</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>22.6963676911059</x:v>
+        <x:v>22.7322406836545</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -613,28 +613,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>5974030</x:v>
+        <x:v>7381775</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>22.92378482659</x:v>
+        <x:v>22.6963319499937</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>5539227</x:v>
+        <x:v>6716741</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>22.9091105456292</x:v>
+        <x:v>22.6953854185736</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>11513257</x:v>
+        <x:v>14098516</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>8.00170805861392</x:v>
+        <x:v>7.98395231087659</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>434803</x:v>
+        <x:v>665034</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>23.1107296574754</x:v>
+        <x:v>22.7058917715922</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -642,28 +642,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1426663</x:v>
+        <x:v>2163822</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>22.8897385507444</x:v>
+        <x:v>22.6918848360746</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1060859</x:v>
+        <x:v>1653413</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>22.8650905683666</x:v>
+        <x:v>22.6789903978868</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2487522</x:v>
+        <x:v>3817235</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.72882658950282</x:v>
+        <x:v>2.16169008138225</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>365804</x:v>
+        <x:v>510409</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>22.9612195458603</x:v>
+        <x:v>22.7336549297198</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -671,28 +671,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>1138644</x:v>
+        <x:v>11087280</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>22.9431128656538</x:v>
+        <x:v>22.7784346566593</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>808196</x:v>
+        <x:v>10709129</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>22.9495506556795</x:v>
+        <x:v>22.7833694764915</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1946840</x:v>
+        <x:v>21796409</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.35305286044009</x:v>
+        <x:v>12.3432487507452</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>330448</x:v>
+        <x:v>378151</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>22.9273675860709</x:v>
+        <x:v>22.6386819595238</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -700,28 +700,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>213000</x:v>
+        <x:v>7190680</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>23.0657281920384</x:v>
+        <x:v>22.8268142695026</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>0</x:v>
+        <x:v>6833379</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>0</x:v>
+        <x:v>22.8048118948134</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>213000</x:v>
+        <x:v>14024059</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.148034897204567</x:v>
+        <x:v>7.94178750876473</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>213000</x:v>
+        <x:v>357301</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.0657281920384</x:v>
+        <x:v>23.2476095237876</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -729,28 +729,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>2452823</x:v>
+        <x:v>743783</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>22.8214714308906</x:v>
+        <x:v>22.4989386256046</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2294327</x:v>
+        <x:v>397800</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>22.9395145694645</x:v>
+        <x:v>22.7037466335776</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>4747150</x:v>
+        <x:v>1141583</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.29926695898902</x:v>
+        <x:v>0.646475432655992</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>158496</x:v>
+        <x:v>345983</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>21.1127244593903</x:v>
+        <x:v>22.2634570395971</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -758,28 +758,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>732947</x:v>
+        <x:v>1462430</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>22.7853628012422</x:v>
+        <x:v>22.6979643014416</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>601767</x:v>
+        <x:v>1148124</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>22.8538644350575</x:v>
+        <x:v>22.7375966186823</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1334714</x:v>
+        <x:v>2610554</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.927625585856793</x:v>
+        <x:v>1.47834982355364</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>131180</x:v>
+        <x:v>314306</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>22.471122652773</x:v>
+        <x:v>22.5531919630207</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -787,28 +787,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>952441</x:v>
+        <x:v>1417760</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>22.9019914058254</x:v>
+        <x:v>22.8277448582805</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>837008</x:v>
+        <x:v>1129621</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>22.9590943235988</x:v>
+        <x:v>22.7803059391161</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1789449</x:v>
+        <x:v>2547381</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.2436661913982</x:v>
+        <x:v>1.44257512078811</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>115433</x:v>
+        <x:v>288139</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>22.4879365081812</x:v>
+        <x:v>23.0137245392868</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -816,28 +816,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1786310</x:v>
+        <x:v>3440442</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>22.9962395395159</x:v>
+        <x:v>22.6908255598969</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1677099</x:v>
+        <x:v>3157629</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>22.9924350865536</x:v>
+        <x:v>22.782136207043</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>3463409</x:v>
+        <x:v>6598071</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>2.40706758353227</x:v>
+        <x:v>3.73647015102709</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>109211</x:v>
+        <x:v>282813</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.0546626311331</x:v>
+        <x:v>21.6713351282785</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -845,28 +845,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>322258</x:v>
+        <x:v>213000</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>22.7800185341381</x:v>
+        <x:v>23.0657281920384</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>221218</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>22.9753241322632</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>543476</x:v>
+        <x:v>213000</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.377715557714317</x:v>
+        <x:v>0.120621336473762</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>101040</x:v>
+        <x:v>213000</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.352414478259</x:v>
+        <x:v>23.0657281920384</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -874,28 +874,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1004979</x:v>
+        <x:v>4975379</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>22.8360498345917</x:v>
+        <x:v>22.7751656305501</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>911669</x:v>
+        <x:v>4769030</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>22.8393888499527</x:v>
+        <x:v>22.789334320179</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>1916648</x:v>
+        <x:v>9744409</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>1.33206943501098</x:v>
+        <x:v>5.51823303627677</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>93310</x:v>
+        <x:v>206349</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>22.8034265702566</x:v>
+        <x:v>22.4477062975714</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -903,28 +903,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>9116320</x:v>
+        <x:v>3184016</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>22.8773821659517</x:v>
+        <x:v>22.7280364619658</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>9026648</x:v>
+        <x:v>2977819</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>22.8681150696536</x:v>
+        <x:v>22.7434337772749</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>18142968</x:v>
+        <x:v>6161835</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>12.6093540040646</x:v>
+        <x:v>3.48943085836057</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>89672</x:v>
+        <x:v>206197</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>23.8102354118301</x:v>
+        <x:v>22.5056742642793</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -932,28 +932,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>852797</x:v>
+        <x:v>448392</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>22.8215260464272</x:v>
+        <x:v>22.6389571877729</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>780702</x:v>
+        <x:v>292333</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>22.8550614396967</x:v>
+        <x:v>22.8158893928006</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1633499</x:v>
+        <x:v>740725</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>1.13528101666086</x:v>
+        <x:v>0.419470607791207</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>72095</x:v>
+        <x:v>156059</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>22.4583781360828</x:v>
+        <x:v>22.3075240612479</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -961,28 +961,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>146119</x:v>
+        <x:v>252215</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>22.9496414322231</x:v>
+        <x:v>22.609483595416</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>89896</x:v>
+        <x:v>136613</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>23.0290846552853</x:v>
+        <x:v>22.7595492960655</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>236015</x:v>
+        <x:v>388828</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.164030311097352</x:v>
+        <x:v>0.220192267692112</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>56223</x:v>
+        <x:v>115602</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>22.8226181858579</x:v>
+        <x:v>22.4321430168548</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -990,28 +990,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>57287</x:v>
+        <x:v>548866</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>22.7240726247474</x:v>
+        <x:v>22.7232199000131</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>5750</x:v>
+        <x:v>435522</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>22.9915474472046</x:v>
+        <x:v>22.8315804245747</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>63037</x:v>
+        <x:v>984388</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0438106845778606</x:v>
+        <x:v>0.557456320041002</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>51537</x:v>
+        <x:v>113344</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>22.6942303710437</x:v>
+        <x:v>22.30684680238</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1019,28 +1019,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>409462</x:v>
+        <x:v>253077</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>22.8614189191913</x:v>
+        <x:v>22.6422421091104</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>359439</x:v>
+        <x:v>165221</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>22.9170451120932</x:v>
+        <x:v>22.7855219733325</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>768901</x:v>
+        <x:v>418298</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.534385823922484</x:v>
+        <x:v>0.236881050724421</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>50023</x:v>
+        <x:v>87856</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.4617183184587</x:v>
+        <x:v>22.3727916168659</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1048,28 +1048,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>695520</x:v>
+        <x:v>802066</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>22.815129390387</x:v>
+        <x:v>22.7512240014466</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>655454</x:v>
+        <x:v>714353</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>22.882433298388</x:v>
+        <x:v>22.8373423575069</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1350974</x:v>
+        <x:v>1516419</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.938926278009593</x:v>
+        <x:v>0.858744067766222</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>40066</x:v>
+        <x:v>87713</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>21.7140807278091</x:v>
+        <x:v>22.0498581148983</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1077,28 +1077,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>387727</x:v>
+        <x:v>124093</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>22.7722535150297</x:v>
+        <x:v>22.5076805938995</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>347673</x:v>
+        <x:v>42911</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>22.7527771875122</x:v>
+        <x:v>22.9085539647815</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>735400</x:v>
+        <x:v>167004</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.511102645090323</x:v>
+        <x:v>0.0945739233636812</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>40054</x:v>
+        <x:v>81182</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>22.9413101190384</x:v>
+        <x:v>22.2957878440544</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1106,28 +1106,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>331300</x:v>
+        <x:v>1336757</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>22.941021785857</x:v>
+        <x:v>22.6757463176981</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>293136</x:v>
+        <x:v>1279287</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>22.8756182943328</x:v>
+        <x:v>22.6850646070016</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>624436</x:v>
+        <x:v>2616044</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.4339827186424</x:v>
+        <x:v>1.48145879602895</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>38164</x:v>
+        <x:v>57470</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>23.4433831183019</x:v>
+        <x:v>22.4683204195199</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1135,28 +1135,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>168744</x:v>
+        <x:v>59059</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>22.7978495710103</x:v>
+        <x:v>22.7147138990525</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>130595</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>22.7756776749008</x:v>
+        <x:v>22.9915474472046</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>299339</x:v>
+        <x:v>64809</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.208040460536704</x:v>
+        <x:v>0.0367011652372208</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>38149</x:v>
+        <x:v>53309</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.8737503488135</x:v>
+        <x:v>22.6848541586357</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1164,28 +1164,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>42599</x:v>
+        <x:v>1035050</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23.0311601169065</x:v>
+        <x:v>22.8556992993641</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>10669</x:v>
+        <x:v>984773</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>22.8849676734495</x:v>
+        <x:v>22.8675781054352</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>53268</x:v>
+        <x:v>2019823</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0370212342924549</x:v>
+        <x:v>1.14382042112884</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>31930</x:v>
+        <x:v>50277</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.0800084469798</x:v>
+        <x:v>22.6230297389082</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1193,28 +1193,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>28565</x:v>
+        <x:v>166124</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>22.6630564088185</x:v>
+        <x:v>22.855753280458</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>628</x:v>
+        <x:v>121896</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>22.5799999237061</x:v>
+        <x:v>22.8327640729008</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>29193</x:v>
+        <x:v>288020</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0202891209112344</x:v>
+        <x:v>0.163104963996117</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>27937</x:v>
+        <x:v>44228</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>22.6649234479656</x:v>
+        <x:v>22.9191134243576</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1222,28 +1222,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>758294</x:v>
+        <x:v>1870360</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23.0535045783472</x:v>
+        <x:v>22.954492595075</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>734401</x:v>
+        <x:v>1835224</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>23.0593257162754</x:v>
+        <x:v>22.9275613388846</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1492695</x:v>
+        <x:v>3705584</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>1.03742230461395</x:v>
+        <x:v>2.09846241547318</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>23893</x:v>
+        <x:v>35136</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>22.8745798089328</x:v>
+        <x:v>24.3611663117978</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1251,28 +1251,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>21826</x:v>
+        <x:v>909741</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>22.6065393565152</x:v>
+        <x:v>22.4863040586682</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>904</x:v>
+        <x:v>875440</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>22.9325224762469</x:v>
+        <x:v>22.5374664558502</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>22730</x:v>
+        <x:v>1785181</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0157973390303278</x:v>
+        <x:v>1.01094327731252</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>20922</x:v>
+        <x:v>34301</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>22.5924542432259</x:v>
+        <x:v>21.1805226240439</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1280,28 +1280,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>5333202</x:v>
+        <x:v>176824</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>22.8435975218312</x:v>
+        <x:v>22.6945370615044</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>5312653</x:v>
+        <x:v>146546</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>22.7992659859032</x:v>
+        <x:v>22.7618265073365</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>10645855</x:v>
+        <x:v>323370</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>7.39886408722878</x:v>
+        <x:v>0.183123575471926</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>20549</x:v>
+        <x:v>30278</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>34.3048884529018</x:v>
+        <x:v>22.368855076931</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1309,28 +1309,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>60446</x:v>
+        <x:v>43572</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>22.9342144016427</x:v>
+        <x:v>23.0128805176632</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>41541</x:v>
+        <x:v>15168</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>22.9265718001623</x:v>
+        <x:v>22.7470530360811</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>101987</x:v>
+        <x:v>58740</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0708809157802921</x:v>
+        <x:v>0.0332643065937501</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>18905</x:v>
+        <x:v>28404</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>22.9510079117245</x:v>
+        <x:v>23.1548348635523</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1338,28 +1338,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>2463473</x:v>
+        <x:v>35586</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>22.8418930074645</x:v>
+        <x:v>22.4863996865382</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2449971</x:v>
+        <x:v>12275</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>22.8201851551451</x:v>
+        <x:v>22.1708500534648</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>4913444</x:v>
+        <x:v>47861</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>3.41484120873426</x:v>
+        <x:v>0.0271035576759188</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>13502</x:v>
+        <x:v>23311</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>26.7808360273689</x:v>
+        <x:v>22.6525603723078</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1367,10 +1367,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>21411</x:v>
+        <x:v>24576</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>22.8306887434541</x:v>
+        <x:v>22.7598354731066</x:v>
       </x:c>
       <x:c r="D29" s="0">
         <x:v>8180</x:v>
@@ -1379,16 +1379,16 @@
         <x:v>23.2055496924664</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>29591</x:v>
+        <x:v>32756</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0205657307191566</x:v>
+        <x:v>0.0185496361386598</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>13231</x:v>
+        <x:v>16396</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>22.5989328245576</x:v>
+        <x:v>22.5374676813059</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1396,28 +1396,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>171594</x:v>
+        <x:v>777005</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>22.8210963915879</x:v>
+        <x:v>23.0313527023059</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>162285</x:v>
+        <x:v>760939</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>22.79613375745</x:v>
+        <x:v>23.0323303130399</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>333879</x:v>
+        <x:v>1537944</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.232045743867435</x:v>
+        <x:v>0.870933618318324</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>9309</x:v>
+        <x:v>16066</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>23.2562732184301</x:v>
+        <x:v>22.985049818308</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1425,28 +1425,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>104882</x:v>
+        <x:v>396106</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>22.9269468830842</x:v>
+        <x:v>22.8235094338326</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>98914</x:v>
+        <x:v>381226</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>22.9278368745009</x:v>
+        <x:v>22.7430887984677</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>203796</x:v>
+        <x:v>777332</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.141638121646488</x:v>
+        <x:v>0.440201055041419</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>5968</x:v>
+        <x:v>14880</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>22.9121961104646</x:v>
+        <x:v>24.8838882737262</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1454,28 +1454,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>9831</x:v>
+        <x:v>23902</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>22.7662804589705</x:v>
+        <x:v>22.5021086481264</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>3917</x:v>
+        <x:v>9947</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>22.9466892220032</x:v>
+        <x:v>22.5306990176598</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>13748</x:v>
+        <x:v>33849</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00955485336510982</x:v>
+        <x:v>0.0191685991469501</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>5914</x:v>
+        <x:v>13955</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>22.6467909214664</x:v>
+        <x:v>22.4817296867685</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1483,10 +1483,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1994</x:v>
+        <x:v>2494</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>23.0326979684017</x:v>
+        <x:v>22.9058538725975</x:v>
       </x:c>
       <x:c r="D33" s="0">
         <x:v>145</x:v>
@@ -1495,16 +1495,16 @@
         <x:v>22.6000003814697</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>2139</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0014866039677022</x:v>
+        <x:v>0.0014944587180951</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>1849</x:v>
+        <x:v>2349</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>23.0666304454731</x:v>
+        <x:v>22.9247337177288</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1512,28 +1512,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>3039</x:v>
+        <x:v>3154</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>23.0030340431316</x:v>
+        <x:v>22.9717883664593</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>1450</x:v>
+        <x:v>1740</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>22.8870485805643</x:v>
+        <x:v>22.7742071568281</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>4489</x:v>
+        <x:v>4894</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00311985283357419</x:v>
+        <x:v>0.00277145925212484</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1589</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.108873514952</x:v>
+        <x:v>23.2149222453548</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1541,10 +1541,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>746</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>22.6129223105096</x:v>
+        <x:v>22.6127175940088</x:v>
       </x:c>
       <x:c r="D35" s="0">
         <x:v>0</x:v>
@@ -1553,16 +1553,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>746</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000518469639974682</x:v>
+        <x:v>0.000423024123689671</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>746</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>22.6129223105096</x:v>
+        <x:v>22.6127175940088</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1585,7 +1585,7 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0001904298677655</x:v>
+        <x:v>0.000155165475088313</x:v>
       </x:c>
       <x:c r="H36" s="0">
         <x:v>0</x:v>
@@ -1614,7 +1614,7 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.000201549860043777</x:v>
+        <x:v>0.000164226232757704</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>-290</x:v>
@@ -1628,28 +1628,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>902261</x:v>
+        <x:v>393755</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>22.8744360406874</x:v>
+        <x:v>22.7232831324824</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>902859</x:v>
+        <x:v>397092</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>22.8328819413804</x:v>
+        <x:v>22.7876606888406</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>1805120</x:v>
+        <x:v>790847</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>1.25455752883525</x:v>
+        <x:v>0.447854563785282</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-598</x:v>
+        <x:v>-3337</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>-39.8638458092476</x:v>
+        <x:v>30.3840001266018</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1657,28 +1657,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>4091287</x:v>
+        <x:v>28565</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>22.8867197437261</x:v>
+        <x:v>22.6630564088185</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>4092999</x:v>
+        <x:v>37602</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>22.8766208611801</x:v>
+        <x:v>22.3582797582831</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>8184286</x:v>
+        <x:v>66167</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>5.68807482020084</x:v>
+        <x:v>0.0374701970444103</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-1712</x:v>
+        <x:v>-9037</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>-1.25739016376923</x:v>
+        <x:v>21.3949130411708</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1686,28 +1686,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>1373512</x:v>
+        <x:v>251417</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>22.9141573134097</x:v>
+        <x:v>22.7929126753977</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>1377944</x:v>
+        <x:v>266639</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>22.895479615901</x:v>
+        <x:v>22.7113740743683</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>2751456</x:v>
+        <x:v>518056</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>1.91226059212624</x:v>
+        <x:v>0.293373742198362</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-4432</x:v>
+        <x:v>-15222</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>17.1071128152338</x:v>
+        <x:v>21.3646265737112</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1715,28 +1715,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>44372</x:v>
+        <x:v>1399442</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>22.6479277068733</x:v>
+        <x:v>22.9033986461813</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>53306</x:v>
+        <x:v>1419612</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>22.6927444405553</x:v>
+        <x:v>22.8796955046548</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>97678</x:v>
+        <x:v>2819054</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.0678861628598485</x:v>
+        <x:v>1.59642282193288</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-8934</x:v>
+        <x:v>-20170</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>22.9153332145576</x:v>
+        <x:v>21.2351158425781</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1744,28 +1744,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>230856</x:v>
+        <x:v>1038272</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>22.8360136533001</x:v>
+        <x:v>22.8012797734924</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>249525</x:v>
+        <x:v>1061055</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>22.7335328157588</x:v>
+        <x:v>22.766369865301</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>480381</x:v>
+        <x:v>2099327</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.333864563164447</x:v>
+        <x:v>1.18884332598804</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-18669</x:v>
+        <x:v>-22783</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>21.4662814240699</x:v>
+        <x:v>21.1754476778052</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1773,28 +1773,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>526697</x:v>
+        <x:v>161157</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>22.6852575094944</x:v>
+        <x:v>22.7407845537295</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>555251</x:v>
+        <x:v>206358</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>22.7061128718682</x:v>
+        <x:v>22.6941096780166</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>1081948</x:v>
+        <x:v>367515</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.751953337843602</x:v>
+        <x:v>0.208122772179129</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-28554</x:v>
+        <x:v>-45201</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>23.090803521032</x:v>
+        <x:v>22.5276978078088</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1802,28 +1802,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>147746</x:v>
+        <x:v>247793</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>22.7870006166115</x:v>
+        <x:v>22.825923376222</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>176525</x:v>
+        <x:v>293710</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>22.75364973867</x:v>
+        <x:v>22.7702611864837</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>324271</x:v>
+        <x:v>541503</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.22536818850433</x:v>
+        <x:v>0.3066517162655</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-28779</x:v>
+        <x:v>-45917</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>22.5824325729466</x:v>
+        <x:v>22.4698778647985</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1831,28 +1831,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>3293907</x:v>
+        <x:v>191907</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>22.7174396301957</x:v>
+        <x:v>22.3079871221042</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>3325906</x:v>
+        <x:v>274065</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>22.7192112393194</x:v>
+        <x:v>22.3025809374827</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>6619813</x:v>
+        <x:v>465972</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>4.60076684022751</x:v>
+        <x:v>0.263878710795078</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-31999</x:v>
+        <x:v>-82158</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>22.9015768036782</x:v>
+        <x:v>22.2899530172296</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1860,28 +1860,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>2454713</x:v>
+        <x:v>3644217</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>22.9422589562513</x:v>
+        <x:v>22.6843475808696</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>2494306</x:v>
+        <x:v>3742273</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>22.9662890056371</x:v>
+        <x:v>22.6825150250372</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>4949019</x:v>
+        <x:v>7386490</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>3.4395658165655</x:v>
+        <x:v>4.18294974483604</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-39593</x:v>
+        <x:v>-98056</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>24.4561199004401</x:v>
+        <x:v>22.6144087274341</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1889,28 +1889,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>226189</x:v>
+        <x:v>2680398</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>22.8779531799091</x:v>
+        <x:v>22.8848912539934</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>269185</x:v>
+        <x:v>2787371</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>22.8099670838554</x:v>
+        <x:v>22.9061745914838</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>495374</x:v>
+        <x:v>5467769</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.344284690928711</x:v>
+        <x:v>3.09638311882537</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-42996</x:v>
+        <x:v>-106973</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>22.4523127187916</x:v>
+        <x:v>23.4394663122244</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1918,28 +1918,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>321167</x:v>
+        <x:v>1028900</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>22.842320261663</x:v>
+        <x:v>22.6482105345054</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>368220</x:v>
+        <x:v>1140515</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>22.8236734051544</x:v>
+        <x:v>22.6018723357949</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>689387</x:v>
+        <x:v>2169415</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0.47912363229655</x:v>
+        <x:v>1.22853397495881</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-47053</x:v>
+        <x:v>-111615</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>22.6963966116602</x:v>
+        <x:v>22.1747131488296</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1947,28 +1947,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>771519</x:v>
+        <x:v>135826</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>22.7330485519473</x:v>
+        <x:v>22.8443753567986</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>890618</x:v>
+        <x:v>254659</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>22.908963644086</x:v>
+        <x:v>22.7616080816865</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>1662137</x:v>
+        <x:v>390485</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.15518441283994</x:v>
+        <x:v>0.221130622408248</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-119099</x:v>
+        <x:v>-118833</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>24.048535227154</x:v>
+        <x:v>22.6670051691171</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1976,28 +1976,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>120008</x:v>
+        <x:v>2684775</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>22.9127472506452</x:v>
+        <x:v>22.7802493264578</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>246487</x:v>
+        <x:v>3110083</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>22.7793187882256</x:v>
+        <x:v>22.7655918910789</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>366495</x:v>
+        <x:v>5794858</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.254713848126704</x:v>
+        <x:v>3.28161275415808</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-126479</x:v>
+        <x:v>-425308</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>22.6527168786748</x:v>
+        <x:v>22.6730662012974</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2005,28 +2005,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2596712</x:v>
+        <x:v>2466099</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>22.8154864070919</x:v>
+        <x:v>22.736564248509</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2787219</x:v>
+        <x:v>3253080</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>22.8365844273948</x:v>
+        <x:v>22.7332281103958</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>5383931</x:v>
+        <x:v>5719179</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>3.74182944667363</x:v>
+        <x:v>3.23875593667921</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-190507</x:v>
+        <x:v>-786981</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>23.1241616948805</x:v>
+        <x:v>22.7227739229825</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2034,28 +2034,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>2042500</x:v>
+        <x:v>5520203</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>22.8198812236791</x:v>
+        <x:v>22.7139336787387</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>2636741</x:v>
+        <x:v>6374999</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>22.8274817225189</x:v>
+        <x:v>22.7400615431801</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>4679241</x:v>
+        <x:v>11895202</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>3.25207023676243</x:v>
+        <x:v>6.73622142190312</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-594241</x:v>
+        <x:v>-854796</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>22.8536058352616</x:v>
+        <x:v>22.9087931653131</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2063,28 +2063,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>4395731</x:v>
+        <x:v>872868</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>22.8123079570008</x:v>
+        <x:v>22.6775779544196</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>5201041</x:v>
+        <x:v>2117093</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>22.8294066836734</x:v>
+        <x:v>22.4256507135542</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>9596772</x:v>
+        <x:v>2989961</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>6.66975190852428</x:v>
+        <x:v>1.69320700387054</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-805310</x:v>
+        <x:v>-1244225</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>22.922738944412</x:v>
+        <x:v>22.2489148121861</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2092,28 +2092,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>4901310</x:v>
+        <x:v>5820430</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>22.8603089653037</x:v>
+        <x:v>22.7807035082441</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>6457134</x:v>
+        <x:v>7453189</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>22.8334115724704</x:v>
+        <x:v>22.7730914646961</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>11358444</x:v>
+        <x:v>13273619</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>7.89411309832786</x:v>
+        <x:v>7.51681532217614</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-1555824</x:v>
+        <x:v>-1632759</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>22.7486767564066</x:v>
+        <x:v>22.7459561883767</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,163 +40,166 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUPAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
+    <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -547,7 +550,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I54"/>
+  <x:dimension ref="A1:I55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -584,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>7176543</x:v>
+        <x:v>7763675</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>22.757394597171</x:v>
+        <x:v>22.5084162464794</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>6384841</x:v>
+        <x:v>6244124</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>22.7605136104149</x:v>
+        <x:v>22.6151554069604</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>13561384</x:v>
+        <x:v>14007799</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>7.6797758803469</x:v>
+        <x:v>6.14266047792636</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>791702</x:v>
+        <x:v>1519551</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>22.7322406836545</x:v>
+        <x:v>22.0698047397256</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -613,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>7381775</x:v>
+        <x:v>10016302</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>22.6963319499937</x:v>
+        <x:v>22.5464000616861</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>6716741</x:v>
+        <x:v>8777165</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>22.6953854185736</x:v>
+        <x:v>22.5543007209994</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>14098516</x:v>
+        <x:v>18793467</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>7.98395231087659</x:v>
+        <x:v>8.24125810087034</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>665034</x:v>
+        <x:v>1239137</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>22.7058917715922</x:v>
+        <x:v>22.4904374115498</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -642,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2163822</x:v>
+        <x:v>13983928</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>22.6918848360746</x:v>
+        <x:v>22.623071525579</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1653413</x:v>
+        <x:v>13203351</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>22.6789903978868</x:v>
+        <x:v>22.6438310404512</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>3817235</x:v>
+        <x:v>27187279</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.16169008138225</x:v>
+        <x:v>11.9220888460534</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>510409</x:v>
+        <x:v>780577</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>22.7336549297198</x:v>
+        <x:v>22.2719272291827</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -671,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>11087280</x:v>
+        <x:v>2526435</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>22.7784346566593</x:v>
+        <x:v>22.5917709357562</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>10709129</x:v>
+        <x:v>1946516</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>22.7833694764915</x:v>
+        <x:v>22.5821010144856</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>21796409</x:v>
+        <x:v>4472951</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>12.3432487507452</x:v>
+        <x:v>1.96146584680443</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>378151</x:v>
+        <x:v>579919</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>22.6386819595238</x:v>
+        <x:v>22.6242283245843</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -700,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>7190680</x:v>
+        <x:v>1926616</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>22.8268142695026</x:v>
+        <x:v>22.525740312948</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>6833379</x:v>
+        <x:v>1496621</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>22.8048118948134</x:v>
+        <x:v>22.5678053449994</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>14024059</x:v>
+        <x:v>3423237</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>7.94178750876473</x:v>
+        <x:v>1.50114822653261</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>357301</x:v>
+        <x:v>429995</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>23.2476095237876</x:v>
+        <x:v>22.3793306795014</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -729,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>743783</x:v>
+        <x:v>4174910</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>22.4989386256046</x:v>
+        <x:v>22.5573911202111</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>397800</x:v>
+        <x:v>3753800</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>22.7037466335776</x:v>
+        <x:v>22.591639388113</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1141583</x:v>
+        <x:v>7928710</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.646475432655992</x:v>
+        <x:v>3.47687552897779</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>345983</x:v>
+        <x:v>421110</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>22.2634570395971</x:v>
+        <x:v>22.2520999895086</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -758,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>1462430</x:v>
+        <x:v>4285104</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>22.6979643014416</x:v>
+        <x:v>22.5592068949721</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1148124</x:v>
+        <x:v>3933162</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>22.7375966186823</x:v>
+        <x:v>22.6333447261457</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>2610554</x:v>
+        <x:v>8218266</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.47834982355364</x:v>
+        <x:v>3.60385080877346</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>314306</x:v>
+        <x:v>351942</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>22.5531919630207</x:v>
+        <x:v>21.7306723627643</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -787,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>1417760</x:v>
+        <x:v>1623963</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>22.8277448582805</x:v>
+        <x:v>22.7251667091218</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1129621</x:v>
+        <x:v>1369220</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>22.7803059391161</x:v>
+        <x:v>22.6476091007547</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>2547381</x:v>
+        <x:v>2993183</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.44257512078811</x:v>
+        <x:v>1.31256216035803</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>288139</x:v>
+        <x:v>254743</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.0137245392868</x:v>
+        <x:v>23.1420316613619</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -816,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>3440442</x:v>
+        <x:v>1009213</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>22.6908255598969</x:v>
+        <x:v>22.6043762294675</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>3157629</x:v>
+        <x:v>776533</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>22.782136207043</x:v>
+        <x:v>22.7728089729463</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>6598071</x:v>
+        <x:v>1785746</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>3.73647015102709</x:v>
+        <x:v>0.783080295327988</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>282813</x:v>
+        <x:v>232680</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>21.6713351282785</x:v>
+        <x:v>22.0422583697812</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -845,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>213000</x:v>
+        <x:v>8664543</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>23.0657281920384</x:v>
+        <x:v>22.6839802101104</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>0</x:v>
+        <x:v>8443974</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>0</x:v>
+        <x:v>22.6534409861221</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>213000</x:v>
+        <x:v>17108517</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.120621336473762</x:v>
+        <x:v>7.50237858294735</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>213000</x:v>
+        <x:v>220569</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.0657281920384</x:v>
+        <x:v>23.8531037648121</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -874,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>4975379</x:v>
+        <x:v>213000</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>22.7751656305501</x:v>
+        <x:v>23.0657281920384</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>4769030</x:v>
+        <x:v>14145</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>22.789334320179</x:v>
+        <x:v>22.1191807622495</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>9744409</x:v>
+        <x:v>227145</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>5.51823303627677</x:v>
+        <x:v>0.0996069842420343</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>206349</x:v>
+        <x:v>198855</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>22.4477062975714</x:v>
+        <x:v>23.13305822344</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -903,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>3184016</x:v>
+        <x:v>540011</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>22.7280364619658</x:v>
+        <x:v>22.5280776792043</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>2977819</x:v>
+        <x:v>347426</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>22.7434337772749</x:v>
+        <x:v>22.6941135110564</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>6161835</x:v>
+        <x:v>887437</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>3.48943085836057</x:v>
+        <x:v>0.38915636828809</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>206197</x:v>
+        <x:v>192585</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>22.5056742642793</x:v>
+        <x:v>22.2285467452423</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -932,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>448392</x:v>
+        <x:v>972945</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>22.6389571877729</x:v>
+        <x:v>22.3731966645677</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>292333</x:v>
+        <x:v>828755</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>22.8158893928006</x:v>
+        <x:v>22.2985971652748</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>740725</x:v>
+        <x:v>1801700</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.419470607791207</x:v>
+        <x:v>0.790076398374929</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>156059</x:v>
+        <x:v>144190</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>22.3075240612479</x:v>
+        <x:v>22.8019691733168</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -961,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>252215</x:v>
+        <x:v>1408138</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>22.609483595416</x:v>
+        <x:v>22.6050253860844</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>136613</x:v>
+        <x:v>1270312</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>22.7595492960655</x:v>
+        <x:v>22.6447373868575</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>388828</x:v>
+        <x:v>2678450</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.220192267692112</x:v>
+        <x:v>1.17454633358902</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>115602</x:v>
+        <x:v>137826</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>22.4321430168548</x:v>
+        <x:v>22.2390085886288</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -990,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>548866</x:v>
+        <x:v>607276</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>22.7232199000131</x:v>
+        <x:v>22.4662594509035</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>435522</x:v>
+        <x:v>472302</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>22.8315804245747</x:v>
+        <x:v>22.6645281708161</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>984388</x:v>
+        <x:v>1079578</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.557456320041002</x:v>
+        <x:v>0.473413497255264</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>113344</x:v>
+        <x:v>134974</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>22.30684680238</x:v>
+        <x:v>21.7724761077993</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1019,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>253077</x:v>
+        <x:v>315037</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>22.6422421091104</x:v>
+        <x:v>22.5103449115488</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>165221</x:v>
+        <x:v>185921</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>22.7855219733325</x:v>
+        <x:v>22.7057598554285</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>418298</x:v>
+        <x:v>500958</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.236881050724421</x:v>
+        <x:v>0.219678688115173</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>87856</x:v>
+        <x:v>129116</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.3727916168659</x:v>
+        <x:v>22.2289565338027</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1048,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>802066</x:v>
+        <x:v>471663</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>22.7512240014466</x:v>
+        <x:v>22.3630045320951</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>714353</x:v>
+        <x:v>384326</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>22.8373423575069</x:v>
+        <x:v>22.262377434795</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1516419</x:v>
+        <x:v>855989</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.858744067766222</x:v>
+        <x:v>0.375365880095775</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>87713</x:v>
+        <x:v>87337</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.0498581148983</x:v>
+        <x:v>22.805813533972</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1077,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>124093</x:v>
+        <x:v>87835</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>22.5076805938995</x:v>
+        <x:v>22.4726620204272</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>42911</x:v>
+        <x:v>11964</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>22.9085539647815</x:v>
+        <x:v>22.5291574808795</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>167004</x:v>
+        <x:v>99799</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0945739233636812</x:v>
+        <x:v>0.0437635757792194</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>81182</x:v>
+        <x:v>75871</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>22.2957878440544</x:v>
+        <x:v>22.4637533242343</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1106,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>1336757</x:v>
+        <x:v>48192</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>22.6757463176981</x:v>
+        <x:v>22.2406322682996</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>1279287</x:v>
+        <x:v>10362</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>22.6850646070016</x:v>
+        <x:v>22.5083230180046</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>2616044</x:v>
+        <x:v>58554</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>1.48145879602895</x:v>
+        <x:v>0.0256769348007135</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>57470</x:v>
+        <x:v>37830</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.4683204195199</x:v>
+        <x:v>22.167309203313</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1135,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>59059</x:v>
+        <x:v>54780</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>22.7147138990525</x:v>
+        <x:v>22.8080586079308</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>5750</x:v>
+        <x:v>18363</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>22.9915474472046</x:v>
+        <x:v>22.608380011326</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>64809</x:v>
+        <x:v>73143</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0367011652372208</x:v>
+        <x:v>0.0320744619006147</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>53309</x:v>
+        <x:v>36417</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.6848541586357</x:v>
+        <x:v>22.9087450474907</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1164,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>1035050</x:v>
+        <x:v>328411</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>22.8556992993641</x:v>
+        <x:v>22.1612751385598</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>984773</x:v>
+        <x:v>303067</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>22.8675781054352</x:v>
+        <x:v>22.1426438905561</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>2019823</x:v>
+        <x:v>631478</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.14382042112884</x:v>
+        <x:v>0.276913950098798</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>50277</x:v>
+        <x:v>25344</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>22.6230297389082</x:v>
+        <x:v>22.3840701369324</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1193,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>166124</x:v>
+        <x:v>201568</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>22.855753280458</x:v>
+        <x:v>22.6147029363914</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>121896</x:v>
+        <x:v>177506</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>22.8327640729008</x:v>
+        <x:v>22.6419172028349</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>288020</x:v>
+        <x:v>379074</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.163104963996117</x:v>
+        <x:v>0.166230460474873</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>44228</x:v>
+        <x:v>24062</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>22.9191134243576</x:v>
+        <x:v>22.4139425848282</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1222,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>1870360</x:v>
+        <x:v>40601</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>22.954492595075</x:v>
+        <x:v>22.4334798831047</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>1835224</x:v>
+        <x:v>17305</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>22.9275613388846</x:v>
+        <x:v>22.1402417896869</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>3705584</x:v>
+        <x:v>57906</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>2.09846241547318</x:v>
+        <x:v>0.0253927756698111</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>35136</x:v>
+        <x:v>23296</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>24.3611663117978</x:v>
+        <x:v>22.6513063428657</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1251,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>909741</x:v>
+        <x:v>1241334</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>22.4863040586682</x:v>
+        <x:v>22.7164596484819</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>875440</x:v>
+        <x:v>1220302</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>22.5374664558502</x:v>
+        <x:v>22.6987025868411</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1785181</x:v>
+        <x:v>2461636</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>1.01094327731252</x:v>
+        <x:v>1.07946967030586</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>34301</x:v>
+        <x:v>21032</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>21.1805226240439</x:v>
+        <x:v>23.7467457760237</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1280,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>176824</x:v>
+        <x:v>26876</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>22.6945370615044</x:v>
+        <x:v>22.6904195488023</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>146546</x:v>
+        <x:v>8180</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>22.7618265073365</x:v>
+        <x:v>23.2055496924664</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>323370</x:v>
+        <x:v>35056</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.183123575471926</x:v>
+        <x:v>0.015372658168081</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>30278</x:v>
+        <x:v>18696</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>22.368855076931</x:v>
+        <x:v>22.4650363344691</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1309,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>43572</x:v>
+        <x:v>17220</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>23.0128805176632</x:v>
+        <x:v>22.0456694289505</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>15168</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>22.7470530360811</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>58740</x:v>
+        <x:v>17220</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0332643065937501</x:v>
+        <x:v>0.00755126579342636</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>28404</x:v>
+        <x:v>17220</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>23.1548348635523</x:v>
+        <x:v>22.0456694289505</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1338,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>35586</x:v>
+        <x:v>889798</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>22.4863996865382</x:v>
+        <x:v>22.9081790366374</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>12275</x:v>
+        <x:v>874587</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>22.1708500534648</x:v>
+        <x:v>22.902040623166</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>47861</x:v>
+        <x:v>1764385</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0271035576759188</x:v>
+        <x:v>0.773713129903285</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>23311</x:v>
+        <x:v>15211</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>22.6525603723078</x:v>
+        <x:v>23.2611194496739</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1367,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>24576</x:v>
+        <x:v>2171436</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>22.7598354731066</x:v>
+        <x:v>22.4120238976948</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>8180</x:v>
+        <x:v>2160706</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>23.2055496924664</x:v>
+        <x:v>22.4010100459461</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>32756</x:v>
+        <x:v>4332142</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0185496361386598</x:v>
+        <x:v>1.89971868158337</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>16396</x:v>
+        <x:v>10730</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>22.5374676813059</x:v>
+        <x:v>24.6298892804205</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1396,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>777005</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>23.0313527023059</x:v>
+        <x:v>22.1399993896484</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>760939</x:v>
+        <x:v>40290</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>23.0323303130399</x:v>
+        <x:v>21.9464795583411</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1537944</x:v>
+        <x:v>90290</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.870933618318324</x:v>
+        <x:v>0.0395937159400968</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>16066</x:v>
+        <x:v>9710</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>22.985049818308</x:v>
+        <x:v>22.9429771448876</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1425,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>396106</x:v>
+        <x:v>230799</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>22.8235094338326</x:v>
+        <x:v>22.6370757894019</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>381226</x:v>
+        <x:v>224831</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>22.7430887984677</x:v>
+        <x:v>22.4474880107915</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>777332</x:v>
+        <x:v>455630</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.440201055041419</x:v>
+        <x:v>0.199801581501676</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>14880</x:v>
+        <x:v>5968</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>24.8838882737262</x:v>
+        <x:v>29.7793696655345</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1454,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>23902</x:v>
+        <x:v>5131</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>22.5021086481264</x:v>
+        <x:v>21.8999996185303</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>9947</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>22.5306990176598</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>33849</x:v>
+        <x:v>5131</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0191685991469501</x:v>
+        <x:v>0.00225003163682176</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>13955</x:v>
+        <x:v>5131</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>22.4817296867685</x:v>
+        <x:v>21.8999996185303</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1483,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>2494</x:v>
+        <x:v>4189</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>22.9058538725975</x:v>
+        <x:v>22.7023441535984</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>145</x:v>
+        <x:v>2280</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>22.6000003814697</x:v>
+        <x:v>22.603403786609</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>2639</x:v>
+        <x:v>6469</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0014944587180951</x:v>
+        <x:v>0.00283676762007405</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>2349</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>22.9247337177288</x:v>
+        <x:v>22.8205128475407</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1512,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>3154</x:v>
+        <x:v>2494</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>22.9717883664593</x:v>
+        <x:v>22.9058538725975</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>1740</x:v>
+        <x:v>1068</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>22.7742071568281</x:v>
+        <x:v>22.0706552351905</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>4894</x:v>
+        <x:v>3562</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00277145925212484</x:v>
+        <x:v>0.00156199818560887</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1414</x:v>
+        <x:v>1426</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.2149222453548</x:v>
+        <x:v>23.5313743107115</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1541,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>747</x:v>
+        <x:v>1137</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>22.6127175940088</x:v>
+        <x:v>22.0901312312224</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>0</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>0</x:v>
+        <x:v>22.7800006866455</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>747</x:v>
+        <x:v>1274</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000423024123689671</x:v>
+        <x:v>0.000558670883903902</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>747</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>22.6127175940088</x:v>
+        <x:v>21.9956191158295</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1570,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>137</x:v>
+        <x:v>2004747</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>23.0400009155273</x:v>
+        <x:v>22.8903219953437</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>137</x:v>
+        <x:v>2010895</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>22.7800006866455</x:v>
+        <x:v>22.8451150316462</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>274</x:v>
+        <x:v>4015642</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.000155165475088313</x:v>
+        <x:v>1.76092799496203</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>0</x:v>
+        <x:v>-6148</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0</x:v>
+        <x:v>8.10397566086143</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1599,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>0</x:v>
+        <x:v>29210</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0</x:v>
+        <x:v>22.6492676099903</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>290</x:v>
+        <x:v>37602</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>22.8401380802023</x:v>
+        <x:v>22.3582797582831</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>290</x:v>
+        <x:v>66812</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.000164226232757704</x:v>
+        <x:v>0.0292982096510106</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-290</x:v>
+        <x:v>-8392</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>22.8401380802023</x:v>
+        <x:v>21.3454395356465</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1628,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>393755</x:v>
+        <x:v>411792</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>22.7232831324824</x:v>
+        <x:v>22.7892981420082</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>397092</x:v>
+        <x:v>420391</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>22.7876606888406</x:v>
+        <x:v>22.6771077268498</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>790847</x:v>
+        <x:v>832183</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.447854563785282</x:v>
+        <x:v>0.364926540172528</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-3337</x:v>
+        <x:v>-8599</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>30.3840001266018</x:v>
+        <x:v>17.3044928368725</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1657,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>28565</x:v>
+        <x:v>1363812</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>22.6630564088185</x:v>
+        <x:v>22.4810456283472</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>37602</x:v>
+        <x:v>1373415</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>22.3582797582831</x:v>
+        <x:v>22.4985407160772</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>66167</x:v>
+        <x:v>2737227</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.0374701970444103</x:v>
+        <x:v>1.20032105772027</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-9037</x:v>
+        <x:v>-9603</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>21.3949130411708</x:v>
+        <x:v>24.9831820351623</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1686,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>251417</x:v>
+        <x:v>1070428</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>22.7929126753977</x:v>
+        <x:v>22.4157520042673</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>266639</x:v>
+        <x:v>1091479</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>22.7113740743683</x:v>
+        <x:v>22.4353390110021</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>518056</x:v>
+        <x:v>2161907</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.293373742198362</x:v>
+        <x:v>0.948033355265331</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-15222</x:v>
+        <x:v>-21051</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>21.3646265737112</x:v>
+        <x:v>23.431324020983</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1715,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>1399442</x:v>
+        <x:v>321621</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>22.9033986461813</x:v>
+        <x:v>22.6311606854085</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>1419612</x:v>
+        <x:v>350832</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>22.8796955046548</x:v>
+        <x:v>22.6406162553378</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>2819054</x:v>
+        <x:v>672453</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.59642282193288</x:v>
+        <x:v>0.294882191439427</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-20170</x:v>
+        <x:v>-29211</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>21.2351158425781</x:v>
+        <x:v>22.7447246342437</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1744,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>1038272</x:v>
+        <x:v>251736</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>22.8012797734924</x:v>
+        <x:v>22.454393683146</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>1061055</x:v>
+        <x:v>289695</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>22.766369865301</x:v>
+        <x:v>22.4915008003455</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>2099327</x:v>
+        <x:v>541431</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.18884332598804</x:v>
+        <x:v>0.237426793832789</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-22783</x:v>
+        <x:v>-37959</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>21.1754476778052</x:v>
+        <x:v>22.7375872951246</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1773,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>161157</x:v>
+        <x:v>344669</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>22.7407845537295</x:v>
+        <x:v>22.5747547534151</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>206358</x:v>
+        <x:v>383068</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>22.6941096780166</x:v>
+        <x:v>22.5201485868656</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>367515</x:v>
+        <x:v>727737</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.208122772179129</x:v>
+        <x:v>0.319125175070309</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-45201</x:v>
+        <x:v>-38399</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>22.5276978078088</x:v>
+        <x:v>22.0300042388768</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1802,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>247793</x:v>
+        <x:v>649353</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>22.825923376222</x:v>
+        <x:v>22.602827832292</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>293710</x:v>
+        <x:v>707615</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>22.7702611864837</x:v>
+        <x:v>22.5377573341384</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>541503</x:v>
+        <x:v>1356968</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.3066517162655</x:v>
+        <x:v>0.595053777071672</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-45917</x:v>
+        <x:v>-58262</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>22.4698778647985</x:v>
+        <x:v>21.8125209332675</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1831,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>191907</x:v>
+        <x:v>202399</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>22.3079871221042</x:v>
+        <x:v>22.2899619225415</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>274065</x:v>
+        <x:v>274878</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>22.3025809374827</x:v>
+        <x:v>22.3018215516798</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>465972</x:v>
+        <x:v>477277</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.263878710795078</x:v>
+        <x:v>0.209294162839091</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-82158</x:v>
+        <x:v>-72479</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>22.2899530172296</x:v>
+        <x:v>22.3349397939013</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1860,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>3644217</x:v>
+        <x:v>1672251</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>22.6843475808696</x:v>
+        <x:v>22.7767722659056</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>3742273</x:v>
+        <x:v>1751987</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>22.6825150250372</x:v>
+        <x:v>22.7257125580017</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>7386490</x:v>
+        <x:v>3424238</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>4.18294974483604</x:v>
+        <x:v>1.5015871822271</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-98056</x:v>
+        <x:v>-79736</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>22.6144087274341</x:v>
+        <x:v>21.6548706847949</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1889,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>2680398</x:v>
+        <x:v>176618</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>22.8848912539934</x:v>
+        <x:v>22.6649540712402</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2787371</x:v>
+        <x:v>304971</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>22.9061745914838</x:v>
+        <x:v>22.6465086540231</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>5467769</x:v>
+        <x:v>481589</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>3.09638311882537</x:v>
+        <x:v>0.211185048907689</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-106973</x:v>
+        <x:v>-128353</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.4394663122244</x:v>
+        <x:v>22.6211271460098</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1918,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>1028900</x:v>
+        <x:v>4149575</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>22.6482105345054</x:v>
+        <x:v>22.6034110776536</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1140515</x:v>
+        <x:v>4306631</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>22.6018723357949</x:v>
+        <x:v>22.5952253129712</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>2169415</x:v>
+        <x:v>8456206</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.22853397495881</x:v>
+        <x:v>3.70819158594464</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-111615</x:v>
+        <x:v>-157056</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>22.1747131488296</x:v>
+        <x:v>22.3789493064377</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1947,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>135826</x:v>
+        <x:v>2999519</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>22.8443753567986</x:v>
+        <x:v>22.7948268852102</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>254659</x:v>
+        <x:v>3250464</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>22.7616080816865</x:v>
+        <x:v>22.7767776602041</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>390485</x:v>
+        <x:v>6249983</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.221130622408248</x:v>
+        <x:v>2.74072490344926</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-118833</x:v>
+        <x:v>-250945</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>22.6670051691171</x:v>
+        <x:v>22.5610371858325</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1976,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2684775</x:v>
+        <x:v>3207225</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>22.7802493264578</x:v>
+        <x:v>22.6568383791197</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>3110083</x:v>
+        <x:v>3555754</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>22.7655918910789</x:v>
+        <x:v>22.6738518570024</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>5794858</x:v>
+        <x:v>6762979</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>3.28161275415808</x:v>
+        <x:v>2.965682461345</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-425308</x:v>
+        <x:v>-348529</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>22.6730662012974</x:v>
+        <x:v>22.8304128651311</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2005,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2466099</x:v>
+        <x:v>3323821</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>22.736564248509</x:v>
+        <x:v>22.5501986521203</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>3253080</x:v>
+        <x:v>4112471</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>22.7332281103958</x:v>
+        <x:v>22.578824128832</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>5719179</x:v>
+        <x:v>7436292</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>3.23875593667921</x:v>
+        <x:v>3.26094177755692</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-786981</x:v>
+        <x:v>-788650</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>22.7227739229825</x:v>
+        <x:v>22.6994682176286</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2034,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>5520203</x:v>
+        <x:v>7201059</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>22.7139336787387</x:v>
+        <x:v>22.5511113366151</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>6374999</x:v>
+        <x:v>8087735</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>22.7400615431801</x:v>
+        <x:v>22.5877803320161</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>11895202</x:v>
+        <x:v>15288794</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>6.73622142190312</x:v>
+        <x:v>6.70439878948561</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-854796</x:v>
+        <x:v>-886676</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>22.9087931653131</x:v>
+        <x:v>22.8855842641783</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2063,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>872868</x:v>
+        <x:v>9964078</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>22.6775779544196</x:v>
+        <x:v>22.5202757209494</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>2117093</x:v>
+        <x:v>11150133</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>22.4256507135542</x:v>
+        <x:v>22.4217753230358</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>2989961</x:v>
+        <x:v>21114211</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>1.69320700387054</x:v>
+        <x:v>9.25894420902942</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1244225</x:v>
+        <x:v>-1186055</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>22.2489148121861</x:v>
+        <x:v>21.5942709932693</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2092,28 +2095,57 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>5820430</x:v>
+        <x:v>7726702</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>22.7807035082441</x:v>
+        <x:v>22.5881441879436</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>7453189</x:v>
+        <x:v>9008718</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>22.7730914646961</x:v>
+        <x:v>22.6412866574258</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>13273619</x:v>
+        <x:v>16735420</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>7.51681532217614</x:v>
+        <x:v>7.33876913964131</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-1632759</x:v>
+        <x:v>-1282016</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>22.7459561883767</x:v>
+        <x:v>22.9615759714697</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:9">
+      <x:c r="A55" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B55" s="0">
+        <x:v>1045444</x:v>
+      </x:c>
+      <x:c r="C55" s="0">
+        <x:v>22.565931620566</x:v>
+      </x:c>
+      <x:c r="D55" s="0">
+        <x:v>3033284</x:v>
+      </x:c>
+      <x:c r="E55" s="0">
+        <x:v>22.2936296655842</x:v>
+      </x:c>
+      <x:c r="F55" s="0">
+        <x:v>4078728</x:v>
+      </x:c>
+      <x:c r="G55" s="0">
+        <x:v>1.78859228961036</x:v>
+      </x:c>
+      <x:c r="H55" s="0">
+        <x:v>-1987840</x:v>
+      </x:c>
+      <x:c r="I55" s="0">
+        <x:v>22.1504207327607</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,166 +40,148 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUPAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -550,7 +532,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I55"/>
+  <x:dimension ref="A1:I49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -587,28 +569,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>7763675</x:v>
+        <x:v>410317</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>22.5084162464794</x:v>
+        <x:v>21.7277769547508</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>6244124</x:v>
+        <x:v>154969</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>22.6151554069604</x:v>
+        <x:v>21.8069308057267</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>14007799</x:v>
+        <x:v>565286</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>6.14266047792636</x:v>
+        <x:v>8.3141493765925</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1519551</x:v>
+        <x:v>255348</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>22.0698047397256</x:v>
+        <x:v>21.6797390099387</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +598,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>10016302</x:v>
+        <x:v>349202</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>22.5464000616861</x:v>
+        <x:v>21.8611457350068</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>8777165</x:v>
+        <x:v>123396</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>22.5543007209994</x:v>
+        <x:v>21.8114865108836</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>18793467</x:v>
+        <x:v>472598</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>8.24125810087034</x:v>
+        <x:v>6.9509069162846</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1239137</x:v>
+        <x:v>225806</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>22.4904374115498</x:v>
+        <x:v>21.8882829661695</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +627,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>13983928</x:v>
+        <x:v>298293</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>22.623071525579</x:v>
+        <x:v>21.785773448005</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>13203351</x:v>
+        <x:v>118947</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>22.6438310404512</x:v>
+        <x:v>21.7935309382635</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>27187279</x:v>
+        <x:v>417240</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>11.9220888460534</x:v>
+        <x:v>6.13670900374227</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>780577</x:v>
+        <x:v>179346</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>22.2719272291827</x:v>
+        <x:v>21.7806284757515</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +656,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>2526435</x:v>
+        <x:v>501903</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>22.5917709357562</x:v>
+        <x:v>21.8483885877568</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1946516</x:v>
+        <x:v>416441</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>22.5821010144856</x:v>
+        <x:v>21.8175314419693</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>4472951</x:v>
+        <x:v>918344</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.96146584680443</x:v>
+        <x:v>13.5068782794859</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>579919</x:v>
+        <x:v>85462</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>22.6242283245843</x:v>
+        <x:v>21.9987499255317</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +685,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>1926616</x:v>
+        <x:v>66919</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>22.525740312948</x:v>
+        <x:v>21.7410909317266</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1496621</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>22.5678053449994</x:v>
+        <x:v>21.8727013026514</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>3423237</x:v>
+        <x:v>69399</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.50114822653261</x:v>
+        <x:v>1.02071102519104</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>429995</x:v>
+        <x:v>64439</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>22.3793306795014</x:v>
+        <x:v>21.7360257736718</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +714,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>4174910</x:v>
+        <x:v>50438</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>22.5573911202111</x:v>
+        <x:v>21.8390339762097</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>3753800</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>22.591639388113</x:v>
+        <x:v>21.920941251867</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>7928710</x:v>
+        <x:v>58938</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.47687552897779</x:v>
+        <x:v>0.866852064189823</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>421110</x:v>
+        <x:v>41938</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>22.2520999895086</x:v>
+        <x:v>21.8224329975486</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +743,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>4285104</x:v>
+        <x:v>92572</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>22.5592068949721</x:v>
+        <x:v>21.8417326994313</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>3933162</x:v>
+        <x:v>51670</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>22.6333447261457</x:v>
+        <x:v>21.8181374444476</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>8218266</x:v>
+        <x:v>144242</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>3.60385080877346</x:v>
+        <x:v>2.12149165975887</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>351942</x:v>
+        <x:v>40902</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>21.7306723627643</x:v>
+        <x:v>21.8715397217042</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +772,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>1623963</x:v>
+        <x:v>136697</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>22.7251667091218</x:v>
+        <x:v>21.8412332834712</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1369220</x:v>
+        <x:v>98826</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>22.6476091007547</x:v>
+        <x:v>21.820764996876</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>2993183</x:v>
+        <x:v>235523</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.31256216035803</x:v>
+        <x:v>3.46404015599748</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>254743</x:v>
+        <x:v>37871</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>23.1420316613619</x:v>
+        <x:v>21.8946461558817</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +801,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1009213</x:v>
+        <x:v>25513</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>22.6043762294675</x:v>
+        <x:v>21.78945766581</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>776533</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>22.7728089729463</x:v>
+        <x:v>21.8799991607666</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1785746</x:v>
+        <x:v>25667</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.783080295327988</x:v>
+        <x:v>0.377506734730737</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>232680</x:v>
+        <x:v>25359</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.0422583697812</x:v>
+        <x:v>21.7889078259022</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +830,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>8664543</x:v>
+        <x:v>30978</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>22.6839802101104</x:v>
+        <x:v>21.7608394978068</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>8443974</x:v>
+        <x:v>5964</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>22.6534409861221</x:v>
+        <x:v>21.903182392389</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>17108517</x:v>
+        <x:v>36942</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>7.50237858294735</x:v>
+        <x:v>0.543337896693143</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>220569</x:v>
+        <x:v>25014</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.8531037648121</x:v>
+        <x:v>21.7269011823319</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +859,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>213000</x:v>
+        <x:v>30475</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>23.0657281920384</x:v>
+        <x:v>21.8036119267352</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>14145</x:v>
+        <x:v>10397</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>22.1191807622495</x:v>
+        <x:v>21.7747075357058</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>227145</x:v>
+        <x:v>40872</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0996069842420343</x:v>
+        <x:v>0.601139800596669</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>198855</x:v>
+        <x:v>20078</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>23.13305822344</x:v>
+        <x:v>21.8185795008726</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +888,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>540011</x:v>
+        <x:v>55022</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>22.5280776792043</x:v>
+        <x:v>21.7900177421887</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>347426</x:v>
+        <x:v>35050</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>22.6941135110564</x:v>
+        <x:v>21.8885590795171</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>887437</x:v>
+        <x:v>90072</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.38915636828809</x:v>
+        <x:v>1.32476668915989</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>192585</x:v>
+        <x:v>19972</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>22.2285467452423</x:v>
+        <x:v>21.6170819383954</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +917,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>972945</x:v>
+        <x:v>19099</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>22.3731966645677</x:v>
+        <x:v>21.7448843118065</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>828755</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>22.2985971652748</x:v>
+        <x:v>21.8984143526438</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1801700</x:v>
+        <x:v>20512</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.790076398374929</x:v>
+        <x:v>0.301687697931074</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>144190</x:v>
+        <x:v>17686</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>22.8019691733168</x:v>
+        <x:v>21.7326182285936</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +946,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>1408138</x:v>
+        <x:v>266139</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>22.6050253860844</x:v>
+        <x:v>21.8239120124502</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>1270312</x:v>
+        <x:v>249336</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>22.6447373868575</x:v>
+        <x:v>21.7998924119206</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>2678450</x:v>
+        <x:v>515475</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>1.17454633358902</x:v>
+        <x:v>7.58153598337658</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>137826</x:v>
+        <x:v>16803</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>22.2390085886288</x:v>
+        <x:v>22.1803335513216</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +975,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>607276</x:v>
+        <x:v>43938</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>22.4662594509035</x:v>
+        <x:v>21.8271338098489</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>472302</x:v>
+        <x:v>29002</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>22.6645281708161</x:v>
+        <x:v>21.787372602133</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>1079578</x:v>
+        <x:v>72940</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.473413497255264</x:v>
+        <x:v>1.07279157015857</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>134974</x:v>
+        <x:v>14936</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>21.7724761077993</x:v>
+        <x:v>21.9043401934977</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1004,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>315037</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>22.5103449115488</x:v>
+        <x:v>21.7932370323768</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>185921</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>22.7057598554285</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>500958</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.219678688115173</x:v>
+        <x:v>0.0956011133264422</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>129116</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.2289565338027</x:v>
+        <x:v>21.7932370323768</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1033,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>471663</x:v>
+        <x:v>10866</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>22.3630045320951</x:v>
+        <x:v>21.8302815395364</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>384326</x:v>
+        <x:v>5629</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>22.262377434795</x:v>
+        <x:v>21.8646579111506</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>855989</x:v>
+        <x:v>16495</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.375365880095775</x:v>
+        <x:v>0.242606209895333</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>87337</x:v>
+        <x:v>5237</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.805813533972</x:v>
+        <x:v>21.7933320272554</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1062,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>87835</x:v>
+        <x:v>4242</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>22.4726620204272</x:v>
+        <x:v>21.8450723852205</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>11964</x:v>
+        <x:v>2105</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>22.5291574808795</x:v>
+        <x:v>21.740987786771</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>99799</x:v>
+        <x:v>6347</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0437635757792194</x:v>
+        <x:v>0.0933508101973736</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>75871</x:v>
+        <x:v>2137</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>22.4637533242343</x:v>
+        <x:v>21.9475983935201</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1091,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>48192</x:v>
+        <x:v>18063</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>22.2406322682996</x:v>
+        <x:v>21.8496844621088</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>10362</x:v>
+        <x:v>16839</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>22.5083230180046</x:v>
+        <x:v>21.8436883766342</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>58554</x:v>
+        <x:v>34902</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0256769348007135</x:v>
+        <x:v>0.513333854972229</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>37830</x:v>
+        <x:v>1224</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.167309203313</x:v>
+        <x:v>21.9321747262493</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1120,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>54780</x:v>
+        <x:v>31420</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>22.8080586079308</x:v>
+        <x:v>21.8100192557468</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>18363</x:v>
+        <x:v>30420</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>22.608380011326</x:v>
+        <x:v>21.8056249579656</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>73143</x:v>
+        <x:v>61840</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0320744619006147</x:v>
+        <x:v>0.909534284324182</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>36417</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.9087450474907</x:v>
+        <x:v>21.9436937942505</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1149,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>328411</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>22.1612751385598</x:v>
+        <x:v>21.8999996185303</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>303067</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>22.1426438905561</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>631478</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.276913950098798</x:v>
+        <x:v>0.0136783131374756</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>25344</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>22.3840701369324</x:v>
+        <x:v>21.8999996185303</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1178,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>201568</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>22.6147029363914</x:v>
+        <x:v>21.8199996948242</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>177506</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>22.6419172028349</x:v>
+        <x:v>21.7600002288818</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>379074</x:v>
+        <x:v>1147</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.166230460474873</x:v>
+        <x:v>0.0168699195362199</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>24062</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>22.4139425848282</x:v>
+        <x:v>21.8303395793418</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1207,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>40601</x:v>
+        <x:v>991</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>22.4334798831047</x:v>
+        <x:v>21.7007272953222</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>17305</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>22.1402417896869</x:v>
+        <x:v>21.8799991607666</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>57906</x:v>
+        <x:v>1281</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0253927756698111</x:v>
+        <x:v>0.0188407732571035</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>23296</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>22.6513063428657</x:v>
+        <x:v>21.626563470816</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1236,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>1241334</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>22.7164596484819</x:v>
+        <x:v>21.8319995880127</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>1220302</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>22.6987025868411</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>2461636</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>1.07946967030586</x:v>
+        <x:v>0.00735393179434171</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>21032</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.7467457760237</x:v>
+        <x:v>21.8319995880127</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1265,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>26876</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>22.6904195488023</x:v>
+        <x:v>21.8799991607666</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>8180</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>23.2055496924664</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>35056</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.015372658168081</x:v>
+        <x:v>0.00735393179434171</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>18696</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>22.4650363344691</x:v>
+        <x:v>21.8799991607666</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1294,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>17220</x:v>
+        <x:v>105113</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>22.0456694289505</x:v>
+        <x:v>21.8007171549712</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>0</x:v>
+        <x:v>104936</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>0</x:v>
+        <x:v>21.8153929957222</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>17220</x:v>
+        <x:v>210049</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00755126579342636</x:v>
+        <x:v>3.08937203893936</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>17220</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>22.0456694289505</x:v>
+        <x:v>13.1000164484574</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1323,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>889798</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>22.9081790366374</x:v>
+        <x:v>21.7644437154134</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>874587</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>22.902040623166</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1764385</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.773713129903285</x:v>
+        <x:v>0.00105896617838521</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>15211</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.2611194496739</x:v>
+        <x:v>21.7644437154134</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1352,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>2171436</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>22.4120238976948</x:v>
+        <x:v>21.75</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>2160706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>22.4010100459461</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4332142</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>1.89971868158337</x:v>
+        <x:v>0.000294157271773668</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>10730</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.6298892804205</x:v>
+        <x:v>21.75</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1381,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>50000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>22.1399993896484</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>40290</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>21.9464795583411</x:v>
+        <x:v>21.8600006103516</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>90290</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0395937159400968</x:v>
+        <x:v>0.00211793235677041</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>9710</x:v>
+        <x:v>-144</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>22.9429771448876</x:v>
+        <x:v>21.8600006103516</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1410,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>230799</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>22.6370757894019</x:v>
+        <x:v>21.8463750519728</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>224831</x:v>
+        <x:v>1214</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>22.4474880107915</x:v>
+        <x:v>21.8506417753669</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>455630</x:v>
+        <x:v>2199</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.199801581501676</x:v>
+        <x:v>0.0323425920315148</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>5968</x:v>
+        <x:v>-229</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>29.7793696655345</x:v>
+        <x:v>21.8689942755553</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1439,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>5131</x:v>
+        <x:v>1325</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>21.8999996185303</x:v>
+        <x:v>21.8603766459339</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>0</x:v>
+        <x:v>1580</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>0</x:v>
+        <x:v>21.924050101751</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>5131</x:v>
+        <x:v>2905</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00225003163682176</x:v>
+        <x:v>0.0427263437251253</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>5131</x:v>
+        <x:v>-255</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>21.8999996185303</x:v>
+        <x:v>22.2549023721732</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1468,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>4189</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>22.7023441535984</x:v>
+        <x:v>21.8699573293391</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>2280</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>22.603403786609</x:v>
+        <x:v>21.8097996661183</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>6469</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00283676762007405</x:v>
+        <x:v>0.0195173349821829</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>1909</x:v>
+        <x:v>-371</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>22.8205128475407</x:v>
+        <x:v>21.7322919490845</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1497,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>2494</x:v>
+        <x:v>1474</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>22.9058538725975</x:v>
+        <x:v>21.7576120989941</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>1068</x:v>
+        <x:v>6509</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>22.0706552351905</x:v>
+        <x:v>21.8176243111439</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>3562</x:v>
+        <x:v>7983</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00156199818560887</x:v>
+        <x:v>0.11741287502846</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1426</x:v>
+        <x:v>-5035</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>23.5313743107115</x:v>
+        <x:v>21.835192930947</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1526,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>1137</x:v>
+        <x:v>1781</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>22.0901312312224</x:v>
+        <x:v>21.755923935699</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>137</x:v>
+        <x:v>9500</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>22.7800006866455</x:v>
+        <x:v>21.7423575857062</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>1274</x:v>
+        <x:v>11281</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000558670883903902</x:v>
+        <x:v>0.165919409143938</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>1000</x:v>
+        <x:v>-7719</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>21.9956191158295</x:v>
+        <x:v>21.7392274303315</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1555,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>2004747</x:v>
+        <x:v>10670</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>22.8903219953437</x:v>
+        <x:v>21.8628766579168</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>2010895</x:v>
+        <x:v>19240</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>22.8451150316462</x:v>
+        <x:v>21.8028998429463</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>4015642</x:v>
+        <x:v>29910</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>1.76092799496203</x:v>
+        <x:v>0.439912199937521</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-6148</x:v>
+        <x:v>-8570</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>8.10397566086143</x:v>
+        <x:v>21.7282262588465</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1584,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>29210</x:v>
+        <x:v>11160</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>22.6492676099903</x:v>
+        <x:v>21.8169532331515</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>37602</x:v>
+        <x:v>21102</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>22.3582797582831</x:v>
+        <x:v>21.8156758814488</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>66812</x:v>
+        <x:v>32262</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.0292982096510106</x:v>
+        <x:v>0.474505095098104</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-8392</x:v>
+        <x:v>-9942</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.3454395356465</x:v>
+        <x:v>21.8142420406721</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1613,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>411792</x:v>
+        <x:v>12696</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>22.7892981420082</x:v>
+        <x:v>21.84415523752</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>420391</x:v>
+        <x:v>26061</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>22.6771077268498</x:v>
+        <x:v>21.7927372329622</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>832183</x:v>
+        <x:v>38757</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.364926540172528</x:v>
+        <x:v>0.570032669106603</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-8599</x:v>
+        <x:v>-13365</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>17.3044928368725</x:v>
+        <x:v>21.7438930140423</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1642,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>1363812</x:v>
+        <x:v>19849</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>22.4810456283472</x:v>
+        <x:v>21.9108448512873</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>1373415</x:v>
+        <x:v>45198</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>22.4985407160772</x:v>
+        <x:v>21.8274678583456</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>2737227</x:v>
+        <x:v>65047</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>1.20032105772027</x:v>
+        <x:v>0.95670240285309</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-9603</x:v>
+        <x:v>-25349</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>24.9831820351623</x:v>
+        <x:v>21.7621812619158</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1671,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>1070428</x:v>
+        <x:v>56974</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>22.4157520042673</x:v>
+        <x:v>21.7882204167266</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>1091479</x:v>
+        <x:v>83762</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>22.4353390110021</x:v>
+        <x:v>21.8027805364029</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>2161907</x:v>
+        <x:v>140736</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.948033355265331</x:v>
+        <x:v>2.06992589001695</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-21051</x:v>
+        <x:v>-26788</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>23.431324020983</x:v>
+        <x:v>21.8337476955201</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1700,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>321621</x:v>
+        <x:v>3329</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>22.6311606854085</x:v>
+        <x:v>21.8799510983312</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>350832</x:v>
+        <x:v>34696</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>22.6406162553378</x:v>
+        <x:v>21.7531919843292</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>672453</x:v>
+        <x:v>38025</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.294882191439427</x:v>
+        <x:v>0.559266512959687</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-29211</x:v>
+        <x:v>-31367</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>22.7447246342437</x:v>
+        <x:v>21.739738957565</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1729,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>251736</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>22.454393683146</x:v>
+        <x:v>21.8161901746477</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>289695</x:v>
+        <x:v>35075</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>22.4915008003455</x:v>
+        <x:v>21.9623669128527</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>541431</x:v>
+        <x:v>37175</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.237426793832789</x:v>
+        <x:v>0.546764828909306</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-37959</x:v>
+        <x:v>-32975</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>22.7375872951246</x:v>
+        <x:v>21.9716761213509</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1758,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>344669</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>22.5747547534151</x:v>
+        <x:v>21.8534755785455</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>383068</x:v>
+        <x:v>37292</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>22.5201485868656</x:v>
+        <x:v>21.8809422481013</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>727737</x:v>
+        <x:v>39959</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.319125175070309</x:v>
+        <x:v>0.587711521140201</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-38399</x:v>
+        <x:v>-34625</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>22.0300042388768</x:v>
+        <x:v>21.8830578757606</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1787,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>649353</x:v>
+        <x:v>36316</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>22.602827832292</x:v>
+        <x:v>21.8221810759263</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>707615</x:v>
+        <x:v>73379</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>22.5377573341384</x:v>
+        <x:v>21.8343201391906</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>1356968</x:v>
+        <x:v>109695</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.595053777071672</x:v>
+        <x:v>1.61337909636063</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-58262</x:v>
+        <x:v>-37063</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>21.8125209332675</x:v>
+        <x:v>21.8462145411955</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1816,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>202399</x:v>
+        <x:v>96240</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>22.2899619225415</x:v>
+        <x:v>21.8455581476167</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>274878</x:v>
+        <x:v>163844</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>22.3018215516798</x:v>
+        <x:v>21.8213529058047</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>477277</x:v>
+        <x:v>260084</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.209294162839091</x:v>
+        <x:v>3.82527999359914</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-72479</x:v>
+        <x:v>-67604</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>22.3349397939013</x:v>
+        <x:v>21.7868947010831</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1845,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>1672251</x:v>
+        <x:v>201997</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>22.7767722659056</x:v>
+        <x:v>21.8606433334437</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>1751987</x:v>
+        <x:v>273922</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>22.7257125580017</x:v>
+        <x:v>21.8036929564697</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>3424238</x:v>
+        <x:v>475919</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.5015871822271</x:v>
+        <x:v>6.99975173126262</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-79736</x:v>
+        <x:v>-71925</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>21.6548706847949</x:v>
+        <x:v>21.6437512769755</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1874,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>176618</x:v>
+        <x:v>41360</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>22.6649540712402</x:v>
+        <x:v>21.8614968413311</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>304971</x:v>
+        <x:v>179494</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>22.6465086540231</x:v>
+        <x:v>21.8097659384787</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>481589</x:v>
+        <x:v>220854</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.211185048907689</x:v>
+        <x:v>3.24829050501509</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-128353</x:v>
+        <x:v>-138134</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>22.6211271460098</x:v>
+        <x:v>21.7942767023604</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1903,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>4149575</x:v>
+        <x:v>251122</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>22.6034110776536</x:v>
+        <x:v>21.8095664727002</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4306631</x:v>
+        <x:v>426521</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>22.5952253129712</x:v>
+        <x:v>21.8215512305369</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>8456206</x:v>
+        <x:v>677643</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>3.70819158594464</x:v>
+        <x:v>9.9666808058262</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-157056</x:v>
+        <x:v>-175399</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>22.3789493064377</x:v>
+        <x:v>21.8387100305155</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,202 +1932,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>2999519</x:v>
+        <x:v>89297</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>22.7948268852102</x:v>
+        <x:v>21.8095850460991</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>3250464</x:v>
+        <x:v>493249</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>22.7767776602041</x:v>
+        <x:v>21.8133035217311</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>6249983</x:v>
+        <x:v>582546</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>2.74072490344926</x:v>
+        <x:v>8.56800710213317</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-250945</x:v>
+        <x:v>-403952</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>22.5610371858325</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:9">
-      <x:c r="A50" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B50" s="0">
-        <x:v>3207225</x:v>
-      </x:c>
-      <x:c r="C50" s="0">
-        <x:v>22.6568383791197</x:v>
-      </x:c>
-      <x:c r="D50" s="0">
-        <x:v>3555754</x:v>
-      </x:c>
-      <x:c r="E50" s="0">
-        <x:v>22.6738518570024</x:v>
-      </x:c>
-      <x:c r="F50" s="0">
-        <x:v>6762979</x:v>
-      </x:c>
-      <x:c r="G50" s="0">
-        <x:v>2.965682461345</x:v>
-      </x:c>
-      <x:c r="H50" s="0">
-        <x:v>-348529</x:v>
-      </x:c>
-      <x:c r="I50" s="0">
-        <x:v>22.8304128651311</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:9">
-      <x:c r="A51" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B51" s="0">
-        <x:v>3323821</x:v>
-      </x:c>
-      <x:c r="C51" s="0">
-        <x:v>22.5501986521203</x:v>
-      </x:c>
-      <x:c r="D51" s="0">
-        <x:v>4112471</x:v>
-      </x:c>
-      <x:c r="E51" s="0">
-        <x:v>22.578824128832</x:v>
-      </x:c>
-      <x:c r="F51" s="0">
-        <x:v>7436292</x:v>
-      </x:c>
-      <x:c r="G51" s="0">
-        <x:v>3.26094177755692</x:v>
-      </x:c>
-      <x:c r="H51" s="0">
-        <x:v>-788650</x:v>
-      </x:c>
-      <x:c r="I51" s="0">
-        <x:v>22.6994682176286</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:9">
-      <x:c r="A52" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B52" s="0">
-        <x:v>7201059</x:v>
-      </x:c>
-      <x:c r="C52" s="0">
-        <x:v>22.5511113366151</x:v>
-      </x:c>
-      <x:c r="D52" s="0">
-        <x:v>8087735</x:v>
-      </x:c>
-      <x:c r="E52" s="0">
-        <x:v>22.5877803320161</x:v>
-      </x:c>
-      <x:c r="F52" s="0">
-        <x:v>15288794</x:v>
-      </x:c>
-      <x:c r="G52" s="0">
-        <x:v>6.70439878948561</x:v>
-      </x:c>
-      <x:c r="H52" s="0">
-        <x:v>-886676</x:v>
-      </x:c>
-      <x:c r="I52" s="0">
-        <x:v>22.8855842641783</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:9">
-      <x:c r="A53" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B53" s="0">
-        <x:v>9964078</x:v>
-      </x:c>
-      <x:c r="C53" s="0">
-        <x:v>22.5202757209494</x:v>
-      </x:c>
-      <x:c r="D53" s="0">
-        <x:v>11150133</x:v>
-      </x:c>
-      <x:c r="E53" s="0">
-        <x:v>22.4217753230358</x:v>
-      </x:c>
-      <x:c r="F53" s="0">
-        <x:v>21114211</x:v>
-      </x:c>
-      <x:c r="G53" s="0">
-        <x:v>9.25894420902942</x:v>
-      </x:c>
-      <x:c r="H53" s="0">
-        <x:v>-1186055</x:v>
-      </x:c>
-      <x:c r="I53" s="0">
-        <x:v>21.5942709932693</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:9">
-      <x:c r="A54" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B54" s="0">
-        <x:v>7726702</x:v>
-      </x:c>
-      <x:c r="C54" s="0">
-        <x:v>22.5881441879436</x:v>
-      </x:c>
-      <x:c r="D54" s="0">
-        <x:v>9008718</x:v>
-      </x:c>
-      <x:c r="E54" s="0">
-        <x:v>22.6412866574258</x:v>
-      </x:c>
-      <x:c r="F54" s="0">
-        <x:v>16735420</x:v>
-      </x:c>
-      <x:c r="G54" s="0">
-        <x:v>7.33876913964131</x:v>
-      </x:c>
-      <x:c r="H54" s="0">
-        <x:v>-1282016</x:v>
-      </x:c>
-      <x:c r="I54" s="0">
-        <x:v>22.9615759714697</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:9">
-      <x:c r="A55" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B55" s="0">
-        <x:v>1045444</x:v>
-      </x:c>
-      <x:c r="C55" s="0">
-        <x:v>22.565931620566</x:v>
-      </x:c>
-      <x:c r="D55" s="0">
-        <x:v>3033284</x:v>
-      </x:c>
-      <x:c r="E55" s="0">
-        <x:v>22.2936296655842</x:v>
-      </x:c>
-      <x:c r="F55" s="0">
-        <x:v>4078728</x:v>
-      </x:c>
-      <x:c r="G55" s="0">
-        <x:v>1.78859228961036</x:v>
-      </x:c>
-      <x:c r="H55" s="0">
-        <x:v>-1987840</x:v>
-      </x:c>
-      <x:c r="I55" s="0">
-        <x:v>22.1504207327607</x:v>
+        <x:v>21.8141255221632</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,148 +40,166 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
   </x:si>
   <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
+    <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -532,7 +550,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I49"/>
+  <x:dimension ref="A1:I55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -569,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>410317</x:v>
+        <x:v>666617</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>21.7277769547508</x:v>
+        <x:v>21.718</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>154969</x:v>
+        <x:v>304694</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>21.8069308057267</x:v>
+        <x:v>21.942</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>565286</x:v>
+        <x:v>971311</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>8.3141493765925</x:v>
+        <x:v>1.59207602592427</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>255348</x:v>
+        <x:v>361923</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>21.6797390099387</x:v>
+        <x:v>21.53</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -598,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>349202</x:v>
+        <x:v>1027115</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>21.8611457350068</x:v>
+        <x:v>21.761</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>123396</x:v>
+        <x:v>711496</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>21.8114865108836</x:v>
+        <x:v>21.829</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>472598</x:v>
+        <x:v>1738611</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>6.9509069162846</x:v>
+        <x:v>2.84975758691935</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>225806</x:v>
+        <x:v>315619</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>21.8882829661695</x:v>
+        <x:v>21.609</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -627,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>298293</x:v>
+        <x:v>2616675</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>21.785773448005</x:v>
+        <x:v>21.838</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>118947</x:v>
+        <x:v>2335212</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>21.7935309382635</x:v>
+        <x:v>21.86</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>417240</x:v>
+        <x:v>4951887</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>6.13670900374227</x:v>
+        <x:v>8.11663882709663</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>179346</x:v>
+        <x:v>281463</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>21.7806284757515</x:v>
+        <x:v>21.662</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -656,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>501903</x:v>
+        <x:v>2902045</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>21.8483885877568</x:v>
+        <x:v>21.815</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>416441</x:v>
+        <x:v>2650616</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>21.8175314419693</x:v>
+        <x:v>21.773</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>918344</x:v>
+        <x:v>5552661</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>13.5068782794859</x:v>
+        <x:v>9.10136759306204</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>85462</x:v>
+        <x:v>251429</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>21.9987499255317</x:v>
+        <x:v>22.248</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -685,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>66919</x:v>
+        <x:v>356276</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>21.7410909317266</x:v>
+        <x:v>21.867</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>2480</x:v>
+        <x:v>131411</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>21.8727013026514</x:v>
+        <x:v>21.955</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>69399</x:v>
+        <x:v>487687</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.02071102519104</x:v>
+        <x:v>0.799367844958957</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>64439</x:v>
+        <x:v>224865</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>21.7360257736718</x:v>
+        <x:v>21.815</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -714,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>50438</x:v>
+        <x:v>1585035</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>21.8390339762097</x:v>
+        <x:v>21.771</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>8500</x:v>
+        <x:v>1455154</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>21.920941251867</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>58938</x:v>
+        <x:v>3040189</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.866852064189823</x:v>
+        <x:v>4.9831743089275</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>41938</x:v>
+        <x:v>129881</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>21.8224329975486</x:v>
+        <x:v>21.443</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -743,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>92572</x:v>
+        <x:v>736889</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>21.8417326994313</x:v>
+        <x:v>21.755</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>51670</x:v>
+        <x:v>643796</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>21.8181374444476</x:v>
+        <x:v>21.749</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>144242</x:v>
+        <x:v>1380685</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.12149165975887</x:v>
+        <x:v>2.26308101921347</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>40902</x:v>
+        <x:v>93093</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>21.8715397217042</x:v>
+        <x:v>21.795</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -772,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>136697</x:v>
+        <x:v>403851</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>21.8412332834712</x:v>
+        <x:v>21.805</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>98826</x:v>
+        <x:v>318951</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>21.820764996876</x:v>
+        <x:v>21.828</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>235523</x:v>
+        <x:v>722802</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>3.46404015599748</x:v>
+        <x:v>1.18474488159829</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>37871</x:v>
+        <x:v>84900</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>21.8946461558817</x:v>
+        <x:v>21.721</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -801,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>25513</x:v>
+        <x:v>126001</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>21.78945766581</x:v>
+        <x:v>21.784</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>154</x:v>
+        <x:v>55001</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>21.8799991607666</x:v>
+        <x:v>21.849</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>25667</x:v>
+        <x:v>181002</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.377506734730737</x:v>
+        <x:v>0.296680409101045</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>25359</x:v>
+        <x:v>71000</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>21.7889078259022</x:v>
+        <x:v>21.734</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -830,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>30978</x:v>
+        <x:v>622692</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>21.7608394978068</x:v>
+        <x:v>21.789</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>5964</x:v>
+        <x:v>559597</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>21.903182392389</x:v>
+        <x:v>21.82</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>36942</x:v>
+        <x:v>1182289</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.543337896693143</x:v>
+        <x:v>1.93789010174288</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>25014</x:v>
+        <x:v>63095</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>21.7269011823319</x:v>
+        <x:v>21.51</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -859,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>30475</x:v>
+        <x:v>208920</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>21.8036119267352</x:v>
+        <x:v>21.798</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>10397</x:v>
+        <x:v>151609</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>21.7747075357058</x:v>
+        <x:v>21.778</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>40872</x:v>
+        <x:v>360529</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.601139800596669</x:v>
+        <x:v>0.590943145450274</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>20078</x:v>
+        <x:v>57311</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>21.8185795008726</x:v>
+        <x:v>21.851</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -888,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>55022</x:v>
+        <x:v>1168263</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>21.7900177421887</x:v>
+        <x:v>21.835</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>35050</x:v>
+        <x:v>1121389</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>21.8885590795171</x:v>
+        <x:v>21.744</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>90072</x:v>
+        <x:v>2289652</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.32476668915989</x:v>
+        <x:v>3.75296898409424</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>19972</x:v>
+        <x:v>46874</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>21.6170819383954</x:v>
+        <x:v>24.006</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -917,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>19099</x:v>
+        <x:v>238904</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>21.7448843118065</x:v>
+        <x:v>21.792</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1413</x:v>
+        <x:v>194310</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>21.8984143526438</x:v>
+        <x:v>21.939</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>20512</x:v>
+        <x:v>433214</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.301687697931074</x:v>
+        <x:v>0.710081141359211</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>17686</x:v>
+        <x:v>44594</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>21.7326182285936</x:v>
+        <x:v>21.153</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -946,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>266139</x:v>
+        <x:v>396003</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>21.8239120124502</x:v>
+        <x:v>21.78</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>249336</x:v>
+        <x:v>351444</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>21.7998924119206</x:v>
+        <x:v>21.892</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>515475</x:v>
+        <x:v>747447</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>7.58153598337658</x:v>
+        <x:v>1.22514050530573</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>16803</x:v>
+        <x:v>44559</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>22.1803335513216</x:v>
+        <x:v>20.898</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -975,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>43938</x:v>
+        <x:v>138113</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>21.8271338098489</x:v>
+        <x:v>21.909</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>29002</x:v>
+        <x:v>106482</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>21.787372602133</x:v>
+        <x:v>21.787</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>72940</x:v>
+        <x:v>244595</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>1.07279157015857</x:v>
+        <x:v>0.400915706257776</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>14936</x:v>
+        <x:v>31631</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>21.9043401934977</x:v>
+        <x:v>22.317</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1004,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>6500</x:v>
+        <x:v>319085</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>21.7932370323768</x:v>
+        <x:v>21.671</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>0</x:v>
+        <x:v>291802</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>0</x:v>
+        <x:v>21.777</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>6500</x:v>
+        <x:v>610887</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0956011133264422</x:v>
+        <x:v>1.00130498599192</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>6500</x:v>
+        <x:v>27283</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>21.7932370323768</x:v>
+        <x:v>20.534</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1033,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>10866</x:v>
+        <x:v>748564</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>21.8302815395364</x:v>
+        <x:v>21.848</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>5629</x:v>
+        <x:v>725034</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>21.8646579111506</x:v>
+        <x:v>21.831</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>16495</x:v>
+        <x:v>1473598</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.242606209895333</x:v>
+        <x:v>2.41537473337577</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>5237</x:v>
+        <x:v>23530</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>21.7933320272554</x:v>
+        <x:v>22.392</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1062,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>4242</x:v>
+        <x:v>182964</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>21.8450723852205</x:v>
+        <x:v>21.848</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>2105</x:v>
+        <x:v>160949</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>21.740987786771</x:v>
+        <x:v>21.863</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>6347</x:v>
+        <x:v>343913</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0933508101973736</x:v>
+        <x:v>0.563707857013556</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>2137</x:v>
+        <x:v>22015</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>21.9475983935201</x:v>
+        <x:v>21.743</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1091,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>18063</x:v>
+        <x:v>42957</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>21.8496844621088</x:v>
+        <x:v>21.827</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>16839</x:v>
+        <x:v>23289</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>21.8436883766342</x:v>
+        <x:v>21.875</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>34902</x:v>
+        <x:v>66246</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.513333854972229</x:v>
+        <x:v>0.108583829909657</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>1224</x:v>
+        <x:v>19668</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>21.9321747262493</x:v>
+        <x:v>21.769</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1120,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>31420</x:v>
+        <x:v>10441</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>21.8100192557468</x:v>
+        <x:v>21.78</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>30420</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>21.8056249579656</x:v>
+        <x:v>21.763</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>61840</x:v>
+        <x:v>10732</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.909534284324182</x:v>
+        <x:v>0.0175908230321898</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>1000</x:v>
+        <x:v>10150</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>21.9436937942505</x:v>
+        <x:v>21.781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1149,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>930</x:v>
+        <x:v>10238</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>21.8999996185303</x:v>
+        <x:v>21.734</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>0</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>0</x:v>
+        <x:v>21.743</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>930</x:v>
+        <x:v>10561</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0136783131374756</x:v>
+        <x:v>0.0173105369029963</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>930</x:v>
+        <x:v>9915</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>21.8999996185303</x:v>
+        <x:v>21.733</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1178,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>1000</x:v>
+        <x:v>5096</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>21.8199996948242</x:v>
+        <x:v>21.796</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>147</x:v>
+        <x:v>2095</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>21.7600002288818</x:v>
+        <x:v>21.827</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1147</x:v>
+        <x:v>7191</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0168699195362199</x:v>
+        <x:v>0.0117867693276627</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>853</x:v>
+        <x:v>3001</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>21.8303395793418</x:v>
+        <x:v>21.775</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1207,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>991</x:v>
+        <x:v>102342</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>21.7007272953222</x:v>
+        <x:v>21.699</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>290</x:v>
+        <x:v>99476</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>21.8799991607666</x:v>
+        <x:v>21.738</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1281</x:v>
+        <x:v>201818</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0188407732571035</x:v>
+        <x:v>0.330799918254796</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>701</x:v>
+        <x:v>2866</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>21.626563470816</x:v>
+        <x:v>20.341</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1236,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>500</x:v>
+        <x:v>3609446</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>21.8319995880127</x:v>
+        <x:v>21.775</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>0</x:v>
+        <x:v>3606828</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>0</x:v>
+        <x:v>21.815</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>500</x:v>
+        <x:v>7216274</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.00735393179434171</x:v>
+        <x:v>11.8281959453776</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>500</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>21.8319995880127</x:v>
+        <x:v>-32.278</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1265,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>500</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>21.8799991607666</x:v>
+        <x:v>21.64</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>0</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>0</x:v>
+        <x:v>21.693</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>500</x:v>
+        <x:v>2140</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00735393179434171</x:v>
+        <x:v>0.00350767436534533</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>500</x:v>
+        <x:v>1860</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>21.8799991607666</x:v>
+        <x:v>21.636</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1294,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>105113</x:v>
+        <x:v>56795</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>21.8007171549712</x:v>
+        <x:v>21.813</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>104936</x:v>
+        <x:v>56423</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>21.8153929957222</x:v>
+        <x:v>21.818</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>210049</x:v>
+        <x:v>113218</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>3.08937203893936</x:v>
+        <x:v>0.185575643128817</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>177</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>13.1000164484574</x:v>
+        <x:v>21.091</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1323,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>72</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>21.7644437154134</x:v>
+        <x:v>21.945</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>0</x:v>
+        <x:v>1763</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>0</x:v>
+        <x:v>21.643</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>72</x:v>
+        <x:v>3763</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00105896617838521</x:v>
+        <x:v>0.00616793394242733</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>72</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>21.7644437154134</x:v>
+        <x:v>24.194</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1352,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>20</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>21.75</x:v>
+        <x:v>21.821</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>0</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>0</x:v>
+        <x:v>21.728</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>20</x:v>
+        <x:v>5077</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.000294157271773668</x:v>
+        <x:v>0.00832171156675619</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>20</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>21.75</x:v>
+        <x:v>23.374</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1381,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>0</x:v>
+        <x:v>57089</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>0</x:v>
+        <x:v>21.707</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>144</x:v>
+        <x:v>56987</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>21.8600006103516</x:v>
+        <x:v>21.881</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>144</x:v>
+        <x:v>114076</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00211793235677041</x:v>
+        <x:v>0.186981991075296</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-144</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>21.8600006103516</x:v>
+        <x:v>-75.588</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1410,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>985</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>21.8463750519728</x:v>
+        <x:v>21.763</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1214</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>21.8506417753669</x:v>
+        <x:v>21.69</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>2199</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0323425920315148</x:v>
+        <x:v>0.000576963260094185</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-229</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>21.8689942755553</x:v>
+        <x:v>21.935</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1439,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1325</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>21.8603766459339</x:v>
+        <x:v>21.65</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1580</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>21.924050101751</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>2905</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0427263437251253</x:v>
+        <x:v>6.55640068288847E-05</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-255</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>22.2549023721732</x:v>
+        <x:v>21.65</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1468,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>478</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>21.8699573293391</x:v>
+        <x:v>21.5</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>849</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>21.8097996661183</x:v>
+        <x:v>21.58</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>1327</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0195173349821829</x:v>
+        <x:v>0.163910017072212</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-371</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>21.7322919490845</x:v>
+        <x:v>21.5</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1497,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>1474</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>21.7576120989941</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>6509</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>21.8176243111439</x:v>
+        <x:v>21.861</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>7983</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.11741287502846</x:v>
+        <x:v>0.000236030424583985</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-5035</x:v>
+        <x:v>-144</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>21.835192930947</x:v>
+        <x:v>21.861</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1526,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>1781</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>21.755923935699</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>9500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>21.7423575857062</x:v>
+        <x:v>22.1</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>11281</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.165919409143938</x:v>
+        <x:v>0.00163910017072212</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-7719</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>21.7392274303315</x:v>
+        <x:v>22.1</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1555,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>10670</x:v>
+        <x:v>16154</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>21.8628766579168</x:v>
+        <x:v>21.742</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>19240</x:v>
+        <x:v>17993</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>21.8028998429463</x:v>
+        <x:v>21.742</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>29910</x:v>
+        <x:v>34147</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.439912199937521</x:v>
+        <x:v>0.0559703535296481</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-8570</x:v>
+        <x:v>-1839</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>21.7282262588465</x:v>
+        <x:v>21.742</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1584,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>11160</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>21.8169532331515</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>21102</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>21.8156758814488</x:v>
+        <x:v>21.72</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>32262</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.474505095098104</x:v>
+        <x:v>0.00409775042680529</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-9942</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.8142420406721</x:v>
+        <x:v>21.72</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1613,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>12696</x:v>
+        <x:v>43788</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>21.84415523752</x:v>
+        <x:v>21.704</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>26061</x:v>
+        <x:v>47404</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>21.7927372329622</x:v>
+        <x:v>21.813</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>38757</x:v>
+        <x:v>91192</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.570032669106603</x:v>
+        <x:v>0.149472822768491</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-13365</x:v>
+        <x:v>-3616</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>21.7438930140423</x:v>
+        <x:v>23.132</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1642,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>19849</x:v>
+        <x:v>2043109</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>21.9108448512873</x:v>
+        <x:v>21.849</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>45198</x:v>
+        <x:v>2051004</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>21.8274678583456</x:v>
+        <x:v>21.854</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>65047</x:v>
+        <x:v>4094113</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.95670240285309</x:v>
+        <x:v>6.71066131725564</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-25349</x:v>
+        <x:v>-7895</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>21.7621812619158</x:v>
+        <x:v>23.184</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1671,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>56974</x:v>
+        <x:v>10329</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>21.7882204167266</x:v>
+        <x:v>21.766</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>83762</x:v>
+        <x:v>22909</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>21.8027805364029</x:v>
+        <x:v>21.805</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>140736</x:v>
+        <x:v>33238</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.06992589001695</x:v>
+        <x:v>0.0544804114744617</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-26788</x:v>
+        <x:v>-12580</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>21.8337476955201</x:v>
+        <x:v>21.838</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1700,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>3329</x:v>
+        <x:v>340562</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>21.8799510983312</x:v>
+        <x:v>21.889</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>34696</x:v>
+        <x:v>353524</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>21.7531919843292</x:v>
+        <x:v>21.942</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>38025</x:v>
+        <x:v>694086</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.559266512959687</x:v>
+        <x:v>1.13767648109583</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-31367</x:v>
+        <x:v>-12962</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>21.739738957565</x:v>
+        <x:v>23.331</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1729,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>2100</x:v>
+        <x:v>50911</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>21.8161901746477</x:v>
+        <x:v>21.779</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>35075</x:v>
+        <x:v>65150</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>21.9623669128527</x:v>
+        <x:v>21.818</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>37175</x:v>
+        <x:v>116061</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.546764828909306</x:v>
+        <x:v>0.19023560491418</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-32975</x:v>
+        <x:v>-14239</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>21.9716761213509</x:v>
+        <x:v>21.956</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1758,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>2667</x:v>
+        <x:v>236736</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>21.8534755785455</x:v>
+        <x:v>21.549</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>37292</x:v>
+        <x:v>257322</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>21.8809422481013</x:v>
+        <x:v>21.633</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>39959</x:v>
+        <x:v>494058</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.587711521140201</x:v>
+        <x:v>0.809810552146628</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-34625</x:v>
+        <x:v>-20586</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>21.8830578757606</x:v>
+        <x:v>22.599</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1787,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>36316</x:v>
+        <x:v>694071</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>21.8221810759263</x:v>
+        <x:v>21.718</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>73379</x:v>
+        <x:v>722716</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>21.8343201391906</x:v>
+        <x:v>21.754</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>109695</x:v>
+        <x:v>1416787</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.61337909636063</x:v>
+        <x:v>2.32225581357688</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-37063</x:v>
+        <x:v>-28645</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>21.8462145411955</x:v>
+        <x:v>22.627</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1816,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>96240</x:v>
+        <x:v>78314</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>21.8455581476167</x:v>
+        <x:v>21.748</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>163844</x:v>
+        <x:v>114060</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>21.8213529058047</x:v>
+        <x:v>21.77</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>260084</x:v>
+        <x:v>192374</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>3.82527999359914</x:v>
+        <x:v>0.315320256242497</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-67604</x:v>
+        <x:v>-35746</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>21.7868947010831</x:v>
+        <x:v>21.817</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1845,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>201997</x:v>
+        <x:v>40354</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>21.8606433334437</x:v>
+        <x:v>21.811</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>273922</x:v>
+        <x:v>104059</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>21.8036929564697</x:v>
+        <x:v>21.844</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>475919</x:v>
+        <x:v>144413</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>6.99975173126262</x:v>
+        <x:v>0.236707372954493</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-71925</x:v>
+        <x:v>-63705</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>21.6437512769755</x:v>
+        <x:v>21.865</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1874,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>41360</x:v>
+        <x:v>31388</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>21.8614968413311</x:v>
+        <x:v>21.711</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>179494</x:v>
+        <x:v>114660</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>21.8097659384787</x:v>
+        <x:v>21.694</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>220854</x:v>
+        <x:v>146048</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>3.24829050501509</x:v>
+        <x:v>0.239387301733624</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-138134</x:v>
+        <x:v>-83272</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>21.7942767023604</x:v>
+        <x:v>21.688</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1903,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>251122</x:v>
+        <x:v>1095216</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>21.8095664727002</x:v>
+        <x:v>21.794</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>426521</x:v>
+        <x:v>1193416</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>21.8215512305369</x:v>
+        <x:v>21.795</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>677643</x:v>
+        <x:v>2288632</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>9.9666808058262</x:v>
+        <x:v>3.7512971019201</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-175399</x:v>
+        <x:v>-98200</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>21.8387100305155</x:v>
+        <x:v>21.801</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1932,28 +1950,202 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>89297</x:v>
+        <x:v>87417</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>21.8095850460991</x:v>
+        <x:v>21.817</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>493249</x:v>
+        <x:v>198644</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>21.8133035217311</x:v>
+        <x:v>21.786</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>582546</x:v>
+        <x:v>286061</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>8.56800710213317</x:v>
+        <x:v>0.46888263393694</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-403952</x:v>
+        <x:v>-111227</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>21.8141255221632</x:v>
+        <x:v>21.761</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
+      <x:c r="A50" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B50" s="0">
+        <x:v>188890</x:v>
+      </x:c>
+      <x:c r="C50" s="0">
+        <x:v>21.743</x:v>
+      </x:c>
+      <x:c r="D50" s="0">
+        <x:v>344860</x:v>
+      </x:c>
+      <x:c r="E50" s="0">
+        <x:v>21.857</x:v>
+      </x:c>
+      <x:c r="F50" s="0">
+        <x:v>533750</x:v>
+      </x:c>
+      <x:c r="G50" s="0">
+        <x:v>0.87486971612293</x:v>
+      </x:c>
+      <x:c r="H50" s="0">
+        <x:v>-155970</x:v>
+      </x:c>
+      <x:c r="I50" s="0">
+        <x:v>21.995</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
+      <x:c r="A51" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B51" s="0">
+        <x:v>749221</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>21.755</x:v>
+      </x:c>
+      <x:c r="D51" s="0">
+        <x:v>949852</x:v>
+      </x:c>
+      <x:c r="E51" s="0">
+        <x:v>21.784</x:v>
+      </x:c>
+      <x:c r="F51" s="0">
+        <x:v>1699073</x:v>
+      </x:c>
+      <x:c r="G51" s="0">
+        <x:v>2.78495084436934</x:v>
+      </x:c>
+      <x:c r="H51" s="0">
+        <x:v>-200631</x:v>
+      </x:c>
+      <x:c r="I51" s="0">
+        <x:v>21.893</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
+      <x:c r="A52" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B52" s="0">
+        <x:v>368218</x:v>
+      </x:c>
+      <x:c r="C52" s="0">
+        <x:v>21.806</x:v>
+      </x:c>
+      <x:c r="D52" s="0">
+        <x:v>577411</x:v>
+      </x:c>
+      <x:c r="E52" s="0">
+        <x:v>21.781</x:v>
+      </x:c>
+      <x:c r="F52" s="0">
+        <x:v>945629</x:v>
+      </x:c>
+      <x:c r="G52" s="0">
+        <x:v>1.54998065533979</x:v>
+      </x:c>
+      <x:c r="H52" s="0">
+        <x:v>-209193</x:v>
+      </x:c>
+      <x:c r="I52" s="0">
+        <x:v>21.736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:9">
+      <x:c r="A53" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B53" s="0">
+        <x:v>1733547</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>21.823</x:v>
+      </x:c>
+      <x:c r="D53" s="0">
+        <x:v>2016182</x:v>
+      </x:c>
+      <x:c r="E53" s="0">
+        <x:v>21.804</x:v>
+      </x:c>
+      <x:c r="F53" s="0">
+        <x:v>3749729</x:v>
+      </x:c>
+      <x:c r="G53" s="0">
+        <x:v>6.14618144406167</x:v>
+      </x:c>
+      <x:c r="H53" s="0">
+        <x:v>-282635</x:v>
+      </x:c>
+      <x:c r="I53" s="0">
+        <x:v>21.689</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:9">
+      <x:c r="A54" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B54" s="0">
+        <x:v>1787600</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>21.803</x:v>
+      </x:c>
+      <x:c r="D54" s="0">
+        <x:v>2135285</x:v>
+      </x:c>
+      <x:c r="E54" s="0">
+        <x:v>21.75</x:v>
+      </x:c>
+      <x:c r="F54" s="0">
+        <x:v>3922885</x:v>
+      </x:c>
+      <x:c r="G54" s="0">
+        <x:v>6.43000147322323</x:v>
+      </x:c>
+      <x:c r="H54" s="0">
+        <x:v>-347685</x:v>
+      </x:c>
+      <x:c r="I54" s="0">
+        <x:v>21.479</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:9">
+      <x:c r="A55" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B55" s="0">
+        <x:v>2513442</x:v>
+      </x:c>
+      <x:c r="C55" s="0">
+        <x:v>21.841</x:v>
+      </x:c>
+      <x:c r="D55" s="0">
+        <x:v>3045275</x:v>
+      </x:c>
+      <x:c r="E55" s="0">
+        <x:v>21.753</x:v>
+      </x:c>
+      <x:c r="F55" s="0">
+        <x:v>5558717</x:v>
+      </x:c>
+      <x:c r="G55" s="0">
+        <x:v>9.11129398369594</x:v>
+      </x:c>
+      <x:c r="H55" s="0">
+        <x:v>-531833</x:v>
+      </x:c>
+      <x:c r="I55" s="0">
+        <x:v>21.332</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,160 +40,160 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
     <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>666617</x:v>
+        <x:v>2371066</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>21.718</x:v>
+        <x:v>21.635</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>304694</x:v>
+        <x:v>1958241</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>21.942</x:v>
+        <x:v>21.629</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>971311</x:v>
+        <x:v>4329307</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>1.59207602592427</x:v>
+        <x:v>3.97994723197705</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>361923</x:v>
+        <x:v>412825</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>21.53</x:v>
+        <x:v>21.664</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1027115</x:v>
+        <x:v>773170</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>21.761</x:v>
+        <x:v>21.673</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>711496</x:v>
+        <x:v>367204</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>21.829</x:v>
+        <x:v>21.832</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1738611</x:v>
+        <x:v>1140374</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2.84975758691935</x:v>
+        <x:v>1.04834985015352</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>315619</x:v>
+        <x:v>405966</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>21.609</x:v>
+        <x:v>21.529</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2616675</x:v>
+        <x:v>4676066</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>21.838</x:v>
+        <x:v>21.669</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>2335212</x:v>
+        <x:v>4289808</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>21.86</x:v>
+        <x:v>21.652</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>4951887</x:v>
+        <x:v>8965874</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>8.11663882709663</x:v>
+        <x:v>8.24235966831528</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>281463</x:v>
+        <x:v>386258</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>21.662</x:v>
+        <x:v>21.861</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>2902045</x:v>
+        <x:v>918046</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>21.815</x:v>
+        <x:v>21.647</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>2650616</x:v>
+        <x:v>678130</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>21.773</x:v>
+        <x:v>21.67</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>5552661</x:v>
+        <x:v>1596176</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>9.10136759306204</x:v>
+        <x:v>1.46737024030594</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>251429</x:v>
+        <x:v>239916</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>22.248</x:v>
+        <x:v>21.584</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>356276</x:v>
+        <x:v>207257</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>21.867</x:v>
+        <x:v>21.659</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>131411</x:v>
+        <x:v>55001</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>21.955</x:v>
+        <x:v>21.849</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>487687</x:v>
+        <x:v>262258</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.799367844958957</x:v>
+        <x:v>0.241094706650242</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>224865</x:v>
+        <x:v>152256</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>21.815</x:v>
+        <x:v>21.59</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>1585035</x:v>
+        <x:v>259234</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>21.771</x:v>
+        <x:v>21.589</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>1455154</x:v>
+        <x:v>119640</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>21.8</x:v>
+        <x:v>21.695</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>3040189</x:v>
+        <x:v>378874</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>4.9831743089275</x:v>
+        <x:v>0.348300207762599</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>129881</x:v>
+        <x:v>139594</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>21.443</x:v>
+        <x:v>21.497</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>736889</x:v>
+        <x:v>448978</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>21.755</x:v>
+        <x:v>21.785</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>643796</x:v>
+        <x:v>315648</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>21.749</x:v>
+        <x:v>21.734</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1380685</x:v>
+        <x:v>764626</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.26308101921347</x:v>
+        <x:v>0.70292338524334</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>93093</x:v>
+        <x:v>133330</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>21.795</x:v>
+        <x:v>21.906</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>403851</x:v>
+        <x:v>2353800</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>21.805</x:v>
+        <x:v>21.671</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>318951</x:v>
+        <x:v>2230318</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>21.828</x:v>
+        <x:v>21.698</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>722802</x:v>
+        <x:v>4584118</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.18474488159829</x:v>
+        <x:v>4.21419588519737</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>84900</x:v>
+        <x:v>123482</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>21.721</x:v>
+        <x:v>21.176</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>126001</x:v>
+        <x:v>510536</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>21.784</x:v>
+        <x:v>21.585</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>55001</x:v>
+        <x:v>399709</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>21.849</x:v>
+        <x:v>21.539</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>181002</x:v>
+        <x:v>910245</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.296680409101045</x:v>
+        <x:v>0.836791446799904</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>71000</x:v>
+        <x:v>110827</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>21.734</x:v>
+        <x:v>21.752</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>622692</x:v>
+        <x:v>4994210</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>21.789</x:v>
+        <x:v>21.659</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>559597</x:v>
+        <x:v>4885953</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>21.82</x:v>
+        <x:v>21.651</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>1182289</x:v>
+        <x:v>9880163</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.93789010174288</x:v>
+        <x:v>9.08286877861332</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>63095</x:v>
+        <x:v>108257</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>21.51</x:v>
+        <x:v>22.017</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>208920</x:v>
+        <x:v>305419</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>21.798</x:v>
+        <x:v>21.735</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>151609</x:v>
+        <x:v>198070</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>21.778</x:v>
+        <x:v>21.929</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>360529</x:v>
+        <x:v>503489</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.590943145450274</x:v>
+        <x:v>0.462859217856552</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>57311</x:v>
+        <x:v>107349</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>21.851</x:v>
+        <x:v>21.377</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1168263</x:v>
+        <x:v>2212260</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>21.835</x:v>
+        <x:v>21.583</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1121389</x:v>
+        <x:v>2110574</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>21.744</x:v>
+        <x:v>21.564</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>2289652</x:v>
+        <x:v>4322834</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>3.75296898409424</x:v>
+        <x:v>3.97399658019085</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>46874</x:v>
+        <x:v>101686</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>24.006</x:v>
+        <x:v>21.982</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>238904</x:v>
+        <x:v>3445638</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>21.792</x:v>
+        <x:v>21.708</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>194310</x:v>
+        <x:v>3351036</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>21.939</x:v>
+        <x:v>21.713</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>433214</x:v>
+        <x:v>6796674</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.710081141359211</x:v>
+        <x:v>6.24820643880196</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>44594</x:v>
+        <x:v>94602</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>21.153</x:v>
+        <x:v>21.523</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>396003</x:v>
+        <x:v>1648441</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>21.78</x:v>
+        <x:v>21.533</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>351444</x:v>
+        <x:v>1586842</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>21.892</x:v>
+        <x:v>21.556</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>747447</x:v>
+        <x:v>3235283</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>1.22514050530573</x:v>
+        <x:v>2.97420710070051</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>44559</x:v>
+        <x:v>61599</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>20.898</x:v>
+        <x:v>20.934</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>138113</x:v>
+        <x:v>51479</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>21.909</x:v>
+        <x:v>21.59</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>106482</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>21.787</x:v>
+        <x:v>21.741</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>244595</x:v>
+        <x:v>51803</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.400915706257776</x:v>
+        <x:v>0.0476226810568313</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>31631</x:v>
+        <x:v>51155</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>22.317</x:v>
+        <x:v>21.589</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>319085</x:v>
+        <x:v>215134</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>21.671</x:v>
+        <x:v>21.548</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>291802</x:v>
+        <x:v>164844</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>21.777</x:v>
+        <x:v>21.604</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>610887</x:v>
+        <x:v>379978</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>1.00130498599192</x:v>
+        <x:v>0.349315118865947</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>27283</x:v>
+        <x:v>50290</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>20.534</x:v>
+        <x:v>21.363</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>748564</x:v>
+        <x:v>99895</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>21.848</x:v>
+        <x:v>21.635</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>725034</x:v>
+        <x:v>56568</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>21.831</x:v>
+        <x:v>21.817</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1473598</x:v>
+        <x:v>156463</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>2.41537473337577</x:v>
+        <x:v>0.14383698909706</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>23530</x:v>
+        <x:v>43327</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>22.392</x:v>
+        <x:v>21.397</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>182964</x:v>
+        <x:v>142199</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>21.848</x:v>
+        <x:v>21.601</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>160949</x:v>
+        <x:v>99989</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>21.863</x:v>
+        <x:v>21.569</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>343913</x:v>
+        <x:v>242188</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.563707857013556</x:v>
+        <x:v>0.222644284689919</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>22015</x:v>
+        <x:v>42210</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>21.743</x:v>
+        <x:v>21.676</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>42957</x:v>
+        <x:v>1070220</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>21.827</x:v>
+        <x:v>21.739</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>23289</x:v>
+        <x:v>1031862</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>21.875</x:v>
+        <x:v>21.721</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>66246</x:v>
+        <x:v>2102082</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.108583829909657</x:v>
+        <x:v>1.93245141480814</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>19668</x:v>
+        <x:v>38358</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>21.769</x:v>
+        <x:v>22.223</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>10441</x:v>
+        <x:v>38556</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>21.78</x:v>
+        <x:v>21.48</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>291</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>21.763</x:v>
+        <x:v>22.1</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>10732</x:v>
+        <x:v>39556</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0175908230321898</x:v>
+        <x:v>0.0363639706558311</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>10150</x:v>
+        <x:v>37556</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>21.781</x:v>
+        <x:v>21.463</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>10238</x:v>
+        <x:v>1075378</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>21.734</x:v>
+        <x:v>21.648</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>323</x:v>
+        <x:v>1042815</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>21.743</x:v>
+        <x:v>21.662</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>10561</x:v>
+        <x:v>2118193</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0173105369029963</x:v>
+        <x:v>1.94726231407086</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>9915</x:v>
+        <x:v>32563</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>21.733</x:v>
+        <x:v>21.201</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>5096</x:v>
+        <x:v>484934</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>21.796</x:v>
+        <x:v>21.628</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>2095</x:v>
+        <x:v>455988</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>21.827</x:v>
+        <x:v>21.64</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>7191</x:v>
+        <x:v>940922</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0117867693276627</x:v>
+        <x:v>0.864992921362776</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>3001</x:v>
+        <x:v>28946</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>21.775</x:v>
+        <x:v>21.443</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>102342</x:v>
+        <x:v>224471</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>21.699</x:v>
+        <x:v>21.774</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>99476</x:v>
+        <x:v>196845</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>21.738</x:v>
+        <x:v>21.784</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>201818</x:v>
+        <x:v>421316</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.330799918254796</x:v>
+        <x:v>0.387317288422291</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>2866</x:v>
+        <x:v>27626</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>20.341</x:v>
+        <x:v>21.701</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>3609446</x:v>
+        <x:v>271013</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>21.775</x:v>
+        <x:v>21.398</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>3606828</x:v>
+        <x:v>249939</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>21.815</x:v>
+        <x:v>21.406</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>7216274</x:v>
+        <x:v>520952</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>11.8281959453776</x:v>
+        <x:v>0.478913015499458</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>2618</x:v>
+        <x:v>21074</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>-32.278</x:v>
+        <x:v>21.3</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>2000</x:v>
+        <x:v>553559</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>21.64</x:v>
+        <x:v>21.561</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>140</x:v>
+        <x:v>535489</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>21.693</x:v>
+        <x:v>21.721</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>2140</x:v>
+        <x:v>1089048</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00350767436534533</x:v>
+        <x:v>1.00116567688319</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>1860</x:v>
+        <x:v>18070</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>21.636</x:v>
+        <x:v>16.817</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>56795</x:v>
+        <x:v>461088</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>21.813</x:v>
+        <x:v>21.772</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>56423</x:v>
+        <x:v>443987</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>21.818</x:v>
+        <x:v>21.831</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>113218</x:v>
+        <x:v>905075</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.185575643128817</x:v>
+        <x:v>0.832038647520638</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>372</x:v>
+        <x:v>17101</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>21.091</x:v>
+        <x:v>20.255</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>2000</x:v>
+        <x:v>289986</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>21.945</x:v>
+        <x:v>21.522</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1763</x:v>
+        <x:v>272895</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>21.643</x:v>
+        <x:v>21.628</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>3763</x:v>
+        <x:v>562881</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00616793394242733</x:v>
+        <x:v>0.517458493445366</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>237</x:v>
+        <x:v>17091</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.194</x:v>
+        <x:v>19.83</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>2612</x:v>
+        <x:v>182456</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>21.821</x:v>
+        <x:v>21.554</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>2465</x:v>
+        <x:v>171465</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>21.728</x:v>
+        <x:v>21.533</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>5077</x:v>
+        <x:v>353921</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00832171156675619</x:v>
+        <x:v>0.325360826637739</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>147</x:v>
+        <x:v>10991</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.374</x:v>
+        <x:v>21.879</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>57089</x:v>
+        <x:v>42983</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>21.707</x:v>
+        <x:v>21.621</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>56987</x:v>
+        <x:v>32137</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>21.881</x:v>
+        <x:v>21.673</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>114076</x:v>
+        <x:v>75120</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.186981991075296</x:v>
+        <x:v>0.0690580815973818</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>102</x:v>
+        <x:v>10846</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>-75.588</x:v>
+        <x:v>21.465</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>207</x:v>
+        <x:v>6646</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>21.763</x:v>
+        <x:v>21.713</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>145</x:v>
+        <x:v>2095</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>21.69</x:v>
+        <x:v>21.827</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>352</x:v>
+        <x:v>8741</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.000576963260094185</x:v>
+        <x:v>0.00803563220504146</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>62</x:v>
+        <x:v>4551</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>21.935</x:v>
+        <x:v>21.661</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>40</x:v>
+        <x:v>13252</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>21.65</x:v>
+        <x:v>21.556</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>0</x:v>
+        <x:v>9465</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>0</x:v>
+        <x:v>21.557</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>40</x:v>
+        <x:v>22717</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>6.55640068288847E-05</x:v>
+        <x:v>0.0208838184191656</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>40</x:v>
+        <x:v>3787</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>21.65</x:v>
+        <x:v>21.554</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>50000</x:v>
+        <x:v>3047</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>21.5</x:v>
+        <x:v>21.63</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>50000</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>21.58</x:v>
+        <x:v>21.693</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>100000</x:v>
+        <x:v>3187</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.163910017072212</x:v>
+        <x:v>0.00292982036808914</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>0</x:v>
+        <x:v>2907</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>21.5</x:v>
+        <x:v>21.627</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>0</x:v>
+        <x:v>51255</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>0</x:v>
+        <x:v>21.5</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>144</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>21.861</x:v>
+        <x:v>21.58</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>144</x:v>
+        <x:v>101255</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.000236030424583985</x:v>
+        <x:v>0.0930840795013698</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-144</x:v>
+        <x:v>1255</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>21.861</x:v>
+        <x:v>18.292</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>0</x:v>
+        <x:v>80274</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>0</x:v>
+        <x:v>21.461</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>1000</x:v>
+        <x:v>80184</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>22.1</x:v>
+        <x:v>21.52</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>1000</x:v>
+        <x:v>160458</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00163910017072212</x:v>
+        <x:v>0.147509606721947</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-1000</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>22.1</x:v>
+        <x:v>-31.367</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>16154</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>21.742</x:v>
+        <x:v>21.65</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>17993</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>21.742</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>34147</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0559703535296481</x:v>
+        <x:v>3.67721414256559E-05</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-1839</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>21.742</x:v>
+        <x:v>21.65</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>0</x:v>
+        <x:v>2075</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0</x:v>
+        <x:v>21.92</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>2500</x:v>
+        <x:v>2298</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>21.72</x:v>
+        <x:v>21.613</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>2500</x:v>
+        <x:v>4373</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00409775042680529</x:v>
+        <x:v>0.00402011436135983</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-2500</x:v>
+        <x:v>-223</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.72</x:v>
+        <x:v>18.762</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>43788</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>21.704</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>47404</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>21.813</x:v>
+        <x:v>21.607</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>91192</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.149472822768491</x:v>
+        <x:v>0.000444942911250437</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-3616</x:v>
+        <x:v>-484</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>23.132</x:v>
+        <x:v>21.607</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>2043109</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>21.849</x:v>
+        <x:v>21.519</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>2051004</x:v>
+        <x:v>2447</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>21.854</x:v>
+        <x:v>21.585</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>4094113</x:v>
+        <x:v>3090</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.71066131725564</x:v>
+        <x:v>0.00284064792513192</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-7895</x:v>
+        <x:v>-1804</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>23.184</x:v>
+        <x:v>21.608</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>10329</x:v>
+        <x:v>6330</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>21.766</x:v>
+        <x:v>21.36</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>22909</x:v>
+        <x:v>8830</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>21.805</x:v>
+        <x:v>21.491</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>33238</x:v>
+        <x:v>15160</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.0544804114744617</x:v>
+        <x:v>0.0139366416003236</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-12580</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>21.838</x:v>
+        <x:v>21.822</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>340562</x:v>
+        <x:v>280496</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>21.889</x:v>
+        <x:v>21.668</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>353524</x:v>
+        <x:v>290082</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>21.942</x:v>
+        <x:v>21.56</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>694086</x:v>
+        <x:v>570578</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.13767648109583</x:v>
+        <x:v>0.524534372759198</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-12962</x:v>
+        <x:v>-9586</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>23.331</x:v>
+        <x:v>18.389</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>50911</x:v>
+        <x:v>77266</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>21.779</x:v>
+        <x:v>21.622</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>65150</x:v>
+        <x:v>103999</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>21.818</x:v>
+        <x:v>21.695</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>116061</x:v>
+        <x:v>181265</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.19023560491418</x:v>
+        <x:v>0.166637555388038</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-14239</x:v>
+        <x:v>-26733</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>21.956</x:v>
+        <x:v>21.908</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>236736</x:v>
+        <x:v>1496758</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>21.549</x:v>
+        <x:v>21.658</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>257322</x:v>
+        <x:v>1530382</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>21.633</x:v>
+        <x:v>21.659</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>494058</x:v>
+        <x:v>3027140</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.809810552146628</x:v>
+        <x:v>2.7828605048815</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-20586</x:v>
+        <x:v>-33624</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>22.599</x:v>
+        <x:v>21.667</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>694071</x:v>
+        <x:v>228113</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>21.718</x:v>
+        <x:v>21.591</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>722716</x:v>
+        <x:v>262712</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>21.754</x:v>
+        <x:v>21.602</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>1416787</x:v>
+        <x:v>490825</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2.32225581357688</x:v>
+        <x:v>0.451217157881189</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-28645</x:v>
+        <x:v>-34599</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>22.627</x:v>
+        <x:v>21.673</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>78314</x:v>
+        <x:v>5851601</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>21.748</x:v>
+        <x:v>21.661</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>114060</x:v>
+        <x:v>5907536</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>21.77</x:v>
+        <x:v>21.687</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>192374</x:v>
+        <x:v>11759137</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.315320256242497</x:v>
+        <x:v>10.8102162201916</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-35746</x:v>
+        <x:v>-55935</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>21.817</x:v>
+        <x:v>24.415</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>40354</x:v>
+        <x:v>180143</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>21.811</x:v>
+        <x:v>21.469</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>104059</x:v>
+        <x:v>238083</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>21.844</x:v>
+        <x:v>21.583</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>144413</x:v>
+        <x:v>418226</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.236707372954493</x:v>
+        <x:v>0.384476640497159</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-63705</x:v>
+        <x:v>-57940</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>21.865</x:v>
+        <x:v>21.939</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>31388</x:v>
+        <x:v>498048</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>21.711</x:v>
+        <x:v>21.716</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>114660</x:v>
+        <x:v>570348</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>21.694</x:v>
+        <x:v>21.736</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>146048</x:v>
+        <x:v>1068396</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.239387301733624</x:v>
+        <x:v>0.982180220265127</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-83272</x:v>
+        <x:v>-72300</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>21.688</x:v>
+        <x:v>21.877</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>1095216</x:v>
+        <x:v>150809</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>21.794</x:v>
+        <x:v>21.554</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1193416</x:v>
+        <x:v>260759</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>21.795</x:v>
+        <x:v>21.598</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>2288632</x:v>
+        <x:v>411568</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>3.7512971019201</x:v>
+        <x:v>0.378355917556859</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-98200</x:v>
+        <x:v>-109950</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>21.801</x:v>
+        <x:v>21.66</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>87417</x:v>
+        <x:v>782560</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>21.817</x:v>
+        <x:v>21.656</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>198644</x:v>
+        <x:v>894208</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>21.786</x:v>
+        <x:v>21.663</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>286061</x:v>
+        <x:v>1676768</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.46888263393694</x:v>
+        <x:v>1.54145875085036</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-111227</x:v>
+        <x:v>-111648</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>21.761</x:v>
+        <x:v>21.714</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>188890</x:v>
+        <x:v>274932</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>21.743</x:v>
+        <x:v>21.566</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>344860</x:v>
+        <x:v>418172</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>21.857</x:v>
+        <x:v>21.552</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>533750</x:v>
+        <x:v>693104</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.87486971612293</x:v>
+        <x:v>0.637172957767196</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-155970</x:v>
+        <x:v>-143240</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>21.995</x:v>
+        <x:v>21.526</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>749221</x:v>
+        <x:v>1495929</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>21.755</x:v>
+        <x:v>21.609</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>949852</x:v>
+        <x:v>1748233</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>21.784</x:v>
+        <x:v>21.625</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1699073</x:v>
+        <x:v>3244162</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.78495084436934</x:v>
+        <x:v>2.98236959679347</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-200631</x:v>
+        <x:v>-252304</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>21.893</x:v>
+        <x:v>21.721</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>368218</x:v>
+        <x:v>3346975</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>21.806</x:v>
+        <x:v>21.65</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>577411</x:v>
+        <x:v>3623309</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>21.781</x:v>
+        <x:v>21.65</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>945629</x:v>
+        <x:v>6970284</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>1.54998065533979</x:v>
+        <x:v>6.40780672562467</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-209193</x:v>
+        <x:v>-276334</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>21.736</x:v>
+        <x:v>21.651</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>1733547</x:v>
+        <x:v>1931778</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>21.823</x:v>
+        <x:v>21.649</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>2016182</x:v>
+        <x:v>2322231</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>21.804</x:v>
+        <x:v>21.625</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>3749729</x:v>
+        <x:v>4254009</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>6.14618144406167</x:v>
+        <x:v>3.91072551435033</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-282635</x:v>
+        <x:v>-390453</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>21.689</x:v>
+        <x:v>21.504</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>1787600</x:v>
+        <x:v>3218872</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>21.803</x:v>
+        <x:v>21.653</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>2135285</x:v>
+        <x:v>3664669</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>21.75</x:v>
+        <x:v>21.633</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>3922885</x:v>
+        <x:v>6883541</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>6.43000147322323</x:v>
+        <x:v>6.32806357903253</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-347685</x:v>
+        <x:v>-445797</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.479</x:v>
+        <x:v>21.485</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>2513442</x:v>
+        <x:v>4083686</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>21.841</x:v>
+        <x:v>21.698</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>3045275</x:v>
+        <x:v>5096013</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>21.753</x:v>
+        <x:v>21.636</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>5558717</x:v>
+        <x:v>9179699</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>9.11129398369594</x:v>
+        <x:v>8.43892974682381</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-531833</x:v>
+        <x:v>-1012327</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>21.332</x:v>
+        <x:v>21.388</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,154 +40,154 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
-    <x:t>GLOBAL</x:t>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
+    <x:t>HALK</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
   </x:si>
   <x:si>
     <x:t>MIDAS</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>2371066</x:v>
+        <x:v>7163915</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>21.635</x:v>
+        <x:v>21.579</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>1958241</x:v>
+        <x:v>6036577</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>21.629</x:v>
+        <x:v>21.588</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>4329307</x:v>
+        <x:v>13200492</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>3.97994723197705</x:v>
+        <x:v>9.00356646622246</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>412825</x:v>
+        <x:v>1127338</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>21.664</x:v>
+        <x:v>21.531</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>773170</x:v>
+        <x:v>797608</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>21.673</x:v>
+        <x:v>21.668</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>367204</x:v>
+        <x:v>427600</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>21.832</x:v>
+        <x:v>21.798</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1140374</x:v>
+        <x:v>1225208</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>1.04834985015352</x:v>
+        <x:v>0.835668978318951</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>405966</x:v>
+        <x:v>370008</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>21.529</x:v>
+        <x:v>21.518</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>4676066</x:v>
+        <x:v>1373760</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>21.669</x:v>
+        <x:v>21.552</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>4289808</x:v>
+        <x:v>1156449</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>21.652</x:v>
+        <x:v>21.554</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>8965874</x:v>
+        <x:v>2530209</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>8.24235966831528</x:v>
+        <x:v>1.72576180531258</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>386258</x:v>
+        <x:v>217311</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>21.861</x:v>
+        <x:v>21.538</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>918046</x:v>
+        <x:v>889246</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>21.647</x:v>
+        <x:v>21.583</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>678130</x:v>
+        <x:v>683202</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>21.67</x:v>
+        <x:v>21.679</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1596176</x:v>
+        <x:v>1572448</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.46737024030594</x:v>
+        <x:v>1.07250851579461</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>239916</x:v>
+        <x:v>206044</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>21.584</x:v>
+        <x:v>21.264</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>207257</x:v>
+        <x:v>501994</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>21.659</x:v>
+        <x:v>21.73</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>55001</x:v>
+        <x:v>318542</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>21.849</x:v>
+        <x:v>21.73</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>262258</x:v>
+        <x:v>820536</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.241094706650242</x:v>
+        <x:v>0.55965720171099</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>152256</x:v>
+        <x:v>183452</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>21.59</x:v>
+        <x:v>21.731</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>259234</x:v>
+        <x:v>2951717</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>21.589</x:v>
+        <x:v>21.587</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>119640</x:v>
+        <x:v>2782942</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>21.695</x:v>
+        <x:v>21.569</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>378874</x:v>
+        <x:v>5734659</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.348300207762599</x:v>
+        <x:v>3.91139841360616</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>139594</x:v>
+        <x:v>168775</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>21.497</x:v>
+        <x:v>21.876</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>448978</x:v>
+        <x:v>8670759</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>21.785</x:v>
+        <x:v>21.588</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>315648</x:v>
+        <x:v>8555320</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>21.734</x:v>
+        <x:v>21.616</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>764626</x:v>
+        <x:v>17226079</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.70292338524334</x:v>
+        <x:v>11.7492701960578</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>133330</x:v>
+        <x:v>115439</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>21.906</x:v>
+        <x:v>19.53</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>2353800</x:v>
+        <x:v>627334</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>21.671</x:v>
+        <x:v>21.571</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>2230318</x:v>
+        <x:v>514889</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>21.698</x:v>
+        <x:v>21.529</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>4584118</x:v>
+        <x:v>1142223</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>4.21419588519737</x:v>
+        <x:v>0.779067984719662</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>123482</x:v>
+        <x:v>112445</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>21.176</x:v>
+        <x:v>21.764</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>510536</x:v>
+        <x:v>482913</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>21.585</x:v>
+        <x:v>21.665</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>399709</x:v>
+        <x:v>370784</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>21.539</x:v>
+        <x:v>21.736</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>910245</x:v>
+        <x:v>853697</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.836791446799904</x:v>
+        <x:v>0.582275091073478</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>110827</x:v>
+        <x:v>112129</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>21.752</x:v>
+        <x:v>21.431</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>4994210</x:v>
+        <x:v>3196702</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>21.659</x:v>
+        <x:v>21.505</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>4885953</x:v>
+        <x:v>3096920</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>21.651</x:v>
+        <x:v>21.484</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>9880163</x:v>
+        <x:v>6293622</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>9.08286877861332</x:v>
+        <x:v>4.29264636426278</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>108257</x:v>
+        <x:v>99782</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.017</x:v>
+        <x:v>22.152</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>305419</x:v>
+        <x:v>2167839</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>21.735</x:v>
+        <x:v>21.489</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>198070</x:v>
+        <x:v>2090730</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>21.929</x:v>
+        <x:v>21.502</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>503489</x:v>
+        <x:v>4258569</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.462859217856552</x:v>
+        <x:v>2.90461211919181</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>107349</x:v>
+        <x:v>77109</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>21.377</x:v>
+        <x:v>21.135</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>2212260</x:v>
+        <x:v>207257</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>21.583</x:v>
+        <x:v>21.659</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>2110574</x:v>
+        <x:v>131101</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>21.564</x:v>
+        <x:v>21.603</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>4322834</x:v>
+        <x:v>338358</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>3.97399658019085</x:v>
+        <x:v>0.230781454386556</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>101686</x:v>
+        <x:v>76156</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>21.982</x:v>
+        <x:v>21.755</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>3445638</x:v>
+        <x:v>1435332</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>21.708</x:v>
+        <x:v>21.671</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>3351036</x:v>
+        <x:v>1366947</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>21.713</x:v>
+        <x:v>21.674</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>6796674</x:v>
+        <x:v>2802279</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>6.24820643880196</x:v>
+        <x:v>1.91133067111434</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>94602</x:v>
+        <x:v>68385</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>21.523</x:v>
+        <x:v>21.617</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>1648441</x:v>
+        <x:v>6426621</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>21.533</x:v>
+        <x:v>21.604</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>1586842</x:v>
+        <x:v>6360770</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>21.556</x:v>
+        <x:v>21.6</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>3235283</x:v>
+        <x:v>12787391</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.97420710070051</x:v>
+        <x:v>8.72180558104008</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>61599</x:v>
+        <x:v>65851</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>20.934</x:v>
+        <x:v>21.942</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>51479</x:v>
+        <x:v>267067</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>21.59</x:v>
+        <x:v>21.584</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>324</x:v>
+        <x:v>212903</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>21.741</x:v>
+        <x:v>21.497</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>51803</x:v>
+        <x:v>479970</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0476226810568313</x:v>
+        <x:v>0.327369752338988</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>51155</x:v>
+        <x:v>54164</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>21.589</x:v>
+        <x:v>21.924</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>215134</x:v>
+        <x:v>273384</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>21.548</x:v>
+        <x:v>21.539</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>164844</x:v>
+        <x:v>220465</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>21.604</x:v>
+        <x:v>21.563</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>379978</x:v>
+        <x:v>493849</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.349315118865947</x:v>
+        <x:v>0.336836103970784</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>50290</x:v>
+        <x:v>52919</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>21.363</x:v>
+        <x:v>21.436</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>99895</x:v>
+        <x:v>51631</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>21.635</x:v>
+        <x:v>21.589</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>56568</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>21.817</x:v>
+        <x:v>21.723</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>156463</x:v>
+        <x:v>52007</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.14383698909706</x:v>
+        <x:v>0.03547204764859</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>43327</x:v>
+        <x:v>51255</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>21.397</x:v>
+        <x:v>21.588</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>142199</x:v>
+        <x:v>793743</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>21.601</x:v>
+        <x:v>21.512</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>99989</x:v>
+        <x:v>744837</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>21.569</x:v>
+        <x:v>21.634</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>242188</x:v>
+        <x:v>1538580</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.222644284689919</x:v>
+        <x:v>1.04940840792908</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>42210</x:v>
+        <x:v>48906</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>21.676</x:v>
+        <x:v>19.659</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>1070220</x:v>
+        <x:v>48106</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>21.739</x:v>
+        <x:v>21.439</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>1031862</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>21.721</x:v>
+        <x:v>22.1</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>2102082</x:v>
+        <x:v>49106</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>1.93245141480814</x:v>
+        <x:v>0.0334933830413533</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>38358</x:v>
+        <x:v>47106</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>22.223</x:v>
+        <x:v>21.425</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>38556</x:v>
+        <x:v>571387</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>21.48</x:v>
+        <x:v>21.708</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>1000</x:v>
+        <x:v>532937</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>22.1</x:v>
+        <x:v>21.78</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>39556</x:v>
+        <x:v>1104324</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0363639706558311</x:v>
+        <x:v>0.753218481117572</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>37556</x:v>
+        <x:v>38450</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>21.463</x:v>
+        <x:v>20.702</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>1075378</x:v>
+        <x:v>302435</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>21.648</x:v>
+        <x:v>21.549</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>1042815</x:v>
+        <x:v>264610</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>21.662</x:v>
+        <x:v>21.578</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>2118193</x:v>
+        <x:v>567045</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.94726231407086</x:v>
+        <x:v>0.386760383388673</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>32563</x:v>
+        <x:v>37825</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>21.201</x:v>
+        <x:v>21.344</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>484934</x:v>
+        <x:v>290291</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>21.628</x:v>
+        <x:v>21.449</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>455988</x:v>
+        <x:v>259156</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>21.64</x:v>
+        <x:v>21.464</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>940922</x:v>
+        <x:v>549447</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.864992921362776</x:v>
+        <x:v>0.374757439659562</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>28946</x:v>
+        <x:v>31135</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>21.443</x:v>
+        <x:v>21.329</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>224471</x:v>
+        <x:v>506853</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>21.774</x:v>
+        <x:v>21.614</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>196845</x:v>
+        <x:v>479072</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>21.784</x:v>
+        <x:v>21.638</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>421316</x:v>
+        <x:v>985925</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.387317288422291</x:v>
+        <x:v>0.672462910337765</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>27626</x:v>
+        <x:v>27781</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>21.701</x:v>
+        <x:v>21.203</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>271013</x:v>
+        <x:v>236268</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>21.398</x:v>
+        <x:v>21.752</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>249939</x:v>
+        <x:v>210683</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>21.406</x:v>
+        <x:v>21.76</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>520952</x:v>
+        <x:v>446951</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.478913015499458</x:v>
+        <x:v>0.304848715914876</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>21074</x:v>
+        <x:v>25585</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>21.3</x:v>
+        <x:v>21.689</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>553559</x:v>
+        <x:v>310128</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>21.561</x:v>
+        <x:v>21.401</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>535489</x:v>
+        <x:v>288275</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>21.721</x:v>
+        <x:v>21.412</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1089048</x:v>
+        <x:v>598403</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>1.00116567688319</x:v>
+        <x:v>0.40814851325897</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>18070</x:v>
+        <x:v>21853</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>16.817</x:v>
+        <x:v>21.263</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>461088</x:v>
+        <x:v>197456</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>21.772</x:v>
+        <x:v>21.553</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>443987</x:v>
+        <x:v>186465</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>21.831</x:v>
+        <x:v>21.534</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>905075</x:v>
+        <x:v>383921</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.832038647520638</x:v>
+        <x:v>0.261858288409144</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>17101</x:v>
+        <x:v>10991</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>20.255</x:v>
+        <x:v>21.879</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>289986</x:v>
+        <x:v>19792</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>21.522</x:v>
+        <x:v>21.516</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>272895</x:v>
+        <x:v>11999</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>21.628</x:v>
+        <x:v>21.548</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>562881</x:v>
+        <x:v>31791</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.517458493445366</x:v>
+        <x:v>0.021683463126047</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>17091</x:v>
+        <x:v>7793</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>19.83</x:v>
+        <x:v>21.467</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>182456</x:v>
+        <x:v>52182</x:v>
       </x:c>
       <x:c r="C29" s="0">
+        <x:v>21.602</x:v>
+      </x:c>
+      <x:c r="D29" s="0">
+        <x:v>45351</x:v>
+      </x:c>
+      <x:c r="E29" s="0">
+        <x:v>21.609</x:v>
+      </x:c>
+      <x:c r="F29" s="0">
+        <x:v>97533</x:v>
+      </x:c>
+      <x:c r="G29" s="0">
+        <x:v>0.0665236453421642</x:v>
+      </x:c>
+      <x:c r="H29" s="0">
+        <x:v>6831</x:v>
+      </x:c>
+      <x:c r="I29" s="0">
         <x:v>21.554</x:v>
-      </x:c>
-      <x:c r="D29" s="0">
-        <x:v>171465</x:v>
-      </x:c>
-      <x:c r="E29" s="0">
-        <x:v>21.533</x:v>
-      </x:c>
-      <x:c r="F29" s="0">
-        <x:v>353921</x:v>
-      </x:c>
-      <x:c r="G29" s="0">
-        <x:v>0.325360826637739</x:v>
-      </x:c>
-      <x:c r="H29" s="0">
-        <x:v>10991</x:v>
-      </x:c>
-      <x:c r="I29" s="0">
-        <x:v>21.879</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>42983</x:v>
+        <x:v>2736468</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>21.621</x:v>
+        <x:v>21.635</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>32137</x:v>
+        <x:v>2731275</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>21.673</x:v>
+        <x:v>21.647</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>75120</x:v>
+        <x:v>5467743</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0690580815973818</x:v>
+        <x:v>3.72934490022967</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>10846</x:v>
+        <x:v>5193</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>21.465</x:v>
+        <x:v>15.164</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>6646</x:v>
+        <x:v>6666</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>21.713</x:v>
+        <x:v>21.712</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2095</x:v>
+        <x:v>2170</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>21.827</x:v>
+        <x:v>21.806</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>8741</x:v>
+        <x:v>8836</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00803563220504146</x:v>
+        <x:v>0.00602670819356897</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>4551</x:v>
+        <x:v>4496</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>21.661</x:v>
+        <x:v>21.666</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>13252</x:v>
+        <x:v>4347</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>21.556</x:v>
+        <x:v>21.496</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>9465</x:v>
+        <x:v>1440</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>21.557</x:v>
+        <x:v>21.681</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>22717</x:v>
+        <x:v>5787</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0208838184191656</x:v>
+        <x:v>0.00394709827027882</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>3787</x:v>
+        <x:v>2907</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>21.554</x:v>
+        <x:v>21.404</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>3047</x:v>
+        <x:v>51255</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>21.63</x:v>
+        <x:v>21.5</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>140</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>21.693</x:v>
+        <x:v>21.58</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>3187</x:v>
+        <x:v>101255</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00292982036808914</x:v>
+        <x:v>0.069062283628319</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>2907</x:v>
+        <x:v>1255</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>21.627</x:v>
+        <x:v>18.292</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>51255</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>21.5</x:v>
+        <x:v>21.775</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>50000</x:v>
+        <x:v>2298</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>21.58</x:v>
+        <x:v>21.613</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>101255</x:v>
+        <x:v>4998</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0930840795013698</x:v>
+        <x:v>0.00340895060564257</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1255</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>18.292</x:v>
+        <x:v>22.699</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>80274</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>21.461</x:v>
+        <x:v>21.65</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>80184</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>21.52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>160458</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.147509606721947</x:v>
+        <x:v>2.72825178522815E-05</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>90</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>-31.367</x:v>
+        <x:v>21.65</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>21.65</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>0</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>0</x:v>
+        <x:v>21.607</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>40</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.67721414256559E-05</x:v>
+        <x:v>0.000330118466012606</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>40</x:v>
+        <x:v>-484</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>21.65</x:v>
+        <x:v>21.607</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>2075</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>21.92</x:v>
+        <x:v>21.519</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>2298</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>21.613</x:v>
+        <x:v>21.584</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>4373</x:v>
+        <x:v>3410</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00402011436135983</x:v>
+        <x:v>0.00232583464690699</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-223</x:v>
+        <x:v>-2124</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>18.762</x:v>
+        <x:v>21.603</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>0</x:v>
+        <x:v>6330</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0</x:v>
+        <x:v>21.36</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>484</x:v>
+        <x:v>8830</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>21.607</x:v>
+        <x:v>21.491</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>484</x:v>
+        <x:v>15160</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000444942911250437</x:v>
+        <x:v>0.0103400742660147</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-484</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>21.607</x:v>
+        <x:v>21.822</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>643</x:v>
+        <x:v>292997</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>21.519</x:v>
+        <x:v>21.521</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>2447</x:v>
+        <x:v>295928</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>21.585</x:v>
+        <x:v>21.599</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>3090</x:v>
+        <x:v>588925</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.00284064792513192</x:v>
+        <x:v>0.401683920653871</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-1804</x:v>
+        <x:v>-2931</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>21.608</x:v>
+        <x:v>29.411</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>6330</x:v>
+        <x:v>311467</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>21.36</x:v>
+        <x:v>21.497</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>8830</x:v>
+        <x:v>321105</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>21.491</x:v>
+        <x:v>21.537</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>15160</x:v>
+        <x:v>632572</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.0139366416003236</x:v>
+        <x:v>0.431453922071335</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-2500</x:v>
+        <x:v>-9638</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>21.822</x:v>
+        <x:v>22.804</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>280496</x:v>
+        <x:v>322851</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>21.668</x:v>
+        <x:v>21.669</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>290082</x:v>
+        <x:v>337414</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>21.56</x:v>
+        <x:v>21.538</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>570578</x:v>
+        <x:v>660265</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.524534372759198</x:v>
+        <x:v>0.450342291243415</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-9586</x:v>
+        <x:v>-14563</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>18.389</x:v>
+        <x:v>18.633</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>77266</x:v>
+        <x:v>313558</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>21.622</x:v>
+        <x:v>21.567</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>103999</x:v>
+        <x:v>338032</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>21.695</x:v>
+        <x:v>21.583</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>181265</x:v>
+        <x:v>651590</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.166637555388038</x:v>
+        <x:v>0.444425395184202</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-26733</x:v>
+        <x:v>-24474</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>21.908</x:v>
+        <x:v>21.787</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>1496758</x:v>
+        <x:v>1150206</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>21.658</x:v>
+        <x:v>21.584</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>1530382</x:v>
+        <x:v>1195343</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>21.659</x:v>
+        <x:v>21.642</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>3027140</x:v>
+        <x:v>2345549</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>2.7828605048815</x:v>
+        <x:v>1.59981206164752</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-33624</x:v>
+        <x:v>-45137</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>21.667</x:v>
+        <x:v>23.136</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>228113</x:v>
+        <x:v>4340452</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>21.591</x:v>
+        <x:v>21.659</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>262712</x:v>
+        <x:v>4393386</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>21.602</x:v>
+        <x:v>21.653</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>490825</x:v>
+        <x:v>8733838</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.451217157881189</x:v>
+        <x:v>5.95702727884835</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-34599</x:v>
+        <x:v>-52934</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>21.673</x:v>
+        <x:v>21.138</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>5851601</x:v>
+        <x:v>110563</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>21.661</x:v>
+        <x:v>21.546</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>5907536</x:v>
+        <x:v>168035</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>21.687</x:v>
+        <x:v>21.578</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>11759137</x:v>
+        <x:v>278598</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>10.8102162201916</x:v>
+        <x:v>0.190021372715248</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-55935</x:v>
+        <x:v>-57472</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>24.415</x:v>
+        <x:v>21.64</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>180143</x:v>
+        <x:v>188973</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>21.469</x:v>
+        <x:v>21.457</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>238083</x:v>
+        <x:v>288243</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>21.583</x:v>
+        <x:v>21.569</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>418226</x:v>
+        <x:v>477216</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.384476640497159</x:v>
+        <x:v>0.325491350984859</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-57940</x:v>
+        <x:v>-99270</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>21.939</x:v>
+        <x:v>21.782</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>498048</x:v>
+        <x:v>1857871</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>21.716</x:v>
+        <x:v>21.618</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>570348</x:v>
+        <x:v>1968767</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>21.736</x:v>
+        <x:v>21.608</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1068396</x:v>
+        <x:v>3826638</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.982180220265127</x:v>
+        <x:v>2.61000798873047</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-72300</x:v>
+        <x:v>-110896</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>21.877</x:v>
+        <x:v>21.442</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>150809</x:v>
+        <x:v>188940</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>21.554</x:v>
+        <x:v>21.521</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>260759</x:v>
+        <x:v>310344</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>21.598</x:v>
+        <x:v>21.564</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>411568</x:v>
+        <x:v>499284</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0.378355917556859</x:v>
+        <x:v>0.340543116083962</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-109950</x:v>
+        <x:v>-121404</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>21.66</x:v>
+        <x:v>21.632</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>782560</x:v>
+        <x:v>1347724</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>21.656</x:v>
+        <x:v>21.604</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>894208</x:v>
+        <x:v>1472044</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>21.663</x:v>
+        <x:v>21.585</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>1676768</x:v>
+        <x:v>2819768</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.54145875085036</x:v>
+        <x:v>1.9232592699823</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-111648</x:v>
+        <x:v>-124320</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>21.714</x:v>
+        <x:v>21.385</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>274932</x:v>
+        <x:v>2069052</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>21.566</x:v>
+        <x:v>21.576</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>418172</x:v>
+        <x:v>2210049</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>21.552</x:v>
+        <x:v>21.585</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>693104</x:v>
+        <x:v>4279101</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0.637172957767196</x:v>
+        <x:v>2.91861623560539</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-143240</x:v>
+        <x:v>-140997</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>21.526</x:v>
+        <x:v>21.715</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>1495929</x:v>
+        <x:v>476304</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>21.609</x:v>
+        <x:v>21.568</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>1748233</x:v>
+        <x:v>628783</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>21.625</x:v>
+        <x:v>21.53</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>3244162</x:v>
+        <x:v>1105087</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.98236959679347</x:v>
+        <x:v>0.753738895145604</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-252304</x:v>
+        <x:v>-152479</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>21.721</x:v>
+        <x:v>21.411</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>3346975</x:v>
+        <x:v>5047275</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>21.65</x:v>
+        <x:v>21.591</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>3623309</x:v>
+        <x:v>5392387</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>21.65</x:v>
+        <x:v>21.581</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>6970284</x:v>
+        <x:v>10439662</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>6.40780672562467</x:v>
+        <x:v>7.12050662216961</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-276334</x:v>
+        <x:v>-345112</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>21.651</x:v>
+        <x:v>21.441</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>1931778</x:v>
+        <x:v>2829966</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>21.649</x:v>
+        <x:v>21.578</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>2322231</x:v>
+        <x:v>3255200</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>21.625</x:v>
+        <x:v>21.564</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>4254009</x:v>
+        <x:v>6085166</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>3.91072551435033</x:v>
+        <x:v>4.1504662507274</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-390453</x:v>
+        <x:v>-425234</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>21.504</x:v>
+        <x:v>21.471</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>3218872</x:v>
+        <x:v>3793735</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>21.653</x:v>
+        <x:v>21.614</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>3664669</x:v>
+        <x:v>4458421</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>21.633</x:v>
+        <x:v>21.589</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>6883541</x:v>
+        <x:v>8252156</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>6.32806357903253</x:v>
+        <x:v>5.62848983474529</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-445797</x:v>
+        <x:v>-664686</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.485</x:v>
+        <x:v>21.445</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>4083686</x:v>
+        <x:v>5042914</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>21.698</x:v>
+        <x:v>21.653</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>5096013</x:v>
+        <x:v>6123370</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>21.636</x:v>
+        <x:v>21.595</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>9179699</x:v>
+        <x:v>11166284</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>8.43892974682381</x:v>
+        <x:v>7.61610856434112</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-1012327</x:v>
+        <x:v>-1080456</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>21.388</x:v>
+        <x:v>21.322</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -46,87 +46,90 @@
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
     <x:t>GCM</x:t>
   </x:si>
   <x:si>
@@ -148,6 +151,9 @@
     <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>NCM INVESTMENT</x:t>
   </x:si>
   <x:si>
@@ -160,34 +166,28 @@
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
+    <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BTCTURK</x:t>
+    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
     <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>MIDAS</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>7163915</x:v>
+        <x:v>7502087</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>21.579</x:v>
+        <x:v>21.5722228011504</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>6036577</x:v>
+        <x:v>6818138</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>21.588</x:v>
+        <x:v>21.5669018737684</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>13200492</x:v>
+        <x:v>14320225</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.00356646622246</x:v>
+        <x:v>9.25040770272964</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1127338</x:v>
+        <x:v>683949</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>21.531</x:v>
+        <x:v>21.625265962524</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>797608</x:v>
+        <x:v>963369</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>21.668</x:v>
+        <x:v>21.6244094762912</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>427600</x:v>
+        <x:v>438080</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>21.798</x:v>
+        <x:v>21.7881123169658</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1225208</x:v>
+        <x:v>1401449</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>0.835668978318951</x:v>
+        <x:v>0.905291266344122</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>370008</x:v>
+        <x:v>525289</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>21.518</x:v>
+        <x:v>21.4878847433486</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1373760</x:v>
+        <x:v>1899260</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>21.552</x:v>
+        <x:v>21.6293928837302</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1156449</x:v>
+        <x:v>1437992</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>21.554</x:v>
+        <x:v>21.6594071829404</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2530209</x:v>
+        <x:v>3337252</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.72576180531258</x:v>
+        <x:v>2.1557581397464</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>217311</x:v>
+        <x:v>461268</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>21.538</x:v>
+        <x:v>21.535824021052</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>889246</x:v>
+        <x:v>981541</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>21.583</x:v>
+        <x:v>21.5654413149014</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>683202</x:v>
+        <x:v>689063</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>21.679</x:v>
+        <x:v>21.6771210358338</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1572448</x:v>
+        <x:v>1670604</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.07250851579461</x:v>
+        <x:v>1.07915679466007</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>206044</x:v>
+        <x:v>292478</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>21.264</x:v>
+        <x:v>21.3023296841298</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>501994</x:v>
+        <x:v>1398916</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>21.73</x:v>
+        <x:v>21.5498292886169</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>318542</x:v>
+        <x:v>1178262</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>21.73</x:v>
+        <x:v>21.5530982966584</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>820536</x:v>
+        <x:v>2577178</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.55965720171099</x:v>
+        <x:v>1.66477462627196</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>183452</x:v>
+        <x:v>220654</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>21.731</x:v>
+        <x:v>21.5323732354609</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>2951717</x:v>
+        <x:v>513558</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>21.587</x:v>
+        <x:v>21.7217250615494</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2782942</x:v>
+        <x:v>343042</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>21.569</x:v>
+        <x:v>21.708913992044</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>5734659</x:v>
+        <x:v>856600</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.91139841360616</x:v>
+        <x:v>0.553336224686289</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>168775</x:v>
+        <x:v>170516</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>21.876</x:v>
+        <x:v>21.7474982142462</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>8670759</x:v>
+        <x:v>2962867</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>21.588</x:v>
+        <x:v>21.6147392145694</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>8555320</x:v>
+        <x:v>2806577</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>21.616</x:v>
+        <x:v>21.6421136060414</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>17226079</x:v>
+        <x:v>5769444</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>11.7492701960578</x:v>
+        <x:v>3.72687644349634</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>115439</x:v>
+        <x:v>156290</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>19.53</x:v>
+        <x:v>21.1231636979376</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>627334</x:v>
+        <x:v>9333985</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>21.571</x:v>
+        <x:v>21.5762747260503</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>514889</x:v>
+        <x:v>9195036</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>21.529</x:v>
+        <x:v>21.605773777051</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1142223</x:v>
+        <x:v>18529021</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.779067984719662</x:v>
+        <x:v>11.9691554135804</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>112445</x:v>
+        <x:v>138949</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>21.764</x:v>
+        <x:v>19.6241567840921</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>482913</x:v>
+        <x:v>6791299</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>21.665</x:v>
+        <x:v>21.5955214952772</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>370784</x:v>
+        <x:v>6663126</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>21.736</x:v>
+        <x:v>21.5936093779724</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>853697</x:v>
+        <x:v>13454425</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.582275091073478</x:v>
+        <x:v>8.69112857205793</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>112129</x:v>
+        <x:v>128173</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>21.431</x:v>
+        <x:v>21.6949236979939</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>3196702</x:v>
+        <x:v>634857</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>21.505</x:v>
+        <x:v>21.5692712263645</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>3096920</x:v>
+        <x:v>527130</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>21.484</x:v>
+        <x:v>21.5266281314673</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>6293622</x:v>
+        <x:v>1161987</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>4.29264636426278</x:v>
+        <x:v>0.750606467096132</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>99782</x:v>
+        <x:v>107727</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.152</x:v>
+        <x:v>21.7779325147428</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2167839</x:v>
+        <x:v>534002</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>21.489</x:v>
+        <x:v>21.6469132144204</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>2090730</x:v>
+        <x:v>433944</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>21.502</x:v>
+        <x:v>21.6872102752178</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>4258569</x:v>
+        <x:v>967946</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.90461211919181</x:v>
+        <x:v>0.625262182279004</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>77109</x:v>
+        <x:v>100058</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>21.135</x:v>
+        <x:v>21.4721479007958</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -909,25 +909,25 @@
         <x:v>207257</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>21.659</x:v>
+        <x:v>21.6588484427649</x:v>
       </x:c>
       <x:c r="D13" s="0">
         <x:v>131101</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>21.603</x:v>
+        <x:v>21.6028555668709</x:v>
       </x:c>
       <x:c r="F13" s="0">
         <x:v>338358</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.230781454386556</x:v>
+        <x:v>0.218568454719126</x:v>
       </x:c>
       <x:c r="H13" s="0">
         <x:v>76156</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>21.755</x:v>
+        <x:v>21.7552390360545</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1435332</x:v>
+        <x:v>2361896</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>21.671</x:v>
+        <x:v>21.4806146454905</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1366947</x:v>
+        <x:v>2297617</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>21.674</x:v>
+        <x:v>21.4922452719207</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>2802279</x:v>
+        <x:v>4659513</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>1.91133067111434</x:v>
+        <x:v>3.00989648878903</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>68385</x:v>
+        <x:v>64279</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>21.617</x:v>
+        <x:v>21.0648843913357</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>6426621</x:v>
+        <x:v>278587</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>21.604</x:v>
+        <x:v>21.535076733382</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>6360770</x:v>
+        <x:v>224335</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>21.6</x:v>
+        <x:v>21.5614827434621</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>12787391</x:v>
+        <x:v>502922</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>8.72180558104008</x:v>
+        <x:v>0.324871539565349</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>65851</x:v>
+        <x:v>54252</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>21.942</x:v>
+        <x:v>21.4258864312487</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>267067</x:v>
+        <x:v>827535</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>21.584</x:v>
+        <x:v>21.5069984454497</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>212903</x:v>
+        <x:v>773824</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>21.497</x:v>
+        <x:v>21.6258661112037</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>479970</x:v>
+        <x:v>1601359</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.327369752338988</x:v>
+        <x:v>1.03442673759913</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>54164</x:v>
+        <x:v>53711</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>21.924</x:v>
+        <x:v>19.7944506882969</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>273384</x:v>
+        <x:v>267079</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>21.539</x:v>
+        <x:v>21.5837028383612</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>220465</x:v>
+        <x:v>213412</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>21.563</x:v>
+        <x:v>21.4969223263789</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>493849</x:v>
+        <x:v>480491</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.336836103970784</x:v>
+        <x:v>0.310381830417627</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>52919</x:v>
+        <x:v>53667</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>21.436</x:v>
+        <x:v>21.9287939115192</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>51631</x:v>
+        <x:v>51651</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>21.589</x:v>
+        <x:v>21.5884606715765</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>376</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>21.723</x:v>
+        <x:v>21.7115151569097</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>52007</x:v>
+        <x:v>52047</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.03547204764859</x:v>
+        <x:v>0.0336206986764502</x:v>
       </x:c>
       <x:c r="H18" s="0">
         <x:v>51255</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>21.588</x:v>
+        <x:v>21.5875099433316</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>793743</x:v>
+        <x:v>3330254</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>21.512</x:v>
+        <x:v>21.5017844960068</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>744837</x:v>
+        <x:v>3280421</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>21.634</x:v>
+        <x:v>21.4825805804437</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>1538580</x:v>
+        <x:v>6610675</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.04940840792908</x:v>
+        <x:v>4.27028478534676</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>48906</x:v>
+        <x:v>49833</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>19.659</x:v>
+        <x:v>22.7659453511695</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1112,25 +1112,25 @@
         <x:v>48106</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>21.439</x:v>
+        <x:v>21.4390541871699</x:v>
       </x:c>
       <x:c r="D20" s="0">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>22.1</x:v>
+        <x:v>22.1000003814697</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>49106</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0334933830413533</x:v>
+        <x:v>0.0317209066652404</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>47106</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>21.425</x:v>
+        <x:v>21.4250231466592</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>571387</x:v>
+        <x:v>520155</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>21.708</x:v>
+        <x:v>21.60803431617</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>532937</x:v>
+        <x:v>482335</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>21.78</x:v>
+        <x:v>21.6366990532359</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1104324</x:v>
+        <x:v>1002490</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.753218481117572</x:v>
+        <x:v>0.647576502318186</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>38450</x:v>
+        <x:v>37820</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>20.702</x:v>
+        <x:v>21.2424603882824</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>302435</x:v>
+        <x:v>317616</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>21.549</x:v>
+        <x:v>21.5456205526952</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>264610</x:v>
+        <x:v>282977</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>21.578</x:v>
+        <x:v>21.5724159461697</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>567045</x:v>
+        <x:v>600593</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.386760383388673</x:v>
+        <x:v>0.387963884185165</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>37825</x:v>
+        <x:v>34639</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>21.344</x:v>
+        <x:v>21.3267204672646</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>290291</x:v>
+        <x:v>584120</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>21.449</x:v>
+        <x:v>21.7039936407653</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>259156</x:v>
+        <x:v>551174</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>21.464</x:v>
+        <x:v>21.7651955819074</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>549447</x:v>
+        <x:v>1135294</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.374757439659562</x:v>
+        <x:v>0.733363642153859</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>31135</x:v>
+        <x:v>32946</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>21.329</x:v>
+        <x:v>20.6801085346189</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>506853</x:v>
+        <x:v>310292</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>21.614</x:v>
+        <x:v>21.4429842061958</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>479072</x:v>
+        <x:v>279156</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>21.638</x:v>
+        <x:v>21.4668083135164</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>985925</x:v>
+        <x:v>589448</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.672462910337765</x:v>
+        <x:v>0.380764570358258</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>27781</x:v>
+        <x:v>31136</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>21.203</x:v>
+        <x:v>21.2293844341252</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>236268</x:v>
+        <x:v>2991566</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>21.752</x:v>
+        <x:v>21.5849824379754</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>210683</x:v>
+        <x:v>2963100</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>21.76</x:v>
+        <x:v>21.5636853866472</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>446951</x:v>
+        <x:v>5954666</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.304848715914876</x:v>
+        <x:v>3.846523936152</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>25585</x:v>
+        <x:v>28466</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>21.689</x:v>
+        <x:v>23.8018479192784</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>310128</x:v>
+        <x:v>310129</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>21.401</x:v>
+        <x:v>21.4010746723035</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>288275</x:v>
+        <x:v>288885</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>21.412</x:v>
+        <x:v>21.4115445580032</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>598403</x:v>
+        <x:v>599014</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.40814851325897</x:v>
+        <x:v>0.386943900647014</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>21853</x:v>
+        <x:v>21244</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>21.263</x:v>
+        <x:v>21.2587006876325</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>197456</x:v>
+        <x:v>357801</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>21.553</x:v>
+        <x:v>21.5480575159478</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>186465</x:v>
+        <x:v>341612</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>21.534</x:v>
+        <x:v>21.5828062266838</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>383921</x:v>
+        <x:v>699413</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.261858288409144</x:v>
+        <x:v>0.451798446085117</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>10991</x:v>
+        <x:v>16189</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>21.879</x:v>
+        <x:v>20.8148079902234</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>19792</x:v>
+        <x:v>197456</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>21.516</x:v>
+        <x:v>21.5531577598275</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>11999</x:v>
+        <x:v>186465</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>21.548</x:v>
+        <x:v>21.5339610732686</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>31791</x:v>
+        <x:v>383921</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.021683463126047</x:v>
+        <x:v>0.248000696611936</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>7793</x:v>
+        <x:v>10991</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>21.467</x:v>
+        <x:v>21.8788342368732</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>52182</x:v>
+        <x:v>236306</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>21.602</x:v>
+        <x:v>21.7520048790139</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>45351</x:v>
+        <x:v>228306</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>21.609</x:v>
+        <x:v>21.7327017344387</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>97533</x:v>
+        <x:v>464612</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0665236453421642</x:v>
+        <x:v>0.300124503880395</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>6831</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>21.554</x:v>
+        <x:v>22.3028828446865</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>2736468</x:v>
+        <x:v>19794</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>21.635</x:v>
+        <x:v>21.5164320926371</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>2731275</x:v>
+        <x:v>11999</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>21.647</x:v>
+        <x:v>21.548297297588</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>5467743</x:v>
+        <x:v>31793</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>3.72934490022967</x:v>
+        <x:v>0.0205372619559318</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>5193</x:v>
+        <x:v>7795</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>15.164</x:v>
+        <x:v>21.4673813428995</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>6666</x:v>
+        <x:v>52182</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>21.712</x:v>
+        <x:v>21.6015726275673</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2170</x:v>
+        <x:v>47351</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>21.806</x:v>
+        <x:v>21.6016711591755</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>8836</x:v>
+        <x:v>99533</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00602670819356897</x:v>
+        <x:v>0.0642951371138225</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>4496</x:v>
+        <x:v>4831</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>21.666</x:v>
+        <x:v>21.6006068709572</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>4347</x:v>
+        <x:v>6759</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>21.496</x:v>
+        <x:v>21.7098742111281</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1440</x:v>
+        <x:v>2170</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>21.681</x:v>
+        <x:v>21.8065437105944</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>5787</x:v>
+        <x:v>8929</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00394709827027882</x:v>
+        <x:v>0.00576784864607036</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>2907</x:v>
+        <x:v>4589</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>21.404</x:v>
+        <x:v>21.6641621139736</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>51255</x:v>
+        <x:v>4347</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>21.5</x:v>
+        <x:v>21.4956705866942</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>50000</x:v>
+        <x:v>1440</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>21.58</x:v>
+        <x:v>21.6813891728719</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>101255</x:v>
+        <x:v>5787</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.069062283628319</x:v>
+        <x:v>0.00373821705843982</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>1255</x:v>
+        <x:v>2907</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>18.292</x:v>
+        <x:v>21.4036737638197</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>2700</x:v>
+        <x:v>51255</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>21.775</x:v>
+        <x:v>21.4995102804703</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>2298</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>21.613</x:v>
+        <x:v>21.5799999237061</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>4998</x:v>
+        <x:v>101255</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00340895060564257</x:v>
+        <x:v>0.0654074940819638</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>402</x:v>
+        <x:v>1255</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>22.699</x:v>
+        <x:v>18.2927515858198</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>40</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>21.65</x:v>
+        <x:v>21.7748144114459</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>0</x:v>
+        <x:v>2298</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>0</x:v>
+        <x:v>21.613186020349</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>40</x:v>
+        <x:v>4998</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.72825178522815E-05</x:v>
+        <x:v>0.00322854827338556</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>40</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>21.65</x:v>
+        <x:v>22.6987498411492</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>21.6500000953674</x:v>
+      </x:c>
+      <x:c r="D36" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C36" s="0">
+      <x:c r="E36" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D36" s="0">
-        <x:v>484</x:v>
-      </x:c>
-      <x:c r="E36" s="0">
-        <x:v>21.607</x:v>
-      </x:c>
       <x:c r="F36" s="0">
-        <x:v>484</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.000330118466012606</x:v>
+        <x:v>2.58387216757548E-05</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-484</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>21.607</x:v>
+        <x:v>21.6500000953674</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>643</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>21.519</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>2767</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>21.584</x:v>
+        <x:v>21.6071076196087</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>3410</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00232583464690699</x:v>
+        <x:v>0.000312648532276633</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-2124</x:v>
+        <x:v>-484</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.603</x:v>
+        <x:v>21.6071076196087</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>6330</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>21.36</x:v>
+        <x:v>21.5198131430761</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>8830</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>21.491</x:v>
+        <x:v>21.5836574298016</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>15160</x:v>
+        <x:v>3410</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.0103400742660147</x:v>
+        <x:v>0.0022027510228581</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-2500</x:v>
+        <x:v>-2124</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>21.822</x:v>
+        <x:v>21.6029850552087</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>292997</x:v>
+        <x:v>1262167</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>21.521</x:v>
+        <x:v>21.5757742289157</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>295928</x:v>
+        <x:v>1264343</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>21.599</x:v>
+        <x:v>21.6290822852525</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>588925</x:v>
+        <x:v>2526510</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.401683920653871</x:v>
+        <x:v>1.63204471752528</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-2931</x:v>
+        <x:v>-2176</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>29.411</x:v>
+        <x:v>52.5498863029129</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>311467</x:v>
+        <x:v>6330</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>21.497</x:v>
+        <x:v>21.3600006103516</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>321105</x:v>
+        <x:v>8830</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>21.537</x:v>
+        <x:v>21.4905997586277</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>632572</x:v>
+        <x:v>15160</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.431453922071335</x:v>
+        <x:v>0.00979287551511106</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-9638</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>22.804</x:v>
+        <x:v>21.821276802063</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>322851</x:v>
+        <x:v>293147</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>21.669</x:v>
+        <x:v>21.5207093270676</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>337414</x:v>
+        <x:v>295988</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>21.538</x:v>
+        <x:v>21.5988947222091</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>660265</x:v>
+        <x:v>589135</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.450342291243415</x:v>
+        <x:v>0.380562382361145</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-14563</x:v>
+        <x:v>-2841</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>18.633</x:v>
+        <x:v>29.6664111000767</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>313558</x:v>
+        <x:v>313608</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>21.567</x:v>
+        <x:v>21.4967474134925</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>338032</x:v>
+        <x:v>323105</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>21.583</x:v>
+        <x:v>21.5366614516249</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>651590</x:v>
+        <x:v>636713</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.444425395184202</x:v>
+        <x:v>0.411296249858372</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-24474</x:v>
+        <x:v>-9497</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>21.787</x:v>
+        <x:v>22.8546946906059</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>1150206</x:v>
+        <x:v>323351</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>21.584</x:v>
+        <x:v>21.6683187751746</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>1195343</x:v>
+        <x:v>359064</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>21.642</x:v>
+        <x:v>21.530175917523</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>2345549</x:v>
+        <x:v>682415</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.59981206164752</x:v>
+        <x:v>0.440818281309005</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-45137</x:v>
+        <x:v>-35713</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>23.136</x:v>
+        <x:v>20.2794092173164</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>4340452</x:v>
+        <x:v>110757</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>21.659</x:v>
+        <x:v>21.5453717976138</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>4393386</x:v>
+        <x:v>168414</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>21.653</x:v>
+        <x:v>21.5775929544797</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>8733838</x:v>
+        <x:v>279171</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>5.95702727884835</x:v>
+        <x:v>0.180335544223554</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-52934</x:v>
+        <x:v>-57657</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>21.138</x:v>
+        <x:v>21.6394886249272</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>110563</x:v>
+        <x:v>4525590</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>21.546</x:v>
+        <x:v>21.6508106641132</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>168035</x:v>
+        <x:v>4605447</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>21.578</x:v>
+        <x:v>21.6439023628976</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>278598</x:v>
+        <x:v>9131037</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.190021372715248</x:v>
+        <x:v>5.89835809135048</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-57472</x:v>
+        <x:v>-79857</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>21.64</x:v>
+        <x:v>21.2524008176552</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>188973</x:v>
+        <x:v>199592</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>21.457</x:v>
+        <x:v>21.4533537026756</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>288243</x:v>
+        <x:v>288333</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>21.569</x:v>
+        <x:v>21.569209027105</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>477216</x:v>
+        <x:v>487925</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.325491350984859</x:v>
+        <x:v>0.315183956841066</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-99270</x:v>
+        <x:v>-88741</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>21.782</x:v>
+        <x:v>21.8297852648477</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1857871</x:v>
+        <x:v>193978</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>21.618</x:v>
+        <x:v>21.5183871945458</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1968767</x:v>
+        <x:v>311053</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>21.608</x:v>
+        <x:v>21.5640711729436</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>3826638</x:v>
+        <x:v>505031</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>2.61000798873047</x:v>
+        <x:v>0.326233886165703</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-110896</x:v>
+        <x:v>-117075</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>21.442</x:v>
+        <x:v>21.6397635646725</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>188940</x:v>
+        <x:v>1883031</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>21.521</x:v>
+        <x:v>21.6157824343282</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>310344</x:v>
+        <x:v>2000833</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>21.564</x:v>
+        <x:v>21.6056809250969</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>499284</x:v>
+        <x:v>3883864</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0.340543116083962</x:v>
+        <x:v>2.50885202306209</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-121404</x:v>
+        <x:v>-117802</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>21.632</x:v>
+        <x:v>21.4442112129578</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>1347724</x:v>
+        <x:v>480407</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>21.604</x:v>
+        <x:v>21.5665729399198</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1472044</x:v>
+        <x:v>638461</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>21.585</x:v>
+        <x:v>21.528475122114</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>2819768</x:v>
+        <x:v>1118868</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.9232592699823</x:v>
+        <x:v>0.72275297109771</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-124320</x:v>
+        <x:v>-158054</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>21.385</x:v>
+        <x:v>21.412676354866</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2069052</x:v>
+        <x:v>1393839</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>21.576</x:v>
+        <x:v>21.5982369831965</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2210049</x:v>
+        <x:v>1599773</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>21.585</x:v>
+        <x:v>21.5722227419881</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>4279101</x:v>
+        <x:v>2993612</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>2.91861623560539</x:v>
+        <x:v>1.93377768182999</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-140997</x:v>
+        <x:v>-205934</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>21.715</x:v>
+        <x:v>21.3961485436933</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>476304</x:v>
+        <x:v>2148860</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>21.568</x:v>
+        <x:v>21.569831241609</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>628783</x:v>
+        <x:v>2364772</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>21.53</x:v>
+        <x:v>21.5740950486189</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1105087</x:v>
+        <x:v>4513632</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>0.753738895145604</x:v>
+        <x:v>2.91566202486951</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-152479</x:v>
+        <x:v>-215912</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>21.411</x:v>
+        <x:v>21.6165305053394</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>5047275</x:v>
+        <x:v>5314967</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>21.591</x:v>
+        <x:v>21.5834407093252</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>5392387</x:v>
+        <x:v>5699515</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>21.581</x:v>
+        <x:v>21.571794500402</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>10439662</x:v>
+        <x:v>11014482</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>7.12050662216961</x:v>
+        <x:v>7.11500337001527</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-345112</x:v>
+        <x:v>-384548</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>21.441</x:v>
+        <x:v>21.4108283372657</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>2829966</x:v>
+        <x:v>2957305</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>21.578</x:v>
+        <x:v>21.5713895375883</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>3255200</x:v>
+        <x:v>3414897</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>21.564</x:v>
+        <x:v>21.5591675947877</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>6085166</x:v>
+        <x:v>6372202</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>4.1504662507274</x:v>
+        <x:v>4.1162388484922</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-425234</x:v>
+        <x:v>-457592</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>21.471</x:v>
+        <x:v>21.4801801724685</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>3793735</x:v>
+        <x:v>3909376</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>21.614</x:v>
+        <x:v>21.6081370944924</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>4458421</x:v>
+        <x:v>4649975</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>21.589</x:v>
+        <x:v>21.5814985219129</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>8252156</x:v>
+        <x:v>8559351</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>5.62848983474529</x:v>
+        <x:v>5.52906720535234</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-664686</x:v>
+        <x:v>-740599</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.445</x:v>
+        <x:v>21.4408823499809</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>5042914</x:v>
+        <x:v>5235638</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>21.653</x:v>
+        <x:v>21.6446212388135</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>6123370</x:v>
+        <x:v>6235392</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>21.595</x:v>
+        <x:v>21.5921596275188</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>11166284</x:v>
+        <x:v>11471030</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>7.61610856434112</x:v>
+        <x:v>7.40991878760584</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-1080456</x:v>
+        <x:v>-999754</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>21.322</x:v>
+        <x:v>21.3174220364359</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,163 +40,163 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>7502087</x:v>
+        <x:v>6967792</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>21.5722228011504</x:v>
+        <x:v>21.5008604769199</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>6818138</x:v>
+        <x:v>6212678</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>21.5669018737684</x:v>
+        <x:v>21.5508809371555</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>14320225</x:v>
+        <x:v>13180470</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>9.25040770272964</x:v>
+        <x:v>6.44512582784151</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>683949</x:v>
+        <x:v>755114</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>21.625265962524</x:v>
+        <x:v>21.0893186264771</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>963369</x:v>
+        <x:v>2368212</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>21.6244094762912</x:v>
+        <x:v>21.5710804803595</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>438080</x:v>
+        <x:v>1672417</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>21.7881123169658</x:v>
+        <x:v>21.6032825677815</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1401449</x:v>
+        <x:v>4040629</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>0.905291266344122</x:v>
+        <x:v>1.9758295666714</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>525289</x:v>
+        <x:v>695795</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>21.4878847433486</x:v>
+        <x:v>21.493679351521</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1899260</x:v>
+        <x:v>1375458</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>21.6293928837302</x:v>
+        <x:v>21.5335567048007</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1437992</x:v>
+        <x:v>724807</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>21.6594071829404</x:v>
+        <x:v>21.5419444569062</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>3337252</x:v>
+        <x:v>2100265</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.1557581397464</x:v>
+        <x:v>1.0270098256596</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>461268</x:v>
+        <x:v>650651</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>21.535824021052</x:v>
+        <x:v>21.5242129837579</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>981541</x:v>
+        <x:v>1311023</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>21.5654413149014</x:v>
+        <x:v>21.4858959403886</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>689063</x:v>
+        <x:v>821722</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>21.6771210358338</x:v>
+        <x:v>21.6120536286655</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1670604</x:v>
+        <x:v>2132745</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.07915679466007</x:v>
+        <x:v>1.04289224008703</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>292478</x:v>
+        <x:v>489301</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>21.3023296841298</x:v>
+        <x:v>21.2740293226498</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>1398916</x:v>
+        <x:v>718365</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>21.5498292886169</x:v>
+        <x:v>21.3334941733939</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1178262</x:v>
+        <x:v>347034</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>21.5530982966584</x:v>
+        <x:v>21.3831116055107</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>2577178</x:v>
+        <x:v>1065399</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.66477462627196</x:v>
+        <x:v>0.520970087702223</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>220654</x:v>
+        <x:v>371331</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>21.5323732354609</x:v>
+        <x:v>21.2871233184499</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>513558</x:v>
+        <x:v>4233574</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>21.7217250615494</x:v>
+        <x:v>21.4780165516915</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>343042</x:v>
+        <x:v>3885125</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>21.708913992044</x:v>
+        <x:v>21.4888214594827</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>856600</x:v>
+        <x:v>8118699</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.553336224686289</x:v>
+        <x:v>3.96996743009703</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>170516</x:v>
+        <x:v>348449</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>21.7474982142462</x:v>
+        <x:v>21.357544352368</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>2962867</x:v>
+        <x:v>3826747</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>21.6147392145694</x:v>
+        <x:v>21.5204548855105</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>2806577</x:v>
+        <x:v>3616946</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>21.6421136060414</x:v>
+        <x:v>21.5518259653337</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>5769444</x:v>
+        <x:v>7443693</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>3.72687644349634</x:v>
+        <x:v>3.63989584656868</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>156290</x:v>
+        <x:v>209801</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>21.1231636979376</x:v>
+        <x:v>20.9796209443831</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>9333985</x:v>
+        <x:v>716591</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>21.5762747260503</x:v>
+        <x:v>21.5857956691771</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>9195036</x:v>
+        <x:v>530044</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>21.605773777051</x:v>
+        <x:v>21.5055221912866</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>18529021</x:v>
+        <x:v>1246635</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>11.9691554135804</x:v>
+        <x:v>0.609592786629855</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>138949</x:v>
+        <x:v>186547</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>19.6241567840921</x:v>
+        <x:v>21.8138801482359</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>6791299</x:v>
+        <x:v>1793729</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>21.5955214952772</x:v>
+        <x:v>21.474917835852</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>6663126</x:v>
+        <x:v>1643004</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>21.5936093779724</x:v>
+        <x:v>21.4439171130242</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>13454425</x:v>
+        <x:v>3436733</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>8.69112857205793</x:v>
+        <x:v>1.68053010413857</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>128173</x:v>
+        <x:v>150725</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>21.6949236979939</x:v>
+        <x:v>21.8128465909289</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>634857</x:v>
+        <x:v>717704</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>21.5692712263645</x:v>
+        <x:v>21.5284033772401</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>527130</x:v>
+        <x:v>586465</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>21.5266281314673</x:v>
+        <x:v>21.5034741416722</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>1161987</x:v>
+        <x:v>1304169</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.750606467096132</x:v>
+        <x:v>0.637726371348688</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>107727</x:v>
+        <x:v>131239</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>21.7779325147428</x:v>
+        <x:v>21.6398041356832</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>534002</x:v>
+        <x:v>8907748</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>21.6469132144204</x:v>
+        <x:v>21.5219939637992</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>433944</x:v>
+        <x:v>8785424</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>21.6872102752178</x:v>
+        <x:v>21.5168483935446</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>967946</x:v>
+        <x:v>17693172</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.625262182279004</x:v>
+        <x:v>8.6517946502395</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>100058</x:v>
+        <x:v>122324</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>21.4721479007958</x:v>
+        <x:v>21.8915536283671</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>207257</x:v>
+        <x:v>1042297</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>21.6588484427649</x:v>
+        <x:v>21.4816621723394</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>131101</x:v>
+        <x:v>935064</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>21.6028555668709</x:v>
+        <x:v>21.516863005334</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>338358</x:v>
+        <x:v>1977361</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.218568454719126</x:v>
+        <x:v>0.966910925943196</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>76156</x:v>
+        <x:v>107233</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>21.7552390360545</x:v>
+        <x:v>21.1747134559625</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>2361896</x:v>
+        <x:v>1002108</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>21.4806146454905</x:v>
+        <x:v>21.4614781370914</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>2297617</x:v>
+        <x:v>911091</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>21.4922452719207</x:v>
+        <x:v>21.5713304521858</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>4659513</x:v>
+        <x:v>1913199</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>3.00989648878903</x:v>
+        <x:v>0.935536311580737</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>64279</x:v>
+        <x:v>91017</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>21.0648843913357</x:v>
+        <x:v>20.3618433918058</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>278587</x:v>
+        <x:v>354814</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>21.535076733382</x:v>
+        <x:v>21.4750618539334</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>224335</x:v>
+        <x:v>264322</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>21.5614827434621</x:v>
+        <x:v>21.5132372140147</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>502922</x:v>
+        <x:v>619136</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.324871539565349</x:v>
+        <x:v>0.302751679154574</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>54252</x:v>
+        <x:v>90492</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>21.4258864312487</x:v>
+        <x:v>21.3635537921447</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>827535</x:v>
+        <x:v>207357</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>21.5069984454497</x:v>
+        <x:v>21.6586657396219</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>773824</x:v>
+        <x:v>131101</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>21.6258661112037</x:v>
+        <x:v>21.6028555668709</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>1601359</x:v>
+        <x:v>338458</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>1.03442673759913</x:v>
+        <x:v>0.165502777779516</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>53711</x:v>
+        <x:v>76256</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>19.7944506882969</x:v>
+        <x:v>21.7546158216853</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>267079</x:v>
+        <x:v>419171</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>21.5837028383612</x:v>
+        <x:v>21.4091326251942</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>213412</x:v>
+        <x:v>343530</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>21.4969223263789</x:v>
+        <x:v>21.4064889430958</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>480491</x:v>
+        <x:v>762701</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.310381830417627</x:v>
+        <x:v>0.372953613491822</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>53667</x:v>
+        <x:v>75641</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>21.9287939115192</x:v>
+        <x:v>21.4211391310742</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>51651</x:v>
+        <x:v>4996380</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>21.5884606715765</x:v>
+        <x:v>21.4199115868877</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>396</x:v>
+        <x:v>4931067</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>21.7115151569097</x:v>
+        <x:v>21.4003480352627</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>52047</x:v>
+        <x:v>9927447</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0336206986764502</x:v>
+        <x:v>4.85442818535513</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>51255</x:v>
+        <x:v>65313</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>21.5875099433316</x:v>
+        <x:v>22.8969404145441</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>3330254</x:v>
+        <x:v>69784</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>21.5017844960068</x:v>
+        <x:v>21.5102119178492</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>3280421</x:v>
+        <x:v>9031</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>21.4825805804437</x:v>
+        <x:v>21.1289959426946</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>6610675</x:v>
+        <x:v>78815</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>4.27028478534676</x:v>
+        <x:v>0.0385397935067057</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>49833</x:v>
+        <x:v>60753</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>22.7659453511695</x:v>
+        <x:v>21.5668800901472</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>48106</x:v>
+        <x:v>432343</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>21.4390541871699</x:v>
+        <x:v>21.5043109519884</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>1000</x:v>
+        <x:v>397969</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>22.1000003814697</x:v>
+        <x:v>21.5350312487893</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>49106</x:v>
+        <x:v>830312</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0317209066652404</x:v>
+        <x:v>0.406014756406012</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>47106</x:v>
+        <x:v>34374</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>21.4250231466592</x:v>
+        <x:v>21.1486431275417</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>520155</x:v>
+        <x:v>381358</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>21.60803431617</x:v>
+        <x:v>21.4446631292994</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>482335</x:v>
+        <x:v>347467</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>21.6366990532359</x:v>
+        <x:v>21.3645011382338</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1002490</x:v>
+        <x:v>728825</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.647576502318186</x:v>
+        <x:v>0.356388568197992</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>37820</x:v>
+        <x:v>33891</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>21.2424603882824</x:v>
+        <x:v>22.2665228132746</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>317616</x:v>
+        <x:v>53122</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>21.5456205526952</x:v>
+        <x:v>21.429646878666</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>282977</x:v>
+        <x:v>27550</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>21.5724159461697</x:v>
+        <x:v>21.3094009496339</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>600593</x:v>
+        <x:v>80672</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.387963884185165</x:v>
+        <x:v>0.0394478490360079</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>34639</x:v>
+        <x:v>25572</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>21.3267204672646</x:v>
+        <x:v>21.5591938575817</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>584120</x:v>
+        <x:v>578898</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>21.7039936407653</x:v>
+        <x:v>21.5715699138351</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>551174</x:v>
+        <x:v>559707</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>21.7651955819074</x:v>
+        <x:v>21.5756631874025</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1135294</x:v>
+        <x:v>1138605</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.733363642153859</x:v>
+        <x:v>0.556767132978527</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>32946</x:v>
+        <x:v>19191</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>20.6801085346189</x:v>
+        <x:v>21.4521892735053</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>310292</x:v>
+        <x:v>298457</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>21.4429842061958</x:v>
+        <x:v>21.4770014085941</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>279156</x:v>
+        <x:v>281710</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>21.4668083135164</x:v>
+        <x:v>21.4665622615378</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>589448</x:v>
+        <x:v>580167</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.380764570358258</x:v>
+        <x:v>0.283696204775803</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>31136</x:v>
+        <x:v>16747</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>21.2293844341252</x:v>
+        <x:v>21.652603732427</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>2991566</x:v>
+        <x:v>69815</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>21.5849824379754</x:v>
+        <x:v>21.4841263681242</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>2963100</x:v>
+        <x:v>56369</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>21.5636853866472</x:v>
+        <x:v>21.5351999966646</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>5954666</x:v>
+        <x:v>126184</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>3.846523936152</x:v>
+        <x:v>0.0617027888580873</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>28466</x:v>
+        <x:v>13446</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23.8018479192784</x:v>
+        <x:v>21.2700129241864</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>310129</x:v>
+        <x:v>2887590</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>21.4010746723035</x:v>
+        <x:v>21.4432096069415</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>288885</x:v>
+        <x:v>2874608</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>21.4115445580032</x:v>
+        <x:v>21.4478046847375</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>599014</x:v>
+        <x:v>5762198</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.386943900647014</x:v>
+        <x:v>2.81766061111149</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>21244</x:v>
+        <x:v>12982</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>21.2587006876325</x:v>
+        <x:v>20.425720206763</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>357801</x:v>
+        <x:v>307572</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>21.5480575159478</x:v>
+        <x:v>21.3767722236435</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>341612</x:v>
+        <x:v>299488</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>21.5828062266838</x:v>
+        <x:v>21.553554672839</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>699413</x:v>
+        <x:v>607060</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.451798446085117</x:v>
+        <x:v>0.296846628765853</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>16189</x:v>
+        <x:v>8084</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>20.8148079902234</x:v>
+        <x:v>14.8275116911505</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>197456</x:v>
+        <x:v>6759</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>21.5531577598275</x:v>
+        <x:v>21.7098742111281</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>186465</x:v>
+        <x:v>2170</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>21.5339610732686</x:v>
+        <x:v>21.8065437105944</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>383921</x:v>
+        <x:v>8929</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.248000696611936</x:v>
+        <x:v>0.00436619699576698</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>10991</x:v>
+        <x:v>4589</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>21.8788342368732</x:v>
+        <x:v>21.6641621139736</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>236306</x:v>
+        <x:v>328289</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>21.7520048790139</x:v>
+        <x:v>21.4811371676101</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>228306</x:v>
+        <x:v>323765</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>21.7327017344387</x:v>
+        <x:v>21.5653763715253</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>464612</x:v>
+        <x:v>652054</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.300124503880395</x:v>
+        <x:v>0.318848271461288</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>8000</x:v>
+        <x:v>4524</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>22.3028828446865</x:v>
+        <x:v>15.4524665540768</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>19794</x:v>
+        <x:v>624345</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>21.5164320926371</x:v>
+        <x:v>21.600301965135</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>11999</x:v>
+        <x:v>621789</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>21.548297297588</x:v>
+        <x:v>21.5219125927023</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>31793</x:v>
+        <x:v>1246134</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0205372619559318</x:v>
+        <x:v>0.609347802343274</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>7795</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>21.4673813428995</x:v>
+        <x:v>40.6698048976665</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>52182</x:v>
+        <x:v>409347</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>21.6015726275673</x:v>
+        <x:v>21.4153756697719</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>47351</x:v>
+        <x:v>406964</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>21.6016711591755</x:v>
+        <x:v>21.4476472382497</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>99533</x:v>
+        <x:v>816311</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0642951371138225</x:v>
+        <x:v>0.399168399127735</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>4831</x:v>
+        <x:v>2383</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>21.6006068709572</x:v>
+        <x:v>15.9041013961773</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>6759</x:v>
+        <x:v>101255</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>21.7098742111281</x:v>
+        <x:v>21.3249460660842</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2170</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>21.8065437105944</x:v>
+        <x:v>21.3540000915527</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>8929</x:v>
+        <x:v>201255</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00576784864607036</x:v>
+        <x:v>0.0984118015884292</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>4589</x:v>
+        <x:v>1255</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>21.6641621139736</x:v>
+        <x:v>19.0098842757632</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1492,22 +1492,22 @@
         <x:v>21.4956705866942</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>1440</x:v>
+        <x:v>3440</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>21.6813891728719</x:v>
+        <x:v>21.3433724336846</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>5787</x:v>
+        <x:v>7787</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00373821705843982</x:v>
+        <x:v>0.00380776973972869</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>2907</x:v>
+        <x:v>907</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>21.4036737638197</x:v>
+        <x:v>22.0732953346025</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>51255</x:v>
+        <x:v>3370</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>21.4995102804703</x:v>
+        <x:v>21.6444508668577</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>50000</x:v>
+        <x:v>2956</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>21.5799999237061</x:v>
+        <x:v>21.5190263265525</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>101255</x:v>
+        <x:v>6326</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0654074940819638</x:v>
+        <x:v>0.00309335448484959</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1255</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>18.2927515858198</x:v>
+        <x:v>22.5399942029502</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>2700</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>21.7748144114459</x:v>
+        <x:v>21.6500000953674</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>2298</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>21.613186020349</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>4998</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00322854827338556</x:v>
+        <x:v>1.95596236790995E-05</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>402</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>22.6987498411492</x:v>
+        <x:v>21.6500000953674</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>40</x:v>
+        <x:v>998</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>21.6500000953674</x:v>
+        <x:v>21.3661722420213</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>0</x:v>
+        <x:v>3501</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>0</x:v>
+        <x:v>21.4909570362186</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>40</x:v>
+        <x:v>4499</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.58387216757548E-05</x:v>
+        <x:v>0.00219996867330672</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>40</x:v>
+        <x:v>-2503</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>21.6500000953674</x:v>
+        <x:v>21.5407114208007</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>0</x:v>
+        <x:v>6330</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0</x:v>
+        <x:v>21.3600006103516</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>484</x:v>
+        <x:v>9030</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>21.6071076196087</x:v>
+        <x:v>21.4841634575051</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>484</x:v>
+        <x:v>15360</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.000312648532276633</x:v>
+        <x:v>0.0075108954927742</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-484</x:v>
+        <x:v>-2700</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.6071076196087</x:v>
+        <x:v>21.7752563547205</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>643</x:v>
+        <x:v>26452</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>21.5198131430761</x:v>
+        <x:v>21.416082503124</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>2767</x:v>
+        <x:v>30903</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>21.5836574298016</x:v>
+        <x:v>21.3384831993918</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>3410</x:v>
+        <x:v>57355</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.0022027510228581</x:v>
+        <x:v>0.0280460554028688</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-2124</x:v>
+        <x:v>-4451</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>21.6029850552087</x:v>
+        <x:v>20.8773156455114</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>1262167</x:v>
+        <x:v>257785</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>21.5757742289157</x:v>
+        <x:v>21.708959472064</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>1264343</x:v>
+        <x:v>267085</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>21.6290822852525</x:v>
+        <x:v>21.6605481833747</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>2526510</x:v>
+        <x:v>524870</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>1.63204471752528</x:v>
+        <x:v>0.256656492011224</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-2176</x:v>
+        <x:v>-9300</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>52.5498863029129</x:v>
+        <x:v>20.3186445215697</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>6330</x:v>
+        <x:v>456500</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>21.3600006103516</x:v>
+        <x:v>21.4518637424231</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>8830</x:v>
+        <x:v>467527</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>21.4905997586277</x:v>
+        <x:v>21.4433678981204</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>15160</x:v>
+        <x:v>924027</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.00979287551511106</x:v>
+        <x:v>0.451840509733182</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-2500</x:v>
+        <x:v>-11027</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>21.821276802063</x:v>
+        <x:v>21.0916536581465</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>293147</x:v>
+        <x:v>367783</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>21.5207093270676</x:v>
+        <x:v>21.6063447199621</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>295988</x:v>
+        <x:v>396609</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>21.5988947222091</x:v>
+        <x:v>21.4912540883214</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>589135</x:v>
+        <x:v>764392</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.380562382361145</x:v>
+        <x:v>0.373780496582856</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-2841</x:v>
+        <x:v>-28826</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>29.6664111000767</x:v>
+        <x:v>20.0228443964907</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>313608</x:v>
+        <x:v>149248</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>21.4967474134925</x:v>
+        <x:v>21.4389067758034</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>323105</x:v>
+        <x:v>197616</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>21.5366614516249</x:v>
+        <x:v>21.5156049252174</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>636713</x:v>
+        <x:v>346864</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.411296249858372</x:v>
+        <x:v>0.169613232695679</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-9497</x:v>
+        <x:v>-48368</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>22.8546946906059</x:v>
+        <x:v>21.752270600948</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>323351</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>21.6683187751746</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>359064</x:v>
+        <x:v>60484</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>21.530175917523</x:v>
+        <x:v>21.1575978980258</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>682415</x:v>
+        <x:v>60484</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.440818281309005</x:v>
+        <x:v>0.0295761069651664</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-35713</x:v>
+        <x:v>-60484</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>20.2794092173164</x:v>
+        <x:v>21.1575978980258</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>110757</x:v>
+        <x:v>3081119</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>21.5453717976138</x:v>
+        <x:v>21.4569592628097</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>168414</x:v>
+        <x:v>3164954</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>21.5775929544797</x:v>
+        <x:v>21.4873061916106</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>279171</x:v>
+        <x:v>6246073</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.180335544223554</x:v>
+        <x:v>3.0542709338046</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-57657</x:v>
+        <x:v>-83835</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>21.6394886249272</x:v>
+        <x:v>22.6026219776195</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>4525590</x:v>
+        <x:v>294061</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>21.6508106641132</x:v>
+        <x:v>21.4182377528617</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>4605447</x:v>
+        <x:v>416436</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>21.6439023628976</x:v>
+        <x:v>21.4726322662392</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>9131037</x:v>
+        <x:v>710497</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>5.89835809135048</x:v>
+        <x:v>0.347426348628229</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-79857</x:v>
+        <x:v>-122375</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>21.2524008176552</x:v>
+        <x:v>21.6033395593817</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>199592</x:v>
+        <x:v>601888</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>21.4533537026756</x:v>
+        <x:v>21.4919898558908</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>288333</x:v>
+        <x:v>763376</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>21.569209027105</x:v>
+        <x:v>21.4913896001684</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>487925</x:v>
+        <x:v>1365264</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.315183956841066</x:v>
+        <x:v>0.667601251565552</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-88741</x:v>
+        <x:v>-161488</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>21.8297852648477</x:v>
+        <x:v>21.4891523644837</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>193978</x:v>
+        <x:v>1766787</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>21.5183871945458</x:v>
+        <x:v>21.5305383678545</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>311053</x:v>
+        <x:v>1931267</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>21.5640711729436</x:v>
+        <x:v>21.5124636100094</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>505031</x:v>
+        <x:v>3698054</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.326233886165703</x:v>
+        <x:v>1.80831361462472</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-117075</x:v>
+        <x:v>-164480</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>21.6397635646725</x:v>
+        <x:v>21.3183108425674</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>1883031</x:v>
+        <x:v>2355784</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>21.6157824343282</x:v>
+        <x:v>21.5392888299371</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>2000833</x:v>
+        <x:v>2551550</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>21.6056809250969</x:v>
+        <x:v>21.5260221981253</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>3883864</x:v>
+        <x:v>4907334</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>2.50885202306209</x:v>
+        <x:v>2.39964015769125</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-117802</x:v>
+        <x:v>-195766</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>21.4442112129578</x:v>
+        <x:v>21.3663758910243</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>480407</x:v>
+        <x:v>1745144</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>21.5665729399198</x:v>
+        <x:v>21.4925249471851</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>638461</x:v>
+        <x:v>1941216</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>21.528475122114</x:v>
+        <x:v>21.4720318202818</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>1118868</x:v>
+        <x:v>3686360</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.72275297109771</x:v>
+        <x:v>1.80259535864213</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-158054</x:v>
+        <x:v>-196072</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>21.412676354866</x:v>
+        <x:v>21.289632204546</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>1393839</x:v>
+        <x:v>6916076</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>21.5982369831965</x:v>
+        <x:v>21.5069382780323</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1599773</x:v>
+        <x:v>7161399</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>21.5722227419881</x:v>
+        <x:v>21.51473474082</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>2993612</x:v>
+        <x:v>14077475</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.93377768182999</x:v>
+        <x:v>6.88375283379828</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-205934</x:v>
+        <x:v>-245323</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>21.3961485436933</x:v>
+        <x:v>21.7345303945946</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2148860</x:v>
+        <x:v>11615175</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>21.569831241609</x:v>
+        <x:v>21.5074003632389</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2364772</x:v>
+        <x:v>12149609</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>21.5740950486189</x:v>
+        <x:v>21.5193645879411</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>4513632</x:v>
+        <x:v>23764784</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.91566202486951</x:v>
+        <x:v>11.6207557963771</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-215912</x:v>
+        <x:v>-534434</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>21.6165305053394</x:v>
+        <x:v>21.779390266799</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>5314967</x:v>
+        <x:v>5251906</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>21.5834407093252</x:v>
+        <x:v>21.5067856257209</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>5699515</x:v>
+        <x:v>5800156</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>21.571794500402</x:v>
+        <x:v>21.5173233201866</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>11014482</x:v>
+        <x:v>11052062</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>7.11500337001527</x:v>
+        <x:v>5.40435433995189</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-384548</x:v>
+        <x:v>-548250</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>21.4108283372657</x:v>
+        <x:v>21.6182681095908</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>2957305</x:v>
+        <x:v>9610326</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>21.5713895375883</x:v>
+        <x:v>21.503903265112</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>3414897</x:v>
+        <x:v>10177191</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>21.5591675947877</x:v>
+        <x:v>21.451342979721</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>6372202</x:v>
+        <x:v>19787517</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>4.1162388484922</x:v>
+        <x:v>9.67590965159459</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-457592</x:v>
+        <x:v>-566865</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>21.4801801724685</x:v>
+        <x:v>20.5602640151355</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>3909376</x:v>
+        <x:v>3568580</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>21.6081370944924</x:v>
+        <x:v>21.511588400229</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>4649975</x:v>
+        <x:v>4281748</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>21.5814985219129</x:v>
+        <x:v>21.494559393117</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>8559351</x:v>
+        <x:v>7850328</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>5.52906720535234</x:v>
+        <x:v>3.83873653593744</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-740599</x:v>
+        <x:v>-713168</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.4408823499809</x:v>
+        <x:v>21.4093489319075</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>5235638</x:v>
+        <x:v>6663753</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>21.6446212388135</x:v>
+        <x:v>21.5528177456182</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>6235392</x:v>
+        <x:v>7822975</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>21.5921596275188</x:v>
+        <x:v>21.522465665522</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>11471030</x:v>
+        <x:v>14486728</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>7.40991878760584</x:v>
+        <x:v>7.08387370053684</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-999754</x:v>
+        <x:v>-1159222</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>21.3174220364359</x:v>
+        <x:v>21.3479876407804</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/halkaarz.xlsx
+++ b/app/halka-arz/data/halkaarz.xlsx
@@ -40,166 +40,148 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
+    <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -550,7 +532,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I55"/>
+  <x:dimension ref="A1:I49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -587,28 +569,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>6967792</x:v>
+        <x:v>1644966</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>21.5008604769199</x:v>
+        <x:v>21.343</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>6212678</x:v>
+        <x:v>1074247</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>21.5508809371555</x:v>
+        <x:v>21.349</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>13180470</x:v>
+        <x:v>2719213</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>6.44512582784151</x:v>
+        <x:v>15.4879436